--- a/assets/responsabilidades.xlsx
+++ b/assets/responsabilidades.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="689">
   <si>
     <t xml:space="preserve">Use Case</t>
   </si>
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Identificar cargo do utilizador</t>
   </si>
   <si>
-    <t xml:space="preserve">método autenticar retorn null pointer se a autenticação falhar. Se a autenticação não falhar, a classe Funcionário que é devolvida é usada para determinar o cargo do funcionário e lhe conceder as suas funcionalidades correspondentes</t>
+    <t xml:space="preserve">método autenticar retorna null pointer se a autenticação falhar. Se a autenticação não falhar, a classe Funcionário que é devolvida é usada para determinar o cargo do funcionário e lhe conceder as suas funcionalidades correspondentes</t>
   </si>
   <si>
     <t xml:space="preserve">4. O sistema concede ao utilizador acesso às funcionalidades correspondentes ao seu papel.</t>
@@ -1198,7 +1198,7 @@
     <t xml:space="preserve">Atualizar stock (alterar o estado das entradas de stock para ‘PendenteDevolucao’)</t>
   </si>
   <si>
-    <t xml:space="preserve">devolverPecas(pecas: List(string))</t>
+    <t xml:space="preserve">alteraEstado_Stock_PendenteDevolucao(pecas: List(string)) : void</t>
   </si>
   <si>
     <t xml:space="preserve">11. O sistema apresenta os dados da nova devolução.</t>
@@ -1269,10 +1269,13 @@
     <t xml:space="preserve">9.1.1 O sistema verifica a transição</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1.2 O sistema adiciona a quantidade especificada ao stock da peça, sem custos adicionais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atualizar stock</t>
+    <t xml:space="preserve">9.1.2 O sistema atualiza o estado das entradas de stock devolvidas para o estado ‘Devolvida ao Fornecedor’</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atualizar stock (alterar o estado das entradas de stock para ‘Devolvida_ao_Fornecedor’)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alteraEstado_Stock_Devolvida(pecas: List(string)) : void</t>
   </si>
   <si>
     <t xml:space="preserve">9.1.3 Retorna ao passo 10</t>
@@ -1281,16 +1284,13 @@
     <t xml:space="preserve">(2) [Transição de estado de 'Pendente de Devolução' para 'Inválida para Devolução'] (Passo 9)</t>
   </si>
   <si>
-    <t xml:space="preserve">calcularCusto(pecas: List(Stock)): float</t>
-  </si>
-  <si>
     <t xml:space="preserve">9.2.1 O sistema aumenta os gastos em peças do mês atual no valor de compra da peça em questão</t>
   </si>
   <si>
-    <t xml:space="preserve">Atualizar gastos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">criarMovimentoFinanceiro(valor: float, data: DateTime, descricao: string, tipo: TipoMovimento): MovimentoFinanceiro</t>
+    <t xml:space="preserve">Atualizar gastos/Método usado para cada 1 entrada afetada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">criarMovimentoFinanceiro(valor_compra: float, data: DateTime, descricao: string, tipo: TipoMovimento): MovimentoFinanceiro</t>
   </si>
   <si>
     <t xml:space="preserve">9.2.2 Retorna ao passo 10</t>
@@ -1346,19 +1346,19 @@
     <t xml:space="preserve">Remover devolução</t>
   </si>
   <si>
-    <t xml:space="preserve">removerDevolucao(id:int)</t>
+    <t xml:space="preserve">removerDevolucao(id:int) : void</t>
   </si>
   <si>
     <t xml:space="preserve">7. O sistema aumenta os gastos em peças do mês atual no valor de compra da peça multiplicado pela quantidade especificada na devolução</t>
   </si>
   <si>
+    <t xml:space="preserve">Atualizar gastos</t>
+  </si>
+  <si>
     <t xml:space="preserve">8. O sistema apresenta uma mensagem de confirmação de eliminação bem-sucedida</t>
   </si>
   <si>
     <t xml:space="preserve">9. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a eliminação e o estado atual da devolução</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rever o que esta dentro</t>
   </si>
   <si>
     <r>
@@ -1710,25 +1710,7 @@
     <t xml:space="preserve">Validar tempo garantia</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8.2.1.5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">O sistema adiciona automaticamente ao stock as peças registadas na lista</t>
-    </r>
+    <t xml:space="preserve">8.2.1.5 O sistema adiciona automaticamente ao stock as peças registadas na lista</t>
   </si>
   <si>
     <t xml:space="preserve">adicionarPecasEncomenda(pecas : List(Stock)) : void</t>
@@ -2197,7 +2179,25 @@
     <t xml:space="preserve">Criar OS</t>
   </si>
   <si>
-    <t xml:space="preserve">registarOS(id_cliente: int, id_trotinete: int, descricao: string, acessorios: List(string), fotos: List(Fotografia)): int (ou DateTime?)</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">registarOS(id_cliente: int, id_trotinete: int, descricao: string) : OrdemServico &amp;&amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">registarOS_Extras(id_cliente: int, id_trotinete: int, descricao: string, acessorios: List(string), fotos: List(Fotografia)) : OrdemServico</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Ordens de Serviço</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">6. O sistema altera o estado da OS para Eliminada, regista data, hora e utilizador, impossibilita o uso dos dados da OS para estatí­sticas e apresenta mensagem de eliminação bem-sucedida</t>
   </si>
   <si>
-    <t xml:space="preserve">removerOS(id: int)</t>
+    <t xml:space="preserve">removerOS(id: int) : void</t>
   </si>
   <si>
     <r>
@@ -2575,7 +2575,7 @@
     <t xml:space="preserve">Validar funcionário</t>
   </si>
   <si>
-    <t xml:space="preserve">existeFuncionario(id: int): bool</t>
+    <t xml:space="preserve">existeFuncionario(id: int): boolean</t>
   </si>
   <si>
     <t xml:space="preserve">7. O sistema procura por ordens de serviço que correspondam aos filtros usados</t>
@@ -2712,6 +2712,9 @@
   </si>
   <si>
     <t xml:space="preserve">5. O sistema desconta do stock as quantidades das peças marcadas como utilizadas e regista a data, hora e utilizador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atualizar stock</t>
   </si>
   <si>
     <t xml:space="preserve">6. O funcionário não pretende adicionar reparações adicionais</t>
@@ -2893,14 +2896,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -2911,7 +2914,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2934,12 +2937,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF8000"/>
-        <bgColor rgb="FFFF6600"/>
       </patternFill>
     </fill>
     <fill>
@@ -3074,7 +3071,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="47">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3159,28 +3156,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -3195,15 +3172,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3211,19 +3196,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3243,8 +3228,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -3326,7 +3315,7 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF8000"/>
+      <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666666"/>
       <rgbColor rgb="FF969696"/>
@@ -3463,7 +3452,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5726,7 +5715,7 @@
       <c r="B203" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="C203" s="18" t="s">
+      <c r="C203" s="21" t="s">
         <v>285</v>
       </c>
       <c r="D203" s="18" t="s">
@@ -5735,7 +5724,7 @@
       <c r="E203" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="F203" s="21"/>
+      <c r="F203" s="15"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2"/>
@@ -5918,21 +5907,25 @@
       <c r="D221" s="18"/>
       <c r="E221" s="11"/>
     </row>
-    <row r="222" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2"/>
       <c r="B222" s="18" t="s">
         <v>303</v>
       </c>
-      <c r="C222" s="18" t="s">
+      <c r="C222" s="27" t="s">
         <v>304</v>
       </c>
-      <c r="D222" s="18"/>
-      <c r="E222" s="11"/>
+      <c r="D222" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="E222" s="11" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2"/>
       <c r="B223" s="18" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C223" s="18"/>
       <c r="D223" s="18"/>
@@ -5941,22 +5934,18 @@
     <row r="224" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2"/>
       <c r="B224" s="18" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C224" s="18"/>
-      <c r="D224" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="E224" s="11" t="s">
-        <v>183</v>
-      </c>
+      <c r="D224" s="18"/>
+      <c r="E224" s="11"/>
     </row>
     <row r="225" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2"/>
       <c r="B225" s="18" t="s">
         <v>308</v>
       </c>
-      <c r="C225" s="18" t="s">
+      <c r="C225" s="21" t="s">
         <v>309</v>
       </c>
       <c r="D225" s="18" t="s">
@@ -6074,7 +6063,7 @@
         <v>323</v>
       </c>
       <c r="C236" s="18" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="D236" s="18"/>
       <c r="E236" s="11"/>
@@ -6082,7 +6071,7 @@
     <row r="237" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="2"/>
       <c r="B237" s="18" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C237" s="18"/>
       <c r="D237" s="18"/>
@@ -6091,7 +6080,7 @@
     <row r="238" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2"/>
       <c r="B238" s="18" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C238" s="18" t="s">
         <v>75</v>
@@ -6104,9 +6093,7 @@
       </c>
     </row>
     <row r="239" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="22" t="s">
-        <v>326</v>
-      </c>
+      <c r="A239" s="22"/>
       <c r="B239" s="23"/>
       <c r="C239" s="23"/>
       <c r="D239" s="23"/>
@@ -6440,13 +6427,13 @@
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="27"/>
-      <c r="B270" s="28"/>
-      <c r="C270" s="28"/>
-      <c r="D270" s="28"/>
-      <c r="E270" s="29"/>
-      <c r="F270" s="21"/>
-      <c r="G270" s="30"/>
+      <c r="A270" s="2"/>
+      <c r="B270" s="18"/>
+      <c r="C270" s="18"/>
+      <c r="D270" s="18"/>
+      <c r="E270" s="11"/>
+      <c r="F270" s="15"/>
+      <c r="G270" s="1"/>
     </row>
     <row r="271" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="6"/>
@@ -6492,10 +6479,10 @@
       <c r="C275" s="18" t="s">
         <v>362</v>
       </c>
-      <c r="D275" s="31" t="s">
+      <c r="D275" s="28" t="s">
         <v>363</v>
       </c>
-      <c r="E275" s="32" t="s">
+      <c r="E275" s="29" t="s">
         <v>183</v>
       </c>
     </row>
@@ -7521,7 +7508,7 @@
       <c r="E370" s="11"/>
     </row>
     <row r="371" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="33"/>
+      <c r="A371" s="30"/>
       <c r="B371" s="19" t="s">
         <v>478</v>
       </c>
@@ -7757,23 +7744,23 @@
       </c>
     </row>
     <row r="393" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A393" s="34" t="s">
+      <c r="A393" s="31" t="s">
         <v>501</v>
       </c>
-      <c r="B393" s="35"/>
-      <c r="C393" s="35"/>
-      <c r="D393" s="35"/>
-      <c r="E393" s="36"/>
-      <c r="F393" s="37"/>
+      <c r="B393" s="32"/>
+      <c r="C393" s="32"/>
+      <c r="D393" s="32"/>
+      <c r="E393" s="33"/>
+      <c r="F393" s="34"/>
     </row>
     <row r="394" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A394" s="38"/>
-      <c r="B394" s="39" t="s">
+      <c r="A394" s="35"/>
+      <c r="B394" s="36" t="s">
         <v>502</v>
       </c>
-      <c r="C394" s="40"/>
-      <c r="D394" s="40"/>
-      <c r="E394" s="41"/>
+      <c r="C394" s="37"/>
+      <c r="D394" s="37"/>
+      <c r="E394" s="38"/>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="2" t="s">
@@ -7888,7 +7875,7 @@
       <c r="C406" s="18" t="s">
         <v>512</v>
       </c>
-      <c r="D406" s="42" t="s">
+      <c r="D406" s="23" t="s">
         <v>513</v>
       </c>
       <c r="E406" s="11" t="s">
@@ -8143,6 +8130,10 @@
       </c>
       <c r="D431" s="18"/>
       <c r="E431" s="11"/>
+      <c r="F431" s="39" t="s">
+        <v>501</v>
+      </c>
+      <c r="G431" s="40"/>
     </row>
     <row r="432" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2"/>
@@ -8166,7 +8157,9 @@
       <c r="D433" s="18" t="s">
         <v>546</v>
       </c>
-      <c r="E433" s="11"/>
+      <c r="E433" s="11" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="2"/>
@@ -8179,7 +8172,7 @@
       <c r="A435" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B435" s="42" t="s">
+      <c r="B435" s="21" t="s">
         <v>547</v>
       </c>
       <c r="C435" s="18"/>
@@ -8217,7 +8210,7 @@
     </row>
     <row r="439" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="2"/>
-      <c r="B439" s="42" t="s">
+      <c r="B439" s="21" t="s">
         <v>551</v>
       </c>
       <c r="C439" s="18"/>
@@ -8255,7 +8248,7 @@
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2"/>
-      <c r="B443" s="42" t="s">
+      <c r="B443" s="21" t="s">
         <v>555</v>
       </c>
       <c r="C443" s="18"/>
@@ -8282,7 +8275,7 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2"/>
-      <c r="B446" s="42" t="s">
+      <c r="B446" s="21" t="s">
         <v>558</v>
       </c>
       <c r="C446" s="18"/>
@@ -8333,7 +8326,7 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="2"/>
-      <c r="B451" s="42" t="s">
+      <c r="B451" s="21" t="s">
         <v>565</v>
       </c>
       <c r="C451" s="18"/>
@@ -8378,7 +8371,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2"/>
-      <c r="B456" s="42" t="s">
+      <c r="B456" s="21" t="s">
         <v>570</v>
       </c>
       <c r="C456" s="18"/>
@@ -8414,7 +8407,7 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="2"/>
-      <c r="B460" s="42" t="s">
+      <c r="B460" s="21" t="s">
         <v>574</v>
       </c>
       <c r="C460" s="18"/>
@@ -8478,7 +8471,7 @@
       <c r="D465" s="18" t="s">
         <v>583</v>
       </c>
-      <c r="E465" s="43" t="s">
+      <c r="E465" s="41" t="s">
         <v>584</v>
       </c>
     </row>
@@ -8508,25 +8501,25 @@
     </row>
     <row r="468" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2"/>
-      <c r="B468" s="42" t="s">
+      <c r="B468" s="21" t="s">
         <v>588</v>
       </c>
-      <c r="C468" s="42"/>
-      <c r="D468" s="42" t="s">
+      <c r="C468" s="21"/>
+      <c r="D468" s="21" t="s">
         <v>589</v>
       </c>
-      <c r="E468" s="43"/>
+      <c r="E468" s="41"/>
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="2"/>
-      <c r="B469" s="42" t="s">
+      <c r="B469" s="21" t="s">
         <v>590</v>
       </c>
-      <c r="C469" s="42" t="s">
+      <c r="C469" s="21" t="s">
         <v>591</v>
       </c>
-      <c r="D469" s="42"/>
-      <c r="E469" s="43"/>
+      <c r="D469" s="21"/>
+      <c r="E469" s="41"/>
     </row>
     <row r="470" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="2"/>
@@ -8861,7 +8854,7 @@
       <c r="C503" s="18" t="s">
         <v>534</v>
       </c>
-      <c r="D503" s="42" t="s">
+      <c r="D503" s="21" t="s">
         <v>627</v>
       </c>
       <c r="E503" s="11"/>
@@ -8967,14 +8960,14 @@
     </row>
     <row r="513" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2"/>
-      <c r="B513" s="42" t="s">
+      <c r="B513" s="21" t="s">
         <v>641</v>
       </c>
-      <c r="C513" s="42" t="s">
+      <c r="C513" s="21" t="s">
         <v>642</v>
       </c>
-      <c r="D513" s="42"/>
-      <c r="E513" s="43"/>
+      <c r="D513" s="21"/>
+      <c r="E513" s="41"/>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="2"/>
@@ -8997,9 +8990,9 @@
       <c r="B516" s="19" t="s">
         <v>644</v>
       </c>
-      <c r="C516" s="44"/>
-      <c r="D516" s="44"/>
-      <c r="E516" s="45"/>
+      <c r="C516" s="42"/>
+      <c r="D516" s="42"/>
+      <c r="E516" s="43"/>
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="2" t="s">
@@ -9056,7 +9049,7 @@
         <v>651</v>
       </c>
       <c r="C522" s="18" t="s">
-        <v>304</v>
+        <v>652</v>
       </c>
       <c r="D522" s="18"/>
       <c r="E522" s="11"/>
@@ -9064,7 +9057,7 @@
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="2"/>
       <c r="B523" s="18" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C523" s="18"/>
       <c r="D523" s="18"/>
@@ -9073,7 +9066,7 @@
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="2"/>
       <c r="B524" s="18" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C524" s="18"/>
       <c r="D524" s="18"/>
@@ -9082,7 +9075,7 @@
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2"/>
       <c r="B525" s="18" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C525" s="18"/>
       <c r="D525" s="18"/>
@@ -9091,7 +9084,7 @@
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2"/>
       <c r="B526" s="18" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C526" s="18"/>
       <c r="D526" s="18"/>
@@ -9100,7 +9093,7 @@
     <row r="527" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2"/>
       <c r="B527" s="18" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C527" s="18"/>
       <c r="D527" s="18"/>
@@ -9109,7 +9102,7 @@
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="2"/>
       <c r="B528" s="18" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C528" s="18"/>
       <c r="D528" s="18"/>
@@ -9118,7 +9111,7 @@
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="2"/>
       <c r="B529" s="18" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C529" s="18"/>
       <c r="D529" s="18"/>
@@ -9127,29 +9120,29 @@
     <row r="530" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="2"/>
       <c r="B530" s="18" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C530" s="18" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D530" s="18"/>
       <c r="E530" s="11"/>
     </row>
     <row r="531" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="2"/>
-      <c r="B531" s="42" t="s">
-        <v>661</v>
-      </c>
-      <c r="C531" s="42" t="s">
+      <c r="B531" s="21" t="s">
+        <v>662</v>
+      </c>
+      <c r="C531" s="21" t="s">
         <v>562</v>
       </c>
-      <c r="D531" s="42"/>
-      <c r="E531" s="43"/>
+      <c r="D531" s="21"/>
+      <c r="E531" s="41"/>
     </row>
     <row r="532" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="2"/>
       <c r="B532" s="18" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C532" s="18" t="s">
         <v>75</v>
@@ -9169,7 +9162,7 @@
         <v>246</v>
       </c>
       <c r="B534" s="18" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C534" s="18"/>
       <c r="D534" s="18"/>
@@ -9178,7 +9171,7 @@
     <row r="535" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="2"/>
       <c r="B535" s="18" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C535" s="18"/>
       <c r="D535" s="18"/>
@@ -9187,7 +9180,7 @@
     <row r="536" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="2"/>
       <c r="B536" s="18" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C536" s="18"/>
       <c r="D536" s="18"/>
@@ -9196,7 +9189,7 @@
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="2"/>
       <c r="B537" s="18" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C537" s="18"/>
       <c r="D537" s="18"/>
@@ -9205,7 +9198,7 @@
     <row r="538" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="2"/>
       <c r="B538" s="18" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C538" s="18" t="s">
         <v>562</v>
@@ -9216,7 +9209,7 @@
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="2"/>
       <c r="B539" s="18" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C539" s="18"/>
       <c r="D539" s="18"/>
@@ -9225,7 +9218,7 @@
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="2"/>
       <c r="B540" s="18" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C540" s="18"/>
       <c r="D540" s="18"/>
@@ -9234,7 +9227,7 @@
     <row r="541" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="2"/>
       <c r="B541" s="18" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C541" s="18"/>
       <c r="D541" s="18"/>
@@ -9243,7 +9236,7 @@
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="2"/>
       <c r="B542" s="18" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C542" s="18"/>
       <c r="D542" s="18"/>
@@ -9252,7 +9245,7 @@
     <row r="543" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="2"/>
       <c r="B543" s="18" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C543" s="18" t="s">
         <v>633</v>
@@ -9263,7 +9256,7 @@
     <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="2"/>
       <c r="B544" s="18" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C544" s="18"/>
       <c r="D544" s="18"/>
@@ -9272,7 +9265,7 @@
     <row r="545" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="2"/>
       <c r="B545" s="18" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C545" s="18"/>
       <c r="D545" s="18"/>
@@ -9281,7 +9274,7 @@
     <row r="546" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="2"/>
       <c r="B546" s="18" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C546" s="18"/>
       <c r="D546" s="18"/>
@@ -9290,7 +9283,7 @@
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="2"/>
       <c r="B547" s="18" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C547" s="18"/>
       <c r="D547" s="18"/>
@@ -9299,7 +9292,7 @@
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="2"/>
       <c r="B548" s="18" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C548" s="18"/>
       <c r="D548" s="18"/>
@@ -9308,7 +9301,7 @@
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="2"/>
       <c r="B549" s="18" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C549" s="18"/>
       <c r="D549" s="18"/>
@@ -9317,10 +9310,10 @@
     <row r="550" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="2"/>
       <c r="B550" s="18" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C550" s="18" t="s">
-        <v>304</v>
+        <v>652</v>
       </c>
       <c r="D550" s="18"/>
       <c r="E550" s="11"/>
@@ -9328,7 +9321,7 @@
     <row r="551" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="2"/>
       <c r="B551" s="18" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C551" s="18" t="s">
         <v>282</v>
@@ -9339,7 +9332,7 @@
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="2"/>
       <c r="B552" s="18" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C552" s="18"/>
       <c r="D552" s="18"/>
@@ -9357,7 +9350,7 @@
         <v>599</v>
       </c>
       <c r="B554" s="18" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C554" s="18"/>
       <c r="D554" s="18"/>
@@ -9366,7 +9359,7 @@
     <row r="555" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="2"/>
       <c r="B555" s="18" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C555" s="18"/>
       <c r="D555" s="18"/>
@@ -9375,7 +9368,7 @@
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="2"/>
       <c r="B556" s="18" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C556" s="18"/>
       <c r="D556" s="18"/>
@@ -9383,13 +9376,13 @@
     </row>
     <row r="557" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="2"/>
-      <c r="B557" s="42" t="s">
-        <v>685</v>
-      </c>
-      <c r="C557" s="42" t="s">
+      <c r="B557" s="21" t="s">
+        <v>686</v>
+      </c>
+      <c r="C557" s="21" t="s">
         <v>562</v>
       </c>
-      <c r="D557" s="42"/>
+      <c r="D557" s="21"/>
       <c r="E557" s="11"/>
     </row>
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9402,20 +9395,20 @@
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="2"/>
       <c r="B559" s="18" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C559" s="18"/>
       <c r="D559" s="18"/>
       <c r="E559" s="11"/>
     </row>
     <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A560" s="46"/>
-      <c r="B560" s="47" t="s">
-        <v>687</v>
-      </c>
-      <c r="C560" s="47"/>
-      <c r="D560" s="47"/>
-      <c r="E560" s="48"/>
+      <c r="A560" s="44"/>
+      <c r="B560" s="45" t="s">
+        <v>688</v>
+      </c>
+      <c r="C560" s="45"/>
+      <c r="D560" s="45"/>
+      <c r="E560" s="46"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/assets/responsabilidades.xlsx
+++ b/assets/responsabilidades.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="687">
   <si>
     <t xml:space="preserve">Use Case</t>
   </si>
@@ -179,9 +179,6 @@
     <t xml:space="preserve">validarTelemovel(telemovel: str): bool</t>
   </si>
   <si>
-    <t xml:space="preserve">algumas destas funções também seriam para usar noutros subsistemas</t>
-  </si>
-  <si>
     <t xml:space="preserve">10. O sistema valida que o email segue o formato válido de acordo com a convenção RFC 5322.</t>
   </si>
   <si>
@@ -197,7 +194,7 @@
     <t xml:space="preserve">Validar data de nascimento</t>
   </si>
   <si>
-    <t xml:space="preserve">validarData(data: str): bool</t>
+    <t xml:space="preserve">validarDataNascimento(data: string): bool</t>
   </si>
   <si>
     <t xml:space="preserve">12. O sistema valida que o NISS é composto por 11 dígitos.</t>
@@ -242,7 +239,7 @@
     <t xml:space="preserve">Validar valor por hora</t>
   </si>
   <si>
-    <t xml:space="preserve">validarValorHora(salario_hora: float): bool</t>
+    <t xml:space="preserve">validarSalarioHora(salario_hora: float): bool</t>
   </si>
   <si>
     <t xml:space="preserve">17. O sistema valida que o valor mensal bruto é um número real positivo com 2 casas decimais.</t>
@@ -260,7 +257,7 @@
     <t xml:space="preserve">Validar salário liquido</t>
   </si>
   <si>
-    <t xml:space="preserve">validarLiquido(salario_liquido: float): bool</t>
+    <t xml:space="preserve">validarSalarioLiquido(salario_liquido: float): bool</t>
   </si>
   <si>
     <t xml:space="preserve">19. O sistema valida que a palavra-passe é um campo textual não vazio.</t>
@@ -502,13 +499,10 @@
     <t xml:space="preserve">Atualizar horas e recalcular salário</t>
   </si>
   <si>
-    <t xml:space="preserve">registarHorasExtra(id:int, horas_extra: int): float</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como são registadas e onde guardar o valor a pagar ao funcionario nesse mês</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Falta Fazer</t>
+    <t xml:space="preserve">adicionarHorasExtra(id:int, horas_extra: int): float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para saber o novo salario pode-se fazer salario liquido + horas extras * salario por hora</t>
   </si>
   <si>
     <t xml:space="preserve">9. O sistema apresenta uma confirmação do registo com o valor total atualizado.</t>
@@ -1195,10 +1189,13 @@
     <t xml:space="preserve">10. O sistema diminui a quantidade em stock da peça consoante a quantidade especificada na devolução.</t>
   </si>
   <si>
-    <t xml:space="preserve">Atualizar stock (alterar o estado das entradas de stock para ‘PendenteDevolucao’)</t>
+    <t xml:space="preserve">Atualizar stock</t>
   </si>
   <si>
     <t xml:space="preserve">alteraEstado_Stock_PendenteDevolucao(pecas: List(string)) : void</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (alterar o estado das entradas de stock para ‘PendenteDevolucao’)</t>
   </si>
   <si>
     <t xml:space="preserve">11. O sistema apresenta os dados da nova devolução.</t>
@@ -1272,12 +1269,12 @@
     <t xml:space="preserve">9.1.2 O sistema atualiza o estado das entradas de stock devolvidas para o estado ‘Devolvida ao Fornecedor’</t>
   </si>
   <si>
-    <t xml:space="preserve">Atualizar stock (alterar o estado das entradas de stock para ‘Devolvida_ao_Fornecedor’)</t>
-  </si>
-  <si>
     <t xml:space="preserve">alteraEstado_Stock_Devolvida(pecas: List(string)) : void</t>
   </si>
   <si>
+    <t xml:space="preserve">(alterar o estado das entradas de stock para ‘Devolvida_ao_Fornecedor’)</t>
+  </si>
+  <si>
     <t xml:space="preserve">9.1.3 Retorna ao passo 10</t>
   </si>
   <si>
@@ -1287,10 +1284,13 @@
     <t xml:space="preserve">9.2.1 O sistema aumenta os gastos em peças do mês atual no valor de compra da peça em questão</t>
   </si>
   <si>
-    <t xml:space="preserve">Atualizar gastos/Método usado para cada 1 entrada afetada</t>
+    <t xml:space="preserve">Atualizar gastos</t>
   </si>
   <si>
     <t xml:space="preserve">criarMovimentoFinanceiro(valor_compra: float, data: DateTime, descricao: string, tipo: TipoMovimento): MovimentoFinanceiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Método usado para cada 1 entrada afetada</t>
   </si>
   <si>
     <t xml:space="preserve">9.2.2 Retorna ao passo 10</t>
@@ -1352,9 +1352,6 @@
     <t xml:space="preserve">7. O sistema aumenta os gastos em peças do mês atual no valor de compra da peça multiplicado pela quantidade especificada na devolução</t>
   </si>
   <si>
-    <t xml:space="preserve">Atualizar gastos</t>
-  </si>
-  <si>
     <t xml:space="preserve">8. O sistema apresenta uma mensagem de confirmação de eliminação bem-sucedida</t>
   </si>
   <si>
@@ -1638,7 +1635,7 @@
     <t xml:space="preserve">Validar estado rascunho</t>
   </si>
   <si>
-    <t xml:space="preserve">validaEncomenda_Rascunho(id: int): bool</t>
+    <t xml:space="preserve">validaEncomenda_Rascunho(id_Encomenda: int): bool</t>
   </si>
   <si>
     <t xml:space="preserve">5. O funcionário adiciona ou remove peças da lista</t>
@@ -1990,9 +1987,6 @@
     <t xml:space="preserve">9. O sistema valida que o número de série é um campo textual não vazio</t>
   </si>
   <si>
-    <t xml:space="preserve">validarNrSerie(nr_serie: string): bool</t>
-  </si>
-  <si>
     <t xml:space="preserve">10. O sistema valida que o tipo de motor é um tipo de motor válido</t>
   </si>
   <si>
@@ -2123,9 +2117,6 @@
     <t xml:space="preserve">removerTrotinete(id: int) : void</t>
   </si>
   <si>
-    <t xml:space="preserve">Fiquei aqui</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -2179,25 +2170,7 @@
     <t xml:space="preserve">Criar OS</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">registarOS(id_cliente: int, id_trotinete: int, descricao: string) : OrdemServico &amp;&amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">registarOS_Extras(id_cliente: int, id_trotinete: int, descricao: string, acessorios: List(string), fotos: List(Fotografia)) : OrdemServico</t>
-    </r>
+    <t xml:space="preserve">registarOS(id_cliente: int, id_trotinete: int, descricao: string) : OrdemServico &amp;&amp; registarOS_Extras(id_cliente: int, id_trotinete: int, descricao: string, acessorios: List(string), fotos: List(Fotografia)) : OrdemServico</t>
   </si>
   <si>
     <t xml:space="preserve">Ordens de Serviço</t>
@@ -2227,7 +2200,7 @@
     <t xml:space="preserve">Validar acessórios</t>
   </si>
   <si>
-    <t xml:space="preserve">validarAcessorio(acessorio: stirng): bool</t>
+    <t xml:space="preserve">validarAcessorio(acessorio: string): bool</t>
   </si>
   <si>
     <t xml:space="preserve">7.3 Retorna ao passo 9</t>
@@ -2316,7 +2289,7 @@
     <t xml:space="preserve">Atualizar OS</t>
   </si>
   <si>
-    <t xml:space="preserve">alterarOS(id: int, descricao: string, acessorios: List(string), fotos: List(Fotografia))</t>
+    <t xml:space="preserve">alterarDescricaoOS(id : int, descricao : string) : void &amp;&amp; alterarAcessoriosOS(id : int, acessorios : List(string)) : void &amp;&amp; alterarFotografiasOS(id : int, fotos : List(Fotografia)) : void</t>
   </si>
   <si>
     <t xml:space="preserve">(1) [O funcionário pretende adicionar ou editar acessórios] (Passo 6)</t>
@@ -2367,7 +2340,7 @@
     <t xml:space="preserve">Atualizar estado OS</t>
   </si>
   <si>
-    <t xml:space="preserve">alterarEstadoOS(id: int, estado: EstadoOS)</t>
+    <t xml:space="preserve">alterarEstadoOS(id: int, estado: EstadoOS) : void</t>
   </si>
   <si>
     <t xml:space="preserve">4.1.4 Retorna ao passo 10</t>
@@ -2394,6 +2367,9 @@
     <t xml:space="preserve">4.2.1.1 O funcionário regista a notificação de término</t>
   </si>
   <si>
+    <t xml:space="preserve">acho que não temos nada no sistema sobre Notificações (?)</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.2.1.2 O funcionário confirma a notificação de término</t>
   </si>
   <si>
@@ -2406,16 +2382,31 @@
     <t xml:space="preserve">4.2.2.1 O funcionário introduz o identificador Único ou a referência do fornecedor da peça que pretende associar</t>
   </si>
   <si>
-    <t xml:space="preserve">pecaEmStock(referencia: string): bool</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.2.2.2 O sistema valida a existência da peça em stock</t>
   </si>
   <si>
     <t xml:space="preserve">Validar se peça está em stock</t>
   </si>
   <si>
-    <t xml:space="preserve">pecaEmStock(id: int): bool</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">obter_quantidade_Stock_Peca_id(id: int): int &amp;&amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">obter_quantidade_Stock_Peca_ref(referencia: string): int</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">4.2.2.3 O funcionário seleciona a peça e especifica a quantidade utilizada</t>
@@ -2427,25 +2418,16 @@
     <t xml:space="preserve">4.2.2.5 O sistema valida que a quantidade é um número inteiro positivo e não excede o stock</t>
   </si>
   <si>
-    <t xml:space="preserve">obterPecaStock(id: int, quantidade: int): List(Stock)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">este método pode devolver uma lista vazia se não houver peças suficiente em stock</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.2.2.6 O sistema associa as peças à OS, regista data, hora e utilizador e atualiza o valor total da OS</t>
   </si>
   <si>
-    <t xml:space="preserve">adicionarPecasReparacaoOS(List(Stock))</t>
+    <t xml:space="preserve">adicionarPecas_Conserto_OS(id:int, pecas : List(Stock)) : void</t>
   </si>
   <si>
     <t xml:space="preserve">4.2.2.7 Retorna ao passo 4.2.3</t>
   </si>
   <si>
     <t xml:space="preserve">(8) [O funcionário regista o pagamento] (Passo 4.2.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acho que não temos nada no sistema sobre Notificações (?)</t>
   </si>
   <si>
     <t xml:space="preserve">4.2.3.1 O sistema valida que o cliente foi previamente notificado</t>
@@ -2619,7 +2601,13 @@
     <t xml:space="preserve">2. O funcionário consulta os dados completos da OS, incluindo os dados da trotinete, do cliente e o histórico de reparações anteriores da trotinete</t>
   </si>
   <si>
-    <t xml:space="preserve">Cliente e Trotinete estão associados à OS, pode-se criar o método obterReparacoesAnteriores(id_trotinete: int): List(Reparacao)</t>
+    <t xml:space="preserve">obterConsertosAnteriores(id_trotinete: int): List(Conserto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clientes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os outros métodos necessários para fazer esta ação já existem</t>
   </si>
   <si>
     <t xml:space="preserve">3. O funcionário adiciona e remove as reparações necessárias da tabela de reparações, pesquisando por identificador ou nomenclatura</t>
@@ -2631,25 +2619,19 @@
     <t xml:space="preserve">5. O funcionário confirma o diagnóstico</t>
   </si>
   <si>
-    <t xml:space="preserve">emStock(referencia: string, quantidade: int): bool</t>
-  </si>
-  <si>
     <t xml:space="preserve">6. O sistema valida que as quantidades são números inteiros positivos e não excedem o stock disponí­vel</t>
   </si>
   <si>
     <t xml:space="preserve">Validar quantidades</t>
   </si>
   <si>
-    <t xml:space="preserve">emStock(id_peca: int, quantidade: int): bool</t>
-  </si>
-  <si>
     <t xml:space="preserve">7. O sistema calcula o valor do orçamento e valida que é inferior a 50€</t>
   </si>
   <si>
     <t xml:space="preserve">Validar limite orçamento</t>
   </si>
   <si>
-    <t xml:space="preserve">calcularOrcamento(pecas: List(Stock)): float</t>
+    <t xml:space="preserve">calcularOrcamento(pecas: List(Stock), reparacoes : List(Reparacao)): float</t>
   </si>
   <si>
     <t xml:space="preserve">8. O sistema altera o estado da OS para 'Pendente Reparação'</t>
@@ -2714,7 +2696,7 @@
     <t xml:space="preserve">5. O sistema desconta do stock as quantidades das peças marcadas como utilizadas e regista a data, hora e utilizador</t>
   </si>
   <si>
-    <t xml:space="preserve">Atualizar stock</t>
+    <t xml:space="preserve">Pensar bem</t>
   </si>
   <si>
     <t xml:space="preserve">6. O funcionário não pretende adicionar reparações adicionais</t>
@@ -2747,10 +2729,13 @@
     <t xml:space="preserve">14. O sistema calcula o custo final da reparação, altera o estado da OS para 'Pendente Pagamento', gera um alerta para a secretária, regista a data, hora e funcionário que realizou a reparação e apresenta um resumo final da OS</t>
   </si>
   <si>
+    <t xml:space="preserve">Atualizar estado OS/Gerar alerta</t>
+  </si>
+  <si>
     <t xml:space="preserve">15. O sistema regista a data e a hora seguindo o formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a reparação</t>
   </si>
   <si>
-    <t xml:space="preserve">(1) [Uma peça prescrita no diagnóstico não está¡ disponí­vel em stock] (Passo 2)</t>
+    <t xml:space="preserve">(1) [Uma peça prescrita no diagnóstico não está disponí­vel em stock] (Passo 2)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1 O sistema informa o funcionário que a quantidade solicitada da peça prescrita não está¡ disponí­vel em stock</t>
@@ -2801,7 +2786,16 @@
     <t xml:space="preserve">8.5 O sistema valida que existem peças iguais na mesma quantidade disponí­veis em stock e adiciona-as às lista de peças usadas e remove as peças defeituosas da lista de peças utilizadas</t>
   </si>
   <si>
+    <t xml:space="preserve">removerPecaConserto_OS(id_OS:int, id_Stock:int) : void</t>
+  </si>
+  <si>
     <t xml:space="preserve">8.6 O sistema cria um registo de devolução marcando as peças defeituosas como 'Possí­vel defeito', repõe ao stock a quantidade correspondente e gera um alerta para o gestor de stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criar devolução/Marcar entrada de stock como defeituosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">registar_Defeito_entradaStock(id_Stock:int) : void</t>
   </si>
   <si>
     <t xml:space="preserve">8.7 Retorna ao passo 9</t>
@@ -2832,7 +2826,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2902,6 +2896,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -2941,8 +2941,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF666666"/>
-        <bgColor rgb="FF808080"/>
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFC9211E"/>
       </patternFill>
     </fill>
   </fills>
@@ -3071,7 +3071,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3140,6 +3140,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3156,39 +3168,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3196,19 +3188,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3228,23 +3212,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3317,7 +3309,7 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666666"/>
+      <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
@@ -3668,7 +3660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="10" t="s">
         <v>36</v>
@@ -3682,20 +3674,18 @@
       <c r="E19" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="16" t="s">
-        <v>39</v>
-      </c>
+      <c r="F19" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="D20" s="12" t="s">
         <v>41</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>42</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>10</v>
@@ -3704,13 +3694,13 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="D21" s="12" t="s">
         <v>44</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>10</v>
@@ -3719,13 +3709,13 @@
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="D22" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>48</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>10</v>
@@ -3734,13 +3724,13 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="D23" s="12" t="s">
         <v>50</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>51</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>10</v>
@@ -3749,13 +3739,13 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="D24" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>54</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>10</v>
@@ -3764,13 +3754,13 @@
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="D25" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>57</v>
       </c>
       <c r="E25" s="12" t="s">
         <v>10</v>
@@ -3779,13 +3769,13 @@
     <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="D26" s="12" t="s">
         <v>59</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>60</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>10</v>
@@ -3794,13 +3784,13 @@
     <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="D27" s="12" t="s">
         <v>62</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>63</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>10</v>
@@ -3809,13 +3799,13 @@
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
       <c r="B28" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="D28" s="12" t="s">
         <v>65</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>66</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>10</v>
@@ -3824,13 +3814,13 @@
     <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
       <c r="B29" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="D29" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>69</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>10</v>
@@ -3839,13 +3829,13 @@
     <row r="30" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="D30" s="12" t="s">
         <v>71</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>72</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>10</v>
@@ -3854,7 +3844,7 @@
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
       <c r="B31" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="12"/>
@@ -3863,13 +3853,13 @@
     <row r="32" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
       <c r="B32" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="D32" s="12" t="s">
         <v>75</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>76</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>10</v>
@@ -3885,7 +3875,7 @@
     <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
       <c r="B34" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="9"/>
@@ -3903,7 +3893,7 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
       <c r="B36" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="12"/>
@@ -3912,13 +3902,13 @@
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
       <c r="B37" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="D37" s="12" t="s">
         <v>80</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>81</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>10</v>
@@ -3927,7 +3917,7 @@
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
       <c r="B38" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="12"/>
@@ -3936,7 +3926,7 @@
     <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
       <c r="B39" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="12"/>
@@ -3945,7 +3935,7 @@
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
       <c r="B40" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="12"/>
@@ -3954,7 +3944,7 @@
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
       <c r="B41" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>21</v>
@@ -3965,7 +3955,7 @@
     <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
       <c r="B42" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>25</v>
@@ -3976,7 +3966,7 @@
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>28</v>
@@ -3987,7 +3977,7 @@
     <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
       <c r="B44" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>31</v>
@@ -3998,7 +3988,7 @@
     <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
       <c r="B45" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>34</v>
@@ -4009,7 +3999,7 @@
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
       <c r="B46" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>37</v>
@@ -4020,10 +4010,10 @@
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
       <c r="B47" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="12"/>
@@ -4031,10 +4021,10 @@
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
       <c r="B48" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="12"/>
@@ -4042,10 +4032,10 @@
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
       <c r="B49" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="12"/>
@@ -4053,10 +4043,10 @@
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
       <c r="B50" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="12"/>
@@ -4064,10 +4054,10 @@
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
       <c r="B51" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="12"/>
@@ -4075,10 +4065,10 @@
     <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
       <c r="B52" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="12"/>
@@ -4086,10 +4076,10 @@
     <row r="53" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
       <c r="B53" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="12"/>
@@ -4097,10 +4087,10 @@
     <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
       <c r="B54" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="12"/>
@@ -4108,10 +4098,10 @@
     <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
       <c r="B55" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D55" s="12"/>
       <c r="E55" s="12"/>
@@ -4119,10 +4109,10 @@
     <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
       <c r="B56" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="12"/>
@@ -4130,13 +4120,13 @@
     <row r="57" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
       <c r="B57" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C57" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D57" s="12" t="s">
         <v>75</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>76</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>10</v>
@@ -4145,13 +4135,13 @@
     <row r="58" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
       <c r="B58" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C58" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="D58" s="12" t="s">
         <v>103</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>104</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>10</v>
@@ -4167,7 +4157,7 @@
     <row r="60" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6"/>
       <c r="B60" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="9"/>
@@ -4185,7 +4175,7 @@
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
       <c r="B62" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="12"/>
@@ -4194,10 +4184,10 @@
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
       <c r="B63" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D63" s="12"/>
       <c r="E63" s="12"/>
@@ -4205,7 +4195,7 @@
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
       <c r="B64" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C64" s="11"/>
       <c r="D64" s="12"/>
@@ -4214,7 +4204,7 @@
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
       <c r="B65" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="12"/>
@@ -4223,10 +4213,10 @@
     <row r="66" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
       <c r="B66" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="12"/>
@@ -4234,13 +4224,13 @@
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
       <c r="B67" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C67" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="D67" s="12" t="s">
         <v>112</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>113</v>
       </c>
       <c r="E67" s="12" t="s">
         <v>10</v>
@@ -4249,7 +4239,7 @@
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
       <c r="B68" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="12"/>
@@ -4265,7 +4255,7 @@
     <row r="70" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6"/>
       <c r="B70" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="9"/>
@@ -4283,7 +4273,7 @@
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
       <c r="B72" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="12"/>
@@ -4292,10 +4282,10 @@
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
       <c r="B73" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C73" s="11" t="s">
         <v>79</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>80</v>
       </c>
       <c r="D73" s="12"/>
       <c r="E73" s="12"/>
@@ -4303,7 +4293,7 @@
     <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
       <c r="B74" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="12"/>
@@ -4312,7 +4302,7 @@
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
       <c r="B75" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C75" s="11"/>
       <c r="D75" s="12"/>
@@ -4321,13 +4311,13 @@
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
       <c r="B76" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C76" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="D76" s="12" t="s">
         <v>119</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>120</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>10</v>
@@ -4336,7 +4326,7 @@
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
       <c r="B77" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C77" s="11"/>
       <c r="D77" s="12"/>
@@ -4345,43 +4335,41 @@
     <row r="78" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
       <c r="B78" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C78" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D78" s="12" t="s">
         <v>75</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>76</v>
       </c>
       <c r="E78" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
       <c r="B79" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C79" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="D79" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>125</v>
       </c>
       <c r="E79" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F79" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G79" s="15" t="s">
-        <v>127</v>
-      </c>
+      <c r="F79" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="G79" s="15"/>
     </row>
     <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
       <c r="B80" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="12"/>
@@ -4397,7 +4385,7 @@
     <row r="82" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6"/>
       <c r="B82" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C82" s="8"/>
       <c r="D82" s="9"/>
@@ -4415,7 +4403,7 @@
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
       <c r="B84" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="12"/>
@@ -4424,7 +4412,7 @@
     <row r="85" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
       <c r="B85" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C85" s="11"/>
       <c r="D85" s="12"/>
@@ -4433,7 +4421,7 @@
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
       <c r="B86" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="12"/>
@@ -4442,16 +4430,16 @@
     <row r="87" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
       <c r="B87" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D87" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="E87" s="12" t="s">
         <v>134</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4464,7 +4452,7 @@
     <row r="89" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6"/>
       <c r="B89" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C89" s="8"/>
       <c r="D89" s="9"/>
@@ -4482,7 +4470,7 @@
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
       <c r="B91" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C91" s="11"/>
       <c r="D91" s="12"/>
@@ -4491,7 +4479,7 @@
     <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
       <c r="B92" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C92" s="11"/>
       <c r="D92" s="12"/>
@@ -4509,76 +4497,76 @@
     <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
       <c r="B94" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D94" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="E94" s="12" t="s">
         <v>141</v>
-      </c>
-      <c r="D94" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="E94" s="12" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
       <c r="B95" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D95" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="C95" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>146</v>
-      </c>
       <c r="E95" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
       <c r="B96" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D96" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="C96" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="D96" s="12" t="s">
-        <v>149</v>
-      </c>
       <c r="E96" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
       <c r="B97" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D97" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="C97" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>152</v>
-      </c>
       <c r="E97" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
       <c r="B98" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C98" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D98" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D98" s="12" t="s">
-        <v>76</v>
-      </c>
       <c r="E98" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4591,7 +4579,7 @@
     <row r="100" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="6"/>
       <c r="B100" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C100" s="8"/>
       <c r="D100" s="9"/>
@@ -4609,7 +4597,7 @@
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
       <c r="B102" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="12"/>
@@ -4618,22 +4606,22 @@
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
       <c r="B103" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D103" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C103" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="D103" s="12" t="s">
-        <v>158</v>
-      </c>
       <c r="E103" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
       <c r="B104" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="12"/>
@@ -4642,7 +4630,7 @@
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2"/>
       <c r="B105" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C105" s="11"/>
       <c r="D105" s="12"/>
@@ -4651,7 +4639,7 @@
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2"/>
       <c r="B106" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="12"/>
@@ -4660,10 +4648,10 @@
     <row r="107" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2"/>
       <c r="B107" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D107" s="12"/>
       <c r="E107" s="12"/>
@@ -4671,10 +4659,10 @@
     <row r="108" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2"/>
       <c r="B108" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D108" s="12"/>
       <c r="E108" s="12"/>
@@ -4682,10 +4670,10 @@
     <row r="109" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2"/>
       <c r="B109" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D109" s="12"/>
       <c r="E109" s="12"/>
@@ -4693,31 +4681,31 @@
     <row r="110" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2"/>
       <c r="B110" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C110" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D110" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D110" s="12" t="s">
-        <v>76</v>
-      </c>
       <c r="E110" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2"/>
       <c r="B111" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D111" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="C111" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="D111" s="12" t="s">
-        <v>167</v>
-      </c>
       <c r="E111" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4730,7 +4718,7 @@
     <row r="113" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6"/>
       <c r="B113" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C113" s="8"/>
       <c r="D113" s="9"/>
@@ -4748,7 +4736,7 @@
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2"/>
       <c r="B115" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C115" s="11"/>
       <c r="D115" s="12"/>
@@ -4757,22 +4745,22 @@
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2"/>
       <c r="B116" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2"/>
       <c r="B117" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C117" s="11"/>
       <c r="D117" s="12"/>
@@ -4781,7 +4769,7 @@
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2"/>
       <c r="B118" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="12"/>
@@ -4790,22 +4778,22 @@
     <row r="119" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2"/>
       <c r="B119" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C119" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D119" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D119" s="12" t="s">
-        <v>76</v>
-      </c>
       <c r="E119" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2"/>
       <c r="B120" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C120" s="11"/>
       <c r="D120" s="12"/>
@@ -4814,16 +4802,16 @@
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2"/>
       <c r="B121" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C121" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D121" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C121" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="D121" s="12" t="s">
-        <v>176</v>
-      </c>
       <c r="E121" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4836,7 +4824,7 @@
     <row r="123" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="6"/>
       <c r="B123" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C123" s="8"/>
       <c r="D123" s="9"/>
@@ -4854,7 +4842,7 @@
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2"/>
       <c r="B125" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C125" s="11"/>
       <c r="D125" s="12"/>
@@ -4863,7 +4851,7 @@
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2"/>
       <c r="B126" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C126" s="11"/>
       <c r="D126" s="12"/>
@@ -4872,22 +4860,22 @@
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2"/>
       <c r="B127" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C127" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D127" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="C127" s="11" t="s">
+      <c r="E127" s="12" t="s">
         <v>181</v>
-      </c>
-      <c r="D127" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="E127" s="12" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2"/>
       <c r="B128" s="10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C128" s="11"/>
       <c r="D128" s="12"/>
@@ -4896,7 +4884,7 @@
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2"/>
       <c r="B129" s="10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C129" s="11"/>
       <c r="D129" s="12"/>
@@ -4905,67 +4893,67 @@
     <row r="130" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2"/>
       <c r="B130" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C130" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D130" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="C130" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D130" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="E130" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2"/>
       <c r="B131" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D131" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="C131" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="D131" s="12" t="s">
-        <v>191</v>
-      </c>
       <c r="E131" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2"/>
       <c r="B132" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="D132" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="C132" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="D132" s="12" t="s">
-        <v>194</v>
-      </c>
       <c r="E132" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2"/>
       <c r="B133" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C133" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="D133" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="C133" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="D133" s="12" t="s">
-        <v>197</v>
-      </c>
       <c r="E133" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2"/>
       <c r="B134" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C134" s="11"/>
       <c r="D134" s="12"/>
@@ -4974,16 +4962,16 @@
     <row r="135" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2"/>
       <c r="B135" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C135" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D135" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D135" s="12" t="s">
-        <v>76</v>
-      </c>
       <c r="E135" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4996,7 +4984,7 @@
     <row r="137" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="6"/>
       <c r="B137" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C137" s="8"/>
       <c r="D137" s="9"/>
@@ -5014,7 +5002,7 @@
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2"/>
       <c r="B139" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C139" s="11"/>
       <c r="D139" s="12"/>
@@ -5023,22 +5011,22 @@
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2"/>
       <c r="B140" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C140" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D140" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="C140" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="D140" s="12" t="s">
-        <v>204</v>
-      </c>
       <c r="E140" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2"/>
       <c r="B141" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C141" s="11"/>
       <c r="D141" s="12"/>
@@ -5047,7 +5035,7 @@
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2"/>
       <c r="B142" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C142" s="11"/>
       <c r="D142" s="12"/>
@@ -5056,7 +5044,7 @@
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2"/>
       <c r="B143" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C143" s="11"/>
       <c r="D143" s="12"/>
@@ -5065,10 +5053,10 @@
     <row r="144" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2"/>
       <c r="B144" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D144" s="12"/>
       <c r="E144" s="12"/>
@@ -5076,10 +5064,10 @@
     <row r="145" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2"/>
       <c r="B145" s="10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D145" s="12"/>
       <c r="E145" s="12"/>
@@ -5087,10 +5075,10 @@
     <row r="146" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2"/>
       <c r="B146" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D146" s="12"/>
       <c r="E146" s="12"/>
@@ -5098,31 +5086,31 @@
     <row r="147" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2"/>
       <c r="B147" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C147" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D147" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D147" s="12" t="s">
-        <v>76</v>
-      </c>
       <c r="E147" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2"/>
       <c r="B148" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C148" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="D148" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="C148" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="D148" s="12" t="s">
-        <v>214</v>
-      </c>
       <c r="E148" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5135,7 +5123,7 @@
     <row r="150" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="6"/>
       <c r="B150" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C150" s="8"/>
       <c r="D150" s="9"/>
@@ -5153,22 +5141,22 @@
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2"/>
       <c r="B152" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D152" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2"/>
       <c r="B153" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C153" s="11"/>
       <c r="D153" s="12"/>
@@ -5177,7 +5165,7 @@
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2"/>
       <c r="B154" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C154" s="11"/>
       <c r="D154" s="12"/>
@@ -5186,7 +5174,7 @@
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2"/>
       <c r="B155" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C155" s="11"/>
       <c r="D155" s="12"/>
@@ -5195,31 +5183,31 @@
     <row r="156" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2"/>
       <c r="B156" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C156" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D156" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D156" s="12" t="s">
-        <v>76</v>
-      </c>
       <c r="E156" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2"/>
       <c r="B157" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="C157" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D157" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="C157" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="D157" s="12" t="s">
-        <v>223</v>
-      </c>
       <c r="E157" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5234,7 +5222,7 @@
     <row r="159" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="6"/>
       <c r="B159" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C159" s="8"/>
       <c r="D159" s="9"/>
@@ -5252,7 +5240,7 @@
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2"/>
       <c r="B161" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C161" s="11"/>
       <c r="D161" s="12"/>
@@ -5261,7 +5249,7 @@
     <row r="162" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2"/>
       <c r="B162" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C162" s="11"/>
       <c r="D162" s="12"/>
@@ -5270,22 +5258,22 @@
     <row r="163" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2"/>
       <c r="B163" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="C163" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D163" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="C163" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="D163" s="12" t="s">
-        <v>229</v>
-      </c>
       <c r="E163" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2"/>
       <c r="B164" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C164" s="11"/>
       <c r="D164" s="12"/>
@@ -5294,7 +5282,7 @@
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2"/>
       <c r="B165" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C165" s="11"/>
       <c r="D165" s="12"/>
@@ -5303,40 +5291,40 @@
     <row r="166" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2"/>
       <c r="B166" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C166" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D166" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="C166" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="D166" s="12" t="s">
-        <v>234</v>
-      </c>
       <c r="E166" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2"/>
       <c r="B167" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="C167" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D167" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="C167" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="D167" s="12" t="s">
-        <v>237</v>
-      </c>
       <c r="E167" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2"/>
       <c r="B168" s="10" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D168" s="12"/>
       <c r="E168" s="12"/>
@@ -5344,10 +5332,10 @@
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2"/>
       <c r="B169" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D169" s="12"/>
       <c r="E169" s="12"/>
@@ -5355,31 +5343,31 @@
     <row r="170" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2"/>
       <c r="B170" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C170" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="D170" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C170" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="D170" s="12" t="s">
-        <v>244</v>
-      </c>
       <c r="E170" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2"/>
       <c r="B171" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C171" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D171" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D171" s="12" t="s">
-        <v>76</v>
-      </c>
       <c r="E171" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5391,10 +5379,10 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C173" s="11"/>
       <c r="D173" s="12"/>
@@ -5403,7 +5391,7 @@
     <row r="174" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2"/>
       <c r="B174" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C174" s="11"/>
       <c r="D174" s="12"/>
@@ -5412,7 +5400,7 @@
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2"/>
       <c r="B175" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C175" s="11"/>
       <c r="D175" s="12"/>
@@ -5421,37 +5409,37 @@
     <row r="176" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2"/>
       <c r="B176" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="C176" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D176" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="C176" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="D176" s="12" t="s">
-        <v>252</v>
-      </c>
       <c r="E176" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2"/>
       <c r="B177" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="C177" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="D177" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="C177" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="D177" s="12" t="s">
-        <v>255</v>
-      </c>
       <c r="E177" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2"/>
       <c r="B178" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C178" s="11"/>
       <c r="D178" s="12"/>
@@ -5467,7 +5455,7 @@
     <row r="180" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="6"/>
       <c r="B180" s="7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C180" s="8"/>
       <c r="D180" s="9"/>
@@ -5478,14 +5466,14 @@
         <v>5</v>
       </c>
       <c r="B181" s="10"/>
-      <c r="C181" s="17"/>
+      <c r="C181" s="20"/>
       <c r="D181" s="12"/>
       <c r="E181" s="12"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2"/>
       <c r="B182" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C182" s="11"/>
       <c r="D182" s="12"/>
@@ -5494,22 +5482,22 @@
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2"/>
       <c r="B183" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D183" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E183" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2"/>
       <c r="B184" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C184" s="11"/>
       <c r="D184" s="12"/>
@@ -5518,7 +5506,7 @@
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2"/>
       <c r="B185" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C185" s="11"/>
       <c r="D185" s="12"/>
@@ -5527,7 +5515,7 @@
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2"/>
       <c r="B186" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C186" s="11"/>
       <c r="D186" s="12"/>
@@ -5536,10 +5524,10 @@
     <row r="187" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2"/>
       <c r="B187" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D187" s="12"/>
       <c r="E187" s="12"/>
@@ -5547,10 +5535,10 @@
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="2"/>
       <c r="B188" s="10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D188" s="12"/>
       <c r="E188" s="12"/>
@@ -5558,10 +5546,10 @@
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2"/>
       <c r="B189" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D189" s="12"/>
       <c r="E189" s="12"/>
@@ -5569,3220 +5557,3216 @@
     <row r="190" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2"/>
       <c r="B190" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="C190" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="D190" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="C190" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="D190" s="12" t="s">
-        <v>267</v>
-      </c>
       <c r="E190" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2"/>
-      <c r="B191" s="18"/>
-      <c r="C191" s="18"/>
+      <c r="B191" s="21"/>
+      <c r="C191" s="21"/>
       <c r="D191" s="12"/>
       <c r="E191" s="12"/>
     </row>
     <row r="192" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="6"/>
-      <c r="B192" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="C192" s="20"/>
-      <c r="D192" s="20"/>
+      <c r="B192" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="C192" s="23"/>
+      <c r="D192" s="23"/>
       <c r="E192" s="8"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B193" s="18"/>
-      <c r="C193" s="18"/>
-      <c r="D193" s="18"/>
+      <c r="B193" s="21"/>
+      <c r="C193" s="21"/>
+      <c r="D193" s="21"/>
       <c r="E193" s="11"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2"/>
-      <c r="B194" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="C194" s="18"/>
-      <c r="D194" s="18"/>
+      <c r="B194" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="C194" s="21"/>
+      <c r="D194" s="21"/>
       <c r="E194" s="11"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2"/>
-      <c r="B195" s="18" t="s">
-        <v>270</v>
-      </c>
-      <c r="C195" s="18"/>
-      <c r="D195" s="18"/>
+      <c r="B195" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="C195" s="21"/>
+      <c r="D195" s="21"/>
       <c r="E195" s="11"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2"/>
-      <c r="B196" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="C196" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="D196" s="18"/>
+      <c r="B196" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="C196" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="D196" s="21"/>
       <c r="E196" s="11"/>
     </row>
     <row r="197" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2"/>
-      <c r="B197" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="C197" s="18"/>
-      <c r="D197" s="18"/>
+      <c r="B197" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="C197" s="21"/>
+      <c r="D197" s="21"/>
       <c r="E197" s="11"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2"/>
-      <c r="B198" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="C198" s="18"/>
-      <c r="D198" s="18"/>
+      <c r="B198" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C198" s="21"/>
+      <c r="D198" s="21"/>
       <c r="E198" s="11"/>
     </row>
     <row r="199" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2"/>
-      <c r="B199" s="18" t="s">
+      <c r="B199" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="C199" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="D199" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="C199" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="D199" s="18" t="s">
-        <v>276</v>
-      </c>
       <c r="E199" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F199" s="15"/>
     </row>
     <row r="200" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2"/>
-      <c r="B200" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="C200" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="D200" s="18"/>
+      <c r="B200" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C200" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D200" s="21"/>
       <c r="E200" s="11"/>
     </row>
     <row r="201" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2"/>
-      <c r="B201" s="18" t="s">
+      <c r="B201" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C201" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="D201" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="C201" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="D201" s="18" t="s">
-        <v>280</v>
-      </c>
       <c r="E201" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2"/>
-      <c r="B202" s="18" t="s">
+      <c r="B202" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="C202" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="D202" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="C202" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="D202" s="18" t="s">
-        <v>283</v>
-      </c>
       <c r="E202" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2"/>
-      <c r="B203" s="18" t="s">
+      <c r="B203" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="C203" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="D203" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="C203" s="21" t="s">
+      <c r="E203" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="F203" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="D203" s="18" t="s">
-        <v>286</v>
-      </c>
-      <c r="E203" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="F203" s="15"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2"/>
-      <c r="B204" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="C204" s="18"/>
-      <c r="D204" s="18"/>
+      <c r="B204" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="C204" s="21"/>
+      <c r="D204" s="21"/>
       <c r="E204" s="11"/>
     </row>
     <row r="205" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2"/>
-      <c r="B205" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="C205" s="18" t="s">
+      <c r="B205" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="C205" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D205" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D205" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="E205" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="22"/>
-      <c r="B206" s="23"/>
-      <c r="C206" s="23"/>
-      <c r="D206" s="23"/>
-      <c r="E206" s="24"/>
-      <c r="F206" s="25"/>
-      <c r="G206" s="26"/>
-      <c r="H206" s="26"/>
-      <c r="I206" s="26"/>
-      <c r="J206" s="26"/>
+      <c r="A206" s="2"/>
+      <c r="B206" s="21"/>
+      <c r="C206" s="21"/>
+      <c r="D206" s="21"/>
+      <c r="E206" s="11"/>
+      <c r="F206" s="15"/>
+      <c r="G206" s="1"/>
+      <c r="H206" s="1"/>
+      <c r="I206" s="1"/>
+      <c r="J206" s="1"/>
     </row>
     <row r="207" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="6"/>
-      <c r="B207" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="C207" s="20"/>
-      <c r="D207" s="20"/>
+      <c r="B207" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="C207" s="23"/>
+      <c r="D207" s="23"/>
       <c r="E207" s="8"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B208" s="18"/>
-      <c r="C208" s="18"/>
-      <c r="D208" s="18"/>
+      <c r="B208" s="21"/>
+      <c r="C208" s="21"/>
+      <c r="D208" s="21"/>
       <c r="E208" s="11"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2"/>
-      <c r="B209" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="C209" s="18"/>
-      <c r="D209" s="18"/>
+      <c r="B209" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="C209" s="21"/>
+      <c r="D209" s="21"/>
       <c r="E209" s="11"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2"/>
-      <c r="B210" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="C210" s="18"/>
-      <c r="D210" s="18"/>
+      <c r="B210" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="C210" s="21"/>
+      <c r="D210" s="21"/>
       <c r="E210" s="11"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2"/>
-      <c r="B211" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="C211" s="18"/>
-      <c r="D211" s="18"/>
+      <c r="B211" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="C211" s="21"/>
+      <c r="D211" s="21"/>
       <c r="E211" s="11"/>
     </row>
     <row r="212" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2"/>
-      <c r="B212" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="C212" s="18"/>
-      <c r="D212" s="18"/>
+      <c r="B212" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C212" s="21"/>
+      <c r="D212" s="21"/>
       <c r="E212" s="11"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2"/>
-      <c r="B213" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="C213" s="18"/>
-      <c r="D213" s="18"/>
+      <c r="B213" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="C213" s="21"/>
+      <c r="D213" s="21"/>
       <c r="E213" s="11"/>
     </row>
     <row r="214" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2"/>
-      <c r="B214" s="18" t="s">
+      <c r="B214" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="C214" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="C214" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="D214" s="18"/>
+      <c r="D214" s="21"/>
       <c r="E214" s="11"/>
     </row>
     <row r="215" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2"/>
-      <c r="B215" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="C215" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="D215" s="18"/>
+      <c r="B215" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="C215" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D215" s="21"/>
       <c r="E215" s="11"/>
     </row>
     <row r="216" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2"/>
-      <c r="B216" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C216" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="D216" s="18"/>
+      <c r="B216" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="C216" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="D216" s="21"/>
       <c r="E216" s="11"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2"/>
-      <c r="B217" s="18" t="s">
+      <c r="B217" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="C217" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="C217" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="D217" s="18"/>
+      <c r="D217" s="21"/>
       <c r="E217" s="11"/>
     </row>
     <row r="218" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2"/>
-      <c r="B218" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="C218" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D218" s="18"/>
+      <c r="B218" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="C218" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D218" s="21"/>
       <c r="E218" s="11"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2"/>
-      <c r="B219" s="18"/>
-      <c r="C219" s="18"/>
-      <c r="D219" s="18"/>
+      <c r="B219" s="21"/>
+      <c r="C219" s="21"/>
+      <c r="D219" s="21"/>
       <c r="E219" s="11"/>
     </row>
     <row r="220" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B220" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="C220" s="18"/>
-      <c r="D220" s="18"/>
+        <v>244</v>
+      </c>
+      <c r="B220" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C220" s="21"/>
+      <c r="D220" s="21"/>
       <c r="E220" s="11"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2"/>
-      <c r="B221" s="18" t="s">
+      <c r="B221" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="C221" s="21"/>
+      <c r="D221" s="21"/>
+      <c r="E221" s="11"/>
+    </row>
+    <row r="222" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="2"/>
+      <c r="B222" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="C221" s="18"/>
-      <c r="D221" s="18"/>
-      <c r="E221" s="11"/>
-    </row>
-    <row r="222" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="2"/>
-      <c r="B222" s="18" t="s">
+      <c r="C222" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="D222" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="C222" s="27" t="s">
+      <c r="E222" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="F222" s="19" t="s">
         <v>304</v>
-      </c>
-      <c r="D222" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="E222" s="11" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2"/>
-      <c r="B223" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="C223" s="18"/>
-      <c r="D223" s="18"/>
+      <c r="B223" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="C223" s="21"/>
+      <c r="D223" s="21"/>
       <c r="E223" s="11"/>
     </row>
     <row r="224" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2"/>
-      <c r="B224" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="C224" s="18"/>
-      <c r="D224" s="18"/>
+      <c r="B224" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="C224" s="21"/>
+      <c r="D224" s="21"/>
       <c r="E224" s="11"/>
     </row>
     <row r="225" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2"/>
-      <c r="B225" s="18" t="s">
+      <c r="B225" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="C225" s="24" t="s">
         <v>308</v>
       </c>
-      <c r="C225" s="21" t="s">
+      <c r="D225" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="D225" s="18" t="s">
+      <c r="E225" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F225" s="19" t="s">
         <v>310</v>
-      </c>
-      <c r="E225" s="11" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2"/>
-      <c r="B226" s="18" t="s">
+      <c r="B226" s="21" t="s">
         <v>311</v>
       </c>
-      <c r="C226" s="18"/>
-      <c r="D226" s="18"/>
+      <c r="C226" s="21"/>
+      <c r="D226" s="21"/>
       <c r="E226" s="11"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2"/>
-      <c r="B227" s="18"/>
-      <c r="C227" s="18"/>
-      <c r="D227" s="18"/>
+      <c r="B227" s="21"/>
+      <c r="C227" s="21"/>
+      <c r="D227" s="21"/>
       <c r="E227" s="11"/>
     </row>
     <row r="228" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="6"/>
-      <c r="B228" s="19" t="s">
+      <c r="B228" s="22" t="s">
         <v>312</v>
       </c>
-      <c r="C228" s="20"/>
-      <c r="D228" s="20"/>
+      <c r="C228" s="23"/>
+      <c r="D228" s="23"/>
       <c r="E228" s="8"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B229" s="18"/>
-      <c r="C229" s="18"/>
-      <c r="D229" s="18"/>
+      <c r="B229" s="21"/>
+      <c r="C229" s="21"/>
+      <c r="D229" s="21"/>
       <c r="E229" s="11"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2"/>
-      <c r="B230" s="18" t="s">
+      <c r="B230" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="C230" s="18"/>
-      <c r="D230" s="18"/>
+      <c r="C230" s="21"/>
+      <c r="D230" s="21"/>
       <c r="E230" s="11"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2"/>
-      <c r="B231" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="C231" s="18" t="s">
+      <c r="B231" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="C231" s="21" t="s">
         <v>314</v>
       </c>
-      <c r="D231" s="18" t="s">
+      <c r="D231" s="21" t="s">
         <v>315</v>
       </c>
       <c r="E231" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="2"/>
-      <c r="B232" s="18" t="s">
+      <c r="B232" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="C232" s="18"/>
-      <c r="D232" s="18"/>
+      <c r="C232" s="21"/>
+      <c r="D232" s="21"/>
       <c r="E232" s="11"/>
     </row>
     <row r="233" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2"/>
-      <c r="B233" s="18" t="s">
+      <c r="B233" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="C233" s="18" t="s">
+      <c r="C233" s="21" t="s">
         <v>318</v>
       </c>
-      <c r="D233" s="18"/>
+      <c r="D233" s="21"/>
       <c r="E233" s="11"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2"/>
-      <c r="B234" s="18" t="s">
+      <c r="B234" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="C234" s="18"/>
-      <c r="D234" s="18"/>
+      <c r="C234" s="21"/>
+      <c r="D234" s="21"/>
       <c r="E234" s="11"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2"/>
-      <c r="B235" s="18" t="s">
+      <c r="B235" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="C235" s="18" t="s">
+      <c r="C235" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="D235" s="18" t="s">
+      <c r="D235" s="21" t="s">
         <v>322</v>
       </c>
       <c r="E235" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2"/>
-      <c r="B236" s="18" t="s">
+      <c r="B236" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="C236" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="D236" s="18"/>
+      <c r="C236" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="D236" s="21"/>
       <c r="E236" s="11"/>
     </row>
     <row r="237" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="2"/>
-      <c r="B237" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="C237" s="18"/>
-      <c r="D237" s="18"/>
+      <c r="B237" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="C237" s="21"/>
+      <c r="D237" s="21"/>
       <c r="E237" s="11"/>
     </row>
     <row r="238" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2"/>
-      <c r="B238" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="C238" s="18" t="s">
+      <c r="B238" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="C238" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D238" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D238" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="E238" s="11" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="239" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="22"/>
-      <c r="B239" s="23"/>
-      <c r="C239" s="23"/>
-      <c r="D239" s="23"/>
-      <c r="E239" s="24"/>
-      <c r="F239" s="26"/>
-      <c r="G239" s="26"/>
-      <c r="H239" s="26"/>
-      <c r="I239" s="26"/>
-      <c r="J239" s="26"/>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="2"/>
+      <c r="B239" s="21"/>
+      <c r="C239" s="21"/>
+      <c r="D239" s="21"/>
+      <c r="E239" s="11"/>
+      <c r="G239" s="1"/>
+      <c r="H239" s="1"/>
+      <c r="I239" s="1"/>
+      <c r="J239" s="1"/>
     </row>
     <row r="240" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="6"/>
-      <c r="B240" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="C240" s="20"/>
-      <c r="D240" s="20"/>
+      <c r="B240" s="22" t="s">
+        <v>326</v>
+      </c>
+      <c r="C240" s="23"/>
+      <c r="D240" s="23"/>
       <c r="E240" s="8"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B241" s="18"/>
-      <c r="C241" s="18"/>
-      <c r="D241" s="18"/>
+      <c r="B241" s="21"/>
+      <c r="C241" s="21"/>
+      <c r="D241" s="21"/>
       <c r="E241" s="11"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2"/>
-      <c r="B242" s="18" t="s">
-        <v>328</v>
-      </c>
-      <c r="C242" s="18"/>
-      <c r="D242" s="18"/>
+      <c r="B242" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="C242" s="21"/>
+      <c r="D242" s="21"/>
       <c r="E242" s="11"/>
     </row>
     <row r="243" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2"/>
-      <c r="B243" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="C243" s="18"/>
-      <c r="D243" s="18"/>
+      <c r="B243" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="C243" s="21"/>
+      <c r="D243" s="21"/>
       <c r="E243" s="11"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2"/>
-      <c r="B244" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="C244" s="18"/>
-      <c r="D244" s="18"/>
+      <c r="B244" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="C244" s="21"/>
+      <c r="D244" s="21"/>
       <c r="E244" s="11"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2"/>
-      <c r="B245" s="18" t="s">
+      <c r="B245" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C245" s="18" t="s">
+      <c r="C245" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D245" s="18"/>
+      <c r="D245" s="21"/>
       <c r="E245" s="11"/>
     </row>
     <row r="246" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="2"/>
-      <c r="B246" s="18" t="s">
+      <c r="B246" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="C246" s="21" t="s">
         <v>331</v>
       </c>
-      <c r="C246" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="D246" s="18"/>
+      <c r="D246" s="21"/>
       <c r="E246" s="11"/>
     </row>
     <row r="247" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="2"/>
-      <c r="B247" s="18" t="s">
+      <c r="B247" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="C247" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="C247" s="18" t="s">
+      <c r="D247" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="D247" s="18" t="s">
-        <v>335</v>
-      </c>
       <c r="E247" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2"/>
-      <c r="B248" s="18" t="s">
-        <v>336</v>
-      </c>
-      <c r="C248" s="18" t="s">
+      <c r="B248" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="C248" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D248" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D248" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="E248" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2"/>
-      <c r="B249" s="18"/>
-      <c r="C249" s="18"/>
-      <c r="D249" s="18"/>
+      <c r="B249" s="21"/>
+      <c r="C249" s="21"/>
+      <c r="D249" s="21"/>
       <c r="E249" s="11"/>
     </row>
     <row r="250" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="6"/>
-      <c r="B250" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="C250" s="20"/>
-      <c r="D250" s="20"/>
+      <c r="B250" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="C250" s="23"/>
+      <c r="D250" s="23"/>
       <c r="E250" s="8"/>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B251" s="18"/>
-      <c r="C251" s="18"/>
-      <c r="D251" s="18"/>
+      <c r="B251" s="21"/>
+      <c r="C251" s="21"/>
+      <c r="D251" s="21"/>
       <c r="E251" s="11"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2"/>
-      <c r="B252" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="C252" s="18"/>
-      <c r="D252" s="18"/>
+      <c r="B252" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="C252" s="21"/>
+      <c r="D252" s="21"/>
       <c r="E252" s="11"/>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2"/>
-      <c r="B253" s="18" t="s">
+      <c r="B253" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="C253" s="21" t="s">
         <v>339</v>
       </c>
-      <c r="C253" s="18" t="s">
+      <c r="D253" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="D253" s="18" t="s">
-        <v>341</v>
-      </c>
       <c r="E253" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="2"/>
-      <c r="B254" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="C254" s="18"/>
-      <c r="D254" s="18"/>
+      <c r="B254" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="C254" s="21"/>
+      <c r="D254" s="21"/>
       <c r="E254" s="11"/>
     </row>
     <row r="255" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="2"/>
-      <c r="B255" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="C255" s="18"/>
-      <c r="D255" s="18"/>
+      <c r="B255" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C255" s="21"/>
+      <c r="D255" s="21"/>
       <c r="E255" s="11"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="2"/>
-      <c r="B256" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="C256" s="18"/>
-      <c r="D256" s="18"/>
+      <c r="B256" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="C256" s="21"/>
+      <c r="D256" s="21"/>
       <c r="E256" s="11"/>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="2"/>
-      <c r="B257" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="C257" s="18" t="s">
+      <c r="B257" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="C257" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D257" s="18"/>
+      <c r="D257" s="21"/>
       <c r="E257" s="11"/>
     </row>
     <row r="258" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="2"/>
-      <c r="B258" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="C258" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="D258" s="18"/>
+      <c r="B258" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="C258" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="D258" s="21"/>
       <c r="E258" s="11"/>
     </row>
     <row r="259" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2"/>
-      <c r="B259" s="18" t="s">
-        <v>345</v>
-      </c>
-      <c r="C259" s="18" t="s">
+      <c r="B259" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="C259" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D259" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D259" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="E259" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="2"/>
-      <c r="B260" s="18" t="s">
+      <c r="B260" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="C260" s="21" t="s">
         <v>346</v>
       </c>
-      <c r="C260" s="18" t="s">
+      <c r="D260" s="21" t="s">
         <v>347</v>
       </c>
-      <c r="D260" s="18" t="s">
-        <v>348</v>
-      </c>
       <c r="E260" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="2"/>
-      <c r="B261" s="18"/>
-      <c r="C261" s="18"/>
-      <c r="D261" s="18"/>
+      <c r="B261" s="21"/>
+      <c r="C261" s="21"/>
+      <c r="D261" s="21"/>
       <c r="E261" s="11"/>
     </row>
     <row r="262" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="6"/>
-      <c r="B262" s="19" t="s">
-        <v>349</v>
-      </c>
-      <c r="C262" s="20"/>
-      <c r="D262" s="20"/>
+      <c r="B262" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="C262" s="23"/>
+      <c r="D262" s="23"/>
       <c r="E262" s="8"/>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B263" s="18"/>
-      <c r="C263" s="18"/>
-      <c r="D263" s="18"/>
+      <c r="B263" s="21"/>
+      <c r="C263" s="21"/>
+      <c r="D263" s="21"/>
       <c r="E263" s="11"/>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="2"/>
-      <c r="B264" s="18" t="s">
-        <v>350</v>
-      </c>
-      <c r="C264" s="18"/>
-      <c r="D264" s="18"/>
+      <c r="B264" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="C264" s="21"/>
+      <c r="D264" s="21"/>
       <c r="E264" s="11"/>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="2"/>
-      <c r="B265" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="C265" s="18" t="s">
+      <c r="B265" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C265" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="D265" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="D265" s="18" t="s">
-        <v>341</v>
-      </c>
       <c r="E265" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="2"/>
-      <c r="B266" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="C266" s="18"/>
-      <c r="D266" s="18"/>
+      <c r="B266" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="C266" s="21"/>
+      <c r="D266" s="21"/>
       <c r="E266" s="11"/>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2"/>
-      <c r="B267" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="C267" s="18"/>
-      <c r="D267" s="18"/>
+      <c r="B267" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C267" s="21"/>
+      <c r="D267" s="21"/>
       <c r="E267" s="11"/>
     </row>
     <row r="268" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="2"/>
-      <c r="B268" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="C268" s="18" t="s">
+      <c r="B268" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C268" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D268" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D268" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="E268" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="2"/>
-      <c r="B269" s="18" t="s">
+      <c r="B269" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="C269" s="21" t="s">
         <v>355</v>
       </c>
-      <c r="C269" s="18" t="s">
+      <c r="D269" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="D269" s="18" t="s">
-        <v>357</v>
-      </c>
       <c r="E269" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="2"/>
-      <c r="B270" s="18"/>
-      <c r="C270" s="18"/>
-      <c r="D270" s="18"/>
+      <c r="B270" s="21"/>
+      <c r="C270" s="21"/>
+      <c r="D270" s="21"/>
       <c r="E270" s="11"/>
       <c r="F270" s="15"/>
       <c r="G270" s="1"/>
     </row>
     <row r="271" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="6"/>
-      <c r="B271" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="C271" s="20"/>
-      <c r="D271" s="20"/>
+      <c r="B271" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="C271" s="23"/>
+      <c r="D271" s="23"/>
       <c r="E271" s="8"/>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B272" s="18"/>
-      <c r="C272" s="18"/>
-      <c r="D272" s="18"/>
+      <c r="B272" s="21"/>
+      <c r="C272" s="21"/>
+      <c r="D272" s="21"/>
       <c r="E272" s="11"/>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="2"/>
-      <c r="B273" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="C273" s="18"/>
-      <c r="D273" s="18"/>
+      <c r="B273" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="C273" s="21"/>
+      <c r="D273" s="21"/>
       <c r="E273" s="11"/>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="2"/>
-      <c r="B274" s="18" t="s">
-        <v>360</v>
-      </c>
-      <c r="C274" s="18"/>
-      <c r="D274" s="18"/>
+      <c r="B274" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="C274" s="21"/>
+      <c r="D274" s="21"/>
       <c r="E274" s="11"/>
     </row>
     <row r="275" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="2"/>
-      <c r="B275" s="18" t="s">
+      <c r="B275" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="C275" s="21" t="s">
         <v>361</v>
       </c>
-      <c r="C275" s="18" t="s">
+      <c r="D275" s="26" t="s">
         <v>362</v>
       </c>
-      <c r="D275" s="28" t="s">
-        <v>363</v>
-      </c>
-      <c r="E275" s="29" t="s">
-        <v>183</v>
+      <c r="E275" s="27" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="2"/>
-      <c r="B276" s="18" t="s">
+      <c r="B276" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="C276" s="21" t="s">
         <v>364</v>
       </c>
-      <c r="C276" s="18" t="s">
+      <c r="D276" s="21" t="s">
         <v>365</v>
       </c>
-      <c r="D276" s="18" t="s">
-        <v>366</v>
-      </c>
       <c r="E276" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="2"/>
-      <c r="B277" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="C277" s="18"/>
-      <c r="D277" s="18"/>
+      <c r="B277" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="C277" s="21"/>
+      <c r="D277" s="21"/>
       <c r="E277" s="11"/>
     </row>
     <row r="278" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="2"/>
-      <c r="B278" s="18" t="s">
-        <v>368</v>
-      </c>
-      <c r="C278" s="18"/>
-      <c r="D278" s="18"/>
+      <c r="B278" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="C278" s="21"/>
+      <c r="D278" s="21"/>
       <c r="E278" s="11"/>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="2"/>
-      <c r="B279" s="18" t="s">
-        <v>369</v>
-      </c>
-      <c r="C279" s="18"/>
-      <c r="D279" s="18"/>
+      <c r="B279" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C279" s="21"/>
+      <c r="D279" s="21"/>
       <c r="E279" s="11"/>
     </row>
     <row r="280" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="2"/>
-      <c r="B280" s="18" t="s">
-        <v>370</v>
-      </c>
-      <c r="C280" s="18"/>
-      <c r="D280" s="18"/>
+      <c r="B280" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="C280" s="21"/>
+      <c r="D280" s="21"/>
       <c r="E280" s="11"/>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="2"/>
-      <c r="B281" s="18" t="s">
-        <v>371</v>
-      </c>
-      <c r="C281" s="18"/>
-      <c r="D281" s="18"/>
+      <c r="B281" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="C281" s="21"/>
+      <c r="D281" s="21"/>
       <c r="E281" s="11"/>
     </row>
     <row r="282" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="2"/>
-      <c r="B282" s="18" t="s">
+      <c r="B282" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="C282" s="21" t="s">
         <v>372</v>
       </c>
-      <c r="C282" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D282" s="18"/>
+      <c r="D282" s="21"/>
       <c r="E282" s="11"/>
     </row>
     <row r="283" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="2"/>
-      <c r="B283" s="18" t="s">
+      <c r="B283" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="C283" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="C283" s="18" t="s">
+      <c r="D283" s="21" t="s">
         <v>375</v>
       </c>
-      <c r="D283" s="18" t="s">
-        <v>376</v>
-      </c>
       <c r="E283" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="2"/>
-      <c r="B284" s="18" t="s">
-        <v>377</v>
-      </c>
-      <c r="C284" s="18" t="s">
+      <c r="B284" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C284" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D284" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D284" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="E284" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="2"/>
-      <c r="B285" s="18"/>
-      <c r="C285" s="18"/>
-      <c r="D285" s="18"/>
+      <c r="B285" s="21"/>
+      <c r="C285" s="21"/>
+      <c r="D285" s="21"/>
       <c r="E285" s="11"/>
     </row>
     <row r="286" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="6"/>
-      <c r="B286" s="19" t="s">
-        <v>378</v>
-      </c>
-      <c r="C286" s="20"/>
-      <c r="D286" s="20"/>
+      <c r="B286" s="22" t="s">
+        <v>377</v>
+      </c>
+      <c r="C286" s="23"/>
+      <c r="D286" s="23"/>
       <c r="E286" s="8"/>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B287" s="18"/>
-      <c r="C287" s="18"/>
-      <c r="D287" s="18"/>
+      <c r="B287" s="21"/>
+      <c r="C287" s="21"/>
+      <c r="D287" s="21"/>
       <c r="E287" s="11"/>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="2"/>
-      <c r="B288" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="C288" s="18"/>
-      <c r="D288" s="18"/>
+      <c r="B288" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="C288" s="21"/>
+      <c r="D288" s="21"/>
       <c r="E288" s="11"/>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="2"/>
-      <c r="B289" s="18" t="s">
+      <c r="B289" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="C289" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="C289" s="18" t="s">
+      <c r="D289" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="D289" s="18" t="s">
-        <v>382</v>
-      </c>
       <c r="E289" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="2"/>
-      <c r="B290" s="18" t="s">
+      <c r="B290" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="C290" s="21"/>
+      <c r="D290" s="21"/>
+      <c r="E290" s="11"/>
+    </row>
+    <row r="291" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="2"/>
+      <c r="B291" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="C290" s="18"/>
-      <c r="D290" s="18"/>
-      <c r="E290" s="11"/>
-    </row>
-    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="2"/>
-      <c r="B291" s="18" t="s">
+      <c r="C291" s="21" t="s">
         <v>384</v>
       </c>
-      <c r="C291" s="18" t="s">
+      <c r="D291" s="21" t="s">
         <v>385</v>
       </c>
-      <c r="D291" s="18" t="s">
-        <v>386</v>
-      </c>
       <c r="E291" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2"/>
-      <c r="B292" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="C292" s="18"/>
-      <c r="D292" s="18"/>
+      <c r="B292" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="C292" s="21"/>
+      <c r="D292" s="21"/>
       <c r="E292" s="11"/>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="2"/>
-      <c r="B293" s="18" t="s">
-        <v>388</v>
-      </c>
-      <c r="C293" s="18"/>
-      <c r="D293" s="18"/>
+      <c r="B293" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="C293" s="21"/>
+      <c r="D293" s="21"/>
       <c r="E293" s="11"/>
     </row>
     <row r="294" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="2"/>
-      <c r="B294" s="18" t="s">
-        <v>389</v>
-      </c>
-      <c r="C294" s="18" t="s">
+      <c r="B294" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="C294" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D294" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D294" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="E294" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="2"/>
-      <c r="B295" s="18" t="s">
-        <v>390</v>
-      </c>
-      <c r="C295" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="D295" s="18"/>
+      <c r="B295" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="C295" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="D295" s="21"/>
       <c r="E295" s="11"/>
     </row>
     <row r="296" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="2"/>
-      <c r="B296" s="18" t="s">
+      <c r="B296" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="C296" s="21" t="s">
         <v>391</v>
       </c>
-      <c r="C296" s="18" t="s">
+      <c r="D296" s="21" t="s">
         <v>392</v>
       </c>
-      <c r="D296" s="18" t="s">
-        <v>393</v>
-      </c>
       <c r="E296" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="2"/>
-      <c r="B297" s="18"/>
-      <c r="C297" s="18"/>
-      <c r="D297" s="18"/>
+      <c r="B297" s="21"/>
+      <c r="C297" s="21"/>
+      <c r="D297" s="21"/>
       <c r="E297" s="11"/>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B298" s="18" t="s">
-        <v>394</v>
-      </c>
-      <c r="C298" s="18"/>
-      <c r="D298" s="18"/>
+        <v>244</v>
+      </c>
+      <c r="B298" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="C298" s="21"/>
+      <c r="D298" s="21"/>
       <c r="E298" s="11"/>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="2"/>
-      <c r="B299" s="18" t="s">
-        <v>395</v>
-      </c>
-      <c r="C299" s="18"/>
-      <c r="D299" s="18"/>
+      <c r="B299" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="C299" s="21"/>
+      <c r="D299" s="21"/>
       <c r="E299" s="11"/>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="2"/>
-      <c r="B300" s="18" t="s">
-        <v>396</v>
-      </c>
-      <c r="C300" s="18"/>
-      <c r="D300" s="18"/>
+      <c r="B300" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="C300" s="21"/>
+      <c r="D300" s="21"/>
       <c r="E300" s="11"/>
     </row>
     <row r="301" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="2"/>
-      <c r="B301" s="18" t="s">
+      <c r="B301" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="C301" s="21" t="s">
         <v>397</v>
       </c>
-      <c r="C301" s="18" t="s">
-        <v>398</v>
-      </c>
-      <c r="D301" s="18"/>
+      <c r="D301" s="21"/>
       <c r="E301" s="11"/>
     </row>
     <row r="302" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="2"/>
-      <c r="B302" s="18" t="s">
+      <c r="B302" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="C302" s="21" t="s">
         <v>399</v>
       </c>
-      <c r="C302" s="18" t="s">
+      <c r="D302" s="21" t="s">
         <v>400</v>
       </c>
-      <c r="D302" s="18" t="s">
-        <v>401</v>
-      </c>
       <c r="E302" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="2"/>
-      <c r="B303" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="C303" s="18"/>
-      <c r="D303" s="18"/>
+      <c r="B303" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="C303" s="21"/>
+      <c r="D303" s="21"/>
       <c r="E303" s="11"/>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="2"/>
-      <c r="B304" s="18" t="s">
-        <v>403</v>
-      </c>
-      <c r="C304" s="18"/>
-      <c r="D304" s="18"/>
+      <c r="B304" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="C304" s="21"/>
+      <c r="D304" s="21"/>
       <c r="E304" s="11"/>
     </row>
     <row r="305" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="2"/>
-      <c r="B305" s="18" t="s">
-        <v>404</v>
-      </c>
-      <c r="C305" s="18"/>
-      <c r="D305" s="18"/>
+      <c r="B305" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="C305" s="21"/>
+      <c r="D305" s="21"/>
       <c r="E305" s="11"/>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="2"/>
-      <c r="B306" s="18" t="s">
-        <v>405</v>
-      </c>
-      <c r="C306" s="18"/>
-      <c r="D306" s="18"/>
+      <c r="B306" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="C306" s="21"/>
+      <c r="D306" s="21"/>
       <c r="E306" s="11"/>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="2"/>
-      <c r="B307" s="18" t="s">
+      <c r="B307" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="C307" s="21" t="s">
         <v>406</v>
       </c>
-      <c r="C307" s="18" t="s">
-        <v>407</v>
-      </c>
-      <c r="D307" s="18"/>
+      <c r="D307" s="21"/>
       <c r="E307" s="11"/>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="2"/>
-      <c r="B308" s="18" t="s">
+      <c r="B308" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="C308" s="21" t="s">
         <v>408</v>
       </c>
-      <c r="C308" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="D308" s="18"/>
+      <c r="D308" s="21"/>
       <c r="E308" s="11"/>
     </row>
     <row r="309" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="2"/>
-      <c r="B309" s="18" t="s">
+      <c r="B309" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="C309" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="D309" s="21" t="s">
         <v>410</v>
       </c>
-      <c r="C309" s="18" t="s">
-        <v>400</v>
-      </c>
-      <c r="D309" s="18" t="s">
-        <v>411</v>
-      </c>
       <c r="E309" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="2"/>
-      <c r="B310" s="18" t="s">
-        <v>412</v>
-      </c>
-      <c r="C310" s="18"/>
-      <c r="D310" s="18"/>
+      <c r="B310" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="C310" s="21"/>
+      <c r="D310" s="21"/>
       <c r="E310" s="11"/>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="2"/>
-      <c r="B311" s="18"/>
-      <c r="C311" s="18"/>
-      <c r="D311" s="18"/>
+      <c r="B311" s="21"/>
+      <c r="C311" s="21"/>
+      <c r="D311" s="21"/>
       <c r="E311" s="11"/>
     </row>
     <row r="312" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="6"/>
-      <c r="B312" s="19" t="s">
-        <v>413</v>
-      </c>
-      <c r="C312" s="20"/>
-      <c r="D312" s="20"/>
+      <c r="B312" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="C312" s="23"/>
+      <c r="D312" s="23"/>
       <c r="E312" s="8"/>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B313" s="17"/>
-      <c r="C313" s="18"/>
-      <c r="D313" s="18"/>
+      <c r="B313" s="20"/>
+      <c r="C313" s="21"/>
+      <c r="D313" s="21"/>
       <c r="E313" s="11"/>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="2"/>
-      <c r="B314" s="18" t="s">
-        <v>414</v>
-      </c>
-      <c r="C314" s="18"/>
-      <c r="D314" s="18"/>
+      <c r="B314" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="C314" s="21"/>
+      <c r="D314" s="21"/>
       <c r="E314" s="11"/>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="2"/>
-      <c r="B315" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="C315" s="18"/>
-      <c r="D315" s="18"/>
+      <c r="B315" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="C315" s="21"/>
+      <c r="D315" s="21"/>
       <c r="E315" s="11"/>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="2"/>
-      <c r="B316" s="18" t="s">
-        <v>416</v>
-      </c>
-      <c r="C316" s="18"/>
-      <c r="D316" s="18"/>
+      <c r="B316" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="C316" s="21"/>
+      <c r="D316" s="21"/>
       <c r="E316" s="11"/>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="2"/>
-      <c r="B317" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="C317" s="18"/>
-      <c r="D317" s="18"/>
+      <c r="B317" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C317" s="21"/>
+      <c r="D317" s="21"/>
       <c r="E317" s="11"/>
     </row>
     <row r="318" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="2"/>
-      <c r="B318" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="C318" s="18" t="s">
+      <c r="B318" s="21" t="s">
+        <v>416</v>
+      </c>
+      <c r="C318" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D318" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D318" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="E318" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="2"/>
-      <c r="B319" s="18" t="s">
+      <c r="B319" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="C319" s="21" t="s">
         <v>418</v>
       </c>
-      <c r="C319" s="18" t="s">
+      <c r="D319" s="21" t="s">
         <v>419</v>
       </c>
-      <c r="D319" s="18" t="s">
-        <v>420</v>
-      </c>
       <c r="E319" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="2"/>
-      <c r="B320" s="17"/>
-      <c r="C320" s="18"/>
-      <c r="D320" s="18"/>
+      <c r="B320" s="20"/>
+      <c r="C320" s="21"/>
+      <c r="D320" s="21"/>
       <c r="E320" s="11"/>
     </row>
     <row r="321" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="6"/>
-      <c r="B321" s="19" t="s">
-        <v>421</v>
-      </c>
-      <c r="C321" s="20"/>
-      <c r="D321" s="20"/>
+      <c r="B321" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="C321" s="23"/>
+      <c r="D321" s="23"/>
       <c r="E321" s="8"/>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B322" s="17"/>
-      <c r="C322" s="18"/>
-      <c r="D322" s="18"/>
+      <c r="B322" s="20"/>
+      <c r="C322" s="21"/>
+      <c r="D322" s="21"/>
       <c r="E322" s="11"/>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="2"/>
-      <c r="B323" s="18" t="s">
-        <v>422</v>
-      </c>
-      <c r="C323" s="18"/>
-      <c r="D323" s="18"/>
+      <c r="B323" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="C323" s="21"/>
+      <c r="D323" s="21"/>
       <c r="E323" s="11"/>
     </row>
     <row r="324" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="2"/>
-      <c r="B324" s="18" t="s">
-        <v>423</v>
-      </c>
-      <c r="C324" s="18"/>
-      <c r="D324" s="18"/>
+      <c r="B324" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="C324" s="21"/>
+      <c r="D324" s="21"/>
       <c r="E324" s="11"/>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="2"/>
-      <c r="B325" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="C325" s="18"/>
-      <c r="D325" s="18"/>
+      <c r="B325" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="C325" s="21"/>
+      <c r="D325" s="21"/>
       <c r="E325" s="11"/>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="2"/>
-      <c r="B326" s="18" t="s">
+      <c r="B326" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C326" s="18" t="s">
+      <c r="C326" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D326" s="18"/>
+      <c r="D326" s="21"/>
       <c r="E326" s="11"/>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="2"/>
-      <c r="B327" s="18" t="s">
-        <v>424</v>
-      </c>
-      <c r="C327" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D327" s="18"/>
+      <c r="B327" s="21" t="s">
+        <v>423</v>
+      </c>
+      <c r="C327" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D327" s="21"/>
       <c r="E327" s="11"/>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="2"/>
-      <c r="B328" s="18" t="s">
+      <c r="B328" s="21" t="s">
+        <v>424</v>
+      </c>
+      <c r="C328" s="21" t="s">
         <v>425</v>
       </c>
-      <c r="C328" s="18" t="s">
-        <v>426</v>
-      </c>
-      <c r="D328" s="18"/>
+      <c r="D328" s="21"/>
       <c r="E328" s="11"/>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="2"/>
-      <c r="B329" s="18" t="s">
-        <v>427</v>
-      </c>
-      <c r="C329" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D329" s="18"/>
+      <c r="B329" s="21" t="s">
+        <v>426</v>
+      </c>
+      <c r="C329" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D329" s="21"/>
       <c r="E329" s="11"/>
     </row>
     <row r="330" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="2"/>
-      <c r="B330" s="18" t="s">
+      <c r="B330" s="21" t="s">
+        <v>427</v>
+      </c>
+      <c r="C330" s="21" t="s">
         <v>428</v>
       </c>
-      <c r="C330" s="18" t="s">
+      <c r="D330" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="D330" s="18" t="s">
+      <c r="E330" s="11" t="s">
         <v>430</v>
-      </c>
-      <c r="E330" s="11" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="2"/>
-      <c r="B331" s="18" t="s">
-        <v>432</v>
-      </c>
-      <c r="C331" s="18" t="s">
+      <c r="B331" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="C331" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D331" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D331" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="E331" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="2"/>
-      <c r="B332" s="18"/>
-      <c r="C332" s="18"/>
-      <c r="D332" s="18"/>
+      <c r="B332" s="21"/>
+      <c r="C332" s="21"/>
+      <c r="D332" s="21"/>
       <c r="E332" s="11"/>
     </row>
     <row r="333" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="6"/>
-      <c r="B333" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="C333" s="20"/>
-      <c r="D333" s="20"/>
+      <c r="B333" s="22" t="s">
+        <v>432</v>
+      </c>
+      <c r="C333" s="23"/>
+      <c r="D333" s="23"/>
       <c r="E333" s="8"/>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B334" s="17"/>
-      <c r="C334" s="18"/>
-      <c r="D334" s="18"/>
+      <c r="B334" s="20"/>
+      <c r="C334" s="21"/>
+      <c r="D334" s="21"/>
       <c r="E334" s="11"/>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="2"/>
-      <c r="B335" s="18" t="s">
-        <v>434</v>
-      </c>
-      <c r="C335" s="18"/>
-      <c r="D335" s="18"/>
+      <c r="B335" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="C335" s="21"/>
+      <c r="D335" s="21"/>
       <c r="E335" s="11"/>
     </row>
     <row r="336" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="2"/>
-      <c r="B336" s="18" t="s">
+      <c r="B336" s="21" t="s">
+        <v>434</v>
+      </c>
+      <c r="C336" s="21" t="s">
         <v>435</v>
       </c>
-      <c r="C336" s="18" t="s">
+      <c r="D336" s="21" t="s">
         <v>436</v>
       </c>
-      <c r="D336" s="18" t="s">
-        <v>437</v>
-      </c>
       <c r="E336" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="2"/>
-      <c r="B337" s="18" t="s">
-        <v>438</v>
-      </c>
-      <c r="C337" s="18"/>
-      <c r="D337" s="18"/>
+      <c r="B337" s="21" t="s">
+        <v>437</v>
+      </c>
+      <c r="C337" s="21"/>
+      <c r="D337" s="21"/>
       <c r="E337" s="11"/>
     </row>
     <row r="338" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="2"/>
-      <c r="B338" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="C338" s="18"/>
-      <c r="D338" s="18"/>
+      <c r="B338" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C338" s="21"/>
+      <c r="D338" s="21"/>
       <c r="E338" s="11"/>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="2"/>
-      <c r="B339" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="C339" s="18"/>
-      <c r="D339" s="18"/>
+      <c r="B339" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="C339" s="21"/>
+      <c r="D339" s="21"/>
       <c r="E339" s="11"/>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="2"/>
-      <c r="B340" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="C340" s="18" t="s">
+      <c r="B340" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="C340" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D340" s="18"/>
+      <c r="D340" s="21"/>
       <c r="E340" s="11"/>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="2"/>
-      <c r="B341" s="18" t="s">
-        <v>439</v>
-      </c>
-      <c r="C341" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D341" s="18"/>
+      <c r="B341" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="C341" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D341" s="21"/>
       <c r="E341" s="11"/>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="2"/>
-      <c r="B342" s="18" t="s">
-        <v>440</v>
-      </c>
-      <c r="C342" s="18" t="s">
-        <v>426</v>
-      </c>
-      <c r="D342" s="18"/>
+      <c r="B342" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="C342" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="D342" s="21"/>
       <c r="E342" s="11"/>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="2"/>
-      <c r="B343" s="18" t="s">
-        <v>441</v>
-      </c>
-      <c r="C343" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D343" s="18"/>
+      <c r="B343" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="C343" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D343" s="21"/>
       <c r="E343" s="11"/>
     </row>
     <row r="344" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="2"/>
-      <c r="B344" s="18" t="s">
-        <v>442</v>
-      </c>
-      <c r="C344" s="18" t="s">
+      <c r="B344" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="C344" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D344" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D344" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="E344" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="2"/>
-      <c r="B345" s="18" t="s">
+      <c r="B345" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="C345" s="21" t="s">
         <v>443</v>
       </c>
-      <c r="C345" s="18" t="s">
+      <c r="D345" s="21" t="s">
         <v>444</v>
       </c>
-      <c r="D345" s="18" t="s">
-        <v>445</v>
-      </c>
       <c r="E345" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="2"/>
-      <c r="B346" s="18"/>
-      <c r="C346" s="18"/>
-      <c r="D346" s="18"/>
+      <c r="B346" s="21"/>
+      <c r="C346" s="21"/>
+      <c r="D346" s="21"/>
       <c r="E346" s="11"/>
     </row>
     <row r="347" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="6"/>
-      <c r="B347" s="19" t="s">
-        <v>446</v>
-      </c>
-      <c r="C347" s="20"/>
-      <c r="D347" s="20"/>
+      <c r="B347" s="22" t="s">
+        <v>445</v>
+      </c>
+      <c r="C347" s="23"/>
+      <c r="D347" s="23"/>
       <c r="E347" s="8"/>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B348" s="17"/>
-      <c r="C348" s="18"/>
-      <c r="D348" s="18"/>
+      <c r="B348" s="20"/>
+      <c r="C348" s="21"/>
+      <c r="D348" s="21"/>
       <c r="E348" s="11"/>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="2"/>
-      <c r="B349" s="18" t="s">
-        <v>447</v>
-      </c>
-      <c r="C349" s="18"/>
-      <c r="D349" s="18"/>
+      <c r="B349" s="21" t="s">
+        <v>446</v>
+      </c>
+      <c r="C349" s="21"/>
+      <c r="D349" s="21"/>
       <c r="E349" s="11"/>
     </row>
     <row r="350" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="2"/>
-      <c r="B350" s="18" t="s">
-        <v>448</v>
-      </c>
-      <c r="C350" s="18" t="s">
+      <c r="B350" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="C350" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="D350" s="21" t="s">
         <v>436</v>
       </c>
-      <c r="D350" s="18" t="s">
-        <v>437</v>
-      </c>
       <c r="E350" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="2"/>
-      <c r="B351" s="18" t="s">
-        <v>449</v>
-      </c>
-      <c r="C351" s="18"/>
-      <c r="D351" s="18"/>
+      <c r="B351" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="C351" s="21"/>
+      <c r="D351" s="21"/>
       <c r="E351" s="11"/>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="2"/>
-      <c r="B352" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="C352" s="18"/>
-      <c r="D352" s="18"/>
+      <c r="B352" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C352" s="21"/>
+      <c r="D352" s="21"/>
       <c r="E352" s="11"/>
     </row>
     <row r="353" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="2"/>
-      <c r="B353" s="18" t="s">
-        <v>450</v>
-      </c>
-      <c r="C353" s="18" t="s">
+      <c r="B353" s="21" t="s">
+        <v>449</v>
+      </c>
+      <c r="C353" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D353" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D353" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="E353" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="2"/>
-      <c r="B354" s="18" t="s">
+      <c r="B354" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="C354" s="21" t="s">
         <v>451</v>
       </c>
-      <c r="C354" s="18" t="s">
+      <c r="D354" s="21" t="s">
         <v>452</v>
       </c>
-      <c r="D354" s="18" t="s">
-        <v>453</v>
-      </c>
       <c r="E354" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="2"/>
-      <c r="B355" s="18"/>
-      <c r="C355" s="18"/>
-      <c r="D355" s="18"/>
+      <c r="B355" s="21"/>
+      <c r="C355" s="21"/>
+      <c r="D355" s="21"/>
       <c r="E355" s="11"/>
     </row>
     <row r="356" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="6"/>
-      <c r="B356" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="C356" s="20"/>
-      <c r="D356" s="20"/>
+      <c r="B356" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="C356" s="23"/>
+      <c r="D356" s="23"/>
       <c r="E356" s="8"/>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B357" s="17"/>
-      <c r="C357" s="18"/>
-      <c r="D357" s="18"/>
+      <c r="B357" s="20"/>
+      <c r="C357" s="21"/>
+      <c r="D357" s="21"/>
       <c r="E357" s="11"/>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2"/>
-      <c r="B358" s="18" t="s">
-        <v>455</v>
-      </c>
-      <c r="C358" s="18"/>
-      <c r="D358" s="18"/>
+      <c r="B358" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="C358" s="21"/>
+      <c r="D358" s="21"/>
       <c r="E358" s="11"/>
     </row>
     <row r="359" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="2"/>
-      <c r="B359" s="18" t="s">
-        <v>456</v>
-      </c>
-      <c r="C359" s="18"/>
-      <c r="D359" s="18"/>
+      <c r="B359" s="21" t="s">
+        <v>455</v>
+      </c>
+      <c r="C359" s="21"/>
+      <c r="D359" s="21"/>
       <c r="E359" s="11"/>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="2"/>
-      <c r="B360" s="18" t="s">
+      <c r="B360" s="21" t="s">
+        <v>456</v>
+      </c>
+      <c r="C360" s="21" t="s">
         <v>457</v>
       </c>
-      <c r="C360" s="18" t="s">
+      <c r="D360" s="21" t="s">
         <v>458</v>
       </c>
-      <c r="D360" s="18" t="s">
-        <v>459</v>
-      </c>
       <c r="E360" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="2"/>
-      <c r="B361" s="18" t="s">
-        <v>460</v>
-      </c>
-      <c r="C361" s="18"/>
-      <c r="D361" s="18"/>
+      <c r="B361" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="C361" s="21"/>
+      <c r="D361" s="21"/>
       <c r="E361" s="11"/>
     </row>
     <row r="362" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="2"/>
-      <c r="B362" s="18" t="s">
-        <v>461</v>
-      </c>
-      <c r="C362" s="18"/>
-      <c r="D362" s="18"/>
+      <c r="B362" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="C362" s="21"/>
+      <c r="D362" s="21"/>
       <c r="E362" s="11"/>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="2"/>
-      <c r="B363" s="18" t="s">
-        <v>462</v>
-      </c>
-      <c r="C363" s="18"/>
-      <c r="D363" s="18"/>
+      <c r="B363" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="C363" s="21"/>
+      <c r="D363" s="21"/>
       <c r="E363" s="11"/>
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="2"/>
-      <c r="B364" s="18" t="s">
+      <c r="B364" s="21" t="s">
+        <v>462</v>
+      </c>
+      <c r="C364" s="21" t="s">
         <v>463</v>
       </c>
-      <c r="C364" s="18" t="s">
+      <c r="D364" s="21" t="s">
         <v>464</v>
       </c>
-      <c r="D364" s="18" t="s">
-        <v>465</v>
-      </c>
       <c r="E364" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="2"/>
-      <c r="B365" s="18" t="s">
+      <c r="B365" s="21" t="s">
+        <v>465</v>
+      </c>
+      <c r="C365" s="21" t="s">
         <v>466</v>
       </c>
-      <c r="C365" s="18" t="s">
+      <c r="D365" s="21" t="s">
         <v>467</v>
       </c>
-      <c r="D365" s="18" t="s">
-        <v>468</v>
-      </c>
       <c r="E365" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="2"/>
-      <c r="B366" s="18" t="s">
-        <v>469</v>
-      </c>
-      <c r="C366" s="18" t="s">
-        <v>407</v>
-      </c>
-      <c r="D366" s="18" t="s">
-        <v>470</v>
-      </c>
+      <c r="B366" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="C366" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="D366" s="21"/>
       <c r="E366" s="11"/>
     </row>
     <row r="367" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="2"/>
-      <c r="B367" s="18" t="s">
+      <c r="B367" s="21" t="s">
+        <v>469</v>
+      </c>
+      <c r="C367" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="D367" s="21" t="s">
         <v>471</v>
       </c>
-      <c r="C367" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="D367" s="18" t="s">
-        <v>473</v>
-      </c>
       <c r="E367" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="2"/>
-      <c r="B368" s="18" t="s">
+      <c r="B368" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="C368" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="D368" s="21" t="s">
         <v>474</v>
       </c>
-      <c r="C368" s="18" t="s">
-        <v>475</v>
-      </c>
-      <c r="D368" s="18" t="s">
-        <v>476</v>
-      </c>
       <c r="E368" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="2"/>
-      <c r="B369" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="C369" s="18" t="s">
+      <c r="B369" s="21" t="s">
+        <v>475</v>
+      </c>
+      <c r="C369" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D369" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D369" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="E369" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="2"/>
-      <c r="B370" s="18"/>
-      <c r="C370" s="18"/>
-      <c r="D370" s="18"/>
+      <c r="B370" s="21"/>
+      <c r="C370" s="21"/>
+      <c r="D370" s="21"/>
       <c r="E370" s="11"/>
     </row>
     <row r="371" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="30"/>
-      <c r="B371" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C371" s="20"/>
-      <c r="D371" s="20"/>
-      <c r="E371" s="20"/>
+      <c r="A371" s="28"/>
+      <c r="B371" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="C371" s="23"/>
+      <c r="D371" s="23"/>
+      <c r="E371" s="23"/>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B372" s="17"/>
-      <c r="C372" s="18"/>
-      <c r="D372" s="18"/>
+      <c r="B372" s="20"/>
+      <c r="C372" s="21"/>
+      <c r="D372" s="21"/>
       <c r="E372" s="11"/>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="2"/>
-      <c r="B373" s="18" t="s">
-        <v>479</v>
-      </c>
-      <c r="C373" s="18"/>
-      <c r="D373" s="18"/>
+      <c r="B373" s="21" t="s">
+        <v>477</v>
+      </c>
+      <c r="C373" s="21"/>
+      <c r="D373" s="21"/>
       <c r="E373" s="11"/>
     </row>
     <row r="374" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="2"/>
-      <c r="B374" s="18" t="s">
+      <c r="B374" s="21" t="s">
+        <v>478</v>
+      </c>
+      <c r="C374" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="D374" s="21" t="s">
         <v>480</v>
       </c>
-      <c r="C374" s="18" t="s">
-        <v>481</v>
-      </c>
-      <c r="D374" s="18" t="s">
-        <v>482</v>
-      </c>
       <c r="E374" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="2"/>
-      <c r="B375" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="C375" s="18"/>
-      <c r="D375" s="18"/>
+      <c r="B375" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="C375" s="21"/>
+      <c r="D375" s="21"/>
       <c r="E375" s="11"/>
     </row>
     <row r="376" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="2"/>
-      <c r="B376" s="18" t="s">
-        <v>484</v>
-      </c>
-      <c r="C376" s="18"/>
-      <c r="D376" s="18"/>
+      <c r="B376" s="21" t="s">
+        <v>482</v>
+      </c>
+      <c r="C376" s="21"/>
+      <c r="D376" s="21"/>
       <c r="E376" s="11"/>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="2"/>
-      <c r="B377" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="C377" s="18"/>
-      <c r="D377" s="18"/>
+      <c r="B377" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="C377" s="21"/>
+      <c r="D377" s="21"/>
       <c r="E377" s="11"/>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="2"/>
-      <c r="B378" s="18" t="s">
-        <v>485</v>
-      </c>
-      <c r="C378" s="18" t="s">
-        <v>464</v>
-      </c>
-      <c r="D378" s="18"/>
+      <c r="B378" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="C378" s="21" t="s">
+        <v>463</v>
+      </c>
+      <c r="D378" s="21"/>
       <c r="E378" s="11"/>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="2"/>
-      <c r="B379" s="18" t="s">
-        <v>486</v>
-      </c>
-      <c r="C379" s="18" t="s">
-        <v>467</v>
-      </c>
-      <c r="D379" s="18"/>
+      <c r="B379" s="21" t="s">
+        <v>484</v>
+      </c>
+      <c r="C379" s="21" t="s">
+        <v>466</v>
+      </c>
+      <c r="D379" s="21"/>
       <c r="E379" s="11"/>
     </row>
     <row r="380" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2"/>
-      <c r="B380" s="18" t="s">
-        <v>487</v>
-      </c>
-      <c r="C380" s="18" t="s">
-        <v>407</v>
-      </c>
-      <c r="D380" s="18"/>
+      <c r="B380" s="21" t="s">
+        <v>485</v>
+      </c>
+      <c r="C380" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="D380" s="21"/>
       <c r="E380" s="11"/>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="2"/>
-      <c r="B381" s="18" t="s">
-        <v>488</v>
-      </c>
-      <c r="C381" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="D381" s="18"/>
+      <c r="B381" s="21" t="s">
+        <v>486</v>
+      </c>
+      <c r="C381" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="D381" s="21"/>
       <c r="E381" s="11"/>
     </row>
     <row r="382" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="2"/>
-      <c r="B382" s="18" t="s">
-        <v>489</v>
-      </c>
-      <c r="C382" s="18" t="s">
+      <c r="B382" s="21" t="s">
+        <v>487</v>
+      </c>
+      <c r="C382" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D382" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D382" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="E382" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="2"/>
-      <c r="B383" s="18" t="s">
+      <c r="B383" s="21" t="s">
+        <v>488</v>
+      </c>
+      <c r="C383" s="21" t="s">
+        <v>489</v>
+      </c>
+      <c r="D383" s="21" t="s">
         <v>490</v>
       </c>
-      <c r="C383" s="18" t="s">
-        <v>491</v>
-      </c>
-      <c r="D383" s="18" t="s">
-        <v>492</v>
-      </c>
       <c r="E383" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="2"/>
-      <c r="B384" s="18"/>
-      <c r="C384" s="18"/>
-      <c r="D384" s="18"/>
+      <c r="B384" s="21"/>
+      <c r="C384" s="21"/>
+      <c r="D384" s="21"/>
       <c r="E384" s="11"/>
     </row>
     <row r="385" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="6"/>
-      <c r="B385" s="19" t="s">
-        <v>493</v>
-      </c>
-      <c r="C385" s="20"/>
-      <c r="D385" s="20"/>
+      <c r="B385" s="22" t="s">
+        <v>491</v>
+      </c>
+      <c r="C385" s="23"/>
+      <c r="D385" s="23"/>
       <c r="E385" s="8"/>
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B386" s="17"/>
-      <c r="C386" s="18"/>
-      <c r="D386" s="18"/>
+      <c r="B386" s="20"/>
+      <c r="C386" s="21"/>
+      <c r="D386" s="21"/>
       <c r="E386" s="11"/>
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="2"/>
-      <c r="B387" s="18" t="s">
-        <v>494</v>
-      </c>
-      <c r="C387" s="18"/>
-      <c r="D387" s="18"/>
+      <c r="B387" s="21" t="s">
+        <v>492</v>
+      </c>
+      <c r="C387" s="21"/>
+      <c r="D387" s="21"/>
       <c r="E387" s="11"/>
     </row>
     <row r="388" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="2"/>
-      <c r="B388" s="18" t="s">
-        <v>495</v>
-      </c>
-      <c r="C388" s="18" t="s">
-        <v>481</v>
-      </c>
-      <c r="D388" s="18" t="s">
-        <v>482</v>
+      <c r="B388" s="21" t="s">
+        <v>493</v>
+      </c>
+      <c r="C388" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="D388" s="21" t="s">
+        <v>480</v>
       </c>
       <c r="E388" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="2"/>
-      <c r="B389" s="18" t="s">
-        <v>496</v>
-      </c>
-      <c r="C389" s="18"/>
-      <c r="D389" s="18"/>
+      <c r="B389" s="21" t="s">
+        <v>494</v>
+      </c>
+      <c r="C389" s="21"/>
+      <c r="D389" s="21"/>
       <c r="E389" s="11"/>
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="2"/>
-      <c r="B390" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="C390" s="18"/>
-      <c r="D390" s="18"/>
+      <c r="B390" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C390" s="21"/>
+      <c r="D390" s="21"/>
       <c r="E390" s="11"/>
     </row>
     <row r="391" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="2"/>
-      <c r="B391" s="18" t="s">
-        <v>497</v>
-      </c>
-      <c r="C391" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D391" s="18"/>
+      <c r="B391" s="21" t="s">
+        <v>495</v>
+      </c>
+      <c r="C391" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D391" s="21"/>
       <c r="E391" s="11"/>
     </row>
     <row r="392" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="2"/>
-      <c r="B392" s="18" t="s">
+      <c r="B392" s="21" t="s">
+        <v>496</v>
+      </c>
+      <c r="C392" s="21" t="s">
+        <v>497</v>
+      </c>
+      <c r="D392" s="21" t="s">
         <v>498</v>
       </c>
-      <c r="C392" s="18" t="s">
+      <c r="E392" s="11" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="393" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A393" s="29"/>
+      <c r="B393" s="24"/>
+      <c r="C393" s="24"/>
+      <c r="D393" s="24"/>
+      <c r="E393" s="18"/>
+      <c r="F393" s="30"/>
+    </row>
+    <row r="394" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A394" s="31"/>
+      <c r="B394" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="D392" s="18" t="s">
-        <v>500</v>
-      </c>
-      <c r="E392" s="11" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="393" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A393" s="31" t="s">
-        <v>501</v>
-      </c>
-      <c r="B393" s="32"/>
-      <c r="C393" s="32"/>
-      <c r="D393" s="32"/>
-      <c r="E393" s="33"/>
-      <c r="F393" s="34"/>
-    </row>
-    <row r="394" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A394" s="35"/>
-      <c r="B394" s="36" t="s">
-        <v>502</v>
-      </c>
-      <c r="C394" s="37"/>
-      <c r="D394" s="37"/>
-      <c r="E394" s="38"/>
+      <c r="C394" s="33"/>
+      <c r="D394" s="33"/>
+      <c r="E394" s="34"/>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B395" s="17"/>
-      <c r="C395" s="18"/>
-      <c r="D395" s="18"/>
+      <c r="B395" s="20"/>
+      <c r="C395" s="21"/>
+      <c r="D395" s="21"/>
       <c r="E395" s="11"/>
     </row>
     <row r="396" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="2"/>
-      <c r="B396" s="18" t="s">
-        <v>503</v>
-      </c>
-      <c r="C396" s="18"/>
-      <c r="D396" s="18"/>
+      <c r="B396" s="21" t="s">
+        <v>500</v>
+      </c>
+      <c r="C396" s="21"/>
+      <c r="D396" s="21"/>
       <c r="E396" s="11"/>
     </row>
     <row r="397" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="2"/>
-      <c r="B397" s="18" t="s">
-        <v>504</v>
-      </c>
-      <c r="C397" s="18"/>
-      <c r="D397" s="18"/>
+      <c r="B397" s="21" t="s">
+        <v>501</v>
+      </c>
+      <c r="C397" s="21"/>
+      <c r="D397" s="21"/>
       <c r="E397" s="11"/>
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="2"/>
-      <c r="B398" s="18" t="s">
+      <c r="B398" s="21" t="s">
+        <v>456</v>
+      </c>
+      <c r="C398" s="21" t="s">
         <v>457</v>
       </c>
-      <c r="C398" s="18" t="s">
-        <v>458</v>
-      </c>
-      <c r="D398" s="18"/>
+      <c r="D398" s="21"/>
       <c r="E398" s="11"/>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="2"/>
-      <c r="B399" s="18" t="s">
-        <v>460</v>
-      </c>
-      <c r="C399" s="18"/>
-      <c r="D399" s="18"/>
+      <c r="B399" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="C399" s="21"/>
+      <c r="D399" s="21"/>
       <c r="E399" s="11"/>
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="2"/>
-      <c r="B400" s="18" t="s">
-        <v>505</v>
-      </c>
-      <c r="C400" s="18"/>
-      <c r="D400" s="18"/>
+      <c r="B400" s="21" t="s">
+        <v>502</v>
+      </c>
+      <c r="C400" s="21"/>
+      <c r="D400" s="21"/>
       <c r="E400" s="11"/>
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="2"/>
-      <c r="B401" s="18" t="s">
-        <v>506</v>
-      </c>
-      <c r="C401" s="18"/>
-      <c r="D401" s="18"/>
+      <c r="B401" s="21" t="s">
+        <v>503</v>
+      </c>
+      <c r="C401" s="21"/>
+      <c r="D401" s="21"/>
       <c r="E401" s="11"/>
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2"/>
-      <c r="B402" s="18" t="s">
-        <v>507</v>
-      </c>
-      <c r="C402" s="18"/>
-      <c r="D402" s="18"/>
+      <c r="B402" s="21" t="s">
+        <v>504</v>
+      </c>
+      <c r="C402" s="21"/>
+      <c r="D402" s="21"/>
       <c r="E402" s="11"/>
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="2"/>
-      <c r="B403" s="18" t="s">
-        <v>508</v>
-      </c>
-      <c r="C403" s="18"/>
-      <c r="D403" s="18"/>
+      <c r="B403" s="21" t="s">
+        <v>505</v>
+      </c>
+      <c r="C403" s="21"/>
+      <c r="D403" s="21"/>
       <c r="E403" s="11"/>
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="2"/>
-      <c r="B404" s="18" t="s">
-        <v>509</v>
-      </c>
-      <c r="C404" s="18"/>
-      <c r="D404" s="18"/>
+      <c r="B404" s="21" t="s">
+        <v>506</v>
+      </c>
+      <c r="C404" s="21"/>
+      <c r="D404" s="21"/>
       <c r="E404" s="11"/>
     </row>
     <row r="405" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="2"/>
-      <c r="B405" s="18" t="s">
-        <v>510</v>
-      </c>
-      <c r="C405" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="D405" s="18" t="s">
-        <v>146</v>
-      </c>
+      <c r="B405" s="21" t="s">
+        <v>507</v>
+      </c>
+      <c r="C405" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D405" s="21"/>
       <c r="E405" s="11"/>
     </row>
     <row r="406" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="2"/>
-      <c r="B406" s="18" t="s">
+      <c r="B406" s="21" t="s">
+        <v>508</v>
+      </c>
+      <c r="C406" s="21" t="s">
+        <v>509</v>
+      </c>
+      <c r="D406" s="21" t="s">
+        <v>510</v>
+      </c>
+      <c r="E406" s="11" t="s">
         <v>511</v>
-      </c>
-      <c r="C406" s="18" t="s">
-        <v>512</v>
-      </c>
-      <c r="D406" s="23" t="s">
-        <v>513</v>
-      </c>
-      <c r="E406" s="11" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="2"/>
-      <c r="B407" s="18" t="s">
-        <v>515</v>
-      </c>
-      <c r="C407" s="18" t="s">
+      <c r="B407" s="21" t="s">
+        <v>512</v>
+      </c>
+      <c r="C407" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D407" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D407" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="E407" s="11" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="2"/>
-      <c r="B408" s="18"/>
-      <c r="C408" s="18"/>
-      <c r="D408" s="18"/>
+      <c r="B408" s="21"/>
+      <c r="C408" s="21"/>
+      <c r="D408" s="21"/>
       <c r="E408" s="11"/>
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B409" s="18" t="s">
-        <v>516</v>
-      </c>
-      <c r="C409" s="18"/>
-      <c r="D409" s="18"/>
+        <v>244</v>
+      </c>
+      <c r="B409" s="21" t="s">
+        <v>513</v>
+      </c>
+      <c r="C409" s="21"/>
+      <c r="D409" s="21"/>
       <c r="E409" s="11"/>
     </row>
     <row r="410" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="2"/>
-      <c r="B410" s="18" t="s">
-        <v>517</v>
-      </c>
-      <c r="C410" s="18"/>
-      <c r="D410" s="18"/>
+      <c r="B410" s="21" t="s">
+        <v>514</v>
+      </c>
+      <c r="C410" s="21"/>
+      <c r="D410" s="21"/>
       <c r="E410" s="11"/>
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="2"/>
-      <c r="B411" s="18" t="s">
-        <v>518</v>
-      </c>
-      <c r="C411" s="18"/>
-      <c r="D411" s="18"/>
+      <c r="B411" s="21" t="s">
+        <v>515</v>
+      </c>
+      <c r="C411" s="21"/>
+      <c r="D411" s="21"/>
       <c r="E411" s="11"/>
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="2"/>
-      <c r="B412" s="18" t="s">
-        <v>519</v>
-      </c>
-      <c r="C412" s="18"/>
-      <c r="D412" s="18"/>
+      <c r="B412" s="21" t="s">
+        <v>516</v>
+      </c>
+      <c r="C412" s="21"/>
+      <c r="D412" s="21"/>
       <c r="E412" s="11"/>
     </row>
     <row r="413" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="2"/>
-      <c r="B413" s="18" t="s">
-        <v>520</v>
-      </c>
-      <c r="C413" s="18"/>
-      <c r="D413" s="18"/>
+      <c r="B413" s="21" t="s">
+        <v>517</v>
+      </c>
+      <c r="C413" s="21"/>
+      <c r="D413" s="21"/>
       <c r="E413" s="11"/>
     </row>
     <row r="414" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="2"/>
-      <c r="B414" s="18" t="s">
-        <v>521</v>
-      </c>
-      <c r="C414" s="18" t="s">
-        <v>522</v>
-      </c>
-      <c r="D414" s="18" t="s">
-        <v>523</v>
+      <c r="B414" s="21" t="s">
+        <v>518</v>
+      </c>
+      <c r="C414" s="21" t="s">
+        <v>519</v>
+      </c>
+      <c r="D414" s="21" t="s">
+        <v>520</v>
       </c>
       <c r="E414" s="11" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="2"/>
-      <c r="B415" s="18" t="s">
-        <v>524</v>
-      </c>
-      <c r="C415" s="18"/>
-      <c r="D415" s="18"/>
+      <c r="B415" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C415" s="21"/>
+      <c r="D415" s="21"/>
       <c r="E415" s="11"/>
     </row>
     <row r="416" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="2"/>
-      <c r="B416" s="18" t="s">
-        <v>525</v>
-      </c>
-      <c r="C416" s="18"/>
-      <c r="D416" s="18"/>
+      <c r="B416" s="21" t="s">
+        <v>522</v>
+      </c>
+      <c r="C416" s="21"/>
+      <c r="D416" s="21"/>
       <c r="E416" s="11"/>
     </row>
     <row r="417" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="2"/>
-      <c r="B417" s="18" t="s">
-        <v>526</v>
-      </c>
-      <c r="C417" s="18"/>
-      <c r="D417" s="18"/>
+      <c r="B417" s="21" t="s">
+        <v>523</v>
+      </c>
+      <c r="C417" s="21"/>
+      <c r="D417" s="21"/>
       <c r="E417" s="11"/>
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="2"/>
-      <c r="B418" s="18" t="s">
-        <v>527</v>
-      </c>
-      <c r="C418" s="18" t="s">
-        <v>528</v>
-      </c>
-      <c r="D418" s="18" t="s">
-        <v>529</v>
+      <c r="B418" s="21" t="s">
+        <v>524</v>
+      </c>
+      <c r="C418" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D418" s="21" t="s">
+        <v>526</v>
       </c>
       <c r="E418" s="11" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="2"/>
-      <c r="B419" s="18" t="s">
-        <v>530</v>
-      </c>
-      <c r="C419" s="18"/>
-      <c r="D419" s="18"/>
+      <c r="B419" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="C419" s="21"/>
+      <c r="D419" s="21"/>
       <c r="E419" s="11"/>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="2"/>
-      <c r="B420" s="18"/>
-      <c r="C420" s="18"/>
-      <c r="D420" s="18"/>
+      <c r="B420" s="21"/>
+      <c r="C420" s="21"/>
+      <c r="D420" s="21"/>
       <c r="E420" s="11"/>
     </row>
     <row r="421" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="6"/>
-      <c r="B421" s="19" t="s">
-        <v>531</v>
-      </c>
-      <c r="C421" s="20"/>
-      <c r="D421" s="20"/>
+      <c r="B421" s="22" t="s">
+        <v>528</v>
+      </c>
+      <c r="C421" s="23"/>
+      <c r="D421" s="23"/>
       <c r="E421" s="8"/>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B422" s="17"/>
-      <c r="C422" s="18"/>
-      <c r="D422" s="18"/>
+      <c r="B422" s="20"/>
+      <c r="C422" s="21"/>
+      <c r="D422" s="21"/>
       <c r="E422" s="11"/>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2"/>
-      <c r="B423" s="18" t="s">
-        <v>532</v>
-      </c>
-      <c r="C423" s="18"/>
-      <c r="D423" s="18"/>
+      <c r="B423" s="21" t="s">
+        <v>529</v>
+      </c>
+      <c r="C423" s="21"/>
+      <c r="D423" s="21"/>
       <c r="E423" s="11"/>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2"/>
-      <c r="B424" s="18" t="s">
-        <v>533</v>
-      </c>
-      <c r="C424" s="18" t="s">
-        <v>534</v>
-      </c>
-      <c r="D424" s="18" t="s">
-        <v>535</v>
+      <c r="B424" s="21" t="s">
+        <v>530</v>
+      </c>
+      <c r="C424" s="21" t="s">
+        <v>531</v>
+      </c>
+      <c r="D424" s="21" t="s">
+        <v>532</v>
       </c>
       <c r="E424" s="11" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2"/>
-      <c r="B425" s="18" t="s">
-        <v>536</v>
-      </c>
-      <c r="C425" s="18"/>
-      <c r="D425" s="18"/>
+      <c r="B425" s="21" t="s">
+        <v>533</v>
+      </c>
+      <c r="C425" s="21"/>
+      <c r="D425" s="21"/>
       <c r="E425" s="11"/>
     </row>
     <row r="426" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2"/>
-      <c r="B426" s="18" t="s">
-        <v>537</v>
-      </c>
-      <c r="C426" s="18"/>
-      <c r="D426" s="18"/>
+      <c r="B426" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="C426" s="21"/>
+      <c r="D426" s="21"/>
       <c r="E426" s="11"/>
     </row>
     <row r="427" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2"/>
-      <c r="B427" s="18" t="s">
-        <v>538</v>
-      </c>
-      <c r="C427" s="18"/>
-      <c r="D427" s="18"/>
+      <c r="B427" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="C427" s="21"/>
+      <c r="D427" s="21"/>
       <c r="E427" s="11"/>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2"/>
-      <c r="B428" s="18" t="s">
-        <v>539</v>
-      </c>
-      <c r="C428" s="18"/>
-      <c r="D428" s="18"/>
+      <c r="B428" s="21" t="s">
+        <v>536</v>
+      </c>
+      <c r="C428" s="21"/>
+      <c r="D428" s="21"/>
       <c r="E428" s="11"/>
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="2"/>
-      <c r="B429" s="18" t="s">
-        <v>540</v>
-      </c>
-      <c r="C429" s="18"/>
-      <c r="D429" s="18"/>
+      <c r="B429" s="24" t="s">
+        <v>537</v>
+      </c>
+      <c r="C429" s="21"/>
+      <c r="D429" s="21"/>
       <c r="E429" s="11"/>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="2"/>
-      <c r="B430" s="18" t="s">
-        <v>541</v>
-      </c>
-      <c r="C430" s="18"/>
-      <c r="D430" s="18"/>
+      <c r="B430" s="24" t="s">
+        <v>538</v>
+      </c>
+      <c r="C430" s="21"/>
+      <c r="D430" s="21"/>
       <c r="E430" s="11"/>
     </row>
     <row r="431" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="2"/>
-      <c r="B431" s="18" t="s">
-        <v>542</v>
-      </c>
-      <c r="C431" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="D431" s="18"/>
+      <c r="B431" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="C431" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D431" s="21"/>
       <c r="E431" s="11"/>
-      <c r="F431" s="39" t="s">
-        <v>501</v>
-      </c>
-      <c r="G431" s="40"/>
+      <c r="F431" s="35"/>
+      <c r="G431" s="30"/>
     </row>
     <row r="432" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2"/>
-      <c r="B432" s="18" t="s">
+      <c r="B432" s="24" t="s">
+        <v>540</v>
+      </c>
+      <c r="C432" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D432" s="21"/>
+      <c r="E432" s="11"/>
+    </row>
+    <row r="433" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A433" s="2"/>
+      <c r="B433" s="24" t="s">
+        <v>541</v>
+      </c>
+      <c r="C433" s="21" t="s">
+        <v>542</v>
+      </c>
+      <c r="D433" s="21" t="s">
         <v>543</v>
       </c>
-      <c r="C432" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D432" s="18"/>
-      <c r="E432" s="11"/>
-    </row>
-    <row r="433" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A433" s="2"/>
-      <c r="B433" s="18" t="s">
-        <v>544</v>
-      </c>
-      <c r="C433" s="18" t="s">
-        <v>545</v>
-      </c>
-      <c r="D433" s="18" t="s">
-        <v>546</v>
-      </c>
       <c r="E433" s="11" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="2"/>
-      <c r="B434" s="18"/>
-      <c r="C434" s="18"/>
-      <c r="D434" s="18"/>
+      <c r="B434" s="24"/>
+      <c r="C434" s="21"/>
+      <c r="D434" s="21"/>
       <c r="E434" s="11"/>
     </row>
     <row r="435" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B435" s="21" t="s">
-        <v>547</v>
-      </c>
-      <c r="C435" s="18"/>
-      <c r="D435" s="18"/>
+        <v>244</v>
+      </c>
+      <c r="B435" s="24" t="s">
+        <v>544</v>
+      </c>
+      <c r="C435" s="21"/>
+      <c r="D435" s="21"/>
       <c r="E435" s="11"/>
     </row>
     <row r="436" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2"/>
-      <c r="B436" s="18" t="s">
-        <v>548</v>
-      </c>
-      <c r="C436" s="18"/>
-      <c r="D436" s="18"/>
+      <c r="B436" s="24" t="s">
+        <v>545</v>
+      </c>
+      <c r="C436" s="21"/>
+      <c r="D436" s="21"/>
       <c r="E436" s="11"/>
     </row>
     <row r="437" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2"/>
-      <c r="B437" s="18" t="s">
-        <v>549</v>
-      </c>
-      <c r="C437" s="18" t="s">
-        <v>522</v>
-      </c>
-      <c r="D437" s="18"/>
+      <c r="B437" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="C437" s="21" t="s">
+        <v>519</v>
+      </c>
+      <c r="D437" s="21"/>
       <c r="E437" s="11"/>
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2"/>
-      <c r="B438" s="18" t="s">
-        <v>550</v>
-      </c>
-      <c r="C438" s="18"/>
-      <c r="D438" s="18"/>
+      <c r="B438" s="24" t="s">
+        <v>547</v>
+      </c>
+      <c r="C438" s="21"/>
+      <c r="D438" s="21"/>
       <c r="E438" s="11"/>
     </row>
     <row r="439" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="2"/>
-      <c r="B439" s="21" t="s">
-        <v>551</v>
-      </c>
-      <c r="C439" s="18"/>
-      <c r="D439" s="18"/>
+      <c r="B439" s="24" t="s">
+        <v>548</v>
+      </c>
+      <c r="C439" s="21"/>
+      <c r="D439" s="21"/>
       <c r="E439" s="11"/>
     </row>
     <row r="440" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="2"/>
-      <c r="B440" s="18" t="s">
-        <v>552</v>
-      </c>
-      <c r="C440" s="18"/>
-      <c r="D440" s="18"/>
+      <c r="B440" s="24" t="s">
+        <v>549</v>
+      </c>
+      <c r="C440" s="21"/>
+      <c r="D440" s="21"/>
       <c r="E440" s="11"/>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="2"/>
-      <c r="B441" s="18" t="s">
-        <v>553</v>
-      </c>
-      <c r="C441" s="18" t="s">
-        <v>528</v>
-      </c>
-      <c r="D441" s="18"/>
+      <c r="B441" s="24" t="s">
+        <v>550</v>
+      </c>
+      <c r="C441" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D441" s="21"/>
       <c r="E441" s="11"/>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2"/>
-      <c r="B442" s="18" t="s">
-        <v>554</v>
-      </c>
-      <c r="C442" s="18"/>
-      <c r="D442" s="18"/>
+      <c r="B442" s="24" t="s">
+        <v>551</v>
+      </c>
+      <c r="C442" s="21"/>
+      <c r="D442" s="21"/>
       <c r="E442" s="11"/>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2"/>
-      <c r="B443" s="21" t="s">
-        <v>555</v>
-      </c>
-      <c r="C443" s="18"/>
-      <c r="D443" s="18"/>
+      <c r="B443" s="24" t="s">
+        <v>552</v>
+      </c>
+      <c r="C443" s="21"/>
+      <c r="D443" s="21"/>
       <c r="E443" s="11"/>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2"/>
-      <c r="B444" s="18" t="s">
-        <v>556</v>
-      </c>
-      <c r="C444" s="18"/>
-      <c r="D444" s="18"/>
+      <c r="B444" s="24" t="s">
+        <v>553</v>
+      </c>
+      <c r="C444" s="21"/>
+      <c r="D444" s="21"/>
       <c r="E444" s="11"/>
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2"/>
-      <c r="B445" s="18" t="s">
-        <v>557</v>
-      </c>
-      <c r="C445" s="18"/>
-      <c r="D445" s="18"/>
+      <c r="B445" s="24" t="s">
+        <v>554</v>
+      </c>
+      <c r="C445" s="21"/>
+      <c r="D445" s="21"/>
       <c r="E445" s="11"/>
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2"/>
-      <c r="B446" s="21" t="s">
-        <v>558</v>
-      </c>
-      <c r="C446" s="18"/>
-      <c r="D446" s="18"/>
+      <c r="B446" s="24" t="s">
+        <v>555</v>
+      </c>
+      <c r="C446" s="21"/>
+      <c r="D446" s="21"/>
       <c r="E446" s="11"/>
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="2"/>
-      <c r="B447" s="18" t="s">
-        <v>559</v>
-      </c>
-      <c r="C447" s="18"/>
-      <c r="D447" s="18"/>
+      <c r="B447" s="24" t="s">
+        <v>556</v>
+      </c>
+      <c r="C447" s="21"/>
+      <c r="D447" s="21"/>
       <c r="E447" s="11"/>
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="2"/>
-      <c r="B448" s="18" t="s">
-        <v>560</v>
-      </c>
-      <c r="C448" s="18"/>
-      <c r="D448" s="18"/>
+      <c r="B448" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="C448" s="21"/>
+      <c r="D448" s="21"/>
       <c r="E448" s="11"/>
     </row>
     <row r="449" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="2"/>
-      <c r="B449" s="18" t="s">
-        <v>561</v>
-      </c>
-      <c r="C449" s="18" t="s">
-        <v>562</v>
-      </c>
-      <c r="D449" s="18" t="s">
-        <v>563</v>
+      <c r="B449" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="C449" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="D449" s="21" t="s">
+        <v>560</v>
       </c>
       <c r="E449" s="11" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="2"/>
-      <c r="B450" s="18" t="s">
-        <v>564</v>
-      </c>
-      <c r="C450" s="18"/>
-      <c r="D450" s="18"/>
+      <c r="B450" s="24" t="s">
+        <v>561</v>
+      </c>
+      <c r="C450" s="21"/>
+      <c r="D450" s="21"/>
       <c r="E450" s="11"/>
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="2"/>
-      <c r="B451" s="21" t="s">
-        <v>565</v>
-      </c>
-      <c r="C451" s="18"/>
-      <c r="D451" s="18"/>
+      <c r="B451" s="24" t="s">
+        <v>562</v>
+      </c>
+      <c r="C451" s="21"/>
+      <c r="D451" s="21"/>
       <c r="E451" s="11"/>
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="2"/>
-      <c r="B452" s="18" t="s">
-        <v>566</v>
-      </c>
-      <c r="C452" s="18"/>
-      <c r="D452" s="18"/>
+      <c r="B452" s="24" t="s">
+        <v>563</v>
+      </c>
+      <c r="C452" s="21"/>
+      <c r="D452" s="21"/>
       <c r="E452" s="11"/>
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="2"/>
-      <c r="B453" s="18" t="s">
-        <v>567</v>
-      </c>
-      <c r="C453" s="18"/>
-      <c r="D453" s="18"/>
+      <c r="B453" s="24" t="s">
+        <v>564</v>
+      </c>
+      <c r="C453" s="21"/>
+      <c r="D453" s="21"/>
       <c r="E453" s="11"/>
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2"/>
-      <c r="B454" s="18" t="s">
-        <v>568</v>
-      </c>
-      <c r="C454" s="18"/>
-      <c r="D454" s="18"/>
+      <c r="B454" s="24" t="s">
+        <v>565</v>
+      </c>
+      <c r="C454" s="21"/>
+      <c r="D454" s="21"/>
       <c r="E454" s="11"/>
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2"/>
-      <c r="B455" s="18" t="s">
-        <v>569</v>
-      </c>
-      <c r="C455" s="18"/>
-      <c r="D455" s="18"/>
+      <c r="B455" s="24" t="s">
+        <v>566</v>
+      </c>
+      <c r="C455" s="21"/>
+      <c r="D455" s="21"/>
       <c r="E455" s="11"/>
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2"/>
-      <c r="B456" s="21" t="s">
-        <v>570</v>
-      </c>
-      <c r="C456" s="18"/>
-      <c r="D456" s="18"/>
+      <c r="B456" s="24" t="s">
+        <v>567</v>
+      </c>
+      <c r="C456" s="21"/>
+      <c r="D456" s="21"/>
       <c r="E456" s="11"/>
     </row>
-    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2"/>
-      <c r="B457" s="18" t="s">
-        <v>571</v>
-      </c>
-      <c r="C457" s="18"/>
-      <c r="D457" s="18"/>
-      <c r="E457" s="11"/>
+      <c r="B457" s="24" t="s">
+        <v>568</v>
+      </c>
+      <c r="C457" s="21"/>
+      <c r="D457" s="36" t="s">
+        <v>569</v>
+      </c>
+      <c r="E457" s="37"/>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2"/>
-      <c r="B458" s="18" t="s">
-        <v>572</v>
-      </c>
-      <c r="C458" s="18"/>
-      <c r="D458" s="18"/>
+      <c r="B458" s="24" t="s">
+        <v>570</v>
+      </c>
+      <c r="C458" s="21"/>
+      <c r="D458" s="21"/>
       <c r="E458" s="11"/>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="2"/>
-      <c r="B459" s="18" t="s">
-        <v>573</v>
-      </c>
-      <c r="C459" s="18"/>
-      <c r="D459" s="18"/>
+      <c r="B459" s="24" t="s">
+        <v>571</v>
+      </c>
+      <c r="C459" s="21"/>
+      <c r="D459" s="21"/>
       <c r="E459" s="11"/>
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="2"/>
-      <c r="B460" s="21" t="s">
+      <c r="B460" s="24" t="s">
+        <v>572</v>
+      </c>
+      <c r="C460" s="21"/>
+      <c r="D460" s="21"/>
+      <c r="E460" s="11"/>
+    </row>
+    <row r="461" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A461" s="2"/>
+      <c r="B461" s="24" t="s">
+        <v>573</v>
+      </c>
+      <c r="C461" s="21"/>
+      <c r="D461" s="21"/>
+      <c r="E461" s="11"/>
+    </row>
+    <row r="462" customFormat="false" ht="67.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A462" s="2"/>
+      <c r="B462" s="24" t="s">
         <v>574</v>
       </c>
-      <c r="C460" s="18"/>
-      <c r="D460" s="18"/>
-      <c r="E460" s="11"/>
-    </row>
-    <row r="461" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A461" s="2"/>
-      <c r="B461" s="18" t="s">
+      <c r="C462" s="24" t="s">
         <v>575</v>
       </c>
-      <c r="C461" s="18"/>
-      <c r="D461" s="18" t="s">
+      <c r="D462" s="21" t="s">
         <v>576</v>
       </c>
-      <c r="E461" s="11" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A462" s="2"/>
-      <c r="B462" s="18" t="s">
-        <v>577</v>
-      </c>
-      <c r="C462" s="18" t="s">
-        <v>578</v>
-      </c>
-      <c r="D462" s="18" t="s">
-        <v>579</v>
-      </c>
       <c r="E462" s="11" t="s">
-        <v>183</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="F462" s="38"/>
     </row>
     <row r="463" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2"/>
-      <c r="B463" s="18" t="s">
-        <v>580</v>
-      </c>
-      <c r="C463" s="18"/>
-      <c r="D463" s="18"/>
+      <c r="B463" s="24" t="s">
+        <v>577</v>
+      </c>
+      <c r="C463" s="21"/>
+      <c r="D463" s="21"/>
       <c r="E463" s="11"/>
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2"/>
-      <c r="B464" s="18" t="s">
-        <v>581</v>
-      </c>
-      <c r="C464" s="18"/>
-      <c r="D464" s="18"/>
+      <c r="B464" s="24" t="s">
+        <v>578</v>
+      </c>
+      <c r="C464" s="21"/>
+      <c r="D464" s="21"/>
       <c r="E464" s="11"/>
     </row>
-    <row r="465" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="465" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2"/>
-      <c r="B465" s="18" t="s">
-        <v>582</v>
-      </c>
-      <c r="C465" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="D465" s="18" t="s">
-        <v>583</v>
-      </c>
-      <c r="E465" s="41" t="s">
-        <v>584</v>
+      <c r="B465" s="24" t="s">
+        <v>579</v>
+      </c>
+      <c r="C465" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="D465" s="21"/>
+      <c r="E465" s="18" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2"/>
-      <c r="B466" s="18" t="s">
-        <v>585</v>
-      </c>
-      <c r="C466" s="18" t="s">
-        <v>545</v>
-      </c>
-      <c r="D466" s="18" t="s">
-        <v>586</v>
+      <c r="B466" s="24" t="s">
+        <v>580</v>
+      </c>
+      <c r="C466" s="21" t="s">
+        <v>542</v>
+      </c>
+      <c r="D466" s="21" t="s">
+        <v>581</v>
       </c>
       <c r="E466" s="11" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2"/>
-      <c r="B467" s="18" t="s">
-        <v>587</v>
-      </c>
-      <c r="C467" s="18"/>
-      <c r="D467" s="18"/>
+      <c r="B467" s="24" t="s">
+        <v>582</v>
+      </c>
+      <c r="C467" s="21"/>
+      <c r="D467" s="21"/>
       <c r="E467" s="11"/>
     </row>
     <row r="468" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2"/>
-      <c r="B468" s="21" t="s">
-        <v>588</v>
-      </c>
-      <c r="C468" s="21"/>
-      <c r="D468" s="21" t="s">
-        <v>589</v>
-      </c>
-      <c r="E468" s="41"/>
-    </row>
-    <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B468" s="24" t="s">
+        <v>583</v>
+      </c>
+      <c r="C468" s="24"/>
+      <c r="D468" s="24"/>
+      <c r="E468" s="18"/>
+    </row>
+    <row r="469" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="2"/>
-      <c r="B469" s="21" t="s">
-        <v>590</v>
-      </c>
-      <c r="C469" s="21" t="s">
-        <v>591</v>
-      </c>
-      <c r="D469" s="21"/>
-      <c r="E469" s="41"/>
+      <c r="B469" s="24" t="s">
+        <v>584</v>
+      </c>
+      <c r="C469" s="24" t="s">
+        <v>585</v>
+      </c>
+      <c r="D469" s="36" t="s">
+        <v>569</v>
+      </c>
+      <c r="E469" s="37"/>
     </row>
     <row r="470" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="2"/>
-      <c r="B470" s="18" t="s">
-        <v>592</v>
-      </c>
-      <c r="C470" s="18" t="s">
-        <v>593</v>
-      </c>
-      <c r="D470" s="18" t="s">
-        <v>594</v>
+      <c r="B470" s="21" t="s">
+        <v>586</v>
+      </c>
+      <c r="C470" s="21" t="s">
+        <v>587</v>
+      </c>
+      <c r="D470" s="21" t="s">
+        <v>588</v>
       </c>
       <c r="E470" s="11" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="2"/>
-      <c r="B471" s="18" t="s">
-        <v>595</v>
-      </c>
-      <c r="C471" s="18"/>
-      <c r="D471" s="18"/>
+      <c r="B471" s="21" t="s">
+        <v>589</v>
+      </c>
+      <c r="C471" s="21"/>
+      <c r="D471" s="21"/>
       <c r="E471" s="11"/>
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="2"/>
-      <c r="B472" s="18" t="s">
-        <v>596</v>
-      </c>
-      <c r="C472" s="18"/>
-      <c r="D472" s="18"/>
+      <c r="B472" s="21" t="s">
+        <v>590</v>
+      </c>
+      <c r="C472" s="21"/>
+      <c r="D472" s="21"/>
       <c r="E472" s="11"/>
     </row>
     <row r="473" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2"/>
-      <c r="B473" s="18" t="s">
-        <v>597</v>
-      </c>
-      <c r="C473" s="18" t="s">
-        <v>562</v>
-      </c>
-      <c r="D473" s="18"/>
+      <c r="B473" s="21" t="s">
+        <v>591</v>
+      </c>
+      <c r="C473" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="D473" s="21"/>
       <c r="E473" s="11"/>
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="2"/>
-      <c r="B474" s="18" t="s">
-        <v>598</v>
-      </c>
-      <c r="C474" s="18"/>
-      <c r="D474" s="18"/>
+      <c r="B474" s="21" t="s">
+        <v>592</v>
+      </c>
+      <c r="C474" s="21"/>
+      <c r="D474" s="21"/>
       <c r="E474" s="11"/>
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="2"/>
-      <c r="B475" s="18"/>
-      <c r="C475" s="18"/>
-      <c r="D475" s="18"/>
+      <c r="B475" s="21"/>
+      <c r="C475" s="21"/>
+      <c r="D475" s="21"/>
       <c r="E475" s="11"/>
     </row>
     <row r="476" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="B476" s="18" t="s">
-        <v>600</v>
-      </c>
-      <c r="C476" s="18"/>
-      <c r="D476" s="18"/>
+        <v>593</v>
+      </c>
+      <c r="B476" s="21" t="s">
+        <v>594</v>
+      </c>
+      <c r="C476" s="21"/>
+      <c r="D476" s="21"/>
       <c r="E476" s="11"/>
     </row>
     <row r="477" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2"/>
-      <c r="B477" s="18" t="s">
-        <v>601</v>
-      </c>
-      <c r="C477" s="18" t="s">
-        <v>562</v>
-      </c>
-      <c r="D477" s="18"/>
+      <c r="B477" s="21" t="s">
+        <v>595</v>
+      </c>
+      <c r="C477" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="D477" s="21"/>
       <c r="E477" s="11"/>
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2"/>
-      <c r="B478" s="18" t="s">
-        <v>602</v>
-      </c>
-      <c r="C478" s="18"/>
-      <c r="D478" s="18"/>
+      <c r="B478" s="21" t="s">
+        <v>596</v>
+      </c>
+      <c r="C478" s="21"/>
+      <c r="D478" s="21"/>
       <c r="E478" s="11"/>
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="2"/>
-      <c r="B479" s="18"/>
-      <c r="C479" s="18"/>
-      <c r="D479" s="18"/>
+      <c r="B479" s="21"/>
+      <c r="C479" s="21"/>
+      <c r="D479" s="21"/>
       <c r="E479" s="11"/>
     </row>
     <row r="480" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="6"/>
-      <c r="B480" s="19" t="s">
-        <v>603</v>
-      </c>
-      <c r="C480" s="20"/>
-      <c r="D480" s="20"/>
+      <c r="B480" s="22" t="s">
+        <v>597</v>
+      </c>
+      <c r="C480" s="23"/>
+      <c r="D480" s="23"/>
       <c r="E480" s="8"/>
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C481" s="18"/>
-      <c r="D481" s="18"/>
+      <c r="C481" s="21"/>
+      <c r="D481" s="21"/>
       <c r="E481" s="11"/>
     </row>
     <row r="482" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2"/>
-      <c r="B482" s="18" t="s">
-        <v>604</v>
-      </c>
-      <c r="C482" s="18"/>
-      <c r="D482" s="18"/>
+      <c r="B482" s="21" t="s">
+        <v>598</v>
+      </c>
+      <c r="C482" s="21"/>
+      <c r="D482" s="21"/>
       <c r="E482" s="11"/>
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="2"/>
-      <c r="B483" s="18" t="s">
-        <v>605</v>
-      </c>
-      <c r="C483" s="18"/>
-      <c r="D483" s="18"/>
+      <c r="B483" s="21" t="s">
+        <v>599</v>
+      </c>
+      <c r="C483" s="21"/>
+      <c r="D483" s="21"/>
       <c r="E483" s="11"/>
     </row>
     <row r="484" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2"/>
-      <c r="B484" s="18" t="s">
-        <v>606</v>
-      </c>
-      <c r="C484" s="18"/>
-      <c r="D484" s="18"/>
+      <c r="B484" s="21" t="s">
+        <v>600</v>
+      </c>
+      <c r="C484" s="21"/>
+      <c r="D484" s="21"/>
       <c r="E484" s="11"/>
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2"/>
-      <c r="B485" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="C485" s="18"/>
-      <c r="D485" s="18"/>
+      <c r="B485" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C485" s="21"/>
+      <c r="D485" s="21"/>
       <c r="E485" s="11"/>
     </row>
     <row r="486" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2"/>
-      <c r="B486" s="18" t="s">
-        <v>607</v>
-      </c>
-      <c r="C486" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D486" s="18"/>
+      <c r="B486" s="21" t="s">
+        <v>601</v>
+      </c>
+      <c r="C486" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D486" s="21"/>
       <c r="E486" s="11"/>
     </row>
     <row r="487" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="2"/>
-      <c r="B487" s="18" t="s">
-        <v>608</v>
-      </c>
-      <c r="C487" s="18" t="s">
-        <v>562</v>
-      </c>
-      <c r="D487" s="18" t="s">
-        <v>609</v>
+      <c r="B487" s="21" t="s">
+        <v>602</v>
+      </c>
+      <c r="C487" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="D487" s="21" t="s">
+        <v>603</v>
       </c>
       <c r="E487" s="11" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="2"/>
-      <c r="B488" s="18"/>
-      <c r="C488" s="18"/>
-      <c r="D488" s="18"/>
+      <c r="B488" s="21"/>
+      <c r="C488" s="21"/>
+      <c r="D488" s="21"/>
       <c r="E488" s="11"/>
     </row>
     <row r="489" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="6"/>
-      <c r="B489" s="19" t="s">
-        <v>610</v>
-      </c>
-      <c r="C489" s="20"/>
-      <c r="D489" s="20"/>
+      <c r="B489" s="22" t="s">
+        <v>604</v>
+      </c>
+      <c r="C489" s="23"/>
+      <c r="D489" s="23"/>
       <c r="E489" s="8"/>
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C490" s="18"/>
-      <c r="D490" s="18"/>
+      <c r="C490" s="21"/>
+      <c r="D490" s="21"/>
       <c r="E490" s="11"/>
     </row>
     <row r="491" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="2"/>
-      <c r="B491" s="18" t="s">
-        <v>611</v>
-      </c>
-      <c r="C491" s="18"/>
-      <c r="D491" s="18"/>
+      <c r="B491" s="21" t="s">
+        <v>605</v>
+      </c>
+      <c r="C491" s="21"/>
+      <c r="D491" s="21"/>
       <c r="E491" s="11"/>
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2"/>
-      <c r="B492" s="18" t="s">
-        <v>612</v>
-      </c>
-      <c r="C492" s="18"/>
-      <c r="D492" s="18"/>
+      <c r="B492" s="21" t="s">
+        <v>606</v>
+      </c>
+      <c r="C492" s="21"/>
+      <c r="D492" s="21"/>
       <c r="E492" s="11"/>
     </row>
     <row r="493" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2"/>
-      <c r="B493" s="18" t="s">
-        <v>613</v>
-      </c>
-      <c r="C493" s="18" t="s">
+      <c r="B493" s="21" t="s">
+        <v>607</v>
+      </c>
+      <c r="C493" s="21" t="s">
         <v>318</v>
       </c>
-      <c r="D493" s="18"/>
+      <c r="D493" s="21"/>
       <c r="E493" s="11"/>
     </row>
     <row r="494" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2"/>
-      <c r="B494" s="18" t="s">
-        <v>614</v>
-      </c>
-      <c r="C494" s="18" t="s">
-        <v>615</v>
-      </c>
-      <c r="D494" s="18"/>
+      <c r="B494" s="21" t="s">
+        <v>608</v>
+      </c>
+      <c r="C494" s="21" t="s">
+        <v>609</v>
+      </c>
+      <c r="D494" s="21"/>
       <c r="E494" s="11"/>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2"/>
-      <c r="B495" s="18" t="s">
-        <v>616</v>
-      </c>
-      <c r="C495" s="18" t="s">
-        <v>458</v>
-      </c>
-      <c r="D495" s="18"/>
+      <c r="B495" s="21" t="s">
+        <v>610</v>
+      </c>
+      <c r="C495" s="21" t="s">
+        <v>457</v>
+      </c>
+      <c r="D495" s="21"/>
       <c r="E495" s="11"/>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2"/>
-      <c r="B496" s="18" t="s">
-        <v>617</v>
-      </c>
-      <c r="C496" s="18" t="s">
-        <v>618</v>
-      </c>
-      <c r="D496" s="18" t="s">
-        <v>619</v>
+      <c r="B496" s="21" t="s">
+        <v>611</v>
+      </c>
+      <c r="C496" s="21" t="s">
+        <v>612</v>
+      </c>
+      <c r="D496" s="21" t="s">
+        <v>613</v>
       </c>
       <c r="E496" s="11" t="s">
         <v>10</v>
@@ -8790,625 +8774,637 @@
     </row>
     <row r="497" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2"/>
-      <c r="B497" s="18" t="s">
-        <v>620</v>
-      </c>
-      <c r="C497" s="18" t="s">
-        <v>621</v>
-      </c>
-      <c r="D497" s="18" t="s">
-        <v>622</v>
+      <c r="B497" s="21" t="s">
+        <v>614</v>
+      </c>
+      <c r="C497" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="D497" s="21" t="s">
+        <v>616</v>
       </c>
       <c r="E497" s="11" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="2"/>
-      <c r="B498" s="18" t="s">
-        <v>623</v>
-      </c>
-      <c r="C498" s="18"/>
-      <c r="D498" s="18"/>
+      <c r="B498" s="21" t="s">
+        <v>617</v>
+      </c>
+      <c r="C498" s="21"/>
+      <c r="D498" s="21"/>
       <c r="E498" s="11"/>
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="2"/>
-      <c r="B499" s="18"/>
-      <c r="C499" s="18"/>
-      <c r="D499" s="18"/>
+      <c r="B499" s="21"/>
+      <c r="C499" s="21"/>
+      <c r="D499" s="21"/>
       <c r="E499" s="11"/>
     </row>
     <row r="500" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="6"/>
-      <c r="B500" s="19" t="s">
-        <v>624</v>
-      </c>
-      <c r="C500" s="20"/>
-      <c r="D500" s="20"/>
+      <c r="B500" s="22" t="s">
+        <v>618</v>
+      </c>
+      <c r="C500" s="23"/>
+      <c r="D500" s="23"/>
       <c r="E500" s="8"/>
     </row>
     <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B501" s="18"/>
-      <c r="C501" s="18"/>
-      <c r="D501" s="18"/>
+      <c r="B501" s="21"/>
+      <c r="C501" s="21"/>
+      <c r="D501" s="21"/>
       <c r="E501" s="11"/>
     </row>
     <row r="502" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="2"/>
-      <c r="B502" s="18" t="s">
-        <v>625</v>
-      </c>
-      <c r="C502" s="18"/>
-      <c r="D502" s="18"/>
+      <c r="B502" s="21" t="s">
+        <v>619</v>
+      </c>
+      <c r="C502" s="21"/>
+      <c r="D502" s="21"/>
       <c r="E502" s="11"/>
     </row>
-    <row r="503" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="503" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="2"/>
-      <c r="B503" s="18" t="s">
-        <v>626</v>
-      </c>
-      <c r="C503" s="18" t="s">
-        <v>534</v>
-      </c>
-      <c r="D503" s="21" t="s">
-        <v>627</v>
-      </c>
-      <c r="E503" s="11"/>
+      <c r="B503" s="21" t="s">
+        <v>620</v>
+      </c>
+      <c r="C503" s="21" t="s">
+        <v>531</v>
+      </c>
+      <c r="D503" s="24" t="s">
+        <v>621</v>
+      </c>
+      <c r="E503" s="11" t="s">
+        <v>622</v>
+      </c>
+      <c r="F503" s="39" t="s">
+        <v>623</v>
+      </c>
     </row>
     <row r="504" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="2"/>
-      <c r="B504" s="18" t="s">
-        <v>628</v>
-      </c>
-      <c r="C504" s="18"/>
-      <c r="D504" s="18"/>
+      <c r="B504" s="21" t="s">
+        <v>624</v>
+      </c>
+      <c r="C504" s="21"/>
+      <c r="D504" s="21"/>
       <c r="E504" s="11"/>
     </row>
     <row r="505" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="2"/>
-      <c r="B505" s="18" t="s">
-        <v>629</v>
-      </c>
-      <c r="C505" s="18"/>
-      <c r="D505" s="18"/>
+      <c r="B505" s="21" t="s">
+        <v>625</v>
+      </c>
+      <c r="C505" s="21"/>
+      <c r="D505" s="21"/>
       <c r="E505" s="11"/>
     </row>
     <row r="506" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="2"/>
-      <c r="B506" s="18" t="s">
-        <v>630</v>
-      </c>
-      <c r="C506" s="18"/>
-      <c r="D506" s="18" t="s">
-        <v>631</v>
-      </c>
+      <c r="B506" s="21" t="s">
+        <v>626</v>
+      </c>
+      <c r="C506" s="21"/>
+      <c r="D506" s="21"/>
       <c r="E506" s="11"/>
     </row>
     <row r="507" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="2"/>
-      <c r="B507" s="18" t="s">
-        <v>632</v>
-      </c>
-      <c r="C507" s="18" t="s">
-        <v>633</v>
-      </c>
-      <c r="D507" s="18" t="s">
-        <v>634</v>
-      </c>
-      <c r="E507" s="11" t="s">
-        <v>183</v>
-      </c>
+      <c r="B507" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="C507" s="21" t="s">
+        <v>628</v>
+      </c>
+      <c r="D507" s="21"/>
+      <c r="E507" s="11"/>
     </row>
     <row r="508" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="2"/>
-      <c r="B508" s="18" t="s">
-        <v>635</v>
-      </c>
-      <c r="C508" s="18" t="s">
-        <v>636</v>
-      </c>
-      <c r="D508" s="18" t="s">
-        <v>637</v>
+      <c r="B508" s="21" t="s">
+        <v>629</v>
+      </c>
+      <c r="C508" s="21" t="s">
+        <v>630</v>
+      </c>
+      <c r="D508" s="21" t="s">
+        <v>631</v>
       </c>
       <c r="E508" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="2"/>
-      <c r="B509" s="18" t="s">
-        <v>638</v>
-      </c>
-      <c r="C509" s="18" t="s">
-        <v>562</v>
-      </c>
-      <c r="D509" s="18"/>
+      <c r="B509" s="21" t="s">
+        <v>632</v>
+      </c>
+      <c r="C509" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="D509" s="21"/>
       <c r="E509" s="11"/>
     </row>
     <row r="510" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="2"/>
-      <c r="B510" s="18" t="s">
-        <v>639</v>
-      </c>
-      <c r="C510" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D510" s="18"/>
+      <c r="B510" s="21" t="s">
+        <v>633</v>
+      </c>
+      <c r="C510" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D510" s="21"/>
       <c r="E510" s="11"/>
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="2"/>
-      <c r="B511" s="18"/>
-      <c r="C511" s="18"/>
-      <c r="D511" s="18"/>
+      <c r="B511" s="21"/>
+      <c r="C511" s="21"/>
+      <c r="D511" s="21"/>
       <c r="E511" s="11"/>
     </row>
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B512" s="18" t="s">
-        <v>640</v>
-      </c>
-      <c r="C512" s="18"/>
-      <c r="D512" s="18"/>
+        <v>244</v>
+      </c>
+      <c r="B512" s="21" t="s">
+        <v>634</v>
+      </c>
+      <c r="C512" s="21"/>
+      <c r="D512" s="21"/>
       <c r="E512" s="11"/>
     </row>
     <row r="513" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2"/>
-      <c r="B513" s="21" t="s">
-        <v>641</v>
-      </c>
-      <c r="C513" s="21" t="s">
-        <v>642</v>
-      </c>
-      <c r="D513" s="21"/>
-      <c r="E513" s="41"/>
+      <c r="B513" s="24" t="s">
+        <v>635</v>
+      </c>
+      <c r="C513" s="36" t="s">
+        <v>636</v>
+      </c>
+      <c r="D513" s="24"/>
+      <c r="E513" s="18"/>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="2"/>
-      <c r="B514" s="18" t="s">
-        <v>643</v>
-      </c>
-      <c r="C514" s="18"/>
-      <c r="D514" s="18"/>
+      <c r="B514" s="21" t="s">
+        <v>637</v>
+      </c>
+      <c r="C514" s="21"/>
+      <c r="D514" s="21"/>
       <c r="E514" s="11"/>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="2"/>
-      <c r="B515" s="18"/>
-      <c r="C515" s="18"/>
-      <c r="D515" s="18"/>
+      <c r="B515" s="21"/>
+      <c r="C515" s="21"/>
+      <c r="D515" s="21"/>
       <c r="E515" s="11"/>
     </row>
     <row r="516" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="6"/>
-      <c r="B516" s="19" t="s">
-        <v>644</v>
-      </c>
-      <c r="C516" s="42"/>
-      <c r="D516" s="42"/>
-      <c r="E516" s="43"/>
+      <c r="B516" s="22" t="s">
+        <v>638</v>
+      </c>
+      <c r="C516" s="23"/>
+      <c r="D516" s="23"/>
+      <c r="E516" s="8"/>
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B517" s="18"/>
-      <c r="C517" s="18"/>
-      <c r="D517" s="18"/>
+      <c r="B517" s="21"/>
+      <c r="C517" s="21"/>
+      <c r="D517" s="21"/>
       <c r="E517" s="11"/>
     </row>
     <row r="518" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="2"/>
-      <c r="B518" s="18" t="s">
-        <v>645</v>
-      </c>
-      <c r="C518" s="18"/>
-      <c r="D518" s="18"/>
+      <c r="B518" s="21" t="s">
+        <v>639</v>
+      </c>
+      <c r="C518" s="21"/>
+      <c r="D518" s="21"/>
       <c r="E518" s="11"/>
     </row>
     <row r="519" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="2"/>
-      <c r="B519" s="18" t="s">
-        <v>646</v>
-      </c>
-      <c r="C519" s="18" t="s">
-        <v>647</v>
-      </c>
-      <c r="D519" s="18" t="s">
-        <v>648</v>
-      </c>
-      <c r="E519" s="11"/>
+      <c r="B519" s="21" t="s">
+        <v>640</v>
+      </c>
+      <c r="C519" s="21" t="s">
+        <v>641</v>
+      </c>
+      <c r="D519" s="21" t="s">
+        <v>642</v>
+      </c>
+      <c r="E519" s="11" t="s">
+        <v>511</v>
+      </c>
     </row>
     <row r="520" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="2"/>
-      <c r="B520" s="18" t="s">
-        <v>649</v>
-      </c>
-      <c r="C520" s="18"/>
-      <c r="D520" s="18"/>
+      <c r="B520" s="21" t="s">
+        <v>643</v>
+      </c>
+      <c r="C520" s="21"/>
+      <c r="D520" s="21"/>
       <c r="E520" s="11"/>
     </row>
     <row r="521" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="2"/>
-      <c r="B521" s="18" t="s">
-        <v>650</v>
-      </c>
-      <c r="C521" s="18"/>
-      <c r="D521" s="18"/>
+      <c r="B521" s="21" t="s">
+        <v>644</v>
+      </c>
+      <c r="C521" s="21"/>
+      <c r="D521" s="21"/>
       <c r="E521" s="11"/>
     </row>
     <row r="522" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="2"/>
-      <c r="B522" s="18" t="s">
-        <v>651</v>
-      </c>
-      <c r="C522" s="18" t="s">
-        <v>652</v>
-      </c>
-      <c r="D522" s="18"/>
-      <c r="E522" s="11"/>
+      <c r="B522" s="21" t="s">
+        <v>645</v>
+      </c>
+      <c r="C522" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="D522" s="40" t="s">
+        <v>646</v>
+      </c>
+      <c r="E522" s="41"/>
+      <c r="F522" s="30"/>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="2"/>
-      <c r="B523" s="18" t="s">
-        <v>653</v>
-      </c>
-      <c r="C523" s="18"/>
-      <c r="D523" s="18"/>
+      <c r="B523" s="21" t="s">
+        <v>647</v>
+      </c>
+      <c r="C523" s="21"/>
+      <c r="D523" s="21"/>
       <c r="E523" s="11"/>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="2"/>
-      <c r="B524" s="18" t="s">
-        <v>654</v>
-      </c>
-      <c r="C524" s="18"/>
-      <c r="D524" s="18"/>
+      <c r="B524" s="21" t="s">
+        <v>648</v>
+      </c>
+      <c r="C524" s="21"/>
+      <c r="D524" s="21"/>
       <c r="E524" s="11"/>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2"/>
-      <c r="B525" s="18" t="s">
-        <v>655</v>
-      </c>
-      <c r="C525" s="18"/>
-      <c r="D525" s="18"/>
+      <c r="B525" s="21" t="s">
+        <v>649</v>
+      </c>
+      <c r="C525" s="21"/>
+      <c r="D525" s="21"/>
       <c r="E525" s="11"/>
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2"/>
-      <c r="B526" s="18" t="s">
-        <v>656</v>
-      </c>
-      <c r="C526" s="18"/>
-      <c r="D526" s="18"/>
+      <c r="B526" s="21" t="s">
+        <v>650</v>
+      </c>
+      <c r="C526" s="21"/>
+      <c r="D526" s="21"/>
       <c r="E526" s="11"/>
     </row>
     <row r="527" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2"/>
-      <c r="B527" s="18" t="s">
-        <v>657</v>
-      </c>
-      <c r="C527" s="18"/>
-      <c r="D527" s="18"/>
+      <c r="B527" s="21" t="s">
+        <v>651</v>
+      </c>
+      <c r="C527" s="21"/>
+      <c r="D527" s="21"/>
       <c r="E527" s="11"/>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="2"/>
-      <c r="B528" s="18" t="s">
-        <v>658</v>
-      </c>
-      <c r="C528" s="18"/>
-      <c r="D528" s="18"/>
+      <c r="B528" s="21" t="s">
+        <v>652</v>
+      </c>
+      <c r="C528" s="21"/>
+      <c r="D528" s="21"/>
       <c r="E528" s="11"/>
     </row>
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="2"/>
-      <c r="B529" s="18" t="s">
-        <v>659</v>
-      </c>
-      <c r="C529" s="18"/>
-      <c r="D529" s="18"/>
+      <c r="B529" s="21" t="s">
+        <v>653</v>
+      </c>
+      <c r="C529" s="21"/>
+      <c r="D529" s="21"/>
       <c r="E529" s="11"/>
     </row>
     <row r="530" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="2"/>
-      <c r="B530" s="18" t="s">
-        <v>660</v>
-      </c>
-      <c r="C530" s="18" t="s">
-        <v>661</v>
-      </c>
-      <c r="D530" s="18"/>
+      <c r="B530" s="21" t="s">
+        <v>654</v>
+      </c>
+      <c r="C530" s="21" t="s">
+        <v>655</v>
+      </c>
+      <c r="D530" s="21"/>
       <c r="E530" s="11"/>
     </row>
     <row r="531" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="2"/>
-      <c r="B531" s="21" t="s">
-        <v>662</v>
-      </c>
-      <c r="C531" s="21" t="s">
-        <v>562</v>
-      </c>
-      <c r="D531" s="21"/>
-      <c r="E531" s="41"/>
+      <c r="B531" s="24" t="s">
+        <v>656</v>
+      </c>
+      <c r="C531" s="24" t="s">
+        <v>657</v>
+      </c>
+      <c r="D531" s="24"/>
+      <c r="E531" s="18"/>
     </row>
     <row r="532" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="2"/>
-      <c r="B532" s="18" t="s">
-        <v>663</v>
-      </c>
-      <c r="C532" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D532" s="18"/>
+      <c r="B532" s="21" t="s">
+        <v>658</v>
+      </c>
+      <c r="C532" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D532" s="21"/>
       <c r="E532" s="11"/>
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="2"/>
-      <c r="B533" s="18"/>
-      <c r="C533" s="18"/>
-      <c r="D533" s="18"/>
+      <c r="B533" s="21"/>
+      <c r="C533" s="21"/>
+      <c r="D533" s="21"/>
       <c r="E533" s="11"/>
     </row>
     <row r="534" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B534" s="18" t="s">
-        <v>664</v>
-      </c>
-      <c r="C534" s="18"/>
-      <c r="D534" s="18"/>
+        <v>244</v>
+      </c>
+      <c r="B534" s="21" t="s">
+        <v>659</v>
+      </c>
+      <c r="C534" s="21"/>
+      <c r="D534" s="21"/>
       <c r="E534" s="11"/>
     </row>
     <row r="535" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="2"/>
-      <c r="B535" s="18" t="s">
-        <v>665</v>
-      </c>
-      <c r="C535" s="18"/>
-      <c r="D535" s="18"/>
+      <c r="B535" s="21" t="s">
+        <v>660</v>
+      </c>
+      <c r="C535" s="21"/>
+      <c r="D535" s="21"/>
       <c r="E535" s="11"/>
     </row>
     <row r="536" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="2"/>
-      <c r="B536" s="18" t="s">
-        <v>666</v>
-      </c>
-      <c r="C536" s="18"/>
-      <c r="D536" s="18"/>
+      <c r="B536" s="21" t="s">
+        <v>661</v>
+      </c>
+      <c r="C536" s="21"/>
+      <c r="D536" s="21"/>
       <c r="E536" s="11"/>
     </row>
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="2"/>
-      <c r="B537" s="18" t="s">
-        <v>667</v>
-      </c>
-      <c r="C537" s="18"/>
-      <c r="D537" s="18"/>
+      <c r="B537" s="21" t="s">
+        <v>662</v>
+      </c>
+      <c r="C537" s="21"/>
+      <c r="D537" s="21"/>
       <c r="E537" s="11"/>
     </row>
     <row r="538" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="2"/>
-      <c r="B538" s="18" t="s">
-        <v>668</v>
-      </c>
-      <c r="C538" s="18" t="s">
-        <v>562</v>
-      </c>
-      <c r="D538" s="18"/>
-      <c r="E538" s="11"/>
+      <c r="B538" s="21" t="s">
+        <v>663</v>
+      </c>
+      <c r="C538" s="36" t="s">
+        <v>657</v>
+      </c>
+      <c r="D538" s="24"/>
+      <c r="E538" s="18"/>
     </row>
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="2"/>
-      <c r="B539" s="18" t="s">
-        <v>669</v>
-      </c>
-      <c r="C539" s="18"/>
-      <c r="D539" s="18"/>
+      <c r="B539" s="21" t="s">
+        <v>664</v>
+      </c>
+      <c r="C539" s="21"/>
+      <c r="D539" s="21"/>
       <c r="E539" s="11"/>
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="2"/>
-      <c r="B540" s="18" t="s">
-        <v>670</v>
-      </c>
-      <c r="C540" s="18"/>
-      <c r="D540" s="18"/>
+      <c r="B540" s="21" t="s">
+        <v>665</v>
+      </c>
+      <c r="C540" s="21"/>
+      <c r="D540" s="21"/>
       <c r="E540" s="11"/>
     </row>
     <row r="541" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="2"/>
-      <c r="B541" s="18" t="s">
-        <v>671</v>
-      </c>
-      <c r="C541" s="18"/>
-      <c r="D541" s="18"/>
+      <c r="B541" s="21" t="s">
+        <v>666</v>
+      </c>
+      <c r="C541" s="21"/>
+      <c r="D541" s="21"/>
       <c r="E541" s="11"/>
     </row>
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="2"/>
-      <c r="B542" s="18" t="s">
-        <v>672</v>
-      </c>
-      <c r="C542" s="18"/>
-      <c r="D542" s="18"/>
+      <c r="B542" s="21" t="s">
+        <v>667</v>
+      </c>
+      <c r="C542" s="21"/>
+      <c r="D542" s="21"/>
       <c r="E542" s="11"/>
     </row>
     <row r="543" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="2"/>
-      <c r="B543" s="18" t="s">
-        <v>673</v>
-      </c>
-      <c r="C543" s="18" t="s">
-        <v>633</v>
-      </c>
-      <c r="D543" s="18"/>
+      <c r="B543" s="21" t="s">
+        <v>668</v>
+      </c>
+      <c r="C543" s="21" t="s">
+        <v>628</v>
+      </c>
+      <c r="D543" s="21"/>
       <c r="E543" s="11"/>
     </row>
     <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="2"/>
-      <c r="B544" s="18" t="s">
-        <v>674</v>
-      </c>
-      <c r="C544" s="18"/>
-      <c r="D544" s="18"/>
+      <c r="B544" s="21" t="s">
+        <v>669</v>
+      </c>
+      <c r="C544" s="21"/>
+      <c r="D544" s="21"/>
       <c r="E544" s="11"/>
     </row>
     <row r="545" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="2"/>
-      <c r="B545" s="18" t="s">
-        <v>675</v>
-      </c>
-      <c r="C545" s="18"/>
-      <c r="D545" s="18"/>
+      <c r="B545" s="21" t="s">
+        <v>670</v>
+      </c>
+      <c r="C545" s="21"/>
+      <c r="D545" s="21"/>
       <c r="E545" s="11"/>
     </row>
     <row r="546" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="2"/>
-      <c r="B546" s="18" t="s">
-        <v>676</v>
-      </c>
-      <c r="C546" s="18"/>
-      <c r="D546" s="18"/>
+      <c r="B546" s="21" t="s">
+        <v>671</v>
+      </c>
+      <c r="C546" s="21"/>
+      <c r="D546" s="21"/>
       <c r="E546" s="11"/>
     </row>
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="2"/>
-      <c r="B547" s="18" t="s">
-        <v>677</v>
-      </c>
-      <c r="C547" s="18"/>
-      <c r="D547" s="18"/>
+      <c r="B547" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="C547" s="21"/>
+      <c r="D547" s="21"/>
       <c r="E547" s="11"/>
     </row>
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="2"/>
-      <c r="B548" s="18" t="s">
-        <v>678</v>
-      </c>
-      <c r="C548" s="18"/>
-      <c r="D548" s="18"/>
+      <c r="B548" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="C548" s="21"/>
+      <c r="D548" s="21"/>
       <c r="E548" s="11"/>
     </row>
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="2"/>
-      <c r="B549" s="18" t="s">
-        <v>679</v>
-      </c>
-      <c r="C549" s="18"/>
-      <c r="D549" s="18"/>
+      <c r="B549" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="C549" s="21"/>
+      <c r="D549" s="21"/>
       <c r="E549" s="11"/>
     </row>
     <row r="550" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="2"/>
-      <c r="B550" s="18" t="s">
-        <v>680</v>
-      </c>
-      <c r="C550" s="18" t="s">
-        <v>652</v>
-      </c>
-      <c r="D550" s="18"/>
-      <c r="E550" s="11"/>
+      <c r="B550" s="21" t="s">
+        <v>675</v>
+      </c>
+      <c r="C550" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="D550" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="E550" s="11" t="s">
+        <v>511</v>
+      </c>
     </row>
     <row r="551" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="2"/>
-      <c r="B551" s="18" t="s">
-        <v>681</v>
-      </c>
-      <c r="C551" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="D551" s="18"/>
-      <c r="E551" s="11"/>
+      <c r="B551" s="21" t="s">
+        <v>677</v>
+      </c>
+      <c r="C551" s="21" t="s">
+        <v>678</v>
+      </c>
+      <c r="D551" s="21" t="s">
+        <v>679</v>
+      </c>
+      <c r="E551" s="11" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="2"/>
-      <c r="B552" s="18" t="s">
-        <v>682</v>
-      </c>
-      <c r="C552" s="18"/>
-      <c r="D552" s="18"/>
+      <c r="B552" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="C552" s="21"/>
+      <c r="D552" s="21"/>
       <c r="E552" s="11"/>
     </row>
     <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="2"/>
-      <c r="B553" s="18"/>
-      <c r="C553" s="18"/>
-      <c r="D553" s="18"/>
+      <c r="B553" s="21"/>
+      <c r="C553" s="21"/>
+      <c r="D553" s="21"/>
       <c r="E553" s="11"/>
     </row>
     <row r="554" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="B554" s="18" t="s">
-        <v>683</v>
-      </c>
-      <c r="C554" s="18"/>
-      <c r="D554" s="18"/>
+        <v>593</v>
+      </c>
+      <c r="B554" s="21" t="s">
+        <v>681</v>
+      </c>
+      <c r="C554" s="21"/>
+      <c r="D554" s="21"/>
       <c r="E554" s="11"/>
     </row>
     <row r="555" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="2"/>
-      <c r="B555" s="18" t="s">
-        <v>684</v>
-      </c>
-      <c r="C555" s="18"/>
-      <c r="D555" s="18"/>
+      <c r="B555" s="21" t="s">
+        <v>682</v>
+      </c>
+      <c r="C555" s="21"/>
+      <c r="D555" s="21"/>
       <c r="E555" s="11"/>
     </row>
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="2"/>
-      <c r="B556" s="18" t="s">
-        <v>685</v>
-      </c>
-      <c r="C556" s="18"/>
-      <c r="D556" s="18"/>
+      <c r="B556" s="21" t="s">
+        <v>683</v>
+      </c>
+      <c r="C556" s="21"/>
+      <c r="D556" s="21"/>
       <c r="E556" s="11"/>
     </row>
     <row r="557" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="2"/>
-      <c r="B557" s="21" t="s">
-        <v>686</v>
-      </c>
-      <c r="C557" s="21" t="s">
-        <v>562</v>
-      </c>
-      <c r="D557" s="21"/>
-      <c r="E557" s="11"/>
+      <c r="B557" s="24" t="s">
+        <v>684</v>
+      </c>
+      <c r="C557" s="36" t="s">
+        <v>657</v>
+      </c>
+      <c r="D557" s="24"/>
+      <c r="E557" s="18"/>
     </row>
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="2"/>
-      <c r="B558" s="18"/>
-      <c r="C558" s="18"/>
-      <c r="D558" s="18"/>
+      <c r="B558" s="21"/>
+      <c r="C558" s="21"/>
+      <c r="D558" s="21"/>
       <c r="E558" s="11"/>
     </row>
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="2"/>
-      <c r="B559" s="18" t="s">
-        <v>687</v>
-      </c>
-      <c r="C559" s="18"/>
-      <c r="D559" s="18"/>
+      <c r="B559" s="21" t="s">
+        <v>685</v>
+      </c>
+      <c r="C559" s="21"/>
+      <c r="D559" s="21"/>
       <c r="E559" s="11"/>
     </row>
     <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A560" s="44"/>
-      <c r="B560" s="45" t="s">
-        <v>688</v>
-      </c>
-      <c r="C560" s="45"/>
-      <c r="D560" s="45"/>
-      <c r="E560" s="46"/>
+      <c r="A560" s="42"/>
+      <c r="B560" s="43" t="s">
+        <v>686</v>
+      </c>
+      <c r="C560" s="43"/>
+      <c r="D560" s="43"/>
+      <c r="E560" s="44"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/assets/responsabilidades.xlsx
+++ b/assets/responsabilidades.xlsx
@@ -441,7 +441,7 @@
     <t xml:space="preserve">Remover funcionário</t>
   </si>
   <si>
-    <t xml:space="preserve">removerFuncionario(id: int) : void</t>
+    <t xml:space="preserve">removerFuncionario(id: int) : bool</t>
   </si>
   <si>
     <t xml:space="preserve">7. O sistema confirma a eliminação.</t>
@@ -736,7 +736,7 @@
     <t xml:space="preserve">Desativar serviço de reparação</t>
   </si>
   <si>
-    <t xml:space="preserve">removerReparacao(id: int) : void</t>
+    <t xml:space="preserve">removerReparacao(id: int) : bool</t>
   </si>
   <si>
     <r>
@@ -941,7 +941,25 @@
     <t xml:space="preserve">Desativar peça</t>
   </si>
   <si>
-    <t xml:space="preserve">removerPeca(id: int) : void</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">removerPeca(id: int) : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">bool</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1346,7 +1364,25 @@
     <t xml:space="preserve">Remover devolução</t>
   </si>
   <si>
-    <t xml:space="preserve">removerDevolucao(id:int) : void</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">removerDevolucao(id:int) : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">bool</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">7. O sistema aumenta os gastos em peças do mês atual no valor de compra da peça multiplicado pela quantidade especificada na devolução</t>
@@ -1508,7 +1544,25 @@
     <t xml:space="preserve">Remover fornecedor</t>
   </si>
   <si>
-    <t xml:space="preserve">removerFornecedor(id: int) : void</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">removerFornecedor(id: int) : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">bool</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1757,7 +1811,25 @@
     <t xml:space="preserve">Remover lista</t>
   </si>
   <si>
-    <t xml:space="preserve">removerEncomenda(id: int) : void</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">removerEncomenda(id: int) : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">bool</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1916,7 +1988,25 @@
     <t xml:space="preserve">Remover cliente</t>
   </si>
   <si>
-    <t xml:space="preserve">removerCliente(id: int) : void</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">removerCliente(id: int) : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">bool</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2114,7 +2204,25 @@
     <t xml:space="preserve">Remover trotinete</t>
   </si>
   <si>
-    <t xml:space="preserve">removerTrotinete(id: int) : void</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">removerTrotinete(id: int) : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">bool</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2388,25 +2496,7 @@
     <t xml:space="preserve">Validar se peça está em stock</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">obter_quantidade_Stock_Peca_id(id: int): int &amp;&amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">obter_quantidade_Stock_Peca_ref(referencia: string): int</t>
-    </r>
+    <t xml:space="preserve">obter_quantidade_Stock_Peca_id(id: int): int &amp;&amp; obter_quantidade_Stock_Peca_ref(referencia: string): int</t>
   </si>
   <si>
     <t xml:space="preserve">4.2.2.3 O funcionário seleciona a peça e especifica a quantidade utilizada</t>
@@ -2507,7 +2597,25 @@
     <t xml:space="preserve">6. O sistema altera o estado da OS para Eliminada, regista data, hora e utilizador, impossibilita o uso dos dados da OS para estatí­sticas e apresenta mensagem de eliminação bem-sucedida</t>
   </si>
   <si>
-    <t xml:space="preserve">removerOS(id: int) : void</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">removerOS(id: int) : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">bool</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2786,7 +2894,25 @@
     <t xml:space="preserve">8.5 O sistema valida que existem peças iguais na mesma quantidade disponí­veis em stock e adiciona-as às lista de peças usadas e remove as peças defeituosas da lista de peças utilizadas</t>
   </si>
   <si>
-    <t xml:space="preserve">removerPecaConserto_OS(id_OS:int, id_Stock:int) : void</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">removerPecaConserto_OS(id_OS:int, id_Stock:int) : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">bool</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">8.6 O sistema cria um registo de devolução marcando as peças defeituosas como 'Possí­vel defeito', repõe ao stock a quantidade correspondente e gera um alerta para o gestor de stock</t>
@@ -2826,7 +2952,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2885,12 +3011,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="12"/>
@@ -3071,7 +3191,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3144,11 +3264,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3168,19 +3284,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3188,12 +3296,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -3212,10 +3316,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3224,15 +3324,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4352,7 +4444,7 @@
       <c r="B79" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="C79" s="18" t="s">
+      <c r="C79" s="11" t="s">
         <v>123</v>
       </c>
       <c r="D79" s="12" t="s">
@@ -4361,7 +4453,7 @@
       <c r="E79" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F79" s="19" t="s">
+      <c r="F79" s="18" t="s">
         <v>125</v>
       </c>
       <c r="G79" s="15"/>
@@ -5466,7 +5558,7 @@
         <v>5</v>
       </c>
       <c r="B181" s="10"/>
-      <c r="C181" s="20"/>
+      <c r="C181" s="19"/>
       <c r="D181" s="12"/>
       <c r="E181" s="12"/>
     </row>
@@ -5571,85 +5663,85 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2"/>
-      <c r="B191" s="21"/>
-      <c r="C191" s="21"/>
+      <c r="B191" s="20"/>
+      <c r="C191" s="20"/>
       <c r="D191" s="12"/>
       <c r="E191" s="12"/>
     </row>
     <row r="192" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="6"/>
-      <c r="B192" s="22" t="s">
+      <c r="B192" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="C192" s="23"/>
-      <c r="D192" s="23"/>
+      <c r="C192" s="22"/>
+      <c r="D192" s="22"/>
       <c r="E192" s="8"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B193" s="21"/>
-      <c r="C193" s="21"/>
-      <c r="D193" s="21"/>
+      <c r="B193" s="20"/>
+      <c r="C193" s="20"/>
+      <c r="D193" s="20"/>
       <c r="E193" s="11"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2"/>
-      <c r="B194" s="21" t="s">
+      <c r="B194" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C194" s="21"/>
-      <c r="D194" s="21"/>
+      <c r="C194" s="20"/>
+      <c r="D194" s="20"/>
       <c r="E194" s="11"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2"/>
-      <c r="B195" s="21" t="s">
+      <c r="B195" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="C195" s="21"/>
-      <c r="D195" s="21"/>
+      <c r="C195" s="20"/>
+      <c r="D195" s="20"/>
       <c r="E195" s="11"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2"/>
-      <c r="B196" s="21" t="s">
+      <c r="B196" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="C196" s="21" t="s">
+      <c r="C196" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="D196" s="21"/>
+      <c r="D196" s="20"/>
       <c r="E196" s="11"/>
     </row>
     <row r="197" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2"/>
-      <c r="B197" s="21" t="s">
+      <c r="B197" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="C197" s="21"/>
-      <c r="D197" s="21"/>
+      <c r="C197" s="20"/>
+      <c r="D197" s="20"/>
       <c r="E197" s="11"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2"/>
-      <c r="B198" s="21" t="s">
+      <c r="B198" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C198" s="21"/>
-      <c r="D198" s="21"/>
+      <c r="C198" s="20"/>
+      <c r="D198" s="20"/>
       <c r="E198" s="11"/>
     </row>
     <row r="199" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2"/>
-      <c r="B199" s="21" t="s">
+      <c r="B199" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="C199" s="21" t="s">
+      <c r="C199" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="D199" s="21" t="s">
+      <c r="D199" s="20" t="s">
         <v>274</v>
       </c>
       <c r="E199" s="11" t="s">
@@ -5659,24 +5751,24 @@
     </row>
     <row r="200" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2"/>
-      <c r="B200" s="21" t="s">
+      <c r="B200" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="C200" s="21" t="s">
+      <c r="C200" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="D200" s="21"/>
+      <c r="D200" s="20"/>
       <c r="E200" s="11"/>
     </row>
     <row r="201" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2"/>
-      <c r="B201" s="21" t="s">
+      <c r="B201" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="C201" s="21" t="s">
+      <c r="C201" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="D201" s="21" t="s">
+      <c r="D201" s="20" t="s">
         <v>278</v>
       </c>
       <c r="E201" s="11" t="s">
@@ -5685,13 +5777,13 @@
     </row>
     <row r="202" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2"/>
-      <c r="B202" s="21" t="s">
+      <c r="B202" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="C202" s="21" t="s">
+      <c r="C202" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="D202" s="21" t="s">
+      <c r="D202" s="20" t="s">
         <v>281</v>
       </c>
       <c r="E202" s="11" t="s">
@@ -5700,40 +5792,40 @@
     </row>
     <row r="203" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2"/>
-      <c r="B203" s="21" t="s">
+      <c r="B203" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C203" s="24" t="s">
+      <c r="C203" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="D203" s="21" t="s">
+      <c r="D203" s="20" t="s">
         <v>284</v>
       </c>
       <c r="E203" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="F203" s="25" t="s">
+      <c r="F203" s="18" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2"/>
-      <c r="B204" s="21" t="s">
+      <c r="B204" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="C204" s="21"/>
-      <c r="D204" s="21"/>
+      <c r="C204" s="20"/>
+      <c r="D204" s="20"/>
       <c r="E204" s="11"/>
     </row>
     <row r="205" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2"/>
-      <c r="B205" s="21" t="s">
+      <c r="B205" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="C205" s="21" t="s">
+      <c r="C205" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D205" s="21" t="s">
+      <c r="D205" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E205" s="11" t="s">
@@ -5742,9 +5834,9 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2"/>
-      <c r="B206" s="21"/>
-      <c r="C206" s="21"/>
-      <c r="D206" s="21"/>
+      <c r="B206" s="20"/>
+      <c r="C206" s="20"/>
+      <c r="D206" s="20"/>
       <c r="E206" s="11"/>
       <c r="F206" s="15"/>
       <c r="G206" s="1"/>
@@ -5754,255 +5846,255 @@
     </row>
     <row r="207" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="6"/>
-      <c r="B207" s="22" t="s">
+      <c r="B207" s="21" t="s">
         <v>288</v>
       </c>
-      <c r="C207" s="23"/>
-      <c r="D207" s="23"/>
+      <c r="C207" s="22"/>
+      <c r="D207" s="22"/>
       <c r="E207" s="8"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B208" s="21"/>
-      <c r="C208" s="21"/>
-      <c r="D208" s="21"/>
+      <c r="B208" s="20"/>
+      <c r="C208" s="20"/>
+      <c r="D208" s="20"/>
       <c r="E208" s="11"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2"/>
-      <c r="B209" s="21" t="s">
+      <c r="B209" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="C209" s="21"/>
-      <c r="D209" s="21"/>
+      <c r="C209" s="20"/>
+      <c r="D209" s="20"/>
       <c r="E209" s="11"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2"/>
-      <c r="B210" s="21" t="s">
+      <c r="B210" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="C210" s="21"/>
-      <c r="D210" s="21"/>
+      <c r="C210" s="20"/>
+      <c r="D210" s="20"/>
       <c r="E210" s="11"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2"/>
-      <c r="B211" s="21" t="s">
+      <c r="B211" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="C211" s="21"/>
-      <c r="D211" s="21"/>
+      <c r="C211" s="20"/>
+      <c r="D211" s="20"/>
       <c r="E211" s="11"/>
     </row>
     <row r="212" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2"/>
-      <c r="B212" s="21" t="s">
+      <c r="B212" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="C212" s="21"/>
-      <c r="D212" s="21"/>
+      <c r="C212" s="20"/>
+      <c r="D212" s="20"/>
       <c r="E212" s="11"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2"/>
-      <c r="B213" s="21" t="s">
+      <c r="B213" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="C213" s="21"/>
-      <c r="D213" s="21"/>
+      <c r="C213" s="20"/>
+      <c r="D213" s="20"/>
       <c r="E213" s="11"/>
     </row>
     <row r="214" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2"/>
-      <c r="B214" s="21" t="s">
+      <c r="B214" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="C214" s="21" t="s">
+      <c r="C214" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="D214" s="21"/>
+      <c r="D214" s="20"/>
       <c r="E214" s="11"/>
     </row>
     <row r="215" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2"/>
-      <c r="B215" s="21" t="s">
+      <c r="B215" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="C215" s="21" t="s">
+      <c r="C215" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="D215" s="21"/>
+      <c r="D215" s="20"/>
       <c r="E215" s="11"/>
     </row>
     <row r="216" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2"/>
-      <c r="B216" s="21" t="s">
+      <c r="B216" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="C216" s="21" t="s">
+      <c r="C216" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="D216" s="21"/>
+      <c r="D216" s="20"/>
       <c r="E216" s="11"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2"/>
-      <c r="B217" s="21" t="s">
+      <c r="B217" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="C217" s="21" t="s">
+      <c r="C217" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="D217" s="21"/>
+      <c r="D217" s="20"/>
       <c r="E217" s="11"/>
     </row>
     <row r="218" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2"/>
-      <c r="B218" s="21" t="s">
+      <c r="B218" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="C218" s="21" t="s">
+      <c r="C218" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D218" s="21"/>
+      <c r="D218" s="20"/>
       <c r="E218" s="11"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2"/>
-      <c r="B219" s="21"/>
-      <c r="C219" s="21"/>
-      <c r="D219" s="21"/>
+      <c r="B219" s="20"/>
+      <c r="C219" s="20"/>
+      <c r="D219" s="20"/>
       <c r="E219" s="11"/>
     </row>
     <row r="220" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B220" s="21" t="s">
+      <c r="B220" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="C220" s="21"/>
-      <c r="D220" s="21"/>
+      <c r="C220" s="20"/>
+      <c r="D220" s="20"/>
       <c r="E220" s="11"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2"/>
-      <c r="B221" s="21" t="s">
+      <c r="B221" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="C221" s="21"/>
-      <c r="D221" s="21"/>
+      <c r="C221" s="20"/>
+      <c r="D221" s="20"/>
       <c r="E221" s="11"/>
     </row>
     <row r="222" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2"/>
-      <c r="B222" s="21" t="s">
+      <c r="B222" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="C222" s="24" t="s">
+      <c r="C222" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="D222" s="21" t="s">
+      <c r="D222" s="20" t="s">
         <v>303</v>
       </c>
       <c r="E222" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="F222" s="19" t="s">
+      <c r="F222" s="18" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2"/>
-      <c r="B223" s="21" t="s">
+      <c r="B223" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="C223" s="21"/>
-      <c r="D223" s="21"/>
+      <c r="C223" s="20"/>
+      <c r="D223" s="20"/>
       <c r="E223" s="11"/>
     </row>
     <row r="224" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2"/>
-      <c r="B224" s="21" t="s">
+      <c r="B224" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="C224" s="21"/>
-      <c r="D224" s="21"/>
+      <c r="C224" s="20"/>
+      <c r="D224" s="20"/>
       <c r="E224" s="11"/>
     </row>
     <row r="225" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2"/>
-      <c r="B225" s="21" t="s">
+      <c r="B225" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="C225" s="24" t="s">
+      <c r="C225" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="D225" s="21" t="s">
+      <c r="D225" s="20" t="s">
         <v>309</v>
       </c>
       <c r="E225" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="F225" s="19" t="s">
+      <c r="F225" s="18" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2"/>
-      <c r="B226" s="21" t="s">
+      <c r="B226" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="C226" s="21"/>
-      <c r="D226" s="21"/>
+      <c r="C226" s="20"/>
+      <c r="D226" s="20"/>
       <c r="E226" s="11"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2"/>
-      <c r="B227" s="21"/>
-      <c r="C227" s="21"/>
-      <c r="D227" s="21"/>
+      <c r="B227" s="20"/>
+      <c r="C227" s="20"/>
+      <c r="D227" s="20"/>
       <c r="E227" s="11"/>
     </row>
     <row r="228" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="6"/>
-      <c r="B228" s="22" t="s">
+      <c r="B228" s="21" t="s">
         <v>312</v>
       </c>
-      <c r="C228" s="23"/>
-      <c r="D228" s="23"/>
+      <c r="C228" s="22"/>
+      <c r="D228" s="22"/>
       <c r="E228" s="8"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B229" s="21"/>
-      <c r="C229" s="21"/>
-      <c r="D229" s="21"/>
+      <c r="B229" s="20"/>
+      <c r="C229" s="20"/>
+      <c r="D229" s="20"/>
       <c r="E229" s="11"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2"/>
-      <c r="B230" s="21" t="s">
+      <c r="B230" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="C230" s="21"/>
-      <c r="D230" s="21"/>
+      <c r="C230" s="20"/>
+      <c r="D230" s="20"/>
       <c r="E230" s="11"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2"/>
-      <c r="B231" s="21" t="s">
+      <c r="B231" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="C231" s="21" t="s">
+      <c r="C231" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="D231" s="21" t="s">
+      <c r="D231" s="20" t="s">
         <v>315</v>
       </c>
       <c r="E231" s="11" t="s">
@@ -6011,42 +6103,42 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="2"/>
-      <c r="B232" s="21" t="s">
+      <c r="B232" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="C232" s="21"/>
-      <c r="D232" s="21"/>
+      <c r="C232" s="20"/>
+      <c r="D232" s="20"/>
       <c r="E232" s="11"/>
     </row>
     <row r="233" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2"/>
-      <c r="B233" s="21" t="s">
+      <c r="B233" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="C233" s="21" t="s">
+      <c r="C233" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="D233" s="21"/>
+      <c r="D233" s="20"/>
       <c r="E233" s="11"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2"/>
-      <c r="B234" s="21" t="s">
+      <c r="B234" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="C234" s="21"/>
-      <c r="D234" s="21"/>
+      <c r="C234" s="20"/>
+      <c r="D234" s="20"/>
       <c r="E234" s="11"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2"/>
-      <c r="B235" s="21" t="s">
+      <c r="B235" s="20" t="s">
         <v>320</v>
       </c>
-      <c r="C235" s="21" t="s">
+      <c r="C235" s="20" t="s">
         <v>321</v>
       </c>
-      <c r="D235" s="21" t="s">
+      <c r="D235" s="20" t="s">
         <v>322</v>
       </c>
       <c r="E235" s="11" t="s">
@@ -6055,33 +6147,33 @@
     </row>
     <row r="236" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2"/>
-      <c r="B236" s="21" t="s">
+      <c r="B236" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="C236" s="21" t="s">
+      <c r="C236" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="D236" s="21"/>
+      <c r="D236" s="20"/>
       <c r="E236" s="11"/>
     </row>
     <row r="237" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="2"/>
-      <c r="B237" s="21" t="s">
+      <c r="B237" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="C237" s="21"/>
-      <c r="D237" s="21"/>
+      <c r="C237" s="20"/>
+      <c r="D237" s="20"/>
       <c r="E237" s="11"/>
     </row>
     <row r="238" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2"/>
-      <c r="B238" s="21" t="s">
+      <c r="B238" s="20" t="s">
         <v>325</v>
       </c>
-      <c r="C238" s="21" t="s">
+      <c r="C238" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D238" s="21" t="s">
+      <c r="D238" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E238" s="11" t="s">
@@ -6090,9 +6182,9 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="2"/>
-      <c r="B239" s="21"/>
-      <c r="C239" s="21"/>
-      <c r="D239" s="21"/>
+      <c r="B239" s="20"/>
+      <c r="C239" s="20"/>
+      <c r="D239" s="20"/>
       <c r="E239" s="11"/>
       <c r="G239" s="1"/>
       <c r="H239" s="1"/>
@@ -6101,80 +6193,80 @@
     </row>
     <row r="240" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="6"/>
-      <c r="B240" s="22" t="s">
+      <c r="B240" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="C240" s="23"/>
-      <c r="D240" s="23"/>
+      <c r="C240" s="22"/>
+      <c r="D240" s="22"/>
       <c r="E240" s="8"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B241" s="21"/>
-      <c r="C241" s="21"/>
-      <c r="D241" s="21"/>
+      <c r="B241" s="20"/>
+      <c r="C241" s="20"/>
+      <c r="D241" s="20"/>
       <c r="E241" s="11"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2"/>
-      <c r="B242" s="21" t="s">
+      <c r="B242" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="C242" s="21"/>
-      <c r="D242" s="21"/>
+      <c r="C242" s="20"/>
+      <c r="D242" s="20"/>
       <c r="E242" s="11"/>
     </row>
     <row r="243" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2"/>
-      <c r="B243" s="21" t="s">
+      <c r="B243" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="C243" s="21"/>
-      <c r="D243" s="21"/>
+      <c r="C243" s="20"/>
+      <c r="D243" s="20"/>
       <c r="E243" s="11"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2"/>
-      <c r="B244" s="21" t="s">
+      <c r="B244" s="20" t="s">
         <v>329</v>
       </c>
-      <c r="C244" s="21"/>
-      <c r="D244" s="21"/>
+      <c r="C244" s="20"/>
+      <c r="D244" s="20"/>
       <c r="E244" s="11"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2"/>
-      <c r="B245" s="21" t="s">
+      <c r="B245" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C245" s="21" t="s">
+      <c r="C245" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D245" s="21"/>
+      <c r="D245" s="20"/>
       <c r="E245" s="11"/>
     </row>
     <row r="246" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="2"/>
-      <c r="B246" s="21" t="s">
+      <c r="B246" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="C246" s="21" t="s">
+      <c r="C246" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="D246" s="21"/>
+      <c r="D246" s="20"/>
       <c r="E246" s="11"/>
     </row>
     <row r="247" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="2"/>
-      <c r="B247" s="21" t="s">
+      <c r="B247" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="C247" s="21" t="s">
+      <c r="C247" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="D247" s="21" t="s">
+      <c r="D247" s="20" t="s">
         <v>334</v>
       </c>
       <c r="E247" s="11" t="s">
@@ -6183,13 +6275,13 @@
     </row>
     <row r="248" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2"/>
-      <c r="B248" s="21" t="s">
+      <c r="B248" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="C248" s="21" t="s">
+      <c r="C248" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D248" s="21" t="s">
+      <c r="D248" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E248" s="11" t="s">
@@ -6198,47 +6290,47 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2"/>
-      <c r="B249" s="21"/>
-      <c r="C249" s="21"/>
-      <c r="D249" s="21"/>
+      <c r="B249" s="20"/>
+      <c r="C249" s="20"/>
+      <c r="D249" s="20"/>
       <c r="E249" s="11"/>
     </row>
     <row r="250" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="6"/>
-      <c r="B250" s="22" t="s">
+      <c r="B250" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="C250" s="23"/>
-      <c r="D250" s="23"/>
+      <c r="C250" s="22"/>
+      <c r="D250" s="22"/>
       <c r="E250" s="8"/>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B251" s="21"/>
-      <c r="C251" s="21"/>
-      <c r="D251" s="21"/>
+      <c r="B251" s="20"/>
+      <c r="C251" s="20"/>
+      <c r="D251" s="20"/>
       <c r="E251" s="11"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2"/>
-      <c r="B252" s="21" t="s">
+      <c r="B252" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="C252" s="21"/>
-      <c r="D252" s="21"/>
+      <c r="C252" s="20"/>
+      <c r="D252" s="20"/>
       <c r="E252" s="11"/>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2"/>
-      <c r="B253" s="21" t="s">
+      <c r="B253" s="20" t="s">
         <v>338</v>
       </c>
-      <c r="C253" s="21" t="s">
+      <c r="C253" s="20" t="s">
         <v>339</v>
       </c>
-      <c r="D253" s="21" t="s">
+      <c r="D253" s="20" t="s">
         <v>340</v>
       </c>
       <c r="E253" s="11" t="s">
@@ -6247,62 +6339,62 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="2"/>
-      <c r="B254" s="21" t="s">
+      <c r="B254" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="C254" s="21"/>
-      <c r="D254" s="21"/>
+      <c r="C254" s="20"/>
+      <c r="D254" s="20"/>
       <c r="E254" s="11"/>
     </row>
     <row r="255" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="2"/>
-      <c r="B255" s="21" t="s">
+      <c r="B255" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="C255" s="21"/>
-      <c r="D255" s="21"/>
+      <c r="C255" s="20"/>
+      <c r="D255" s="20"/>
       <c r="E255" s="11"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="2"/>
-      <c r="B256" s="21" t="s">
+      <c r="B256" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="C256" s="21"/>
-      <c r="D256" s="21"/>
+      <c r="C256" s="20"/>
+      <c r="D256" s="20"/>
       <c r="E256" s="11"/>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="2"/>
-      <c r="B257" s="21" t="s">
+      <c r="B257" s="20" t="s">
         <v>342</v>
       </c>
-      <c r="C257" s="21" t="s">
+      <c r="C257" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D257" s="21"/>
+      <c r="D257" s="20"/>
       <c r="E257" s="11"/>
     </row>
     <row r="258" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="2"/>
-      <c r="B258" s="21" t="s">
+      <c r="B258" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="C258" s="21" t="s">
+      <c r="C258" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="D258" s="21"/>
+      <c r="D258" s="20"/>
       <c r="E258" s="11"/>
     </row>
     <row r="259" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2"/>
-      <c r="B259" s="21" t="s">
+      <c r="B259" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="C259" s="21" t="s">
+      <c r="C259" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D259" s="21" t="s">
+      <c r="D259" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E259" s="11" t="s">
@@ -6311,13 +6403,13 @@
     </row>
     <row r="260" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="2"/>
-      <c r="B260" s="21" t="s">
+      <c r="B260" s="20" t="s">
         <v>345</v>
       </c>
-      <c r="C260" s="21" t="s">
+      <c r="C260" s="20" t="s">
         <v>346</v>
       </c>
-      <c r="D260" s="21" t="s">
+      <c r="D260" s="20" t="s">
         <v>347</v>
       </c>
       <c r="E260" s="11" t="s">
@@ -6326,47 +6418,47 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="2"/>
-      <c r="B261" s="21"/>
-      <c r="C261" s="21"/>
-      <c r="D261" s="21"/>
+      <c r="B261" s="20"/>
+      <c r="C261" s="20"/>
+      <c r="D261" s="20"/>
       <c r="E261" s="11"/>
     </row>
     <row r="262" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="6"/>
-      <c r="B262" s="22" t="s">
+      <c r="B262" s="21" t="s">
         <v>348</v>
       </c>
-      <c r="C262" s="23"/>
-      <c r="D262" s="23"/>
+      <c r="C262" s="22"/>
+      <c r="D262" s="22"/>
       <c r="E262" s="8"/>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B263" s="21"/>
-      <c r="C263" s="21"/>
-      <c r="D263" s="21"/>
+      <c r="B263" s="20"/>
+      <c r="C263" s="20"/>
+      <c r="D263" s="20"/>
       <c r="E263" s="11"/>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="2"/>
-      <c r="B264" s="21" t="s">
+      <c r="B264" s="20" t="s">
         <v>349</v>
       </c>
-      <c r="C264" s="21"/>
-      <c r="D264" s="21"/>
+      <c r="C264" s="20"/>
+      <c r="D264" s="20"/>
       <c r="E264" s="11"/>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="2"/>
-      <c r="B265" s="21" t="s">
+      <c r="B265" s="20" t="s">
         <v>350</v>
       </c>
-      <c r="C265" s="21" t="s">
+      <c r="C265" s="20" t="s">
         <v>339</v>
       </c>
-      <c r="D265" s="21" t="s">
+      <c r="D265" s="20" t="s">
         <v>340</v>
       </c>
       <c r="E265" s="11" t="s">
@@ -6375,31 +6467,31 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="2"/>
-      <c r="B266" s="21" t="s">
+      <c r="B266" s="20" t="s">
         <v>351</v>
       </c>
-      <c r="C266" s="21"/>
-      <c r="D266" s="21"/>
+      <c r="C266" s="20"/>
+      <c r="D266" s="20"/>
       <c r="E266" s="11"/>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2"/>
-      <c r="B267" s="21" t="s">
+      <c r="B267" s="20" t="s">
         <v>352</v>
       </c>
-      <c r="C267" s="21"/>
-      <c r="D267" s="21"/>
+      <c r="C267" s="20"/>
+      <c r="D267" s="20"/>
       <c r="E267" s="11"/>
     </row>
     <row r="268" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="2"/>
-      <c r="B268" s="21" t="s">
+      <c r="B268" s="20" t="s">
         <v>353</v>
       </c>
-      <c r="C268" s="21" t="s">
+      <c r="C268" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D268" s="21" t="s">
+      <c r="D268" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E268" s="11" t="s">
@@ -6408,13 +6500,13 @@
     </row>
     <row r="269" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="2"/>
-      <c r="B269" s="21" t="s">
+      <c r="B269" s="20" t="s">
         <v>354</v>
       </c>
-      <c r="C269" s="21" t="s">
+      <c r="C269" s="20" t="s">
         <v>355</v>
       </c>
-      <c r="D269" s="21" t="s">
+      <c r="D269" s="20" t="s">
         <v>356</v>
       </c>
       <c r="E269" s="11" t="s">
@@ -6423,73 +6515,73 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="2"/>
-      <c r="B270" s="21"/>
-      <c r="C270" s="21"/>
-      <c r="D270" s="21"/>
+      <c r="B270" s="20"/>
+      <c r="C270" s="20"/>
+      <c r="D270" s="20"/>
       <c r="E270" s="11"/>
       <c r="F270" s="15"/>
       <c r="G270" s="1"/>
     </row>
     <row r="271" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="6"/>
-      <c r="B271" s="22" t="s">
+      <c r="B271" s="21" t="s">
         <v>357</v>
       </c>
-      <c r="C271" s="23"/>
-      <c r="D271" s="23"/>
+      <c r="C271" s="22"/>
+      <c r="D271" s="22"/>
       <c r="E271" s="8"/>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B272" s="21"/>
-      <c r="C272" s="21"/>
-      <c r="D272" s="21"/>
+      <c r="B272" s="20"/>
+      <c r="C272" s="20"/>
+      <c r="D272" s="20"/>
       <c r="E272" s="11"/>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="2"/>
-      <c r="B273" s="21" t="s">
+      <c r="B273" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="C273" s="21"/>
-      <c r="D273" s="21"/>
+      <c r="C273" s="20"/>
+      <c r="D273" s="20"/>
       <c r="E273" s="11"/>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="2"/>
-      <c r="B274" s="21" t="s">
+      <c r="B274" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="C274" s="21"/>
-      <c r="D274" s="21"/>
+      <c r="C274" s="20"/>
+      <c r="D274" s="20"/>
       <c r="E274" s="11"/>
     </row>
     <row r="275" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="2"/>
-      <c r="B275" s="21" t="s">
+      <c r="B275" s="20" t="s">
         <v>360</v>
       </c>
-      <c r="C275" s="21" t="s">
+      <c r="C275" s="20" t="s">
         <v>361</v>
       </c>
-      <c r="D275" s="26" t="s">
+      <c r="D275" s="23" t="s">
         <v>362</v>
       </c>
-      <c r="E275" s="27" t="s">
+      <c r="E275" s="24" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="2"/>
-      <c r="B276" s="21" t="s">
+      <c r="B276" s="20" t="s">
         <v>363</v>
       </c>
-      <c r="C276" s="21" t="s">
+      <c r="C276" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="D276" s="21" t="s">
+      <c r="D276" s="20" t="s">
         <v>365</v>
       </c>
       <c r="E276" s="11" t="s">
@@ -6498,69 +6590,69 @@
     </row>
     <row r="277" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="2"/>
-      <c r="B277" s="21" t="s">
+      <c r="B277" s="20" t="s">
         <v>366</v>
       </c>
-      <c r="C277" s="21"/>
-      <c r="D277" s="21"/>
+      <c r="C277" s="20"/>
+      <c r="D277" s="20"/>
       <c r="E277" s="11"/>
     </row>
     <row r="278" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="2"/>
-      <c r="B278" s="21" t="s">
+      <c r="B278" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="C278" s="21"/>
-      <c r="D278" s="21"/>
+      <c r="C278" s="20"/>
+      <c r="D278" s="20"/>
       <c r="E278" s="11"/>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="2"/>
-      <c r="B279" s="21" t="s">
+      <c r="B279" s="20" t="s">
         <v>368</v>
       </c>
-      <c r="C279" s="21"/>
-      <c r="D279" s="21"/>
+      <c r="C279" s="20"/>
+      <c r="D279" s="20"/>
       <c r="E279" s="11"/>
     </row>
     <row r="280" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="2"/>
-      <c r="B280" s="21" t="s">
+      <c r="B280" s="20" t="s">
         <v>369</v>
       </c>
-      <c r="C280" s="21"/>
-      <c r="D280" s="21"/>
+      <c r="C280" s="20"/>
+      <c r="D280" s="20"/>
       <c r="E280" s="11"/>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="2"/>
-      <c r="B281" s="21" t="s">
+      <c r="B281" s="20" t="s">
         <v>370</v>
       </c>
-      <c r="C281" s="21"/>
-      <c r="D281" s="21"/>
+      <c r="C281" s="20"/>
+      <c r="D281" s="20"/>
       <c r="E281" s="11"/>
     </row>
     <row r="282" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="2"/>
-      <c r="B282" s="21" t="s">
+      <c r="B282" s="20" t="s">
         <v>371</v>
       </c>
-      <c r="C282" s="21" t="s">
+      <c r="C282" s="20" t="s">
         <v>372</v>
       </c>
-      <c r="D282" s="21"/>
+      <c r="D282" s="20"/>
       <c r="E282" s="11"/>
     </row>
     <row r="283" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="2"/>
-      <c r="B283" s="21" t="s">
+      <c r="B283" s="20" t="s">
         <v>373</v>
       </c>
-      <c r="C283" s="21" t="s">
+      <c r="C283" s="20" t="s">
         <v>374</v>
       </c>
-      <c r="D283" s="21" t="s">
+      <c r="D283" s="20" t="s">
         <v>375</v>
       </c>
       <c r="E283" s="11" t="s">
@@ -6569,13 +6661,13 @@
     </row>
     <row r="284" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="2"/>
-      <c r="B284" s="21" t="s">
+      <c r="B284" s="20" t="s">
         <v>376</v>
       </c>
-      <c r="C284" s="21" t="s">
+      <c r="C284" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D284" s="21" t="s">
+      <c r="D284" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E284" s="11" t="s">
@@ -6584,47 +6676,47 @@
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="2"/>
-      <c r="B285" s="21"/>
-      <c r="C285" s="21"/>
-      <c r="D285" s="21"/>
+      <c r="B285" s="20"/>
+      <c r="C285" s="20"/>
+      <c r="D285" s="20"/>
       <c r="E285" s="11"/>
     </row>
     <row r="286" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="6"/>
-      <c r="B286" s="22" t="s">
+      <c r="B286" s="21" t="s">
         <v>377</v>
       </c>
-      <c r="C286" s="23"/>
-      <c r="D286" s="23"/>
+      <c r="C286" s="22"/>
+      <c r="D286" s="22"/>
       <c r="E286" s="8"/>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B287" s="21"/>
-      <c r="C287" s="21"/>
-      <c r="D287" s="21"/>
+      <c r="B287" s="20"/>
+      <c r="C287" s="20"/>
+      <c r="D287" s="20"/>
       <c r="E287" s="11"/>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="2"/>
-      <c r="B288" s="21" t="s">
+      <c r="B288" s="20" t="s">
         <v>378</v>
       </c>
-      <c r="C288" s="21"/>
-      <c r="D288" s="21"/>
+      <c r="C288" s="20"/>
+      <c r="D288" s="20"/>
       <c r="E288" s="11"/>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="2"/>
-      <c r="B289" s="21" t="s">
+      <c r="B289" s="20" t="s">
         <v>379</v>
       </c>
-      <c r="C289" s="21" t="s">
+      <c r="C289" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="D289" s="21" t="s">
+      <c r="D289" s="20" t="s">
         <v>381</v>
       </c>
       <c r="E289" s="11" t="s">
@@ -6633,22 +6725,22 @@
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="2"/>
-      <c r="B290" s="21" t="s">
+      <c r="B290" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="C290" s="21"/>
-      <c r="D290" s="21"/>
+      <c r="C290" s="20"/>
+      <c r="D290" s="20"/>
       <c r="E290" s="11"/>
     </row>
     <row r="291" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="2"/>
-      <c r="B291" s="21" t="s">
+      <c r="B291" s="20" t="s">
         <v>383</v>
       </c>
-      <c r="C291" s="21" t="s">
+      <c r="C291" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="D291" s="21" t="s">
+      <c r="D291" s="20" t="s">
         <v>385</v>
       </c>
       <c r="E291" s="11" t="s">
@@ -6657,31 +6749,31 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2"/>
-      <c r="B292" s="21" t="s">
+      <c r="B292" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="C292" s="21"/>
-      <c r="D292" s="21"/>
+      <c r="C292" s="20"/>
+      <c r="D292" s="20"/>
       <c r="E292" s="11"/>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="2"/>
-      <c r="B293" s="21" t="s">
+      <c r="B293" s="20" t="s">
         <v>387</v>
       </c>
-      <c r="C293" s="21"/>
-      <c r="D293" s="21"/>
+      <c r="C293" s="20"/>
+      <c r="D293" s="20"/>
       <c r="E293" s="11"/>
     </row>
     <row r="294" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="2"/>
-      <c r="B294" s="21" t="s">
+      <c r="B294" s="20" t="s">
         <v>388</v>
       </c>
-      <c r="C294" s="21" t="s">
+      <c r="C294" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D294" s="21" t="s">
+      <c r="D294" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E294" s="11" t="s">
@@ -6690,24 +6782,24 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="2"/>
-      <c r="B295" s="21" t="s">
+      <c r="B295" s="20" t="s">
         <v>389</v>
       </c>
-      <c r="C295" s="21" t="s">
+      <c r="C295" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="D295" s="21"/>
+      <c r="D295" s="20"/>
       <c r="E295" s="11"/>
     </row>
     <row r="296" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="2"/>
-      <c r="B296" s="21" t="s">
+      <c r="B296" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="C296" s="21" t="s">
+      <c r="C296" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="D296" s="21" t="s">
+      <c r="D296" s="20" t="s">
         <v>392</v>
       </c>
       <c r="E296" s="11" t="s">
@@ -6716,60 +6808,60 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="2"/>
-      <c r="B297" s="21"/>
-      <c r="C297" s="21"/>
-      <c r="D297" s="21"/>
+      <c r="B297" s="20"/>
+      <c r="C297" s="20"/>
+      <c r="D297" s="20"/>
       <c r="E297" s="11"/>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B298" s="21" t="s">
+      <c r="B298" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="C298" s="21"/>
-      <c r="D298" s="21"/>
+      <c r="C298" s="20"/>
+      <c r="D298" s="20"/>
       <c r="E298" s="11"/>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="2"/>
-      <c r="B299" s="21" t="s">
+      <c r="B299" s="20" t="s">
         <v>394</v>
       </c>
-      <c r="C299" s="21"/>
-      <c r="D299" s="21"/>
+      <c r="C299" s="20"/>
+      <c r="D299" s="20"/>
       <c r="E299" s="11"/>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="2"/>
-      <c r="B300" s="21" t="s">
+      <c r="B300" s="20" t="s">
         <v>395</v>
       </c>
-      <c r="C300" s="21"/>
-      <c r="D300" s="21"/>
+      <c r="C300" s="20"/>
+      <c r="D300" s="20"/>
       <c r="E300" s="11"/>
     </row>
     <row r="301" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="2"/>
-      <c r="B301" s="21" t="s">
+      <c r="B301" s="20" t="s">
         <v>396</v>
       </c>
-      <c r="C301" s="21" t="s">
+      <c r="C301" s="20" t="s">
         <v>397</v>
       </c>
-      <c r="D301" s="21"/>
+      <c r="D301" s="20"/>
       <c r="E301" s="11"/>
     </row>
     <row r="302" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="2"/>
-      <c r="B302" s="21" t="s">
+      <c r="B302" s="20" t="s">
         <v>398</v>
       </c>
-      <c r="C302" s="21" t="s">
+      <c r="C302" s="20" t="s">
         <v>399</v>
       </c>
-      <c r="D302" s="21" t="s">
+      <c r="D302" s="20" t="s">
         <v>400</v>
       </c>
       <c r="E302" s="11" t="s">
@@ -6778,71 +6870,71 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="2"/>
-      <c r="B303" s="21" t="s">
+      <c r="B303" s="20" t="s">
         <v>401</v>
       </c>
-      <c r="C303" s="21"/>
-      <c r="D303" s="21"/>
+      <c r="C303" s="20"/>
+      <c r="D303" s="20"/>
       <c r="E303" s="11"/>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="2"/>
-      <c r="B304" s="21" t="s">
+      <c r="B304" s="20" t="s">
         <v>402</v>
       </c>
-      <c r="C304" s="21"/>
-      <c r="D304" s="21"/>
+      <c r="C304" s="20"/>
+      <c r="D304" s="20"/>
       <c r="E304" s="11"/>
     </row>
     <row r="305" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="2"/>
-      <c r="B305" s="21" t="s">
+      <c r="B305" s="20" t="s">
         <v>403</v>
       </c>
-      <c r="C305" s="21"/>
-      <c r="D305" s="21"/>
+      <c r="C305" s="20"/>
+      <c r="D305" s="20"/>
       <c r="E305" s="11"/>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="2"/>
-      <c r="B306" s="21" t="s">
+      <c r="B306" s="20" t="s">
         <v>404</v>
       </c>
-      <c r="C306" s="21"/>
-      <c r="D306" s="21"/>
+      <c r="C306" s="20"/>
+      <c r="D306" s="20"/>
       <c r="E306" s="11"/>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="2"/>
-      <c r="B307" s="21" t="s">
+      <c r="B307" s="20" t="s">
         <v>405</v>
       </c>
-      <c r="C307" s="21" t="s">
+      <c r="C307" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="D307" s="21"/>
+      <c r="D307" s="20"/>
       <c r="E307" s="11"/>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="2"/>
-      <c r="B308" s="21" t="s">
+      <c r="B308" s="20" t="s">
         <v>407</v>
       </c>
-      <c r="C308" s="21" t="s">
+      <c r="C308" s="20" t="s">
         <v>408</v>
       </c>
-      <c r="D308" s="21"/>
+      <c r="D308" s="20"/>
       <c r="E308" s="11"/>
     </row>
     <row r="309" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="2"/>
-      <c r="B309" s="21" t="s">
+      <c r="B309" s="20" t="s">
         <v>409</v>
       </c>
-      <c r="C309" s="21" t="s">
+      <c r="C309" s="20" t="s">
         <v>399</v>
       </c>
-      <c r="D309" s="21" t="s">
+      <c r="D309" s="20" t="s">
         <v>410</v>
       </c>
       <c r="E309" s="11" t="s">
@@ -6851,83 +6943,83 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="2"/>
-      <c r="B310" s="21" t="s">
+      <c r="B310" s="20" t="s">
         <v>411</v>
       </c>
-      <c r="C310" s="21"/>
-      <c r="D310" s="21"/>
+      <c r="C310" s="20"/>
+      <c r="D310" s="20"/>
       <c r="E310" s="11"/>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="2"/>
-      <c r="B311" s="21"/>
-      <c r="C311" s="21"/>
-      <c r="D311" s="21"/>
+      <c r="B311" s="20"/>
+      <c r="C311" s="20"/>
+      <c r="D311" s="20"/>
       <c r="E311" s="11"/>
     </row>
     <row r="312" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="6"/>
-      <c r="B312" s="22" t="s">
+      <c r="B312" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="C312" s="23"/>
-      <c r="D312" s="23"/>
+      <c r="C312" s="22"/>
+      <c r="D312" s="22"/>
       <c r="E312" s="8"/>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B313" s="20"/>
-      <c r="C313" s="21"/>
-      <c r="D313" s="21"/>
+      <c r="B313" s="19"/>
+      <c r="C313" s="20"/>
+      <c r="D313" s="20"/>
       <c r="E313" s="11"/>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="2"/>
-      <c r="B314" s="21" t="s">
+      <c r="B314" s="20" t="s">
         <v>413</v>
       </c>
-      <c r="C314" s="21"/>
-      <c r="D314" s="21"/>
+      <c r="C314" s="20"/>
+      <c r="D314" s="20"/>
       <c r="E314" s="11"/>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="2"/>
-      <c r="B315" s="21" t="s">
+      <c r="B315" s="20" t="s">
         <v>414</v>
       </c>
-      <c r="C315" s="21"/>
-      <c r="D315" s="21"/>
+      <c r="C315" s="20"/>
+      <c r="D315" s="20"/>
       <c r="E315" s="11"/>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="2"/>
-      <c r="B316" s="21" t="s">
+      <c r="B316" s="20" t="s">
         <v>415</v>
       </c>
-      <c r="C316" s="21"/>
-      <c r="D316" s="21"/>
+      <c r="C316" s="20"/>
+      <c r="D316" s="20"/>
       <c r="E316" s="11"/>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="2"/>
-      <c r="B317" s="21" t="s">
+      <c r="B317" s="20" t="s">
         <v>352</v>
       </c>
-      <c r="C317" s="21"/>
-      <c r="D317" s="21"/>
+      <c r="C317" s="20"/>
+      <c r="D317" s="20"/>
       <c r="E317" s="11"/>
     </row>
     <row r="318" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="2"/>
-      <c r="B318" s="21" t="s">
+      <c r="B318" s="20" t="s">
         <v>416</v>
       </c>
-      <c r="C318" s="21" t="s">
+      <c r="C318" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D318" s="21" t="s">
+      <c r="D318" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E318" s="11" t="s">
@@ -6936,13 +7028,13 @@
     </row>
     <row r="319" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="2"/>
-      <c r="B319" s="21" t="s">
+      <c r="B319" s="20" t="s">
         <v>417</v>
       </c>
-      <c r="C319" s="21" t="s">
+      <c r="C319" s="20" t="s">
         <v>418</v>
       </c>
-      <c r="D319" s="21" t="s">
+      <c r="D319" s="20" t="s">
         <v>419</v>
       </c>
       <c r="E319" s="11" t="s">
@@ -6951,109 +7043,109 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="2"/>
-      <c r="B320" s="20"/>
-      <c r="C320" s="21"/>
-      <c r="D320" s="21"/>
+      <c r="B320" s="19"/>
+      <c r="C320" s="20"/>
+      <c r="D320" s="20"/>
       <c r="E320" s="11"/>
     </row>
     <row r="321" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="6"/>
-      <c r="B321" s="22" t="s">
+      <c r="B321" s="21" t="s">
         <v>420</v>
       </c>
-      <c r="C321" s="23"/>
-      <c r="D321" s="23"/>
+      <c r="C321" s="22"/>
+      <c r="D321" s="22"/>
       <c r="E321" s="8"/>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B322" s="20"/>
-      <c r="C322" s="21"/>
-      <c r="D322" s="21"/>
+      <c r="B322" s="19"/>
+      <c r="C322" s="20"/>
+      <c r="D322" s="20"/>
       <c r="E322" s="11"/>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="2"/>
-      <c r="B323" s="21" t="s">
+      <c r="B323" s="20" t="s">
         <v>421</v>
       </c>
-      <c r="C323" s="21"/>
-      <c r="D323" s="21"/>
+      <c r="C323" s="20"/>
+      <c r="D323" s="20"/>
       <c r="E323" s="11"/>
     </row>
     <row r="324" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="2"/>
-      <c r="B324" s="21" t="s">
+      <c r="B324" s="20" t="s">
         <v>422</v>
       </c>
-      <c r="C324" s="21"/>
-      <c r="D324" s="21"/>
+      <c r="C324" s="20"/>
+      <c r="D324" s="20"/>
       <c r="E324" s="11"/>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="2"/>
-      <c r="B325" s="21" t="s">
+      <c r="B325" s="20" t="s">
         <v>329</v>
       </c>
-      <c r="C325" s="21"/>
-      <c r="D325" s="21"/>
+      <c r="C325" s="20"/>
+      <c r="D325" s="20"/>
       <c r="E325" s="11"/>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="2"/>
-      <c r="B326" s="21" t="s">
+      <c r="B326" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C326" s="21" t="s">
+      <c r="C326" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D326" s="21"/>
+      <c r="D326" s="20"/>
       <c r="E326" s="11"/>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="2"/>
-      <c r="B327" s="21" t="s">
+      <c r="B327" s="20" t="s">
         <v>423</v>
       </c>
-      <c r="C327" s="21" t="s">
+      <c r="C327" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D327" s="21"/>
+      <c r="D327" s="20"/>
       <c r="E327" s="11"/>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="2"/>
-      <c r="B328" s="21" t="s">
+      <c r="B328" s="20" t="s">
         <v>424</v>
       </c>
-      <c r="C328" s="21" t="s">
+      <c r="C328" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="D328" s="21"/>
+      <c r="D328" s="20"/>
       <c r="E328" s="11"/>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="2"/>
-      <c r="B329" s="21" t="s">
+      <c r="B329" s="20" t="s">
         <v>426</v>
       </c>
-      <c r="C329" s="21" t="s">
+      <c r="C329" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="D329" s="21"/>
+      <c r="D329" s="20"/>
       <c r="E329" s="11"/>
     </row>
     <row r="330" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="2"/>
-      <c r="B330" s="21" t="s">
+      <c r="B330" s="20" t="s">
         <v>427</v>
       </c>
-      <c r="C330" s="21" t="s">
+      <c r="C330" s="20" t="s">
         <v>428</v>
       </c>
-      <c r="D330" s="21" t="s">
+      <c r="D330" s="20" t="s">
         <v>429</v>
       </c>
       <c r="E330" s="11" t="s">
@@ -7062,13 +7154,13 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="2"/>
-      <c r="B331" s="21" t="s">
+      <c r="B331" s="20" t="s">
         <v>431</v>
       </c>
-      <c r="C331" s="21" t="s">
+      <c r="C331" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D331" s="21" t="s">
+      <c r="D331" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E331" s="11" t="s">
@@ -7077,47 +7169,47 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="2"/>
-      <c r="B332" s="21"/>
-      <c r="C332" s="21"/>
-      <c r="D332" s="21"/>
+      <c r="B332" s="20"/>
+      <c r="C332" s="20"/>
+      <c r="D332" s="20"/>
       <c r="E332" s="11"/>
     </row>
     <row r="333" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="6"/>
-      <c r="B333" s="22" t="s">
+      <c r="B333" s="21" t="s">
         <v>432</v>
       </c>
-      <c r="C333" s="23"/>
-      <c r="D333" s="23"/>
+      <c r="C333" s="22"/>
+      <c r="D333" s="22"/>
       <c r="E333" s="8"/>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B334" s="20"/>
-      <c r="C334" s="21"/>
-      <c r="D334" s="21"/>
+      <c r="B334" s="19"/>
+      <c r="C334" s="20"/>
+      <c r="D334" s="20"/>
       <c r="E334" s="11"/>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="2"/>
-      <c r="B335" s="21" t="s">
+      <c r="B335" s="20" t="s">
         <v>433</v>
       </c>
-      <c r="C335" s="21"/>
-      <c r="D335" s="21"/>
+      <c r="C335" s="20"/>
+      <c r="D335" s="20"/>
       <c r="E335" s="11"/>
     </row>
     <row r="336" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="2"/>
-      <c r="B336" s="21" t="s">
+      <c r="B336" s="20" t="s">
         <v>434</v>
       </c>
-      <c r="C336" s="21" t="s">
+      <c r="C336" s="20" t="s">
         <v>435</v>
       </c>
-      <c r="D336" s="21" t="s">
+      <c r="D336" s="20" t="s">
         <v>436</v>
       </c>
       <c r="E336" s="11" t="s">
@@ -7126,84 +7218,84 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="2"/>
-      <c r="B337" s="21" t="s">
+      <c r="B337" s="20" t="s">
         <v>437</v>
       </c>
-      <c r="C337" s="21"/>
-      <c r="D337" s="21"/>
+      <c r="C337" s="20"/>
+      <c r="D337" s="20"/>
       <c r="E337" s="11"/>
     </row>
     <row r="338" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="2"/>
-      <c r="B338" s="21" t="s">
+      <c r="B338" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="C338" s="21"/>
-      <c r="D338" s="21"/>
+      <c r="C338" s="20"/>
+      <c r="D338" s="20"/>
       <c r="E338" s="11"/>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="2"/>
-      <c r="B339" s="21" t="s">
+      <c r="B339" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="C339" s="21"/>
-      <c r="D339" s="21"/>
+      <c r="C339" s="20"/>
+      <c r="D339" s="20"/>
       <c r="E339" s="11"/>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="2"/>
-      <c r="B340" s="21" t="s">
+      <c r="B340" s="20" t="s">
         <v>342</v>
       </c>
-      <c r="C340" s="21" t="s">
+      <c r="C340" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D340" s="21"/>
+      <c r="D340" s="20"/>
       <c r="E340" s="11"/>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="2"/>
-      <c r="B341" s="21" t="s">
+      <c r="B341" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="C341" s="21" t="s">
+      <c r="C341" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D341" s="21"/>
+      <c r="D341" s="20"/>
       <c r="E341" s="11"/>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="2"/>
-      <c r="B342" s="21" t="s">
+      <c r="B342" s="20" t="s">
         <v>439</v>
       </c>
-      <c r="C342" s="21" t="s">
+      <c r="C342" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="D342" s="21"/>
+      <c r="D342" s="20"/>
       <c r="E342" s="11"/>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="2"/>
-      <c r="B343" s="21" t="s">
+      <c r="B343" s="20" t="s">
         <v>440</v>
       </c>
-      <c r="C343" s="21" t="s">
+      <c r="C343" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="D343" s="21"/>
+      <c r="D343" s="20"/>
       <c r="E343" s="11"/>
     </row>
     <row r="344" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="2"/>
-      <c r="B344" s="21" t="s">
+      <c r="B344" s="20" t="s">
         <v>441</v>
       </c>
-      <c r="C344" s="21" t="s">
+      <c r="C344" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D344" s="21" t="s">
+      <c r="D344" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E344" s="11" t="s">
@@ -7212,13 +7304,13 @@
     </row>
     <row r="345" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="2"/>
-      <c r="B345" s="21" t="s">
+      <c r="B345" s="20" t="s">
         <v>442</v>
       </c>
-      <c r="C345" s="21" t="s">
+      <c r="C345" s="20" t="s">
         <v>443</v>
       </c>
-      <c r="D345" s="21" t="s">
+      <c r="D345" s="20" t="s">
         <v>444</v>
       </c>
       <c r="E345" s="11" t="s">
@@ -7227,47 +7319,47 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="2"/>
-      <c r="B346" s="21"/>
-      <c r="C346" s="21"/>
-      <c r="D346" s="21"/>
+      <c r="B346" s="20"/>
+      <c r="C346" s="20"/>
+      <c r="D346" s="20"/>
       <c r="E346" s="11"/>
     </row>
     <row r="347" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="6"/>
-      <c r="B347" s="22" t="s">
+      <c r="B347" s="21" t="s">
         <v>445</v>
       </c>
-      <c r="C347" s="23"/>
-      <c r="D347" s="23"/>
+      <c r="C347" s="22"/>
+      <c r="D347" s="22"/>
       <c r="E347" s="8"/>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B348" s="20"/>
-      <c r="C348" s="21"/>
-      <c r="D348" s="21"/>
+      <c r="B348" s="19"/>
+      <c r="C348" s="20"/>
+      <c r="D348" s="20"/>
       <c r="E348" s="11"/>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="2"/>
-      <c r="B349" s="21" t="s">
+      <c r="B349" s="20" t="s">
         <v>446</v>
       </c>
-      <c r="C349" s="21"/>
-      <c r="D349" s="21"/>
+      <c r="C349" s="20"/>
+      <c r="D349" s="20"/>
       <c r="E349" s="11"/>
     </row>
     <row r="350" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="2"/>
-      <c r="B350" s="21" t="s">
+      <c r="B350" s="20" t="s">
         <v>447</v>
       </c>
-      <c r="C350" s="21" t="s">
+      <c r="C350" s="20" t="s">
         <v>435</v>
       </c>
-      <c r="D350" s="21" t="s">
+      <c r="D350" s="20" t="s">
         <v>436</v>
       </c>
       <c r="E350" s="11" t="s">
@@ -7276,31 +7368,31 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="2"/>
-      <c r="B351" s="21" t="s">
+      <c r="B351" s="20" t="s">
         <v>448</v>
       </c>
-      <c r="C351" s="21"/>
-      <c r="D351" s="21"/>
+      <c r="C351" s="20"/>
+      <c r="D351" s="20"/>
       <c r="E351" s="11"/>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="2"/>
-      <c r="B352" s="21" t="s">
+      <c r="B352" s="20" t="s">
         <v>352</v>
       </c>
-      <c r="C352" s="21"/>
-      <c r="D352" s="21"/>
+      <c r="C352" s="20"/>
+      <c r="D352" s="20"/>
       <c r="E352" s="11"/>
     </row>
     <row r="353" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="2"/>
-      <c r="B353" s="21" t="s">
+      <c r="B353" s="20" t="s">
         <v>449</v>
       </c>
-      <c r="C353" s="21" t="s">
+      <c r="C353" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D353" s="21" t="s">
+      <c r="D353" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E353" s="11" t="s">
@@ -7309,13 +7401,13 @@
     </row>
     <row r="354" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="2"/>
-      <c r="B354" s="21" t="s">
+      <c r="B354" s="20" t="s">
         <v>450</v>
       </c>
-      <c r="C354" s="21" t="s">
+      <c r="C354" s="20" t="s">
         <v>451</v>
       </c>
-      <c r="D354" s="21" t="s">
+      <c r="D354" s="20" t="s">
         <v>452</v>
       </c>
       <c r="E354" s="11" t="s">
@@ -7324,56 +7416,56 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="2"/>
-      <c r="B355" s="21"/>
-      <c r="C355" s="21"/>
-      <c r="D355" s="21"/>
+      <c r="B355" s="20"/>
+      <c r="C355" s="20"/>
+      <c r="D355" s="20"/>
       <c r="E355" s="11"/>
     </row>
     <row r="356" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="6"/>
-      <c r="B356" s="22" t="s">
+      <c r="B356" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="C356" s="23"/>
-      <c r="D356" s="23"/>
+      <c r="C356" s="22"/>
+      <c r="D356" s="22"/>
       <c r="E356" s="8"/>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B357" s="20"/>
-      <c r="C357" s="21"/>
-      <c r="D357" s="21"/>
+      <c r="B357" s="19"/>
+      <c r="C357" s="20"/>
+      <c r="D357" s="20"/>
       <c r="E357" s="11"/>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2"/>
-      <c r="B358" s="21" t="s">
+      <c r="B358" s="20" t="s">
         <v>454</v>
       </c>
-      <c r="C358" s="21"/>
-      <c r="D358" s="21"/>
+      <c r="C358" s="20"/>
+      <c r="D358" s="20"/>
       <c r="E358" s="11"/>
     </row>
     <row r="359" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="2"/>
-      <c r="B359" s="21" t="s">
+      <c r="B359" s="20" t="s">
         <v>455</v>
       </c>
-      <c r="C359" s="21"/>
-      <c r="D359" s="21"/>
+      <c r="C359" s="20"/>
+      <c r="D359" s="20"/>
       <c r="E359" s="11"/>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="2"/>
-      <c r="B360" s="21" t="s">
+      <c r="B360" s="20" t="s">
         <v>456</v>
       </c>
-      <c r="C360" s="21" t="s">
+      <c r="C360" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="D360" s="21" t="s">
+      <c r="D360" s="20" t="s">
         <v>458</v>
       </c>
       <c r="E360" s="11" t="s">
@@ -7382,40 +7474,40 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="2"/>
-      <c r="B361" s="21" t="s">
+      <c r="B361" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C361" s="21"/>
-      <c r="D361" s="21"/>
+      <c r="C361" s="20"/>
+      <c r="D361" s="20"/>
       <c r="E361" s="11"/>
     </row>
     <row r="362" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="2"/>
-      <c r="B362" s="21" t="s">
+      <c r="B362" s="20" t="s">
         <v>460</v>
       </c>
-      <c r="C362" s="21"/>
-      <c r="D362" s="21"/>
+      <c r="C362" s="20"/>
+      <c r="D362" s="20"/>
       <c r="E362" s="11"/>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="2"/>
-      <c r="B363" s="21" t="s">
+      <c r="B363" s="20" t="s">
         <v>461</v>
       </c>
-      <c r="C363" s="21"/>
-      <c r="D363" s="21"/>
+      <c r="C363" s="20"/>
+      <c r="D363" s="20"/>
       <c r="E363" s="11"/>
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="2"/>
-      <c r="B364" s="21" t="s">
+      <c r="B364" s="20" t="s">
         <v>462</v>
       </c>
-      <c r="C364" s="21" t="s">
+      <c r="C364" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="D364" s="21" t="s">
+      <c r="D364" s="20" t="s">
         <v>464</v>
       </c>
       <c r="E364" s="11" t="s">
@@ -7424,13 +7516,13 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="2"/>
-      <c r="B365" s="21" t="s">
+      <c r="B365" s="20" t="s">
         <v>465</v>
       </c>
-      <c r="C365" s="21" t="s">
+      <c r="C365" s="20" t="s">
         <v>466</v>
       </c>
-      <c r="D365" s="21" t="s">
+      <c r="D365" s="20" t="s">
         <v>467</v>
       </c>
       <c r="E365" s="11" t="s">
@@ -7439,24 +7531,24 @@
     </row>
     <row r="366" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="2"/>
-      <c r="B366" s="21" t="s">
+      <c r="B366" s="20" t="s">
         <v>468</v>
       </c>
-      <c r="C366" s="21" t="s">
+      <c r="C366" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="D366" s="21"/>
+      <c r="D366" s="20"/>
       <c r="E366" s="11"/>
     </row>
     <row r="367" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="2"/>
-      <c r="B367" s="21" t="s">
+      <c r="B367" s="20" t="s">
         <v>469</v>
       </c>
-      <c r="C367" s="21" t="s">
+      <c r="C367" s="20" t="s">
         <v>470</v>
       </c>
-      <c r="D367" s="21" t="s">
+      <c r="D367" s="20" t="s">
         <v>471</v>
       </c>
       <c r="E367" s="11" t="s">
@@ -7465,13 +7557,13 @@
     </row>
     <row r="368" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="2"/>
-      <c r="B368" s="21" t="s">
+      <c r="B368" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C368" s="21" t="s">
+      <c r="C368" s="20" t="s">
         <v>473</v>
       </c>
-      <c r="D368" s="21" t="s">
+      <c r="D368" s="20" t="s">
         <v>474</v>
       </c>
       <c r="E368" s="11" t="s">
@@ -7480,13 +7572,13 @@
     </row>
     <row r="369" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="2"/>
-      <c r="B369" s="21" t="s">
+      <c r="B369" s="20" t="s">
         <v>475</v>
       </c>
-      <c r="C369" s="21" t="s">
+      <c r="C369" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D369" s="21" t="s">
+      <c r="D369" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E369" s="11" t="s">
@@ -7495,47 +7587,47 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="2"/>
-      <c r="B370" s="21"/>
-      <c r="C370" s="21"/>
-      <c r="D370" s="21"/>
+      <c r="B370" s="20"/>
+      <c r="C370" s="20"/>
+      <c r="D370" s="20"/>
       <c r="E370" s="11"/>
     </row>
     <row r="371" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="28"/>
-      <c r="B371" s="22" t="s">
+      <c r="A371" s="25"/>
+      <c r="B371" s="21" t="s">
         <v>476</v>
       </c>
-      <c r="C371" s="23"/>
-      <c r="D371" s="23"/>
-      <c r="E371" s="23"/>
+      <c r="C371" s="22"/>
+      <c r="D371" s="22"/>
+      <c r="E371" s="22"/>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B372" s="20"/>
-      <c r="C372" s="21"/>
-      <c r="D372" s="21"/>
+      <c r="B372" s="19"/>
+      <c r="C372" s="20"/>
+      <c r="D372" s="20"/>
       <c r="E372" s="11"/>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="2"/>
-      <c r="B373" s="21" t="s">
+      <c r="B373" s="20" t="s">
         <v>477</v>
       </c>
-      <c r="C373" s="21"/>
-      <c r="D373" s="21"/>
+      <c r="C373" s="20"/>
+      <c r="D373" s="20"/>
       <c r="E373" s="11"/>
     </row>
     <row r="374" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="2"/>
-      <c r="B374" s="21" t="s">
+      <c r="B374" s="20" t="s">
         <v>478</v>
       </c>
-      <c r="C374" s="21" t="s">
+      <c r="C374" s="20" t="s">
         <v>479</v>
       </c>
-      <c r="D374" s="21" t="s">
+      <c r="D374" s="20" t="s">
         <v>480</v>
       </c>
       <c r="E374" s="11" t="s">
@@ -7544,84 +7636,84 @@
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="2"/>
-      <c r="B375" s="21" t="s">
+      <c r="B375" s="20" t="s">
         <v>481</v>
       </c>
-      <c r="C375" s="21"/>
-      <c r="D375" s="21"/>
+      <c r="C375" s="20"/>
+      <c r="D375" s="20"/>
       <c r="E375" s="11"/>
     </row>
     <row r="376" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="2"/>
-      <c r="B376" s="21" t="s">
+      <c r="B376" s="20" t="s">
         <v>482</v>
       </c>
-      <c r="C376" s="21"/>
-      <c r="D376" s="21"/>
+      <c r="C376" s="20"/>
+      <c r="D376" s="20"/>
       <c r="E376" s="11"/>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="2"/>
-      <c r="B377" s="21" t="s">
+      <c r="B377" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="C377" s="21"/>
-      <c r="D377" s="21"/>
+      <c r="C377" s="20"/>
+      <c r="D377" s="20"/>
       <c r="E377" s="11"/>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="2"/>
-      <c r="B378" s="21" t="s">
+      <c r="B378" s="20" t="s">
         <v>483</v>
       </c>
-      <c r="C378" s="21" t="s">
+      <c r="C378" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="D378" s="21"/>
+      <c r="D378" s="20"/>
       <c r="E378" s="11"/>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="2"/>
-      <c r="B379" s="21" t="s">
+      <c r="B379" s="20" t="s">
         <v>484</v>
       </c>
-      <c r="C379" s="21" t="s">
+      <c r="C379" s="20" t="s">
         <v>466</v>
       </c>
-      <c r="D379" s="21"/>
+      <c r="D379" s="20"/>
       <c r="E379" s="11"/>
     </row>
     <row r="380" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2"/>
-      <c r="B380" s="21" t="s">
+      <c r="B380" s="20" t="s">
         <v>485</v>
       </c>
-      <c r="C380" s="21" t="s">
+      <c r="C380" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="D380" s="21"/>
+      <c r="D380" s="20"/>
       <c r="E380" s="11"/>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="2"/>
-      <c r="B381" s="21" t="s">
+      <c r="B381" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C381" s="21" t="s">
+      <c r="C381" s="20" t="s">
         <v>470</v>
       </c>
-      <c r="D381" s="21"/>
+      <c r="D381" s="20"/>
       <c r="E381" s="11"/>
     </row>
     <row r="382" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="2"/>
-      <c r="B382" s="21" t="s">
+      <c r="B382" s="20" t="s">
         <v>487</v>
       </c>
-      <c r="C382" s="21" t="s">
+      <c r="C382" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D382" s="21" t="s">
+      <c r="D382" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E382" s="11" t="s">
@@ -7630,13 +7722,13 @@
     </row>
     <row r="383" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="2"/>
-      <c r="B383" s="21" t="s">
+      <c r="B383" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="C383" s="21" t="s">
+      <c r="C383" s="20" t="s">
         <v>489</v>
       </c>
-      <c r="D383" s="21" t="s">
+      <c r="D383" s="20" t="s">
         <v>490</v>
       </c>
       <c r="E383" s="11" t="s">
@@ -7645,47 +7737,47 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="2"/>
-      <c r="B384" s="21"/>
-      <c r="C384" s="21"/>
-      <c r="D384" s="21"/>
+      <c r="B384" s="20"/>
+      <c r="C384" s="20"/>
+      <c r="D384" s="20"/>
       <c r="E384" s="11"/>
     </row>
     <row r="385" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="6"/>
-      <c r="B385" s="22" t="s">
+      <c r="B385" s="21" t="s">
         <v>491</v>
       </c>
-      <c r="C385" s="23"/>
-      <c r="D385" s="23"/>
+      <c r="C385" s="22"/>
+      <c r="D385" s="22"/>
       <c r="E385" s="8"/>
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B386" s="20"/>
-      <c r="C386" s="21"/>
-      <c r="D386" s="21"/>
+      <c r="B386" s="19"/>
+      <c r="C386" s="20"/>
+      <c r="D386" s="20"/>
       <c r="E386" s="11"/>
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="2"/>
-      <c r="B387" s="21" t="s">
+      <c r="B387" s="20" t="s">
         <v>492</v>
       </c>
-      <c r="C387" s="21"/>
-      <c r="D387" s="21"/>
+      <c r="C387" s="20"/>
+      <c r="D387" s="20"/>
       <c r="E387" s="11"/>
     </row>
     <row r="388" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="2"/>
-      <c r="B388" s="21" t="s">
+      <c r="B388" s="20" t="s">
         <v>493</v>
       </c>
-      <c r="C388" s="21" t="s">
+      <c r="C388" s="20" t="s">
         <v>479</v>
       </c>
-      <c r="D388" s="21" t="s">
+      <c r="D388" s="20" t="s">
         <v>480</v>
       </c>
       <c r="E388" s="11" t="s">
@@ -7694,42 +7786,42 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="2"/>
-      <c r="B389" s="21" t="s">
+      <c r="B389" s="20" t="s">
         <v>494</v>
       </c>
-      <c r="C389" s="21"/>
-      <c r="D389" s="21"/>
+      <c r="C389" s="20"/>
+      <c r="D389" s="20"/>
       <c r="E389" s="11"/>
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="2"/>
-      <c r="B390" s="21" t="s">
+      <c r="B390" s="20" t="s">
         <v>352</v>
       </c>
-      <c r="C390" s="21"/>
-      <c r="D390" s="21"/>
+      <c r="C390" s="20"/>
+      <c r="D390" s="20"/>
       <c r="E390" s="11"/>
     </row>
     <row r="391" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="2"/>
-      <c r="B391" s="21" t="s">
+      <c r="B391" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C391" s="21" t="s">
+      <c r="C391" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D391" s="21"/>
+      <c r="D391" s="20"/>
       <c r="E391" s="11"/>
     </row>
     <row r="392" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="2"/>
-      <c r="B392" s="21" t="s">
+      <c r="B392" s="20" t="s">
         <v>496</v>
       </c>
-      <c r="C392" s="21" t="s">
+      <c r="C392" s="20" t="s">
         <v>497</v>
       </c>
-      <c r="D392" s="21" t="s">
+      <c r="D392" s="20" t="s">
         <v>498</v>
       </c>
       <c r="E392" s="11" t="s">
@@ -7737,134 +7829,133 @@
       </c>
     </row>
     <row r="393" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A393" s="29"/>
-      <c r="B393" s="24"/>
-      <c r="C393" s="24"/>
-      <c r="D393" s="24"/>
-      <c r="E393" s="18"/>
-      <c r="F393" s="30"/>
+      <c r="A393" s="26"/>
+      <c r="B393" s="20"/>
+      <c r="C393" s="20"/>
+      <c r="D393" s="20"/>
+      <c r="E393" s="11"/>
     </row>
     <row r="394" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A394" s="31"/>
-      <c r="B394" s="32" t="s">
+      <c r="A394" s="27"/>
+      <c r="B394" s="28" t="s">
         <v>499</v>
       </c>
-      <c r="C394" s="33"/>
-      <c r="D394" s="33"/>
-      <c r="E394" s="34"/>
+      <c r="C394" s="29"/>
+      <c r="D394" s="29"/>
+      <c r="E394" s="30"/>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B395" s="20"/>
-      <c r="C395" s="21"/>
-      <c r="D395" s="21"/>
+      <c r="B395" s="19"/>
+      <c r="C395" s="20"/>
+      <c r="D395" s="20"/>
       <c r="E395" s="11"/>
     </row>
     <row r="396" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="2"/>
-      <c r="B396" s="21" t="s">
+      <c r="B396" s="20" t="s">
         <v>500</v>
       </c>
-      <c r="C396" s="21"/>
-      <c r="D396" s="21"/>
+      <c r="C396" s="20"/>
+      <c r="D396" s="20"/>
       <c r="E396" s="11"/>
     </row>
     <row r="397" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="2"/>
-      <c r="B397" s="21" t="s">
+      <c r="B397" s="20" t="s">
         <v>501</v>
       </c>
-      <c r="C397" s="21"/>
-      <c r="D397" s="21"/>
+      <c r="C397" s="20"/>
+      <c r="D397" s="20"/>
       <c r="E397" s="11"/>
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="2"/>
-      <c r="B398" s="21" t="s">
+      <c r="B398" s="20" t="s">
         <v>456</v>
       </c>
-      <c r="C398" s="21" t="s">
+      <c r="C398" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="D398" s="21"/>
+      <c r="D398" s="20"/>
       <c r="E398" s="11"/>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="2"/>
-      <c r="B399" s="21" t="s">
+      <c r="B399" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C399" s="21"/>
-      <c r="D399" s="21"/>
+      <c r="C399" s="20"/>
+      <c r="D399" s="20"/>
       <c r="E399" s="11"/>
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="2"/>
-      <c r="B400" s="21" t="s">
+      <c r="B400" s="20" t="s">
         <v>502</v>
       </c>
-      <c r="C400" s="21"/>
-      <c r="D400" s="21"/>
+      <c r="C400" s="20"/>
+      <c r="D400" s="20"/>
       <c r="E400" s="11"/>
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="2"/>
-      <c r="B401" s="21" t="s">
+      <c r="B401" s="20" t="s">
         <v>503</v>
       </c>
-      <c r="C401" s="21"/>
-      <c r="D401" s="21"/>
+      <c r="C401" s="20"/>
+      <c r="D401" s="20"/>
       <c r="E401" s="11"/>
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2"/>
-      <c r="B402" s="21" t="s">
+      <c r="B402" s="20" t="s">
         <v>504</v>
       </c>
-      <c r="C402" s="21"/>
-      <c r="D402" s="21"/>
+      <c r="C402" s="20"/>
+      <c r="D402" s="20"/>
       <c r="E402" s="11"/>
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="2"/>
-      <c r="B403" s="21" t="s">
+      <c r="B403" s="20" t="s">
         <v>505</v>
       </c>
-      <c r="C403" s="21"/>
-      <c r="D403" s="21"/>
+      <c r="C403" s="20"/>
+      <c r="D403" s="20"/>
       <c r="E403" s="11"/>
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="2"/>
-      <c r="B404" s="21" t="s">
+      <c r="B404" s="20" t="s">
         <v>506</v>
       </c>
-      <c r="C404" s="21"/>
-      <c r="D404" s="21"/>
+      <c r="C404" s="20"/>
+      <c r="D404" s="20"/>
       <c r="E404" s="11"/>
     </row>
     <row r="405" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="2"/>
-      <c r="B405" s="21" t="s">
+      <c r="B405" s="20" t="s">
         <v>507</v>
       </c>
-      <c r="C405" s="21" t="s">
+      <c r="C405" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="D405" s="21"/>
+      <c r="D405" s="20"/>
       <c r="E405" s="11"/>
     </row>
     <row r="406" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="2"/>
-      <c r="B406" s="21" t="s">
+      <c r="B406" s="20" t="s">
         <v>508</v>
       </c>
-      <c r="C406" s="21" t="s">
+      <c r="C406" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="D406" s="21" t="s">
+      <c r="D406" s="20" t="s">
         <v>510</v>
       </c>
       <c r="E406" s="11" t="s">
@@ -7873,13 +7964,13 @@
     </row>
     <row r="407" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="2"/>
-      <c r="B407" s="21" t="s">
+      <c r="B407" s="20" t="s">
         <v>512</v>
       </c>
-      <c r="C407" s="21" t="s">
+      <c r="C407" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D407" s="21" t="s">
+      <c r="D407" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E407" s="11" t="s">
@@ -7888,67 +7979,67 @@
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="2"/>
-      <c r="B408" s="21"/>
-      <c r="C408" s="21"/>
-      <c r="D408" s="21"/>
+      <c r="B408" s="20"/>
+      <c r="C408" s="20"/>
+      <c r="D408" s="20"/>
       <c r="E408" s="11"/>
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B409" s="21" t="s">
+      <c r="B409" s="20" t="s">
         <v>513</v>
       </c>
-      <c r="C409" s="21"/>
-      <c r="D409" s="21"/>
+      <c r="C409" s="20"/>
+      <c r="D409" s="20"/>
       <c r="E409" s="11"/>
     </row>
     <row r="410" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="2"/>
-      <c r="B410" s="21" t="s">
+      <c r="B410" s="20" t="s">
         <v>514</v>
       </c>
-      <c r="C410" s="21"/>
-      <c r="D410" s="21"/>
+      <c r="C410" s="20"/>
+      <c r="D410" s="20"/>
       <c r="E410" s="11"/>
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="2"/>
-      <c r="B411" s="21" t="s">
+      <c r="B411" s="20" t="s">
         <v>515</v>
       </c>
-      <c r="C411" s="21"/>
-      <c r="D411" s="21"/>
+      <c r="C411" s="20"/>
+      <c r="D411" s="20"/>
       <c r="E411" s="11"/>
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="2"/>
-      <c r="B412" s="21" t="s">
+      <c r="B412" s="20" t="s">
         <v>516</v>
       </c>
-      <c r="C412" s="21"/>
-      <c r="D412" s="21"/>
+      <c r="C412" s="20"/>
+      <c r="D412" s="20"/>
       <c r="E412" s="11"/>
     </row>
     <row r="413" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="2"/>
-      <c r="B413" s="21" t="s">
+      <c r="B413" s="20" t="s">
         <v>517</v>
       </c>
-      <c r="C413" s="21"/>
-      <c r="D413" s="21"/>
+      <c r="C413" s="20"/>
+      <c r="D413" s="20"/>
       <c r="E413" s="11"/>
     </row>
     <row r="414" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="2"/>
-      <c r="B414" s="21" t="s">
+      <c r="B414" s="20" t="s">
         <v>518</v>
       </c>
-      <c r="C414" s="21" t="s">
+      <c r="C414" s="20" t="s">
         <v>519</v>
       </c>
-      <c r="D414" s="21" t="s">
+      <c r="D414" s="20" t="s">
         <v>520</v>
       </c>
       <c r="E414" s="11" t="s">
@@ -7957,40 +8048,40 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="2"/>
-      <c r="B415" s="21" t="s">
+      <c r="B415" s="20" t="s">
         <v>521</v>
       </c>
-      <c r="C415" s="21"/>
-      <c r="D415" s="21"/>
+      <c r="C415" s="20"/>
+      <c r="D415" s="20"/>
       <c r="E415" s="11"/>
     </row>
     <row r="416" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="2"/>
-      <c r="B416" s="21" t="s">
+      <c r="B416" s="20" t="s">
         <v>522</v>
       </c>
-      <c r="C416" s="21"/>
-      <c r="D416" s="21"/>
+      <c r="C416" s="20"/>
+      <c r="D416" s="20"/>
       <c r="E416" s="11"/>
     </row>
     <row r="417" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="2"/>
-      <c r="B417" s="21" t="s">
+      <c r="B417" s="20" t="s">
         <v>523</v>
       </c>
-      <c r="C417" s="21"/>
-      <c r="D417" s="21"/>
+      <c r="C417" s="20"/>
+      <c r="D417" s="20"/>
       <c r="E417" s="11"/>
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="2"/>
-      <c r="B418" s="21" t="s">
+      <c r="B418" s="20" t="s">
         <v>524</v>
       </c>
-      <c r="C418" s="21" t="s">
+      <c r="C418" s="20" t="s">
         <v>525</v>
       </c>
-      <c r="D418" s="21" t="s">
+      <c r="D418" s="20" t="s">
         <v>526</v>
       </c>
       <c r="E418" s="11" t="s">
@@ -7999,56 +8090,56 @@
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="2"/>
-      <c r="B419" s="21" t="s">
+      <c r="B419" s="20" t="s">
         <v>527</v>
       </c>
-      <c r="C419" s="21"/>
-      <c r="D419" s="21"/>
+      <c r="C419" s="20"/>
+      <c r="D419" s="20"/>
       <c r="E419" s="11"/>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="2"/>
-      <c r="B420" s="21"/>
-      <c r="C420" s="21"/>
-      <c r="D420" s="21"/>
+      <c r="B420" s="20"/>
+      <c r="C420" s="20"/>
+      <c r="D420" s="20"/>
       <c r="E420" s="11"/>
     </row>
     <row r="421" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="6"/>
-      <c r="B421" s="22" t="s">
+      <c r="B421" s="21" t="s">
         <v>528</v>
       </c>
-      <c r="C421" s="23"/>
-      <c r="D421" s="23"/>
+      <c r="C421" s="22"/>
+      <c r="D421" s="22"/>
       <c r="E421" s="8"/>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B422" s="20"/>
-      <c r="C422" s="21"/>
-      <c r="D422" s="21"/>
+      <c r="B422" s="19"/>
+      <c r="C422" s="20"/>
+      <c r="D422" s="20"/>
       <c r="E422" s="11"/>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2"/>
-      <c r="B423" s="21" t="s">
+      <c r="B423" s="20" t="s">
         <v>529</v>
       </c>
-      <c r="C423" s="21"/>
-      <c r="D423" s="21"/>
+      <c r="C423" s="20"/>
+      <c r="D423" s="20"/>
       <c r="E423" s="11"/>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2"/>
-      <c r="B424" s="21" t="s">
+      <c r="B424" s="20" t="s">
         <v>530</v>
       </c>
-      <c r="C424" s="21" t="s">
+      <c r="C424" s="20" t="s">
         <v>531</v>
       </c>
-      <c r="D424" s="21" t="s">
+      <c r="D424" s="20" t="s">
         <v>532</v>
       </c>
       <c r="E424" s="11" t="s">
@@ -8057,91 +8148,91 @@
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2"/>
-      <c r="B425" s="21" t="s">
+      <c r="B425" s="20" t="s">
         <v>533</v>
       </c>
-      <c r="C425" s="21"/>
-      <c r="D425" s="21"/>
+      <c r="C425" s="20"/>
+      <c r="D425" s="20"/>
       <c r="E425" s="11"/>
     </row>
     <row r="426" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2"/>
-      <c r="B426" s="21" t="s">
+      <c r="B426" s="20" t="s">
         <v>534</v>
       </c>
-      <c r="C426" s="21"/>
-      <c r="D426" s="21"/>
+      <c r="C426" s="20"/>
+      <c r="D426" s="20"/>
       <c r="E426" s="11"/>
     </row>
     <row r="427" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2"/>
-      <c r="B427" s="21" t="s">
+      <c r="B427" s="20" t="s">
         <v>535</v>
       </c>
-      <c r="C427" s="21"/>
-      <c r="D427" s="21"/>
+      <c r="C427" s="20"/>
+      <c r="D427" s="20"/>
       <c r="E427" s="11"/>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2"/>
-      <c r="B428" s="21" t="s">
+      <c r="B428" s="20" t="s">
         <v>536</v>
       </c>
-      <c r="C428" s="21"/>
-      <c r="D428" s="21"/>
+      <c r="C428" s="20"/>
+      <c r="D428" s="20"/>
       <c r="E428" s="11"/>
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="2"/>
-      <c r="B429" s="24" t="s">
+      <c r="B429" s="20" t="s">
         <v>537</v>
       </c>
-      <c r="C429" s="21"/>
-      <c r="D429" s="21"/>
+      <c r="C429" s="20"/>
+      <c r="D429" s="20"/>
       <c r="E429" s="11"/>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="2"/>
-      <c r="B430" s="24" t="s">
+      <c r="B430" s="20" t="s">
         <v>538</v>
       </c>
-      <c r="C430" s="21"/>
-      <c r="D430" s="21"/>
+      <c r="C430" s="20"/>
+      <c r="D430" s="20"/>
       <c r="E430" s="11"/>
     </row>
     <row r="431" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="2"/>
-      <c r="B431" s="24" t="s">
+      <c r="B431" s="20" t="s">
         <v>539</v>
       </c>
-      <c r="C431" s="21" t="s">
+      <c r="C431" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="D431" s="21"/>
+      <c r="D431" s="20"/>
       <c r="E431" s="11"/>
-      <c r="F431" s="35"/>
-      <c r="G431" s="30"/>
+      <c r="F431" s="15"/>
+      <c r="G431" s="1"/>
     </row>
     <row r="432" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2"/>
-      <c r="B432" s="24" t="s">
+      <c r="B432" s="20" t="s">
         <v>540</v>
       </c>
-      <c r="C432" s="21" t="s">
+      <c r="C432" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D432" s="21"/>
+      <c r="D432" s="20"/>
       <c r="E432" s="11"/>
     </row>
     <row r="433" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="2"/>
-      <c r="B433" s="24" t="s">
+      <c r="B433" s="20" t="s">
         <v>541</v>
       </c>
-      <c r="C433" s="21" t="s">
+      <c r="C433" s="20" t="s">
         <v>542</v>
       </c>
-      <c r="D433" s="21" t="s">
+      <c r="D433" s="20" t="s">
         <v>543</v>
       </c>
       <c r="E433" s="11" t="s">
@@ -8150,152 +8241,152 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="2"/>
-      <c r="B434" s="24"/>
-      <c r="C434" s="21"/>
-      <c r="D434" s="21"/>
+      <c r="B434" s="20"/>
+      <c r="C434" s="20"/>
+      <c r="D434" s="20"/>
       <c r="E434" s="11"/>
     </row>
     <row r="435" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B435" s="24" t="s">
+      <c r="B435" s="20" t="s">
         <v>544</v>
       </c>
-      <c r="C435" s="21"/>
-      <c r="D435" s="21"/>
+      <c r="C435" s="20"/>
+      <c r="D435" s="20"/>
       <c r="E435" s="11"/>
     </row>
     <row r="436" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2"/>
-      <c r="B436" s="24" t="s">
+      <c r="B436" s="20" t="s">
         <v>545</v>
       </c>
-      <c r="C436" s="21"/>
-      <c r="D436" s="21"/>
+      <c r="C436" s="20"/>
+      <c r="D436" s="20"/>
       <c r="E436" s="11"/>
     </row>
     <row r="437" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2"/>
-      <c r="B437" s="24" t="s">
+      <c r="B437" s="20" t="s">
         <v>546</v>
       </c>
-      <c r="C437" s="21" t="s">
+      <c r="C437" s="20" t="s">
         <v>519</v>
       </c>
-      <c r="D437" s="21"/>
+      <c r="D437" s="20"/>
       <c r="E437" s="11"/>
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2"/>
-      <c r="B438" s="24" t="s">
+      <c r="B438" s="20" t="s">
         <v>547</v>
       </c>
-      <c r="C438" s="21"/>
-      <c r="D438" s="21"/>
+      <c r="C438" s="20"/>
+      <c r="D438" s="20"/>
       <c r="E438" s="11"/>
     </row>
     <row r="439" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="2"/>
-      <c r="B439" s="24" t="s">
+      <c r="B439" s="20" t="s">
         <v>548</v>
       </c>
-      <c r="C439" s="21"/>
-      <c r="D439" s="21"/>
+      <c r="C439" s="20"/>
+      <c r="D439" s="20"/>
       <c r="E439" s="11"/>
     </row>
     <row r="440" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="2"/>
-      <c r="B440" s="24" t="s">
+      <c r="B440" s="20" t="s">
         <v>549</v>
       </c>
-      <c r="C440" s="21"/>
-      <c r="D440" s="21"/>
+      <c r="C440" s="20"/>
+      <c r="D440" s="20"/>
       <c r="E440" s="11"/>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="2"/>
-      <c r="B441" s="24" t="s">
+      <c r="B441" s="20" t="s">
         <v>550</v>
       </c>
-      <c r="C441" s="21" t="s">
+      <c r="C441" s="20" t="s">
         <v>525</v>
       </c>
-      <c r="D441" s="21"/>
+      <c r="D441" s="20"/>
       <c r="E441" s="11"/>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2"/>
-      <c r="B442" s="24" t="s">
+      <c r="B442" s="20" t="s">
         <v>551</v>
       </c>
-      <c r="C442" s="21"/>
-      <c r="D442" s="21"/>
+      <c r="C442" s="20"/>
+      <c r="D442" s="20"/>
       <c r="E442" s="11"/>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2"/>
-      <c r="B443" s="24" t="s">
+      <c r="B443" s="20" t="s">
         <v>552</v>
       </c>
-      <c r="C443" s="21"/>
-      <c r="D443" s="21"/>
+      <c r="C443" s="20"/>
+      <c r="D443" s="20"/>
       <c r="E443" s="11"/>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2"/>
-      <c r="B444" s="24" t="s">
+      <c r="B444" s="20" t="s">
         <v>553</v>
       </c>
-      <c r="C444" s="21"/>
-      <c r="D444" s="21"/>
+      <c r="C444" s="20"/>
+      <c r="D444" s="20"/>
       <c r="E444" s="11"/>
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2"/>
-      <c r="B445" s="24" t="s">
+      <c r="B445" s="20" t="s">
         <v>554</v>
       </c>
-      <c r="C445" s="21"/>
-      <c r="D445" s="21"/>
+      <c r="C445" s="20"/>
+      <c r="D445" s="20"/>
       <c r="E445" s="11"/>
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2"/>
-      <c r="B446" s="24" t="s">
+      <c r="B446" s="20" t="s">
         <v>555</v>
       </c>
-      <c r="C446" s="21"/>
-      <c r="D446" s="21"/>
+      <c r="C446" s="20"/>
+      <c r="D446" s="20"/>
       <c r="E446" s="11"/>
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="2"/>
-      <c r="B447" s="24" t="s">
+      <c r="B447" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="C447" s="21"/>
-      <c r="D447" s="21"/>
+      <c r="C447" s="20"/>
+      <c r="D447" s="20"/>
       <c r="E447" s="11"/>
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="2"/>
-      <c r="B448" s="24" t="s">
+      <c r="B448" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="C448" s="21"/>
-      <c r="D448" s="21"/>
+      <c r="C448" s="20"/>
+      <c r="D448" s="20"/>
       <c r="E448" s="11"/>
     </row>
     <row r="449" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="2"/>
-      <c r="B449" s="24" t="s">
+      <c r="B449" s="20" t="s">
         <v>558</v>
       </c>
-      <c r="C449" s="21" t="s">
+      <c r="C449" s="20" t="s">
         <v>559</v>
       </c>
-      <c r="D449" s="21" t="s">
+      <c r="D449" s="20" t="s">
         <v>560</v>
       </c>
       <c r="E449" s="11" t="s">
@@ -8304,170 +8395,170 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="2"/>
-      <c r="B450" s="24" t="s">
+      <c r="B450" s="20" t="s">
         <v>561</v>
       </c>
-      <c r="C450" s="21"/>
-      <c r="D450" s="21"/>
+      <c r="C450" s="20"/>
+      <c r="D450" s="20"/>
       <c r="E450" s="11"/>
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="2"/>
-      <c r="B451" s="24" t="s">
+      <c r="B451" s="20" t="s">
         <v>562</v>
       </c>
-      <c r="C451" s="21"/>
-      <c r="D451" s="21"/>
+      <c r="C451" s="20"/>
+      <c r="D451" s="20"/>
       <c r="E451" s="11"/>
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="2"/>
-      <c r="B452" s="24" t="s">
+      <c r="B452" s="20" t="s">
         <v>563</v>
       </c>
-      <c r="C452" s="21"/>
-      <c r="D452" s="21"/>
+      <c r="C452" s="20"/>
+      <c r="D452" s="20"/>
       <c r="E452" s="11"/>
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="2"/>
-      <c r="B453" s="24" t="s">
+      <c r="B453" s="20" t="s">
         <v>564</v>
       </c>
-      <c r="C453" s="21"/>
-      <c r="D453" s="21"/>
+      <c r="C453" s="20"/>
+      <c r="D453" s="20"/>
       <c r="E453" s="11"/>
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2"/>
-      <c r="B454" s="24" t="s">
+      <c r="B454" s="20" t="s">
         <v>565</v>
       </c>
-      <c r="C454" s="21"/>
-      <c r="D454" s="21"/>
+      <c r="C454" s="20"/>
+      <c r="D454" s="20"/>
       <c r="E454" s="11"/>
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2"/>
-      <c r="B455" s="24" t="s">
+      <c r="B455" s="20" t="s">
         <v>566</v>
       </c>
-      <c r="C455" s="21"/>
-      <c r="D455" s="21"/>
+      <c r="C455" s="20"/>
+      <c r="D455" s="20"/>
       <c r="E455" s="11"/>
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2"/>
-      <c r="B456" s="24" t="s">
+      <c r="B456" s="20" t="s">
         <v>567</v>
       </c>
-      <c r="C456" s="21"/>
-      <c r="D456" s="21"/>
+      <c r="C456" s="20"/>
+      <c r="D456" s="20"/>
       <c r="E456" s="11"/>
     </row>
     <row r="457" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2"/>
-      <c r="B457" s="24" t="s">
+      <c r="B457" s="20" t="s">
         <v>568</v>
       </c>
-      <c r="C457" s="21"/>
-      <c r="D457" s="36" t="s">
+      <c r="C457" s="20"/>
+      <c r="D457" s="31" t="s">
         <v>569</v>
       </c>
-      <c r="E457" s="37"/>
+      <c r="E457" s="32"/>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2"/>
-      <c r="B458" s="24" t="s">
+      <c r="B458" s="20" t="s">
         <v>570</v>
       </c>
-      <c r="C458" s="21"/>
-      <c r="D458" s="21"/>
+      <c r="C458" s="20"/>
+      <c r="D458" s="20"/>
       <c r="E458" s="11"/>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="2"/>
-      <c r="B459" s="24" t="s">
+      <c r="B459" s="20" t="s">
         <v>571</v>
       </c>
-      <c r="C459" s="21"/>
-      <c r="D459" s="21"/>
+      <c r="C459" s="20"/>
+      <c r="D459" s="20"/>
       <c r="E459" s="11"/>
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="2"/>
-      <c r="B460" s="24" t="s">
+      <c r="B460" s="20" t="s">
         <v>572</v>
       </c>
-      <c r="C460" s="21"/>
-      <c r="D460" s="21"/>
+      <c r="C460" s="20"/>
+      <c r="D460" s="20"/>
       <c r="E460" s="11"/>
     </row>
     <row r="461" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="2"/>
-      <c r="B461" s="24" t="s">
+      <c r="B461" s="20" t="s">
         <v>573</v>
       </c>
-      <c r="C461" s="21"/>
-      <c r="D461" s="21"/>
+      <c r="C461" s="20"/>
+      <c r="D461" s="20"/>
       <c r="E461" s="11"/>
     </row>
     <row r="462" customFormat="false" ht="67.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="2"/>
-      <c r="B462" s="24" t="s">
+      <c r="B462" s="20" t="s">
         <v>574</v>
       </c>
-      <c r="C462" s="24" t="s">
+      <c r="C462" s="20" t="s">
         <v>575</v>
       </c>
-      <c r="D462" s="21" t="s">
+      <c r="D462" s="20" t="s">
         <v>576</v>
       </c>
       <c r="E462" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="F462" s="38"/>
+      <c r="F462" s="20"/>
     </row>
     <row r="463" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2"/>
-      <c r="B463" s="24" t="s">
+      <c r="B463" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="C463" s="21"/>
-      <c r="D463" s="21"/>
+      <c r="C463" s="20"/>
+      <c r="D463" s="20"/>
       <c r="E463" s="11"/>
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2"/>
-      <c r="B464" s="24" t="s">
+      <c r="B464" s="20" t="s">
         <v>578</v>
       </c>
-      <c r="C464" s="21"/>
-      <c r="D464" s="21"/>
+      <c r="C464" s="20"/>
+      <c r="D464" s="20"/>
       <c r="E464" s="11"/>
     </row>
     <row r="465" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2"/>
-      <c r="B465" s="24" t="s">
+      <c r="B465" s="20" t="s">
         <v>579</v>
       </c>
-      <c r="C465" s="21" t="s">
+      <c r="C465" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="D465" s="21"/>
-      <c r="E465" s="18" t="s">
+      <c r="D465" s="20"/>
+      <c r="E465" s="11" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2"/>
-      <c r="B466" s="24" t="s">
+      <c r="B466" s="20" t="s">
         <v>580</v>
       </c>
-      <c r="C466" s="21" t="s">
+      <c r="C466" s="20" t="s">
         <v>542</v>
       </c>
-      <c r="D466" s="21" t="s">
+      <c r="D466" s="20" t="s">
         <v>581</v>
       </c>
       <c r="E466" s="11" t="s">
@@ -8476,44 +8567,44 @@
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2"/>
-      <c r="B467" s="24" t="s">
+      <c r="B467" s="20" t="s">
         <v>582</v>
       </c>
-      <c r="C467" s="21"/>
-      <c r="D467" s="21"/>
+      <c r="C467" s="20"/>
+      <c r="D467" s="20"/>
       <c r="E467" s="11"/>
     </row>
-    <row r="468" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2"/>
-      <c r="B468" s="24" t="s">
+      <c r="B468" s="20" t="s">
         <v>583</v>
       </c>
-      <c r="C468" s="24"/>
-      <c r="D468" s="24"/>
-      <c r="E468" s="18"/>
+      <c r="C468" s="20"/>
+      <c r="D468" s="20"/>
+      <c r="E468" s="11"/>
     </row>
     <row r="469" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="2"/>
-      <c r="B469" s="24" t="s">
+      <c r="B469" s="20" t="s">
         <v>584</v>
       </c>
-      <c r="C469" s="24" t="s">
+      <c r="C469" s="20" t="s">
         <v>585</v>
       </c>
-      <c r="D469" s="36" t="s">
+      <c r="D469" s="31" t="s">
         <v>569</v>
       </c>
-      <c r="E469" s="37"/>
+      <c r="E469" s="32"/>
     </row>
     <row r="470" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="2"/>
-      <c r="B470" s="21" t="s">
+      <c r="B470" s="20" t="s">
         <v>586</v>
       </c>
-      <c r="C470" s="21" t="s">
+      <c r="C470" s="20" t="s">
         <v>587</v>
       </c>
-      <c r="D470" s="21" t="s">
+      <c r="D470" s="20" t="s">
         <v>588</v>
       </c>
       <c r="E470" s="11" t="s">
@@ -8522,160 +8613,160 @@
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="2"/>
-      <c r="B471" s="21" t="s">
+      <c r="B471" s="20" t="s">
         <v>589</v>
       </c>
-      <c r="C471" s="21"/>
-      <c r="D471" s="21"/>
+      <c r="C471" s="20"/>
+      <c r="D471" s="20"/>
       <c r="E471" s="11"/>
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="2"/>
-      <c r="B472" s="21" t="s">
+      <c r="B472" s="20" t="s">
         <v>590</v>
       </c>
-      <c r="C472" s="21"/>
-      <c r="D472" s="21"/>
+      <c r="C472" s="20"/>
+      <c r="D472" s="20"/>
       <c r="E472" s="11"/>
     </row>
     <row r="473" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2"/>
-      <c r="B473" s="21" t="s">
+      <c r="B473" s="20" t="s">
         <v>591</v>
       </c>
-      <c r="C473" s="21" t="s">
+      <c r="C473" s="20" t="s">
         <v>559</v>
       </c>
-      <c r="D473" s="21"/>
+      <c r="D473" s="20"/>
       <c r="E473" s="11"/>
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="2"/>
-      <c r="B474" s="21" t="s">
+      <c r="B474" s="20" t="s">
         <v>592</v>
       </c>
-      <c r="C474" s="21"/>
-      <c r="D474" s="21"/>
+      <c r="C474" s="20"/>
+      <c r="D474" s="20"/>
       <c r="E474" s="11"/>
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="2"/>
-      <c r="B475" s="21"/>
-      <c r="C475" s="21"/>
-      <c r="D475" s="21"/>
+      <c r="B475" s="20"/>
+      <c r="C475" s="20"/>
+      <c r="D475" s="20"/>
       <c r="E475" s="11"/>
     </row>
     <row r="476" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B476" s="21" t="s">
+      <c r="B476" s="20" t="s">
         <v>594</v>
       </c>
-      <c r="C476" s="21"/>
-      <c r="D476" s="21"/>
+      <c r="C476" s="20"/>
+      <c r="D476" s="20"/>
       <c r="E476" s="11"/>
     </row>
     <row r="477" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2"/>
-      <c r="B477" s="21" t="s">
+      <c r="B477" s="20" t="s">
         <v>595</v>
       </c>
-      <c r="C477" s="21" t="s">
+      <c r="C477" s="20" t="s">
         <v>559</v>
       </c>
-      <c r="D477" s="21"/>
+      <c r="D477" s="20"/>
       <c r="E477" s="11"/>
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2"/>
-      <c r="B478" s="21" t="s">
+      <c r="B478" s="20" t="s">
         <v>596</v>
       </c>
-      <c r="C478" s="21"/>
-      <c r="D478" s="21"/>
+      <c r="C478" s="20"/>
+      <c r="D478" s="20"/>
       <c r="E478" s="11"/>
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="2"/>
-      <c r="B479" s="21"/>
-      <c r="C479" s="21"/>
-      <c r="D479" s="21"/>
+      <c r="B479" s="20"/>
+      <c r="C479" s="20"/>
+      <c r="D479" s="20"/>
       <c r="E479" s="11"/>
     </row>
     <row r="480" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="6"/>
-      <c r="B480" s="22" t="s">
+      <c r="B480" s="21" t="s">
         <v>597</v>
       </c>
-      <c r="C480" s="23"/>
-      <c r="D480" s="23"/>
+      <c r="C480" s="22"/>
+      <c r="D480" s="22"/>
       <c r="E480" s="8"/>
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C481" s="21"/>
-      <c r="D481" s="21"/>
+      <c r="C481" s="20"/>
+      <c r="D481" s="20"/>
       <c r="E481" s="11"/>
     </row>
     <row r="482" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2"/>
-      <c r="B482" s="21" t="s">
+      <c r="B482" s="20" t="s">
         <v>598</v>
       </c>
-      <c r="C482" s="21"/>
-      <c r="D482" s="21"/>
+      <c r="C482" s="20"/>
+      <c r="D482" s="20"/>
       <c r="E482" s="11"/>
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="2"/>
-      <c r="B483" s="21" t="s">
+      <c r="B483" s="20" t="s">
         <v>599</v>
       </c>
-      <c r="C483" s="21"/>
-      <c r="D483" s="21"/>
+      <c r="C483" s="20"/>
+      <c r="D483" s="20"/>
       <c r="E483" s="11"/>
     </row>
     <row r="484" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2"/>
-      <c r="B484" s="21" t="s">
+      <c r="B484" s="20" t="s">
         <v>600</v>
       </c>
-      <c r="C484" s="21"/>
-      <c r="D484" s="21"/>
+      <c r="C484" s="20"/>
+      <c r="D484" s="20"/>
       <c r="E484" s="11"/>
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2"/>
-      <c r="B485" s="21" t="s">
+      <c r="B485" s="20" t="s">
         <v>352</v>
       </c>
-      <c r="C485" s="21"/>
-      <c r="D485" s="21"/>
+      <c r="C485" s="20"/>
+      <c r="D485" s="20"/>
       <c r="E485" s="11"/>
     </row>
     <row r="486" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2"/>
-      <c r="B486" s="21" t="s">
+      <c r="B486" s="20" t="s">
         <v>601</v>
       </c>
-      <c r="C486" s="21" t="s">
+      <c r="C486" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D486" s="21"/>
+      <c r="D486" s="20"/>
       <c r="E486" s="11"/>
     </row>
     <row r="487" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="2"/>
-      <c r="B487" s="21" t="s">
+      <c r="B487" s="20" t="s">
         <v>602</v>
       </c>
-      <c r="C487" s="21" t="s">
+      <c r="C487" s="20" t="s">
         <v>559</v>
       </c>
-      <c r="D487" s="21" t="s">
+      <c r="D487" s="20" t="s">
         <v>603</v>
       </c>
       <c r="E487" s="11" t="s">
@@ -8684,88 +8775,88 @@
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="2"/>
-      <c r="B488" s="21"/>
-      <c r="C488" s="21"/>
-      <c r="D488" s="21"/>
+      <c r="B488" s="20"/>
+      <c r="C488" s="20"/>
+      <c r="D488" s="20"/>
       <c r="E488" s="11"/>
     </row>
     <row r="489" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="6"/>
-      <c r="B489" s="22" t="s">
+      <c r="B489" s="21" t="s">
         <v>604</v>
       </c>
-      <c r="C489" s="23"/>
-      <c r="D489" s="23"/>
+      <c r="C489" s="22"/>
+      <c r="D489" s="22"/>
       <c r="E489" s="8"/>
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C490" s="21"/>
-      <c r="D490" s="21"/>
+      <c r="C490" s="20"/>
+      <c r="D490" s="20"/>
       <c r="E490" s="11"/>
     </row>
     <row r="491" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="2"/>
-      <c r="B491" s="21" t="s">
+      <c r="B491" s="20" t="s">
         <v>605</v>
       </c>
-      <c r="C491" s="21"/>
-      <c r="D491" s="21"/>
+      <c r="C491" s="20"/>
+      <c r="D491" s="20"/>
       <c r="E491" s="11"/>
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2"/>
-      <c r="B492" s="21" t="s">
+      <c r="B492" s="20" t="s">
         <v>606</v>
       </c>
-      <c r="C492" s="21"/>
-      <c r="D492" s="21"/>
+      <c r="C492" s="20"/>
+      <c r="D492" s="20"/>
       <c r="E492" s="11"/>
     </row>
     <row r="493" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2"/>
-      <c r="B493" s="21" t="s">
+      <c r="B493" s="20" t="s">
         <v>607</v>
       </c>
-      <c r="C493" s="21" t="s">
+      <c r="C493" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="D493" s="21"/>
+      <c r="D493" s="20"/>
       <c r="E493" s="11"/>
     </row>
     <row r="494" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2"/>
-      <c r="B494" s="21" t="s">
+      <c r="B494" s="20" t="s">
         <v>608</v>
       </c>
-      <c r="C494" s="21" t="s">
+      <c r="C494" s="20" t="s">
         <v>609</v>
       </c>
-      <c r="D494" s="21"/>
+      <c r="D494" s="20"/>
       <c r="E494" s="11"/>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2"/>
-      <c r="B495" s="21" t="s">
+      <c r="B495" s="20" t="s">
         <v>610</v>
       </c>
-      <c r="C495" s="21" t="s">
+      <c r="C495" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="D495" s="21"/>
+      <c r="D495" s="20"/>
       <c r="E495" s="11"/>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2"/>
-      <c r="B496" s="21" t="s">
+      <c r="B496" s="20" t="s">
         <v>611</v>
       </c>
-      <c r="C496" s="21" t="s">
+      <c r="C496" s="20" t="s">
         <v>612</v>
       </c>
-      <c r="D496" s="21" t="s">
+      <c r="D496" s="20" t="s">
         <v>613</v>
       </c>
       <c r="E496" s="11" t="s">
@@ -8774,13 +8865,13 @@
     </row>
     <row r="497" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2"/>
-      <c r="B497" s="21" t="s">
+      <c r="B497" s="20" t="s">
         <v>614</v>
       </c>
-      <c r="C497" s="21" t="s">
+      <c r="C497" s="20" t="s">
         <v>615</v>
       </c>
-      <c r="D497" s="21" t="s">
+      <c r="D497" s="20" t="s">
         <v>616</v>
       </c>
       <c r="E497" s="11" t="s">
@@ -8789,112 +8880,112 @@
     </row>
     <row r="498" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="2"/>
-      <c r="B498" s="21" t="s">
+      <c r="B498" s="20" t="s">
         <v>617</v>
       </c>
-      <c r="C498" s="21"/>
-      <c r="D498" s="21"/>
+      <c r="C498" s="20"/>
+      <c r="D498" s="20"/>
       <c r="E498" s="11"/>
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="2"/>
-      <c r="B499" s="21"/>
-      <c r="C499" s="21"/>
-      <c r="D499" s="21"/>
+      <c r="B499" s="20"/>
+      <c r="C499" s="20"/>
+      <c r="D499" s="20"/>
       <c r="E499" s="11"/>
     </row>
     <row r="500" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="6"/>
-      <c r="B500" s="22" t="s">
+      <c r="B500" s="21" t="s">
         <v>618</v>
       </c>
-      <c r="C500" s="23"/>
-      <c r="D500" s="23"/>
+      <c r="C500" s="22"/>
+      <c r="D500" s="22"/>
       <c r="E500" s="8"/>
     </row>
     <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B501" s="21"/>
-      <c r="C501" s="21"/>
-      <c r="D501" s="21"/>
+      <c r="B501" s="20"/>
+      <c r="C501" s="20"/>
+      <c r="D501" s="20"/>
       <c r="E501" s="11"/>
     </row>
     <row r="502" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="2"/>
-      <c r="B502" s="21" t="s">
+      <c r="B502" s="20" t="s">
         <v>619</v>
       </c>
-      <c r="C502" s="21"/>
-      <c r="D502" s="21"/>
+      <c r="C502" s="20"/>
+      <c r="D502" s="20"/>
       <c r="E502" s="11"/>
     </row>
     <row r="503" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="2"/>
-      <c r="B503" s="21" t="s">
+      <c r="B503" s="20" t="s">
         <v>620</v>
       </c>
-      <c r="C503" s="21" t="s">
+      <c r="C503" s="20" t="s">
         <v>531</v>
       </c>
-      <c r="D503" s="24" t="s">
+      <c r="D503" s="20" t="s">
         <v>621</v>
       </c>
       <c r="E503" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="F503" s="39" t="s">
+      <c r="F503" s="33" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="2"/>
-      <c r="B504" s="21" t="s">
+      <c r="B504" s="20" t="s">
         <v>624</v>
       </c>
-      <c r="C504" s="21"/>
-      <c r="D504" s="21"/>
+      <c r="C504" s="20"/>
+      <c r="D504" s="20"/>
       <c r="E504" s="11"/>
     </row>
     <row r="505" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="2"/>
-      <c r="B505" s="21" t="s">
+      <c r="B505" s="20" t="s">
         <v>625</v>
       </c>
-      <c r="C505" s="21"/>
-      <c r="D505" s="21"/>
+      <c r="C505" s="20"/>
+      <c r="D505" s="20"/>
       <c r="E505" s="11"/>
     </row>
-    <row r="506" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="2"/>
-      <c r="B506" s="21" t="s">
+      <c r="B506" s="20" t="s">
         <v>626</v>
       </c>
-      <c r="C506" s="21"/>
-      <c r="D506" s="21"/>
+      <c r="C506" s="20"/>
+      <c r="D506" s="20"/>
       <c r="E506" s="11"/>
     </row>
     <row r="507" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="2"/>
-      <c r="B507" s="21" t="s">
+      <c r="B507" s="20" t="s">
         <v>627</v>
       </c>
-      <c r="C507" s="21" t="s">
+      <c r="C507" s="20" t="s">
         <v>628</v>
       </c>
-      <c r="D507" s="21"/>
+      <c r="D507" s="20"/>
       <c r="E507" s="11"/>
     </row>
     <row r="508" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="2"/>
-      <c r="B508" s="21" t="s">
+      <c r="B508" s="20" t="s">
         <v>629</v>
       </c>
-      <c r="C508" s="21" t="s">
+      <c r="C508" s="20" t="s">
         <v>630</v>
       </c>
-      <c r="D508" s="21" t="s">
+      <c r="D508" s="20" t="s">
         <v>631</v>
       </c>
       <c r="E508" s="11" t="s">
@@ -8903,107 +8994,107 @@
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="2"/>
-      <c r="B509" s="21" t="s">
+      <c r="B509" s="20" t="s">
         <v>632</v>
       </c>
-      <c r="C509" s="21" t="s">
+      <c r="C509" s="20" t="s">
         <v>559</v>
       </c>
-      <c r="D509" s="21"/>
+      <c r="D509" s="20"/>
       <c r="E509" s="11"/>
     </row>
     <row r="510" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="2"/>
-      <c r="B510" s="21" t="s">
+      <c r="B510" s="20" t="s">
         <v>633</v>
       </c>
-      <c r="C510" s="21" t="s">
+      <c r="C510" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D510" s="21"/>
+      <c r="D510" s="20"/>
       <c r="E510" s="11"/>
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="2"/>
-      <c r="B511" s="21"/>
-      <c r="C511" s="21"/>
-      <c r="D511" s="21"/>
+      <c r="B511" s="20"/>
+      <c r="C511" s="20"/>
+      <c r="D511" s="20"/>
       <c r="E511" s="11"/>
     </row>
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B512" s="21" t="s">
+      <c r="B512" s="20" t="s">
         <v>634</v>
       </c>
-      <c r="C512" s="21"/>
-      <c r="D512" s="21"/>
+      <c r="C512" s="20"/>
+      <c r="D512" s="20"/>
       <c r="E512" s="11"/>
     </row>
     <row r="513" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2"/>
-      <c r="B513" s="24" t="s">
+      <c r="B513" s="20" t="s">
         <v>635</v>
       </c>
-      <c r="C513" s="36" t="s">
+      <c r="C513" s="31" t="s">
         <v>636</v>
       </c>
-      <c r="D513" s="24"/>
-      <c r="E513" s="18"/>
+      <c r="D513" s="20"/>
+      <c r="E513" s="11"/>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="2"/>
-      <c r="B514" s="21" t="s">
+      <c r="B514" s="20" t="s">
         <v>637</v>
       </c>
-      <c r="C514" s="21"/>
-      <c r="D514" s="21"/>
+      <c r="C514" s="20"/>
+      <c r="D514" s="20"/>
       <c r="E514" s="11"/>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="2"/>
-      <c r="B515" s="21"/>
-      <c r="C515" s="21"/>
-      <c r="D515" s="21"/>
+      <c r="B515" s="20"/>
+      <c r="C515" s="20"/>
+      <c r="D515" s="20"/>
       <c r="E515" s="11"/>
     </row>
     <row r="516" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="6"/>
-      <c r="B516" s="22" t="s">
+      <c r="B516" s="21" t="s">
         <v>638</v>
       </c>
-      <c r="C516" s="23"/>
-      <c r="D516" s="23"/>
+      <c r="C516" s="22"/>
+      <c r="D516" s="22"/>
       <c r="E516" s="8"/>
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B517" s="21"/>
-      <c r="C517" s="21"/>
-      <c r="D517" s="21"/>
+      <c r="B517" s="20"/>
+      <c r="C517" s="20"/>
+      <c r="D517" s="20"/>
       <c r="E517" s="11"/>
     </row>
     <row r="518" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="2"/>
-      <c r="B518" s="21" t="s">
+      <c r="B518" s="20" t="s">
         <v>639</v>
       </c>
-      <c r="C518" s="21"/>
-      <c r="D518" s="21"/>
+      <c r="C518" s="20"/>
+      <c r="D518" s="20"/>
       <c r="E518" s="11"/>
     </row>
     <row r="519" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="2"/>
-      <c r="B519" s="21" t="s">
+      <c r="B519" s="20" t="s">
         <v>640</v>
       </c>
-      <c r="C519" s="21" t="s">
+      <c r="C519" s="20" t="s">
         <v>641</v>
       </c>
-      <c r="D519" s="21" t="s">
+      <c r="D519" s="20" t="s">
         <v>642</v>
       </c>
       <c r="E519" s="11" t="s">
@@ -9012,298 +9103,297 @@
     </row>
     <row r="520" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="2"/>
-      <c r="B520" s="21" t="s">
+      <c r="B520" s="20" t="s">
         <v>643</v>
       </c>
-      <c r="C520" s="21"/>
-      <c r="D520" s="21"/>
+      <c r="C520" s="20"/>
+      <c r="D520" s="20"/>
       <c r="E520" s="11"/>
     </row>
     <row r="521" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="2"/>
-      <c r="B521" s="21" t="s">
+      <c r="B521" s="20" t="s">
         <v>644</v>
       </c>
-      <c r="C521" s="21"/>
-      <c r="D521" s="21"/>
+      <c r="C521" s="20"/>
+      <c r="D521" s="20"/>
       <c r="E521" s="11"/>
     </row>
     <row r="522" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="2"/>
-      <c r="B522" s="21" t="s">
+      <c r="B522" s="20" t="s">
         <v>645</v>
       </c>
-      <c r="C522" s="21" t="s">
+      <c r="C522" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="D522" s="40" t="s">
+      <c r="D522" s="18" t="s">
         <v>646</v>
       </c>
-      <c r="E522" s="41"/>
-      <c r="F522" s="30"/>
+      <c r="E522" s="34"/>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="2"/>
-      <c r="B523" s="21" t="s">
+      <c r="B523" s="20" t="s">
         <v>647</v>
       </c>
-      <c r="C523" s="21"/>
-      <c r="D523" s="21"/>
+      <c r="C523" s="20"/>
+      <c r="D523" s="20"/>
       <c r="E523" s="11"/>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="2"/>
-      <c r="B524" s="21" t="s">
+      <c r="B524" s="20" t="s">
         <v>648</v>
       </c>
-      <c r="C524" s="21"/>
-      <c r="D524" s="21"/>
+      <c r="C524" s="20"/>
+      <c r="D524" s="20"/>
       <c r="E524" s="11"/>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2"/>
-      <c r="B525" s="21" t="s">
+      <c r="B525" s="20" t="s">
         <v>649</v>
       </c>
-      <c r="C525" s="21"/>
-      <c r="D525" s="21"/>
+      <c r="C525" s="20"/>
+      <c r="D525" s="20"/>
       <c r="E525" s="11"/>
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2"/>
-      <c r="B526" s="21" t="s">
+      <c r="B526" s="20" t="s">
         <v>650</v>
       </c>
-      <c r="C526" s="21"/>
-      <c r="D526" s="21"/>
+      <c r="C526" s="20"/>
+      <c r="D526" s="20"/>
       <c r="E526" s="11"/>
     </row>
     <row r="527" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2"/>
-      <c r="B527" s="21" t="s">
+      <c r="B527" s="20" t="s">
         <v>651</v>
       </c>
-      <c r="C527" s="21"/>
-      <c r="D527" s="21"/>
+      <c r="C527" s="20"/>
+      <c r="D527" s="20"/>
       <c r="E527" s="11"/>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="2"/>
-      <c r="B528" s="21" t="s">
+      <c r="B528" s="20" t="s">
         <v>652</v>
       </c>
-      <c r="C528" s="21"/>
-      <c r="D528" s="21"/>
+      <c r="C528" s="20"/>
+      <c r="D528" s="20"/>
       <c r="E528" s="11"/>
     </row>
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="2"/>
-      <c r="B529" s="21" t="s">
+      <c r="B529" s="20" t="s">
         <v>653</v>
       </c>
-      <c r="C529" s="21"/>
-      <c r="D529" s="21"/>
+      <c r="C529" s="20"/>
+      <c r="D529" s="20"/>
       <c r="E529" s="11"/>
     </row>
     <row r="530" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="2"/>
-      <c r="B530" s="21" t="s">
+      <c r="B530" s="20" t="s">
         <v>654</v>
       </c>
-      <c r="C530" s="21" t="s">
+      <c r="C530" s="20" t="s">
         <v>655</v>
       </c>
-      <c r="D530" s="21"/>
+      <c r="D530" s="20"/>
       <c r="E530" s="11"/>
     </row>
     <row r="531" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="2"/>
-      <c r="B531" s="24" t="s">
+      <c r="B531" s="20" t="s">
         <v>656</v>
       </c>
-      <c r="C531" s="24" t="s">
+      <c r="C531" s="20" t="s">
         <v>657</v>
       </c>
-      <c r="D531" s="24"/>
-      <c r="E531" s="18"/>
+      <c r="D531" s="20"/>
+      <c r="E531" s="11"/>
     </row>
     <row r="532" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="2"/>
-      <c r="B532" s="21" t="s">
+      <c r="B532" s="20" t="s">
         <v>658</v>
       </c>
-      <c r="C532" s="21" t="s">
+      <c r="C532" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D532" s="21"/>
+      <c r="D532" s="20"/>
       <c r="E532" s="11"/>
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="2"/>
-      <c r="B533" s="21"/>
-      <c r="C533" s="21"/>
-      <c r="D533" s="21"/>
+      <c r="B533" s="20"/>
+      <c r="C533" s="20"/>
+      <c r="D533" s="20"/>
       <c r="E533" s="11"/>
     </row>
     <row r="534" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B534" s="21" t="s">
+      <c r="B534" s="20" t="s">
         <v>659</v>
       </c>
-      <c r="C534" s="21"/>
-      <c r="D534" s="21"/>
+      <c r="C534" s="20"/>
+      <c r="D534" s="20"/>
       <c r="E534" s="11"/>
     </row>
     <row r="535" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="2"/>
-      <c r="B535" s="21" t="s">
+      <c r="B535" s="20" t="s">
         <v>660</v>
       </c>
-      <c r="C535" s="21"/>
-      <c r="D535" s="21"/>
+      <c r="C535" s="20"/>
+      <c r="D535" s="20"/>
       <c r="E535" s="11"/>
     </row>
     <row r="536" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="2"/>
-      <c r="B536" s="21" t="s">
+      <c r="B536" s="20" t="s">
         <v>661</v>
       </c>
-      <c r="C536" s="21"/>
-      <c r="D536" s="21"/>
+      <c r="C536" s="20"/>
+      <c r="D536" s="20"/>
       <c r="E536" s="11"/>
     </row>
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="2"/>
-      <c r="B537" s="21" t="s">
+      <c r="B537" s="20" t="s">
         <v>662</v>
       </c>
-      <c r="C537" s="21"/>
-      <c r="D537" s="21"/>
+      <c r="C537" s="20"/>
+      <c r="D537" s="20"/>
       <c r="E537" s="11"/>
     </row>
     <row r="538" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="2"/>
-      <c r="B538" s="21" t="s">
+      <c r="B538" s="20" t="s">
         <v>663</v>
       </c>
-      <c r="C538" s="36" t="s">
+      <c r="C538" s="31" t="s">
         <v>657</v>
       </c>
-      <c r="D538" s="24"/>
-      <c r="E538" s="18"/>
+      <c r="D538" s="20"/>
+      <c r="E538" s="11"/>
     </row>
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="2"/>
-      <c r="B539" s="21" t="s">
+      <c r="B539" s="20" t="s">
         <v>664</v>
       </c>
-      <c r="C539" s="21"/>
-      <c r="D539" s="21"/>
+      <c r="C539" s="20"/>
+      <c r="D539" s="20"/>
       <c r="E539" s="11"/>
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="2"/>
-      <c r="B540" s="21" t="s">
+      <c r="B540" s="20" t="s">
         <v>665</v>
       </c>
-      <c r="C540" s="21"/>
-      <c r="D540" s="21"/>
+      <c r="C540" s="20"/>
+      <c r="D540" s="20"/>
       <c r="E540" s="11"/>
     </row>
     <row r="541" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="2"/>
-      <c r="B541" s="21" t="s">
+      <c r="B541" s="20" t="s">
         <v>666</v>
       </c>
-      <c r="C541" s="21"/>
-      <c r="D541" s="21"/>
+      <c r="C541" s="20"/>
+      <c r="D541" s="20"/>
       <c r="E541" s="11"/>
     </row>
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="2"/>
-      <c r="B542" s="21" t="s">
+      <c r="B542" s="20" t="s">
         <v>667</v>
       </c>
-      <c r="C542" s="21"/>
-      <c r="D542" s="21"/>
+      <c r="C542" s="20"/>
+      <c r="D542" s="20"/>
       <c r="E542" s="11"/>
     </row>
     <row r="543" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="2"/>
-      <c r="B543" s="21" t="s">
+      <c r="B543" s="20" t="s">
         <v>668</v>
       </c>
-      <c r="C543" s="21" t="s">
+      <c r="C543" s="20" t="s">
         <v>628</v>
       </c>
-      <c r="D543" s="21"/>
+      <c r="D543" s="20"/>
       <c r="E543" s="11"/>
     </row>
     <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="2"/>
-      <c r="B544" s="21" t="s">
+      <c r="B544" s="20" t="s">
         <v>669</v>
       </c>
-      <c r="C544" s="21"/>
-      <c r="D544" s="21"/>
+      <c r="C544" s="20"/>
+      <c r="D544" s="20"/>
       <c r="E544" s="11"/>
     </row>
     <row r="545" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="2"/>
-      <c r="B545" s="21" t="s">
+      <c r="B545" s="20" t="s">
         <v>670</v>
       </c>
-      <c r="C545" s="21"/>
-      <c r="D545" s="21"/>
+      <c r="C545" s="20"/>
+      <c r="D545" s="20"/>
       <c r="E545" s="11"/>
     </row>
     <row r="546" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="2"/>
-      <c r="B546" s="21" t="s">
+      <c r="B546" s="20" t="s">
         <v>671</v>
       </c>
-      <c r="C546" s="21"/>
-      <c r="D546" s="21"/>
+      <c r="C546" s="20"/>
+      <c r="D546" s="20"/>
       <c r="E546" s="11"/>
     </row>
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="2"/>
-      <c r="B547" s="21" t="s">
+      <c r="B547" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="C547" s="21"/>
-      <c r="D547" s="21"/>
+      <c r="C547" s="20"/>
+      <c r="D547" s="20"/>
       <c r="E547" s="11"/>
     </row>
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="2"/>
-      <c r="B548" s="21" t="s">
+      <c r="B548" s="20" t="s">
         <v>673</v>
       </c>
-      <c r="C548" s="21"/>
-      <c r="D548" s="21"/>
+      <c r="C548" s="20"/>
+      <c r="D548" s="20"/>
       <c r="E548" s="11"/>
     </row>
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="2"/>
-      <c r="B549" s="21" t="s">
+      <c r="B549" s="20" t="s">
         <v>674</v>
       </c>
-      <c r="C549" s="21"/>
-      <c r="D549" s="21"/>
+      <c r="C549" s="20"/>
+      <c r="D549" s="20"/>
       <c r="E549" s="11"/>
     </row>
     <row r="550" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="2"/>
-      <c r="B550" s="21" t="s">
+      <c r="B550" s="20" t="s">
         <v>675</v>
       </c>
-      <c r="C550" s="21" t="s">
+      <c r="C550" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="D550" s="21" t="s">
+      <c r="D550" s="20" t="s">
         <v>676</v>
       </c>
       <c r="E550" s="11" t="s">
@@ -9312,13 +9402,13 @@
     </row>
     <row r="551" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="2"/>
-      <c r="B551" s="21" t="s">
+      <c r="B551" s="20" t="s">
         <v>677</v>
       </c>
-      <c r="C551" s="21" t="s">
+      <c r="C551" s="20" t="s">
         <v>678</v>
       </c>
-      <c r="D551" s="21" t="s">
+      <c r="D551" s="20" t="s">
         <v>679</v>
       </c>
       <c r="E551" s="11" t="s">
@@ -9327,84 +9417,84 @@
     </row>
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="2"/>
-      <c r="B552" s="21" t="s">
+      <c r="B552" s="20" t="s">
         <v>680</v>
       </c>
-      <c r="C552" s="21"/>
-      <c r="D552" s="21"/>
+      <c r="C552" s="20"/>
+      <c r="D552" s="20"/>
       <c r="E552" s="11"/>
     </row>
     <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="2"/>
-      <c r="B553" s="21"/>
-      <c r="C553" s="21"/>
-      <c r="D553" s="21"/>
+      <c r="B553" s="20"/>
+      <c r="C553" s="20"/>
+      <c r="D553" s="20"/>
       <c r="E553" s="11"/>
     </row>
     <row r="554" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B554" s="21" t="s">
+      <c r="B554" s="20" t="s">
         <v>681</v>
       </c>
-      <c r="C554" s="21"/>
-      <c r="D554" s="21"/>
+      <c r="C554" s="20"/>
+      <c r="D554" s="20"/>
       <c r="E554" s="11"/>
     </row>
     <row r="555" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="2"/>
-      <c r="B555" s="21" t="s">
+      <c r="B555" s="20" t="s">
         <v>682</v>
       </c>
-      <c r="C555" s="21"/>
-      <c r="D555" s="21"/>
+      <c r="C555" s="20"/>
+      <c r="D555" s="20"/>
       <c r="E555" s="11"/>
     </row>
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="2"/>
-      <c r="B556" s="21" t="s">
+      <c r="B556" s="20" t="s">
         <v>683</v>
       </c>
-      <c r="C556" s="21"/>
-      <c r="D556" s="21"/>
+      <c r="C556" s="20"/>
+      <c r="D556" s="20"/>
       <c r="E556" s="11"/>
     </row>
     <row r="557" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="2"/>
-      <c r="B557" s="24" t="s">
+      <c r="B557" s="20" t="s">
         <v>684</v>
       </c>
-      <c r="C557" s="36" t="s">
+      <c r="C557" s="31" t="s">
         <v>657</v>
       </c>
-      <c r="D557" s="24"/>
-      <c r="E557" s="18"/>
+      <c r="D557" s="20"/>
+      <c r="E557" s="11"/>
     </row>
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="2"/>
-      <c r="B558" s="21"/>
-      <c r="C558" s="21"/>
-      <c r="D558" s="21"/>
+      <c r="B558" s="20"/>
+      <c r="C558" s="20"/>
+      <c r="D558" s="20"/>
       <c r="E558" s="11"/>
     </row>
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="2"/>
-      <c r="B559" s="21" t="s">
+      <c r="B559" s="20" t="s">
         <v>685</v>
       </c>
-      <c r="C559" s="21"/>
-      <c r="D559" s="21"/>
+      <c r="C559" s="20"/>
+      <c r="D559" s="20"/>
       <c r="E559" s="11"/>
     </row>
     <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A560" s="42"/>
-      <c r="B560" s="43" t="s">
+      <c r="A560" s="35"/>
+      <c r="B560" s="36" t="s">
         <v>686</v>
       </c>
-      <c r="C560" s="43"/>
-      <c r="D560" s="43"/>
-      <c r="E560" s="44"/>
+      <c r="C560" s="36"/>
+      <c r="D560" s="36"/>
+      <c r="E560" s="37"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/assets/responsabilidades.xlsx
+++ b/assets/responsabilidades.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="696">
   <si>
     <t xml:space="preserve">Use Case</t>
   </si>
@@ -393,7 +393,7 @@
     <t xml:space="preserve">Atualizar funcionário</t>
   </si>
   <si>
-    <t xml:space="preserve">atualizarFuncionario(id:int, nome: string, numero_porta: string, rua: string, localidade: string, codigo_postal: string, telemovel: string, email: string, data_nascimento: string, niss: string, nif: string, nus: string, iban: string, salario_hora: float, salario_bruto: float, salario_liquido: float, palavra_passe: string) : void</t>
+    <t xml:space="preserve">atualizarNomeFuncionario(id : int, nome : string) : void &amp;&amp; atualizarNumeroPortaFuncionario(id : int, numero_porta : string) : void &amp;&amp; atualizarRuaFuncionario(id : int, rua : string) : void &amp;&amp; atualizarLocalidadeFuncionario(id : int, localidade : string) : void &amp;&amp; atualizarCodigoPostalFuncionario(id : int, codigo_postal : string) : void &amp;&amp; atualizarTelemovelFuncionario(id : int, telemovel : string) : void &amp;&amp; atualizarEmailFuncionario(id : int, email : string) : void &amp;&amp; atualizarDataNascimentoFuncionario(id : int, data_nascimento : string) : void &amp;&amp; atualizarNISSFuncionario(id : int, niss : string) : void &amp;&amp; atualizarNIFFuncionario(id : int, nif : string) : void &amp;&amp; atualizarNUSFuncionario(id : int, nus : string) : void &amp;&amp; atualizarIBANFuncionario(id : int, iban : string) : void &amp;&amp; atualizarSalarioHoraFuncionario(id : int, salario_hora : float) : void &amp;&amp; atualizarSalarioBrutoFuncionario(id : int, salario_bruto : float) : void &amp;&amp; atualizarSalarioLiquidoFuncionario(id : int, salario_liquido : float) : void &amp;&amp; atualizarPalavraPasseFuncionario(id : int, palavra_passe : string) : void</t>
   </si>
   <si>
     <r>
@@ -688,7 +688,7 @@
     <t xml:space="preserve">Atualizar serviço de reparação</t>
   </si>
   <si>
-    <t xml:space="preserve">atualizarReparacao(id:int, nomenclatura: string, descricao: string, preco: Float) : void</t>
+    <t xml:space="preserve">atualizarNomenclaturaReparacao(id : int, nomenclatura : string) : void &amp;&amp; atualizarDescricaoReparacao(id : int, descricao : string) : void &amp;&amp; atualizarPrecoReparacao(id : int, preco : float) : void</t>
   </si>
   <si>
     <r>
@@ -892,7 +892,7 @@
     <t xml:space="preserve">Atualizar peça</t>
   </si>
   <si>
-    <t xml:space="preserve">atualizarPeca(id: int, referencia: string, stock_minimo: int, preco_venda: float, id_fornecedor: int) : void</t>
+    <t xml:space="preserve">atualizarReferenciaPeca(id : int, referencia : string) : void &amp;&amp; atualizarStockMinimoPeca(id : int, stock_minimo : int) : void &amp;&amp; atualizarPrecoVendaPeca(id : int, preco_venda : float) : void &amp;&amp; atualizarIdFornecedorPeca(id : int, id_fornecedor : int) : void</t>
   </si>
   <si>
     <r>
@@ -941,25 +941,7 @@
     <t xml:space="preserve">Desativar peça</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">removerPeca(id: int) : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">bool</t>
-    </r>
+    <t xml:space="preserve">removerPeca(id: int) : bool</t>
   </si>
   <si>
     <r>
@@ -1043,7 +1025,7 @@
     <t xml:space="preserve">Criar entradas de stock</t>
   </si>
   <si>
-    <t xml:space="preserve">registarStock_PecaNormal(id_peca: int, preco_compra: float, data: DateTime, quantidade : int): Stock &amp;&amp; registarStock_PecaSuperior70(id_peca: int, preco_compra: float, data: DateTime, quantidade : int, garantia : int, nrs_serie : List(string)): Stock</t>
+    <t xml:space="preserve">registarStock_PecaSuperior70(id_peca : int, preco_compra : float, data : DateTime, garantia : int, nr_serie : string) : Stock &amp;&amp; registarStock_PecaNormal(id_peca : int, preco_compra : float, data : DateTime) : Stock</t>
   </si>
   <si>
     <t xml:space="preserve">11. O sistema regista a data e a hora seguindo o formato (YYYY-MM-DD-HH:MM), juntamente com
@@ -1133,7 +1115,7 @@
     <t xml:space="preserve">Atualizar entrada de stock</t>
   </si>
   <si>
-    <t xml:space="preserve">atualizarStock(id_stock: int, id_peca: int, preco_compra: float, data_rececao : DateTime) : void</t>
+    <t xml:space="preserve">atualizarIdPecaStock(id_stock : int, id_peca : int) : void &amp;&amp; atualizarPrecoCompraStock(id_stock : int, preco_compra : float) : void &amp;&amp; atualizarDataRececaoStock(id_stock : int, data_rececao : DateTime) : void &amp;&amp; atualizarGarantiaStock(id_stock : int, garantia : int) : void &amp;&amp; atualizarNrSerieStock(id_stock : int, nr_serie : string) : void</t>
   </si>
   <si>
     <r>
@@ -1201,7 +1183,7 @@
     <t xml:space="preserve">Criar devolução</t>
   </si>
   <si>
-    <t xml:space="preserve">criarDevoluçao(data_devolucao: DateTime, motivo: string, peca : Stock): Devolucao</t>
+    <t xml:space="preserve">criarDevoluçao(data_devolucao: DateTime, motivo: string, id_stock : int): Devolucao</t>
   </si>
   <si>
     <t xml:space="preserve">10. O sistema diminui a quantidade em stock da peça consoante a quantidade especificada na devolução.</t>
@@ -1210,7 +1192,7 @@
     <t xml:space="preserve">Atualizar stock</t>
   </si>
   <si>
-    <t xml:space="preserve">alteraEstado_Stock_PendenteDevolucao(pecas: List(string)) : void</t>
+    <t xml:space="preserve">atualizaEstadoStock(id : int, estado : EstadosStock) : void</t>
   </si>
   <si>
     <t xml:space="preserve"> (alterar o estado das entradas de stock para ‘PendenteDevolucao’)</t>
@@ -1355,6 +1337,9 @@
     <t xml:space="preserve">Validar estado</t>
   </si>
   <si>
+    <t xml:space="preserve">validaEstadoDevolucao_PendenteDevolucao(id : int) : bool</t>
+  </si>
+  <si>
     <t xml:space="preserve">5. O funcionário confirma a eliminação</t>
   </si>
   <si>
@@ -1364,25 +1349,7 @@
     <t xml:space="preserve">Remover devolução</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">removerDevolucao(id:int) : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">bool</t>
-    </r>
+    <t xml:space="preserve">removerDevolucao(id:int) : bool</t>
   </si>
   <si>
     <t xml:space="preserve">7. O sistema aumenta os gastos em peças do mês atual no valor de compra da peça multiplicado pela quantidade especificada na devolução</t>
@@ -1497,7 +1464,7 @@
     <t xml:space="preserve">Atualizar fornecedor</t>
   </si>
   <si>
-    <t xml:space="preserve">atualizarFornecedor(id: int, nome: string, telemóvel: string, email_string) : void</t>
+    <t xml:space="preserve">atualizarNomeFornecedor(id : int, nome : string) : void &amp;&amp; atualizarTelemovelFornecedor(id : int, telemovel : string) : void &amp;&amp; atualizarEmailFornecedor(id : int, email : string) : void</t>
   </si>
   <si>
     <r>
@@ -1544,25 +1511,7 @@
     <t xml:space="preserve">Remover fornecedor</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">removerFornecedor(id: int) : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">bool</t>
-    </r>
+    <t xml:space="preserve">removerFornecedor(id: int) : bool</t>
   </si>
   <si>
     <r>
@@ -1710,7 +1659,7 @@
     <t xml:space="preserve">Atualizar lista encomendas</t>
   </si>
   <si>
-    <t xml:space="preserve">atualizarEncomenda(id: int, pecas: List(Stock)) : void</t>
+    <t xml:space="preserve">atualizarPecasEncomenda(id : int, pecas : List(Stock)) : void &amp;&amp; atualizarDataChegadaEncomenda(id : int, data_chegada : DateTime) : void &amp;&amp; atualizarDataPedidoEncomenda(id : int, data_pedido : DateTime) : void &amp;&amp; atualizarEstadoEncomenda(id : int, estado : EstadoEncomenda) : void</t>
   </si>
   <si>
     <t xml:space="preserve">(1) [Estado alterado de 'Rascunho' para 'Enviada'] (Passo 8)</t>
@@ -1811,25 +1760,7 @@
     <t xml:space="preserve">Remover lista</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">removerEncomenda(id: int) : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">bool</t>
-    </r>
+    <t xml:space="preserve">removerEncomenda(id: int) : bool</t>
   </si>
   <si>
     <r>
@@ -1944,7 +1875,7 @@
     <t xml:space="preserve">Atualizar cliente</t>
   </si>
   <si>
-    <t xml:space="preserve">atualizarCliente(id: int, nome: string, email: string, telemóvel: string, nif: string) : void</t>
+    <t xml:space="preserve">atualizarNomeCliente(id : int, nome : string) : void &amp;&amp; atualizarEmailCliente(id : int, email : string) : void &amp;&amp; atualizarTelemovelCliente(id : int, telemovel : string) : void &amp;&amp; atualizarNIFCliente(id : int, nif : string) : void</t>
   </si>
   <si>
     <r>
@@ -1988,25 +1919,7 @@
     <t xml:space="preserve">Remover cliente</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">removerCliente(id: int) : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">bool</t>
-    </r>
+    <t xml:space="preserve">removerCliente(id: int) : bool</t>
   </si>
   <si>
     <r>
@@ -2160,7 +2073,7 @@
     <t xml:space="preserve">Atualizar trotinete</t>
   </si>
   <si>
-    <t xml:space="preserve">atualizarTrotinete(id: int, modelo: string, marca: string, numero_serie: string, tipo_motor : string) : void</t>
+    <t xml:space="preserve">atualizarModeloTrotinete(id : int, modelo : string) : void &amp;&amp; atualizarMarcaTrotinete(id : int, marca : string) : void &amp;&amp; atualizarNumeroSerieTrotinete(id : int, numero_serie : string) : void &amp;&amp; atualizarTipoMotorTrotinete(id : int, tipo_motor : string) : void</t>
   </si>
   <si>
     <r>
@@ -2204,25 +2117,7 @@
     <t xml:space="preserve">Remover trotinete</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">removerTrotinete(id: int) : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">bool</t>
-    </r>
+    <t xml:space="preserve">removerTrotinete(id: int) : bool</t>
   </si>
   <si>
     <r>
@@ -2475,7 +2370,13 @@
     <t xml:space="preserve">4.2.1.1 O funcionário regista a notificação de término</t>
   </si>
   <si>
-    <t xml:space="preserve">acho que não temos nada no sistema sobre Notificações (?)</t>
+    <t xml:space="preserve">criarNotificacao(descricao : string, id_remetente : int, id_destinatario : int) : Notificacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notificacoes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notificação enviada da secretaria para o cliente</t>
   </si>
   <si>
     <t xml:space="preserve">4.2.1.2 O funcionário confirma a notificação de término</t>
@@ -2526,6 +2427,9 @@
     <t xml:space="preserve">Validar notificação</t>
   </si>
   <si>
+    <t xml:space="preserve">obterNotificacoesPorClienteEIntervalo(id_cliente : int, data_inicio : DateTime, data_fim : DateTime) : List(Notificacao)</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.2.3.2 O sistema valida que não existem outras OS pendentes do mesmo cliente com data anterior</t>
   </si>
   <si>
@@ -2542,6 +2446,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.2.3.5 O sistema regista o pagamento e altera o estado da OS para 'Paga'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alterarEstadoOS(id : int, estado : EstadoOS) : void</t>
   </si>
   <si>
     <t xml:space="preserve">4.2.3.6 Retorna ao passo 10</t>
@@ -2597,25 +2504,7 @@
     <t xml:space="preserve">6. O sistema altera o estado da OS para Eliminada, regista data, hora e utilizador, impossibilita o uso dos dados da OS para estatí­sticas e apresenta mensagem de eliminação bem-sucedida</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">removerOS(id: int) : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">bool</t>
-    </r>
+    <t xml:space="preserve">removerOS(id: int) : bool</t>
   </si>
   <si>
     <r>
@@ -2674,7 +2563,7 @@
     <t xml:space="preserve">Filtrar OS</t>
   </si>
   <si>
-    <t xml:space="preserve">filtrarOSs(estado: EstadoOS, desde: DateTime, ate: DateTime, id_cliente: int, id_funcionario: int): List(Ordemservico)</t>
+    <t xml:space="preserve">filtrarOSsPorCliente(id_cliente : int) : List(OrdemServico) &amp;&amp; filtrarOSsPorFuncionario(id_funcionario : int) : List(OrdemServico) &amp;&amp; filtrarOSsPorIntervalo(desde : DateTime, ate : DateTime) : List(OrdemServico) &amp;&amp; filtrarOSsPorClienteEIntervalo(id_cliente : int, desde : DateTime, ate : DateTime) : List(OrdemServico) &amp;&amp; filtrarOSsPorFuncionarioEIntervalo(id_funcionario : int, desde : DateTime, ate : DateTime) : List(OrdemServico) &amp;&amp; filtrarOSsPorClienteEFuncionario(id_cliente : int, id_funcionario : int) : List(OrdemServico)</t>
   </si>
   <si>
     <t xml:space="preserve">8. O sistema apresenta todas as ordens de serviço filtradas, incluindo: identificador, cliente, trotinete, estado, data de criação, funcionário responsável, valor total do orçamento e, se aplicável, data da última alteração</t>
@@ -2739,7 +2628,7 @@
     <t xml:space="preserve">Validar limite orçamento</t>
   </si>
   <si>
-    <t xml:space="preserve">calcularOrcamento(pecas: List(Stock), reparacoes : List(Reparacao)): float</t>
+    <t xml:space="preserve">calcularOrcamento(listaPecas: List(QuantidadePeca), reparacoes : List(Reparacao)): float</t>
   </si>
   <si>
     <t xml:space="preserve">8. O sistema altera o estado da OS para 'Pendente Reparação'</t>
@@ -2754,7 +2643,49 @@
     <t xml:space="preserve">7.1 O sistema altera o estado da OS para 'Pendente aprovação do orçamento' e gera um alerta com o identificador da OS e o seu estado para a secretária</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerar alerta</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Gerar alerta &amp;&amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Atualizar estado OS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">criarNotificacao(descricao : string, id_remetente : int, id_destinatario : int) : Notificacao &amp;&amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">alterarEstadoOS(id : int, estado : EstadoOS) : void</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Ordens de Serviço &amp;&amp; Notificacoes</t>
   </si>
   <si>
     <t xml:space="preserve">7.2 Retorna ao passo 9</t>
@@ -2792,19 +2723,22 @@
     <t xml:space="preserve">Validar stock</t>
   </si>
   <si>
-    <t xml:space="preserve">pecasDisponiveisReparacao(id_OS: int): bool</t>
+    <t xml:space="preserve">pecasDiagnosticoDisponiveisReparacao(id_OS: int): bool</t>
   </si>
   <si>
     <t xml:space="preserve">3. O funcionário consulta os dados completos da OS, incluindo o histórico de reparações anteriores da trotinete e as reparações e peças prescritas no diagnóstico</t>
   </si>
   <si>
+    <t xml:space="preserve">obterPecasQuantidadeDiagnosticoOS(id_OS : int) : List(QuantidadePeca) &amp;&amp; obterReparacoesDiagnosticoOS(id_OS : int) : List(Reparacao)</t>
+  </si>
+  <si>
     <t xml:space="preserve">4. O funcionário marca as reparações prescritas que executou como concluí­das e as peças prescritas (e disponí­veis em stock) que precisou como utilizadas</t>
   </si>
   <si>
     <t xml:space="preserve">5. O sistema desconta do stock as quantidades das peças marcadas como utilizadas e regista a data, hora e utilizador</t>
   </si>
   <si>
-    <t xml:space="preserve">Pensar bem</t>
+    <t xml:space="preserve">Muda o estado das entradas de stock para Usada</t>
   </si>
   <si>
     <t xml:space="preserve">6. O funcionário não pretende adicionar reparações adicionais</t>
@@ -2834,6 +2768,9 @@
     <t xml:space="preserve">Validar checklist</t>
   </si>
   <si>
+    <t xml:space="preserve">validarCheckList_ConsertoOS(idOS : int) : bool</t>
+  </si>
+  <si>
     <t xml:space="preserve">14. O sistema calcula o custo final da reparação, altera o estado da OS para 'Pendente Pagamento', gera um alerta para a secretária, regista a data, hora e funcionário que realizou a reparação e apresenta um resumo final da OS</t>
   </si>
   <si>
@@ -2894,25 +2831,7 @@
     <t xml:space="preserve">8.5 O sistema valida que existem peças iguais na mesma quantidade disponí­veis em stock e adiciona-as às lista de peças usadas e remove as peças defeituosas da lista de peças utilizadas</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">removerPecaConserto_OS(id_OS:int, id_Stock:int) : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">bool</t>
-    </r>
+    <t xml:space="preserve">removerPecaConserto_OS(id_OS:int, id_Stock:int) : bool &amp;&amp; adicionarPecaConserto_OS(id_OS : int, id_Stock : int) : void</t>
   </si>
   <si>
     <t xml:space="preserve">8.6 O sistema cria um registo de devolução marcando as peças defeituosas como 'Possí­vel defeito', repõe ao stock a quantidade correspondente e gera um alerta para o gestor de stock</t>
@@ -3016,12 +2935,6 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -3033,8 +2946,14 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3057,12 +2976,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFC9211E"/>
       </patternFill>
     </fill>
   </fills>
@@ -3191,7 +3104,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3284,11 +3197,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3296,7 +3213,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3316,19 +3233,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3533,7 +3450,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="65.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="35.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="65.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
@@ -4224,7 +4141,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="244.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
       <c r="B58" s="10" t="s">
         <v>101</v>
@@ -4785,7 +4702,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2"/>
       <c r="B111" s="10" t="s">
         <v>163</v>
@@ -5190,7 +5107,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2"/>
       <c r="B148" s="10" t="s">
         <v>210</v>
@@ -5646,7 +5563,7 @@
       <c r="D189" s="12"/>
       <c r="E189" s="12"/>
     </row>
-    <row r="190" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2"/>
       <c r="B190" s="10" t="s">
         <v>263</v>
@@ -6118,13 +6035,17 @@
       <c r="C233" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="D233" s="20"/>
-      <c r="E233" s="11"/>
+      <c r="D233" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="E233" s="11" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2"/>
       <c r="B234" s="20" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C234" s="20"/>
       <c r="D234" s="20"/>
@@ -6133,13 +6054,13 @@
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2"/>
       <c r="B235" s="20" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C235" s="20" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D235" s="20" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E235" s="11" t="s">
         <v>181</v>
@@ -6148,18 +6069,22 @@
     <row r="236" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2"/>
       <c r="B236" s="20" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C236" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="D236" s="20"/>
-      <c r="E236" s="11"/>
+      <c r="D236" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="E236" s="11" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="237" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="2"/>
       <c r="B237" s="20" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C237" s="20"/>
       <c r="D237" s="20"/>
@@ -6168,7 +6093,7 @@
     <row r="238" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2"/>
       <c r="B238" s="20" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C238" s="20" t="s">
         <v>74</v>
@@ -6194,7 +6119,7 @@
     <row r="240" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="6"/>
       <c r="B240" s="21" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C240" s="22"/>
       <c r="D240" s="22"/>
@@ -6212,7 +6137,7 @@
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2"/>
       <c r="B242" s="20" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C242" s="20"/>
       <c r="D242" s="20"/>
@@ -6221,7 +6146,7 @@
     <row r="243" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2"/>
       <c r="B243" s="20" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C243" s="20"/>
       <c r="D243" s="20"/>
@@ -6230,7 +6155,7 @@
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2"/>
       <c r="B244" s="20" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C244" s="20"/>
       <c r="D244" s="20"/>
@@ -6250,10 +6175,10 @@
     <row r="246" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="2"/>
       <c r="B246" s="20" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C246" s="20" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D246" s="20"/>
       <c r="E246" s="11"/>
@@ -6261,13 +6186,13 @@
     <row r="247" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="2"/>
       <c r="B247" s="20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C247" s="20" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D247" s="20" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E247" s="11" t="s">
         <v>181</v>
@@ -6276,7 +6201,7 @@
     <row r="248" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2"/>
       <c r="B248" s="20" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C248" s="20" t="s">
         <v>74</v>
@@ -6298,7 +6223,7 @@
     <row r="250" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="6"/>
       <c r="B250" s="21" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C250" s="22"/>
       <c r="D250" s="22"/>
@@ -6316,7 +6241,7 @@
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2"/>
       <c r="B252" s="20" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C252" s="20"/>
       <c r="D252" s="20"/>
@@ -6325,13 +6250,13 @@
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2"/>
       <c r="B253" s="20" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C253" s="20" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D253" s="20" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E253" s="11" t="s">
         <v>181</v>
@@ -6340,7 +6265,7 @@
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="2"/>
       <c r="B254" s="20" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C254" s="20"/>
       <c r="D254" s="20"/>
@@ -6367,7 +6292,7 @@
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="2"/>
       <c r="B257" s="20" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C257" s="20" t="s">
         <v>21</v>
@@ -6378,10 +6303,10 @@
     <row r="258" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="2"/>
       <c r="B258" s="20" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C258" s="20" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D258" s="20"/>
       <c r="E258" s="11"/>
@@ -6389,7 +6314,7 @@
     <row r="259" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2"/>
       <c r="B259" s="20" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C259" s="20" t="s">
         <v>74</v>
@@ -6401,16 +6326,16 @@
         <v>181</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="2"/>
       <c r="B260" s="20" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C260" s="20" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D260" s="20" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E260" s="11" t="s">
         <v>181</v>
@@ -6426,7 +6351,7 @@
     <row r="262" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="6"/>
       <c r="B262" s="21" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C262" s="22"/>
       <c r="D262" s="22"/>
@@ -6444,7 +6369,7 @@
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="2"/>
       <c r="B264" s="20" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C264" s="20"/>
       <c r="D264" s="20"/>
@@ -6453,13 +6378,13 @@
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="2"/>
       <c r="B265" s="20" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C265" s="20" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D265" s="20" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E265" s="11" t="s">
         <v>181</v>
@@ -6468,7 +6393,7 @@
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="2"/>
       <c r="B266" s="20" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C266" s="20"/>
       <c r="D266" s="20"/>
@@ -6477,7 +6402,7 @@
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2"/>
       <c r="B267" s="20" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C267" s="20"/>
       <c r="D267" s="20"/>
@@ -6486,7 +6411,7 @@
     <row r="268" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="2"/>
       <c r="B268" s="20" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C268" s="20" t="s">
         <v>74</v>
@@ -6501,13 +6426,13 @@
     <row r="269" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="2"/>
       <c r="B269" s="20" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C269" s="20" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D269" s="20" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E269" s="11" t="s">
         <v>181</v>
@@ -6525,7 +6450,7 @@
     <row r="271" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="6"/>
       <c r="B271" s="21" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C271" s="22"/>
       <c r="D271" s="22"/>
@@ -6543,7 +6468,7 @@
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="2"/>
       <c r="B273" s="20" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C273" s="20"/>
       <c r="D273" s="20"/>
@@ -6552,7 +6477,7 @@
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="2"/>
       <c r="B274" s="20" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C274" s="20"/>
       <c r="D274" s="20"/>
@@ -6561,28 +6486,28 @@
     <row r="275" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="2"/>
       <c r="B275" s="20" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C275" s="20" t="s">
-        <v>361</v>
-      </c>
-      <c r="D275" s="23" t="s">
         <v>362</v>
       </c>
-      <c r="E275" s="24" t="s">
+      <c r="D275" s="24" t="s">
+        <v>363</v>
+      </c>
+      <c r="E275" s="25" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="2"/>
       <c r="B276" s="20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C276" s="20" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D276" s="20" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E276" s="11" t="s">
         <v>181</v>
@@ -6591,7 +6516,7 @@
     <row r="277" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="2"/>
       <c r="B277" s="20" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C277" s="20"/>
       <c r="D277" s="20"/>
@@ -6600,7 +6525,7 @@
     <row r="278" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="2"/>
       <c r="B278" s="20" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C278" s="20"/>
       <c r="D278" s="20"/>
@@ -6609,7 +6534,7 @@
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="2"/>
       <c r="B279" s="20" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C279" s="20"/>
       <c r="D279" s="20"/>
@@ -6618,7 +6543,7 @@
     <row r="280" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="2"/>
       <c r="B280" s="20" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C280" s="20"/>
       <c r="D280" s="20"/>
@@ -6627,7 +6552,7 @@
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="2"/>
       <c r="B281" s="20" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C281" s="20"/>
       <c r="D281" s="20"/>
@@ -6636,10 +6561,10 @@
     <row r="282" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="2"/>
       <c r="B282" s="20" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C282" s="20" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D282" s="20"/>
       <c r="E282" s="11"/>
@@ -6647,13 +6572,13 @@
     <row r="283" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="2"/>
       <c r="B283" s="20" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C283" s="20" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D283" s="20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E283" s="11" t="s">
         <v>181</v>
@@ -6662,7 +6587,7 @@
     <row r="284" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="2"/>
       <c r="B284" s="20" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C284" s="20" t="s">
         <v>74</v>
@@ -6684,7 +6609,7 @@
     <row r="286" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="6"/>
       <c r="B286" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C286" s="22"/>
       <c r="D286" s="22"/>
@@ -6702,7 +6627,7 @@
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="2"/>
       <c r="B288" s="20" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C288" s="20"/>
       <c r="D288" s="20"/>
@@ -6711,13 +6636,13 @@
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="2"/>
       <c r="B289" s="20" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C289" s="20" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D289" s="20" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E289" s="11" t="s">
         <v>181</v>
@@ -6726,7 +6651,7 @@
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="2"/>
       <c r="B290" s="20" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C290" s="20"/>
       <c r="D290" s="20"/>
@@ -6735,13 +6660,13 @@
     <row r="291" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="2"/>
       <c r="B291" s="20" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C291" s="20" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D291" s="20" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E291" s="11" t="s">
         <v>181</v>
@@ -6750,7 +6675,7 @@
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2"/>
       <c r="B292" s="20" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C292" s="20"/>
       <c r="D292" s="20"/>
@@ -6759,7 +6684,7 @@
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="2"/>
       <c r="B293" s="20" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C293" s="20"/>
       <c r="D293" s="20"/>
@@ -6768,7 +6693,7 @@
     <row r="294" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="2"/>
       <c r="B294" s="20" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C294" s="20" t="s">
         <v>74</v>
@@ -6783,7 +6708,7 @@
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="2"/>
       <c r="B295" s="20" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C295" s="20" t="s">
         <v>298</v>
@@ -6791,16 +6716,16 @@
       <c r="D295" s="20"/>
       <c r="E295" s="11"/>
     </row>
-    <row r="296" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="2"/>
       <c r="B296" s="20" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C296" s="20" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D296" s="20" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E296" s="11" t="s">
         <v>181</v>
@@ -6818,7 +6743,7 @@
         <v>244</v>
       </c>
       <c r="B298" s="20" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C298" s="20"/>
       <c r="D298" s="20"/>
@@ -6827,7 +6752,7 @@
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="2"/>
       <c r="B299" s="20" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C299" s="20"/>
       <c r="D299" s="20"/>
@@ -6836,7 +6761,7 @@
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="2"/>
       <c r="B300" s="20" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C300" s="20"/>
       <c r="D300" s="20"/>
@@ -6845,10 +6770,10 @@
     <row r="301" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="2"/>
       <c r="B301" s="20" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C301" s="20" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D301" s="20"/>
       <c r="E301" s="11"/>
@@ -6856,13 +6781,13 @@
     <row r="302" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="2"/>
       <c r="B302" s="20" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C302" s="20" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D302" s="20" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E302" s="11" t="s">
         <v>181</v>
@@ -6871,7 +6796,7 @@
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="2"/>
       <c r="B303" s="20" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C303" s="20"/>
       <c r="D303" s="20"/>
@@ -6880,7 +6805,7 @@
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="2"/>
       <c r="B304" s="20" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C304" s="20"/>
       <c r="D304" s="20"/>
@@ -6889,7 +6814,7 @@
     <row r="305" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="2"/>
       <c r="B305" s="20" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C305" s="20"/>
       <c r="D305" s="20"/>
@@ -6898,7 +6823,7 @@
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="2"/>
       <c r="B306" s="20" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C306" s="20"/>
       <c r="D306" s="20"/>
@@ -6907,10 +6832,10 @@
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="2"/>
       <c r="B307" s="20" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C307" s="20" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D307" s="20"/>
       <c r="E307" s="11"/>
@@ -6918,10 +6843,10 @@
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="2"/>
       <c r="B308" s="20" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C308" s="20" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D308" s="20"/>
       <c r="E308" s="11"/>
@@ -6929,13 +6854,13 @@
     <row r="309" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="2"/>
       <c r="B309" s="20" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C309" s="20" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D309" s="20" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E309" s="11" t="s">
         <v>181</v>
@@ -6944,7 +6869,7 @@
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="2"/>
       <c r="B310" s="20" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C310" s="20"/>
       <c r="D310" s="20"/>
@@ -6960,7 +6885,7 @@
     <row r="312" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="6"/>
       <c r="B312" s="21" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C312" s="22"/>
       <c r="D312" s="22"/>
@@ -6978,7 +6903,7 @@
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="2"/>
       <c r="B314" s="20" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C314" s="20"/>
       <c r="D314" s="20"/>
@@ -6987,7 +6912,7 @@
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="2"/>
       <c r="B315" s="20" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C315" s="20"/>
       <c r="D315" s="20"/>
@@ -6996,7 +6921,7 @@
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="2"/>
       <c r="B316" s="20" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C316" s="20"/>
       <c r="D316" s="20"/>
@@ -7005,7 +6930,7 @@
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="2"/>
       <c r="B317" s="20" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C317" s="20"/>
       <c r="D317" s="20"/>
@@ -7014,7 +6939,7 @@
     <row r="318" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="2"/>
       <c r="B318" s="20" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C318" s="20" t="s">
         <v>74</v>
@@ -7029,13 +6954,13 @@
     <row r="319" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="2"/>
       <c r="B319" s="20" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C319" s="20" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D319" s="20" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E319" s="11" t="s">
         <v>181</v>
@@ -7051,7 +6976,7 @@
     <row r="321" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="6"/>
       <c r="B321" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C321" s="22"/>
       <c r="D321" s="22"/>
@@ -7069,7 +6994,7 @@
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="2"/>
       <c r="B323" s="20" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C323" s="20"/>
       <c r="D323" s="20"/>
@@ -7078,7 +7003,7 @@
     <row r="324" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="2"/>
       <c r="B324" s="20" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C324" s="20"/>
       <c r="D324" s="20"/>
@@ -7087,7 +7012,7 @@
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="2"/>
       <c r="B325" s="20" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C325" s="20"/>
       <c r="D325" s="20"/>
@@ -7107,7 +7032,7 @@
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="2"/>
       <c r="B327" s="20" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C327" s="20" t="s">
         <v>40</v>
@@ -7118,10 +7043,10 @@
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="2"/>
       <c r="B328" s="20" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C328" s="20" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D328" s="20"/>
       <c r="E328" s="11"/>
@@ -7129,7 +7054,7 @@
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="2"/>
       <c r="B329" s="20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C329" s="20" t="s">
         <v>49</v>
@@ -7140,22 +7065,22 @@
     <row r="330" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="2"/>
       <c r="B330" s="20" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C330" s="20" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D330" s="20" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E330" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="2"/>
       <c r="B331" s="20" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C331" s="20" t="s">
         <v>74</v>
@@ -7164,7 +7089,7 @@
         <v>75</v>
       </c>
       <c r="E331" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7177,7 +7102,7 @@
     <row r="333" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="6"/>
       <c r="B333" s="21" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C333" s="22"/>
       <c r="D333" s="22"/>
@@ -7195,7 +7120,7 @@
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="2"/>
       <c r="B335" s="20" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C335" s="20"/>
       <c r="D335" s="20"/>
@@ -7204,22 +7129,22 @@
     <row r="336" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="2"/>
       <c r="B336" s="20" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C336" s="20" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D336" s="20" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E336" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="2"/>
       <c r="B337" s="20" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C337" s="20"/>
       <c r="D337" s="20"/>
@@ -7246,7 +7171,7 @@
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="2"/>
       <c r="B340" s="20" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C340" s="20" t="s">
         <v>21</v>
@@ -7257,7 +7182,7 @@
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="2"/>
       <c r="B341" s="20" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C341" s="20" t="s">
         <v>40</v>
@@ -7268,10 +7193,10 @@
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="2"/>
       <c r="B342" s="20" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C342" s="20" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D342" s="20"/>
       <c r="E342" s="11"/>
@@ -7279,7 +7204,7 @@
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="2"/>
       <c r="B343" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C343" s="20" t="s">
         <v>49</v>
@@ -7290,7 +7215,7 @@
     <row r="344" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="2"/>
       <c r="B344" s="20" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C344" s="20" t="s">
         <v>74</v>
@@ -7299,22 +7224,22 @@
         <v>75</v>
       </c>
       <c r="E344" s="11" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="345" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="345" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="2"/>
       <c r="B345" s="20" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C345" s="20" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D345" s="20" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E345" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7327,7 +7252,7 @@
     <row r="347" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="6"/>
       <c r="B347" s="21" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C347" s="22"/>
       <c r="D347" s="22"/>
@@ -7345,7 +7270,7 @@
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="2"/>
       <c r="B349" s="20" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C349" s="20"/>
       <c r="D349" s="20"/>
@@ -7354,22 +7279,22 @@
     <row r="350" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="2"/>
       <c r="B350" s="20" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C350" s="20" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D350" s="20" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E350" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="2"/>
       <c r="B351" s="20" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C351" s="20"/>
       <c r="D351" s="20"/>
@@ -7378,7 +7303,7 @@
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="2"/>
       <c r="B352" s="20" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C352" s="20"/>
       <c r="D352" s="20"/>
@@ -7387,7 +7312,7 @@
     <row r="353" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="2"/>
       <c r="B353" s="20" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C353" s="20" t="s">
         <v>74</v>
@@ -7396,22 +7321,22 @@
         <v>75</v>
       </c>
       <c r="E353" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="2"/>
       <c r="B354" s="20" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C354" s="20" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D354" s="20" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E354" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7424,7 +7349,7 @@
     <row r="356" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="6"/>
       <c r="B356" s="21" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C356" s="22"/>
       <c r="D356" s="22"/>
@@ -7442,7 +7367,7 @@
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2"/>
       <c r="B358" s="20" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C358" s="20"/>
       <c r="D358" s="20"/>
@@ -7451,7 +7376,7 @@
     <row r="359" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="2"/>
       <c r="B359" s="20" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C359" s="20"/>
       <c r="D359" s="20"/>
@@ -7460,22 +7385,22 @@
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="2"/>
       <c r="B360" s="20" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C360" s="20" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D360" s="20" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E360" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="2"/>
       <c r="B361" s="20" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C361" s="20"/>
       <c r="D361" s="20"/>
@@ -7484,7 +7409,7 @@
     <row r="362" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="2"/>
       <c r="B362" s="20" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C362" s="20"/>
       <c r="D362" s="20"/>
@@ -7493,7 +7418,7 @@
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="2"/>
       <c r="B363" s="20" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C363" s="20"/>
       <c r="D363" s="20"/>
@@ -7502,40 +7427,40 @@
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="2"/>
       <c r="B364" s="20" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C364" s="20" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D364" s="20" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E364" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="2"/>
       <c r="B365" s="20" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C365" s="20" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D365" s="20" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E365" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="2"/>
       <c r="B366" s="20" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C366" s="20" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D366" s="20"/>
       <c r="E366" s="11"/>
@@ -7543,37 +7468,37 @@
     <row r="367" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="2"/>
       <c r="B367" s="20" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C367" s="20" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D367" s="20" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E367" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="2"/>
       <c r="B368" s="20" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C368" s="20" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D368" s="20" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E368" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="2"/>
       <c r="B369" s="20" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C369" s="20" t="s">
         <v>74</v>
@@ -7582,7 +7507,7 @@
         <v>75</v>
       </c>
       <c r="E369" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7593,9 +7518,9 @@
       <c r="E370" s="11"/>
     </row>
     <row r="371" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="25"/>
+      <c r="A371" s="26"/>
       <c r="B371" s="21" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C371" s="22"/>
       <c r="D371" s="22"/>
@@ -7613,7 +7538,7 @@
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="2"/>
       <c r="B373" s="20" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C373" s="20"/>
       <c r="D373" s="20"/>
@@ -7622,22 +7547,22 @@
     <row r="374" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="2"/>
       <c r="B374" s="20" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C374" s="20" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D374" s="20" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E374" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="2"/>
       <c r="B375" s="20" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C375" s="20"/>
       <c r="D375" s="20"/>
@@ -7646,7 +7571,7 @@
     <row r="376" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="2"/>
       <c r="B376" s="20" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C376" s="20"/>
       <c r="D376" s="20"/>
@@ -7664,10 +7589,10 @@
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="2"/>
       <c r="B378" s="20" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C378" s="20" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D378" s="20"/>
       <c r="E378" s="11"/>
@@ -7675,10 +7600,10 @@
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="2"/>
       <c r="B379" s="20" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C379" s="20" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D379" s="20"/>
       <c r="E379" s="11"/>
@@ -7686,10 +7611,10 @@
     <row r="380" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2"/>
       <c r="B380" s="20" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C380" s="20" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D380" s="20"/>
       <c r="E380" s="11"/>
@@ -7697,10 +7622,10 @@
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="2"/>
       <c r="B381" s="20" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C381" s="20" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D381" s="20"/>
       <c r="E381" s="11"/>
@@ -7708,7 +7633,7 @@
     <row r="382" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="2"/>
       <c r="B382" s="20" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C382" s="20" t="s">
         <v>74</v>
@@ -7717,22 +7642,22 @@
         <v>75</v>
       </c>
       <c r="E382" s="11" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="383" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="383" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="2"/>
       <c r="B383" s="20" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C383" s="20" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D383" s="20" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E383" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7745,7 +7670,7 @@
     <row r="385" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="6"/>
       <c r="B385" s="21" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C385" s="22"/>
       <c r="D385" s="22"/>
@@ -7763,7 +7688,7 @@
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="2"/>
       <c r="B387" s="20" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C387" s="20"/>
       <c r="D387" s="20"/>
@@ -7772,22 +7697,22 @@
     <row r="388" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="2"/>
       <c r="B388" s="20" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C388" s="20" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D388" s="20" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E388" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="2"/>
       <c r="B389" s="20" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C389" s="20"/>
       <c r="D389" s="20"/>
@@ -7796,7 +7721,7 @@
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="2"/>
       <c r="B390" s="20" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C390" s="20"/>
       <c r="D390" s="20"/>
@@ -7805,7 +7730,7 @@
     <row r="391" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="2"/>
       <c r="B391" s="20" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C391" s="20" t="s">
         <v>74</v>
@@ -7816,33 +7741,33 @@
     <row r="392" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="2"/>
       <c r="B392" s="20" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C392" s="20" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D392" s="20" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E392" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A393" s="26"/>
+      <c r="A393" s="27"/>
       <c r="B393" s="20"/>
       <c r="C393" s="20"/>
       <c r="D393" s="20"/>
       <c r="E393" s="11"/>
     </row>
     <row r="394" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A394" s="27"/>
-      <c r="B394" s="28" t="s">
-        <v>499</v>
-      </c>
-      <c r="C394" s="29"/>
-      <c r="D394" s="29"/>
-      <c r="E394" s="30"/>
+      <c r="A394" s="28"/>
+      <c r="B394" s="29" t="s">
+        <v>500</v>
+      </c>
+      <c r="C394" s="30"/>
+      <c r="D394" s="30"/>
+      <c r="E394" s="31"/>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="2" t="s">
@@ -7856,7 +7781,7 @@
     <row r="396" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="2"/>
       <c r="B396" s="20" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C396" s="20"/>
       <c r="D396" s="20"/>
@@ -7865,7 +7790,7 @@
     <row r="397" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="2"/>
       <c r="B397" s="20" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C397" s="20"/>
       <c r="D397" s="20"/>
@@ -7874,10 +7799,10 @@
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="2"/>
       <c r="B398" s="20" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C398" s="20" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D398" s="20"/>
       <c r="E398" s="11"/>
@@ -7885,7 +7810,7 @@
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="2"/>
       <c r="B399" s="20" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C399" s="20"/>
       <c r="D399" s="20"/>
@@ -7894,7 +7819,7 @@
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="2"/>
       <c r="B400" s="20" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C400" s="20"/>
       <c r="D400" s="20"/>
@@ -7903,7 +7828,7 @@
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="2"/>
       <c r="B401" s="20" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C401" s="20"/>
       <c r="D401" s="20"/>
@@ -7912,7 +7837,7 @@
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2"/>
       <c r="B402" s="20" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C402" s="20"/>
       <c r="D402" s="20"/>
@@ -7921,7 +7846,7 @@
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="2"/>
       <c r="B403" s="20" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C403" s="20"/>
       <c r="D403" s="20"/>
@@ -7930,7 +7855,7 @@
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="2"/>
       <c r="B404" s="20" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C404" s="20"/>
       <c r="D404" s="20"/>
@@ -7939,7 +7864,7 @@
     <row r="405" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="2"/>
       <c r="B405" s="20" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C405" s="20" t="s">
         <v>143</v>
@@ -7950,22 +7875,22 @@
     <row r="406" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="2"/>
       <c r="B406" s="20" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C406" s="20" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D406" s="20" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E406" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="2"/>
       <c r="B407" s="20" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C407" s="20" t="s">
         <v>74</v>
@@ -7974,7 +7899,7 @@
         <v>75</v>
       </c>
       <c r="E407" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7989,7 +7914,7 @@
         <v>244</v>
       </c>
       <c r="B409" s="20" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C409" s="20"/>
       <c r="D409" s="20"/>
@@ -7998,7 +7923,7 @@
     <row r="410" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="2"/>
       <c r="B410" s="20" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C410" s="20"/>
       <c r="D410" s="20"/>
@@ -8007,7 +7932,7 @@
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="2"/>
       <c r="B411" s="20" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C411" s="20"/>
       <c r="D411" s="20"/>
@@ -8016,7 +7941,7 @@
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="2"/>
       <c r="B412" s="20" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C412" s="20"/>
       <c r="D412" s="20"/>
@@ -8025,7 +7950,7 @@
     <row r="413" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="2"/>
       <c r="B413" s="20" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C413" s="20"/>
       <c r="D413" s="20"/>
@@ -8034,22 +7959,22 @@
     <row r="414" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="2"/>
       <c r="B414" s="20" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C414" s="20" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D414" s="20" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E414" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="2"/>
       <c r="B415" s="20" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C415" s="20"/>
       <c r="D415" s="20"/>
@@ -8058,7 +7983,7 @@
     <row r="416" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="2"/>
       <c r="B416" s="20" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C416" s="20"/>
       <c r="D416" s="20"/>
@@ -8067,7 +7992,7 @@
     <row r="417" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="2"/>
       <c r="B417" s="20" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C417" s="20"/>
       <c r="D417" s="20"/>
@@ -8076,22 +8001,22 @@
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="2"/>
       <c r="B418" s="20" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C418" s="20" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D418" s="20" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E418" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="2"/>
       <c r="B419" s="20" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C419" s="20"/>
       <c r="D419" s="20"/>
@@ -8107,7 +8032,7 @@
     <row r="421" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="6"/>
       <c r="B421" s="21" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C421" s="22"/>
       <c r="D421" s="22"/>
@@ -8125,7 +8050,7 @@
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2"/>
       <c r="B423" s="20" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C423" s="20"/>
       <c r="D423" s="20"/>
@@ -8134,22 +8059,22 @@
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2"/>
       <c r="B424" s="20" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C424" s="20" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D424" s="20" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E424" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2"/>
       <c r="B425" s="20" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C425" s="20"/>
       <c r="D425" s="20"/>
@@ -8158,7 +8083,7 @@
     <row r="426" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2"/>
       <c r="B426" s="20" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C426" s="20"/>
       <c r="D426" s="20"/>
@@ -8167,7 +8092,7 @@
     <row r="427" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2"/>
       <c r="B427" s="20" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C427" s="20"/>
       <c r="D427" s="20"/>
@@ -8176,7 +8101,7 @@
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2"/>
       <c r="B428" s="20" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C428" s="20"/>
       <c r="D428" s="20"/>
@@ -8185,7 +8110,7 @@
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="2"/>
       <c r="B429" s="20" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C429" s="20"/>
       <c r="D429" s="20"/>
@@ -8194,7 +8119,7 @@
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="2"/>
       <c r="B430" s="20" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C430" s="20"/>
       <c r="D430" s="20"/>
@@ -8203,7 +8128,7 @@
     <row r="431" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="2"/>
       <c r="B431" s="20" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C431" s="20" t="s">
         <v>143</v>
@@ -8216,7 +8141,7 @@
     <row r="432" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2"/>
       <c r="B432" s="20" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C432" s="20" t="s">
         <v>74</v>
@@ -8227,16 +8152,16 @@
     <row r="433" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="2"/>
       <c r="B433" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C433" s="20" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D433" s="20" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E433" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8251,7 +8176,7 @@
         <v>244</v>
       </c>
       <c r="B435" s="20" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C435" s="20"/>
       <c r="D435" s="20"/>
@@ -8260,7 +8185,7 @@
     <row r="436" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2"/>
       <c r="B436" s="20" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C436" s="20"/>
       <c r="D436" s="20"/>
@@ -8269,10 +8194,10 @@
     <row r="437" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2"/>
       <c r="B437" s="20" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C437" s="20" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D437" s="20"/>
       <c r="E437" s="11"/>
@@ -8280,7 +8205,7 @@
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2"/>
       <c r="B438" s="20" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C438" s="20"/>
       <c r="D438" s="20"/>
@@ -8289,7 +8214,7 @@
     <row r="439" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="2"/>
       <c r="B439" s="20" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C439" s="20"/>
       <c r="D439" s="20"/>
@@ -8298,7 +8223,7 @@
     <row r="440" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="2"/>
       <c r="B440" s="20" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C440" s="20"/>
       <c r="D440" s="20"/>
@@ -8307,10 +8232,10 @@
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="2"/>
       <c r="B441" s="20" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C441" s="20" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D441" s="20"/>
       <c r="E441" s="11"/>
@@ -8318,7 +8243,7 @@
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2"/>
       <c r="B442" s="20" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C442" s="20"/>
       <c r="D442" s="20"/>
@@ -8327,7 +8252,7 @@
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2"/>
       <c r="B443" s="20" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C443" s="20"/>
       <c r="D443" s="20"/>
@@ -8336,7 +8261,7 @@
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2"/>
       <c r="B444" s="20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C444" s="20"/>
       <c r="D444" s="20"/>
@@ -8345,7 +8270,7 @@
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2"/>
       <c r="B445" s="20" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C445" s="20"/>
       <c r="D445" s="20"/>
@@ -8354,7 +8279,7 @@
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2"/>
       <c r="B446" s="20" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C446" s="20"/>
       <c r="D446" s="20"/>
@@ -8363,7 +8288,7 @@
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="2"/>
       <c r="B447" s="20" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C447" s="20"/>
       <c r="D447" s="20"/>
@@ -8372,7 +8297,7 @@
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="2"/>
       <c r="B448" s="20" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C448" s="20"/>
       <c r="D448" s="20"/>
@@ -8381,22 +8306,22 @@
     <row r="449" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="2"/>
       <c r="B449" s="20" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C449" s="20" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D449" s="20" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E449" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="2"/>
       <c r="B450" s="20" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C450" s="20"/>
       <c r="D450" s="20"/>
@@ -8405,7 +8330,7 @@
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="2"/>
       <c r="B451" s="20" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C451" s="20"/>
       <c r="D451" s="20"/>
@@ -8414,7 +8339,7 @@
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="2"/>
       <c r="B452" s="20" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C452" s="20"/>
       <c r="D452" s="20"/>
@@ -8423,7 +8348,7 @@
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="2"/>
       <c r="B453" s="20" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C453" s="20"/>
       <c r="D453" s="20"/>
@@ -8432,7 +8357,7 @@
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2"/>
       <c r="B454" s="20" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C454" s="20"/>
       <c r="D454" s="20"/>
@@ -8441,7 +8366,7 @@
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2"/>
       <c r="B455" s="20" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C455" s="20"/>
       <c r="D455" s="20"/>
@@ -8450,7 +8375,7 @@
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2"/>
       <c r="B456" s="20" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C456" s="20"/>
       <c r="D456" s="20"/>
@@ -8459,18 +8384,23 @@
     <row r="457" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2"/>
       <c r="B457" s="20" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C457" s="20"/>
-      <c r="D457" s="31" t="s">
-        <v>569</v>
-      </c>
-      <c r="E457" s="32"/>
+      <c r="D457" s="32" t="s">
+        <v>570</v>
+      </c>
+      <c r="E457" s="33" t="s">
+        <v>571</v>
+      </c>
+      <c r="F457" s="34" t="s">
+        <v>572</v>
+      </c>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2"/>
       <c r="B458" s="20" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C458" s="20"/>
       <c r="D458" s="20"/>
@@ -8479,7 +8409,7 @@
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="2"/>
       <c r="B459" s="20" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C459" s="20"/>
       <c r="D459" s="20"/>
@@ -8488,7 +8418,7 @@
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="2"/>
       <c r="B460" s="20" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C460" s="20"/>
       <c r="D460" s="20"/>
@@ -8497,7 +8427,7 @@
     <row r="461" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="2"/>
       <c r="B461" s="20" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C461" s="20"/>
       <c r="D461" s="20"/>
@@ -8506,13 +8436,13 @@
     <row r="462" customFormat="false" ht="67.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="2"/>
       <c r="B462" s="20" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C462" s="20" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D462" s="20" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E462" s="11" t="s">
         <v>181</v>
@@ -8522,7 +8452,7 @@
     <row r="463" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2"/>
       <c r="B463" s="20" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C463" s="20"/>
       <c r="D463" s="20"/>
@@ -8531,7 +8461,7 @@
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2"/>
       <c r="B464" s="20" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C464" s="20"/>
       <c r="D464" s="20"/>
@@ -8540,7 +8470,7 @@
     <row r="465" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2"/>
       <c r="B465" s="20" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C465" s="20" t="s">
         <v>231</v>
@@ -8553,22 +8483,22 @@
     <row r="466" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2"/>
       <c r="B466" s="20" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C466" s="20" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D466" s="20" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E466" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2"/>
       <c r="B467" s="20" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C467" s="20"/>
       <c r="D467" s="20"/>
@@ -8577,7 +8507,7 @@
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2"/>
       <c r="B468" s="20" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C468" s="20"/>
       <c r="D468" s="20"/>
@@ -8586,35 +8516,37 @@
     <row r="469" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="2"/>
       <c r="B469" s="20" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C469" s="20" t="s">
-        <v>585</v>
-      </c>
-      <c r="D469" s="31" t="s">
-        <v>569</v>
-      </c>
-      <c r="E469" s="32"/>
+        <v>588</v>
+      </c>
+      <c r="D469" s="32" t="s">
+        <v>589</v>
+      </c>
+      <c r="E469" s="33" t="s">
+        <v>571</v>
+      </c>
     </row>
     <row r="470" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="2"/>
       <c r="B470" s="20" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C470" s="20" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="D470" s="20" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="E470" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="2"/>
       <c r="B471" s="20" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C471" s="20"/>
       <c r="D471" s="20"/>
@@ -8623,7 +8555,7 @@
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="2"/>
       <c r="B472" s="20" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C472" s="20"/>
       <c r="D472" s="20"/>
@@ -8632,18 +8564,22 @@
     <row r="473" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2"/>
       <c r="B473" s="20" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C473" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="D473" s="20"/>
-      <c r="E473" s="11"/>
+        <v>560</v>
+      </c>
+      <c r="D473" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="E473" s="11" t="s">
+        <v>512</v>
+      </c>
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="2"/>
       <c r="B474" s="20" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C474" s="20"/>
       <c r="D474" s="20"/>
@@ -8658,10 +8594,10 @@
     </row>
     <row r="476" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B476" s="20" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C476" s="20"/>
       <c r="D476" s="20"/>
@@ -8670,18 +8606,22 @@
     <row r="477" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2"/>
       <c r="B477" s="20" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="C477" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="D477" s="20"/>
-      <c r="E477" s="11"/>
+        <v>560</v>
+      </c>
+      <c r="D477" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="E477" s="11" t="s">
+        <v>512</v>
+      </c>
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2"/>
       <c r="B478" s="20" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C478" s="20"/>
       <c r="D478" s="20"/>
@@ -8697,7 +8637,7 @@
     <row r="480" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="6"/>
       <c r="B480" s="21" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C480" s="22"/>
       <c r="D480" s="22"/>
@@ -8714,7 +8654,7 @@
     <row r="482" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2"/>
       <c r="B482" s="20" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C482" s="20"/>
       <c r="D482" s="20"/>
@@ -8723,7 +8663,7 @@
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="2"/>
       <c r="B483" s="20" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="C483" s="20"/>
       <c r="D483" s="20"/>
@@ -8732,7 +8672,7 @@
     <row r="484" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2"/>
       <c r="B484" s="20" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="C484" s="20"/>
       <c r="D484" s="20"/>
@@ -8741,7 +8681,7 @@
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2"/>
       <c r="B485" s="20" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C485" s="20"/>
       <c r="D485" s="20"/>
@@ -8750,7 +8690,7 @@
     <row r="486" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2"/>
       <c r="B486" s="20" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="C486" s="20" t="s">
         <v>74</v>
@@ -8761,16 +8701,16 @@
     <row r="487" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="2"/>
       <c r="B487" s="20" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C487" s="20" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D487" s="20" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="E487" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8783,7 +8723,7 @@
     <row r="489" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="6"/>
       <c r="B489" s="21" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="C489" s="22"/>
       <c r="D489" s="22"/>
@@ -8800,7 +8740,7 @@
     <row r="491" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="2"/>
       <c r="B491" s="20" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="C491" s="20"/>
       <c r="D491" s="20"/>
@@ -8809,7 +8749,7 @@
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2"/>
       <c r="B492" s="20" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="C492" s="20"/>
       <c r="D492" s="20"/>
@@ -8818,7 +8758,7 @@
     <row r="493" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2"/>
       <c r="B493" s="20" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="C493" s="20" t="s">
         <v>318</v>
@@ -8829,10 +8769,10 @@
     <row r="494" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2"/>
       <c r="B494" s="20" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="C494" s="20" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D494" s="20"/>
       <c r="E494" s="11"/>
@@ -8840,10 +8780,10 @@
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2"/>
       <c r="B495" s="20" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="C495" s="20" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D495" s="20"/>
       <c r="E495" s="11"/>
@@ -8851,37 +8791,37 @@
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2"/>
       <c r="B496" s="20" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C496" s="20" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D496" s="20" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="E496" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="497" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="497" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2"/>
       <c r="B497" s="20" t="s">
-        <v>614</v>
-      </c>
-      <c r="C497" s="20" t="s">
-        <v>615</v>
-      </c>
-      <c r="D497" s="20" t="s">
-        <v>616</v>
+        <v>619</v>
+      </c>
+      <c r="C497" s="32" t="s">
+        <v>620</v>
+      </c>
+      <c r="D497" s="32" t="s">
+        <v>621</v>
       </c>
       <c r="E497" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="2"/>
       <c r="B498" s="20" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="C498" s="20"/>
       <c r="D498" s="20"/>
@@ -8897,7 +8837,7 @@
     <row r="500" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="6"/>
       <c r="B500" s="21" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="C500" s="22"/>
       <c r="D500" s="22"/>
@@ -8915,7 +8855,7 @@
     <row r="502" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="2"/>
       <c r="B502" s="20" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="C502" s="20"/>
       <c r="D502" s="20"/>
@@ -8924,25 +8864,25 @@
     <row r="503" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="2"/>
       <c r="B503" s="20" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="C503" s="20" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D503" s="20" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="E503" s="11" t="s">
-        <v>622</v>
-      </c>
-      <c r="F503" s="33" t="s">
-        <v>623</v>
+        <v>627</v>
+      </c>
+      <c r="F503" s="34" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="2"/>
       <c r="B504" s="20" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="C504" s="20"/>
       <c r="D504" s="20"/>
@@ -8951,7 +8891,7 @@
     <row r="505" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="2"/>
       <c r="B505" s="20" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="C505" s="20"/>
       <c r="D505" s="20"/>
@@ -8960,7 +8900,7 @@
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="2"/>
       <c r="B506" s="20" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="C506" s="20"/>
       <c r="D506" s="20"/>
@@ -8969,10 +8909,10 @@
     <row r="507" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="2"/>
       <c r="B507" s="20" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="C507" s="20" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="D507" s="20"/>
       <c r="E507" s="11"/>
@@ -8980,13 +8920,13 @@
     <row r="508" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="2"/>
       <c r="B508" s="20" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="C508" s="20" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="D508" s="20" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="E508" s="11" t="s">
         <v>181</v>
@@ -8995,18 +8935,22 @@
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="2"/>
       <c r="B509" s="20" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C509" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="D509" s="20"/>
-      <c r="E509" s="11"/>
+        <v>560</v>
+      </c>
+      <c r="D509" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="E509" s="11" t="s">
+        <v>512</v>
+      </c>
     </row>
     <row r="510" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="2"/>
       <c r="B510" s="20" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="C510" s="20" t="s">
         <v>74</v>
@@ -9026,7 +8970,7 @@
         <v>244</v>
       </c>
       <c r="B512" s="20" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="C512" s="20"/>
       <c r="D512" s="20"/>
@@ -9035,18 +8979,22 @@
     <row r="513" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2"/>
       <c r="B513" s="20" t="s">
-        <v>635</v>
-      </c>
-      <c r="C513" s="31" t="s">
-        <v>636</v>
-      </c>
-      <c r="D513" s="20"/>
-      <c r="E513" s="11"/>
+        <v>640</v>
+      </c>
+      <c r="C513" s="32" t="s">
+        <v>641</v>
+      </c>
+      <c r="D513" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="E513" s="11" t="s">
+        <v>643</v>
+      </c>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="2"/>
       <c r="B514" s="20" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="C514" s="20"/>
       <c r="D514" s="20"/>
@@ -9062,7 +9010,7 @@
     <row r="516" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="6"/>
       <c r="B516" s="21" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="C516" s="22"/>
       <c r="D516" s="22"/>
@@ -9080,7 +9028,7 @@
     <row r="518" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="2"/>
       <c r="B518" s="20" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="C518" s="20"/>
       <c r="D518" s="20"/>
@@ -9089,53 +9037,62 @@
     <row r="519" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="2"/>
       <c r="B519" s="20" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="C519" s="20" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="D519" s="20" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="E519" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="2"/>
       <c r="B520" s="20" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="C520" s="20"/>
-      <c r="D520" s="20"/>
-      <c r="E520" s="11"/>
+      <c r="D520" s="20" t="s">
+        <v>651</v>
+      </c>
+      <c r="E520" s="11" t="s">
+        <v>512</v>
+      </c>
     </row>
     <row r="521" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="2"/>
       <c r="B521" s="20" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="C521" s="20"/>
       <c r="D521" s="20"/>
       <c r="E521" s="11"/>
     </row>
-    <row r="522" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="522" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="2"/>
       <c r="B522" s="20" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="C522" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="D522" s="18" t="s">
-        <v>646</v>
-      </c>
-      <c r="E522" s="34"/>
+      <c r="D522" s="35" t="s">
+        <v>284</v>
+      </c>
+      <c r="E522" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="F522" s="34" t="s">
+        <v>654</v>
+      </c>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="2"/>
       <c r="B523" s="20" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="C523" s="20"/>
       <c r="D523" s="20"/>
@@ -9144,7 +9101,7 @@
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="2"/>
       <c r="B524" s="20" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="C524" s="20"/>
       <c r="D524" s="20"/>
@@ -9153,7 +9110,7 @@
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2"/>
       <c r="B525" s="20" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="C525" s="20"/>
       <c r="D525" s="20"/>
@@ -9162,7 +9119,7 @@
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2"/>
       <c r="B526" s="20" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="C526" s="20"/>
       <c r="D526" s="20"/>
@@ -9171,7 +9128,7 @@
     <row r="527" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2"/>
       <c r="B527" s="20" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="C527" s="20"/>
       <c r="D527" s="20"/>
@@ -9180,7 +9137,7 @@
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="2"/>
       <c r="B528" s="20" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="C528" s="20"/>
       <c r="D528" s="20"/>
@@ -9189,7 +9146,7 @@
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="2"/>
       <c r="B529" s="20" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="C529" s="20"/>
       <c r="D529" s="20"/>
@@ -9198,21 +9155,25 @@
     <row r="530" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="2"/>
       <c r="B530" s="20" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="C530" s="20" t="s">
-        <v>655</v>
-      </c>
-      <c r="D530" s="20"/>
-      <c r="E530" s="11"/>
+        <v>663</v>
+      </c>
+      <c r="D530" s="20" t="s">
+        <v>664</v>
+      </c>
+      <c r="E530" s="11" t="s">
+        <v>512</v>
+      </c>
     </row>
     <row r="531" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="2"/>
       <c r="B531" s="20" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="C531" s="20" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="D531" s="20"/>
       <c r="E531" s="11"/>
@@ -9220,7 +9181,7 @@
     <row r="532" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="2"/>
       <c r="B532" s="20" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="C532" s="20" t="s">
         <v>74</v>
@@ -9240,7 +9201,7 @@
         <v>244</v>
       </c>
       <c r="B534" s="20" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="C534" s="20"/>
       <c r="D534" s="20"/>
@@ -9249,7 +9210,7 @@
     <row r="535" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="2"/>
       <c r="B535" s="20" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="C535" s="20"/>
       <c r="D535" s="20"/>
@@ -9258,7 +9219,7 @@
     <row r="536" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="2"/>
       <c r="B536" s="20" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="C536" s="20"/>
       <c r="D536" s="20"/>
@@ -9267,7 +9228,7 @@
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="2"/>
       <c r="B537" s="20" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="C537" s="20"/>
       <c r="D537" s="20"/>
@@ -9276,10 +9237,10 @@
     <row r="538" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="2"/>
       <c r="B538" s="20" t="s">
-        <v>663</v>
-      </c>
-      <c r="C538" s="31" t="s">
-        <v>657</v>
+        <v>672</v>
+      </c>
+      <c r="C538" s="32" t="s">
+        <v>666</v>
       </c>
       <c r="D538" s="20"/>
       <c r="E538" s="11"/>
@@ -9287,7 +9248,7 @@
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="2"/>
       <c r="B539" s="20" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="C539" s="20"/>
       <c r="D539" s="20"/>
@@ -9296,7 +9257,7 @@
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="2"/>
       <c r="B540" s="20" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="C540" s="20"/>
       <c r="D540" s="20"/>
@@ -9305,7 +9266,7 @@
     <row r="541" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="2"/>
       <c r="B541" s="20" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="C541" s="20"/>
       <c r="D541" s="20"/>
@@ -9314,7 +9275,7 @@
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="2"/>
       <c r="B542" s="20" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="C542" s="20"/>
       <c r="D542" s="20"/>
@@ -9323,10 +9284,10 @@
     <row r="543" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="2"/>
       <c r="B543" s="20" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="C543" s="20" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="D543" s="20"/>
       <c r="E543" s="11"/>
@@ -9334,7 +9295,7 @@
     <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="2"/>
       <c r="B544" s="20" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="C544" s="20"/>
       <c r="D544" s="20"/>
@@ -9343,7 +9304,7 @@
     <row r="545" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="2"/>
       <c r="B545" s="20" t="s">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="C545" s="20"/>
       <c r="D545" s="20"/>
@@ -9352,7 +9313,7 @@
     <row r="546" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="2"/>
       <c r="B546" s="20" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="C546" s="20"/>
       <c r="D546" s="20"/>
@@ -9361,7 +9322,7 @@
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="2"/>
       <c r="B547" s="20" t="s">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="C547" s="20"/>
       <c r="D547" s="20"/>
@@ -9370,7 +9331,7 @@
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="2"/>
       <c r="B548" s="20" t="s">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="C548" s="20"/>
       <c r="D548" s="20"/>
@@ -9379,7 +9340,7 @@
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="2"/>
       <c r="B549" s="20" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="C549" s="20"/>
       <c r="D549" s="20"/>
@@ -9388,28 +9349,28 @@
     <row r="550" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="2"/>
       <c r="B550" s="20" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="C550" s="20" t="s">
         <v>283</v>
       </c>
       <c r="D550" s="20" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="E550" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="551" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="2"/>
       <c r="B551" s="20" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="C551" s="20" t="s">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="D551" s="20" t="s">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="E551" s="11" t="s">
         <v>181</v>
@@ -9418,7 +9379,7 @@
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="2"/>
       <c r="B552" s="20" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="C552" s="20"/>
       <c r="D552" s="20"/>
@@ -9433,10 +9394,10 @@
     </row>
     <row r="554" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="2" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B554" s="20" t="s">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="C554" s="20"/>
       <c r="D554" s="20"/>
@@ -9445,7 +9406,7 @@
     <row r="555" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="2"/>
       <c r="B555" s="20" t="s">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="C555" s="20"/>
       <c r="D555" s="20"/>
@@ -9454,7 +9415,7 @@
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="2"/>
       <c r="B556" s="20" t="s">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="C556" s="20"/>
       <c r="D556" s="20"/>
@@ -9463,10 +9424,10 @@
     <row r="557" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="2"/>
       <c r="B557" s="20" t="s">
-        <v>684</v>
-      </c>
-      <c r="C557" s="31" t="s">
-        <v>657</v>
+        <v>693</v>
+      </c>
+      <c r="C557" s="32" t="s">
+        <v>666</v>
       </c>
       <c r="D557" s="20"/>
       <c r="E557" s="11"/>
@@ -9481,20 +9442,20 @@
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="2"/>
       <c r="B559" s="20" t="s">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="C559" s="20"/>
       <c r="D559" s="20"/>
       <c r="E559" s="11"/>
     </row>
     <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A560" s="35"/>
-      <c r="B560" s="36" t="s">
-        <v>686</v>
-      </c>
-      <c r="C560" s="36"/>
-      <c r="D560" s="36"/>
-      <c r="E560" s="37"/>
+      <c r="A560" s="36"/>
+      <c r="B560" s="37" t="s">
+        <v>695</v>
+      </c>
+      <c r="C560" s="37"/>
+      <c r="D560" s="37"/>
+      <c r="E560" s="38"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/assets/responsabilidades.xlsx
+++ b/assets/responsabilidades.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="696">
   <si>
     <t xml:space="preserve">Use Case</t>
   </si>
@@ -69,10 +69,10 @@
     <t xml:space="preserve">Validar credenciais</t>
   </si>
   <si>
-    <t xml:space="preserve">autenticar(id: int, palavra_passe: string): Funcionario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funcionários</t>
+    <t xml:space="preserve">autenticar(id: int, palavra_passe: string) : bool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autenticacao</t>
   </si>
   <si>
     <t xml:space="preserve">3. O sistema identifica o cargo do utilizador autenticado.</t>
@@ -81,7 +81,10 @@
     <t xml:space="preserve">Identificar cargo do utilizador</t>
   </si>
   <si>
-    <t xml:space="preserve">método autenticar retorna null pointer se a autenticação falhar. Se a autenticação não falhar, a classe Funcionário que é devolvida é usada para determinar o cargo do funcionário e lhe conceder as suas funcionalidades correspondentes</t>
+    <t xml:space="preserve">obterCargoUtilizador(id : int) : Cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O id é o id do utilizador</t>
   </si>
   <si>
     <t xml:space="preserve">4. O sistema concede ao utilizador acesso às funcionalidades correspondentes ao seu papel.</t>
@@ -131,6 +134,9 @@
     <t xml:space="preserve">validarNome(nome: string): bool</t>
   </si>
   <si>
+    <t xml:space="preserve">Funcionários</t>
+  </si>
+  <si>
     <t xml:space="preserve">decidir se vale a pena fazer estes métodos de validação específicos ou algo mais generalizado</t>
   </si>
   <si>
@@ -275,7 +281,10 @@
     <t xml:space="preserve">Criar funcionário</t>
   </si>
   <si>
-    <t xml:space="preserve">registarFuncionario(nome: string, numero_porta: string, rua: string, localidade: string, codigo_postal: string, telemovel: string, email: string, data_nascimento: string, niss: string, nif: string, nus: string, iban: string, salario_hora: float, salario_bruto: float, salario_liquido: float, palavra_passe: string): Funcionario</t>
+    <t xml:space="preserve">registarFuncionario(nome: string, numero_porta: string, rua: string, localidade: string, codigo_postal: string, telemovel: string, email: string, data_nascimento: string, niss: string, nif: string, nus: string, iban: string, salario_hora: float, salario_bruto: float, salario_liquido: float): Funcionario &amp;&amp; criarUtilizador(id_funcionario : int, palavra_passe : string, cargo : Cargo) : Utilizador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ao registar um funcionario também tens de registar o user</t>
   </si>
   <si>
     <t xml:space="preserve">21. O sistema confirma o registo apresentando os dados do funcionário criado.</t>
@@ -393,7 +402,7 @@
     <t xml:space="preserve">Atualizar funcionário</t>
   </si>
   <si>
-    <t xml:space="preserve">atualizarNomeFuncionario(id : int, nome : string) : void &amp;&amp; atualizarNumeroPortaFuncionario(id : int, numero_porta : string) : void &amp;&amp; atualizarRuaFuncionario(id : int, rua : string) : void &amp;&amp; atualizarLocalidadeFuncionario(id : int, localidade : string) : void &amp;&amp; atualizarCodigoPostalFuncionario(id : int, codigo_postal : string) : void &amp;&amp; atualizarTelemovelFuncionario(id : int, telemovel : string) : void &amp;&amp; atualizarEmailFuncionario(id : int, email : string) : void &amp;&amp; atualizarDataNascimentoFuncionario(id : int, data_nascimento : string) : void &amp;&amp; atualizarNISSFuncionario(id : int, niss : string) : void &amp;&amp; atualizarNIFFuncionario(id : int, nif : string) : void &amp;&amp; atualizarNUSFuncionario(id : int, nus : string) : void &amp;&amp; atualizarIBANFuncionario(id : int, iban : string) : void &amp;&amp; atualizarSalarioHoraFuncionario(id : int, salario_hora : float) : void &amp;&amp; atualizarSalarioBrutoFuncionario(id : int, salario_bruto : float) : void &amp;&amp; atualizarSalarioLiquidoFuncionario(id : int, salario_liquido : float) : void &amp;&amp; atualizarPalavraPasseFuncionario(id : int, palavra_passe : string) : void</t>
+    <t xml:space="preserve">atualizarNomeFuncionario(id : int, nome : string) : void &amp;&amp; atualizarNumeroPortaFuncionario(id : int, numero_porta : string) : void &amp;&amp; atualizarRuaFuncionario(id : int, rua : string) : void &amp;&amp; atualizarLocalidadeFuncionario(id : int, localidade : string) : void &amp;&amp; atualizarCodigoPostalFuncionario(id : int, codigo_postal : string) : void &amp;&amp; atualizarTelemovelFuncionario(id : int, telemovel : string) : void &amp;&amp; atualizarEmailFuncionario(id : int, email : string) : void &amp;&amp; atualizarDataNascimentoFuncionario(id : int, data_nascimento : string) : void &amp;&amp; atualizarNISSFuncionario(id : int, niss : string) : void &amp;&amp; atualizarNIFFuncionario(id : int, nif : string) : void &amp;&amp; atualizarNUSFuncionario(id : int, nus : string) : void &amp;&amp; atualizarIBANFuncionario(id : int, iban : string) : void &amp;&amp; atualizarSalarioHoraFuncionario(id : int, salario_hora : float) : void &amp;&amp; atualizarSalarioBrutoFuncionario(id : int, salario_bruto : float) : void &amp;&amp; atualizarSalarioLiquidoFuncionario(id : int, salario_liquido : float) : void &amp;&amp; atualizarPalavraPasseUtilizador(id : int, palavra_passe : string) : void</t>
   </si>
   <si>
     <r>
@@ -2370,15 +2379,15 @@
     <t xml:space="preserve">4.2.1.1 O funcionário regista a notificação de término</t>
   </si>
   <si>
+    <t xml:space="preserve">Registar a notificação</t>
+  </si>
+  <si>
     <t xml:space="preserve">criarNotificacao(descricao : string, id_remetente : int, id_destinatario : int) : Notificacao</t>
   </si>
   <si>
     <t xml:space="preserve">Notificacoes</t>
   </si>
   <si>
-    <t xml:space="preserve">Notificação enviada da secretaria para o cliente</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.2.1.2 O funcionário confirma a notificação de término</t>
   </si>
   <si>
@@ -2421,16 +2430,7 @@
     <t xml:space="preserve">(8) [O funcionário regista o pagamento] (Passo 4.2.3)</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2.3.1 O sistema valida que o cliente foi previamente notificado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validar notificação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obterNotificacoesPorClienteEIntervalo(id_cliente : int, data_inicio : DateTime, data_fim : DateTime) : List(Notificacao)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2.3.2 O sistema valida que não existem outras OS pendentes do mesmo cliente com data anterior</t>
+    <t xml:space="preserve">4.2.3.1 O sistema valida que não existem outras OS pendentes do mesmo cliente com data anterior</t>
   </si>
   <si>
     <t xml:space="preserve">Validar pendências</t>
@@ -2439,19 +2439,19 @@
     <t xml:space="preserve">clienteNaoTemPagamentosPendentes(id: int): bool</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2.3.3 O funcionário seleciona o método de pagamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2.3.4 O funcionário confirma o registo do pagamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2.3.5 O sistema regista o pagamento e altera o estado da OS para 'Paga'</t>
+    <t xml:space="preserve">4.2.3.2 O funcionário seleciona o método de pagamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2.3.3 O funcionário confirma o registo do pagamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2.3.4 O sistema regista o pagamento e altera o estado da OS para 'Paga'</t>
   </si>
   <si>
     <t xml:space="preserve">alterarEstadoOS(id : int, estado : EstadoOS) : void</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2.3.6 Retorna ao passo 10</t>
+    <t xml:space="preserve">4.2.3.5 Retorna ao passo 10</t>
   </si>
   <si>
     <t xml:space="preserve">Fluxos de Exceção:</t>
@@ -2643,46 +2643,10 @@
     <t xml:space="preserve">7.1 O sistema altera o estado da OS para 'Pendente aprovação do orçamento' e gera um alerta com o identificador da OS e o seu estado para a secretária</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Gerar alerta &amp;&amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">Atualizar estado OS</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">criarNotificacao(descricao : string, id_remetente : int, id_destinatario : int) : Notificacao &amp;&amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">alterarEstadoOS(id : int, estado : EstadoOS) : void</t>
-    </r>
+    <t xml:space="preserve">Gerar alerta &amp;&amp; Atualizar estado OS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">criarNotificacao(descricao : string, id_remetente : int, id_destinatario : int) : Notificacao &amp;&amp; alterarEstadoOS(id : int, estado : EstadoOS) : void</t>
   </si>
   <si>
     <t xml:space="preserve">Ordens de Serviço &amp;&amp; Notificacoes</t>
@@ -2935,6 +2899,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -2945,12 +2915,6 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -3157,8 +3121,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -3174,6 +3142,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3197,15 +3173,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3213,7 +3185,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3237,15 +3209,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3444,7 +3408,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J560"/>
+  <dimension ref="A1:J1048576"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.57"/>
@@ -3498,7 +3462,7 @@
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2"/>
       <c r="B5" s="10" t="s">
         <v>7</v>
@@ -3513,7 +3477,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
       <c r="B6" s="10" t="s">
         <v>11</v>
@@ -3524,20 +3488,25 @@
       <c r="D6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="12"/>
+      <c r="E6" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -3549,7 +3518,7 @@
     <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
       <c r="B9" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="9"/>
@@ -3567,7 +3536,7 @@
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="12"/>
@@ -3576,7 +3545,7 @@
     <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="12"/>
@@ -3585,7 +3554,7 @@
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
       <c r="B13" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="12"/>
@@ -3594,266 +3563,269 @@
     <row r="14" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="12" t="s">
         <v>24</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
       <c r="B16" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
       <c r="B17" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="17"/>
+        <v>24</v>
+      </c>
+      <c r="F19" s="18"/>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
       <c r="B28" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
       <c r="B29" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" s="19" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
       <c r="B31" s="10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="12"/>
@@ -3862,16 +3834,16 @@
     <row r="32" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
       <c r="B32" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3884,7 +3856,7 @@
     <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
       <c r="B34" s="7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="9"/>
@@ -3902,7 +3874,7 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
       <c r="B36" s="10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="12"/>
@@ -3911,22 +3883,22 @@
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
       <c r="B37" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
       <c r="B38" s="10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="12"/>
@@ -3935,7 +3907,7 @@
     <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
       <c r="B39" s="10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="12"/>
@@ -3944,7 +3916,7 @@
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
       <c r="B40" s="10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="12"/>
@@ -3953,10 +3925,10 @@
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
       <c r="B41" s="10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="12"/>
@@ -3964,10 +3936,10 @@
     <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
       <c r="B42" s="10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="12"/>
@@ -3975,10 +3947,10 @@
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="12"/>
@@ -3986,10 +3958,10 @@
     <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
       <c r="B44" s="10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="12"/>
@@ -3997,10 +3969,10 @@
     <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
       <c r="B45" s="10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="12"/>
@@ -4008,10 +3980,10 @@
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
       <c r="B46" s="10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="12"/>
@@ -4019,10 +3991,10 @@
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
       <c r="B47" s="10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="12"/>
@@ -4030,10 +4002,10 @@
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
       <c r="B48" s="10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="12"/>
@@ -4041,10 +4013,10 @@
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
       <c r="B49" s="10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="12"/>
@@ -4052,10 +4024,10 @@
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
       <c r="B50" s="10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="12"/>
@@ -4063,10 +4035,10 @@
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
       <c r="B51" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="12"/>
@@ -4074,10 +4046,10 @@
     <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
       <c r="B52" s="10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="12"/>
@@ -4085,10 +4057,10 @@
     <row r="53" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
       <c r="B53" s="10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="12"/>
@@ -4096,10 +4068,10 @@
     <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
       <c r="B54" s="10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="12"/>
@@ -4107,10 +4079,10 @@
     <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
       <c r="B55" s="10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D55" s="12"/>
       <c r="E55" s="12"/>
@@ -4118,10 +4090,10 @@
     <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
       <c r="B56" s="10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="12"/>
@@ -4129,31 +4101,31 @@
     <row r="57" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
       <c r="B57" s="10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="244.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
       <c r="B58" s="10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4166,7 +4138,7 @@
     <row r="60" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6"/>
       <c r="B60" s="7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="9"/>
@@ -4184,7 +4156,7 @@
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
       <c r="B62" s="10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="12"/>
@@ -4193,10 +4165,10 @@
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
       <c r="B63" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D63" s="12"/>
       <c r="E63" s="12"/>
@@ -4204,7 +4176,7 @@
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
       <c r="B64" s="10" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C64" s="11"/>
       <c r="D64" s="12"/>
@@ -4213,7 +4185,7 @@
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
       <c r="B65" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="12"/>
@@ -4222,10 +4194,10 @@
     <row r="66" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
       <c r="B66" s="10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="12"/>
@@ -4233,22 +4205,22 @@
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
       <c r="B67" s="10" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
       <c r="B68" s="10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="12"/>
@@ -4264,7 +4236,7 @@
     <row r="70" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6"/>
       <c r="B70" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="9"/>
@@ -4282,7 +4254,7 @@
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
       <c r="B72" s="10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="12"/>
@@ -4291,10 +4263,10 @@
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
       <c r="B73" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D73" s="12"/>
       <c r="E73" s="12"/>
@@ -4302,7 +4274,7 @@
     <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
       <c r="B74" s="10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="12"/>
@@ -4311,7 +4283,7 @@
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
       <c r="B75" s="10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C75" s="11"/>
       <c r="D75" s="12"/>
@@ -4320,22 +4292,22 @@
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
       <c r="B76" s="10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
       <c r="B77" s="10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C77" s="11"/>
       <c r="D77" s="12"/>
@@ -4344,41 +4316,41 @@
     <row r="78" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
       <c r="B78" s="10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
       <c r="B79" s="10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F79" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="G79" s="15"/>
+        <v>24</v>
+      </c>
+      <c r="F79" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="G79" s="16"/>
     </row>
     <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
       <c r="B80" s="10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="12"/>
@@ -4394,7 +4366,7 @@
     <row r="82" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6"/>
       <c r="B82" s="7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C82" s="8"/>
       <c r="D82" s="9"/>
@@ -4412,7 +4384,7 @@
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
       <c r="B84" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="12"/>
@@ -4421,7 +4393,7 @@
     <row r="85" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
       <c r="B85" s="10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C85" s="11"/>
       <c r="D85" s="12"/>
@@ -4430,7 +4402,7 @@
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
       <c r="B86" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="12"/>
@@ -4439,16 +4411,16 @@
     <row r="87" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
       <c r="B87" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4461,7 +4433,7 @@
     <row r="89" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6"/>
       <c r="B89" s="7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C89" s="8"/>
       <c r="D89" s="9"/>
@@ -4479,7 +4451,7 @@
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
       <c r="B91" s="10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C91" s="11"/>
       <c r="D91" s="12"/>
@@ -4488,7 +4460,7 @@
     <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
       <c r="B92" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C92" s="11"/>
       <c r="D92" s="12"/>
@@ -4497,7 +4469,7 @@
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
       <c r="B93" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="12"/>
@@ -4506,76 +4478,76 @@
     <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
       <c r="B94" s="10" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
       <c r="B95" s="10" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D95" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E95" s="12" t="s">
         <v>144</v>
-      </c>
-      <c r="E95" s="12" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
       <c r="B96" s="10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
       <c r="B97" s="10" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
       <c r="B98" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4588,7 +4560,7 @@
     <row r="100" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="6"/>
       <c r="B100" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C100" s="8"/>
       <c r="D100" s="9"/>
@@ -4606,7 +4578,7 @@
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
       <c r="B102" s="10" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="12"/>
@@ -4615,22 +4587,22 @@
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
       <c r="B103" s="10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
       <c r="B104" s="10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="12"/>
@@ -4639,7 +4611,7 @@
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2"/>
       <c r="B105" s="10" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C105" s="11"/>
       <c r="D105" s="12"/>
@@ -4648,7 +4620,7 @@
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2"/>
       <c r="B106" s="10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="12"/>
@@ -4657,10 +4629,10 @@
     <row r="107" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2"/>
       <c r="B107" s="10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D107" s="12"/>
       <c r="E107" s="12"/>
@@ -4668,10 +4640,10 @@
     <row r="108" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2"/>
       <c r="B108" s="10" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D108" s="12"/>
       <c r="E108" s="12"/>
@@ -4679,10 +4651,10 @@
     <row r="109" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2"/>
       <c r="B109" s="10" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D109" s="12"/>
       <c r="E109" s="12"/>
@@ -4690,31 +4662,31 @@
     <row r="110" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2"/>
       <c r="B110" s="10" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2"/>
       <c r="B111" s="10" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4727,7 +4699,7 @@
     <row r="113" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6"/>
       <c r="B113" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C113" s="8"/>
       <c r="D113" s="9"/>
@@ -4745,7 +4717,7 @@
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2"/>
       <c r="B115" s="10" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C115" s="11"/>
       <c r="D115" s="12"/>
@@ -4754,22 +4726,22 @@
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2"/>
       <c r="B116" s="10" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2"/>
       <c r="B117" s="10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C117" s="11"/>
       <c r="D117" s="12"/>
@@ -4778,7 +4750,7 @@
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2"/>
       <c r="B118" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="12"/>
@@ -4787,22 +4759,22 @@
     <row r="119" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2"/>
       <c r="B119" s="10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E119" s="12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2"/>
       <c r="B120" s="10" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C120" s="11"/>
       <c r="D120" s="12"/>
@@ -4811,16 +4783,16 @@
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2"/>
       <c r="B121" s="10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E121" s="12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4833,7 +4805,7 @@
     <row r="123" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="6"/>
       <c r="B123" s="7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C123" s="8"/>
       <c r="D123" s="9"/>
@@ -4851,7 +4823,7 @@
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2"/>
       <c r="B125" s="10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C125" s="11"/>
       <c r="D125" s="12"/>
@@ -4860,7 +4832,7 @@
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2"/>
       <c r="B126" s="10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C126" s="11"/>
       <c r="D126" s="12"/>
@@ -4869,22 +4841,22 @@
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2"/>
       <c r="B127" s="10" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E127" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2"/>
       <c r="B128" s="10" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C128" s="11"/>
       <c r="D128" s="12"/>
@@ -4893,7 +4865,7 @@
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2"/>
       <c r="B129" s="10" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C129" s="11"/>
       <c r="D129" s="12"/>
@@ -4902,67 +4874,67 @@
     <row r="130" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2"/>
       <c r="B130" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C130" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="E130" s="12" t="s">
         <v>184</v>
-      </c>
-      <c r="C130" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="D130" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="E130" s="12" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2"/>
       <c r="B131" s="10" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2"/>
       <c r="B132" s="10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2"/>
       <c r="B133" s="10" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2"/>
       <c r="B134" s="10" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C134" s="11"/>
       <c r="D134" s="12"/>
@@ -4971,16 +4943,16 @@
     <row r="135" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2"/>
       <c r="B135" s="10" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D135" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E135" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4993,7 +4965,7 @@
     <row r="137" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="6"/>
       <c r="B137" s="7" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C137" s="8"/>
       <c r="D137" s="9"/>
@@ -5011,7 +4983,7 @@
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2"/>
       <c r="B139" s="10" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C139" s="11"/>
       <c r="D139" s="12"/>
@@ -5020,22 +4992,22 @@
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2"/>
       <c r="B140" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D140" s="12" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E140" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2"/>
       <c r="B141" s="10" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C141" s="11"/>
       <c r="D141" s="12"/>
@@ -5044,7 +5016,7 @@
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2"/>
       <c r="B142" s="10" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C142" s="11"/>
       <c r="D142" s="12"/>
@@ -5053,7 +5025,7 @@
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2"/>
       <c r="B143" s="10" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C143" s="11"/>
       <c r="D143" s="12"/>
@@ -5062,10 +5034,10 @@
     <row r="144" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2"/>
       <c r="B144" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D144" s="12"/>
       <c r="E144" s="12"/>
@@ -5073,10 +5045,10 @@
     <row r="145" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2"/>
       <c r="B145" s="10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D145" s="12"/>
       <c r="E145" s="12"/>
@@ -5084,10 +5056,10 @@
     <row r="146" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2"/>
       <c r="B146" s="10" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D146" s="12"/>
       <c r="E146" s="12"/>
@@ -5095,31 +5067,31 @@
     <row r="147" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2"/>
       <c r="B147" s="10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E147" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2"/>
       <c r="B148" s="10" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5132,7 +5104,7 @@
     <row r="150" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="6"/>
       <c r="B150" s="7" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C150" s="8"/>
       <c r="D150" s="9"/>
@@ -5150,22 +5122,22 @@
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2"/>
       <c r="B152" s="10" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D152" s="12" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2"/>
       <c r="B153" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C153" s="11"/>
       <c r="D153" s="12"/>
@@ -5174,7 +5146,7 @@
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2"/>
       <c r="B154" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C154" s="11"/>
       <c r="D154" s="12"/>
@@ -5183,7 +5155,7 @@
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2"/>
       <c r="B155" s="10" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C155" s="11"/>
       <c r="D155" s="12"/>
@@ -5192,31 +5164,31 @@
     <row r="156" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2"/>
       <c r="B156" s="10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D156" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2"/>
       <c r="B157" s="10" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D157" s="12" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5231,7 +5203,7 @@
     <row r="159" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="6"/>
       <c r="B159" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C159" s="8"/>
       <c r="D159" s="9"/>
@@ -5249,7 +5221,7 @@
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2"/>
       <c r="B161" s="10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C161" s="11"/>
       <c r="D161" s="12"/>
@@ -5258,31 +5230,31 @@
     <row r="162" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2"/>
       <c r="B162" s="10" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C162" s="11"/>
       <c r="D162" s="12"/>
       <c r="E162" s="12"/>
     </row>
-    <row r="163" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2"/>
       <c r="B163" s="10" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D163" s="12" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E163" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2"/>
       <c r="B164" s="10" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C164" s="11"/>
       <c r="D164" s="12"/>
@@ -5291,7 +5263,7 @@
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2"/>
       <c r="B165" s="10" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C165" s="11"/>
       <c r="D165" s="12"/>
@@ -5300,40 +5272,40 @@
     <row r="166" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2"/>
       <c r="B166" s="10" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E166" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2"/>
       <c r="B167" s="10" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D167" s="12" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E167" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2"/>
       <c r="B168" s="10" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D168" s="12"/>
       <c r="E168" s="12"/>
@@ -5341,42 +5313,42 @@
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2"/>
       <c r="B169" s="10" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D169" s="12"/>
       <c r="E169" s="12"/>
     </row>
-    <row r="170" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2"/>
       <c r="B170" s="10" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E170" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2"/>
       <c r="B171" s="10" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D171" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E171" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5388,10 +5360,10 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C173" s="11"/>
       <c r="D173" s="12"/>
@@ -5400,7 +5372,7 @@
     <row r="174" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2"/>
       <c r="B174" s="10" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C174" s="11"/>
       <c r="D174" s="12"/>
@@ -5409,7 +5381,7 @@
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2"/>
       <c r="B175" s="10" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C175" s="11"/>
       <c r="D175" s="12"/>
@@ -5418,37 +5390,37 @@
     <row r="176" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2"/>
       <c r="B176" s="10" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D176" s="12" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E176" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2"/>
       <c r="B177" s="10" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D177" s="12" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E177" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2"/>
       <c r="B178" s="10" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C178" s="11"/>
       <c r="D178" s="12"/>
@@ -5464,7 +5436,7 @@
     <row r="180" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="6"/>
       <c r="B180" s="7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C180" s="8"/>
       <c r="D180" s="9"/>
@@ -5475,14 +5447,14 @@
         <v>5</v>
       </c>
       <c r="B181" s="10"/>
-      <c r="C181" s="19"/>
+      <c r="C181" s="22"/>
       <c r="D181" s="12"/>
       <c r="E181" s="12"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2"/>
       <c r="B182" s="10" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C182" s="11"/>
       <c r="D182" s="12"/>
@@ -5491,22 +5463,22 @@
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2"/>
       <c r="B183" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D183" s="12" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E183" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2"/>
       <c r="B184" s="10" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C184" s="11"/>
       <c r="D184" s="12"/>
@@ -5515,7 +5487,7 @@
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2"/>
       <c r="B185" s="10" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C185" s="11"/>
       <c r="D185" s="12"/>
@@ -5524,7 +5496,7 @@
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2"/>
       <c r="B186" s="10" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C186" s="11"/>
       <c r="D186" s="12"/>
@@ -5533,10 +5505,10 @@
     <row r="187" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2"/>
       <c r="B187" s="10" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D187" s="12"/>
       <c r="E187" s="12"/>
@@ -5544,10 +5516,10 @@
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="2"/>
       <c r="B188" s="10" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D188" s="12"/>
       <c r="E188" s="12"/>
@@ -5555,207 +5527,207 @@
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2"/>
       <c r="B189" s="10" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D189" s="12"/>
       <c r="E189" s="12"/>
     </row>
-    <row r="190" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2"/>
       <c r="B190" s="10" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D190" s="12" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E190" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2"/>
-      <c r="B191" s="20"/>
-      <c r="C191" s="20"/>
+      <c r="B191" s="23"/>
+      <c r="C191" s="23"/>
       <c r="D191" s="12"/>
       <c r="E191" s="12"/>
     </row>
     <row r="192" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="6"/>
-      <c r="B192" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="C192" s="22"/>
-      <c r="D192" s="22"/>
+      <c r="B192" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="C192" s="25"/>
+      <c r="D192" s="25"/>
       <c r="E192" s="8"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B193" s="20"/>
-      <c r="C193" s="20"/>
-      <c r="D193" s="20"/>
+      <c r="B193" s="23"/>
+      <c r="C193" s="23"/>
+      <c r="D193" s="23"/>
       <c r="E193" s="11"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2"/>
-      <c r="B194" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="C194" s="20"/>
-      <c r="D194" s="20"/>
+      <c r="B194" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="C194" s="23"/>
+      <c r="D194" s="23"/>
       <c r="E194" s="11"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2"/>
-      <c r="B195" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="C195" s="20"/>
-      <c r="D195" s="20"/>
+      <c r="B195" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="C195" s="23"/>
+      <c r="D195" s="23"/>
       <c r="E195" s="11"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2"/>
-      <c r="B196" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="C196" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="D196" s="20"/>
+      <c r="B196" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="C196" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="D196" s="23"/>
       <c r="E196" s="11"/>
     </row>
     <row r="197" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2"/>
-      <c r="B197" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="C197" s="20"/>
-      <c r="D197" s="20"/>
+      <c r="B197" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="C197" s="23"/>
+      <c r="D197" s="23"/>
       <c r="E197" s="11"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2"/>
-      <c r="B198" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="C198" s="20"/>
-      <c r="D198" s="20"/>
+      <c r="B198" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="C198" s="23"/>
+      <c r="D198" s="23"/>
       <c r="E198" s="11"/>
     </row>
     <row r="199" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2"/>
-      <c r="B199" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="C199" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="D199" s="20" t="s">
-        <v>274</v>
+      <c r="B199" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="C199" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="D199" s="23" t="s">
+        <v>277</v>
       </c>
       <c r="E199" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="F199" s="15"/>
+        <v>184</v>
+      </c>
+      <c r="F199" s="16"/>
     </row>
     <row r="200" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2"/>
-      <c r="B200" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="C200" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="D200" s="20"/>
+      <c r="B200" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="C200" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="D200" s="23"/>
       <c r="E200" s="11"/>
     </row>
     <row r="201" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2"/>
-      <c r="B201" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="C201" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="D201" s="20" t="s">
-        <v>278</v>
+      <c r="B201" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="C201" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="D201" s="23" t="s">
+        <v>281</v>
       </c>
       <c r="E201" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2"/>
-      <c r="B202" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="C202" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="D202" s="20" t="s">
-        <v>281</v>
+      <c r="B202" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="C202" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="D202" s="23" t="s">
+        <v>284</v>
       </c>
       <c r="E202" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2"/>
-      <c r="B203" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="C203" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="D203" s="20" t="s">
-        <v>284</v>
+      <c r="B203" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="C203" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="D203" s="23" t="s">
+        <v>287</v>
       </c>
       <c r="E203" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="F203" s="18" t="s">
-        <v>285</v>
+        <v>184</v>
+      </c>
+      <c r="F203" s="21" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2"/>
-      <c r="B204" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="C204" s="20"/>
-      <c r="D204" s="20"/>
+      <c r="B204" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="C204" s="23"/>
+      <c r="D204" s="23"/>
       <c r="E204" s="11"/>
     </row>
     <row r="205" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2"/>
-      <c r="B205" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="C205" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D205" s="20" t="s">
-        <v>75</v>
+      <c r="B205" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="C205" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D205" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="E205" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2"/>
-      <c r="B206" s="20"/>
-      <c r="C206" s="20"/>
-      <c r="D206" s="20"/>
+      <c r="B206" s="23"/>
+      <c r="C206" s="23"/>
+      <c r="D206" s="23"/>
       <c r="E206" s="11"/>
-      <c r="F206" s="15"/>
+      <c r="F206" s="16"/>
       <c r="G206" s="1"/>
       <c r="H206" s="1"/>
       <c r="I206" s="1"/>
@@ -5763,353 +5735,353 @@
     </row>
     <row r="207" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="6"/>
-      <c r="B207" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="C207" s="22"/>
-      <c r="D207" s="22"/>
+      <c r="B207" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="C207" s="25"/>
+      <c r="D207" s="25"/>
       <c r="E207" s="8"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B208" s="20"/>
-      <c r="C208" s="20"/>
-      <c r="D208" s="20"/>
+      <c r="B208" s="23"/>
+      <c r="C208" s="23"/>
+      <c r="D208" s="23"/>
       <c r="E208" s="11"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2"/>
-      <c r="B209" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="C209" s="20"/>
-      <c r="D209" s="20"/>
+      <c r="B209" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="C209" s="23"/>
+      <c r="D209" s="23"/>
       <c r="E209" s="11"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2"/>
-      <c r="B210" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="C210" s="20"/>
-      <c r="D210" s="20"/>
+      <c r="B210" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="C210" s="23"/>
+      <c r="D210" s="23"/>
       <c r="E210" s="11"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2"/>
-      <c r="B211" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="C211" s="20"/>
-      <c r="D211" s="20"/>
+      <c r="B211" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="C211" s="23"/>
+      <c r="D211" s="23"/>
       <c r="E211" s="11"/>
     </row>
     <row r="212" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2"/>
-      <c r="B212" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C212" s="20"/>
-      <c r="D212" s="20"/>
+      <c r="B212" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="C212" s="23"/>
+      <c r="D212" s="23"/>
       <c r="E212" s="11"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2"/>
-      <c r="B213" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="C213" s="20"/>
-      <c r="D213" s="20"/>
+      <c r="B213" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="C213" s="23"/>
+      <c r="D213" s="23"/>
       <c r="E213" s="11"/>
     </row>
     <row r="214" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2"/>
-      <c r="B214" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="C214" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="D214" s="20"/>
+      <c r="B214" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="C214" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="D214" s="23"/>
       <c r="E214" s="11"/>
     </row>
     <row r="215" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2"/>
-      <c r="B215" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="C215" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="D215" s="20"/>
+      <c r="B215" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="C215" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="D215" s="23"/>
       <c r="E215" s="11"/>
     </row>
     <row r="216" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2"/>
-      <c r="B216" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="C216" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="D216" s="20"/>
+      <c r="B216" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="C216" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="D216" s="23"/>
       <c r="E216" s="11"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2"/>
-      <c r="B217" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="C217" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="D217" s="20"/>
+      <c r="B217" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C217" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="D217" s="23"/>
       <c r="E217" s="11"/>
     </row>
     <row r="218" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2"/>
-      <c r="B218" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="C218" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D218" s="20"/>
+      <c r="B218" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C218" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D218" s="23"/>
       <c r="E218" s="11"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2"/>
-      <c r="B219" s="20"/>
-      <c r="C219" s="20"/>
-      <c r="D219" s="20"/>
+      <c r="B219" s="23"/>
+      <c r="C219" s="23"/>
+      <c r="D219" s="23"/>
       <c r="E219" s="11"/>
     </row>
     <row r="220" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B220" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="C220" s="20"/>
-      <c r="D220" s="20"/>
+        <v>247</v>
+      </c>
+      <c r="B220" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="C220" s="23"/>
+      <c r="D220" s="23"/>
       <c r="E220" s="11"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2"/>
-      <c r="B221" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="C221" s="20"/>
-      <c r="D221" s="20"/>
+      <c r="B221" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="C221" s="23"/>
+      <c r="D221" s="23"/>
       <c r="E221" s="11"/>
     </row>
     <row r="222" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2"/>
-      <c r="B222" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="C222" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="D222" s="20" t="s">
-        <v>303</v>
+      <c r="B222" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="C222" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="D222" s="23" t="s">
+        <v>306</v>
       </c>
       <c r="E222" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="F222" s="18" t="s">
-        <v>304</v>
+        <v>184</v>
+      </c>
+      <c r="F222" s="21" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2"/>
-      <c r="B223" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="C223" s="20"/>
-      <c r="D223" s="20"/>
+      <c r="B223" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="C223" s="23"/>
+      <c r="D223" s="23"/>
       <c r="E223" s="11"/>
     </row>
     <row r="224" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2"/>
-      <c r="B224" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="C224" s="20"/>
-      <c r="D224" s="20"/>
+      <c r="B224" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="C224" s="23"/>
+      <c r="D224" s="23"/>
       <c r="E224" s="11"/>
     </row>
-    <row r="225" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2"/>
-      <c r="B225" s="20" t="s">
-        <v>307</v>
-      </c>
-      <c r="C225" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="D225" s="20" t="s">
-        <v>309</v>
+      <c r="B225" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="C225" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="D225" s="23" t="s">
+        <v>312</v>
       </c>
       <c r="E225" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="F225" s="18" t="s">
-        <v>310</v>
+        <v>137</v>
+      </c>
+      <c r="F225" s="21" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2"/>
-      <c r="B226" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="C226" s="20"/>
-      <c r="D226" s="20"/>
+      <c r="B226" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="C226" s="23"/>
+      <c r="D226" s="23"/>
       <c r="E226" s="11"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2"/>
-      <c r="B227" s="20"/>
-      <c r="C227" s="20"/>
-      <c r="D227" s="20"/>
+      <c r="B227" s="23"/>
+      <c r="C227" s="23"/>
+      <c r="D227" s="23"/>
       <c r="E227" s="11"/>
     </row>
     <row r="228" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="6"/>
-      <c r="B228" s="21" t="s">
-        <v>312</v>
-      </c>
-      <c r="C228" s="22"/>
-      <c r="D228" s="22"/>
+      <c r="B228" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="C228" s="25"/>
+      <c r="D228" s="25"/>
       <c r="E228" s="8"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B229" s="20"/>
-      <c r="C229" s="20"/>
-      <c r="D229" s="20"/>
+      <c r="B229" s="23"/>
+      <c r="C229" s="23"/>
+      <c r="D229" s="23"/>
       <c r="E229" s="11"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2"/>
-      <c r="B230" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="C230" s="20"/>
-      <c r="D230" s="20"/>
+      <c r="B230" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="C230" s="23"/>
+      <c r="D230" s="23"/>
       <c r="E230" s="11"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2"/>
-      <c r="B231" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="C231" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="D231" s="20" t="s">
-        <v>315</v>
+      <c r="B231" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="C231" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="D231" s="23" t="s">
+        <v>318</v>
       </c>
       <c r="E231" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="2"/>
-      <c r="B232" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="C232" s="20"/>
-      <c r="D232" s="20"/>
+      <c r="B232" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="C232" s="23"/>
+      <c r="D232" s="23"/>
       <c r="E232" s="11"/>
     </row>
     <row r="233" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2"/>
-      <c r="B233" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="C233" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="D233" s="23" t="s">
-        <v>319</v>
+      <c r="B233" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="C233" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="D233" s="26" t="s">
+        <v>322</v>
       </c>
       <c r="E233" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2"/>
-      <c r="B234" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="C234" s="20"/>
-      <c r="D234" s="20"/>
+      <c r="B234" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="C234" s="23"/>
+      <c r="D234" s="23"/>
       <c r="E234" s="11"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2"/>
-      <c r="B235" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="C235" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="D235" s="20" t="s">
-        <v>323</v>
+      <c r="B235" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="C235" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="D235" s="23" t="s">
+        <v>326</v>
       </c>
       <c r="E235" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2"/>
-      <c r="B236" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="C236" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="D236" s="20" t="s">
-        <v>309</v>
+      <c r="B236" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="C236" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="D236" s="23" t="s">
+        <v>312</v>
       </c>
       <c r="E236" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="2"/>
-      <c r="B237" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="C237" s="20"/>
-      <c r="D237" s="20"/>
+      <c r="B237" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="C237" s="23"/>
+      <c r="D237" s="23"/>
       <c r="E237" s="11"/>
     </row>
     <row r="238" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2"/>
-      <c r="B238" s="20" t="s">
-        <v>326</v>
-      </c>
-      <c r="C238" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D238" s="20" t="s">
-        <v>75</v>
+      <c r="B238" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="C238" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D238" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="E238" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="2"/>
-      <c r="B239" s="20"/>
-      <c r="C239" s="20"/>
-      <c r="D239" s="20"/>
+      <c r="B239" s="23"/>
+      <c r="C239" s="23"/>
+      <c r="D239" s="23"/>
       <c r="E239" s="11"/>
       <c r="G239" s="1"/>
       <c r="H239" s="1"/>
@@ -6118,3345 +6090,3331 @@
     </row>
     <row r="240" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="6"/>
-      <c r="B240" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="C240" s="22"/>
-      <c r="D240" s="22"/>
+      <c r="B240" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="C240" s="25"/>
+      <c r="D240" s="25"/>
       <c r="E240" s="8"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B241" s="20"/>
-      <c r="C241" s="20"/>
-      <c r="D241" s="20"/>
+      <c r="B241" s="23"/>
+      <c r="C241" s="23"/>
+      <c r="D241" s="23"/>
       <c r="E241" s="11"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2"/>
-      <c r="B242" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="C242" s="20"/>
-      <c r="D242" s="20"/>
+      <c r="B242" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="C242" s="23"/>
+      <c r="D242" s="23"/>
       <c r="E242" s="11"/>
     </row>
     <row r="243" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2"/>
-      <c r="B243" s="20" t="s">
-        <v>329</v>
-      </c>
-      <c r="C243" s="20"/>
-      <c r="D243" s="20"/>
+      <c r="B243" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C243" s="23"/>
+      <c r="D243" s="23"/>
       <c r="E243" s="11"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2"/>
-      <c r="B244" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="C244" s="20"/>
-      <c r="D244" s="20"/>
+      <c r="B244" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="C244" s="23"/>
+      <c r="D244" s="23"/>
       <c r="E244" s="11"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2"/>
-      <c r="B245" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C245" s="20" t="s">
+      <c r="B245" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D245" s="20"/>
+      <c r="C245" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D245" s="23"/>
       <c r="E245" s="11"/>
     </row>
     <row r="246" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="2"/>
-      <c r="B246" s="20" t="s">
-        <v>331</v>
-      </c>
-      <c r="C246" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="D246" s="20"/>
+      <c r="B246" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="C246" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="D246" s="23"/>
       <c r="E246" s="11"/>
     </row>
     <row r="247" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="2"/>
-      <c r="B247" s="20" t="s">
-        <v>333</v>
-      </c>
-      <c r="C247" s="20" t="s">
-        <v>334</v>
-      </c>
-      <c r="D247" s="20" t="s">
-        <v>335</v>
+      <c r="B247" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="C247" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D247" s="23" t="s">
+        <v>338</v>
       </c>
       <c r="E247" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2"/>
-      <c r="B248" s="20" t="s">
-        <v>336</v>
-      </c>
-      <c r="C248" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D248" s="20" t="s">
-        <v>75</v>
+      <c r="B248" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="C248" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D248" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="E248" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2"/>
-      <c r="B249" s="20"/>
-      <c r="C249" s="20"/>
-      <c r="D249" s="20"/>
+      <c r="B249" s="23"/>
+      <c r="C249" s="23"/>
+      <c r="D249" s="23"/>
       <c r="E249" s="11"/>
     </row>
     <row r="250" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="6"/>
-      <c r="B250" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="C250" s="22"/>
-      <c r="D250" s="22"/>
+      <c r="B250" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="C250" s="25"/>
+      <c r="D250" s="25"/>
       <c r="E250" s="8"/>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B251" s="20"/>
-      <c r="C251" s="20"/>
-      <c r="D251" s="20"/>
+      <c r="B251" s="23"/>
+      <c r="C251" s="23"/>
+      <c r="D251" s="23"/>
       <c r="E251" s="11"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2"/>
-      <c r="B252" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="C252" s="20"/>
-      <c r="D252" s="20"/>
+      <c r="B252" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="C252" s="23"/>
+      <c r="D252" s="23"/>
       <c r="E252" s="11"/>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2"/>
-      <c r="B253" s="20" t="s">
-        <v>339</v>
-      </c>
-      <c r="C253" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="D253" s="20" t="s">
-        <v>341</v>
+      <c r="B253" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="C253" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="D253" s="23" t="s">
+        <v>344</v>
       </c>
       <c r="E253" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="2"/>
-      <c r="B254" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="C254" s="20"/>
-      <c r="D254" s="20"/>
+      <c r="B254" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="C254" s="23"/>
+      <c r="D254" s="23"/>
       <c r="E254" s="11"/>
     </row>
     <row r="255" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="2"/>
-      <c r="B255" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C255" s="20"/>
-      <c r="D255" s="20"/>
+      <c r="B255" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="C255" s="23"/>
+      <c r="D255" s="23"/>
       <c r="E255" s="11"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="2"/>
-      <c r="B256" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="C256" s="20"/>
-      <c r="D256" s="20"/>
+      <c r="B256" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="C256" s="23"/>
+      <c r="D256" s="23"/>
       <c r="E256" s="11"/>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="2"/>
-      <c r="B257" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="C257" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D257" s="20"/>
+      <c r="B257" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="C257" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D257" s="23"/>
       <c r="E257" s="11"/>
     </row>
     <row r="258" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="2"/>
-      <c r="B258" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="C258" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="D258" s="20"/>
+      <c r="B258" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="C258" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="D258" s="23"/>
       <c r="E258" s="11"/>
     </row>
     <row r="259" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2"/>
-      <c r="B259" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="C259" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D259" s="20" t="s">
-        <v>75</v>
+      <c r="B259" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="C259" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D259" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="E259" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="2"/>
-      <c r="B260" s="20" t="s">
-        <v>346</v>
-      </c>
-      <c r="C260" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="D260" s="20" t="s">
-        <v>348</v>
+      <c r="B260" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="C260" s="23" t="s">
+        <v>350</v>
+      </c>
+      <c r="D260" s="23" t="s">
+        <v>351</v>
       </c>
       <c r="E260" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="2"/>
-      <c r="B261" s="20"/>
-      <c r="C261" s="20"/>
-      <c r="D261" s="20"/>
+      <c r="B261" s="23"/>
+      <c r="C261" s="23"/>
+      <c r="D261" s="23"/>
       <c r="E261" s="11"/>
     </row>
     <row r="262" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="6"/>
-      <c r="B262" s="21" t="s">
-        <v>349</v>
-      </c>
-      <c r="C262" s="22"/>
-      <c r="D262" s="22"/>
+      <c r="B262" s="24" t="s">
+        <v>352</v>
+      </c>
+      <c r="C262" s="25"/>
+      <c r="D262" s="25"/>
       <c r="E262" s="8"/>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B263" s="20"/>
-      <c r="C263" s="20"/>
-      <c r="D263" s="20"/>
+      <c r="B263" s="23"/>
+      <c r="C263" s="23"/>
+      <c r="D263" s="23"/>
       <c r="E263" s="11"/>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="2"/>
-      <c r="B264" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="C264" s="20"/>
-      <c r="D264" s="20"/>
+      <c r="B264" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="C264" s="23"/>
+      <c r="D264" s="23"/>
       <c r="E264" s="11"/>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="2"/>
-      <c r="B265" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C265" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="D265" s="20" t="s">
-        <v>341</v>
+      <c r="B265" s="23" t="s">
+        <v>354</v>
+      </c>
+      <c r="C265" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="D265" s="23" t="s">
+        <v>344</v>
       </c>
       <c r="E265" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="2"/>
-      <c r="B266" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="C266" s="20"/>
-      <c r="D266" s="20"/>
+      <c r="B266" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="C266" s="23"/>
+      <c r="D266" s="23"/>
       <c r="E266" s="11"/>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2"/>
-      <c r="B267" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="C267" s="20"/>
-      <c r="D267" s="20"/>
+      <c r="B267" s="23" t="s">
+        <v>356</v>
+      </c>
+      <c r="C267" s="23"/>
+      <c r="D267" s="23"/>
       <c r="E267" s="11"/>
     </row>
     <row r="268" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="2"/>
-      <c r="B268" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="C268" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D268" s="20" t="s">
-        <v>75</v>
+      <c r="B268" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="C268" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D268" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="E268" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="2"/>
-      <c r="B269" s="20" t="s">
-        <v>355</v>
-      </c>
-      <c r="C269" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="D269" s="20" t="s">
-        <v>357</v>
+      <c r="B269" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="C269" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="D269" s="23" t="s">
+        <v>360</v>
       </c>
       <c r="E269" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="2"/>
-      <c r="B270" s="20"/>
-      <c r="C270" s="20"/>
-      <c r="D270" s="20"/>
+      <c r="B270" s="23"/>
+      <c r="C270" s="23"/>
+      <c r="D270" s="23"/>
       <c r="E270" s="11"/>
-      <c r="F270" s="15"/>
+      <c r="F270" s="16"/>
       <c r="G270" s="1"/>
     </row>
     <row r="271" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="6"/>
-      <c r="B271" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="C271" s="22"/>
-      <c r="D271" s="22"/>
+      <c r="B271" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="C271" s="25"/>
+      <c r="D271" s="25"/>
       <c r="E271" s="8"/>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B272" s="20"/>
-      <c r="C272" s="20"/>
-      <c r="D272" s="20"/>
+      <c r="B272" s="23"/>
+      <c r="C272" s="23"/>
+      <c r="D272" s="23"/>
       <c r="E272" s="11"/>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="2"/>
-      <c r="B273" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="C273" s="20"/>
-      <c r="D273" s="20"/>
+      <c r="B273" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="C273" s="23"/>
+      <c r="D273" s="23"/>
       <c r="E273" s="11"/>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="2"/>
-      <c r="B274" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="C274" s="20"/>
-      <c r="D274" s="20"/>
+      <c r="B274" s="23" t="s">
+        <v>363</v>
+      </c>
+      <c r="C274" s="23"/>
+      <c r="D274" s="23"/>
       <c r="E274" s="11"/>
     </row>
     <row r="275" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="2"/>
-      <c r="B275" s="20" t="s">
-        <v>361</v>
-      </c>
-      <c r="C275" s="20" t="s">
-        <v>362</v>
-      </c>
-      <c r="D275" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="E275" s="25" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="276" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B275" s="23" t="s">
+        <v>364</v>
+      </c>
+      <c r="C275" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="D275" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="E275" s="27" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="2"/>
-      <c r="B276" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="C276" s="20" t="s">
-        <v>365</v>
-      </c>
-      <c r="D276" s="20" t="s">
-        <v>366</v>
+      <c r="B276" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="C276" s="23" t="s">
+        <v>368</v>
+      </c>
+      <c r="D276" s="23" t="s">
+        <v>369</v>
       </c>
       <c r="E276" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="2"/>
-      <c r="B277" s="20" t="s">
-        <v>367</v>
-      </c>
-      <c r="C277" s="20"/>
-      <c r="D277" s="20"/>
+      <c r="B277" s="23" t="s">
+        <v>370</v>
+      </c>
+      <c r="C277" s="23"/>
+      <c r="D277" s="23"/>
       <c r="E277" s="11"/>
     </row>
     <row r="278" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="2"/>
-      <c r="B278" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="C278" s="20"/>
-      <c r="D278" s="20"/>
+      <c r="B278" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="C278" s="23"/>
+      <c r="D278" s="23"/>
       <c r="E278" s="11"/>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="2"/>
-      <c r="B279" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="C279" s="20"/>
-      <c r="D279" s="20"/>
+      <c r="B279" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="C279" s="23"/>
+      <c r="D279" s="23"/>
       <c r="E279" s="11"/>
     </row>
     <row r="280" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="2"/>
-      <c r="B280" s="20" t="s">
-        <v>370</v>
-      </c>
-      <c r="C280" s="20"/>
-      <c r="D280" s="20"/>
+      <c r="B280" s="23" t="s">
+        <v>373</v>
+      </c>
+      <c r="C280" s="23"/>
+      <c r="D280" s="23"/>
       <c r="E280" s="11"/>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="2"/>
-      <c r="B281" s="20" t="s">
-        <v>371</v>
-      </c>
-      <c r="C281" s="20"/>
-      <c r="D281" s="20"/>
+      <c r="B281" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="C281" s="23"/>
+      <c r="D281" s="23"/>
       <c r="E281" s="11"/>
     </row>
     <row r="282" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="2"/>
-      <c r="B282" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="C282" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="D282" s="20"/>
+      <c r="B282" s="23" t="s">
+        <v>375</v>
+      </c>
+      <c r="C282" s="23" t="s">
+        <v>376</v>
+      </c>
+      <c r="D282" s="23"/>
       <c r="E282" s="11"/>
     </row>
     <row r="283" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="2"/>
-      <c r="B283" s="20" t="s">
-        <v>374</v>
-      </c>
-      <c r="C283" s="20" t="s">
-        <v>375</v>
-      </c>
-      <c r="D283" s="20" t="s">
-        <v>376</v>
+      <c r="B283" s="23" t="s">
+        <v>377</v>
+      </c>
+      <c r="C283" s="23" t="s">
+        <v>378</v>
+      </c>
+      <c r="D283" s="23" t="s">
+        <v>379</v>
       </c>
       <c r="E283" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="2"/>
-      <c r="B284" s="20" t="s">
-        <v>377</v>
-      </c>
-      <c r="C284" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D284" s="20" t="s">
-        <v>75</v>
+      <c r="B284" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="C284" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D284" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="E284" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="2"/>
-      <c r="B285" s="20"/>
-      <c r="C285" s="20"/>
-      <c r="D285" s="20"/>
+      <c r="B285" s="23"/>
+      <c r="C285" s="23"/>
+      <c r="D285" s="23"/>
       <c r="E285" s="11"/>
     </row>
     <row r="286" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="6"/>
-      <c r="B286" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="C286" s="22"/>
-      <c r="D286" s="22"/>
+      <c r="B286" s="24" t="s">
+        <v>381</v>
+      </c>
+      <c r="C286" s="25"/>
+      <c r="D286" s="25"/>
       <c r="E286" s="8"/>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B287" s="20"/>
-      <c r="C287" s="20"/>
-      <c r="D287" s="20"/>
+      <c r="B287" s="23"/>
+      <c r="C287" s="23"/>
+      <c r="D287" s="23"/>
       <c r="E287" s="11"/>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="2"/>
-      <c r="B288" s="20" t="s">
-        <v>379</v>
-      </c>
-      <c r="C288" s="20"/>
-      <c r="D288" s="20"/>
+      <c r="B288" s="23" t="s">
+        <v>382</v>
+      </c>
+      <c r="C288" s="23"/>
+      <c r="D288" s="23"/>
       <c r="E288" s="11"/>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="2"/>
-      <c r="B289" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="C289" s="20" t="s">
-        <v>381</v>
-      </c>
-      <c r="D289" s="20" t="s">
-        <v>382</v>
+      <c r="B289" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C289" s="23" t="s">
+        <v>384</v>
+      </c>
+      <c r="D289" s="23" t="s">
+        <v>385</v>
       </c>
       <c r="E289" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="2"/>
-      <c r="B290" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="C290" s="20"/>
-      <c r="D290" s="20"/>
+      <c r="B290" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="C290" s="23"/>
+      <c r="D290" s="23"/>
       <c r="E290" s="11"/>
     </row>
-    <row r="291" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="2"/>
-      <c r="B291" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="C291" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="D291" s="20" t="s">
-        <v>386</v>
+      <c r="B291" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="C291" s="23" t="s">
+        <v>388</v>
+      </c>
+      <c r="D291" s="23" t="s">
+        <v>389</v>
       </c>
       <c r="E291" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2"/>
-      <c r="B292" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="C292" s="20"/>
-      <c r="D292" s="20"/>
+      <c r="B292" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="C292" s="23"/>
+      <c r="D292" s="23"/>
       <c r="E292" s="11"/>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="2"/>
-      <c r="B293" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="C293" s="20"/>
-      <c r="D293" s="20"/>
+      <c r="B293" s="23" t="s">
+        <v>391</v>
+      </c>
+      <c r="C293" s="23"/>
+      <c r="D293" s="23"/>
       <c r="E293" s="11"/>
     </row>
     <row r="294" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="2"/>
-      <c r="B294" s="20" t="s">
-        <v>389</v>
-      </c>
-      <c r="C294" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D294" s="20" t="s">
-        <v>75</v>
+      <c r="B294" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C294" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D294" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="E294" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="2"/>
-      <c r="B295" s="20" t="s">
-        <v>390</v>
-      </c>
-      <c r="C295" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="D295" s="20"/>
+      <c r="B295" s="23" t="s">
+        <v>393</v>
+      </c>
+      <c r="C295" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="D295" s="23"/>
       <c r="E295" s="11"/>
     </row>
     <row r="296" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="2"/>
-      <c r="B296" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="C296" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="D296" s="20" t="s">
-        <v>393</v>
+      <c r="B296" s="23" t="s">
+        <v>394</v>
+      </c>
+      <c r="C296" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="D296" s="23" t="s">
+        <v>396</v>
       </c>
       <c r="E296" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="2"/>
-      <c r="B297" s="20"/>
-      <c r="C297" s="20"/>
-      <c r="D297" s="20"/>
+      <c r="B297" s="23"/>
+      <c r="C297" s="23"/>
+      <c r="D297" s="23"/>
       <c r="E297" s="11"/>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B298" s="20" t="s">
-        <v>394</v>
-      </c>
-      <c r="C298" s="20"/>
-      <c r="D298" s="20"/>
+        <v>247</v>
+      </c>
+      <c r="B298" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="C298" s="23"/>
+      <c r="D298" s="23"/>
       <c r="E298" s="11"/>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="2"/>
-      <c r="B299" s="20" t="s">
-        <v>395</v>
-      </c>
-      <c r="C299" s="20"/>
-      <c r="D299" s="20"/>
+      <c r="B299" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="C299" s="23"/>
+      <c r="D299" s="23"/>
       <c r="E299" s="11"/>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="2"/>
-      <c r="B300" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="C300" s="20"/>
-      <c r="D300" s="20"/>
+      <c r="B300" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="C300" s="23"/>
+      <c r="D300" s="23"/>
       <c r="E300" s="11"/>
     </row>
     <row r="301" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="2"/>
-      <c r="B301" s="20" t="s">
-        <v>397</v>
-      </c>
-      <c r="C301" s="20" t="s">
-        <v>398</v>
-      </c>
-      <c r="D301" s="20"/>
+      <c r="B301" s="23" t="s">
+        <v>400</v>
+      </c>
+      <c r="C301" s="23" t="s">
+        <v>401</v>
+      </c>
+      <c r="D301" s="23"/>
       <c r="E301" s="11"/>
     </row>
     <row r="302" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="2"/>
-      <c r="B302" s="20" t="s">
-        <v>399</v>
-      </c>
-      <c r="C302" s="20" t="s">
-        <v>400</v>
-      </c>
-      <c r="D302" s="20" t="s">
-        <v>401</v>
+      <c r="B302" s="23" t="s">
+        <v>402</v>
+      </c>
+      <c r="C302" s="23" t="s">
+        <v>403</v>
+      </c>
+      <c r="D302" s="23" t="s">
+        <v>404</v>
       </c>
       <c r="E302" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="2"/>
-      <c r="B303" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="C303" s="20"/>
-      <c r="D303" s="20"/>
+      <c r="B303" s="23" t="s">
+        <v>405</v>
+      </c>
+      <c r="C303" s="23"/>
+      <c r="D303" s="23"/>
       <c r="E303" s="11"/>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="2"/>
-      <c r="B304" s="20" t="s">
-        <v>403</v>
-      </c>
-      <c r="C304" s="20"/>
-      <c r="D304" s="20"/>
+      <c r="B304" s="23" t="s">
+        <v>406</v>
+      </c>
+      <c r="C304" s="23"/>
+      <c r="D304" s="23"/>
       <c r="E304" s="11"/>
     </row>
     <row r="305" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="2"/>
-      <c r="B305" s="20" t="s">
-        <v>404</v>
-      </c>
-      <c r="C305" s="20"/>
-      <c r="D305" s="20"/>
+      <c r="B305" s="23" t="s">
+        <v>407</v>
+      </c>
+      <c r="C305" s="23"/>
+      <c r="D305" s="23"/>
       <c r="E305" s="11"/>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="2"/>
-      <c r="B306" s="20" t="s">
-        <v>405</v>
-      </c>
-      <c r="C306" s="20"/>
-      <c r="D306" s="20"/>
+      <c r="B306" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="C306" s="23"/>
+      <c r="D306" s="23"/>
       <c r="E306" s="11"/>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="2"/>
-      <c r="B307" s="20" t="s">
-        <v>406</v>
-      </c>
-      <c r="C307" s="20" t="s">
-        <v>407</v>
-      </c>
-      <c r="D307" s="20"/>
+      <c r="B307" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="C307" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="D307" s="23"/>
       <c r="E307" s="11"/>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="2"/>
-      <c r="B308" s="20" t="s">
-        <v>408</v>
-      </c>
-      <c r="C308" s="20" t="s">
-        <v>409</v>
-      </c>
-      <c r="D308" s="20"/>
+      <c r="B308" s="23" t="s">
+        <v>411</v>
+      </c>
+      <c r="C308" s="23" t="s">
+        <v>412</v>
+      </c>
+      <c r="D308" s="23"/>
       <c r="E308" s="11"/>
     </row>
     <row r="309" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="2"/>
-      <c r="B309" s="20" t="s">
-        <v>410</v>
-      </c>
-      <c r="C309" s="20" t="s">
-        <v>400</v>
-      </c>
-      <c r="D309" s="20" t="s">
-        <v>411</v>
+      <c r="B309" s="23" t="s">
+        <v>413</v>
+      </c>
+      <c r="C309" s="23" t="s">
+        <v>403</v>
+      </c>
+      <c r="D309" s="23" t="s">
+        <v>414</v>
       </c>
       <c r="E309" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="2"/>
-      <c r="B310" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="C310" s="20"/>
-      <c r="D310" s="20"/>
+      <c r="B310" s="23" t="s">
+        <v>415</v>
+      </c>
+      <c r="C310" s="23"/>
+      <c r="D310" s="23"/>
       <c r="E310" s="11"/>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="2"/>
-      <c r="B311" s="20"/>
-      <c r="C311" s="20"/>
-      <c r="D311" s="20"/>
+      <c r="B311" s="23"/>
+      <c r="C311" s="23"/>
+      <c r="D311" s="23"/>
       <c r="E311" s="11"/>
     </row>
     <row r="312" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="6"/>
-      <c r="B312" s="21" t="s">
-        <v>413</v>
-      </c>
-      <c r="C312" s="22"/>
-      <c r="D312" s="22"/>
+      <c r="B312" s="24" t="s">
+        <v>416</v>
+      </c>
+      <c r="C312" s="25"/>
+      <c r="D312" s="25"/>
       <c r="E312" s="8"/>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B313" s="19"/>
-      <c r="C313" s="20"/>
-      <c r="D313" s="20"/>
+      <c r="B313" s="22"/>
+      <c r="C313" s="23"/>
+      <c r="D313" s="23"/>
       <c r="E313" s="11"/>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="2"/>
-      <c r="B314" s="20" t="s">
-        <v>414</v>
-      </c>
-      <c r="C314" s="20"/>
-      <c r="D314" s="20"/>
+      <c r="B314" s="23" t="s">
+        <v>417</v>
+      </c>
+      <c r="C314" s="23"/>
+      <c r="D314" s="23"/>
       <c r="E314" s="11"/>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="2"/>
-      <c r="B315" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="C315" s="20"/>
-      <c r="D315" s="20"/>
+      <c r="B315" s="23" t="s">
+        <v>418</v>
+      </c>
+      <c r="C315" s="23"/>
+      <c r="D315" s="23"/>
       <c r="E315" s="11"/>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="2"/>
-      <c r="B316" s="20" t="s">
-        <v>416</v>
-      </c>
-      <c r="C316" s="20"/>
-      <c r="D316" s="20"/>
+      <c r="B316" s="23" t="s">
+        <v>419</v>
+      </c>
+      <c r="C316" s="23"/>
+      <c r="D316" s="23"/>
       <c r="E316" s="11"/>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="2"/>
-      <c r="B317" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="C317" s="20"/>
-      <c r="D317" s="20"/>
+      <c r="B317" s="23" t="s">
+        <v>356</v>
+      </c>
+      <c r="C317" s="23"/>
+      <c r="D317" s="23"/>
       <c r="E317" s="11"/>
     </row>
     <row r="318" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="2"/>
-      <c r="B318" s="20" t="s">
-        <v>417</v>
-      </c>
-      <c r="C318" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D318" s="20" t="s">
-        <v>75</v>
+      <c r="B318" s="23" t="s">
+        <v>420</v>
+      </c>
+      <c r="C318" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D318" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="E318" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="2"/>
-      <c r="B319" s="20" t="s">
-        <v>418</v>
-      </c>
-      <c r="C319" s="20" t="s">
-        <v>419</v>
-      </c>
-      <c r="D319" s="20" t="s">
-        <v>420</v>
+      <c r="B319" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="C319" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="D319" s="23" t="s">
+        <v>423</v>
       </c>
       <c r="E319" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="2"/>
-      <c r="B320" s="19"/>
-      <c r="C320" s="20"/>
-      <c r="D320" s="20"/>
+      <c r="B320" s="22"/>
+      <c r="C320" s="23"/>
+      <c r="D320" s="23"/>
       <c r="E320" s="11"/>
     </row>
     <row r="321" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="6"/>
-      <c r="B321" s="21" t="s">
-        <v>421</v>
-      </c>
-      <c r="C321" s="22"/>
-      <c r="D321" s="22"/>
+      <c r="B321" s="24" t="s">
+        <v>424</v>
+      </c>
+      <c r="C321" s="25"/>
+      <c r="D321" s="25"/>
       <c r="E321" s="8"/>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B322" s="19"/>
-      <c r="C322" s="20"/>
-      <c r="D322" s="20"/>
+      <c r="B322" s="22"/>
+      <c r="C322" s="23"/>
+      <c r="D322" s="23"/>
       <c r="E322" s="11"/>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="2"/>
-      <c r="B323" s="20" t="s">
-        <v>422</v>
-      </c>
-      <c r="C323" s="20"/>
-      <c r="D323" s="20"/>
+      <c r="B323" s="23" t="s">
+        <v>425</v>
+      </c>
+      <c r="C323" s="23"/>
+      <c r="D323" s="23"/>
       <c r="E323" s="11"/>
     </row>
     <row r="324" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="2"/>
-      <c r="B324" s="20" t="s">
-        <v>423</v>
-      </c>
-      <c r="C324" s="20"/>
-      <c r="D324" s="20"/>
+      <c r="B324" s="23" t="s">
+        <v>426</v>
+      </c>
+      <c r="C324" s="23"/>
+      <c r="D324" s="23"/>
       <c r="E324" s="11"/>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="2"/>
-      <c r="B325" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="C325" s="20"/>
-      <c r="D325" s="20"/>
+      <c r="B325" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="C325" s="23"/>
+      <c r="D325" s="23"/>
       <c r="E325" s="11"/>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="2"/>
-      <c r="B326" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C326" s="20" t="s">
+      <c r="B326" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D326" s="20"/>
+      <c r="C326" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D326" s="23"/>
       <c r="E326" s="11"/>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="2"/>
-      <c r="B327" s="20" t="s">
-        <v>424</v>
-      </c>
-      <c r="C327" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D327" s="20"/>
+      <c r="B327" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="C327" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D327" s="23"/>
       <c r="E327" s="11"/>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="2"/>
-      <c r="B328" s="20" t="s">
-        <v>425</v>
-      </c>
-      <c r="C328" s="20" t="s">
-        <v>426</v>
-      </c>
-      <c r="D328" s="20"/>
+      <c r="B328" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="C328" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="D328" s="23"/>
       <c r="E328" s="11"/>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="2"/>
-      <c r="B329" s="20" t="s">
-        <v>427</v>
-      </c>
-      <c r="C329" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D329" s="20"/>
+      <c r="B329" s="23" t="s">
+        <v>430</v>
+      </c>
+      <c r="C329" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D329" s="23"/>
       <c r="E329" s="11"/>
     </row>
     <row r="330" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="2"/>
-      <c r="B330" s="20" t="s">
-        <v>428</v>
-      </c>
-      <c r="C330" s="20" t="s">
-        <v>429</v>
-      </c>
-      <c r="D330" s="20" t="s">
-        <v>430</v>
+      <c r="B330" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="C330" s="23" t="s">
+        <v>432</v>
+      </c>
+      <c r="D330" s="23" t="s">
+        <v>433</v>
       </c>
       <c r="E330" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="2"/>
-      <c r="B331" s="20" t="s">
-        <v>432</v>
-      </c>
-      <c r="C331" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D331" s="20" t="s">
-        <v>75</v>
+      <c r="B331" s="23" t="s">
+        <v>435</v>
+      </c>
+      <c r="C331" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D331" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="E331" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="2"/>
-      <c r="B332" s="20"/>
-      <c r="C332" s="20"/>
-      <c r="D332" s="20"/>
+      <c r="B332" s="23"/>
+      <c r="C332" s="23"/>
+      <c r="D332" s="23"/>
       <c r="E332" s="11"/>
     </row>
     <row r="333" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="6"/>
-      <c r="B333" s="21" t="s">
-        <v>433</v>
-      </c>
-      <c r="C333" s="22"/>
-      <c r="D333" s="22"/>
+      <c r="B333" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="C333" s="25"/>
+      <c r="D333" s="25"/>
       <c r="E333" s="8"/>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B334" s="19"/>
-      <c r="C334" s="20"/>
-      <c r="D334" s="20"/>
+      <c r="B334" s="22"/>
+      <c r="C334" s="23"/>
+      <c r="D334" s="23"/>
       <c r="E334" s="11"/>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="2"/>
-      <c r="B335" s="20" t="s">
+      <c r="B335" s="23" t="s">
+        <v>437</v>
+      </c>
+      <c r="C335" s="23"/>
+      <c r="D335" s="23"/>
+      <c r="E335" s="11"/>
+    </row>
+    <row r="336" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A336" s="2"/>
+      <c r="B336" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="C336" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="D336" s="23" t="s">
+        <v>440</v>
+      </c>
+      <c r="E336" s="11" t="s">
         <v>434</v>
-      </c>
-      <c r="C335" s="20"/>
-      <c r="D335" s="20"/>
-      <c r="E335" s="11"/>
-    </row>
-    <row r="336" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="2"/>
-      <c r="B336" s="20" t="s">
-        <v>435</v>
-      </c>
-      <c r="C336" s="20" t="s">
-        <v>436</v>
-      </c>
-      <c r="D336" s="20" t="s">
-        <v>437</v>
-      </c>
-      <c r="E336" s="11" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="2"/>
-      <c r="B337" s="20" t="s">
-        <v>438</v>
-      </c>
-      <c r="C337" s="20"/>
-      <c r="D337" s="20"/>
+      <c r="B337" s="23" t="s">
+        <v>441</v>
+      </c>
+      <c r="C337" s="23"/>
+      <c r="D337" s="23"/>
       <c r="E337" s="11"/>
     </row>
     <row r="338" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="2"/>
-      <c r="B338" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C338" s="20"/>
-      <c r="D338" s="20"/>
+      <c r="B338" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="C338" s="23"/>
+      <c r="D338" s="23"/>
       <c r="E338" s="11"/>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="2"/>
-      <c r="B339" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="C339" s="20"/>
-      <c r="D339" s="20"/>
+      <c r="B339" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="C339" s="23"/>
+      <c r="D339" s="23"/>
       <c r="E339" s="11"/>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="2"/>
-      <c r="B340" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="C340" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D340" s="20"/>
+      <c r="B340" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="C340" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D340" s="23"/>
       <c r="E340" s="11"/>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="2"/>
-      <c r="B341" s="20" t="s">
-        <v>439</v>
-      </c>
-      <c r="C341" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D341" s="20"/>
+      <c r="B341" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="C341" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D341" s="23"/>
       <c r="E341" s="11"/>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="2"/>
-      <c r="B342" s="20" t="s">
-        <v>440</v>
-      </c>
-      <c r="C342" s="20" t="s">
-        <v>426</v>
-      </c>
-      <c r="D342" s="20"/>
+      <c r="B342" s="23" t="s">
+        <v>443</v>
+      </c>
+      <c r="C342" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="D342" s="23"/>
       <c r="E342" s="11"/>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="2"/>
-      <c r="B343" s="20" t="s">
-        <v>441</v>
-      </c>
-      <c r="C343" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D343" s="20"/>
+      <c r="B343" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="C343" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D343" s="23"/>
       <c r="E343" s="11"/>
     </row>
     <row r="344" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="2"/>
-      <c r="B344" s="20" t="s">
-        <v>442</v>
-      </c>
-      <c r="C344" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D344" s="20" t="s">
-        <v>75</v>
+      <c r="B344" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="C344" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D344" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="E344" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="2"/>
-      <c r="B345" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="C345" s="20" t="s">
-        <v>444</v>
-      </c>
-      <c r="D345" s="20" t="s">
-        <v>445</v>
+      <c r="B345" s="23" t="s">
+        <v>446</v>
+      </c>
+      <c r="C345" s="23" t="s">
+        <v>447</v>
+      </c>
+      <c r="D345" s="23" t="s">
+        <v>448</v>
       </c>
       <c r="E345" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="2"/>
-      <c r="B346" s="20"/>
-      <c r="C346" s="20"/>
-      <c r="D346" s="20"/>
+      <c r="B346" s="23"/>
+      <c r="C346" s="23"/>
+      <c r="D346" s="23"/>
       <c r="E346" s="11"/>
     </row>
     <row r="347" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="6"/>
-      <c r="B347" s="21" t="s">
-        <v>446</v>
-      </c>
-      <c r="C347" s="22"/>
-      <c r="D347" s="22"/>
+      <c r="B347" s="24" t="s">
+        <v>449</v>
+      </c>
+      <c r="C347" s="25"/>
+      <c r="D347" s="25"/>
       <c r="E347" s="8"/>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B348" s="19"/>
-      <c r="C348" s="20"/>
-      <c r="D348" s="20"/>
+      <c r="B348" s="22"/>
+      <c r="C348" s="23"/>
+      <c r="D348" s="23"/>
       <c r="E348" s="11"/>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="2"/>
-      <c r="B349" s="20" t="s">
-        <v>447</v>
-      </c>
-      <c r="C349" s="20"/>
-      <c r="D349" s="20"/>
+      <c r="B349" s="23" t="s">
+        <v>450</v>
+      </c>
+      <c r="C349" s="23"/>
+      <c r="D349" s="23"/>
       <c r="E349" s="11"/>
     </row>
-    <row r="350" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="2"/>
-      <c r="B350" s="20" t="s">
-        <v>448</v>
-      </c>
-      <c r="C350" s="20" t="s">
-        <v>436</v>
-      </c>
-      <c r="D350" s="20" t="s">
-        <v>437</v>
+      <c r="B350" s="23" t="s">
+        <v>451</v>
+      </c>
+      <c r="C350" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="D350" s="23" t="s">
+        <v>440</v>
       </c>
       <c r="E350" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="2"/>
-      <c r="B351" s="20" t="s">
-        <v>449</v>
-      </c>
-      <c r="C351" s="20"/>
-      <c r="D351" s="20"/>
+      <c r="B351" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="C351" s="23"/>
+      <c r="D351" s="23"/>
       <c r="E351" s="11"/>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="2"/>
-      <c r="B352" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="C352" s="20"/>
-      <c r="D352" s="20"/>
+      <c r="B352" s="23" t="s">
+        <v>356</v>
+      </c>
+      <c r="C352" s="23"/>
+      <c r="D352" s="23"/>
       <c r="E352" s="11"/>
     </row>
     <row r="353" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="2"/>
-      <c r="B353" s="20" t="s">
-        <v>450</v>
-      </c>
-      <c r="C353" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D353" s="20" t="s">
-        <v>75</v>
+      <c r="B353" s="23" t="s">
+        <v>453</v>
+      </c>
+      <c r="C353" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D353" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="E353" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="2"/>
-      <c r="B354" s="20" t="s">
-        <v>451</v>
-      </c>
-      <c r="C354" s="20" t="s">
-        <v>452</v>
-      </c>
-      <c r="D354" s="20" t="s">
-        <v>453</v>
+      <c r="B354" s="23" t="s">
+        <v>454</v>
+      </c>
+      <c r="C354" s="23" t="s">
+        <v>455</v>
+      </c>
+      <c r="D354" s="23" t="s">
+        <v>456</v>
       </c>
       <c r="E354" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="2"/>
-      <c r="B355" s="20"/>
-      <c r="C355" s="20"/>
-      <c r="D355" s="20"/>
+      <c r="B355" s="23"/>
+      <c r="C355" s="23"/>
+      <c r="D355" s="23"/>
       <c r="E355" s="11"/>
     </row>
     <row r="356" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="6"/>
-      <c r="B356" s="21" t="s">
-        <v>454</v>
-      </c>
-      <c r="C356" s="22"/>
-      <c r="D356" s="22"/>
+      <c r="B356" s="24" t="s">
+        <v>457</v>
+      </c>
+      <c r="C356" s="25"/>
+      <c r="D356" s="25"/>
       <c r="E356" s="8"/>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B357" s="19"/>
-      <c r="C357" s="20"/>
-      <c r="D357" s="20"/>
+      <c r="B357" s="22"/>
+      <c r="C357" s="23"/>
+      <c r="D357" s="23"/>
       <c r="E357" s="11"/>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2"/>
-      <c r="B358" s="20" t="s">
-        <v>455</v>
-      </c>
-      <c r="C358" s="20"/>
-      <c r="D358" s="20"/>
+      <c r="B358" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="C358" s="23"/>
+      <c r="D358" s="23"/>
       <c r="E358" s="11"/>
     </row>
     <row r="359" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="2"/>
-      <c r="B359" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="C359" s="20"/>
-      <c r="D359" s="20"/>
+      <c r="B359" s="23" t="s">
+        <v>459</v>
+      </c>
+      <c r="C359" s="23"/>
+      <c r="D359" s="23"/>
       <c r="E359" s="11"/>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="2"/>
-      <c r="B360" s="20" t="s">
-        <v>457</v>
-      </c>
-      <c r="C360" s="20" t="s">
-        <v>458</v>
-      </c>
-      <c r="D360" s="20" t="s">
-        <v>459</v>
+      <c r="B360" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="C360" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="D360" s="23" t="s">
+        <v>462</v>
       </c>
       <c r="E360" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="2"/>
-      <c r="B361" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="C361" s="20"/>
-      <c r="D361" s="20"/>
+      <c r="B361" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="C361" s="23"/>
+      <c r="D361" s="23"/>
       <c r="E361" s="11"/>
     </row>
     <row r="362" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="2"/>
-      <c r="B362" s="20" t="s">
-        <v>461</v>
-      </c>
-      <c r="C362" s="20"/>
-      <c r="D362" s="20"/>
+      <c r="B362" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="C362" s="23"/>
+      <c r="D362" s="23"/>
       <c r="E362" s="11"/>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="2"/>
-      <c r="B363" s="20" t="s">
-        <v>462</v>
-      </c>
-      <c r="C363" s="20"/>
-      <c r="D363" s="20"/>
+      <c r="B363" s="23" t="s">
+        <v>465</v>
+      </c>
+      <c r="C363" s="23"/>
+      <c r="D363" s="23"/>
       <c r="E363" s="11"/>
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="2"/>
-      <c r="B364" s="20" t="s">
-        <v>463</v>
-      </c>
-      <c r="C364" s="20" t="s">
-        <v>464</v>
-      </c>
-      <c r="D364" s="20" t="s">
-        <v>465</v>
+      <c r="B364" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="C364" s="23" t="s">
+        <v>467</v>
+      </c>
+      <c r="D364" s="23" t="s">
+        <v>468</v>
       </c>
       <c r="E364" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="2"/>
-      <c r="B365" s="20" t="s">
-        <v>466</v>
-      </c>
-      <c r="C365" s="20" t="s">
-        <v>467</v>
-      </c>
-      <c r="D365" s="20" t="s">
-        <v>468</v>
+      <c r="B365" s="23" t="s">
+        <v>469</v>
+      </c>
+      <c r="C365" s="23" t="s">
+        <v>470</v>
+      </c>
+      <c r="D365" s="23" t="s">
+        <v>471</v>
       </c>
       <c r="E365" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="2"/>
-      <c r="B366" s="20" t="s">
-        <v>469</v>
-      </c>
-      <c r="C366" s="20" t="s">
-        <v>407</v>
-      </c>
-      <c r="D366" s="20"/>
+      <c r="B366" s="23" t="s">
+        <v>472</v>
+      </c>
+      <c r="C366" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="D366" s="23"/>
       <c r="E366" s="11"/>
     </row>
     <row r="367" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="2"/>
-      <c r="B367" s="20" t="s">
-        <v>470</v>
-      </c>
-      <c r="C367" s="20" t="s">
-        <v>471</v>
-      </c>
-      <c r="D367" s="20" t="s">
-        <v>472</v>
+      <c r="B367" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="C367" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="D367" s="23" t="s">
+        <v>475</v>
       </c>
       <c r="E367" s="11" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="368" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="2"/>
-      <c r="B368" s="20" t="s">
-        <v>473</v>
-      </c>
-      <c r="C368" s="20" t="s">
-        <v>474</v>
-      </c>
-      <c r="D368" s="20" t="s">
-        <v>475</v>
+      <c r="B368" s="23" t="s">
+        <v>476</v>
+      </c>
+      <c r="C368" s="23" t="s">
+        <v>477</v>
+      </c>
+      <c r="D368" s="23" t="s">
+        <v>478</v>
       </c>
       <c r="E368" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="2"/>
-      <c r="B369" s="20" t="s">
-        <v>476</v>
-      </c>
-      <c r="C369" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D369" s="20" t="s">
-        <v>75</v>
+      <c r="B369" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="C369" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D369" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="E369" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="2"/>
-      <c r="B370" s="20"/>
-      <c r="C370" s="20"/>
-      <c r="D370" s="20"/>
+      <c r="B370" s="23"/>
+      <c r="C370" s="23"/>
+      <c r="D370" s="23"/>
       <c r="E370" s="11"/>
     </row>
     <row r="371" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="26"/>
-      <c r="B371" s="21" t="s">
-        <v>477</v>
-      </c>
-      <c r="C371" s="22"/>
-      <c r="D371" s="22"/>
-      <c r="E371" s="22"/>
+      <c r="A371" s="28"/>
+      <c r="B371" s="24" t="s">
+        <v>480</v>
+      </c>
+      <c r="C371" s="25"/>
+      <c r="D371" s="25"/>
+      <c r="E371" s="25"/>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B372" s="19"/>
-      <c r="C372" s="20"/>
-      <c r="D372" s="20"/>
+      <c r="B372" s="22"/>
+      <c r="C372" s="23"/>
+      <c r="D372" s="23"/>
       <c r="E372" s="11"/>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="2"/>
-      <c r="B373" s="20" t="s">
-        <v>478</v>
-      </c>
-      <c r="C373" s="20"/>
-      <c r="D373" s="20"/>
+      <c r="B373" s="23" t="s">
+        <v>481</v>
+      </c>
+      <c r="C373" s="23"/>
+      <c r="D373" s="23"/>
       <c r="E373" s="11"/>
     </row>
-    <row r="374" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="2"/>
-      <c r="B374" s="20" t="s">
-        <v>479</v>
-      </c>
-      <c r="C374" s="20" t="s">
-        <v>480</v>
-      </c>
-      <c r="D374" s="20" t="s">
-        <v>481</v>
+      <c r="B374" s="23" t="s">
+        <v>482</v>
+      </c>
+      <c r="C374" s="23" t="s">
+        <v>483</v>
+      </c>
+      <c r="D374" s="23" t="s">
+        <v>484</v>
       </c>
       <c r="E374" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="2"/>
-      <c r="B375" s="20" t="s">
-        <v>482</v>
-      </c>
-      <c r="C375" s="20"/>
-      <c r="D375" s="20"/>
+      <c r="B375" s="23" t="s">
+        <v>485</v>
+      </c>
+      <c r="C375" s="23"/>
+      <c r="D375" s="23"/>
       <c r="E375" s="11"/>
     </row>
     <row r="376" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="2"/>
-      <c r="B376" s="20" t="s">
-        <v>483</v>
-      </c>
-      <c r="C376" s="20"/>
-      <c r="D376" s="20"/>
+      <c r="B376" s="23" t="s">
+        <v>486</v>
+      </c>
+      <c r="C376" s="23"/>
+      <c r="D376" s="23"/>
       <c r="E376" s="11"/>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="2"/>
-      <c r="B377" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="C377" s="20"/>
-      <c r="D377" s="20"/>
+      <c r="B377" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="C377" s="23"/>
+      <c r="D377" s="23"/>
       <c r="E377" s="11"/>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="2"/>
-      <c r="B378" s="20" t="s">
-        <v>484</v>
-      </c>
-      <c r="C378" s="20" t="s">
-        <v>464</v>
-      </c>
-      <c r="D378" s="20"/>
+      <c r="B378" s="23" t="s">
+        <v>487</v>
+      </c>
+      <c r="C378" s="23" t="s">
+        <v>467</v>
+      </c>
+      <c r="D378" s="23"/>
       <c r="E378" s="11"/>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="2"/>
-      <c r="B379" s="20" t="s">
-        <v>485</v>
-      </c>
-      <c r="C379" s="20" t="s">
-        <v>467</v>
-      </c>
-      <c r="D379" s="20"/>
+      <c r="B379" s="23" t="s">
+        <v>488</v>
+      </c>
+      <c r="C379" s="23" t="s">
+        <v>470</v>
+      </c>
+      <c r="D379" s="23"/>
       <c r="E379" s="11"/>
     </row>
     <row r="380" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2"/>
-      <c r="B380" s="20" t="s">
-        <v>486</v>
-      </c>
-      <c r="C380" s="20" t="s">
-        <v>407</v>
-      </c>
-      <c r="D380" s="20"/>
+      <c r="B380" s="23" t="s">
+        <v>489</v>
+      </c>
+      <c r="C380" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="D380" s="23"/>
       <c r="E380" s="11"/>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="2"/>
-      <c r="B381" s="20" t="s">
-        <v>487</v>
-      </c>
-      <c r="C381" s="20" t="s">
-        <v>471</v>
-      </c>
-      <c r="D381" s="20"/>
+      <c r="B381" s="23" t="s">
+        <v>490</v>
+      </c>
+      <c r="C381" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="D381" s="23"/>
       <c r="E381" s="11"/>
     </row>
     <row r="382" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="2"/>
-      <c r="B382" s="20" t="s">
-        <v>488</v>
-      </c>
-      <c r="C382" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D382" s="20" t="s">
-        <v>75</v>
+      <c r="B382" s="23" t="s">
+        <v>491</v>
+      </c>
+      <c r="C382" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D382" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="E382" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="2"/>
-      <c r="B383" s="20" t="s">
-        <v>489</v>
-      </c>
-      <c r="C383" s="20" t="s">
-        <v>490</v>
-      </c>
-      <c r="D383" s="20" t="s">
-        <v>491</v>
+      <c r="B383" s="23" t="s">
+        <v>492</v>
+      </c>
+      <c r="C383" s="23" t="s">
+        <v>493</v>
+      </c>
+      <c r="D383" s="23" t="s">
+        <v>494</v>
       </c>
       <c r="E383" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="2"/>
-      <c r="B384" s="20"/>
-      <c r="C384" s="20"/>
-      <c r="D384" s="20"/>
+      <c r="B384" s="23"/>
+      <c r="C384" s="23"/>
+      <c r="D384" s="23"/>
       <c r="E384" s="11"/>
     </row>
     <row r="385" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="6"/>
-      <c r="B385" s="21" t="s">
-        <v>492</v>
-      </c>
-      <c r="C385" s="22"/>
-      <c r="D385" s="22"/>
+      <c r="B385" s="24" t="s">
+        <v>495</v>
+      </c>
+      <c r="C385" s="25"/>
+      <c r="D385" s="25"/>
       <c r="E385" s="8"/>
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B386" s="19"/>
-      <c r="C386" s="20"/>
-      <c r="D386" s="20"/>
+      <c r="B386" s="22"/>
+      <c r="C386" s="23"/>
+      <c r="D386" s="23"/>
       <c r="E386" s="11"/>
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="2"/>
-      <c r="B387" s="20" t="s">
-        <v>493</v>
-      </c>
-      <c r="C387" s="20"/>
-      <c r="D387" s="20"/>
+      <c r="B387" s="23" t="s">
+        <v>496</v>
+      </c>
+      <c r="C387" s="23"/>
+      <c r="D387" s="23"/>
       <c r="E387" s="11"/>
     </row>
-    <row r="388" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="2"/>
-      <c r="B388" s="20" t="s">
-        <v>494</v>
-      </c>
-      <c r="C388" s="20" t="s">
-        <v>480</v>
-      </c>
-      <c r="D388" s="20" t="s">
-        <v>481</v>
+      <c r="B388" s="23" t="s">
+        <v>497</v>
+      </c>
+      <c r="C388" s="23" t="s">
+        <v>483</v>
+      </c>
+      <c r="D388" s="23" t="s">
+        <v>484</v>
       </c>
       <c r="E388" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="2"/>
-      <c r="B389" s="20" t="s">
-        <v>495</v>
-      </c>
-      <c r="C389" s="20"/>
-      <c r="D389" s="20"/>
+      <c r="B389" s="23" t="s">
+        <v>498</v>
+      </c>
+      <c r="C389" s="23"/>
+      <c r="D389" s="23"/>
       <c r="E389" s="11"/>
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="2"/>
-      <c r="B390" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="C390" s="20"/>
-      <c r="D390" s="20"/>
+      <c r="B390" s="23" t="s">
+        <v>356</v>
+      </c>
+      <c r="C390" s="23"/>
+      <c r="D390" s="23"/>
       <c r="E390" s="11"/>
     </row>
     <row r="391" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="2"/>
-      <c r="B391" s="20" t="s">
-        <v>496</v>
-      </c>
-      <c r="C391" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D391" s="20"/>
+      <c r="B391" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="C391" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D391" s="23"/>
       <c r="E391" s="11"/>
     </row>
     <row r="392" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="2"/>
-      <c r="B392" s="20" t="s">
-        <v>497</v>
-      </c>
-      <c r="C392" s="20" t="s">
-        <v>498</v>
-      </c>
-      <c r="D392" s="20" t="s">
-        <v>499</v>
+      <c r="B392" s="23" t="s">
+        <v>500</v>
+      </c>
+      <c r="C392" s="23" t="s">
+        <v>501</v>
+      </c>
+      <c r="D392" s="23" t="s">
+        <v>502</v>
       </c>
       <c r="E392" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A393" s="27"/>
-      <c r="B393" s="20"/>
-      <c r="C393" s="20"/>
-      <c r="D393" s="20"/>
+      <c r="A393" s="29"/>
+      <c r="B393" s="23"/>
+      <c r="C393" s="23"/>
+      <c r="D393" s="23"/>
       <c r="E393" s="11"/>
     </row>
     <row r="394" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A394" s="28"/>
-      <c r="B394" s="29" t="s">
-        <v>500</v>
-      </c>
-      <c r="C394" s="30"/>
-      <c r="D394" s="30"/>
-      <c r="E394" s="31"/>
+      <c r="A394" s="30"/>
+      <c r="B394" s="31" t="s">
+        <v>503</v>
+      </c>
+      <c r="C394" s="32"/>
+      <c r="D394" s="32"/>
+      <c r="E394" s="33"/>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B395" s="19"/>
-      <c r="C395" s="20"/>
-      <c r="D395" s="20"/>
+      <c r="B395" s="22"/>
+      <c r="C395" s="23"/>
+      <c r="D395" s="23"/>
       <c r="E395" s="11"/>
     </row>
     <row r="396" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="2"/>
-      <c r="B396" s="20" t="s">
-        <v>501</v>
-      </c>
-      <c r="C396" s="20"/>
-      <c r="D396" s="20"/>
+      <c r="B396" s="23" t="s">
+        <v>504</v>
+      </c>
+      <c r="C396" s="23"/>
+      <c r="D396" s="23"/>
       <c r="E396" s="11"/>
     </row>
     <row r="397" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="2"/>
-      <c r="B397" s="20" t="s">
-        <v>502</v>
-      </c>
-      <c r="C397" s="20"/>
-      <c r="D397" s="20"/>
+      <c r="B397" s="23" t="s">
+        <v>505</v>
+      </c>
+      <c r="C397" s="23"/>
+      <c r="D397" s="23"/>
       <c r="E397" s="11"/>
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="2"/>
-      <c r="B398" s="20" t="s">
-        <v>457</v>
-      </c>
-      <c r="C398" s="20" t="s">
-        <v>458</v>
-      </c>
-      <c r="D398" s="20"/>
+      <c r="B398" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="C398" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="D398" s="23"/>
       <c r="E398" s="11"/>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="2"/>
-      <c r="B399" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="C399" s="20"/>
-      <c r="D399" s="20"/>
+      <c r="B399" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="C399" s="23"/>
+      <c r="D399" s="23"/>
       <c r="E399" s="11"/>
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="2"/>
-      <c r="B400" s="20" t="s">
-        <v>503</v>
-      </c>
-      <c r="C400" s="20"/>
-      <c r="D400" s="20"/>
+      <c r="B400" s="23" t="s">
+        <v>506</v>
+      </c>
+      <c r="C400" s="23"/>
+      <c r="D400" s="23"/>
       <c r="E400" s="11"/>
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="2"/>
-      <c r="B401" s="20" t="s">
-        <v>504</v>
-      </c>
-      <c r="C401" s="20"/>
-      <c r="D401" s="20"/>
+      <c r="B401" s="23" t="s">
+        <v>507</v>
+      </c>
+      <c r="C401" s="23"/>
+      <c r="D401" s="23"/>
       <c r="E401" s="11"/>
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2"/>
-      <c r="B402" s="20" t="s">
-        <v>505</v>
-      </c>
-      <c r="C402" s="20"/>
-      <c r="D402" s="20"/>
+      <c r="B402" s="23" t="s">
+        <v>508</v>
+      </c>
+      <c r="C402" s="23"/>
+      <c r="D402" s="23"/>
       <c r="E402" s="11"/>
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="2"/>
-      <c r="B403" s="20" t="s">
-        <v>506</v>
-      </c>
-      <c r="C403" s="20"/>
-      <c r="D403" s="20"/>
+      <c r="B403" s="23" t="s">
+        <v>509</v>
+      </c>
+      <c r="C403" s="23"/>
+      <c r="D403" s="23"/>
       <c r="E403" s="11"/>
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="2"/>
-      <c r="B404" s="20" t="s">
-        <v>507</v>
-      </c>
-      <c r="C404" s="20"/>
-      <c r="D404" s="20"/>
+      <c r="B404" s="23" t="s">
+        <v>510</v>
+      </c>
+      <c r="C404" s="23"/>
+      <c r="D404" s="23"/>
       <c r="E404" s="11"/>
     </row>
     <row r="405" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="2"/>
-      <c r="B405" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="C405" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="D405" s="20"/>
+      <c r="B405" s="23" t="s">
+        <v>511</v>
+      </c>
+      <c r="C405" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D405" s="23"/>
       <c r="E405" s="11"/>
     </row>
     <row r="406" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="2"/>
-      <c r="B406" s="20" t="s">
-        <v>509</v>
-      </c>
-      <c r="C406" s="20" t="s">
-        <v>510</v>
-      </c>
-      <c r="D406" s="20" t="s">
-        <v>511</v>
+      <c r="B406" s="23" t="s">
+        <v>512</v>
+      </c>
+      <c r="C406" s="23" t="s">
+        <v>513</v>
+      </c>
+      <c r="D406" s="23" t="s">
+        <v>514</v>
       </c>
       <c r="E406" s="11" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="2"/>
-      <c r="B407" s="20" t="s">
-        <v>513</v>
-      </c>
-      <c r="C407" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D407" s="20" t="s">
-        <v>75</v>
+      <c r="B407" s="23" t="s">
+        <v>516</v>
+      </c>
+      <c r="C407" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D407" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="E407" s="11" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="2"/>
-      <c r="B408" s="20"/>
-      <c r="C408" s="20"/>
-      <c r="D408" s="20"/>
+      <c r="B408" s="23"/>
+      <c r="C408" s="23"/>
+      <c r="D408" s="23"/>
       <c r="E408" s="11"/>
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B409" s="20" t="s">
-        <v>514</v>
-      </c>
-      <c r="C409" s="20"/>
-      <c r="D409" s="20"/>
+        <v>247</v>
+      </c>
+      <c r="B409" s="23" t="s">
+        <v>517</v>
+      </c>
+      <c r="C409" s="23"/>
+      <c r="D409" s="23"/>
       <c r="E409" s="11"/>
     </row>
     <row r="410" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="2"/>
-      <c r="B410" s="20" t="s">
-        <v>515</v>
-      </c>
-      <c r="C410" s="20"/>
-      <c r="D410" s="20"/>
+      <c r="B410" s="23" t="s">
+        <v>518</v>
+      </c>
+      <c r="C410" s="23"/>
+      <c r="D410" s="23"/>
       <c r="E410" s="11"/>
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="2"/>
-      <c r="B411" s="20" t="s">
-        <v>516</v>
-      </c>
-      <c r="C411" s="20"/>
-      <c r="D411" s="20"/>
+      <c r="B411" s="23" t="s">
+        <v>519</v>
+      </c>
+      <c r="C411" s="23"/>
+      <c r="D411" s="23"/>
       <c r="E411" s="11"/>
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="2"/>
-      <c r="B412" s="20" t="s">
-        <v>517</v>
-      </c>
-      <c r="C412" s="20"/>
-      <c r="D412" s="20"/>
+      <c r="B412" s="23" t="s">
+        <v>520</v>
+      </c>
+      <c r="C412" s="23"/>
+      <c r="D412" s="23"/>
       <c r="E412" s="11"/>
     </row>
     <row r="413" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="2"/>
-      <c r="B413" s="20" t="s">
-        <v>518</v>
-      </c>
-      <c r="C413" s="20"/>
-      <c r="D413" s="20"/>
+      <c r="B413" s="23" t="s">
+        <v>521</v>
+      </c>
+      <c r="C413" s="23"/>
+      <c r="D413" s="23"/>
       <c r="E413" s="11"/>
     </row>
     <row r="414" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="2"/>
-      <c r="B414" s="20" t="s">
-        <v>519</v>
-      </c>
-      <c r="C414" s="20" t="s">
-        <v>520</v>
-      </c>
-      <c r="D414" s="20" t="s">
-        <v>521</v>
+      <c r="B414" s="23" t="s">
+        <v>522</v>
+      </c>
+      <c r="C414" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="D414" s="23" t="s">
+        <v>524</v>
       </c>
       <c r="E414" s="11" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="2"/>
-      <c r="B415" s="20" t="s">
-        <v>522</v>
-      </c>
-      <c r="C415" s="20"/>
-      <c r="D415" s="20"/>
+      <c r="B415" s="23" t="s">
+        <v>525</v>
+      </c>
+      <c r="C415" s="23"/>
+      <c r="D415" s="23"/>
       <c r="E415" s="11"/>
     </row>
     <row r="416" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="2"/>
-      <c r="B416" s="20" t="s">
-        <v>523</v>
-      </c>
-      <c r="C416" s="20"/>
-      <c r="D416" s="20"/>
+      <c r="B416" s="23" t="s">
+        <v>526</v>
+      </c>
+      <c r="C416" s="23"/>
+      <c r="D416" s="23"/>
       <c r="E416" s="11"/>
     </row>
     <row r="417" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="2"/>
-      <c r="B417" s="20" t="s">
-        <v>524</v>
-      </c>
-      <c r="C417" s="20"/>
-      <c r="D417" s="20"/>
+      <c r="B417" s="23" t="s">
+        <v>527</v>
+      </c>
+      <c r="C417" s="23"/>
+      <c r="D417" s="23"/>
       <c r="E417" s="11"/>
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="2"/>
-      <c r="B418" s="20" t="s">
-        <v>525</v>
-      </c>
-      <c r="C418" s="20" t="s">
-        <v>526</v>
-      </c>
-      <c r="D418" s="20" t="s">
-        <v>527</v>
+      <c r="B418" s="23" t="s">
+        <v>528</v>
+      </c>
+      <c r="C418" s="23" t="s">
+        <v>529</v>
+      </c>
+      <c r="D418" s="23" t="s">
+        <v>530</v>
       </c>
       <c r="E418" s="11" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="2"/>
-      <c r="B419" s="20" t="s">
-        <v>528</v>
-      </c>
-      <c r="C419" s="20"/>
-      <c r="D419" s="20"/>
+      <c r="B419" s="23" t="s">
+        <v>531</v>
+      </c>
+      <c r="C419" s="23"/>
+      <c r="D419" s="23"/>
       <c r="E419" s="11"/>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="2"/>
-      <c r="B420" s="20"/>
-      <c r="C420" s="20"/>
-      <c r="D420" s="20"/>
+      <c r="B420" s="23"/>
+      <c r="C420" s="23"/>
+      <c r="D420" s="23"/>
       <c r="E420" s="11"/>
     </row>
     <row r="421" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="6"/>
-      <c r="B421" s="21" t="s">
-        <v>529</v>
-      </c>
-      <c r="C421" s="22"/>
-      <c r="D421" s="22"/>
+      <c r="B421" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="C421" s="25"/>
+      <c r="D421" s="25"/>
       <c r="E421" s="8"/>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B422" s="19"/>
-      <c r="C422" s="20"/>
-      <c r="D422" s="20"/>
+      <c r="B422" s="22"/>
+      <c r="C422" s="23"/>
+      <c r="D422" s="23"/>
       <c r="E422" s="11"/>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2"/>
-      <c r="B423" s="20" t="s">
-        <v>530</v>
-      </c>
-      <c r="C423" s="20"/>
-      <c r="D423" s="20"/>
+      <c r="B423" s="23" t="s">
+        <v>533</v>
+      </c>
+      <c r="C423" s="23"/>
+      <c r="D423" s="23"/>
       <c r="E423" s="11"/>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2"/>
-      <c r="B424" s="20" t="s">
-        <v>531</v>
-      </c>
-      <c r="C424" s="20" t="s">
-        <v>532</v>
-      </c>
-      <c r="D424" s="20" t="s">
-        <v>533</v>
+      <c r="B424" s="23" t="s">
+        <v>534</v>
+      </c>
+      <c r="C424" s="23" t="s">
+        <v>535</v>
+      </c>
+      <c r="D424" s="23" t="s">
+        <v>536</v>
       </c>
       <c r="E424" s="11" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2"/>
-      <c r="B425" s="20" t="s">
-        <v>534</v>
-      </c>
-      <c r="C425" s="20"/>
-      <c r="D425" s="20"/>
+      <c r="B425" s="23" t="s">
+        <v>537</v>
+      </c>
+      <c r="C425" s="23"/>
+      <c r="D425" s="23"/>
       <c r="E425" s="11"/>
     </row>
     <row r="426" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2"/>
-      <c r="B426" s="20" t="s">
-        <v>535</v>
-      </c>
-      <c r="C426" s="20"/>
-      <c r="D426" s="20"/>
+      <c r="B426" s="23" t="s">
+        <v>538</v>
+      </c>
+      <c r="C426" s="23"/>
+      <c r="D426" s="23"/>
       <c r="E426" s="11"/>
     </row>
     <row r="427" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2"/>
-      <c r="B427" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="C427" s="20"/>
-      <c r="D427" s="20"/>
+      <c r="B427" s="23" t="s">
+        <v>539</v>
+      </c>
+      <c r="C427" s="23"/>
+      <c r="D427" s="23"/>
       <c r="E427" s="11"/>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2"/>
-      <c r="B428" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="C428" s="20"/>
-      <c r="D428" s="20"/>
+      <c r="B428" s="23" t="s">
+        <v>540</v>
+      </c>
+      <c r="C428" s="23"/>
+      <c r="D428" s="23"/>
       <c r="E428" s="11"/>
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="2"/>
-      <c r="B429" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="C429" s="20"/>
-      <c r="D429" s="20"/>
+      <c r="B429" s="23" t="s">
+        <v>541</v>
+      </c>
+      <c r="C429" s="23"/>
+      <c r="D429" s="23"/>
       <c r="E429" s="11"/>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="2"/>
-      <c r="B430" s="20" t="s">
-        <v>539</v>
-      </c>
-      <c r="C430" s="20"/>
-      <c r="D430" s="20"/>
+      <c r="B430" s="23" t="s">
+        <v>542</v>
+      </c>
+      <c r="C430" s="23"/>
+      <c r="D430" s="23"/>
       <c r="E430" s="11"/>
     </row>
     <row r="431" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="2"/>
-      <c r="B431" s="20" t="s">
-        <v>540</v>
-      </c>
-      <c r="C431" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="D431" s="20"/>
+      <c r="B431" s="23" t="s">
+        <v>543</v>
+      </c>
+      <c r="C431" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D431" s="23"/>
       <c r="E431" s="11"/>
-      <c r="F431" s="15"/>
+      <c r="F431" s="16"/>
       <c r="G431" s="1"/>
     </row>
     <row r="432" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2"/>
-      <c r="B432" s="20" t="s">
-        <v>541</v>
-      </c>
-      <c r="C432" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D432" s="20"/>
+      <c r="B432" s="23" t="s">
+        <v>544</v>
+      </c>
+      <c r="C432" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D432" s="23"/>
       <c r="E432" s="11"/>
     </row>
-    <row r="433" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="2"/>
-      <c r="B433" s="20" t="s">
-        <v>542</v>
-      </c>
-      <c r="C433" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="D433" s="20" t="s">
-        <v>544</v>
+      <c r="B433" s="23" t="s">
+        <v>545</v>
+      </c>
+      <c r="C433" s="23" t="s">
+        <v>546</v>
+      </c>
+      <c r="D433" s="23" t="s">
+        <v>547</v>
       </c>
       <c r="E433" s="11" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="2"/>
-      <c r="B434" s="20"/>
-      <c r="C434" s="20"/>
-      <c r="D434" s="20"/>
+      <c r="B434" s="23"/>
+      <c r="C434" s="23"/>
+      <c r="D434" s="23"/>
       <c r="E434" s="11"/>
     </row>
     <row r="435" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B435" s="20" t="s">
-        <v>545</v>
-      </c>
-      <c r="C435" s="20"/>
-      <c r="D435" s="20"/>
+        <v>247</v>
+      </c>
+      <c r="B435" s="23" t="s">
+        <v>548</v>
+      </c>
+      <c r="C435" s="23"/>
+      <c r="D435" s="23"/>
       <c r="E435" s="11"/>
     </row>
     <row r="436" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2"/>
-      <c r="B436" s="20" t="s">
-        <v>546</v>
-      </c>
-      <c r="C436" s="20"/>
-      <c r="D436" s="20"/>
+      <c r="B436" s="23" t="s">
+        <v>549</v>
+      </c>
+      <c r="C436" s="23"/>
+      <c r="D436" s="23"/>
       <c r="E436" s="11"/>
     </row>
     <row r="437" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2"/>
-      <c r="B437" s="20" t="s">
-        <v>547</v>
-      </c>
-      <c r="C437" s="20" t="s">
-        <v>520</v>
-      </c>
-      <c r="D437" s="20"/>
+      <c r="B437" s="23" t="s">
+        <v>550</v>
+      </c>
+      <c r="C437" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="D437" s="23"/>
       <c r="E437" s="11"/>
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2"/>
-      <c r="B438" s="20" t="s">
-        <v>548</v>
-      </c>
-      <c r="C438" s="20"/>
-      <c r="D438" s="20"/>
+      <c r="B438" s="23" t="s">
+        <v>551</v>
+      </c>
+      <c r="C438" s="23"/>
+      <c r="D438" s="23"/>
       <c r="E438" s="11"/>
     </row>
     <row r="439" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="2"/>
-      <c r="B439" s="20" t="s">
-        <v>549</v>
-      </c>
-      <c r="C439" s="20"/>
-      <c r="D439" s="20"/>
+      <c r="B439" s="23" t="s">
+        <v>552</v>
+      </c>
+      <c r="C439" s="23"/>
+      <c r="D439" s="23"/>
       <c r="E439" s="11"/>
     </row>
     <row r="440" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="2"/>
-      <c r="B440" s="20" t="s">
-        <v>550</v>
-      </c>
-      <c r="C440" s="20"/>
-      <c r="D440" s="20"/>
+      <c r="B440" s="23" t="s">
+        <v>553</v>
+      </c>
+      <c r="C440" s="23"/>
+      <c r="D440" s="23"/>
       <c r="E440" s="11"/>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="2"/>
-      <c r="B441" s="20" t="s">
-        <v>551</v>
-      </c>
-      <c r="C441" s="20" t="s">
-        <v>526</v>
-      </c>
-      <c r="D441" s="20"/>
+      <c r="B441" s="23" t="s">
+        <v>554</v>
+      </c>
+      <c r="C441" s="23" t="s">
+        <v>529</v>
+      </c>
+      <c r="D441" s="23"/>
       <c r="E441" s="11"/>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2"/>
-      <c r="B442" s="20" t="s">
-        <v>552</v>
-      </c>
-      <c r="C442" s="20"/>
-      <c r="D442" s="20"/>
+      <c r="B442" s="23" t="s">
+        <v>555</v>
+      </c>
+      <c r="C442" s="23"/>
+      <c r="D442" s="23"/>
       <c r="E442" s="11"/>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2"/>
-      <c r="B443" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="C443" s="20"/>
-      <c r="D443" s="20"/>
+      <c r="B443" s="23" t="s">
+        <v>556</v>
+      </c>
+      <c r="C443" s="23"/>
+      <c r="D443" s="23"/>
       <c r="E443" s="11"/>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2"/>
-      <c r="B444" s="20" t="s">
-        <v>554</v>
-      </c>
-      <c r="C444" s="20"/>
-      <c r="D444" s="20"/>
+      <c r="B444" s="23" t="s">
+        <v>557</v>
+      </c>
+      <c r="C444" s="23"/>
+      <c r="D444" s="23"/>
       <c r="E444" s="11"/>
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2"/>
-      <c r="B445" s="20" t="s">
-        <v>555</v>
-      </c>
-      <c r="C445" s="20"/>
-      <c r="D445" s="20"/>
+      <c r="B445" s="23" t="s">
+        <v>558</v>
+      </c>
+      <c r="C445" s="23"/>
+      <c r="D445" s="23"/>
       <c r="E445" s="11"/>
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2"/>
-      <c r="B446" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="C446" s="20"/>
-      <c r="D446" s="20"/>
+      <c r="B446" s="23" t="s">
+        <v>559</v>
+      </c>
+      <c r="C446" s="23"/>
+      <c r="D446" s="23"/>
       <c r="E446" s="11"/>
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="2"/>
-      <c r="B447" s="20" t="s">
-        <v>557</v>
-      </c>
-      <c r="C447" s="20"/>
-      <c r="D447" s="20"/>
+      <c r="B447" s="23" t="s">
+        <v>560</v>
+      </c>
+      <c r="C447" s="23"/>
+      <c r="D447" s="23"/>
       <c r="E447" s="11"/>
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="2"/>
-      <c r="B448" s="20" t="s">
-        <v>558</v>
-      </c>
-      <c r="C448" s="20"/>
-      <c r="D448" s="20"/>
+      <c r="B448" s="23" t="s">
+        <v>561</v>
+      </c>
+      <c r="C448" s="23"/>
+      <c r="D448" s="23"/>
       <c r="E448" s="11"/>
     </row>
     <row r="449" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="2"/>
-      <c r="B449" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="C449" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="D449" s="20" t="s">
-        <v>561</v>
+      <c r="B449" s="23" t="s">
+        <v>562</v>
+      </c>
+      <c r="C449" s="23" t="s">
+        <v>563</v>
+      </c>
+      <c r="D449" s="23" t="s">
+        <v>564</v>
       </c>
       <c r="E449" s="11" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="2"/>
-      <c r="B450" s="20" t="s">
-        <v>562</v>
-      </c>
-      <c r="C450" s="20"/>
-      <c r="D450" s="20"/>
+      <c r="B450" s="23" t="s">
+        <v>565</v>
+      </c>
+      <c r="C450" s="23"/>
+      <c r="D450" s="23"/>
       <c r="E450" s="11"/>
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="2"/>
-      <c r="B451" s="20" t="s">
-        <v>563</v>
-      </c>
-      <c r="C451" s="20"/>
-      <c r="D451" s="20"/>
+      <c r="B451" s="23" t="s">
+        <v>566</v>
+      </c>
+      <c r="C451" s="23"/>
+      <c r="D451" s="23"/>
       <c r="E451" s="11"/>
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="2"/>
-      <c r="B452" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="C452" s="20"/>
-      <c r="D452" s="20"/>
+      <c r="B452" s="23" t="s">
+        <v>567</v>
+      </c>
+      <c r="C452" s="23"/>
+      <c r="D452" s="23"/>
       <c r="E452" s="11"/>
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="2"/>
-      <c r="B453" s="20" t="s">
-        <v>565</v>
-      </c>
-      <c r="C453" s="20"/>
-      <c r="D453" s="20"/>
+      <c r="B453" s="23" t="s">
+        <v>568</v>
+      </c>
+      <c r="C453" s="23"/>
+      <c r="D453" s="23"/>
       <c r="E453" s="11"/>
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2"/>
-      <c r="B454" s="20" t="s">
-        <v>566</v>
-      </c>
-      <c r="C454" s="20"/>
-      <c r="D454" s="20"/>
+      <c r="B454" s="23" t="s">
+        <v>569</v>
+      </c>
+      <c r="C454" s="23"/>
+      <c r="D454" s="23"/>
       <c r="E454" s="11"/>
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2"/>
-      <c r="B455" s="20" t="s">
-        <v>567</v>
-      </c>
-      <c r="C455" s="20"/>
-      <c r="D455" s="20"/>
+      <c r="B455" s="23" t="s">
+        <v>570</v>
+      </c>
+      <c r="C455" s="23"/>
+      <c r="D455" s="23"/>
       <c r="E455" s="11"/>
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2"/>
-      <c r="B456" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="C456" s="20"/>
-      <c r="D456" s="20"/>
+      <c r="B456" s="23" t="s">
+        <v>571</v>
+      </c>
+      <c r="C456" s="23"/>
+      <c r="D456" s="23"/>
       <c r="E456" s="11"/>
     </row>
     <row r="457" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2"/>
-      <c r="B457" s="20" t="s">
-        <v>569</v>
-      </c>
-      <c r="C457" s="20"/>
-      <c r="D457" s="32" t="s">
-        <v>570</v>
-      </c>
-      <c r="E457" s="33" t="s">
-        <v>571</v>
-      </c>
-      <c r="F457" s="34" t="s">
+      <c r="B457" s="23" t="s">
         <v>572</v>
       </c>
+      <c r="C457" s="34" t="s">
+        <v>573</v>
+      </c>
+      <c r="D457" s="23" t="s">
+        <v>574</v>
+      </c>
+      <c r="E457" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="F457" s="35"/>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2"/>
-      <c r="B458" s="20" t="s">
-        <v>573</v>
-      </c>
-      <c r="C458" s="20"/>
-      <c r="D458" s="20"/>
+      <c r="B458" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="C458" s="23"/>
+      <c r="D458" s="23"/>
       <c r="E458" s="11"/>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="2"/>
-      <c r="B459" s="20" t="s">
-        <v>574</v>
-      </c>
-      <c r="C459" s="20"/>
-      <c r="D459" s="20"/>
+      <c r="B459" s="23" t="s">
+        <v>577</v>
+      </c>
+      <c r="C459" s="23"/>
+      <c r="D459" s="23"/>
       <c r="E459" s="11"/>
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="2"/>
-      <c r="B460" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="C460" s="20"/>
-      <c r="D460" s="20"/>
+      <c r="B460" s="23" t="s">
+        <v>578</v>
+      </c>
+      <c r="C460" s="23"/>
+      <c r="D460" s="23"/>
       <c r="E460" s="11"/>
     </row>
     <row r="461" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="2"/>
-      <c r="B461" s="20" t="s">
-        <v>576</v>
-      </c>
-      <c r="C461" s="20"/>
-      <c r="D461" s="20"/>
+      <c r="B461" s="23" t="s">
+        <v>579</v>
+      </c>
+      <c r="C461" s="23"/>
+      <c r="D461" s="23"/>
       <c r="E461" s="11"/>
     </row>
     <row r="462" customFormat="false" ht="67.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="2"/>
-      <c r="B462" s="20" t="s">
-        <v>577</v>
-      </c>
-      <c r="C462" s="20" t="s">
-        <v>578</v>
-      </c>
-      <c r="D462" s="20" t="s">
-        <v>579</v>
+      <c r="B462" s="23" t="s">
+        <v>580</v>
+      </c>
+      <c r="C462" s="23" t="s">
+        <v>581</v>
+      </c>
+      <c r="D462" s="23" t="s">
+        <v>582</v>
       </c>
       <c r="E462" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="F462" s="20"/>
+        <v>184</v>
+      </c>
+      <c r="F462" s="23"/>
     </row>
     <row r="463" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2"/>
-      <c r="B463" s="20" t="s">
-        <v>580</v>
-      </c>
-      <c r="C463" s="20"/>
-      <c r="D463" s="20"/>
+      <c r="B463" s="23" t="s">
+        <v>583</v>
+      </c>
+      <c r="C463" s="23"/>
+      <c r="D463" s="23"/>
       <c r="E463" s="11"/>
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2"/>
-      <c r="B464" s="20" t="s">
-        <v>581</v>
-      </c>
-      <c r="C464" s="20"/>
-      <c r="D464" s="20"/>
+      <c r="B464" s="23" t="s">
+        <v>584</v>
+      </c>
+      <c r="C464" s="23"/>
+      <c r="D464" s="23"/>
       <c r="E464" s="11"/>
     </row>
     <row r="465" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2"/>
-      <c r="B465" s="20" t="s">
-        <v>582</v>
-      </c>
-      <c r="C465" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="D465" s="20"/>
+      <c r="B465" s="23" t="s">
+        <v>585</v>
+      </c>
+      <c r="C465" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="D465" s="23"/>
       <c r="E465" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2"/>
-      <c r="B466" s="20" t="s">
-        <v>583</v>
-      </c>
-      <c r="C466" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="D466" s="20" t="s">
-        <v>584</v>
+      <c r="B466" s="23" t="s">
+        <v>586</v>
+      </c>
+      <c r="C466" s="23" t="s">
+        <v>546</v>
+      </c>
+      <c r="D466" s="23" t="s">
+        <v>587</v>
       </c>
       <c r="E466" s="11" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2"/>
-      <c r="B467" s="20" t="s">
-        <v>585</v>
-      </c>
-      <c r="C467" s="20"/>
-      <c r="D467" s="20"/>
+      <c r="B467" s="23" t="s">
+        <v>588</v>
+      </c>
+      <c r="C467" s="23"/>
+      <c r="D467" s="23"/>
       <c r="E467" s="11"/>
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2"/>
-      <c r="B468" s="20" t="s">
-        <v>586</v>
-      </c>
-      <c r="C468" s="20"/>
-      <c r="D468" s="20"/>
+      <c r="B468" s="23" t="s">
+        <v>589</v>
+      </c>
+      <c r="C468" s="23"/>
+      <c r="D468" s="23"/>
       <c r="E468" s="11"/>
     </row>
     <row r="469" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="2"/>
-      <c r="B469" s="20" t="s">
-        <v>587</v>
-      </c>
-      <c r="C469" s="20" t="s">
-        <v>588</v>
-      </c>
-      <c r="D469" s="32" t="s">
-        <v>589</v>
-      </c>
-      <c r="E469" s="33" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="470" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B469" s="23" t="s">
+        <v>590</v>
+      </c>
+      <c r="C469" s="23" t="s">
+        <v>591</v>
+      </c>
+      <c r="D469" s="23" t="s">
+        <v>592</v>
+      </c>
+      <c r="E469" s="11" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="2"/>
-      <c r="B470" s="20" t="s">
-        <v>590</v>
-      </c>
-      <c r="C470" s="20" t="s">
-        <v>591</v>
-      </c>
-      <c r="D470" s="20" t="s">
-        <v>592</v>
-      </c>
-      <c r="E470" s="11" t="s">
-        <v>512</v>
-      </c>
+      <c r="B470" s="23" t="s">
+        <v>593</v>
+      </c>
+      <c r="C470" s="23"/>
+      <c r="D470" s="23"/>
+      <c r="E470" s="11"/>
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="2"/>
-      <c r="B471" s="20" t="s">
-        <v>593</v>
-      </c>
-      <c r="C471" s="20"/>
-      <c r="D471" s="20"/>
+      <c r="B471" s="23" t="s">
+        <v>594</v>
+      </c>
+      <c r="C471" s="23"/>
+      <c r="D471" s="23"/>
       <c r="E471" s="11"/>
     </row>
-    <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="472" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="2"/>
-      <c r="B472" s="20" t="s">
-        <v>594</v>
-      </c>
-      <c r="C472" s="20"/>
-      <c r="D472" s="20"/>
-      <c r="E472" s="11"/>
-    </row>
-    <row r="473" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B472" s="23" t="s">
+        <v>595</v>
+      </c>
+      <c r="C472" s="23" t="s">
+        <v>563</v>
+      </c>
+      <c r="D472" s="23" t="s">
+        <v>596</v>
+      </c>
+      <c r="E472" s="11" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2"/>
-      <c r="B473" s="20" t="s">
-        <v>595</v>
-      </c>
-      <c r="C473" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="D473" s="20" t="s">
-        <v>596</v>
-      </c>
-      <c r="E473" s="11" t="s">
-        <v>512</v>
-      </c>
+      <c r="B473" s="23" t="s">
+        <v>597</v>
+      </c>
+      <c r="C473" s="23"/>
+      <c r="D473" s="23"/>
+      <c r="E473" s="11"/>
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="2"/>
-      <c r="B474" s="20" t="s">
-        <v>597</v>
-      </c>
-      <c r="C474" s="20"/>
-      <c r="D474" s="20"/>
+      <c r="B474" s="23"/>
+      <c r="C474" s="23"/>
+      <c r="D474" s="23"/>
       <c r="E474" s="11"/>
     </row>
-    <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A475" s="2"/>
-      <c r="B475" s="20"/>
-      <c r="C475" s="20"/>
-      <c r="D475" s="20"/>
+    <row r="475" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A475" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B475" s="23" t="s">
+        <v>599</v>
+      </c>
+      <c r="C475" s="23"/>
+      <c r="D475" s="23"/>
       <c r="E475" s="11"/>
     </row>
-    <row r="476" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A476" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="B476" s="20" t="s">
-        <v>599</v>
-      </c>
-      <c r="C476" s="20"/>
-      <c r="D476" s="20"/>
-      <c r="E476" s="11"/>
-    </row>
-    <row r="477" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="476" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A476" s="2"/>
+      <c r="B476" s="23" t="s">
+        <v>600</v>
+      </c>
+      <c r="C476" s="23" t="s">
+        <v>563</v>
+      </c>
+      <c r="D476" s="23" t="s">
+        <v>596</v>
+      </c>
+      <c r="E476" s="11" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2"/>
-      <c r="B477" s="20" t="s">
-        <v>600</v>
-      </c>
-      <c r="C477" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="D477" s="20" t="s">
-        <v>596</v>
-      </c>
-      <c r="E477" s="11" t="s">
-        <v>512</v>
-      </c>
+      <c r="B477" s="23" t="s">
+        <v>601</v>
+      </c>
+      <c r="C477" s="23"/>
+      <c r="D477" s="23"/>
+      <c r="E477" s="11"/>
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2"/>
-      <c r="B478" s="20" t="s">
-        <v>601</v>
-      </c>
-      <c r="C478" s="20"/>
-      <c r="D478" s="20"/>
+      <c r="B478" s="23"/>
+      <c r="C478" s="23"/>
+      <c r="D478" s="23"/>
       <c r="E478" s="11"/>
     </row>
-    <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A479" s="2"/>
-      <c r="B479" s="20"/>
-      <c r="C479" s="20"/>
-      <c r="D479" s="20"/>
-      <c r="E479" s="11"/>
-    </row>
-    <row r="480" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A480" s="6"/>
-      <c r="B480" s="21" t="s">
+    <row r="479" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A479" s="6"/>
+      <c r="B479" s="24" t="s">
         <v>602</v>
       </c>
-      <c r="C480" s="22"/>
-      <c r="D480" s="22"/>
-      <c r="E480" s="8"/>
-    </row>
-    <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A481" s="2" t="s">
+      <c r="C479" s="25"/>
+      <c r="D479" s="25"/>
+      <c r="E479" s="8"/>
+    </row>
+    <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A480" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C481" s="20"/>
-      <c r="D481" s="20"/>
+      <c r="C480" s="23"/>
+      <c r="D480" s="23"/>
+      <c r="E480" s="11"/>
+    </row>
+    <row r="481" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A481" s="2"/>
+      <c r="B481" s="23" t="s">
+        <v>603</v>
+      </c>
+      <c r="C481" s="23"/>
+      <c r="D481" s="23"/>
       <c r="E481" s="11"/>
     </row>
-    <row r="482" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2"/>
-      <c r="B482" s="20" t="s">
-        <v>603</v>
-      </c>
-      <c r="C482" s="20"/>
-      <c r="D482" s="20"/>
+      <c r="B482" s="23" t="s">
+        <v>604</v>
+      </c>
+      <c r="C482" s="23"/>
+      <c r="D482" s="23"/>
       <c r="E482" s="11"/>
     </row>
-    <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="2"/>
-      <c r="B483" s="20" t="s">
-        <v>604</v>
-      </c>
-      <c r="C483" s="20"/>
-      <c r="D483" s="20"/>
+      <c r="B483" s="23" t="s">
+        <v>605</v>
+      </c>
+      <c r="C483" s="23"/>
+      <c r="D483" s="23"/>
       <c r="E483" s="11"/>
     </row>
-    <row r="484" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2"/>
-      <c r="B484" s="20" t="s">
-        <v>605</v>
-      </c>
-      <c r="C484" s="20"/>
-      <c r="D484" s="20"/>
+      <c r="B484" s="23" t="s">
+        <v>356</v>
+      </c>
+      <c r="C484" s="23"/>
+      <c r="D484" s="23"/>
       <c r="E484" s="11"/>
     </row>
-    <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2"/>
-      <c r="B485" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="C485" s="20"/>
-      <c r="D485" s="20"/>
+      <c r="B485" s="23" t="s">
+        <v>606</v>
+      </c>
+      <c r="C485" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D485" s="23"/>
       <c r="E485" s="11"/>
     </row>
     <row r="486" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2"/>
-      <c r="B486" s="20" t="s">
-        <v>606</v>
-      </c>
-      <c r="C486" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D486" s="20"/>
-      <c r="E486" s="11"/>
-    </row>
-    <row r="487" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B486" s="23" t="s">
+        <v>607</v>
+      </c>
+      <c r="C486" s="23" t="s">
+        <v>563</v>
+      </c>
+      <c r="D486" s="23" t="s">
+        <v>608</v>
+      </c>
+      <c r="E486" s="11" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="2"/>
-      <c r="B487" s="20" t="s">
-        <v>607</v>
-      </c>
-      <c r="C487" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="D487" s="20" t="s">
-        <v>608</v>
-      </c>
-      <c r="E487" s="11" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A488" s="2"/>
-      <c r="B488" s="20"/>
-      <c r="C488" s="20"/>
-      <c r="D488" s="20"/>
-      <c r="E488" s="11"/>
-    </row>
-    <row r="489" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A489" s="6"/>
-      <c r="B489" s="21" t="s">
+      <c r="B487" s="23"/>
+      <c r="C487" s="23"/>
+      <c r="D487" s="23"/>
+      <c r="E487" s="11"/>
+    </row>
+    <row r="488" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A488" s="6"/>
+      <c r="B488" s="24" t="s">
         <v>609</v>
       </c>
-      <c r="C489" s="22"/>
-      <c r="D489" s="22"/>
-      <c r="E489" s="8"/>
-    </row>
-    <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A490" s="2" t="s">
+      <c r="C488" s="25"/>
+      <c r="D488" s="25"/>
+      <c r="E488" s="8"/>
+    </row>
+    <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A489" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C490" s="20"/>
-      <c r="D490" s="20"/>
+      <c r="C489" s="23"/>
+      <c r="D489" s="23"/>
+      <c r="E489" s="11"/>
+    </row>
+    <row r="490" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A490" s="2"/>
+      <c r="B490" s="23" t="s">
+        <v>610</v>
+      </c>
+      <c r="C490" s="23"/>
+      <c r="D490" s="23"/>
       <c r="E490" s="11"/>
     </row>
-    <row r="491" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="2"/>
-      <c r="B491" s="20" t="s">
-        <v>610</v>
-      </c>
-      <c r="C491" s="20"/>
-      <c r="D491" s="20"/>
+      <c r="B491" s="23" t="s">
+        <v>611</v>
+      </c>
+      <c r="C491" s="23"/>
+      <c r="D491" s="23"/>
       <c r="E491" s="11"/>
     </row>
-    <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2"/>
-      <c r="B492" s="20" t="s">
-        <v>611</v>
-      </c>
-      <c r="C492" s="20"/>
-      <c r="D492" s="20"/>
+      <c r="B492" s="23" t="s">
+        <v>612</v>
+      </c>
+      <c r="C492" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="D492" s="23"/>
       <c r="E492" s="11"/>
     </row>
-    <row r="493" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="493" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2"/>
-      <c r="B493" s="20" t="s">
-        <v>612</v>
-      </c>
-      <c r="C493" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="D493" s="20"/>
+      <c r="B493" s="23" t="s">
+        <v>613</v>
+      </c>
+      <c r="C493" s="23" t="s">
+        <v>614</v>
+      </c>
+      <c r="D493" s="23"/>
       <c r="E493" s="11"/>
     </row>
-    <row r="494" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2"/>
-      <c r="B494" s="20" t="s">
-        <v>613</v>
-      </c>
-      <c r="C494" s="20" t="s">
-        <v>614</v>
-      </c>
-      <c r="D494" s="20"/>
+      <c r="B494" s="23" t="s">
+        <v>615</v>
+      </c>
+      <c r="C494" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="D494" s="23"/>
       <c r="E494" s="11"/>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2"/>
-      <c r="B495" s="20" t="s">
-        <v>615</v>
-      </c>
-      <c r="C495" s="20" t="s">
-        <v>458</v>
-      </c>
-      <c r="D495" s="20"/>
-      <c r="E495" s="11"/>
-    </row>
-    <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B495" s="23" t="s">
+        <v>616</v>
+      </c>
+      <c r="C495" s="23" t="s">
+        <v>617</v>
+      </c>
+      <c r="D495" s="23" t="s">
+        <v>618</v>
+      </c>
+      <c r="E495" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="496" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2"/>
-      <c r="B496" s="20" t="s">
-        <v>616</v>
-      </c>
-      <c r="C496" s="20" t="s">
-        <v>617</v>
-      </c>
-      <c r="D496" s="20" t="s">
-        <v>618</v>
+      <c r="B496" s="23" t="s">
+        <v>619</v>
+      </c>
+      <c r="C496" s="23" t="s">
+        <v>620</v>
+      </c>
+      <c r="D496" s="23" t="s">
+        <v>621</v>
       </c>
       <c r="E496" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="497" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="497" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2"/>
-      <c r="B497" s="20" t="s">
-        <v>619</v>
-      </c>
-      <c r="C497" s="32" t="s">
-        <v>620</v>
-      </c>
-      <c r="D497" s="32" t="s">
-        <v>621</v>
-      </c>
-      <c r="E497" s="11" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="498" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B497" s="23" t="s">
+        <v>622</v>
+      </c>
+      <c r="C497" s="23"/>
+      <c r="D497" s="23"/>
+      <c r="E497" s="11"/>
+    </row>
+    <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="2"/>
-      <c r="B498" s="20" t="s">
-        <v>622</v>
-      </c>
-      <c r="C498" s="20"/>
-      <c r="D498" s="20"/>
+      <c r="B498" s="23"/>
+      <c r="C498" s="23"/>
+      <c r="D498" s="23"/>
       <c r="E498" s="11"/>
     </row>
-    <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A499" s="2"/>
-      <c r="B499" s="20"/>
-      <c r="C499" s="20"/>
-      <c r="D499" s="20"/>
-      <c r="E499" s="11"/>
-    </row>
-    <row r="500" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A500" s="6"/>
-      <c r="B500" s="21" t="s">
+    <row r="499" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A499" s="6"/>
+      <c r="B499" s="24" t="s">
         <v>623</v>
       </c>
-      <c r="C500" s="22"/>
-      <c r="D500" s="22"/>
-      <c r="E500" s="8"/>
-    </row>
-    <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A501" s="2" t="s">
+      <c r="C499" s="25"/>
+      <c r="D499" s="25"/>
+      <c r="E499" s="8"/>
+    </row>
+    <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A500" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B501" s="20"/>
-      <c r="C501" s="20"/>
-      <c r="D501" s="20"/>
+      <c r="B500" s="23"/>
+      <c r="C500" s="23"/>
+      <c r="D500" s="23"/>
+      <c r="E500" s="11"/>
+    </row>
+    <row r="501" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A501" s="2"/>
+      <c r="B501" s="23" t="s">
+        <v>624</v>
+      </c>
+      <c r="C501" s="23"/>
+      <c r="D501" s="23"/>
       <c r="E501" s="11"/>
     </row>
-    <row r="502" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="502" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="2"/>
-      <c r="B502" s="20" t="s">
-        <v>624</v>
-      </c>
-      <c r="C502" s="20"/>
-      <c r="D502" s="20"/>
-      <c r="E502" s="11"/>
+      <c r="B502" s="23" t="s">
+        <v>625</v>
+      </c>
+      <c r="C502" s="23" t="s">
+        <v>535</v>
+      </c>
+      <c r="D502" s="23" t="s">
+        <v>626</v>
+      </c>
+      <c r="E502" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="F502" s="20" t="s">
+        <v>628</v>
+      </c>
     </row>
     <row r="503" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="2"/>
-      <c r="B503" s="20" t="s">
-        <v>625</v>
-      </c>
-      <c r="C503" s="20" t="s">
-        <v>532</v>
-      </c>
-      <c r="D503" s="20" t="s">
-        <v>626</v>
-      </c>
-      <c r="E503" s="11" t="s">
-        <v>627</v>
-      </c>
-      <c r="F503" s="34" t="s">
-        <v>628</v>
-      </c>
+      <c r="B503" s="23" t="s">
+        <v>629</v>
+      </c>
+      <c r="C503" s="23"/>
+      <c r="D503" s="23"/>
+      <c r="E503" s="11"/>
     </row>
     <row r="504" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="2"/>
-      <c r="B504" s="20" t="s">
-        <v>629</v>
-      </c>
-      <c r="C504" s="20"/>
-      <c r="D504" s="20"/>
+      <c r="B504" s="23" t="s">
+        <v>630</v>
+      </c>
+      <c r="C504" s="23"/>
+      <c r="D504" s="23"/>
       <c r="E504" s="11"/>
     </row>
-    <row r="505" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="2"/>
-      <c r="B505" s="20" t="s">
-        <v>630</v>
-      </c>
-      <c r="C505" s="20"/>
-      <c r="D505" s="20"/>
+      <c r="B505" s="23" t="s">
+        <v>631</v>
+      </c>
+      <c r="C505" s="23"/>
+      <c r="D505" s="23"/>
       <c r="E505" s="11"/>
     </row>
-    <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="2"/>
-      <c r="B506" s="20" t="s">
-        <v>631</v>
-      </c>
-      <c r="C506" s="20"/>
-      <c r="D506" s="20"/>
+      <c r="B506" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="C506" s="23" t="s">
+        <v>633</v>
+      </c>
+      <c r="D506" s="23"/>
       <c r="E506" s="11"/>
     </row>
     <row r="507" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="2"/>
-      <c r="B507" s="20" t="s">
-        <v>632</v>
-      </c>
-      <c r="C507" s="20" t="s">
-        <v>633</v>
-      </c>
-      <c r="D507" s="20"/>
-      <c r="E507" s="11"/>
-    </row>
-    <row r="508" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B507" s="23" t="s">
+        <v>634</v>
+      </c>
+      <c r="C507" s="23" t="s">
+        <v>635</v>
+      </c>
+      <c r="D507" s="23" t="s">
+        <v>636</v>
+      </c>
+      <c r="E507" s="11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="2"/>
-      <c r="B508" s="20" t="s">
-        <v>634</v>
-      </c>
-      <c r="C508" s="20" t="s">
-        <v>635</v>
-      </c>
-      <c r="D508" s="20" t="s">
-        <v>636</v>
+      <c r="B508" s="23" t="s">
+        <v>637</v>
+      </c>
+      <c r="C508" s="23" t="s">
+        <v>563</v>
+      </c>
+      <c r="D508" s="23" t="s">
+        <v>596</v>
       </c>
       <c r="E508" s="11" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="509" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="2"/>
-      <c r="B509" s="20" t="s">
-        <v>637</v>
-      </c>
-      <c r="C509" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="D509" s="20" t="s">
-        <v>596</v>
-      </c>
-      <c r="E509" s="11" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="510" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B509" s="23" t="s">
+        <v>638</v>
+      </c>
+      <c r="C509" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D509" s="23"/>
+      <c r="E509" s="11"/>
+    </row>
+    <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="2"/>
-      <c r="B510" s="20" t="s">
-        <v>638</v>
-      </c>
-      <c r="C510" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D510" s="20"/>
+      <c r="B510" s="23"/>
+      <c r="C510" s="23"/>
+      <c r="D510" s="23"/>
       <c r="E510" s="11"/>
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A511" s="2"/>
-      <c r="B511" s="20"/>
-      <c r="C511" s="20"/>
-      <c r="D511" s="20"/>
+      <c r="A511" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B511" s="23" t="s">
+        <v>639</v>
+      </c>
+      <c r="C511" s="23"/>
+      <c r="D511" s="23"/>
       <c r="E511" s="11"/>
     </row>
-    <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A512" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B512" s="20" t="s">
-        <v>639</v>
-      </c>
-      <c r="C512" s="20"/>
-      <c r="D512" s="20"/>
-      <c r="E512" s="11"/>
-    </row>
-    <row r="513" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="512" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A512" s="2"/>
+      <c r="B512" s="23" t="s">
+        <v>640</v>
+      </c>
+      <c r="C512" s="23" t="s">
+        <v>641</v>
+      </c>
+      <c r="D512" s="23" t="s">
+        <v>642</v>
+      </c>
+      <c r="E512" s="11" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2"/>
-      <c r="B513" s="20" t="s">
-        <v>640</v>
-      </c>
-      <c r="C513" s="32" t="s">
-        <v>641</v>
-      </c>
-      <c r="D513" s="20" t="s">
-        <v>642</v>
-      </c>
-      <c r="E513" s="11" t="s">
-        <v>643</v>
-      </c>
+      <c r="B513" s="23" t="s">
+        <v>644</v>
+      </c>
+      <c r="C513" s="23"/>
+      <c r="D513" s="23"/>
+      <c r="E513" s="11"/>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="2"/>
-      <c r="B514" s="20" t="s">
-        <v>644</v>
-      </c>
-      <c r="C514" s="20"/>
-      <c r="D514" s="20"/>
+      <c r="B514" s="23"/>
+      <c r="C514" s="23"/>
+      <c r="D514" s="23"/>
       <c r="E514" s="11"/>
     </row>
-    <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A515" s="2"/>
-      <c r="B515" s="20"/>
-      <c r="C515" s="20"/>
-      <c r="D515" s="20"/>
-      <c r="E515" s="11"/>
-    </row>
-    <row r="516" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A516" s="6"/>
-      <c r="B516" s="21" t="s">
+    <row r="515" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A515" s="6"/>
+      <c r="B515" s="24" t="s">
         <v>645</v>
       </c>
-      <c r="C516" s="22"/>
-      <c r="D516" s="22"/>
-      <c r="E516" s="8"/>
-    </row>
-    <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A517" s="2" t="s">
+      <c r="C515" s="25"/>
+      <c r="D515" s="25"/>
+      <c r="E515" s="8"/>
+    </row>
+    <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A516" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B517" s="20"/>
-      <c r="C517" s="20"/>
-      <c r="D517" s="20"/>
+      <c r="B516" s="23"/>
+      <c r="C516" s="23"/>
+      <c r="D516" s="23"/>
+      <c r="E516" s="11"/>
+    </row>
+    <row r="517" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A517" s="2"/>
+      <c r="B517" s="23" t="s">
+        <v>646</v>
+      </c>
+      <c r="C517" s="23"/>
+      <c r="D517" s="23"/>
       <c r="E517" s="11"/>
     </row>
     <row r="518" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="2"/>
-      <c r="B518" s="20" t="s">
-        <v>646</v>
-      </c>
-      <c r="C518" s="20"/>
-      <c r="D518" s="20"/>
-      <c r="E518" s="11"/>
-    </row>
-    <row r="519" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B518" s="23" t="s">
+        <v>647</v>
+      </c>
+      <c r="C518" s="23" t="s">
+        <v>648</v>
+      </c>
+      <c r="D518" s="23" t="s">
+        <v>649</v>
+      </c>
+      <c r="E518" s="11" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="519" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="2"/>
-      <c r="B519" s="20" t="s">
-        <v>647</v>
-      </c>
-      <c r="C519" s="20" t="s">
-        <v>648</v>
-      </c>
-      <c r="D519" s="20" t="s">
-        <v>649</v>
+      <c r="B519" s="23" t="s">
+        <v>650</v>
+      </c>
+      <c r="C519" s="23"/>
+      <c r="D519" s="23" t="s">
+        <v>651</v>
       </c>
       <c r="E519" s="11" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="2"/>
-      <c r="B520" s="20" t="s">
-        <v>650</v>
-      </c>
-      <c r="C520" s="20"/>
-      <c r="D520" s="20" t="s">
-        <v>651</v>
-      </c>
-      <c r="E520" s="11" t="s">
-        <v>512</v>
-      </c>
+      <c r="B520" s="23" t="s">
+        <v>652</v>
+      </c>
+      <c r="C520" s="23"/>
+      <c r="D520" s="23"/>
+      <c r="E520" s="11"/>
     </row>
     <row r="521" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="2"/>
-      <c r="B521" s="20" t="s">
-        <v>652</v>
-      </c>
-      <c r="C521" s="20"/>
-      <c r="D521" s="20"/>
-      <c r="E521" s="11"/>
-    </row>
-    <row r="522" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B521" s="23" t="s">
+        <v>653</v>
+      </c>
+      <c r="C521" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="D521" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="E521" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F521" s="20" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="2"/>
-      <c r="B522" s="20" t="s">
-        <v>653</v>
-      </c>
-      <c r="C522" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="D522" s="35" t="s">
-        <v>284</v>
-      </c>
-      <c r="E522" s="33" t="s">
-        <v>181</v>
-      </c>
-      <c r="F522" s="34" t="s">
-        <v>654</v>
-      </c>
+      <c r="B522" s="23" t="s">
+        <v>655</v>
+      </c>
+      <c r="C522" s="23"/>
+      <c r="D522" s="23"/>
+      <c r="E522" s="11"/>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="2"/>
-      <c r="B523" s="20" t="s">
-        <v>655</v>
-      </c>
-      <c r="C523" s="20"/>
-      <c r="D523" s="20"/>
+      <c r="B523" s="23" t="s">
+        <v>656</v>
+      </c>
+      <c r="C523" s="23"/>
+      <c r="D523" s="23"/>
       <c r="E523" s="11"/>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="2"/>
-      <c r="B524" s="20" t="s">
-        <v>656</v>
-      </c>
-      <c r="C524" s="20"/>
-      <c r="D524" s="20"/>
+      <c r="B524" s="23" t="s">
+        <v>657</v>
+      </c>
+      <c r="C524" s="23"/>
+      <c r="D524" s="23"/>
       <c r="E524" s="11"/>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2"/>
-      <c r="B525" s="20" t="s">
-        <v>657</v>
-      </c>
-      <c r="C525" s="20"/>
-      <c r="D525" s="20"/>
+      <c r="B525" s="23" t="s">
+        <v>658</v>
+      </c>
+      <c r="C525" s="23"/>
+      <c r="D525" s="23"/>
       <c r="E525" s="11"/>
     </row>
-    <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="526" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2"/>
-      <c r="B526" s="20" t="s">
-        <v>658</v>
-      </c>
-      <c r="C526" s="20"/>
-      <c r="D526" s="20"/>
+      <c r="B526" s="23" t="s">
+        <v>659</v>
+      </c>
+      <c r="C526" s="23"/>
+      <c r="D526" s="23"/>
       <c r="E526" s="11"/>
     </row>
-    <row r="527" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2"/>
-      <c r="B527" s="20" t="s">
-        <v>659</v>
-      </c>
-      <c r="C527" s="20"/>
-      <c r="D527" s="20"/>
+      <c r="B527" s="23" t="s">
+        <v>660</v>
+      </c>
+      <c r="C527" s="23"/>
+      <c r="D527" s="23"/>
       <c r="E527" s="11"/>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="2"/>
-      <c r="B528" s="20" t="s">
-        <v>660</v>
-      </c>
-      <c r="C528" s="20"/>
-      <c r="D528" s="20"/>
+      <c r="B528" s="23" t="s">
+        <v>661</v>
+      </c>
+      <c r="C528" s="23"/>
+      <c r="D528" s="23"/>
       <c r="E528" s="11"/>
     </row>
-    <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="529" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="2"/>
-      <c r="B529" s="20" t="s">
-        <v>661</v>
-      </c>
-      <c r="C529" s="20"/>
-      <c r="D529" s="20"/>
-      <c r="E529" s="11"/>
-    </row>
-    <row r="530" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B529" s="23" t="s">
+        <v>662</v>
+      </c>
+      <c r="C529" s="23" t="s">
+        <v>663</v>
+      </c>
+      <c r="D529" s="23" t="s">
+        <v>664</v>
+      </c>
+      <c r="E529" s="11" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="530" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="2"/>
-      <c r="B530" s="20" t="s">
-        <v>662</v>
-      </c>
-      <c r="C530" s="20" t="s">
-        <v>663</v>
-      </c>
-      <c r="D530" s="20" t="s">
-        <v>664</v>
-      </c>
-      <c r="E530" s="11" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="531" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B530" s="23" t="s">
+        <v>665</v>
+      </c>
+      <c r="C530" s="23" t="s">
+        <v>666</v>
+      </c>
+      <c r="D530" s="23"/>
+      <c r="E530" s="11"/>
+    </row>
+    <row r="531" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="2"/>
-      <c r="B531" s="20" t="s">
-        <v>665</v>
-      </c>
-      <c r="C531" s="20" t="s">
-        <v>666</v>
-      </c>
-      <c r="D531" s="20"/>
+      <c r="B531" s="23" t="s">
+        <v>667</v>
+      </c>
+      <c r="C531" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D531" s="23"/>
       <c r="E531" s="11"/>
     </row>
-    <row r="532" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="2"/>
-      <c r="B532" s="20" t="s">
-        <v>667</v>
-      </c>
-      <c r="C532" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D532" s="20"/>
+      <c r="B532" s="23"/>
+      <c r="C532" s="23"/>
+      <c r="D532" s="23"/>
       <c r="E532" s="11"/>
     </row>
-    <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A533" s="2"/>
-      <c r="B533" s="20"/>
-      <c r="C533" s="20"/>
-      <c r="D533" s="20"/>
+    <row r="533" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A533" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B533" s="23" t="s">
+        <v>668</v>
+      </c>
+      <c r="C533" s="23"/>
+      <c r="D533" s="23"/>
       <c r="E533" s="11"/>
     </row>
     <row r="534" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A534" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B534" s="20" t="s">
-        <v>668</v>
-      </c>
-      <c r="C534" s="20"/>
-      <c r="D534" s="20"/>
+      <c r="A534" s="2"/>
+      <c r="B534" s="23" t="s">
+        <v>669</v>
+      </c>
+      <c r="C534" s="23"/>
+      <c r="D534" s="23"/>
       <c r="E534" s="11"/>
     </row>
     <row r="535" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="2"/>
-      <c r="B535" s="20" t="s">
-        <v>669</v>
-      </c>
-      <c r="C535" s="20"/>
-      <c r="D535" s="20"/>
+      <c r="B535" s="23" t="s">
+        <v>670</v>
+      </c>
+      <c r="C535" s="23"/>
+      <c r="D535" s="23"/>
       <c r="E535" s="11"/>
     </row>
-    <row r="536" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="2"/>
-      <c r="B536" s="20" t="s">
-        <v>670</v>
-      </c>
-      <c r="C536" s="20"/>
-      <c r="D536" s="20"/>
+      <c r="B536" s="23" t="s">
+        <v>671</v>
+      </c>
+      <c r="C536" s="23"/>
+      <c r="D536" s="23"/>
       <c r="E536" s="11"/>
     </row>
-    <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="537" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="2"/>
-      <c r="B537" s="20" t="s">
-        <v>671</v>
-      </c>
-      <c r="C537" s="20"/>
-      <c r="D537" s="20"/>
+      <c r="B537" s="23" t="s">
+        <v>672</v>
+      </c>
+      <c r="C537" s="23" t="s">
+        <v>666</v>
+      </c>
+      <c r="D537" s="23"/>
       <c r="E537" s="11"/>
     </row>
-    <row r="538" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="2"/>
-      <c r="B538" s="20" t="s">
-        <v>672</v>
-      </c>
-      <c r="C538" s="32" t="s">
-        <v>666</v>
-      </c>
-      <c r="D538" s="20"/>
+      <c r="B538" s="23" t="s">
+        <v>673</v>
+      </c>
+      <c r="C538" s="23"/>
+      <c r="D538" s="23"/>
       <c r="E538" s="11"/>
     </row>
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="2"/>
-      <c r="B539" s="20" t="s">
-        <v>673</v>
-      </c>
-      <c r="C539" s="20"/>
-      <c r="D539" s="20"/>
+      <c r="B539" s="23" t="s">
+        <v>674</v>
+      </c>
+      <c r="C539" s="23"/>
+      <c r="D539" s="23"/>
       <c r="E539" s="11"/>
     </row>
-    <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="540" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="2"/>
-      <c r="B540" s="20" t="s">
-        <v>674</v>
-      </c>
-      <c r="C540" s="20"/>
-      <c r="D540" s="20"/>
+      <c r="B540" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="C540" s="23"/>
+      <c r="D540" s="23"/>
       <c r="E540" s="11"/>
     </row>
-    <row r="541" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="2"/>
-      <c r="B541" s="20" t="s">
-        <v>675</v>
-      </c>
-      <c r="C541" s="20"/>
-      <c r="D541" s="20"/>
+      <c r="B541" s="23" t="s">
+        <v>676</v>
+      </c>
+      <c r="C541" s="23"/>
+      <c r="D541" s="23"/>
       <c r="E541" s="11"/>
     </row>
-    <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="542" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="2"/>
-      <c r="B542" s="20" t="s">
-        <v>676</v>
-      </c>
-      <c r="C542" s="20"/>
-      <c r="D542" s="20"/>
+      <c r="B542" s="23" t="s">
+        <v>677</v>
+      </c>
+      <c r="C542" s="23" t="s">
+        <v>633</v>
+      </c>
+      <c r="D542" s="23"/>
       <c r="E542" s="11"/>
     </row>
-    <row r="543" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="2"/>
-      <c r="B543" s="20" t="s">
-        <v>677</v>
-      </c>
-      <c r="C543" s="20" t="s">
-        <v>633</v>
-      </c>
-      <c r="D543" s="20"/>
+      <c r="B543" s="23" t="s">
+        <v>678</v>
+      </c>
+      <c r="C543" s="23"/>
+      <c r="D543" s="23"/>
       <c r="E543" s="11"/>
     </row>
-    <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="544" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="2"/>
-      <c r="B544" s="20" t="s">
-        <v>678</v>
-      </c>
-      <c r="C544" s="20"/>
-      <c r="D544" s="20"/>
+      <c r="B544" s="23" t="s">
+        <v>679</v>
+      </c>
+      <c r="C544" s="23"/>
+      <c r="D544" s="23"/>
       <c r="E544" s="11"/>
     </row>
     <row r="545" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="2"/>
-      <c r="B545" s="20" t="s">
-        <v>679</v>
-      </c>
-      <c r="C545" s="20"/>
-      <c r="D545" s="20"/>
+      <c r="B545" s="23" t="s">
+        <v>680</v>
+      </c>
+      <c r="C545" s="23"/>
+      <c r="D545" s="23"/>
       <c r="E545" s="11"/>
     </row>
-    <row r="546" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="2"/>
-      <c r="B546" s="20" t="s">
-        <v>680</v>
-      </c>
-      <c r="C546" s="20"/>
-      <c r="D546" s="20"/>
+      <c r="B546" s="23" t="s">
+        <v>681</v>
+      </c>
+      <c r="C546" s="23"/>
+      <c r="D546" s="23"/>
       <c r="E546" s="11"/>
     </row>
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="2"/>
-      <c r="B547" s="20" t="s">
-        <v>681</v>
-      </c>
-      <c r="C547" s="20"/>
-      <c r="D547" s="20"/>
+      <c r="B547" s="23" t="s">
+        <v>682</v>
+      </c>
+      <c r="C547" s="23"/>
+      <c r="D547" s="23"/>
       <c r="E547" s="11"/>
     </row>
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="2"/>
-      <c r="B548" s="20" t="s">
-        <v>682</v>
-      </c>
-      <c r="C548" s="20"/>
-      <c r="D548" s="20"/>
+      <c r="B548" s="23" t="s">
+        <v>683</v>
+      </c>
+      <c r="C548" s="23"/>
+      <c r="D548" s="23"/>
       <c r="E548" s="11"/>
     </row>
-    <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="549" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="2"/>
-      <c r="B549" s="20" t="s">
-        <v>683</v>
-      </c>
-      <c r="C549" s="20"/>
-      <c r="D549" s="20"/>
-      <c r="E549" s="11"/>
-    </row>
-    <row r="550" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B549" s="23" t="s">
+        <v>684</v>
+      </c>
+      <c r="C549" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="D549" s="23" t="s">
+        <v>685</v>
+      </c>
+      <c r="E549" s="11" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="550" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="2"/>
-      <c r="B550" s="20" t="s">
-        <v>684</v>
-      </c>
-      <c r="C550" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="D550" s="20" t="s">
-        <v>685</v>
+      <c r="B550" s="23" t="s">
+        <v>686</v>
+      </c>
+      <c r="C550" s="23" t="s">
+        <v>687</v>
+      </c>
+      <c r="D550" s="23" t="s">
+        <v>688</v>
       </c>
       <c r="E550" s="11" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="551" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="2"/>
-      <c r="B551" s="20" t="s">
-        <v>686</v>
-      </c>
-      <c r="C551" s="20" t="s">
-        <v>687</v>
-      </c>
-      <c r="D551" s="20" t="s">
-        <v>688</v>
-      </c>
-      <c r="E551" s="11" t="s">
-        <v>181</v>
-      </c>
+      <c r="B551" s="23" t="s">
+        <v>689</v>
+      </c>
+      <c r="C551" s="23"/>
+      <c r="D551" s="23"/>
+      <c r="E551" s="11"/>
     </row>
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="2"/>
-      <c r="B552" s="20" t="s">
-        <v>689</v>
-      </c>
-      <c r="C552" s="20"/>
-      <c r="D552" s="20"/>
+      <c r="B552" s="23"/>
+      <c r="C552" s="23"/>
+      <c r="D552" s="23"/>
       <c r="E552" s="11"/>
     </row>
-    <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A553" s="2"/>
-      <c r="B553" s="20"/>
-      <c r="C553" s="20"/>
-      <c r="D553" s="20"/>
+    <row r="553" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A553" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B553" s="23" t="s">
+        <v>690</v>
+      </c>
+      <c r="C553" s="23"/>
+      <c r="D553" s="23"/>
       <c r="E553" s="11"/>
     </row>
     <row r="554" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A554" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="B554" s="20" t="s">
-        <v>690</v>
-      </c>
-      <c r="C554" s="20"/>
-      <c r="D554" s="20"/>
+      <c r="A554" s="2"/>
+      <c r="B554" s="23" t="s">
+        <v>691</v>
+      </c>
+      <c r="C554" s="23"/>
+      <c r="D554" s="23"/>
       <c r="E554" s="11"/>
     </row>
-    <row r="555" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="2"/>
-      <c r="B555" s="20" t="s">
-        <v>691</v>
-      </c>
-      <c r="C555" s="20"/>
-      <c r="D555" s="20"/>
+      <c r="B555" s="23" t="s">
+        <v>692</v>
+      </c>
+      <c r="C555" s="23"/>
+      <c r="D555" s="23"/>
       <c r="E555" s="11"/>
     </row>
-    <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="556" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="2"/>
-      <c r="B556" s="20" t="s">
-        <v>692</v>
-      </c>
-      <c r="C556" s="20"/>
-      <c r="D556" s="20"/>
+      <c r="B556" s="23" t="s">
+        <v>693</v>
+      </c>
+      <c r="C556" s="23" t="s">
+        <v>666</v>
+      </c>
+      <c r="D556" s="23"/>
       <c r="E556" s="11"/>
     </row>
-    <row r="557" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="2"/>
-      <c r="B557" s="20" t="s">
-        <v>693</v>
-      </c>
-      <c r="C557" s="32" t="s">
-        <v>666</v>
-      </c>
-      <c r="D557" s="20"/>
+      <c r="B557" s="23"/>
+      <c r="C557" s="23"/>
+      <c r="D557" s="23"/>
       <c r="E557" s="11"/>
     </row>
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="2"/>
-      <c r="B558" s="20"/>
-      <c r="C558" s="20"/>
-      <c r="D558" s="20"/>
+      <c r="B558" s="23" t="s">
+        <v>694</v>
+      </c>
+      <c r="C558" s="23"/>
+      <c r="D558" s="23"/>
       <c r="E558" s="11"/>
     </row>
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A559" s="2"/>
-      <c r="B559" s="20" t="s">
-        <v>694</v>
-      </c>
-      <c r="C559" s="20"/>
-      <c r="D559" s="20"/>
-      <c r="E559" s="11"/>
-    </row>
-    <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A560" s="36"/>
-      <c r="B560" s="37" t="s">
+      <c r="A559" s="36"/>
+      <c r="B559" s="37" t="s">
         <v>695</v>
       </c>
-      <c r="C560" s="37"/>
-      <c r="D560" s="37"/>
-      <c r="E560" s="38"/>
-    </row>
+      <c r="C559" s="37"/>
+      <c r="D559" s="37"/>
+      <c r="E559" s="38"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/assets/responsabilidades.xlsx
+++ b/assets/responsabilidades.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="697">
   <si>
     <t xml:space="preserve">Use Case</t>
   </si>
@@ -2379,13 +2379,16 @@
     <t xml:space="preserve">4.2.1.1 O funcionário regista a notificação de término</t>
   </si>
   <si>
-    <t xml:space="preserve">Registar a notificação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">criarNotificacao(descricao : string, id_remetente : int, id_destinatario : int) : Notificacao</t>
+    <t xml:space="preserve">Registar que a notificação foi recebida e tratada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sinalizarNotificacao_comoTratada(id : int) : bool</t>
   </si>
   <si>
     <t xml:space="preserve">Notificacoes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alterar o atributo booleano da notificação para registar que a mesma foi tratada. Retorna true em caso de sucesso e false em caso de falha(se a notificacao já estiver marcada como tratada por exemplo)</t>
   </si>
   <si>
     <t xml:space="preserve">4.2.1.2 O funcionário confirma a notificação de término</t>
@@ -2835,7 +2838,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2894,12 +2897,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="12"/>
@@ -3068,7 +3065,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3121,10 +3118,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3145,11 +3138,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3173,11 +3162,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3185,7 +3174,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3202,14 +3191,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3485,13 +3466,13 @@
       <c r="C6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="13" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3505,8 +3486,8 @@
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="16"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -3574,7 +3555,7 @@
       <c r="E14" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="16" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3652,7 +3633,7 @@
       <c r="E19" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="18"/>
+      <c r="F19" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
@@ -3800,7 +3781,7 @@
       <c r="D29" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="12" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3818,7 +3799,7 @@
       <c r="E30" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" s="18" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4342,10 +4323,10 @@
       <c r="E79" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F79" s="21" t="s">
+      <c r="F79" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="G79" s="16"/>
+      <c r="G79" s="15"/>
     </row>
     <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
@@ -5447,7 +5428,7 @@
         <v>5</v>
       </c>
       <c r="B181" s="10"/>
-      <c r="C181" s="22"/>
+      <c r="C181" s="20"/>
       <c r="D181" s="12"/>
       <c r="E181" s="12"/>
     </row>
@@ -5552,112 +5533,112 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2"/>
-      <c r="B191" s="23"/>
-      <c r="C191" s="23"/>
+      <c r="B191" s="21"/>
+      <c r="C191" s="21"/>
       <c r="D191" s="12"/>
       <c r="E191" s="12"/>
     </row>
     <row r="192" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="6"/>
-      <c r="B192" s="24" t="s">
+      <c r="B192" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="C192" s="25"/>
-      <c r="D192" s="25"/>
+      <c r="C192" s="23"/>
+      <c r="D192" s="23"/>
       <c r="E192" s="8"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B193" s="23"/>
-      <c r="C193" s="23"/>
-      <c r="D193" s="23"/>
+      <c r="B193" s="21"/>
+      <c r="C193" s="21"/>
+      <c r="D193" s="21"/>
       <c r="E193" s="11"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2"/>
-      <c r="B194" s="23" t="s">
+      <c r="B194" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="C194" s="23"/>
-      <c r="D194" s="23"/>
+      <c r="C194" s="21"/>
+      <c r="D194" s="21"/>
       <c r="E194" s="11"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2"/>
-      <c r="B195" s="23" t="s">
+      <c r="B195" s="21" t="s">
         <v>271</v>
       </c>
-      <c r="C195" s="23"/>
-      <c r="D195" s="23"/>
+      <c r="C195" s="21"/>
+      <c r="D195" s="21"/>
       <c r="E195" s="11"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2"/>
-      <c r="B196" s="23" t="s">
+      <c r="B196" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="C196" s="23" t="s">
+      <c r="C196" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="D196" s="23"/>
+      <c r="D196" s="21"/>
       <c r="E196" s="11"/>
     </row>
     <row r="197" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2"/>
-      <c r="B197" s="23" t="s">
+      <c r="B197" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="C197" s="23"/>
-      <c r="D197" s="23"/>
+      <c r="C197" s="21"/>
+      <c r="D197" s="21"/>
       <c r="E197" s="11"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2"/>
-      <c r="B198" s="23" t="s">
+      <c r="B198" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="C198" s="23"/>
-      <c r="D198" s="23"/>
+      <c r="C198" s="21"/>
+      <c r="D198" s="21"/>
       <c r="E198" s="11"/>
     </row>
     <row r="199" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2"/>
-      <c r="B199" s="23" t="s">
+      <c r="B199" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="C199" s="23" t="s">
+      <c r="C199" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="D199" s="23" t="s">
+      <c r="D199" s="21" t="s">
         <v>277</v>
       </c>
       <c r="E199" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="F199" s="16"/>
+      <c r="F199" s="15"/>
     </row>
     <row r="200" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2"/>
-      <c r="B200" s="23" t="s">
+      <c r="B200" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="C200" s="23" t="s">
+      <c r="C200" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="D200" s="23"/>
+      <c r="D200" s="21"/>
       <c r="E200" s="11"/>
     </row>
     <row r="201" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2"/>
-      <c r="B201" s="23" t="s">
+      <c r="B201" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C201" s="23" t="s">
+      <c r="C201" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="D201" s="23" t="s">
+      <c r="D201" s="21" t="s">
         <v>281</v>
       </c>
       <c r="E201" s="11" t="s">
@@ -5666,13 +5647,13 @@
     </row>
     <row r="202" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2"/>
-      <c r="B202" s="23" t="s">
+      <c r="B202" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="C202" s="23" t="s">
+      <c r="C202" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="D202" s="23" t="s">
+      <c r="D202" s="21" t="s">
         <v>284</v>
       </c>
       <c r="E202" s="11" t="s">
@@ -5681,40 +5662,40 @@
     </row>
     <row r="203" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2"/>
-      <c r="B203" s="23" t="s">
+      <c r="B203" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="C203" s="23" t="s">
+      <c r="C203" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="D203" s="23" t="s">
+      <c r="D203" s="21" t="s">
         <v>287</v>
       </c>
       <c r="E203" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="F203" s="21" t="s">
+      <c r="F203" s="19" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2"/>
-      <c r="B204" s="23" t="s">
+      <c r="B204" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="C204" s="23"/>
-      <c r="D204" s="23"/>
+      <c r="C204" s="21"/>
+      <c r="D204" s="21"/>
       <c r="E204" s="11"/>
     </row>
     <row r="205" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2"/>
-      <c r="B205" s="23" t="s">
+      <c r="B205" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="C205" s="23" t="s">
+      <c r="C205" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D205" s="23" t="s">
+      <c r="D205" s="21" t="s">
         <v>78</v>
       </c>
       <c r="E205" s="11" t="s">
@@ -5723,11 +5704,11 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2"/>
-      <c r="B206" s="23"/>
-      <c r="C206" s="23"/>
-      <c r="D206" s="23"/>
+      <c r="B206" s="21"/>
+      <c r="C206" s="21"/>
+      <c r="D206" s="21"/>
       <c r="E206" s="11"/>
-      <c r="F206" s="16"/>
+      <c r="F206" s="15"/>
       <c r="G206" s="1"/>
       <c r="H206" s="1"/>
       <c r="I206" s="1"/>
@@ -5735,255 +5716,255 @@
     </row>
     <row r="207" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="6"/>
-      <c r="B207" s="24" t="s">
+      <c r="B207" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="C207" s="25"/>
-      <c r="D207" s="25"/>
+      <c r="C207" s="23"/>
+      <c r="D207" s="23"/>
       <c r="E207" s="8"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B208" s="23"/>
-      <c r="C208" s="23"/>
-      <c r="D208" s="23"/>
+      <c r="B208" s="21"/>
+      <c r="C208" s="21"/>
+      <c r="D208" s="21"/>
       <c r="E208" s="11"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2"/>
-      <c r="B209" s="23" t="s">
+      <c r="B209" s="21" t="s">
         <v>292</v>
       </c>
-      <c r="C209" s="23"/>
-      <c r="D209" s="23"/>
+      <c r="C209" s="21"/>
+      <c r="D209" s="21"/>
       <c r="E209" s="11"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2"/>
-      <c r="B210" s="23" t="s">
+      <c r="B210" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="C210" s="23"/>
-      <c r="D210" s="23"/>
+      <c r="C210" s="21"/>
+      <c r="D210" s="21"/>
       <c r="E210" s="11"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2"/>
-      <c r="B211" s="23" t="s">
+      <c r="B211" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="C211" s="23"/>
-      <c r="D211" s="23"/>
+      <c r="C211" s="21"/>
+      <c r="D211" s="21"/>
       <c r="E211" s="11"/>
     </row>
     <row r="212" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2"/>
-      <c r="B212" s="23" t="s">
+      <c r="B212" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="C212" s="23"/>
-      <c r="D212" s="23"/>
+      <c r="C212" s="21"/>
+      <c r="D212" s="21"/>
       <c r="E212" s="11"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2"/>
-      <c r="B213" s="23" t="s">
+      <c r="B213" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="C213" s="23"/>
-      <c r="D213" s="23"/>
+      <c r="C213" s="21"/>
+      <c r="D213" s="21"/>
       <c r="E213" s="11"/>
     </row>
     <row r="214" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2"/>
-      <c r="B214" s="23" t="s">
+      <c r="B214" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="C214" s="23" t="s">
+      <c r="C214" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="D214" s="23"/>
+      <c r="D214" s="21"/>
       <c r="E214" s="11"/>
     </row>
     <row r="215" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2"/>
-      <c r="B215" s="23" t="s">
+      <c r="B215" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="C215" s="23" t="s">
+      <c r="C215" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="D215" s="23"/>
+      <c r="D215" s="21"/>
       <c r="E215" s="11"/>
     </row>
     <row r="216" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2"/>
-      <c r="B216" s="23" t="s">
+      <c r="B216" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="C216" s="23" t="s">
+      <c r="C216" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="D216" s="23"/>
+      <c r="D216" s="21"/>
       <c r="E216" s="11"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2"/>
-      <c r="B217" s="23" t="s">
+      <c r="B217" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="C217" s="23" t="s">
+      <c r="C217" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="D217" s="23"/>
+      <c r="D217" s="21"/>
       <c r="E217" s="11"/>
     </row>
     <row r="218" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2"/>
-      <c r="B218" s="23" t="s">
+      <c r="B218" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="C218" s="23" t="s">
+      <c r="C218" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D218" s="23"/>
+      <c r="D218" s="21"/>
       <c r="E218" s="11"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2"/>
-      <c r="B219" s="23"/>
-      <c r="C219" s="23"/>
-      <c r="D219" s="23"/>
+      <c r="B219" s="21"/>
+      <c r="C219" s="21"/>
+      <c r="D219" s="21"/>
       <c r="E219" s="11"/>
     </row>
     <row r="220" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B220" s="23" t="s">
+      <c r="B220" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="C220" s="23"/>
-      <c r="D220" s="23"/>
+      <c r="C220" s="21"/>
+      <c r="D220" s="21"/>
       <c r="E220" s="11"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2"/>
-      <c r="B221" s="23" t="s">
+      <c r="B221" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="C221" s="23"/>
-      <c r="D221" s="23"/>
+      <c r="C221" s="21"/>
+      <c r="D221" s="21"/>
       <c r="E221" s="11"/>
     </row>
     <row r="222" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2"/>
-      <c r="B222" s="23" t="s">
+      <c r="B222" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="C222" s="23" t="s">
+      <c r="C222" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="D222" s="23" t="s">
+      <c r="D222" s="21" t="s">
         <v>306</v>
       </c>
       <c r="E222" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="F222" s="21" t="s">
+      <c r="F222" s="19" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2"/>
-      <c r="B223" s="23" t="s">
+      <c r="B223" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="C223" s="23"/>
-      <c r="D223" s="23"/>
+      <c r="C223" s="21"/>
+      <c r="D223" s="21"/>
       <c r="E223" s="11"/>
     </row>
     <row r="224" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2"/>
-      <c r="B224" s="23" t="s">
+      <c r="B224" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="C224" s="23"/>
-      <c r="D224" s="23"/>
+      <c r="C224" s="21"/>
+      <c r="D224" s="21"/>
       <c r="E224" s="11"/>
     </row>
     <row r="225" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2"/>
-      <c r="B225" s="23" t="s">
+      <c r="B225" s="21" t="s">
         <v>310</v>
       </c>
-      <c r="C225" s="23" t="s">
+      <c r="C225" s="21" t="s">
         <v>311</v>
       </c>
-      <c r="D225" s="23" t="s">
+      <c r="D225" s="21" t="s">
         <v>312</v>
       </c>
       <c r="E225" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="F225" s="21" t="s">
+      <c r="F225" s="19" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2"/>
-      <c r="B226" s="23" t="s">
+      <c r="B226" s="21" t="s">
         <v>314</v>
       </c>
-      <c r="C226" s="23"/>
-      <c r="D226" s="23"/>
+      <c r="C226" s="21"/>
+      <c r="D226" s="21"/>
       <c r="E226" s="11"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2"/>
-      <c r="B227" s="23"/>
-      <c r="C227" s="23"/>
-      <c r="D227" s="23"/>
+      <c r="B227" s="21"/>
+      <c r="C227" s="21"/>
+      <c r="D227" s="21"/>
       <c r="E227" s="11"/>
     </row>
     <row r="228" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="6"/>
-      <c r="B228" s="24" t="s">
+      <c r="B228" s="22" t="s">
         <v>315</v>
       </c>
-      <c r="C228" s="25"/>
-      <c r="D228" s="25"/>
+      <c r="C228" s="23"/>
+      <c r="D228" s="23"/>
       <c r="E228" s="8"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B229" s="23"/>
-      <c r="C229" s="23"/>
-      <c r="D229" s="23"/>
+      <c r="B229" s="21"/>
+      <c r="C229" s="21"/>
+      <c r="D229" s="21"/>
       <c r="E229" s="11"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2"/>
-      <c r="B230" s="23" t="s">
+      <c r="B230" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="C230" s="23"/>
-      <c r="D230" s="23"/>
+      <c r="C230" s="21"/>
+      <c r="D230" s="21"/>
       <c r="E230" s="11"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2"/>
-      <c r="B231" s="23" t="s">
+      <c r="B231" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="C231" s="23" t="s">
+      <c r="C231" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="D231" s="23" t="s">
+      <c r="D231" s="21" t="s">
         <v>318</v>
       </c>
       <c r="E231" s="11" t="s">
@@ -5992,22 +5973,22 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="2"/>
-      <c r="B232" s="23" t="s">
+      <c r="B232" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="C232" s="23"/>
-      <c r="D232" s="23"/>
+      <c r="C232" s="21"/>
+      <c r="D232" s="21"/>
       <c r="E232" s="11"/>
     </row>
     <row r="233" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2"/>
-      <c r="B233" s="23" t="s">
+      <c r="B233" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="C233" s="23" t="s">
+      <c r="C233" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="D233" s="26" t="s">
+      <c r="D233" s="24" t="s">
         <v>322</v>
       </c>
       <c r="E233" s="11" t="s">
@@ -6016,22 +5997,22 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2"/>
-      <c r="B234" s="23" t="s">
+      <c r="B234" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="C234" s="23"/>
-      <c r="D234" s="23"/>
+      <c r="C234" s="21"/>
+      <c r="D234" s="21"/>
       <c r="E234" s="11"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2"/>
-      <c r="B235" s="23" t="s">
+      <c r="B235" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="C235" s="23" t="s">
+      <c r="C235" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="D235" s="23" t="s">
+      <c r="D235" s="21" t="s">
         <v>326</v>
       </c>
       <c r="E235" s="11" t="s">
@@ -6040,13 +6021,13 @@
     </row>
     <row r="236" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2"/>
-      <c r="B236" s="23" t="s">
+      <c r="B236" s="21" t="s">
         <v>327</v>
       </c>
-      <c r="C236" s="23" t="s">
+      <c r="C236" s="21" t="s">
         <v>311</v>
       </c>
-      <c r="D236" s="23" t="s">
+      <c r="D236" s="21" t="s">
         <v>312</v>
       </c>
       <c r="E236" s="11" t="s">
@@ -6055,22 +6036,22 @@
     </row>
     <row r="237" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="2"/>
-      <c r="B237" s="23" t="s">
+      <c r="B237" s="21" t="s">
         <v>328</v>
       </c>
-      <c r="C237" s="23"/>
-      <c r="D237" s="23"/>
+      <c r="C237" s="21"/>
+      <c r="D237" s="21"/>
       <c r="E237" s="11"/>
     </row>
     <row r="238" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2"/>
-      <c r="B238" s="23" t="s">
+      <c r="B238" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="C238" s="23" t="s">
+      <c r="C238" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D238" s="23" t="s">
+      <c r="D238" s="21" t="s">
         <v>78</v>
       </c>
       <c r="E238" s="11" t="s">
@@ -6079,9 +6060,9 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="2"/>
-      <c r="B239" s="23"/>
-      <c r="C239" s="23"/>
-      <c r="D239" s="23"/>
+      <c r="B239" s="21"/>
+      <c r="C239" s="21"/>
+      <c r="D239" s="21"/>
       <c r="E239" s="11"/>
       <c r="G239" s="1"/>
       <c r="H239" s="1"/>
@@ -6090,80 +6071,80 @@
     </row>
     <row r="240" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="6"/>
-      <c r="B240" s="24" t="s">
+      <c r="B240" s="22" t="s">
         <v>330</v>
       </c>
-      <c r="C240" s="25"/>
-      <c r="D240" s="25"/>
+      <c r="C240" s="23"/>
+      <c r="D240" s="23"/>
       <c r="E240" s="8"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B241" s="23"/>
-      <c r="C241" s="23"/>
-      <c r="D241" s="23"/>
+      <c r="B241" s="21"/>
+      <c r="C241" s="21"/>
+      <c r="D241" s="21"/>
       <c r="E241" s="11"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2"/>
-      <c r="B242" s="23" t="s">
+      <c r="B242" s="21" t="s">
         <v>331</v>
       </c>
-      <c r="C242" s="23"/>
-      <c r="D242" s="23"/>
+      <c r="C242" s="21"/>
+      <c r="D242" s="21"/>
       <c r="E242" s="11"/>
     </row>
     <row r="243" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2"/>
-      <c r="B243" s="23" t="s">
+      <c r="B243" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="C243" s="23"/>
-      <c r="D243" s="23"/>
+      <c r="C243" s="21"/>
+      <c r="D243" s="21"/>
       <c r="E243" s="11"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2"/>
-      <c r="B244" s="23" t="s">
+      <c r="B244" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="C244" s="23"/>
-      <c r="D244" s="23"/>
+      <c r="C244" s="21"/>
+      <c r="D244" s="21"/>
       <c r="E244" s="11"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2"/>
-      <c r="B245" s="23" t="s">
+      <c r="B245" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C245" s="23" t="s">
+      <c r="C245" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D245" s="23"/>
+      <c r="D245" s="21"/>
       <c r="E245" s="11"/>
     </row>
     <row r="246" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="2"/>
-      <c r="B246" s="23" t="s">
+      <c r="B246" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="C246" s="23" t="s">
+      <c r="C246" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="D246" s="23"/>
+      <c r="D246" s="21"/>
       <c r="E246" s="11"/>
     </row>
     <row r="247" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="2"/>
-      <c r="B247" s="23" t="s">
+      <c r="B247" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="C247" s="23" t="s">
+      <c r="C247" s="21" t="s">
         <v>337</v>
       </c>
-      <c r="D247" s="23" t="s">
+      <c r="D247" s="21" t="s">
         <v>338</v>
       </c>
       <c r="E247" s="11" t="s">
@@ -6172,13 +6153,13 @@
     </row>
     <row r="248" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2"/>
-      <c r="B248" s="23" t="s">
+      <c r="B248" s="21" t="s">
         <v>339</v>
       </c>
-      <c r="C248" s="23" t="s">
+      <c r="C248" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D248" s="23" t="s">
+      <c r="D248" s="21" t="s">
         <v>78</v>
       </c>
       <c r="E248" s="11" t="s">
@@ -6187,47 +6168,47 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2"/>
-      <c r="B249" s="23"/>
-      <c r="C249" s="23"/>
-      <c r="D249" s="23"/>
+      <c r="B249" s="21"/>
+      <c r="C249" s="21"/>
+      <c r="D249" s="21"/>
       <c r="E249" s="11"/>
     </row>
     <row r="250" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="6"/>
-      <c r="B250" s="24" t="s">
+      <c r="B250" s="22" t="s">
         <v>340</v>
       </c>
-      <c r="C250" s="25"/>
-      <c r="D250" s="25"/>
+      <c r="C250" s="23"/>
+      <c r="D250" s="23"/>
       <c r="E250" s="8"/>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B251" s="23"/>
-      <c r="C251" s="23"/>
-      <c r="D251" s="23"/>
+      <c r="B251" s="21"/>
+      <c r="C251" s="21"/>
+      <c r="D251" s="21"/>
       <c r="E251" s="11"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2"/>
-      <c r="B252" s="23" t="s">
+      <c r="B252" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="C252" s="23"/>
-      <c r="D252" s="23"/>
+      <c r="C252" s="21"/>
+      <c r="D252" s="21"/>
       <c r="E252" s="11"/>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2"/>
-      <c r="B253" s="23" t="s">
+      <c r="B253" s="21" t="s">
         <v>342</v>
       </c>
-      <c r="C253" s="23" t="s">
+      <c r="C253" s="21" t="s">
         <v>343</v>
       </c>
-      <c r="D253" s="23" t="s">
+      <c r="D253" s="21" t="s">
         <v>344</v>
       </c>
       <c r="E253" s="11" t="s">
@@ -6236,62 +6217,62 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="2"/>
-      <c r="B254" s="23" t="s">
+      <c r="B254" s="21" t="s">
         <v>345</v>
       </c>
-      <c r="C254" s="23"/>
-      <c r="D254" s="23"/>
+      <c r="C254" s="21"/>
+      <c r="D254" s="21"/>
       <c r="E254" s="11"/>
     </row>
     <row r="255" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="2"/>
-      <c r="B255" s="23" t="s">
+      <c r="B255" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="C255" s="23"/>
-      <c r="D255" s="23"/>
+      <c r="C255" s="21"/>
+      <c r="D255" s="21"/>
       <c r="E255" s="11"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="2"/>
-      <c r="B256" s="23" t="s">
+      <c r="B256" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="C256" s="23"/>
-      <c r="D256" s="23"/>
+      <c r="C256" s="21"/>
+      <c r="D256" s="21"/>
       <c r="E256" s="11"/>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="2"/>
-      <c r="B257" s="23" t="s">
+      <c r="B257" s="21" t="s">
         <v>346</v>
       </c>
-      <c r="C257" s="23" t="s">
+      <c r="C257" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D257" s="23"/>
+      <c r="D257" s="21"/>
       <c r="E257" s="11"/>
     </row>
     <row r="258" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="2"/>
-      <c r="B258" s="23" t="s">
+      <c r="B258" s="21" t="s">
         <v>347</v>
       </c>
-      <c r="C258" s="23" t="s">
+      <c r="C258" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="D258" s="23"/>
+      <c r="D258" s="21"/>
       <c r="E258" s="11"/>
     </row>
     <row r="259" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2"/>
-      <c r="B259" s="23" t="s">
+      <c r="B259" s="21" t="s">
         <v>348</v>
       </c>
-      <c r="C259" s="23" t="s">
+      <c r="C259" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D259" s="23" t="s">
+      <c r="D259" s="21" t="s">
         <v>78</v>
       </c>
       <c r="E259" s="11" t="s">
@@ -6300,13 +6281,13 @@
     </row>
     <row r="260" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="2"/>
-      <c r="B260" s="23" t="s">
+      <c r="B260" s="21" t="s">
         <v>349</v>
       </c>
-      <c r="C260" s="23" t="s">
+      <c r="C260" s="21" t="s">
         <v>350</v>
       </c>
-      <c r="D260" s="23" t="s">
+      <c r="D260" s="21" t="s">
         <v>351</v>
       </c>
       <c r="E260" s="11" t="s">
@@ -6315,47 +6296,47 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="2"/>
-      <c r="B261" s="23"/>
-      <c r="C261" s="23"/>
-      <c r="D261" s="23"/>
+      <c r="B261" s="21"/>
+      <c r="C261" s="21"/>
+      <c r="D261" s="21"/>
       <c r="E261" s="11"/>
     </row>
     <row r="262" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="6"/>
-      <c r="B262" s="24" t="s">
+      <c r="B262" s="22" t="s">
         <v>352</v>
       </c>
-      <c r="C262" s="25"/>
-      <c r="D262" s="25"/>
+      <c r="C262" s="23"/>
+      <c r="D262" s="23"/>
       <c r="E262" s="8"/>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B263" s="23"/>
-      <c r="C263" s="23"/>
-      <c r="D263" s="23"/>
+      <c r="B263" s="21"/>
+      <c r="C263" s="21"/>
+      <c r="D263" s="21"/>
       <c r="E263" s="11"/>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="2"/>
-      <c r="B264" s="23" t="s">
+      <c r="B264" s="21" t="s">
         <v>353</v>
       </c>
-      <c r="C264" s="23"/>
-      <c r="D264" s="23"/>
+      <c r="C264" s="21"/>
+      <c r="D264" s="21"/>
       <c r="E264" s="11"/>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="2"/>
-      <c r="B265" s="23" t="s">
+      <c r="B265" s="21" t="s">
         <v>354</v>
       </c>
-      <c r="C265" s="23" t="s">
+      <c r="C265" s="21" t="s">
         <v>343</v>
       </c>
-      <c r="D265" s="23" t="s">
+      <c r="D265" s="21" t="s">
         <v>344</v>
       </c>
       <c r="E265" s="11" t="s">
@@ -6364,31 +6345,31 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="2"/>
-      <c r="B266" s="23" t="s">
+      <c r="B266" s="21" t="s">
         <v>355</v>
       </c>
-      <c r="C266" s="23"/>
-      <c r="D266" s="23"/>
+      <c r="C266" s="21"/>
+      <c r="D266" s="21"/>
       <c r="E266" s="11"/>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2"/>
-      <c r="B267" s="23" t="s">
+      <c r="B267" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="C267" s="23"/>
-      <c r="D267" s="23"/>
+      <c r="C267" s="21"/>
+      <c r="D267" s="21"/>
       <c r="E267" s="11"/>
     </row>
     <row r="268" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="2"/>
-      <c r="B268" s="23" t="s">
+      <c r="B268" s="21" t="s">
         <v>357</v>
       </c>
-      <c r="C268" s="23" t="s">
+      <c r="C268" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D268" s="23" t="s">
+      <c r="D268" s="21" t="s">
         <v>78</v>
       </c>
       <c r="E268" s="11" t="s">
@@ -6397,13 +6378,13 @@
     </row>
     <row r="269" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="2"/>
-      <c r="B269" s="23" t="s">
+      <c r="B269" s="21" t="s">
         <v>358</v>
       </c>
-      <c r="C269" s="23" t="s">
+      <c r="C269" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="D269" s="23" t="s">
+      <c r="D269" s="21" t="s">
         <v>360</v>
       </c>
       <c r="E269" s="11" t="s">
@@ -6412,73 +6393,73 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="2"/>
-      <c r="B270" s="23"/>
-      <c r="C270" s="23"/>
-      <c r="D270" s="23"/>
+      <c r="B270" s="21"/>
+      <c r="C270" s="21"/>
+      <c r="D270" s="21"/>
       <c r="E270" s="11"/>
-      <c r="F270" s="16"/>
+      <c r="F270" s="15"/>
       <c r="G270" s="1"/>
     </row>
     <row r="271" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="6"/>
-      <c r="B271" s="24" t="s">
+      <c r="B271" s="22" t="s">
         <v>361</v>
       </c>
-      <c r="C271" s="25"/>
-      <c r="D271" s="25"/>
+      <c r="C271" s="23"/>
+      <c r="D271" s="23"/>
       <c r="E271" s="8"/>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B272" s="23"/>
-      <c r="C272" s="23"/>
-      <c r="D272" s="23"/>
+      <c r="B272" s="21"/>
+      <c r="C272" s="21"/>
+      <c r="D272" s="21"/>
       <c r="E272" s="11"/>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="2"/>
-      <c r="B273" s="23" t="s">
+      <c r="B273" s="21" t="s">
         <v>362</v>
       </c>
-      <c r="C273" s="23"/>
-      <c r="D273" s="23"/>
+      <c r="C273" s="21"/>
+      <c r="D273" s="21"/>
       <c r="E273" s="11"/>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="2"/>
-      <c r="B274" s="23" t="s">
+      <c r="B274" s="21" t="s">
         <v>363</v>
       </c>
-      <c r="C274" s="23"/>
-      <c r="D274" s="23"/>
+      <c r="C274" s="21"/>
+      <c r="D274" s="21"/>
       <c r="E274" s="11"/>
     </row>
     <row r="275" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="2"/>
-      <c r="B275" s="23" t="s">
+      <c r="B275" s="21" t="s">
         <v>364</v>
       </c>
-      <c r="C275" s="23" t="s">
+      <c r="C275" s="21" t="s">
         <v>365</v>
       </c>
-      <c r="D275" s="26" t="s">
+      <c r="D275" s="24" t="s">
         <v>366</v>
       </c>
-      <c r="E275" s="27" t="s">
+      <c r="E275" s="25" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="2"/>
-      <c r="B276" s="23" t="s">
+      <c r="B276" s="21" t="s">
         <v>367</v>
       </c>
-      <c r="C276" s="23" t="s">
+      <c r="C276" s="21" t="s">
         <v>368</v>
       </c>
-      <c r="D276" s="23" t="s">
+      <c r="D276" s="21" t="s">
         <v>369</v>
       </c>
       <c r="E276" s="11" t="s">
@@ -6487,69 +6468,69 @@
     </row>
     <row r="277" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="2"/>
-      <c r="B277" s="23" t="s">
+      <c r="B277" s="21" t="s">
         <v>370</v>
       </c>
-      <c r="C277" s="23"/>
-      <c r="D277" s="23"/>
+      <c r="C277" s="21"/>
+      <c r="D277" s="21"/>
       <c r="E277" s="11"/>
     </row>
     <row r="278" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="2"/>
-      <c r="B278" s="23" t="s">
+      <c r="B278" s="21" t="s">
         <v>371</v>
       </c>
-      <c r="C278" s="23"/>
-      <c r="D278" s="23"/>
+      <c r="C278" s="21"/>
+      <c r="D278" s="21"/>
       <c r="E278" s="11"/>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="2"/>
-      <c r="B279" s="23" t="s">
+      <c r="B279" s="21" t="s">
         <v>372</v>
       </c>
-      <c r="C279" s="23"/>
-      <c r="D279" s="23"/>
+      <c r="C279" s="21"/>
+      <c r="D279" s="21"/>
       <c r="E279" s="11"/>
     </row>
     <row r="280" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="2"/>
-      <c r="B280" s="23" t="s">
+      <c r="B280" s="21" t="s">
         <v>373</v>
       </c>
-      <c r="C280" s="23"/>
-      <c r="D280" s="23"/>
+      <c r="C280" s="21"/>
+      <c r="D280" s="21"/>
       <c r="E280" s="11"/>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="2"/>
-      <c r="B281" s="23" t="s">
+      <c r="B281" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="C281" s="23"/>
-      <c r="D281" s="23"/>
+      <c r="C281" s="21"/>
+      <c r="D281" s="21"/>
       <c r="E281" s="11"/>
     </row>
     <row r="282" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="2"/>
-      <c r="B282" s="23" t="s">
+      <c r="B282" s="21" t="s">
         <v>375</v>
       </c>
-      <c r="C282" s="23" t="s">
+      <c r="C282" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="D282" s="23"/>
+      <c r="D282" s="21"/>
       <c r="E282" s="11"/>
     </row>
     <row r="283" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="2"/>
-      <c r="B283" s="23" t="s">
+      <c r="B283" s="21" t="s">
         <v>377</v>
       </c>
-      <c r="C283" s="23" t="s">
+      <c r="C283" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="D283" s="23" t="s">
+      <c r="D283" s="21" t="s">
         <v>379</v>
       </c>
       <c r="E283" s="11" t="s">
@@ -6558,13 +6539,13 @@
     </row>
     <row r="284" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="2"/>
-      <c r="B284" s="23" t="s">
+      <c r="B284" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="C284" s="23" t="s">
+      <c r="C284" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D284" s="23" t="s">
+      <c r="D284" s="21" t="s">
         <v>78</v>
       </c>
       <c r="E284" s="11" t="s">
@@ -6573,47 +6554,47 @@
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="2"/>
-      <c r="B285" s="23"/>
-      <c r="C285" s="23"/>
-      <c r="D285" s="23"/>
+      <c r="B285" s="21"/>
+      <c r="C285" s="21"/>
+      <c r="D285" s="21"/>
       <c r="E285" s="11"/>
     </row>
     <row r="286" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="6"/>
-      <c r="B286" s="24" t="s">
+      <c r="B286" s="22" t="s">
         <v>381</v>
       </c>
-      <c r="C286" s="25"/>
-      <c r="D286" s="25"/>
+      <c r="C286" s="23"/>
+      <c r="D286" s="23"/>
       <c r="E286" s="8"/>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B287" s="23"/>
-      <c r="C287" s="23"/>
-      <c r="D287" s="23"/>
+      <c r="B287" s="21"/>
+      <c r="C287" s="21"/>
+      <c r="D287" s="21"/>
       <c r="E287" s="11"/>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="2"/>
-      <c r="B288" s="23" t="s">
+      <c r="B288" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="C288" s="23"/>
-      <c r="D288" s="23"/>
+      <c r="C288" s="21"/>
+      <c r="D288" s="21"/>
       <c r="E288" s="11"/>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="2"/>
-      <c r="B289" s="23" t="s">
+      <c r="B289" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="C289" s="23" t="s">
+      <c r="C289" s="21" t="s">
         <v>384</v>
       </c>
-      <c r="D289" s="23" t="s">
+      <c r="D289" s="21" t="s">
         <v>385</v>
       </c>
       <c r="E289" s="11" t="s">
@@ -6622,22 +6603,22 @@
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="2"/>
-      <c r="B290" s="23" t="s">
+      <c r="B290" s="21" t="s">
         <v>386</v>
       </c>
-      <c r="C290" s="23"/>
-      <c r="D290" s="23"/>
+      <c r="C290" s="21"/>
+      <c r="D290" s="21"/>
       <c r="E290" s="11"/>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="2"/>
-      <c r="B291" s="23" t="s">
+      <c r="B291" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="C291" s="23" t="s">
+      <c r="C291" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="D291" s="23" t="s">
+      <c r="D291" s="21" t="s">
         <v>389</v>
       </c>
       <c r="E291" s="11" t="s">
@@ -6646,31 +6627,31 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2"/>
-      <c r="B292" s="23" t="s">
+      <c r="B292" s="21" t="s">
         <v>390</v>
       </c>
-      <c r="C292" s="23"/>
-      <c r="D292" s="23"/>
+      <c r="C292" s="21"/>
+      <c r="D292" s="21"/>
       <c r="E292" s="11"/>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="2"/>
-      <c r="B293" s="23" t="s">
+      <c r="B293" s="21" t="s">
         <v>391</v>
       </c>
-      <c r="C293" s="23"/>
-      <c r="D293" s="23"/>
+      <c r="C293" s="21"/>
+      <c r="D293" s="21"/>
       <c r="E293" s="11"/>
     </row>
     <row r="294" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="2"/>
-      <c r="B294" s="23" t="s">
+      <c r="B294" s="21" t="s">
         <v>392</v>
       </c>
-      <c r="C294" s="23" t="s">
+      <c r="C294" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D294" s="23" t="s">
+      <c r="D294" s="21" t="s">
         <v>78</v>
       </c>
       <c r="E294" s="11" t="s">
@@ -6679,24 +6660,24 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="2"/>
-      <c r="B295" s="23" t="s">
+      <c r="B295" s="21" t="s">
         <v>393</v>
       </c>
-      <c r="C295" s="23" t="s">
+      <c r="C295" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="D295" s="23"/>
+      <c r="D295" s="21"/>
       <c r="E295" s="11"/>
     </row>
     <row r="296" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="2"/>
-      <c r="B296" s="23" t="s">
+      <c r="B296" s="21" t="s">
         <v>394</v>
       </c>
-      <c r="C296" s="23" t="s">
+      <c r="C296" s="21" t="s">
         <v>395</v>
       </c>
-      <c r="D296" s="23" t="s">
+      <c r="D296" s="21" t="s">
         <v>396</v>
       </c>
       <c r="E296" s="11" t="s">
@@ -6705,60 +6686,60 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="2"/>
-      <c r="B297" s="23"/>
-      <c r="C297" s="23"/>
-      <c r="D297" s="23"/>
+      <c r="B297" s="21"/>
+      <c r="C297" s="21"/>
+      <c r="D297" s="21"/>
       <c r="E297" s="11"/>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B298" s="23" t="s">
+      <c r="B298" s="21" t="s">
         <v>397</v>
       </c>
-      <c r="C298" s="23"/>
-      <c r="D298" s="23"/>
+      <c r="C298" s="21"/>
+      <c r="D298" s="21"/>
       <c r="E298" s="11"/>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="2"/>
-      <c r="B299" s="23" t="s">
+      <c r="B299" s="21" t="s">
         <v>398</v>
       </c>
-      <c r="C299" s="23"/>
-      <c r="D299" s="23"/>
+      <c r="C299" s="21"/>
+      <c r="D299" s="21"/>
       <c r="E299" s="11"/>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="2"/>
-      <c r="B300" s="23" t="s">
+      <c r="B300" s="21" t="s">
         <v>399</v>
       </c>
-      <c r="C300" s="23"/>
-      <c r="D300" s="23"/>
+      <c r="C300" s="21"/>
+      <c r="D300" s="21"/>
       <c r="E300" s="11"/>
     </row>
     <row r="301" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="2"/>
-      <c r="B301" s="23" t="s">
+      <c r="B301" s="21" t="s">
         <v>400</v>
       </c>
-      <c r="C301" s="23" t="s">
+      <c r="C301" s="21" t="s">
         <v>401</v>
       </c>
-      <c r="D301" s="23"/>
+      <c r="D301" s="21"/>
       <c r="E301" s="11"/>
     </row>
     <row r="302" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="2"/>
-      <c r="B302" s="23" t="s">
+      <c r="B302" s="21" t="s">
         <v>402</v>
       </c>
-      <c r="C302" s="23" t="s">
+      <c r="C302" s="21" t="s">
         <v>403</v>
       </c>
-      <c r="D302" s="23" t="s">
+      <c r="D302" s="21" t="s">
         <v>404</v>
       </c>
       <c r="E302" s="11" t="s">
@@ -6767,71 +6748,71 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="2"/>
-      <c r="B303" s="23" t="s">
+      <c r="B303" s="21" t="s">
         <v>405</v>
       </c>
-      <c r="C303" s="23"/>
-      <c r="D303" s="23"/>
+      <c r="C303" s="21"/>
+      <c r="D303" s="21"/>
       <c r="E303" s="11"/>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="2"/>
-      <c r="B304" s="23" t="s">
+      <c r="B304" s="21" t="s">
         <v>406</v>
       </c>
-      <c r="C304" s="23"/>
-      <c r="D304" s="23"/>
+      <c r="C304" s="21"/>
+      <c r="D304" s="21"/>
       <c r="E304" s="11"/>
     </row>
     <row r="305" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="2"/>
-      <c r="B305" s="23" t="s">
+      <c r="B305" s="21" t="s">
         <v>407</v>
       </c>
-      <c r="C305" s="23"/>
-      <c r="D305" s="23"/>
+      <c r="C305" s="21"/>
+      <c r="D305" s="21"/>
       <c r="E305" s="11"/>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="2"/>
-      <c r="B306" s="23" t="s">
+      <c r="B306" s="21" t="s">
         <v>408</v>
       </c>
-      <c r="C306" s="23"/>
-      <c r="D306" s="23"/>
+      <c r="C306" s="21"/>
+      <c r="D306" s="21"/>
       <c r="E306" s="11"/>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="2"/>
-      <c r="B307" s="23" t="s">
+      <c r="B307" s="21" t="s">
         <v>409</v>
       </c>
-      <c r="C307" s="23" t="s">
+      <c r="C307" s="21" t="s">
         <v>410</v>
       </c>
-      <c r="D307" s="23"/>
+      <c r="D307" s="21"/>
       <c r="E307" s="11"/>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="2"/>
-      <c r="B308" s="23" t="s">
+      <c r="B308" s="21" t="s">
         <v>411</v>
       </c>
-      <c r="C308" s="23" t="s">
+      <c r="C308" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="D308" s="23"/>
+      <c r="D308" s="21"/>
       <c r="E308" s="11"/>
     </row>
     <row r="309" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="2"/>
-      <c r="B309" s="23" t="s">
+      <c r="B309" s="21" t="s">
         <v>413</v>
       </c>
-      <c r="C309" s="23" t="s">
+      <c r="C309" s="21" t="s">
         <v>403</v>
       </c>
-      <c r="D309" s="23" t="s">
+      <c r="D309" s="21" t="s">
         <v>414</v>
       </c>
       <c r="E309" s="11" t="s">
@@ -6840,83 +6821,83 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="2"/>
-      <c r="B310" s="23" t="s">
+      <c r="B310" s="21" t="s">
         <v>415</v>
       </c>
-      <c r="C310" s="23"/>
-      <c r="D310" s="23"/>
+      <c r="C310" s="21"/>
+      <c r="D310" s="21"/>
       <c r="E310" s="11"/>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="2"/>
-      <c r="B311" s="23"/>
-      <c r="C311" s="23"/>
-      <c r="D311" s="23"/>
+      <c r="B311" s="21"/>
+      <c r="C311" s="21"/>
+      <c r="D311" s="21"/>
       <c r="E311" s="11"/>
     </row>
     <row r="312" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="6"/>
-      <c r="B312" s="24" t="s">
+      <c r="B312" s="22" t="s">
         <v>416</v>
       </c>
-      <c r="C312" s="25"/>
-      <c r="D312" s="25"/>
+      <c r="C312" s="23"/>
+      <c r="D312" s="23"/>
       <c r="E312" s="8"/>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B313" s="22"/>
-      <c r="C313" s="23"/>
-      <c r="D313" s="23"/>
+      <c r="B313" s="20"/>
+      <c r="C313" s="21"/>
+      <c r="D313" s="21"/>
       <c r="E313" s="11"/>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="2"/>
-      <c r="B314" s="23" t="s">
+      <c r="B314" s="21" t="s">
         <v>417</v>
       </c>
-      <c r="C314" s="23"/>
-      <c r="D314" s="23"/>
+      <c r="C314" s="21"/>
+      <c r="D314" s="21"/>
       <c r="E314" s="11"/>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="2"/>
-      <c r="B315" s="23" t="s">
+      <c r="B315" s="21" t="s">
         <v>418</v>
       </c>
-      <c r="C315" s="23"/>
-      <c r="D315" s="23"/>
+      <c r="C315" s="21"/>
+      <c r="D315" s="21"/>
       <c r="E315" s="11"/>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="2"/>
-      <c r="B316" s="23" t="s">
+      <c r="B316" s="21" t="s">
         <v>419</v>
       </c>
-      <c r="C316" s="23"/>
-      <c r="D316" s="23"/>
+      <c r="C316" s="21"/>
+      <c r="D316" s="21"/>
       <c r="E316" s="11"/>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="2"/>
-      <c r="B317" s="23" t="s">
+      <c r="B317" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="C317" s="23"/>
-      <c r="D317" s="23"/>
+      <c r="C317" s="21"/>
+      <c r="D317" s="21"/>
       <c r="E317" s="11"/>
     </row>
     <row r="318" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="2"/>
-      <c r="B318" s="23" t="s">
+      <c r="B318" s="21" t="s">
         <v>420</v>
       </c>
-      <c r="C318" s="23" t="s">
+      <c r="C318" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D318" s="23" t="s">
+      <c r="D318" s="21" t="s">
         <v>78</v>
       </c>
       <c r="E318" s="11" t="s">
@@ -6925,13 +6906,13 @@
     </row>
     <row r="319" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="2"/>
-      <c r="B319" s="23" t="s">
+      <c r="B319" s="21" t="s">
         <v>421</v>
       </c>
-      <c r="C319" s="23" t="s">
+      <c r="C319" s="21" t="s">
         <v>422</v>
       </c>
-      <c r="D319" s="23" t="s">
+      <c r="D319" s="21" t="s">
         <v>423</v>
       </c>
       <c r="E319" s="11" t="s">
@@ -6940,109 +6921,109 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="2"/>
-      <c r="B320" s="22"/>
-      <c r="C320" s="23"/>
-      <c r="D320" s="23"/>
+      <c r="B320" s="20"/>
+      <c r="C320" s="21"/>
+      <c r="D320" s="21"/>
       <c r="E320" s="11"/>
     </row>
     <row r="321" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="6"/>
-      <c r="B321" s="24" t="s">
+      <c r="B321" s="22" t="s">
         <v>424</v>
       </c>
-      <c r="C321" s="25"/>
-      <c r="D321" s="25"/>
+      <c r="C321" s="23"/>
+      <c r="D321" s="23"/>
       <c r="E321" s="8"/>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B322" s="22"/>
-      <c r="C322" s="23"/>
-      <c r="D322" s="23"/>
+      <c r="B322" s="20"/>
+      <c r="C322" s="21"/>
+      <c r="D322" s="21"/>
       <c r="E322" s="11"/>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="2"/>
-      <c r="B323" s="23" t="s">
+      <c r="B323" s="21" t="s">
         <v>425</v>
       </c>
-      <c r="C323" s="23"/>
-      <c r="D323" s="23"/>
+      <c r="C323" s="21"/>
+      <c r="D323" s="21"/>
       <c r="E323" s="11"/>
     </row>
     <row r="324" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="2"/>
-      <c r="B324" s="23" t="s">
+      <c r="B324" s="21" t="s">
         <v>426</v>
       </c>
-      <c r="C324" s="23"/>
-      <c r="D324" s="23"/>
+      <c r="C324" s="21"/>
+      <c r="D324" s="21"/>
       <c r="E324" s="11"/>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="2"/>
-      <c r="B325" s="23" t="s">
+      <c r="B325" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="C325" s="23"/>
-      <c r="D325" s="23"/>
+      <c r="C325" s="21"/>
+      <c r="D325" s="21"/>
       <c r="E325" s="11"/>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="2"/>
-      <c r="B326" s="23" t="s">
+      <c r="B326" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C326" s="23" t="s">
+      <c r="C326" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D326" s="23"/>
+      <c r="D326" s="21"/>
       <c r="E326" s="11"/>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="2"/>
-      <c r="B327" s="23" t="s">
+      <c r="B327" s="21" t="s">
         <v>427</v>
       </c>
-      <c r="C327" s="23" t="s">
+      <c r="C327" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D327" s="23"/>
+      <c r="D327" s="21"/>
       <c r="E327" s="11"/>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="2"/>
-      <c r="B328" s="23" t="s">
+      <c r="B328" s="21" t="s">
         <v>428</v>
       </c>
-      <c r="C328" s="23" t="s">
+      <c r="C328" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="D328" s="23"/>
+      <c r="D328" s="21"/>
       <c r="E328" s="11"/>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="2"/>
-      <c r="B329" s="23" t="s">
+      <c r="B329" s="21" t="s">
         <v>430</v>
       </c>
-      <c r="C329" s="23" t="s">
+      <c r="C329" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D329" s="23"/>
+      <c r="D329" s="21"/>
       <c r="E329" s="11"/>
     </row>
     <row r="330" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="2"/>
-      <c r="B330" s="23" t="s">
+      <c r="B330" s="21" t="s">
         <v>431</v>
       </c>
-      <c r="C330" s="23" t="s">
+      <c r="C330" s="21" t="s">
         <v>432</v>
       </c>
-      <c r="D330" s="23" t="s">
+      <c r="D330" s="21" t="s">
         <v>433</v>
       </c>
       <c r="E330" s="11" t="s">
@@ -7051,13 +7032,13 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="2"/>
-      <c r="B331" s="23" t="s">
+      <c r="B331" s="21" t="s">
         <v>435</v>
       </c>
-      <c r="C331" s="23" t="s">
+      <c r="C331" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D331" s="23" t="s">
+      <c r="D331" s="21" t="s">
         <v>78</v>
       </c>
       <c r="E331" s="11" t="s">
@@ -7066,47 +7047,47 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="2"/>
-      <c r="B332" s="23"/>
-      <c r="C332" s="23"/>
-      <c r="D332" s="23"/>
+      <c r="B332" s="21"/>
+      <c r="C332" s="21"/>
+      <c r="D332" s="21"/>
       <c r="E332" s="11"/>
     </row>
     <row r="333" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="6"/>
-      <c r="B333" s="24" t="s">
+      <c r="B333" s="22" t="s">
         <v>436</v>
       </c>
-      <c r="C333" s="25"/>
-      <c r="D333" s="25"/>
+      <c r="C333" s="23"/>
+      <c r="D333" s="23"/>
       <c r="E333" s="8"/>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B334" s="22"/>
-      <c r="C334" s="23"/>
-      <c r="D334" s="23"/>
+      <c r="B334" s="20"/>
+      <c r="C334" s="21"/>
+      <c r="D334" s="21"/>
       <c r="E334" s="11"/>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="2"/>
-      <c r="B335" s="23" t="s">
+      <c r="B335" s="21" t="s">
         <v>437</v>
       </c>
-      <c r="C335" s="23"/>
-      <c r="D335" s="23"/>
+      <c r="C335" s="21"/>
+      <c r="D335" s="21"/>
       <c r="E335" s="11"/>
     </row>
     <row r="336" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="2"/>
-      <c r="B336" s="23" t="s">
+      <c r="B336" s="21" t="s">
         <v>438</v>
       </c>
-      <c r="C336" s="23" t="s">
+      <c r="C336" s="21" t="s">
         <v>439</v>
       </c>
-      <c r="D336" s="23" t="s">
+      <c r="D336" s="21" t="s">
         <v>440</v>
       </c>
       <c r="E336" s="11" t="s">
@@ -7115,84 +7096,84 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="2"/>
-      <c r="B337" s="23" t="s">
+      <c r="B337" s="21" t="s">
         <v>441</v>
       </c>
-      <c r="C337" s="23"/>
-      <c r="D337" s="23"/>
+      <c r="C337" s="21"/>
+      <c r="D337" s="21"/>
       <c r="E337" s="11"/>
     </row>
     <row r="338" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="2"/>
-      <c r="B338" s="23" t="s">
+      <c r="B338" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="C338" s="23"/>
-      <c r="D338" s="23"/>
+      <c r="C338" s="21"/>
+      <c r="D338" s="21"/>
       <c r="E338" s="11"/>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="2"/>
-      <c r="B339" s="23" t="s">
+      <c r="B339" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="C339" s="23"/>
-      <c r="D339" s="23"/>
+      <c r="C339" s="21"/>
+      <c r="D339" s="21"/>
       <c r="E339" s="11"/>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="2"/>
-      <c r="B340" s="23" t="s">
+      <c r="B340" s="21" t="s">
         <v>346</v>
       </c>
-      <c r="C340" s="23" t="s">
+      <c r="C340" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D340" s="23"/>
+      <c r="D340" s="21"/>
       <c r="E340" s="11"/>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="2"/>
-      <c r="B341" s="23" t="s">
+      <c r="B341" s="21" t="s">
         <v>442</v>
       </c>
-      <c r="C341" s="23" t="s">
+      <c r="C341" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D341" s="23"/>
+      <c r="D341" s="21"/>
       <c r="E341" s="11"/>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="2"/>
-      <c r="B342" s="23" t="s">
+      <c r="B342" s="21" t="s">
         <v>443</v>
       </c>
-      <c r="C342" s="23" t="s">
+      <c r="C342" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="D342" s="23"/>
+      <c r="D342" s="21"/>
       <c r="E342" s="11"/>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="2"/>
-      <c r="B343" s="23" t="s">
+      <c r="B343" s="21" t="s">
         <v>444</v>
       </c>
-      <c r="C343" s="23" t="s">
+      <c r="C343" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D343" s="23"/>
+      <c r="D343" s="21"/>
       <c r="E343" s="11"/>
     </row>
     <row r="344" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="2"/>
-      <c r="B344" s="23" t="s">
+      <c r="B344" s="21" t="s">
         <v>445</v>
       </c>
-      <c r="C344" s="23" t="s">
+      <c r="C344" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D344" s="23" t="s">
+      <c r="D344" s="21" t="s">
         <v>78</v>
       </c>
       <c r="E344" s="11" t="s">
@@ -7201,13 +7182,13 @@
     </row>
     <row r="345" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="2"/>
-      <c r="B345" s="23" t="s">
+      <c r="B345" s="21" t="s">
         <v>446</v>
       </c>
-      <c r="C345" s="23" t="s">
+      <c r="C345" s="21" t="s">
         <v>447</v>
       </c>
-      <c r="D345" s="23" t="s">
+      <c r="D345" s="21" t="s">
         <v>448</v>
       </c>
       <c r="E345" s="11" t="s">
@@ -7216,47 +7197,47 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="2"/>
-      <c r="B346" s="23"/>
-      <c r="C346" s="23"/>
-      <c r="D346" s="23"/>
+      <c r="B346" s="21"/>
+      <c r="C346" s="21"/>
+      <c r="D346" s="21"/>
       <c r="E346" s="11"/>
     </row>
     <row r="347" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="6"/>
-      <c r="B347" s="24" t="s">
+      <c r="B347" s="22" t="s">
         <v>449</v>
       </c>
-      <c r="C347" s="25"/>
-      <c r="D347" s="25"/>
+      <c r="C347" s="23"/>
+      <c r="D347" s="23"/>
       <c r="E347" s="8"/>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B348" s="22"/>
-      <c r="C348" s="23"/>
-      <c r="D348" s="23"/>
+      <c r="B348" s="20"/>
+      <c r="C348" s="21"/>
+      <c r="D348" s="21"/>
       <c r="E348" s="11"/>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="2"/>
-      <c r="B349" s="23" t="s">
+      <c r="B349" s="21" t="s">
         <v>450</v>
       </c>
-      <c r="C349" s="23"/>
-      <c r="D349" s="23"/>
+      <c r="C349" s="21"/>
+      <c r="D349" s="21"/>
       <c r="E349" s="11"/>
     </row>
     <row r="350" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="2"/>
-      <c r="B350" s="23" t="s">
+      <c r="B350" s="21" t="s">
         <v>451</v>
       </c>
-      <c r="C350" s="23" t="s">
+      <c r="C350" s="21" t="s">
         <v>439</v>
       </c>
-      <c r="D350" s="23" t="s">
+      <c r="D350" s="21" t="s">
         <v>440</v>
       </c>
       <c r="E350" s="11" t="s">
@@ -7265,31 +7246,31 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="2"/>
-      <c r="B351" s="23" t="s">
+      <c r="B351" s="21" t="s">
         <v>452</v>
       </c>
-      <c r="C351" s="23"/>
-      <c r="D351" s="23"/>
+      <c r="C351" s="21"/>
+      <c r="D351" s="21"/>
       <c r="E351" s="11"/>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="2"/>
-      <c r="B352" s="23" t="s">
+      <c r="B352" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="C352" s="23"/>
-      <c r="D352" s="23"/>
+      <c r="C352" s="21"/>
+      <c r="D352" s="21"/>
       <c r="E352" s="11"/>
     </row>
     <row r="353" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="2"/>
-      <c r="B353" s="23" t="s">
+      <c r="B353" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="C353" s="23" t="s">
+      <c r="C353" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D353" s="23" t="s">
+      <c r="D353" s="21" t="s">
         <v>78</v>
       </c>
       <c r="E353" s="11" t="s">
@@ -7298,13 +7279,13 @@
     </row>
     <row r="354" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="2"/>
-      <c r="B354" s="23" t="s">
+      <c r="B354" s="21" t="s">
         <v>454</v>
       </c>
-      <c r="C354" s="23" t="s">
+      <c r="C354" s="21" t="s">
         <v>455</v>
       </c>
-      <c r="D354" s="23" t="s">
+      <c r="D354" s="21" t="s">
         <v>456</v>
       </c>
       <c r="E354" s="11" t="s">
@@ -7313,56 +7294,56 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="2"/>
-      <c r="B355" s="23"/>
-      <c r="C355" s="23"/>
-      <c r="D355" s="23"/>
+      <c r="B355" s="21"/>
+      <c r="C355" s="21"/>
+      <c r="D355" s="21"/>
       <c r="E355" s="11"/>
     </row>
     <row r="356" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="6"/>
-      <c r="B356" s="24" t="s">
+      <c r="B356" s="22" t="s">
         <v>457</v>
       </c>
-      <c r="C356" s="25"/>
-      <c r="D356" s="25"/>
+      <c r="C356" s="23"/>
+      <c r="D356" s="23"/>
       <c r="E356" s="8"/>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B357" s="22"/>
-      <c r="C357" s="23"/>
-      <c r="D357" s="23"/>
+      <c r="B357" s="20"/>
+      <c r="C357" s="21"/>
+      <c r="D357" s="21"/>
       <c r="E357" s="11"/>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2"/>
-      <c r="B358" s="23" t="s">
+      <c r="B358" s="21" t="s">
         <v>458</v>
       </c>
-      <c r="C358" s="23"/>
-      <c r="D358" s="23"/>
+      <c r="C358" s="21"/>
+      <c r="D358" s="21"/>
       <c r="E358" s="11"/>
     </row>
     <row r="359" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="2"/>
-      <c r="B359" s="23" t="s">
+      <c r="B359" s="21" t="s">
         <v>459</v>
       </c>
-      <c r="C359" s="23"/>
-      <c r="D359" s="23"/>
+      <c r="C359" s="21"/>
+      <c r="D359" s="21"/>
       <c r="E359" s="11"/>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="2"/>
-      <c r="B360" s="23" t="s">
+      <c r="B360" s="21" t="s">
         <v>460</v>
       </c>
-      <c r="C360" s="23" t="s">
+      <c r="C360" s="21" t="s">
         <v>461</v>
       </c>
-      <c r="D360" s="23" t="s">
+      <c r="D360" s="21" t="s">
         <v>462</v>
       </c>
       <c r="E360" s="11" t="s">
@@ -7371,40 +7352,40 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="2"/>
-      <c r="B361" s="23" t="s">
+      <c r="B361" s="21" t="s">
         <v>463</v>
       </c>
-      <c r="C361" s="23"/>
-      <c r="D361" s="23"/>
+      <c r="C361" s="21"/>
+      <c r="D361" s="21"/>
       <c r="E361" s="11"/>
     </row>
     <row r="362" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="2"/>
-      <c r="B362" s="23" t="s">
+      <c r="B362" s="21" t="s">
         <v>464</v>
       </c>
-      <c r="C362" s="23"/>
-      <c r="D362" s="23"/>
+      <c r="C362" s="21"/>
+      <c r="D362" s="21"/>
       <c r="E362" s="11"/>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="2"/>
-      <c r="B363" s="23" t="s">
+      <c r="B363" s="21" t="s">
         <v>465</v>
       </c>
-      <c r="C363" s="23"/>
-      <c r="D363" s="23"/>
+      <c r="C363" s="21"/>
+      <c r="D363" s="21"/>
       <c r="E363" s="11"/>
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="2"/>
-      <c r="B364" s="23" t="s">
+      <c r="B364" s="21" t="s">
         <v>466</v>
       </c>
-      <c r="C364" s="23" t="s">
+      <c r="C364" s="21" t="s">
         <v>467</v>
       </c>
-      <c r="D364" s="23" t="s">
+      <c r="D364" s="21" t="s">
         <v>468</v>
       </c>
       <c r="E364" s="11" t="s">
@@ -7413,13 +7394,13 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="2"/>
-      <c r="B365" s="23" t="s">
+      <c r="B365" s="21" t="s">
         <v>469</v>
       </c>
-      <c r="C365" s="23" t="s">
+      <c r="C365" s="21" t="s">
         <v>470</v>
       </c>
-      <c r="D365" s="23" t="s">
+      <c r="D365" s="21" t="s">
         <v>471</v>
       </c>
       <c r="E365" s="11" t="s">
@@ -7428,24 +7409,24 @@
     </row>
     <row r="366" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="2"/>
-      <c r="B366" s="23" t="s">
+      <c r="B366" s="21" t="s">
         <v>472</v>
       </c>
-      <c r="C366" s="23" t="s">
+      <c r="C366" s="21" t="s">
         <v>410</v>
       </c>
-      <c r="D366" s="23"/>
+      <c r="D366" s="21"/>
       <c r="E366" s="11"/>
     </row>
     <row r="367" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="2"/>
-      <c r="B367" s="23" t="s">
+      <c r="B367" s="21" t="s">
         <v>473</v>
       </c>
-      <c r="C367" s="23" t="s">
+      <c r="C367" s="21" t="s">
         <v>474</v>
       </c>
-      <c r="D367" s="23" t="s">
+      <c r="D367" s="21" t="s">
         <v>475</v>
       </c>
       <c r="E367" s="11" t="s">
@@ -7454,13 +7435,13 @@
     </row>
     <row r="368" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="2"/>
-      <c r="B368" s="23" t="s">
+      <c r="B368" s="21" t="s">
         <v>476</v>
       </c>
-      <c r="C368" s="23" t="s">
+      <c r="C368" s="21" t="s">
         <v>477</v>
       </c>
-      <c r="D368" s="23" t="s">
+      <c r="D368" s="21" t="s">
         <v>478</v>
       </c>
       <c r="E368" s="11" t="s">
@@ -7469,13 +7450,13 @@
     </row>
     <row r="369" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="2"/>
-      <c r="B369" s="23" t="s">
+      <c r="B369" s="21" t="s">
         <v>479</v>
       </c>
-      <c r="C369" s="23" t="s">
+      <c r="C369" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D369" s="23" t="s">
+      <c r="D369" s="21" t="s">
         <v>78</v>
       </c>
       <c r="E369" s="11" t="s">
@@ -7484,47 +7465,47 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="2"/>
-      <c r="B370" s="23"/>
-      <c r="C370" s="23"/>
-      <c r="D370" s="23"/>
+      <c r="B370" s="21"/>
+      <c r="C370" s="21"/>
+      <c r="D370" s="21"/>
       <c r="E370" s="11"/>
     </row>
     <row r="371" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="28"/>
-      <c r="B371" s="24" t="s">
+      <c r="A371" s="26"/>
+      <c r="B371" s="22" t="s">
         <v>480</v>
       </c>
-      <c r="C371" s="25"/>
-      <c r="D371" s="25"/>
-      <c r="E371" s="25"/>
+      <c r="C371" s="23"/>
+      <c r="D371" s="23"/>
+      <c r="E371" s="23"/>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B372" s="22"/>
-      <c r="C372" s="23"/>
-      <c r="D372" s="23"/>
+      <c r="B372" s="20"/>
+      <c r="C372" s="21"/>
+      <c r="D372" s="21"/>
       <c r="E372" s="11"/>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="2"/>
-      <c r="B373" s="23" t="s">
+      <c r="B373" s="21" t="s">
         <v>481</v>
       </c>
-      <c r="C373" s="23"/>
-      <c r="D373" s="23"/>
+      <c r="C373" s="21"/>
+      <c r="D373" s="21"/>
       <c r="E373" s="11"/>
     </row>
     <row r="374" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="2"/>
-      <c r="B374" s="23" t="s">
+      <c r="B374" s="21" t="s">
         <v>482</v>
       </c>
-      <c r="C374" s="23" t="s">
+      <c r="C374" s="21" t="s">
         <v>483</v>
       </c>
-      <c r="D374" s="23" t="s">
+      <c r="D374" s="21" t="s">
         <v>484</v>
       </c>
       <c r="E374" s="11" t="s">
@@ -7533,84 +7514,84 @@
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="2"/>
-      <c r="B375" s="23" t="s">
+      <c r="B375" s="21" t="s">
         <v>485</v>
       </c>
-      <c r="C375" s="23"/>
-      <c r="D375" s="23"/>
+      <c r="C375" s="21"/>
+      <c r="D375" s="21"/>
       <c r="E375" s="11"/>
     </row>
     <row r="376" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="2"/>
-      <c r="B376" s="23" t="s">
+      <c r="B376" s="21" t="s">
         <v>486</v>
       </c>
-      <c r="C376" s="23"/>
-      <c r="D376" s="23"/>
+      <c r="C376" s="21"/>
+      <c r="D376" s="21"/>
       <c r="E376" s="11"/>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="2"/>
-      <c r="B377" s="23" t="s">
+      <c r="B377" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="C377" s="23"/>
-      <c r="D377" s="23"/>
+      <c r="C377" s="21"/>
+      <c r="D377" s="21"/>
       <c r="E377" s="11"/>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="2"/>
-      <c r="B378" s="23" t="s">
+      <c r="B378" s="21" t="s">
         <v>487</v>
       </c>
-      <c r="C378" s="23" t="s">
+      <c r="C378" s="21" t="s">
         <v>467</v>
       </c>
-      <c r="D378" s="23"/>
+      <c r="D378" s="21"/>
       <c r="E378" s="11"/>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="2"/>
-      <c r="B379" s="23" t="s">
+      <c r="B379" s="21" t="s">
         <v>488</v>
       </c>
-      <c r="C379" s="23" t="s">
+      <c r="C379" s="21" t="s">
         <v>470</v>
       </c>
-      <c r="D379" s="23"/>
+      <c r="D379" s="21"/>
       <c r="E379" s="11"/>
     </row>
     <row r="380" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2"/>
-      <c r="B380" s="23" t="s">
+      <c r="B380" s="21" t="s">
         <v>489</v>
       </c>
-      <c r="C380" s="23" t="s">
+      <c r="C380" s="21" t="s">
         <v>410</v>
       </c>
-      <c r="D380" s="23"/>
+      <c r="D380" s="21"/>
       <c r="E380" s="11"/>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="2"/>
-      <c r="B381" s="23" t="s">
+      <c r="B381" s="21" t="s">
         <v>490</v>
       </c>
-      <c r="C381" s="23" t="s">
+      <c r="C381" s="21" t="s">
         <v>474</v>
       </c>
-      <c r="D381" s="23"/>
+      <c r="D381" s="21"/>
       <c r="E381" s="11"/>
     </row>
     <row r="382" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="2"/>
-      <c r="B382" s="23" t="s">
+      <c r="B382" s="21" t="s">
         <v>491</v>
       </c>
-      <c r="C382" s="23" t="s">
+      <c r="C382" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D382" s="23" t="s">
+      <c r="D382" s="21" t="s">
         <v>78</v>
       </c>
       <c r="E382" s="11" t="s">
@@ -7619,13 +7600,13 @@
     </row>
     <row r="383" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="2"/>
-      <c r="B383" s="23" t="s">
+      <c r="B383" s="21" t="s">
         <v>492</v>
       </c>
-      <c r="C383" s="23" t="s">
+      <c r="C383" s="21" t="s">
         <v>493</v>
       </c>
-      <c r="D383" s="23" t="s">
+      <c r="D383" s="21" t="s">
         <v>494</v>
       </c>
       <c r="E383" s="11" t="s">
@@ -7634,47 +7615,47 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="2"/>
-      <c r="B384" s="23"/>
-      <c r="C384" s="23"/>
-      <c r="D384" s="23"/>
+      <c r="B384" s="21"/>
+      <c r="C384" s="21"/>
+      <c r="D384" s="21"/>
       <c r="E384" s="11"/>
     </row>
     <row r="385" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="6"/>
-      <c r="B385" s="24" t="s">
+      <c r="B385" s="22" t="s">
         <v>495</v>
       </c>
-      <c r="C385" s="25"/>
-      <c r="D385" s="25"/>
+      <c r="C385" s="23"/>
+      <c r="D385" s="23"/>
       <c r="E385" s="8"/>
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B386" s="22"/>
-      <c r="C386" s="23"/>
-      <c r="D386" s="23"/>
+      <c r="B386" s="20"/>
+      <c r="C386" s="21"/>
+      <c r="D386" s="21"/>
       <c r="E386" s="11"/>
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="2"/>
-      <c r="B387" s="23" t="s">
+      <c r="B387" s="21" t="s">
         <v>496</v>
       </c>
-      <c r="C387" s="23"/>
-      <c r="D387" s="23"/>
+      <c r="C387" s="21"/>
+      <c r="D387" s="21"/>
       <c r="E387" s="11"/>
     </row>
     <row r="388" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="2"/>
-      <c r="B388" s="23" t="s">
+      <c r="B388" s="21" t="s">
         <v>497</v>
       </c>
-      <c r="C388" s="23" t="s">
+      <c r="C388" s="21" t="s">
         <v>483</v>
       </c>
-      <c r="D388" s="23" t="s">
+      <c r="D388" s="21" t="s">
         <v>484</v>
       </c>
       <c r="E388" s="11" t="s">
@@ -7683,42 +7664,42 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="2"/>
-      <c r="B389" s="23" t="s">
+      <c r="B389" s="21" t="s">
         <v>498</v>
       </c>
-      <c r="C389" s="23"/>
-      <c r="D389" s="23"/>
+      <c r="C389" s="21"/>
+      <c r="D389" s="21"/>
       <c r="E389" s="11"/>
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="2"/>
-      <c r="B390" s="23" t="s">
+      <c r="B390" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="C390" s="23"/>
-      <c r="D390" s="23"/>
+      <c r="C390" s="21"/>
+      <c r="D390" s="21"/>
       <c r="E390" s="11"/>
     </row>
     <row r="391" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="2"/>
-      <c r="B391" s="23" t="s">
+      <c r="B391" s="21" t="s">
         <v>499</v>
       </c>
-      <c r="C391" s="23" t="s">
+      <c r="C391" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D391" s="23"/>
+      <c r="D391" s="21"/>
       <c r="E391" s="11"/>
     </row>
     <row r="392" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="2"/>
-      <c r="B392" s="23" t="s">
+      <c r="B392" s="21" t="s">
         <v>500</v>
       </c>
-      <c r="C392" s="23" t="s">
+      <c r="C392" s="21" t="s">
         <v>501</v>
       </c>
-      <c r="D392" s="23" t="s">
+      <c r="D392" s="21" t="s">
         <v>502</v>
       </c>
       <c r="E392" s="11" t="s">
@@ -7726,133 +7707,133 @@
       </c>
     </row>
     <row r="393" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A393" s="29"/>
-      <c r="B393" s="23"/>
-      <c r="C393" s="23"/>
-      <c r="D393" s="23"/>
+      <c r="A393" s="27"/>
+      <c r="B393" s="21"/>
+      <c r="C393" s="21"/>
+      <c r="D393" s="21"/>
       <c r="E393" s="11"/>
     </row>
     <row r="394" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A394" s="30"/>
-      <c r="B394" s="31" t="s">
+      <c r="A394" s="28"/>
+      <c r="B394" s="29" t="s">
         <v>503</v>
       </c>
-      <c r="C394" s="32"/>
-      <c r="D394" s="32"/>
-      <c r="E394" s="33"/>
+      <c r="C394" s="30"/>
+      <c r="D394" s="30"/>
+      <c r="E394" s="31"/>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B395" s="22"/>
-      <c r="C395" s="23"/>
-      <c r="D395" s="23"/>
+      <c r="B395" s="20"/>
+      <c r="C395" s="21"/>
+      <c r="D395" s="21"/>
       <c r="E395" s="11"/>
     </row>
     <row r="396" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="2"/>
-      <c r="B396" s="23" t="s">
+      <c r="B396" s="21" t="s">
         <v>504</v>
       </c>
-      <c r="C396" s="23"/>
-      <c r="D396" s="23"/>
+      <c r="C396" s="21"/>
+      <c r="D396" s="21"/>
       <c r="E396" s="11"/>
     </row>
     <row r="397" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="2"/>
-      <c r="B397" s="23" t="s">
+      <c r="B397" s="21" t="s">
         <v>505</v>
       </c>
-      <c r="C397" s="23"/>
-      <c r="D397" s="23"/>
+      <c r="C397" s="21"/>
+      <c r="D397" s="21"/>
       <c r="E397" s="11"/>
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="2"/>
-      <c r="B398" s="23" t="s">
+      <c r="B398" s="21" t="s">
         <v>460</v>
       </c>
-      <c r="C398" s="23" t="s">
+      <c r="C398" s="21" t="s">
         <v>461</v>
       </c>
-      <c r="D398" s="23"/>
+      <c r="D398" s="21"/>
       <c r="E398" s="11"/>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="2"/>
-      <c r="B399" s="23" t="s">
+      <c r="B399" s="21" t="s">
         <v>463</v>
       </c>
-      <c r="C399" s="23"/>
-      <c r="D399" s="23"/>
+      <c r="C399" s="21"/>
+      <c r="D399" s="21"/>
       <c r="E399" s="11"/>
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="2"/>
-      <c r="B400" s="23" t="s">
+      <c r="B400" s="21" t="s">
         <v>506</v>
       </c>
-      <c r="C400" s="23"/>
-      <c r="D400" s="23"/>
+      <c r="C400" s="21"/>
+      <c r="D400" s="21"/>
       <c r="E400" s="11"/>
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="2"/>
-      <c r="B401" s="23" t="s">
+      <c r="B401" s="21" t="s">
         <v>507</v>
       </c>
-      <c r="C401" s="23"/>
-      <c r="D401" s="23"/>
+      <c r="C401" s="21"/>
+      <c r="D401" s="21"/>
       <c r="E401" s="11"/>
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2"/>
-      <c r="B402" s="23" t="s">
+      <c r="B402" s="21" t="s">
         <v>508</v>
       </c>
-      <c r="C402" s="23"/>
-      <c r="D402" s="23"/>
+      <c r="C402" s="21"/>
+      <c r="D402" s="21"/>
       <c r="E402" s="11"/>
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="2"/>
-      <c r="B403" s="23" t="s">
+      <c r="B403" s="21" t="s">
         <v>509</v>
       </c>
-      <c r="C403" s="23"/>
-      <c r="D403" s="23"/>
+      <c r="C403" s="21"/>
+      <c r="D403" s="21"/>
       <c r="E403" s="11"/>
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="2"/>
-      <c r="B404" s="23" t="s">
+      <c r="B404" s="21" t="s">
         <v>510</v>
       </c>
-      <c r="C404" s="23"/>
-      <c r="D404" s="23"/>
+      <c r="C404" s="21"/>
+      <c r="D404" s="21"/>
       <c r="E404" s="11"/>
     </row>
     <row r="405" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="2"/>
-      <c r="B405" s="23" t="s">
+      <c r="B405" s="21" t="s">
         <v>511</v>
       </c>
-      <c r="C405" s="23" t="s">
+      <c r="C405" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D405" s="23"/>
+      <c r="D405" s="21"/>
       <c r="E405" s="11"/>
     </row>
     <row r="406" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="2"/>
-      <c r="B406" s="23" t="s">
+      <c r="B406" s="21" t="s">
         <v>512</v>
       </c>
-      <c r="C406" s="23" t="s">
+      <c r="C406" s="21" t="s">
         <v>513</v>
       </c>
-      <c r="D406" s="23" t="s">
+      <c r="D406" s="21" t="s">
         <v>514</v>
       </c>
       <c r="E406" s="11" t="s">
@@ -7861,13 +7842,13 @@
     </row>
     <row r="407" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="2"/>
-      <c r="B407" s="23" t="s">
+      <c r="B407" s="21" t="s">
         <v>516</v>
       </c>
-      <c r="C407" s="23" t="s">
+      <c r="C407" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D407" s="23" t="s">
+      <c r="D407" s="21" t="s">
         <v>78</v>
       </c>
       <c r="E407" s="11" t="s">
@@ -7876,67 +7857,67 @@
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="2"/>
-      <c r="B408" s="23"/>
-      <c r="C408" s="23"/>
-      <c r="D408" s="23"/>
+      <c r="B408" s="21"/>
+      <c r="C408" s="21"/>
+      <c r="D408" s="21"/>
       <c r="E408" s="11"/>
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B409" s="23" t="s">
+      <c r="B409" s="21" t="s">
         <v>517</v>
       </c>
-      <c r="C409" s="23"/>
-      <c r="D409" s="23"/>
+      <c r="C409" s="21"/>
+      <c r="D409" s="21"/>
       <c r="E409" s="11"/>
     </row>
     <row r="410" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="2"/>
-      <c r="B410" s="23" t="s">
+      <c r="B410" s="21" t="s">
         <v>518</v>
       </c>
-      <c r="C410" s="23"/>
-      <c r="D410" s="23"/>
+      <c r="C410" s="21"/>
+      <c r="D410" s="21"/>
       <c r="E410" s="11"/>
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="2"/>
-      <c r="B411" s="23" t="s">
+      <c r="B411" s="21" t="s">
         <v>519</v>
       </c>
-      <c r="C411" s="23"/>
-      <c r="D411" s="23"/>
+      <c r="C411" s="21"/>
+      <c r="D411" s="21"/>
       <c r="E411" s="11"/>
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="2"/>
-      <c r="B412" s="23" t="s">
+      <c r="B412" s="21" t="s">
         <v>520</v>
       </c>
-      <c r="C412" s="23"/>
-      <c r="D412" s="23"/>
+      <c r="C412" s="21"/>
+      <c r="D412" s="21"/>
       <c r="E412" s="11"/>
     </row>
     <row r="413" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="2"/>
-      <c r="B413" s="23" t="s">
+      <c r="B413" s="21" t="s">
         <v>521</v>
       </c>
-      <c r="C413" s="23"/>
-      <c r="D413" s="23"/>
+      <c r="C413" s="21"/>
+      <c r="D413" s="21"/>
       <c r="E413" s="11"/>
     </row>
     <row r="414" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="2"/>
-      <c r="B414" s="23" t="s">
+      <c r="B414" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="C414" s="23" t="s">
+      <c r="C414" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="D414" s="23" t="s">
+      <c r="D414" s="21" t="s">
         <v>524</v>
       </c>
       <c r="E414" s="11" t="s">
@@ -7945,40 +7926,40 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="2"/>
-      <c r="B415" s="23" t="s">
+      <c r="B415" s="21" t="s">
         <v>525</v>
       </c>
-      <c r="C415" s="23"/>
-      <c r="D415" s="23"/>
+      <c r="C415" s="21"/>
+      <c r="D415" s="21"/>
       <c r="E415" s="11"/>
     </row>
     <row r="416" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="2"/>
-      <c r="B416" s="23" t="s">
+      <c r="B416" s="21" t="s">
         <v>526</v>
       </c>
-      <c r="C416" s="23"/>
-      <c r="D416" s="23"/>
+      <c r="C416" s="21"/>
+      <c r="D416" s="21"/>
       <c r="E416" s="11"/>
     </row>
     <row r="417" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="2"/>
-      <c r="B417" s="23" t="s">
+      <c r="B417" s="21" t="s">
         <v>527</v>
       </c>
-      <c r="C417" s="23"/>
-      <c r="D417" s="23"/>
+      <c r="C417" s="21"/>
+      <c r="D417" s="21"/>
       <c r="E417" s="11"/>
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="2"/>
-      <c r="B418" s="23" t="s">
+      <c r="B418" s="21" t="s">
         <v>528</v>
       </c>
-      <c r="C418" s="23" t="s">
+      <c r="C418" s="21" t="s">
         <v>529</v>
       </c>
-      <c r="D418" s="23" t="s">
+      <c r="D418" s="21" t="s">
         <v>530</v>
       </c>
       <c r="E418" s="11" t="s">
@@ -7987,56 +7968,56 @@
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="2"/>
-      <c r="B419" s="23" t="s">
+      <c r="B419" s="21" t="s">
         <v>531</v>
       </c>
-      <c r="C419" s="23"/>
-      <c r="D419" s="23"/>
+      <c r="C419" s="21"/>
+      <c r="D419" s="21"/>
       <c r="E419" s="11"/>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="2"/>
-      <c r="B420" s="23"/>
-      <c r="C420" s="23"/>
-      <c r="D420" s="23"/>
+      <c r="B420" s="21"/>
+      <c r="C420" s="21"/>
+      <c r="D420" s="21"/>
       <c r="E420" s="11"/>
     </row>
     <row r="421" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="6"/>
-      <c r="B421" s="24" t="s">
+      <c r="B421" s="22" t="s">
         <v>532</v>
       </c>
-      <c r="C421" s="25"/>
-      <c r="D421" s="25"/>
+      <c r="C421" s="23"/>
+      <c r="D421" s="23"/>
       <c r="E421" s="8"/>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B422" s="22"/>
-      <c r="C422" s="23"/>
-      <c r="D422" s="23"/>
+      <c r="B422" s="20"/>
+      <c r="C422" s="21"/>
+      <c r="D422" s="21"/>
       <c r="E422" s="11"/>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2"/>
-      <c r="B423" s="23" t="s">
+      <c r="B423" s="21" t="s">
         <v>533</v>
       </c>
-      <c r="C423" s="23"/>
-      <c r="D423" s="23"/>
+      <c r="C423" s="21"/>
+      <c r="D423" s="21"/>
       <c r="E423" s="11"/>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2"/>
-      <c r="B424" s="23" t="s">
+      <c r="B424" s="21" t="s">
         <v>534</v>
       </c>
-      <c r="C424" s="23" t="s">
+      <c r="C424" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="D424" s="23" t="s">
+      <c r="D424" s="21" t="s">
         <v>536</v>
       </c>
       <c r="E424" s="11" t="s">
@@ -8045,91 +8026,91 @@
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2"/>
-      <c r="B425" s="23" t="s">
+      <c r="B425" s="21" t="s">
         <v>537</v>
       </c>
-      <c r="C425" s="23"/>
-      <c r="D425" s="23"/>
+      <c r="C425" s="21"/>
+      <c r="D425" s="21"/>
       <c r="E425" s="11"/>
     </row>
     <row r="426" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2"/>
-      <c r="B426" s="23" t="s">
+      <c r="B426" s="21" t="s">
         <v>538</v>
       </c>
-      <c r="C426" s="23"/>
-      <c r="D426" s="23"/>
+      <c r="C426" s="21"/>
+      <c r="D426" s="21"/>
       <c r="E426" s="11"/>
     </row>
     <row r="427" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2"/>
-      <c r="B427" s="23" t="s">
+      <c r="B427" s="21" t="s">
         <v>539</v>
       </c>
-      <c r="C427" s="23"/>
-      <c r="D427" s="23"/>
+      <c r="C427" s="21"/>
+      <c r="D427" s="21"/>
       <c r="E427" s="11"/>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2"/>
-      <c r="B428" s="23" t="s">
+      <c r="B428" s="21" t="s">
         <v>540</v>
       </c>
-      <c r="C428" s="23"/>
-      <c r="D428" s="23"/>
+      <c r="C428" s="21"/>
+      <c r="D428" s="21"/>
       <c r="E428" s="11"/>
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="2"/>
-      <c r="B429" s="23" t="s">
+      <c r="B429" s="21" t="s">
         <v>541</v>
       </c>
-      <c r="C429" s="23"/>
-      <c r="D429" s="23"/>
+      <c r="C429" s="21"/>
+      <c r="D429" s="21"/>
       <c r="E429" s="11"/>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="2"/>
-      <c r="B430" s="23" t="s">
+      <c r="B430" s="21" t="s">
         <v>542</v>
       </c>
-      <c r="C430" s="23"/>
-      <c r="D430" s="23"/>
+      <c r="C430" s="21"/>
+      <c r="D430" s="21"/>
       <c r="E430" s="11"/>
     </row>
     <row r="431" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="2"/>
-      <c r="B431" s="23" t="s">
+      <c r="B431" s="21" t="s">
         <v>543</v>
       </c>
-      <c r="C431" s="23" t="s">
+      <c r="C431" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D431" s="23"/>
+      <c r="D431" s="21"/>
       <c r="E431" s="11"/>
-      <c r="F431" s="16"/>
+      <c r="F431" s="15"/>
       <c r="G431" s="1"/>
     </row>
     <row r="432" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2"/>
-      <c r="B432" s="23" t="s">
+      <c r="B432" s="21" t="s">
         <v>544</v>
       </c>
-      <c r="C432" s="23" t="s">
+      <c r="C432" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D432" s="23"/>
+      <c r="D432" s="21"/>
       <c r="E432" s="11"/>
     </row>
     <row r="433" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="2"/>
-      <c r="B433" s="23" t="s">
+      <c r="B433" s="21" t="s">
         <v>545</v>
       </c>
-      <c r="C433" s="23" t="s">
+      <c r="C433" s="21" t="s">
         <v>546</v>
       </c>
-      <c r="D433" s="23" t="s">
+      <c r="D433" s="21" t="s">
         <v>547</v>
       </c>
       <c r="E433" s="11" t="s">
@@ -8138,152 +8119,152 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="2"/>
-      <c r="B434" s="23"/>
-      <c r="C434" s="23"/>
-      <c r="D434" s="23"/>
+      <c r="B434" s="21"/>
+      <c r="C434" s="21"/>
+      <c r="D434" s="21"/>
       <c r="E434" s="11"/>
     </row>
     <row r="435" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B435" s="23" t="s">
+      <c r="B435" s="21" t="s">
         <v>548</v>
       </c>
-      <c r="C435" s="23"/>
-      <c r="D435" s="23"/>
+      <c r="C435" s="21"/>
+      <c r="D435" s="21"/>
       <c r="E435" s="11"/>
     </row>
     <row r="436" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2"/>
-      <c r="B436" s="23" t="s">
+      <c r="B436" s="21" t="s">
         <v>549</v>
       </c>
-      <c r="C436" s="23"/>
-      <c r="D436" s="23"/>
+      <c r="C436" s="21"/>
+      <c r="D436" s="21"/>
       <c r="E436" s="11"/>
     </row>
     <row r="437" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2"/>
-      <c r="B437" s="23" t="s">
+      <c r="B437" s="21" t="s">
         <v>550</v>
       </c>
-      <c r="C437" s="23" t="s">
+      <c r="C437" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="D437" s="23"/>
+      <c r="D437" s="21"/>
       <c r="E437" s="11"/>
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2"/>
-      <c r="B438" s="23" t="s">
+      <c r="B438" s="21" t="s">
         <v>551</v>
       </c>
-      <c r="C438" s="23"/>
-      <c r="D438" s="23"/>
+      <c r="C438" s="21"/>
+      <c r="D438" s="21"/>
       <c r="E438" s="11"/>
     </row>
     <row r="439" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="2"/>
-      <c r="B439" s="23" t="s">
+      <c r="B439" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="C439" s="23"/>
-      <c r="D439" s="23"/>
+      <c r="C439" s="21"/>
+      <c r="D439" s="21"/>
       <c r="E439" s="11"/>
     </row>
     <row r="440" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="2"/>
-      <c r="B440" s="23" t="s">
+      <c r="B440" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="C440" s="23"/>
-      <c r="D440" s="23"/>
+      <c r="C440" s="21"/>
+      <c r="D440" s="21"/>
       <c r="E440" s="11"/>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="2"/>
-      <c r="B441" s="23" t="s">
+      <c r="B441" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="C441" s="23" t="s">
+      <c r="C441" s="21" t="s">
         <v>529</v>
       </c>
-      <c r="D441" s="23"/>
+      <c r="D441" s="21"/>
       <c r="E441" s="11"/>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2"/>
-      <c r="B442" s="23" t="s">
+      <c r="B442" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="C442" s="23"/>
-      <c r="D442" s="23"/>
+      <c r="C442" s="21"/>
+      <c r="D442" s="21"/>
       <c r="E442" s="11"/>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2"/>
-      <c r="B443" s="23" t="s">
+      <c r="B443" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="C443" s="23"/>
-      <c r="D443" s="23"/>
+      <c r="C443" s="21"/>
+      <c r="D443" s="21"/>
       <c r="E443" s="11"/>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2"/>
-      <c r="B444" s="23" t="s">
+      <c r="B444" s="21" t="s">
         <v>557</v>
       </c>
-      <c r="C444" s="23"/>
-      <c r="D444" s="23"/>
+      <c r="C444" s="21"/>
+      <c r="D444" s="21"/>
       <c r="E444" s="11"/>
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2"/>
-      <c r="B445" s="23" t="s">
+      <c r="B445" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="C445" s="23"/>
-      <c r="D445" s="23"/>
+      <c r="C445" s="21"/>
+      <c r="D445" s="21"/>
       <c r="E445" s="11"/>
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2"/>
-      <c r="B446" s="23" t="s">
+      <c r="B446" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="C446" s="23"/>
-      <c r="D446" s="23"/>
+      <c r="C446" s="21"/>
+      <c r="D446" s="21"/>
       <c r="E446" s="11"/>
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="2"/>
-      <c r="B447" s="23" t="s">
+      <c r="B447" s="21" t="s">
         <v>560</v>
       </c>
-      <c r="C447" s="23"/>
-      <c r="D447" s="23"/>
+      <c r="C447" s="21"/>
+      <c r="D447" s="21"/>
       <c r="E447" s="11"/>
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="2"/>
-      <c r="B448" s="23" t="s">
+      <c r="B448" s="21" t="s">
         <v>561</v>
       </c>
-      <c r="C448" s="23"/>
-      <c r="D448" s="23"/>
+      <c r="C448" s="21"/>
+      <c r="D448" s="21"/>
       <c r="E448" s="11"/>
     </row>
     <row r="449" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="2"/>
-      <c r="B449" s="23" t="s">
+      <c r="B449" s="21" t="s">
         <v>562</v>
       </c>
-      <c r="C449" s="23" t="s">
+      <c r="C449" s="21" t="s">
         <v>563</v>
       </c>
-      <c r="D449" s="23" t="s">
+      <c r="D449" s="21" t="s">
         <v>564</v>
       </c>
       <c r="E449" s="11" t="s">
@@ -8292,176 +8273,178 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="2"/>
-      <c r="B450" s="23" t="s">
+      <c r="B450" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="C450" s="23"/>
-      <c r="D450" s="23"/>
+      <c r="C450" s="21"/>
+      <c r="D450" s="21"/>
       <c r="E450" s="11"/>
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="2"/>
-      <c r="B451" s="23" t="s">
+      <c r="B451" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="C451" s="23"/>
-      <c r="D451" s="23"/>
+      <c r="C451" s="21"/>
+      <c r="D451" s="21"/>
       <c r="E451" s="11"/>
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="2"/>
-      <c r="B452" s="23" t="s">
+      <c r="B452" s="21" t="s">
         <v>567</v>
       </c>
-      <c r="C452" s="23"/>
-      <c r="D452" s="23"/>
+      <c r="C452" s="21"/>
+      <c r="D452" s="21"/>
       <c r="E452" s="11"/>
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="2"/>
-      <c r="B453" s="23" t="s">
+      <c r="B453" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="C453" s="23"/>
-      <c r="D453" s="23"/>
+      <c r="C453" s="21"/>
+      <c r="D453" s="21"/>
       <c r="E453" s="11"/>
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2"/>
-      <c r="B454" s="23" t="s">
+      <c r="B454" s="21" t="s">
         <v>569</v>
       </c>
-      <c r="C454" s="23"/>
-      <c r="D454" s="23"/>
+      <c r="C454" s="21"/>
+      <c r="D454" s="21"/>
       <c r="E454" s="11"/>
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2"/>
-      <c r="B455" s="23" t="s">
+      <c r="B455" s="21" t="s">
         <v>570</v>
       </c>
-      <c r="C455" s="23"/>
-      <c r="D455" s="23"/>
+      <c r="C455" s="21"/>
+      <c r="D455" s="21"/>
       <c r="E455" s="11"/>
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2"/>
-      <c r="B456" s="23" t="s">
+      <c r="B456" s="21" t="s">
         <v>571</v>
       </c>
-      <c r="C456" s="23"/>
-      <c r="D456" s="23"/>
+      <c r="C456" s="21"/>
+      <c r="D456" s="21"/>
       <c r="E456" s="11"/>
     </row>
-    <row r="457" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2"/>
-      <c r="B457" s="23" t="s">
+      <c r="B457" s="21" t="s">
         <v>572</v>
       </c>
-      <c r="C457" s="34" t="s">
+      <c r="C457" s="21" t="s">
         <v>573</v>
       </c>
-      <c r="D457" s="23" t="s">
+      <c r="D457" s="21" t="s">
         <v>574</v>
       </c>
       <c r="E457" s="11" t="s">
         <v>575</v>
       </c>
-      <c r="F457" s="35"/>
+      <c r="F457" s="18" t="s">
+        <v>576</v>
+      </c>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2"/>
-      <c r="B458" s="23" t="s">
-        <v>576</v>
-      </c>
-      <c r="C458" s="23"/>
-      <c r="D458" s="23"/>
+      <c r="B458" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="C458" s="21"/>
+      <c r="D458" s="21"/>
       <c r="E458" s="11"/>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="2"/>
-      <c r="B459" s="23" t="s">
-        <v>577</v>
-      </c>
-      <c r="C459" s="23"/>
-      <c r="D459" s="23"/>
+      <c r="B459" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="C459" s="21"/>
+      <c r="D459" s="21"/>
       <c r="E459" s="11"/>
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="2"/>
-      <c r="B460" s="23" t="s">
-        <v>578</v>
-      </c>
-      <c r="C460" s="23"/>
-      <c r="D460" s="23"/>
+      <c r="B460" s="21" t="s">
+        <v>579</v>
+      </c>
+      <c r="C460" s="21"/>
+      <c r="D460" s="21"/>
       <c r="E460" s="11"/>
     </row>
     <row r="461" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="2"/>
-      <c r="B461" s="23" t="s">
-        <v>579</v>
-      </c>
-      <c r="C461" s="23"/>
-      <c r="D461" s="23"/>
+      <c r="B461" s="21" t="s">
+        <v>580</v>
+      </c>
+      <c r="C461" s="21"/>
+      <c r="D461" s="21"/>
       <c r="E461" s="11"/>
     </row>
     <row r="462" customFormat="false" ht="67.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="2"/>
-      <c r="B462" s="23" t="s">
-        <v>580</v>
-      </c>
-      <c r="C462" s="23" t="s">
+      <c r="B462" s="21" t="s">
         <v>581</v>
       </c>
-      <c r="D462" s="23" t="s">
+      <c r="C462" s="21" t="s">
         <v>582</v>
+      </c>
+      <c r="D462" s="21" t="s">
+        <v>583</v>
       </c>
       <c r="E462" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="F462" s="23"/>
+      <c r="F462" s="21"/>
     </row>
     <row r="463" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2"/>
-      <c r="B463" s="23" t="s">
-        <v>583</v>
-      </c>
-      <c r="C463" s="23"/>
-      <c r="D463" s="23"/>
+      <c r="B463" s="21" t="s">
+        <v>584</v>
+      </c>
+      <c r="C463" s="21"/>
+      <c r="D463" s="21"/>
       <c r="E463" s="11"/>
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2"/>
-      <c r="B464" s="23" t="s">
-        <v>584</v>
-      </c>
-      <c r="C464" s="23"/>
-      <c r="D464" s="23"/>
+      <c r="B464" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="C464" s="21"/>
+      <c r="D464" s="21"/>
       <c r="E464" s="11"/>
     </row>
     <row r="465" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2"/>
-      <c r="B465" s="23" t="s">
-        <v>585</v>
-      </c>
-      <c r="C465" s="23" t="s">
+      <c r="B465" s="21" t="s">
+        <v>586</v>
+      </c>
+      <c r="C465" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="D465" s="23"/>
+      <c r="D465" s="21"/>
       <c r="E465" s="11" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2"/>
-      <c r="B466" s="23" t="s">
-        <v>586</v>
-      </c>
-      <c r="C466" s="23" t="s">
+      <c r="B466" s="21" t="s">
+        <v>587</v>
+      </c>
+      <c r="C466" s="21" t="s">
         <v>546</v>
       </c>
-      <c r="D466" s="23" t="s">
-        <v>587</v>
+      <c r="D466" s="21" t="s">
+        <v>588</v>
       </c>
       <c r="E466" s="11" t="s">
         <v>515</v>
@@ -8469,32 +8452,32 @@
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2"/>
-      <c r="B467" s="23" t="s">
-        <v>588</v>
-      </c>
-      <c r="C467" s="23"/>
-      <c r="D467" s="23"/>
+      <c r="B467" s="21" t="s">
+        <v>589</v>
+      </c>
+      <c r="C467" s="21"/>
+      <c r="D467" s="21"/>
       <c r="E467" s="11"/>
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2"/>
-      <c r="B468" s="23" t="s">
-        <v>589</v>
-      </c>
-      <c r="C468" s="23"/>
-      <c r="D468" s="23"/>
+      <c r="B468" s="21" t="s">
+        <v>590</v>
+      </c>
+      <c r="C468" s="21"/>
+      <c r="D468" s="21"/>
       <c r="E468" s="11"/>
     </row>
     <row r="469" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="2"/>
-      <c r="B469" s="23" t="s">
-        <v>590</v>
-      </c>
-      <c r="C469" s="23" t="s">
+      <c r="B469" s="21" t="s">
         <v>591</v>
       </c>
-      <c r="D469" s="23" t="s">
+      <c r="C469" s="21" t="s">
         <v>592</v>
+      </c>
+      <c r="D469" s="21" t="s">
+        <v>593</v>
       </c>
       <c r="E469" s="11" t="s">
         <v>515</v>
@@ -8502,32 +8485,32 @@
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="2"/>
-      <c r="B470" s="23" t="s">
-        <v>593</v>
-      </c>
-      <c r="C470" s="23"/>
-      <c r="D470" s="23"/>
+      <c r="B470" s="21" t="s">
+        <v>594</v>
+      </c>
+      <c r="C470" s="21"/>
+      <c r="D470" s="21"/>
       <c r="E470" s="11"/>
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="2"/>
-      <c r="B471" s="23" t="s">
-        <v>594</v>
-      </c>
-      <c r="C471" s="23"/>
-      <c r="D471" s="23"/>
+      <c r="B471" s="21" t="s">
+        <v>595</v>
+      </c>
+      <c r="C471" s="21"/>
+      <c r="D471" s="21"/>
       <c r="E471" s="11"/>
     </row>
     <row r="472" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="2"/>
-      <c r="B472" s="23" t="s">
-        <v>595</v>
-      </c>
-      <c r="C472" s="23" t="s">
+      <c r="B472" s="21" t="s">
+        <v>596</v>
+      </c>
+      <c r="C472" s="21" t="s">
         <v>563</v>
       </c>
-      <c r="D472" s="23" t="s">
-        <v>596</v>
+      <c r="D472" s="21" t="s">
+        <v>597</v>
       </c>
       <c r="E472" s="11" t="s">
         <v>515</v>
@@ -8535,41 +8518,41 @@
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2"/>
-      <c r="B473" s="23" t="s">
-        <v>597</v>
-      </c>
-      <c r="C473" s="23"/>
-      <c r="D473" s="23"/>
+      <c r="B473" s="21" t="s">
+        <v>598</v>
+      </c>
+      <c r="C473" s="21"/>
+      <c r="D473" s="21"/>
       <c r="E473" s="11"/>
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="2"/>
-      <c r="B474" s="23"/>
-      <c r="C474" s="23"/>
-      <c r="D474" s="23"/>
+      <c r="B474" s="21"/>
+      <c r="C474" s="21"/>
+      <c r="D474" s="21"/>
       <c r="E474" s="11"/>
     </row>
     <row r="475" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="B475" s="23" t="s">
         <v>599</v>
       </c>
-      <c r="C475" s="23"/>
-      <c r="D475" s="23"/>
+      <c r="B475" s="21" t="s">
+        <v>600</v>
+      </c>
+      <c r="C475" s="21"/>
+      <c r="D475" s="21"/>
       <c r="E475" s="11"/>
     </row>
     <row r="476" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2"/>
-      <c r="B476" s="23" t="s">
-        <v>600</v>
-      </c>
-      <c r="C476" s="23" t="s">
+      <c r="B476" s="21" t="s">
+        <v>601</v>
+      </c>
+      <c r="C476" s="21" t="s">
         <v>563</v>
       </c>
-      <c r="D476" s="23" t="s">
-        <v>596</v>
+      <c r="D476" s="21" t="s">
+        <v>597</v>
       </c>
       <c r="E476" s="11" t="s">
         <v>515</v>
@@ -8577,94 +8560,94 @@
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2"/>
-      <c r="B477" s="23" t="s">
-        <v>601</v>
-      </c>
-      <c r="C477" s="23"/>
-      <c r="D477" s="23"/>
+      <c r="B477" s="21" t="s">
+        <v>602</v>
+      </c>
+      <c r="C477" s="21"/>
+      <c r="D477" s="21"/>
       <c r="E477" s="11"/>
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2"/>
-      <c r="B478" s="23"/>
-      <c r="C478" s="23"/>
-      <c r="D478" s="23"/>
+      <c r="B478" s="21"/>
+      <c r="C478" s="21"/>
+      <c r="D478" s="21"/>
       <c r="E478" s="11"/>
     </row>
     <row r="479" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="6"/>
-      <c r="B479" s="24" t="s">
-        <v>602</v>
-      </c>
-      <c r="C479" s="25"/>
-      <c r="D479" s="25"/>
+      <c r="B479" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="C479" s="23"/>
+      <c r="D479" s="23"/>
       <c r="E479" s="8"/>
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C480" s="23"/>
-      <c r="D480" s="23"/>
+      <c r="C480" s="21"/>
+      <c r="D480" s="21"/>
       <c r="E480" s="11"/>
     </row>
     <row r="481" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="2"/>
-      <c r="B481" s="23" t="s">
-        <v>603</v>
-      </c>
-      <c r="C481" s="23"/>
-      <c r="D481" s="23"/>
+      <c r="B481" s="21" t="s">
+        <v>604</v>
+      </c>
+      <c r="C481" s="21"/>
+      <c r="D481" s="21"/>
       <c r="E481" s="11"/>
     </row>
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2"/>
-      <c r="B482" s="23" t="s">
-        <v>604</v>
-      </c>
-      <c r="C482" s="23"/>
-      <c r="D482" s="23"/>
+      <c r="B482" s="21" t="s">
+        <v>605</v>
+      </c>
+      <c r="C482" s="21"/>
+      <c r="D482" s="21"/>
       <c r="E482" s="11"/>
     </row>
     <row r="483" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="2"/>
-      <c r="B483" s="23" t="s">
-        <v>605</v>
-      </c>
-      <c r="C483" s="23"/>
-      <c r="D483" s="23"/>
+      <c r="B483" s="21" t="s">
+        <v>606</v>
+      </c>
+      <c r="C483" s="21"/>
+      <c r="D483" s="21"/>
       <c r="E483" s="11"/>
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2"/>
-      <c r="B484" s="23" t="s">
+      <c r="B484" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="C484" s="23"/>
-      <c r="D484" s="23"/>
+      <c r="C484" s="21"/>
+      <c r="D484" s="21"/>
       <c r="E484" s="11"/>
     </row>
     <row r="485" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2"/>
-      <c r="B485" s="23" t="s">
-        <v>606</v>
-      </c>
-      <c r="C485" s="23" t="s">
+      <c r="B485" s="21" t="s">
+        <v>607</v>
+      </c>
+      <c r="C485" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D485" s="23"/>
+      <c r="D485" s="21"/>
       <c r="E485" s="11"/>
     </row>
     <row r="486" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2"/>
-      <c r="B486" s="23" t="s">
-        <v>607</v>
-      </c>
-      <c r="C486" s="23" t="s">
+      <c r="B486" s="21" t="s">
+        <v>608</v>
+      </c>
+      <c r="C486" s="21" t="s">
         <v>563</v>
       </c>
-      <c r="D486" s="23" t="s">
-        <v>608</v>
+      <c r="D486" s="21" t="s">
+        <v>609</v>
       </c>
       <c r="E486" s="11" t="s">
         <v>515</v>
@@ -8672,89 +8655,89 @@
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="2"/>
-      <c r="B487" s="23"/>
-      <c r="C487" s="23"/>
-      <c r="D487" s="23"/>
+      <c r="B487" s="21"/>
+      <c r="C487" s="21"/>
+      <c r="D487" s="21"/>
       <c r="E487" s="11"/>
     </row>
     <row r="488" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="6"/>
-      <c r="B488" s="24" t="s">
-        <v>609</v>
-      </c>
-      <c r="C488" s="25"/>
-      <c r="D488" s="25"/>
+      <c r="B488" s="22" t="s">
+        <v>610</v>
+      </c>
+      <c r="C488" s="23"/>
+      <c r="D488" s="23"/>
       <c r="E488" s="8"/>
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C489" s="23"/>
-      <c r="D489" s="23"/>
+      <c r="C489" s="21"/>
+      <c r="D489" s="21"/>
       <c r="E489" s="11"/>
     </row>
     <row r="490" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="2"/>
-      <c r="B490" s="23" t="s">
-        <v>610</v>
-      </c>
-      <c r="C490" s="23"/>
-      <c r="D490" s="23"/>
+      <c r="B490" s="21" t="s">
+        <v>611</v>
+      </c>
+      <c r="C490" s="21"/>
+      <c r="D490" s="21"/>
       <c r="E490" s="11"/>
     </row>
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="2"/>
-      <c r="B491" s="23" t="s">
-        <v>611</v>
-      </c>
-      <c r="C491" s="23"/>
-      <c r="D491" s="23"/>
+      <c r="B491" s="21" t="s">
+        <v>612</v>
+      </c>
+      <c r="C491" s="21"/>
+      <c r="D491" s="21"/>
       <c r="E491" s="11"/>
     </row>
     <row r="492" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2"/>
-      <c r="B492" s="23" t="s">
-        <v>612</v>
-      </c>
-      <c r="C492" s="23" t="s">
+      <c r="B492" s="21" t="s">
+        <v>613</v>
+      </c>
+      <c r="C492" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="D492" s="23"/>
+      <c r="D492" s="21"/>
       <c r="E492" s="11"/>
     </row>
     <row r="493" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2"/>
-      <c r="B493" s="23" t="s">
-        <v>613</v>
-      </c>
-      <c r="C493" s="23" t="s">
+      <c r="B493" s="21" t="s">
         <v>614</v>
       </c>
-      <c r="D493" s="23"/>
+      <c r="C493" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="D493" s="21"/>
       <c r="E493" s="11"/>
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2"/>
-      <c r="B494" s="23" t="s">
-        <v>615</v>
-      </c>
-      <c r="C494" s="23" t="s">
+      <c r="B494" s="21" t="s">
+        <v>616</v>
+      </c>
+      <c r="C494" s="21" t="s">
         <v>461</v>
       </c>
-      <c r="D494" s="23"/>
+      <c r="D494" s="21"/>
       <c r="E494" s="11"/>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2"/>
-      <c r="B495" s="23" t="s">
-        <v>616</v>
-      </c>
-      <c r="C495" s="23" t="s">
+      <c r="B495" s="21" t="s">
         <v>617</v>
       </c>
-      <c r="D495" s="23" t="s">
+      <c r="C495" s="21" t="s">
         <v>618</v>
+      </c>
+      <c r="D495" s="21" t="s">
+        <v>619</v>
       </c>
       <c r="E495" s="11" t="s">
         <v>24</v>
@@ -8762,14 +8745,14 @@
     </row>
     <row r="496" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2"/>
-      <c r="B496" s="23" t="s">
-        <v>619</v>
-      </c>
-      <c r="C496" s="23" t="s">
+      <c r="B496" s="21" t="s">
         <v>620</v>
       </c>
-      <c r="D496" s="23" t="s">
+      <c r="C496" s="21" t="s">
         <v>621</v>
+      </c>
+      <c r="D496" s="21" t="s">
+        <v>622</v>
       </c>
       <c r="E496" s="11" t="s">
         <v>515</v>
@@ -8777,113 +8760,113 @@
     </row>
     <row r="497" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2"/>
-      <c r="B497" s="23" t="s">
-        <v>622</v>
-      </c>
-      <c r="C497" s="23"/>
-      <c r="D497" s="23"/>
+      <c r="B497" s="21" t="s">
+        <v>623</v>
+      </c>
+      <c r="C497" s="21"/>
+      <c r="D497" s="21"/>
       <c r="E497" s="11"/>
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="2"/>
-      <c r="B498" s="23"/>
-      <c r="C498" s="23"/>
-      <c r="D498" s="23"/>
+      <c r="B498" s="21"/>
+      <c r="C498" s="21"/>
+      <c r="D498" s="21"/>
       <c r="E498" s="11"/>
     </row>
     <row r="499" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="6"/>
-      <c r="B499" s="24" t="s">
-        <v>623</v>
-      </c>
-      <c r="C499" s="25"/>
-      <c r="D499" s="25"/>
+      <c r="B499" s="22" t="s">
+        <v>624</v>
+      </c>
+      <c r="C499" s="23"/>
+      <c r="D499" s="23"/>
       <c r="E499" s="8"/>
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B500" s="23"/>
-      <c r="C500" s="23"/>
-      <c r="D500" s="23"/>
+      <c r="B500" s="21"/>
+      <c r="C500" s="21"/>
+      <c r="D500" s="21"/>
       <c r="E500" s="11"/>
     </row>
     <row r="501" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="2"/>
-      <c r="B501" s="23" t="s">
-        <v>624</v>
-      </c>
-      <c r="C501" s="23"/>
-      <c r="D501" s="23"/>
+      <c r="B501" s="21" t="s">
+        <v>625</v>
+      </c>
+      <c r="C501" s="21"/>
+      <c r="D501" s="21"/>
       <c r="E501" s="11"/>
     </row>
     <row r="502" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="2"/>
-      <c r="B502" s="23" t="s">
-        <v>625</v>
-      </c>
-      <c r="C502" s="23" t="s">
+      <c r="B502" s="21" t="s">
+        <v>626</v>
+      </c>
+      <c r="C502" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="D502" s="23" t="s">
-        <v>626</v>
+      <c r="D502" s="21" t="s">
+        <v>627</v>
       </c>
       <c r="E502" s="11" t="s">
-        <v>627</v>
-      </c>
-      <c r="F502" s="20" t="s">
         <v>628</v>
+      </c>
+      <c r="F502" s="18" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="2"/>
-      <c r="B503" s="23" t="s">
-        <v>629</v>
-      </c>
-      <c r="C503" s="23"/>
-      <c r="D503" s="23"/>
+      <c r="B503" s="21" t="s">
+        <v>630</v>
+      </c>
+      <c r="C503" s="21"/>
+      <c r="D503" s="21"/>
       <c r="E503" s="11"/>
     </row>
     <row r="504" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="2"/>
-      <c r="B504" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C504" s="23"/>
-      <c r="D504" s="23"/>
+      <c r="B504" s="21" t="s">
+        <v>631</v>
+      </c>
+      <c r="C504" s="21"/>
+      <c r="D504" s="21"/>
       <c r="E504" s="11"/>
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="2"/>
-      <c r="B505" s="23" t="s">
-        <v>631</v>
-      </c>
-      <c r="C505" s="23"/>
-      <c r="D505" s="23"/>
+      <c r="B505" s="21" t="s">
+        <v>632</v>
+      </c>
+      <c r="C505" s="21"/>
+      <c r="D505" s="21"/>
       <c r="E505" s="11"/>
     </row>
     <row r="506" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="2"/>
-      <c r="B506" s="23" t="s">
-        <v>632</v>
-      </c>
-      <c r="C506" s="23" t="s">
+      <c r="B506" s="21" t="s">
         <v>633</v>
       </c>
-      <c r="D506" s="23"/>
+      <c r="C506" s="21" t="s">
+        <v>634</v>
+      </c>
+      <c r="D506" s="21"/>
       <c r="E506" s="11"/>
     </row>
     <row r="507" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="2"/>
-      <c r="B507" s="23" t="s">
-        <v>634</v>
-      </c>
-      <c r="C507" s="23" t="s">
+      <c r="B507" s="21" t="s">
         <v>635</v>
       </c>
-      <c r="D507" s="23" t="s">
+      <c r="C507" s="21" t="s">
         <v>636</v>
+      </c>
+      <c r="D507" s="21" t="s">
+        <v>637</v>
       </c>
       <c r="E507" s="11" t="s">
         <v>184</v>
@@ -8891,14 +8874,14 @@
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="2"/>
-      <c r="B508" s="23" t="s">
-        <v>637</v>
-      </c>
-      <c r="C508" s="23" t="s">
+      <c r="B508" s="21" t="s">
+        <v>638</v>
+      </c>
+      <c r="C508" s="21" t="s">
         <v>563</v>
       </c>
-      <c r="D508" s="23" t="s">
-        <v>596</v>
+      <c r="D508" s="21" t="s">
+        <v>597</v>
       </c>
       <c r="E508" s="11" t="s">
         <v>515</v>
@@ -8906,101 +8889,101 @@
     </row>
     <row r="509" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="2"/>
-      <c r="B509" s="23" t="s">
-        <v>638</v>
-      </c>
-      <c r="C509" s="23" t="s">
+      <c r="B509" s="21" t="s">
+        <v>639</v>
+      </c>
+      <c r="C509" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D509" s="23"/>
+      <c r="D509" s="21"/>
       <c r="E509" s="11"/>
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="2"/>
-      <c r="B510" s="23"/>
-      <c r="C510" s="23"/>
-      <c r="D510" s="23"/>
+      <c r="B510" s="21"/>
+      <c r="C510" s="21"/>
+      <c r="D510" s="21"/>
       <c r="E510" s="11"/>
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B511" s="23" t="s">
-        <v>639</v>
-      </c>
-      <c r="C511" s="23"/>
-      <c r="D511" s="23"/>
+      <c r="B511" s="21" t="s">
+        <v>640</v>
+      </c>
+      <c r="C511" s="21"/>
+      <c r="D511" s="21"/>
       <c r="E511" s="11"/>
     </row>
     <row r="512" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="2"/>
-      <c r="B512" s="23" t="s">
-        <v>640</v>
-      </c>
-      <c r="C512" s="23" t="s">
+      <c r="B512" s="21" t="s">
         <v>641</v>
       </c>
-      <c r="D512" s="23" t="s">
+      <c r="C512" s="21" t="s">
         <v>642</v>
       </c>
+      <c r="D512" s="21" t="s">
+        <v>643</v>
+      </c>
       <c r="E512" s="11" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2"/>
-      <c r="B513" s="23" t="s">
-        <v>644</v>
-      </c>
-      <c r="C513" s="23"/>
-      <c r="D513" s="23"/>
+      <c r="B513" s="21" t="s">
+        <v>645</v>
+      </c>
+      <c r="C513" s="21"/>
+      <c r="D513" s="21"/>
       <c r="E513" s="11"/>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="2"/>
-      <c r="B514" s="23"/>
-      <c r="C514" s="23"/>
-      <c r="D514" s="23"/>
+      <c r="B514" s="21"/>
+      <c r="C514" s="21"/>
+      <c r="D514" s="21"/>
       <c r="E514" s="11"/>
     </row>
     <row r="515" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="6"/>
-      <c r="B515" s="24" t="s">
-        <v>645</v>
-      </c>
-      <c r="C515" s="25"/>
-      <c r="D515" s="25"/>
+      <c r="B515" s="22" t="s">
+        <v>646</v>
+      </c>
+      <c r="C515" s="23"/>
+      <c r="D515" s="23"/>
       <c r="E515" s="8"/>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B516" s="23"/>
-      <c r="C516" s="23"/>
-      <c r="D516" s="23"/>
+      <c r="B516" s="21"/>
+      <c r="C516" s="21"/>
+      <c r="D516" s="21"/>
       <c r="E516" s="11"/>
     </row>
     <row r="517" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="2"/>
-      <c r="B517" s="23" t="s">
-        <v>646</v>
-      </c>
-      <c r="C517" s="23"/>
-      <c r="D517" s="23"/>
+      <c r="B517" s="21" t="s">
+        <v>647</v>
+      </c>
+      <c r="C517" s="21"/>
+      <c r="D517" s="21"/>
       <c r="E517" s="11"/>
     </row>
     <row r="518" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="2"/>
-      <c r="B518" s="23" t="s">
-        <v>647</v>
-      </c>
-      <c r="C518" s="23" t="s">
+      <c r="B518" s="21" t="s">
         <v>648</v>
       </c>
-      <c r="D518" s="23" t="s">
+      <c r="C518" s="21" t="s">
         <v>649</v>
+      </c>
+      <c r="D518" s="21" t="s">
+        <v>650</v>
       </c>
       <c r="E518" s="11" t="s">
         <v>515</v>
@@ -9008,12 +8991,12 @@
     </row>
     <row r="519" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="2"/>
-      <c r="B519" s="23" t="s">
-        <v>650</v>
-      </c>
-      <c r="C519" s="23"/>
-      <c r="D519" s="23" t="s">
+      <c r="B519" s="21" t="s">
         <v>651</v>
+      </c>
+      <c r="C519" s="21"/>
+      <c r="D519" s="21" t="s">
+        <v>652</v>
       </c>
       <c r="E519" s="11" t="s">
         <v>515</v>
@@ -9021,104 +9004,104 @@
     </row>
     <row r="520" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="2"/>
-      <c r="B520" s="23" t="s">
-        <v>652</v>
-      </c>
-      <c r="C520" s="23"/>
-      <c r="D520" s="23"/>
+      <c r="B520" s="21" t="s">
+        <v>653</v>
+      </c>
+      <c r="C520" s="21"/>
+      <c r="D520" s="21"/>
       <c r="E520" s="11"/>
     </row>
     <row r="521" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="2"/>
-      <c r="B521" s="23" t="s">
-        <v>653</v>
-      </c>
-      <c r="C521" s="23" t="s">
+      <c r="B521" s="21" t="s">
+        <v>654</v>
+      </c>
+      <c r="C521" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="D521" s="23" t="s">
+      <c r="D521" s="21" t="s">
         <v>287</v>
       </c>
       <c r="E521" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="F521" s="20" t="s">
-        <v>654</v>
+      <c r="F521" s="18" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="2"/>
-      <c r="B522" s="23" t="s">
-        <v>655</v>
-      </c>
-      <c r="C522" s="23"/>
-      <c r="D522" s="23"/>
+      <c r="B522" s="21" t="s">
+        <v>656</v>
+      </c>
+      <c r="C522" s="21"/>
+      <c r="D522" s="21"/>
       <c r="E522" s="11"/>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="2"/>
-      <c r="B523" s="23" t="s">
-        <v>656</v>
-      </c>
-      <c r="C523" s="23"/>
-      <c r="D523" s="23"/>
+      <c r="B523" s="21" t="s">
+        <v>657</v>
+      </c>
+      <c r="C523" s="21"/>
+      <c r="D523" s="21"/>
       <c r="E523" s="11"/>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="2"/>
-      <c r="B524" s="23" t="s">
-        <v>657</v>
-      </c>
-      <c r="C524" s="23"/>
-      <c r="D524" s="23"/>
+      <c r="B524" s="21" t="s">
+        <v>658</v>
+      </c>
+      <c r="C524" s="21"/>
+      <c r="D524" s="21"/>
       <c r="E524" s="11"/>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2"/>
-      <c r="B525" s="23" t="s">
-        <v>658</v>
-      </c>
-      <c r="C525" s="23"/>
-      <c r="D525" s="23"/>
+      <c r="B525" s="21" t="s">
+        <v>659</v>
+      </c>
+      <c r="C525" s="21"/>
+      <c r="D525" s="21"/>
       <c r="E525" s="11"/>
     </row>
     <row r="526" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2"/>
-      <c r="B526" s="23" t="s">
-        <v>659</v>
-      </c>
-      <c r="C526" s="23"/>
-      <c r="D526" s="23"/>
+      <c r="B526" s="21" t="s">
+        <v>660</v>
+      </c>
+      <c r="C526" s="21"/>
+      <c r="D526" s="21"/>
       <c r="E526" s="11"/>
     </row>
     <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2"/>
-      <c r="B527" s="23" t="s">
-        <v>660</v>
-      </c>
-      <c r="C527" s="23"/>
-      <c r="D527" s="23"/>
+      <c r="B527" s="21" t="s">
+        <v>661</v>
+      </c>
+      <c r="C527" s="21"/>
+      <c r="D527" s="21"/>
       <c r="E527" s="11"/>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="2"/>
-      <c r="B528" s="23" t="s">
-        <v>661</v>
-      </c>
-      <c r="C528" s="23"/>
-      <c r="D528" s="23"/>
+      <c r="B528" s="21" t="s">
+        <v>662</v>
+      </c>
+      <c r="C528" s="21"/>
+      <c r="D528" s="21"/>
       <c r="E528" s="11"/>
     </row>
     <row r="529" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="2"/>
-      <c r="B529" s="23" t="s">
-        <v>662</v>
-      </c>
-      <c r="C529" s="23" t="s">
+      <c r="B529" s="21" t="s">
         <v>663</v>
       </c>
-      <c r="D529" s="23" t="s">
+      <c r="C529" s="21" t="s">
         <v>664</v>
+      </c>
+      <c r="D529" s="21" t="s">
+        <v>665</v>
       </c>
       <c r="E529" s="11" t="s">
         <v>515</v>
@@ -9126,193 +9109,193 @@
     </row>
     <row r="530" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="2"/>
-      <c r="B530" s="23" t="s">
-        <v>665</v>
-      </c>
-      <c r="C530" s="23" t="s">
+      <c r="B530" s="21" t="s">
         <v>666</v>
       </c>
-      <c r="D530" s="23"/>
+      <c r="C530" s="21" t="s">
+        <v>667</v>
+      </c>
+      <c r="D530" s="21"/>
       <c r="E530" s="11"/>
     </row>
     <row r="531" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="2"/>
-      <c r="B531" s="23" t="s">
-        <v>667</v>
-      </c>
-      <c r="C531" s="23" t="s">
+      <c r="B531" s="21" t="s">
+        <v>668</v>
+      </c>
+      <c r="C531" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D531" s="23"/>
+      <c r="D531" s="21"/>
       <c r="E531" s="11"/>
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="2"/>
-      <c r="B532" s="23"/>
-      <c r="C532" s="23"/>
-      <c r="D532" s="23"/>
+      <c r="B532" s="21"/>
+      <c r="C532" s="21"/>
+      <c r="D532" s="21"/>
       <c r="E532" s="11"/>
     </row>
     <row r="533" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B533" s="23" t="s">
-        <v>668</v>
-      </c>
-      <c r="C533" s="23"/>
-      <c r="D533" s="23"/>
+      <c r="B533" s="21" t="s">
+        <v>669</v>
+      </c>
+      <c r="C533" s="21"/>
+      <c r="D533" s="21"/>
       <c r="E533" s="11"/>
     </row>
     <row r="534" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="2"/>
-      <c r="B534" s="23" t="s">
-        <v>669</v>
-      </c>
-      <c r="C534" s="23"/>
-      <c r="D534" s="23"/>
+      <c r="B534" s="21" t="s">
+        <v>670</v>
+      </c>
+      <c r="C534" s="21"/>
+      <c r="D534" s="21"/>
       <c r="E534" s="11"/>
     </row>
     <row r="535" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="2"/>
-      <c r="B535" s="23" t="s">
-        <v>670</v>
-      </c>
-      <c r="C535" s="23"/>
-      <c r="D535" s="23"/>
+      <c r="B535" s="21" t="s">
+        <v>671</v>
+      </c>
+      <c r="C535" s="21"/>
+      <c r="D535" s="21"/>
       <c r="E535" s="11"/>
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="2"/>
-      <c r="B536" s="23" t="s">
-        <v>671</v>
-      </c>
-      <c r="C536" s="23"/>
-      <c r="D536" s="23"/>
+      <c r="B536" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="C536" s="21"/>
+      <c r="D536" s="21"/>
       <c r="E536" s="11"/>
     </row>
     <row r="537" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="2"/>
-      <c r="B537" s="23" t="s">
-        <v>672</v>
-      </c>
-      <c r="C537" s="23" t="s">
-        <v>666</v>
-      </c>
-      <c r="D537" s="23"/>
+      <c r="B537" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="C537" s="21" t="s">
+        <v>667</v>
+      </c>
+      <c r="D537" s="21"/>
       <c r="E537" s="11"/>
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="2"/>
-      <c r="B538" s="23" t="s">
-        <v>673</v>
-      </c>
-      <c r="C538" s="23"/>
-      <c r="D538" s="23"/>
+      <c r="B538" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="C538" s="21"/>
+      <c r="D538" s="21"/>
       <c r="E538" s="11"/>
     </row>
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="2"/>
-      <c r="B539" s="23" t="s">
-        <v>674</v>
-      </c>
-      <c r="C539" s="23"/>
-      <c r="D539" s="23"/>
+      <c r="B539" s="21" t="s">
+        <v>675</v>
+      </c>
+      <c r="C539" s="21"/>
+      <c r="D539" s="21"/>
       <c r="E539" s="11"/>
     </row>
     <row r="540" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="2"/>
-      <c r="B540" s="23" t="s">
-        <v>675</v>
-      </c>
-      <c r="C540" s="23"/>
-      <c r="D540" s="23"/>
+      <c r="B540" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="C540" s="21"/>
+      <c r="D540" s="21"/>
       <c r="E540" s="11"/>
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="2"/>
-      <c r="B541" s="23" t="s">
-        <v>676</v>
-      </c>
-      <c r="C541" s="23"/>
-      <c r="D541" s="23"/>
+      <c r="B541" s="21" t="s">
+        <v>677</v>
+      </c>
+      <c r="C541" s="21"/>
+      <c r="D541" s="21"/>
       <c r="E541" s="11"/>
     </row>
     <row r="542" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="2"/>
-      <c r="B542" s="23" t="s">
-        <v>677</v>
-      </c>
-      <c r="C542" s="23" t="s">
-        <v>633</v>
-      </c>
-      <c r="D542" s="23"/>
+      <c r="B542" s="21" t="s">
+        <v>678</v>
+      </c>
+      <c r="C542" s="21" t="s">
+        <v>634</v>
+      </c>
+      <c r="D542" s="21"/>
       <c r="E542" s="11"/>
     </row>
     <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="2"/>
-      <c r="B543" s="23" t="s">
-        <v>678</v>
-      </c>
-      <c r="C543" s="23"/>
-      <c r="D543" s="23"/>
+      <c r="B543" s="21" t="s">
+        <v>679</v>
+      </c>
+      <c r="C543" s="21"/>
+      <c r="D543" s="21"/>
       <c r="E543" s="11"/>
     </row>
     <row r="544" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="2"/>
-      <c r="B544" s="23" t="s">
-        <v>679</v>
-      </c>
-      <c r="C544" s="23"/>
-      <c r="D544" s="23"/>
+      <c r="B544" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="C544" s="21"/>
+      <c r="D544" s="21"/>
       <c r="E544" s="11"/>
     </row>
     <row r="545" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="2"/>
-      <c r="B545" s="23" t="s">
-        <v>680</v>
-      </c>
-      <c r="C545" s="23"/>
-      <c r="D545" s="23"/>
+      <c r="B545" s="21" t="s">
+        <v>681</v>
+      </c>
+      <c r="C545" s="21"/>
+      <c r="D545" s="21"/>
       <c r="E545" s="11"/>
     </row>
     <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="2"/>
-      <c r="B546" s="23" t="s">
-        <v>681</v>
-      </c>
-      <c r="C546" s="23"/>
-      <c r="D546" s="23"/>
+      <c r="B546" s="21" t="s">
+        <v>682</v>
+      </c>
+      <c r="C546" s="21"/>
+      <c r="D546" s="21"/>
       <c r="E546" s="11"/>
     </row>
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="2"/>
-      <c r="B547" s="23" t="s">
-        <v>682</v>
-      </c>
-      <c r="C547" s="23"/>
-      <c r="D547" s="23"/>
+      <c r="B547" s="21" t="s">
+        <v>683</v>
+      </c>
+      <c r="C547" s="21"/>
+      <c r="D547" s="21"/>
       <c r="E547" s="11"/>
     </row>
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="2"/>
-      <c r="B548" s="23" t="s">
-        <v>683</v>
-      </c>
-      <c r="C548" s="23"/>
-      <c r="D548" s="23"/>
+      <c r="B548" s="21" t="s">
+        <v>684</v>
+      </c>
+      <c r="C548" s="21"/>
+      <c r="D548" s="21"/>
       <c r="E548" s="11"/>
     </row>
     <row r="549" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="2"/>
-      <c r="B549" s="23" t="s">
-        <v>684</v>
-      </c>
-      <c r="C549" s="23" t="s">
+      <c r="B549" s="21" t="s">
+        <v>685</v>
+      </c>
+      <c r="C549" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="D549" s="23" t="s">
-        <v>685</v>
+      <c r="D549" s="21" t="s">
+        <v>686</v>
       </c>
       <c r="E549" s="11" t="s">
         <v>515</v>
@@ -9320,14 +9303,14 @@
     </row>
     <row r="550" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="2"/>
-      <c r="B550" s="23" t="s">
-        <v>686</v>
-      </c>
-      <c r="C550" s="23" t="s">
+      <c r="B550" s="21" t="s">
         <v>687</v>
       </c>
-      <c r="D550" s="23" t="s">
+      <c r="C550" s="21" t="s">
         <v>688</v>
+      </c>
+      <c r="D550" s="21" t="s">
+        <v>689</v>
       </c>
       <c r="E550" s="11" t="s">
         <v>184</v>
@@ -9335,84 +9318,84 @@
     </row>
     <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="2"/>
-      <c r="B551" s="23" t="s">
-        <v>689</v>
-      </c>
-      <c r="C551" s="23"/>
-      <c r="D551" s="23"/>
+      <c r="B551" s="21" t="s">
+        <v>690</v>
+      </c>
+      <c r="C551" s="21"/>
+      <c r="D551" s="21"/>
       <c r="E551" s="11"/>
     </row>
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="2"/>
-      <c r="B552" s="23"/>
-      <c r="C552" s="23"/>
-      <c r="D552" s="23"/>
+      <c r="B552" s="21"/>
+      <c r="C552" s="21"/>
+      <c r="D552" s="21"/>
       <c r="E552" s="11"/>
     </row>
     <row r="553" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="B553" s="23" t="s">
-        <v>690</v>
-      </c>
-      <c r="C553" s="23"/>
-      <c r="D553" s="23"/>
+        <v>599</v>
+      </c>
+      <c r="B553" s="21" t="s">
+        <v>691</v>
+      </c>
+      <c r="C553" s="21"/>
+      <c r="D553" s="21"/>
       <c r="E553" s="11"/>
     </row>
     <row r="554" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="2"/>
-      <c r="B554" s="23" t="s">
-        <v>691</v>
-      </c>
-      <c r="C554" s="23"/>
-      <c r="D554" s="23"/>
+      <c r="B554" s="21" t="s">
+        <v>692</v>
+      </c>
+      <c r="C554" s="21"/>
+      <c r="D554" s="21"/>
       <c r="E554" s="11"/>
     </row>
     <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="2"/>
-      <c r="B555" s="23" t="s">
-        <v>692</v>
-      </c>
-      <c r="C555" s="23"/>
-      <c r="D555" s="23"/>
+      <c r="B555" s="21" t="s">
+        <v>693</v>
+      </c>
+      <c r="C555" s="21"/>
+      <c r="D555" s="21"/>
       <c r="E555" s="11"/>
     </row>
     <row r="556" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="2"/>
-      <c r="B556" s="23" t="s">
-        <v>693</v>
-      </c>
-      <c r="C556" s="23" t="s">
-        <v>666</v>
-      </c>
-      <c r="D556" s="23"/>
+      <c r="B556" s="21" t="s">
+        <v>694</v>
+      </c>
+      <c r="C556" s="21" t="s">
+        <v>667</v>
+      </c>
+      <c r="D556" s="21"/>
       <c r="E556" s="11"/>
     </row>
     <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="2"/>
-      <c r="B557" s="23"/>
-      <c r="C557" s="23"/>
-      <c r="D557" s="23"/>
+      <c r="B557" s="21"/>
+      <c r="C557" s="21"/>
+      <c r="D557" s="21"/>
       <c r="E557" s="11"/>
     </row>
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="2"/>
-      <c r="B558" s="23" t="s">
-        <v>694</v>
-      </c>
-      <c r="C558" s="23"/>
-      <c r="D558" s="23"/>
+      <c r="B558" s="21" t="s">
+        <v>695</v>
+      </c>
+      <c r="C558" s="21"/>
+      <c r="D558" s="21"/>
       <c r="E558" s="11"/>
     </row>
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A559" s="36"/>
-      <c r="B559" s="37" t="s">
-        <v>695</v>
-      </c>
-      <c r="C559" s="37"/>
-      <c r="D559" s="37"/>
-      <c r="E559" s="38"/>
+      <c r="A559" s="32"/>
+      <c r="B559" s="33" t="s">
+        <v>696</v>
+      </c>
+      <c r="C559" s="33"/>
+      <c r="D559" s="33"/>
+      <c r="E559" s="34"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/assets/responsabilidades.xlsx
+++ b/assets/responsabilidades.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="701">
   <si>
     <t xml:space="preserve">Use Case</t>
   </si>
@@ -2391,6 +2391,9 @@
     <t xml:space="preserve">Alterar o atributo booleano da notificação para registar que a mesma foi tratada. Retorna true em caso de sucesso e false em caso de falha(se a notificacao já estiver marcada como tratada por exemplo)</t>
   </si>
   <si>
+    <t xml:space="preserve">Registar a data em que a notificação foi tratada na notificação</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.2.1.2 O funcionário confirma a notificação de término</t>
   </si>
   <si>
@@ -2595,6 +2598,12 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">registarDiagnosticoOS(idOS : int, listaPecas : List(QuantidadePeca), reparacoes : List(Reparacao), descricao : string, idMecanico : int) : void</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O orçamento é calculado com a função calcularOrcamento</t>
+  </si>
+  <si>
     <t xml:space="preserve">1. O funcionário seleciona uma das OS que estão no estado 'Pendente Diagnóstico'</t>
   </si>
   <si>
@@ -2679,6 +2688,9 @@
       </rPr>
       <t xml:space="preserve">Executar Reparação de Ordem de Serviço</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">registarConsertoOS(id_OS : int, idMecanico : int, pecas : List(Stock), reparacoes : List(Reparacao)) : void</t>
   </si>
   <si>
     <t xml:space="preserve">1. O funcionário seleciona uma das OS que estão no estado 'Pendente Reparação'</t>
@@ -3065,7 +3077,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3191,6 +3203,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3398,6 +3414,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="65.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -8351,11 +8368,14 @@
       <c r="F457" s="18" t="s">
         <v>576</v>
       </c>
+      <c r="G457" s="32" t="s">
+        <v>577</v>
+      </c>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2"/>
       <c r="B458" s="21" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C458" s="21"/>
       <c r="D458" s="21"/>
@@ -8364,7 +8384,7 @@
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="2"/>
       <c r="B459" s="21" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C459" s="21"/>
       <c r="D459" s="21"/>
@@ -8373,7 +8393,7 @@
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="2"/>
       <c r="B460" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C460" s="21"/>
       <c r="D460" s="21"/>
@@ -8382,7 +8402,7 @@
     <row r="461" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="2"/>
       <c r="B461" s="21" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C461" s="21"/>
       <c r="D461" s="21"/>
@@ -8391,13 +8411,13 @@
     <row r="462" customFormat="false" ht="67.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="2"/>
       <c r="B462" s="21" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C462" s="21" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D462" s="21" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E462" s="11" t="s">
         <v>184</v>
@@ -8407,7 +8427,7 @@
     <row r="463" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2"/>
       <c r="B463" s="21" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C463" s="21"/>
       <c r="D463" s="21"/>
@@ -8416,7 +8436,7 @@
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2"/>
       <c r="B464" s="21" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C464" s="21"/>
       <c r="D464" s="21"/>
@@ -8425,7 +8445,7 @@
     <row r="465" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2"/>
       <c r="B465" s="21" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C465" s="21" t="s">
         <v>234</v>
@@ -8438,13 +8458,13 @@
     <row r="466" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2"/>
       <c r="B466" s="21" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C466" s="21" t="s">
         <v>546</v>
       </c>
       <c r="D466" s="21" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E466" s="11" t="s">
         <v>515</v>
@@ -8453,7 +8473,7 @@
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2"/>
       <c r="B467" s="21" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C467" s="21"/>
       <c r="D467" s="21"/>
@@ -8462,7 +8482,7 @@
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2"/>
       <c r="B468" s="21" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C468" s="21"/>
       <c r="D468" s="21"/>
@@ -8471,13 +8491,13 @@
     <row r="469" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="2"/>
       <c r="B469" s="21" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C469" s="21" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D469" s="21" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E469" s="11" t="s">
         <v>515</v>
@@ -8486,7 +8506,7 @@
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="2"/>
       <c r="B470" s="21" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C470" s="21"/>
       <c r="D470" s="21"/>
@@ -8495,7 +8515,7 @@
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="2"/>
       <c r="B471" s="21" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C471" s="21"/>
       <c r="D471" s="21"/>
@@ -8504,13 +8524,13 @@
     <row r="472" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="2"/>
       <c r="B472" s="21" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C472" s="21" t="s">
         <v>563</v>
       </c>
       <c r="D472" s="21" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E472" s="11" t="s">
         <v>515</v>
@@ -8519,7 +8539,7 @@
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2"/>
       <c r="B473" s="21" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C473" s="21"/>
       <c r="D473" s="21"/>
@@ -8534,10 +8554,10 @@
     </row>
     <row r="475" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B475" s="21" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C475" s="21"/>
       <c r="D475" s="21"/>
@@ -8546,13 +8566,13 @@
     <row r="476" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2"/>
       <c r="B476" s="21" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C476" s="21" t="s">
         <v>563</v>
       </c>
       <c r="D476" s="21" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E476" s="11" t="s">
         <v>515</v>
@@ -8561,7 +8581,7 @@
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2"/>
       <c r="B477" s="21" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C477" s="21"/>
       <c r="D477" s="21"/>
@@ -8577,7 +8597,7 @@
     <row r="479" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="6"/>
       <c r="B479" s="22" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C479" s="23"/>
       <c r="D479" s="23"/>
@@ -8594,7 +8614,7 @@
     <row r="481" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="2"/>
       <c r="B481" s="21" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C481" s="21"/>
       <c r="D481" s="21"/>
@@ -8603,7 +8623,7 @@
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2"/>
       <c r="B482" s="21" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C482" s="21"/>
       <c r="D482" s="21"/>
@@ -8612,7 +8632,7 @@
     <row r="483" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="2"/>
       <c r="B483" s="21" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C483" s="21"/>
       <c r="D483" s="21"/>
@@ -8630,7 +8650,7 @@
     <row r="485" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2"/>
       <c r="B485" s="21" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C485" s="21" t="s">
         <v>77</v>
@@ -8641,13 +8661,13 @@
     <row r="486" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2"/>
       <c r="B486" s="21" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C486" s="21" t="s">
         <v>563</v>
       </c>
       <c r="D486" s="21" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E486" s="11" t="s">
         <v>515</v>
@@ -8663,7 +8683,7 @@
     <row r="488" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="6"/>
       <c r="B488" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C488" s="23"/>
       <c r="D488" s="23"/>
@@ -8680,7 +8700,7 @@
     <row r="490" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="2"/>
       <c r="B490" s="21" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C490" s="21"/>
       <c r="D490" s="21"/>
@@ -8689,7 +8709,7 @@
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="2"/>
       <c r="B491" s="21" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C491" s="21"/>
       <c r="D491" s="21"/>
@@ -8698,7 +8718,7 @@
     <row r="492" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2"/>
       <c r="B492" s="21" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C492" s="21" t="s">
         <v>321</v>
@@ -8709,10 +8729,10 @@
     <row r="493" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2"/>
       <c r="B493" s="21" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C493" s="21" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D493" s="21"/>
       <c r="E493" s="11"/>
@@ -8720,7 +8740,7 @@
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2"/>
       <c r="B494" s="21" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C494" s="21" t="s">
         <v>461</v>
@@ -8731,13 +8751,13 @@
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2"/>
       <c r="B495" s="21" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C495" s="21" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D495" s="21" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E495" s="11" t="s">
         <v>24</v>
@@ -8746,13 +8766,13 @@
     <row r="496" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2"/>
       <c r="B496" s="21" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C496" s="21" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D496" s="21" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E496" s="11" t="s">
         <v>515</v>
@@ -8761,7 +8781,7 @@
     <row r="497" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2"/>
       <c r="B497" s="21" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C497" s="21"/>
       <c r="D497" s="21"/>
@@ -8774,14 +8794,21 @@
       <c r="D498" s="21"/>
       <c r="E498" s="11"/>
     </row>
-    <row r="499" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="499" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="6"/>
       <c r="B499" s="22" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C499" s="23"/>
-      <c r="D499" s="23"/>
-      <c r="E499" s="8"/>
+      <c r="D499" s="23" t="s">
+        <v>626</v>
+      </c>
+      <c r="E499" s="23" t="s">
+        <v>515</v>
+      </c>
+      <c r="F499" s="18" t="s">
+        <v>627</v>
+      </c>
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="2" t="s">
@@ -8795,7 +8822,7 @@
     <row r="501" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="2"/>
       <c r="B501" s="21" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C501" s="21"/>
       <c r="D501" s="21"/>
@@ -8804,25 +8831,25 @@
     <row r="502" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="2"/>
       <c r="B502" s="21" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C502" s="21" t="s">
         <v>535</v>
       </c>
       <c r="D502" s="21" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E502" s="11" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="F502" s="18" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="2"/>
       <c r="B503" s="21" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C503" s="21"/>
       <c r="D503" s="21"/>
@@ -8831,7 +8858,7 @@
     <row r="504" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="2"/>
       <c r="B504" s="21" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C504" s="21"/>
       <c r="D504" s="21"/>
@@ -8840,7 +8867,7 @@
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="2"/>
       <c r="B505" s="21" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C505" s="21"/>
       <c r="D505" s="21"/>
@@ -8849,10 +8876,10 @@
     <row r="506" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="2"/>
       <c r="B506" s="21" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C506" s="21" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D506" s="21"/>
       <c r="E506" s="11"/>
@@ -8860,13 +8887,13 @@
     <row r="507" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="2"/>
       <c r="B507" s="21" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C507" s="21" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D507" s="21" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E507" s="11" t="s">
         <v>184</v>
@@ -8875,13 +8902,13 @@
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="2"/>
       <c r="B508" s="21" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C508" s="21" t="s">
         <v>563</v>
       </c>
       <c r="D508" s="21" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E508" s="11" t="s">
         <v>515</v>
@@ -8890,7 +8917,7 @@
     <row r="509" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="2"/>
       <c r="B509" s="21" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C509" s="21" t="s">
         <v>77</v>
@@ -8910,7 +8937,7 @@
         <v>247</v>
       </c>
       <c r="B511" s="21" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C511" s="21"/>
       <c r="D511" s="21"/>
@@ -8919,22 +8946,22 @@
     <row r="512" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="2"/>
       <c r="B512" s="21" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C512" s="21" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D512" s="21" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E512" s="11" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2"/>
       <c r="B513" s="21" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C513" s="21"/>
       <c r="D513" s="21"/>
@@ -8947,14 +8974,18 @@
       <c r="D514" s="21"/>
       <c r="E514" s="11"/>
     </row>
-    <row r="515" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="515" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="6"/>
       <c r="B515" s="22" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C515" s="23"/>
-      <c r="D515" s="23"/>
-      <c r="E515" s="8"/>
+      <c r="D515" s="23" t="s">
+        <v>650</v>
+      </c>
+      <c r="E515" s="8" t="s">
+        <v>515</v>
+      </c>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="2" t="s">
@@ -8968,7 +8999,7 @@
     <row r="517" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="2"/>
       <c r="B517" s="21" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C517" s="21"/>
       <c r="D517" s="21"/>
@@ -8977,13 +9008,13 @@
     <row r="518" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="2"/>
       <c r="B518" s="21" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C518" s="21" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="D518" s="21" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E518" s="11" t="s">
         <v>515</v>
@@ -8992,11 +9023,11 @@
     <row r="519" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="2"/>
       <c r="B519" s="21" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C519" s="21"/>
       <c r="D519" s="21" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E519" s="11" t="s">
         <v>515</v>
@@ -9005,7 +9036,7 @@
     <row r="520" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="2"/>
       <c r="B520" s="21" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C520" s="21"/>
       <c r="D520" s="21"/>
@@ -9014,7 +9045,7 @@
     <row r="521" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="2"/>
       <c r="B521" s="21" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C521" s="21" t="s">
         <v>286</v>
@@ -9026,13 +9057,13 @@
         <v>184</v>
       </c>
       <c r="F521" s="18" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="2"/>
       <c r="B522" s="21" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C522" s="21"/>
       <c r="D522" s="21"/>
@@ -9041,7 +9072,7 @@
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="2"/>
       <c r="B523" s="21" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C523" s="21"/>
       <c r="D523" s="21"/>
@@ -9050,7 +9081,7 @@
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="2"/>
       <c r="B524" s="21" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C524" s="21"/>
       <c r="D524" s="21"/>
@@ -9059,7 +9090,7 @@
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2"/>
       <c r="B525" s="21" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C525" s="21"/>
       <c r="D525" s="21"/>
@@ -9068,7 +9099,7 @@
     <row r="526" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2"/>
       <c r="B526" s="21" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C526" s="21"/>
       <c r="D526" s="21"/>
@@ -9077,7 +9108,7 @@
     <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2"/>
       <c r="B527" s="21" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C527" s="21"/>
       <c r="D527" s="21"/>
@@ -9086,7 +9117,7 @@
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="2"/>
       <c r="B528" s="21" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C528" s="21"/>
       <c r="D528" s="21"/>
@@ -9095,13 +9126,13 @@
     <row r="529" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="2"/>
       <c r="B529" s="21" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C529" s="21" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D529" s="21" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E529" s="11" t="s">
         <v>515</v>
@@ -9110,10 +9141,10 @@
     <row r="530" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="2"/>
       <c r="B530" s="21" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="C530" s="21" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="D530" s="21"/>
       <c r="E530" s="11"/>
@@ -9121,7 +9152,7 @@
     <row r="531" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="2"/>
       <c r="B531" s="21" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="C531" s="21" t="s">
         <v>77</v>
@@ -9141,7 +9172,7 @@
         <v>247</v>
       </c>
       <c r="B533" s="21" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C533" s="21"/>
       <c r="D533" s="21"/>
@@ -9150,7 +9181,7 @@
     <row r="534" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="2"/>
       <c r="B534" s="21" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="C534" s="21"/>
       <c r="D534" s="21"/>
@@ -9159,7 +9190,7 @@
     <row r="535" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="2"/>
       <c r="B535" s="21" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="C535" s="21"/>
       <c r="D535" s="21"/>
@@ -9168,7 +9199,7 @@
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="2"/>
       <c r="B536" s="21" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C536" s="21"/>
       <c r="D536" s="21"/>
@@ -9177,10 +9208,10 @@
     <row r="537" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="2"/>
       <c r="B537" s="21" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C537" s="21" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="D537" s="21"/>
       <c r="E537" s="11"/>
@@ -9188,7 +9219,7 @@
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="2"/>
       <c r="B538" s="21" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="C538" s="21"/>
       <c r="D538" s="21"/>
@@ -9197,7 +9228,7 @@
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="2"/>
       <c r="B539" s="21" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C539" s="21"/>
       <c r="D539" s="21"/>
@@ -9206,7 +9237,7 @@
     <row r="540" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="2"/>
       <c r="B540" s="21" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C540" s="21"/>
       <c r="D540" s="21"/>
@@ -9215,7 +9246,7 @@
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="2"/>
       <c r="B541" s="21" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C541" s="21"/>
       <c r="D541" s="21"/>
@@ -9224,10 +9255,10 @@
     <row r="542" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="2"/>
       <c r="B542" s="21" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C542" s="21" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D542" s="21"/>
       <c r="E542" s="11"/>
@@ -9235,7 +9266,7 @@
     <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="2"/>
       <c r="B543" s="21" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C543" s="21"/>
       <c r="D543" s="21"/>
@@ -9244,7 +9275,7 @@
     <row r="544" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="2"/>
       <c r="B544" s="21" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C544" s="21"/>
       <c r="D544" s="21"/>
@@ -9253,7 +9284,7 @@
     <row r="545" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="2"/>
       <c r="B545" s="21" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="C545" s="21"/>
       <c r="D545" s="21"/>
@@ -9262,7 +9293,7 @@
     <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="2"/>
       <c r="B546" s="21" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C546" s="21"/>
       <c r="D546" s="21"/>
@@ -9271,7 +9302,7 @@
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="2"/>
       <c r="B547" s="21" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="C547" s="21"/>
       <c r="D547" s="21"/>
@@ -9280,7 +9311,7 @@
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="2"/>
       <c r="B548" s="21" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C548" s="21"/>
       <c r="D548" s="21"/>
@@ -9289,13 +9320,13 @@
     <row r="549" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="2"/>
       <c r="B549" s="21" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C549" s="21" t="s">
         <v>286</v>
       </c>
       <c r="D549" s="21" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E549" s="11" t="s">
         <v>515</v>
@@ -9304,13 +9335,13 @@
     <row r="550" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="2"/>
       <c r="B550" s="21" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="C550" s="21" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D550" s="21" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="E550" s="11" t="s">
         <v>184</v>
@@ -9319,7 +9350,7 @@
     <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="2"/>
       <c r="B551" s="21" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C551" s="21"/>
       <c r="D551" s="21"/>
@@ -9334,10 +9365,10 @@
     </row>
     <row r="553" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B553" s="21" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C553" s="21"/>
       <c r="D553" s="21"/>
@@ -9346,7 +9377,7 @@
     <row r="554" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="2"/>
       <c r="B554" s="21" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C554" s="21"/>
       <c r="D554" s="21"/>
@@ -9355,7 +9386,7 @@
     <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="2"/>
       <c r="B555" s="21" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C555" s="21"/>
       <c r="D555" s="21"/>
@@ -9364,10 +9395,10 @@
     <row r="556" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="2"/>
       <c r="B556" s="21" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C556" s="21" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="D556" s="21"/>
       <c r="E556" s="11"/>
@@ -9382,20 +9413,20 @@
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="2"/>
       <c r="B558" s="21" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="C558" s="21"/>
       <c r="D558" s="21"/>
       <c r="E558" s="11"/>
     </row>
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A559" s="32"/>
-      <c r="B559" s="33" t="s">
-        <v>696</v>
-      </c>
-      <c r="C559" s="33"/>
-      <c r="D559" s="33"/>
-      <c r="E559" s="34"/>
+      <c r="A559" s="33"/>
+      <c r="B559" s="34" t="s">
+        <v>700</v>
+      </c>
+      <c r="C559" s="34"/>
+      <c r="D559" s="34"/>
+      <c r="E559" s="35"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/assets/responsabilidades.xlsx
+++ b/assets/responsabilidades.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="670">
   <si>
     <t xml:space="preserve">Use Case</t>
   </si>
@@ -290,16 +290,6 @@
     <t xml:space="preserve">21. O sistema confirma o registo apresentando os dados do funcionário criado.</t>
   </si>
   <si>
-    <t xml:space="preserve">22. O sistema regista a data e a hora seguindo o formato (YYYY-MM-DD-HH:MM), juntamente com
-o utilizador que realizou o registo e o registo em si.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registar auditoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">criarSnapshot(): ObjetoAuditavel</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -392,11 +382,7 @@
     <t xml:space="preserve">21. O sistema valida que a palavra-passe é um campo textual não vazio.</t>
   </si>
   <si>
-    <t xml:space="preserve">22. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utili­
-zador que realizou a edição e o estado atual do registo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23. O sistema atualiza os dados do funcionário.</t>
+    <t xml:space="preserve">22. O sistema atualiza os dados do funcionário.</t>
   </si>
   <si>
     <t xml:space="preserve">Atualizar funcionário</t>
@@ -440,11 +426,7 @@
     <t xml:space="preserve">4. O gerente confirma a eliminação.</t>
   </si>
   <si>
-    <t xml:space="preserve">5. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador
-que realizou a eliminação e o estado atual do registo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. O sistema remove o funcionário e bloqueia o seu acesso.</t>
+    <t xml:space="preserve">5. O sistema remove o funcionário e bloqueia o seu acesso.</t>
   </si>
   <si>
     <t xml:space="preserve">Remover funcionário</t>
@@ -453,7 +435,7 @@
     <t xml:space="preserve">removerFuncionario(id: int) : bool</t>
   </si>
   <si>
-    <t xml:space="preserve">7. O sistema confirma a eliminação.</t>
+    <t xml:space="preserve">6. O sistema confirma a eliminação.</t>
   </si>
   <si>
     <r>
@@ -497,11 +479,7 @@
     <t xml:space="preserve">6. O gerente confirma o registo.</t>
   </si>
   <si>
-    <t xml:space="preserve">7. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador
-que realizou o registo e o estado atual do funcionário.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. O sistema regista as horas extraordinárias e recalcula automaticamente o valor total a pagar ao
+    <t xml:space="preserve">7. O sistema regista as horas extraordinárias e recalcula automaticamente o valor total a pagar ao
 funcionário no mês corrente.</t>
   </si>
   <si>
@@ -514,7 +492,7 @@
     <t xml:space="preserve">Para saber o novo salario pode-se fazer salario liquido + horas extras * salario por hora</t>
   </si>
   <si>
-    <t xml:space="preserve">9. O sistema apresenta uma confirmação do registo com o valor total atualizado.</t>
+    <t xml:space="preserve">8. O sistema apresenta uma confirmação do registo com o valor total atualizado.</t>
   </si>
   <si>
     <r>
@@ -633,10 +611,6 @@
     <t xml:space="preserve">registarReparacao(nomenclatura: string, descricao: string, preco: Float): Reparacao</t>
   </si>
   <si>
-    <t xml:space="preserve">8. O sistema regista a data e a hora seguindo o formato (YYYY-MM-DD-HH:MM), juntamente com o
-utilizador que realizou o registo e a reparação em si.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -687,11 +661,7 @@
     <t xml:space="preserve">8. O sistema valida que o preço é um valor real positivo com 2 casas decimais.</t>
   </si>
   <si>
-    <t xml:space="preserve">9. sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utili­
-zador que realizou a edição e o estado atual da reparação.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. O sistema atualiza os dados da entrada e apresenta os dados atualizados.</t>
+    <t xml:space="preserve">9. O sistema atualiza os dados da entrada e apresenta os dados atualizados.</t>
   </si>
   <si>
     <t xml:space="preserve">Atualizar serviço de reparação</t>
@@ -732,14 +702,10 @@
     <t xml:space="preserve">3. O gerente seleciona eliminar.</t>
   </si>
   <si>
-    <t xml:space="preserve">5. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador
-que realizou a eliminação e o estado atual da reparação.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. O sistema confirma eliminação.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. O sistema impossibilita o uso da entrada em novas ordens.</t>
+    <t xml:space="preserve">5. O sistema confirma eliminação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. O sistema impossibilita o uso da entrada em novas ordens.</t>
   </si>
   <si>
     <t xml:space="preserve">Desativar serviço de reparação</t>
@@ -834,10 +800,6 @@
     <t xml:space="preserve">10. O sistema apresenta os dados da peça.</t>
   </si>
   <si>
-    <t xml:space="preserve">11. O sistema regista a data e a hora seguindo o formato (YYYY-MM-DD-HH:MM), juntamente com
-o utilizador que realizou o registo e a peça registado.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -891,11 +853,7 @@
     <t xml:space="preserve">8. O sistema valida que o preço de venda é um valor real positivo com 2 casas decimais</t>
   </si>
   <si>
-    <t xml:space="preserve">9. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utili­
-zador que realizou a edição e o estado atual da peça.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. O sistema atualiza os dados da peça</t>
+    <t xml:space="preserve">9. O sistema atualiza os dados da peça</t>
   </si>
   <si>
     <t xml:space="preserve">Atualizar peça</t>
@@ -939,11 +897,7 @@
     <t xml:space="preserve">4. O funcionário confirma a eliminação.</t>
   </si>
   <si>
-    <t xml:space="preserve">5. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador
-que realizou a eliminação e o estado atual da peça.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. O sistema impossibilita a adição de novas entradas em stock da peça removida a partir deste
+    <t xml:space="preserve">5. O sistema impossibilita a adição de novas entradas em stock da peça removida a partir deste
 momento e apresenta uma mensagem de confirmação de eliminação bem-sucedida.</t>
   </si>
   <si>
@@ -1037,10 +991,6 @@
     <t xml:space="preserve">registarStock_PecaSuperior70(id_peca : int, preco_compra : float, data : DateTime, garantia : int, nr_serie : string) : Stock &amp;&amp; registarStock_PecaNormal(id_peca : int, preco_compra : float, data : DateTime) : Stock</t>
   </si>
   <si>
-    <t xml:space="preserve">11. O sistema regista a data e a hora seguindo o formato (YYYY-MM-DD-HH:MM), juntamente com
-o utilizador que realizou os registos e o stock adicionado.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fluxos Alternativos:</t>
   </si>
   <si>
@@ -1118,6 +1068,9 @@
     <t xml:space="preserve">8. O sistema regista data e hora</t>
   </si>
   <si>
+    <t xml:space="preserve">Registar auditoria</t>
+  </si>
+  <si>
     <t xml:space="preserve">9. O sistema atualiza os dados da entrada</t>
   </si>
   <si>
@@ -1210,9 +1163,6 @@
     <t xml:space="preserve">11. O sistema apresenta os dados da nova devolução.</t>
   </si>
   <si>
-    <t xml:space="preserve">12. O sistema regista a data e a hora seguindo o formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou o registo e a devolução.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -1266,7 +1216,7 @@
     <t xml:space="preserve">Validar transição estado</t>
   </si>
   <si>
-    <t xml:space="preserve">10. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a edição e o estado atual da devolução</t>
+    <t xml:space="preserve">10. O sistema confirma as alterações</t>
   </si>
   <si>
     <t xml:space="preserve">(1) [Transição de estado de 'Pendente de Devolução' para 'Devolvida ao Fornecedor'] (Passo 9)</t>
@@ -1367,9 +1317,6 @@
     <t xml:space="preserve">8. O sistema apresenta uma mensagem de confirmação de eliminação bem-sucedida</t>
   </si>
   <si>
-    <t xml:space="preserve">9. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a eliminação e o estado atual da devolução</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -1417,9 +1364,6 @@
     <t xml:space="preserve">registarFornecedor(nome: string, telemovel: string, e-mail: string): Fornecedor</t>
   </si>
   <si>
-    <t xml:space="preserve">7. O sistema regista a data e a hora seguindo o formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou o registo e o fornecedor</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -1464,10 +1408,7 @@
     <t xml:space="preserve">7. O sistema valida que o contacto é um email válido e/ou número de telefone válido</t>
   </si>
   <si>
-    <t xml:space="preserve">8. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a edição e o estado atual do fornecedor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. O sistema atualiza os dados do fornecedor, regista a data, hora e utilizador da edição e apresenta os dados atualizados</t>
+    <t xml:space="preserve">8. O sistema atualiza os dados do fornecedor e apresenta os dados atualizados.</t>
   </si>
   <si>
     <t xml:space="preserve">Atualizar fornecedor</t>
@@ -1511,10 +1452,7 @@
     <t xml:space="preserve">4. O funcionário confirma a eliminação</t>
   </si>
   <si>
-    <t xml:space="preserve">5. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a eliminação e o estado atual do fornecedor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. O sistema impossibilita a associação de peças a este fornecedor e apresenta mensagem de eliminação bem-sucedida</t>
+    <t xml:space="preserve">5. O sistema impossibilita a associação de peças a este fornecedor e apresenta mensagem de eliminação bem-sucedida</t>
   </si>
   <si>
     <t xml:space="preserve">Remover fornecedor</t>
@@ -1600,9 +1538,6 @@
     <t xml:space="preserve">criarEncomenda(pecas: List(Stock)): Encomenda</t>
   </si>
   <si>
-    <t xml:space="preserve">12. O sistema regista a data e a hora seguindo o formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou o registo e a lista criada</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -1656,13 +1591,10 @@
     <t xml:space="preserve">6. O funcionário confirma as alterações</t>
   </si>
   <si>
-    <t xml:space="preserve">7. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a edição e o estado atual da lista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. O sistema valida que nenhuma mudança no estado foi feita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. O sistema atualiza os dados da lista e apresenta os dados atualizados</t>
+    <t xml:space="preserve">7. O sistema valida que nenhuma mudança no estado foi feita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. O sistema atualiza os dados da lista e apresenta os dados atualizados</t>
   </si>
   <si>
     <t xml:space="preserve">Atualizar lista encomendas</t>
@@ -1671,22 +1603,22 @@
     <t xml:space="preserve">atualizarPecasEncomenda(id : int, pecas : List(Stock)) : void &amp;&amp; atualizarDataChegadaEncomenda(id : int, data_chegada : DateTime) : void &amp;&amp; atualizarDataPedidoEncomenda(id : int, data_pedido : DateTime) : void &amp;&amp; atualizarEstadoEncomenda(id : int, estado : EstadoEncomenda) : void</t>
   </si>
   <si>
-    <t xml:space="preserve">(1) [Estado alterado de 'Rascunho' para 'Enviada'] (Passo 8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1.1 Retorna ao passo 9</t>
+    <t xml:space="preserve">(1) [Estado alterado de 'Rascunho' para 'Enviada'] (Passo 7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1.1 Retorna ao passo 8</t>
   </si>
   <si>
     <t xml:space="preserve">(2) [Estado alterado de 'Enviada' para 'Recebida'] (Passo 7)</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2.1 O sistema valida que nenhuma peça tem preço superior a 70€</t>
+    <t xml:space="preserve">7.2.1 O sistema valida que nenhuma peça tem preço superior a 70€</t>
   </si>
   <si>
     <t xml:space="preserve">Validar limite preço</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2.2 O sistema adiciona automaticamente ao stock as peças registadas na lista</t>
+    <t xml:space="preserve">7.2.2 O sistema adiciona automaticamente ao stock as peças registadas na lista</t>
   </si>
   <si>
     <t xml:space="preserve">Adicionar ao stock as peças recebidas na encomenda</t>
@@ -1695,37 +1627,37 @@
     <t xml:space="preserve">adicionar_PecasEncomenda_Stock(pecas : List(Stock)) : void</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2.3 Retorna ao passo 9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3) [Preço superior a 70€] (Passo 8.2.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2.1.1 O funcionário introduz o número de série para cada unidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2.1.2 O funcionário introduz o tempo de garantia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2.1.3 O sistema valida o número de série</t>
+    <t xml:space="preserve">7.2.3 Retorna ao passo 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3) [Preço superior a 70€] (Passo 7.2.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2.1.1 O funcionário introduz o número de série para cada unidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2.1.2 O funcionário introduz o tempo de garantia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2.1.3 O sistema valida o número de série</t>
   </si>
   <si>
     <t xml:space="preserve">Validar número série</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2.1.4 O sistema valida o tempo de garantia</t>
+    <t xml:space="preserve">7.2.1.4 O sistema valida o tempo de garantia</t>
   </si>
   <si>
     <t xml:space="preserve">Validar tempo garantia</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2.1.5 O sistema adiciona automaticamente ao stock as peças registadas na lista</t>
+    <t xml:space="preserve">7.2.1.5 O sistema adiciona automaticamente ao stock as peças registadas na lista</t>
   </si>
   <si>
     <t xml:space="preserve">adicionarPecasEncomenda(pecas : List(Stock)) : void</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2.1.6 Retorna ao passo 9</t>
+    <t xml:space="preserve">7.2.1.6 Retorna ao passo 8</t>
   </si>
   <si>
     <r>
@@ -1760,10 +1692,7 @@
     <t xml:space="preserve">3. O funcionário seleciona a opção de eliminar a lista</t>
   </si>
   <si>
-    <t xml:space="preserve">5. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a eliminação e o estado atual da lista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. O sistema remove a lista e apresenta mensagem de eliminação bem-sucedida</t>
+    <t xml:space="preserve">5. O sistema remove a lista e apresenta mensagem de eliminação bem-sucedida</t>
   </si>
   <si>
     <t xml:space="preserve">Remover lista</t>
@@ -1825,9 +1754,6 @@
     <t xml:space="preserve">Cliente</t>
   </si>
   <si>
-    <t xml:space="preserve">9. O sistema regista data e hora</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -1875,10 +1801,7 @@
     <t xml:space="preserve">9. O sistema valida que o NIF é composto por 9 dígitos</t>
   </si>
   <si>
-    <t xml:space="preserve">10. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a edição e o estado atual do cliente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. O sistema atualiza os dados do cliente e apresenta os dados atualizados</t>
+    <t xml:space="preserve">10. O sistema atualiza os dados do cliente e apresenta os dados atualizados</t>
   </si>
   <si>
     <t xml:space="preserve">Atualizar cliente</t>
@@ -1919,10 +1842,7 @@
     <t xml:space="preserve">3. O funcionário seleciona a opção de eliminar o cliente</t>
   </si>
   <si>
-    <t xml:space="preserve">5. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a eliminação e o estado atual do cliente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. A partir deste momento, o sistema impossibilita a associação de novas OS e propriedades a este cliente e apresenta uma mensagem de confirmação de eliminação bem-sucedida</t>
+    <t xml:space="preserve">5. A partir deste momento, o sistema impossibilita a associação de novas OS e propriedades a este cliente e apresenta uma mensagem de confirmação de eliminação bem-sucedida</t>
   </si>
   <si>
     <t xml:space="preserve">Remover cliente</t>
@@ -2017,9 +1937,6 @@
     <t xml:space="preserve">registarTrotinete(modelo: string, marca: string, numero_serie: string, tipo_moto: string, id_cliente: int): Trotinete</t>
   </si>
   <si>
-    <t xml:space="preserve">12. O sistema regista a data e a hora seguindo o formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou o registo e a trotinete</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -2073,10 +1990,7 @@
     <t xml:space="preserve">9. O sistema valida que o tipo de motor é um tipo de motor válido</t>
   </si>
   <si>
-    <t xml:space="preserve">10. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a edição e o estado atual da trotinete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. O sistema atualiza os dados da trotinete e apresenta os dados atualizados</t>
+    <t xml:space="preserve">10. O sistema atualiza os dados da trotinete e apresenta os dados atualizados</t>
   </si>
   <si>
     <t xml:space="preserve">Atualizar trotinete</t>
@@ -2117,10 +2031,7 @@
     <t xml:space="preserve">3. O funcionário seleciona a opção de eliminar a trotinete</t>
   </si>
   <si>
-    <t xml:space="preserve">5. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a eliminação e o estado atual da trotinete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. O sistema remove a trotinete, impossibilita a associação de novas ordens de serviço a esta trotinete e apresenta uma mensagem de eliminação bem-sucedida</t>
+    <t xml:space="preserve">5. O sistema remove a trotinete, impossibilita a associação de novas ordens de serviço a esta trotinete e apresenta uma mensagem de eliminação bem-sucedida</t>
   </si>
   <si>
     <t xml:space="preserve">Remover trotinete</t>
@@ -2176,7 +2087,7 @@
     <t xml:space="preserve">10. O sistema valida que a descrição do problema é um campo textual não vazio</t>
   </si>
   <si>
-    <t xml:space="preserve">11. O sistema cria a ordem de serviço, atribui um identificador Único numérico, define o estado como Pendente Diagnóstico, regista a data, hora e utilizador da criação, calcula o tempo estimado para a conclusão da reparação e apresenta os dados da nova ordem de serviço e o tempo estimado</t>
+    <t xml:space="preserve">11. O sistema cria a ordem de serviço, atribui um identificador Único numérico, define o estado como Pendente Diagnóstico e apresenta os dados da nova ordem de serviço.</t>
   </si>
   <si>
     <t xml:space="preserve">Criar OS</t>
@@ -2186,9 +2097,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ordens de Serviço</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12. O sistema regista a data e a hora seguindo o formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou o registo e a OS</t>
   </si>
   <si>
     <t xml:space="preserve">(1) [O cliente não tem trotinetes registadas] (Passo 5)</t>
@@ -2292,10 +2200,7 @@
     <t xml:space="preserve">9. O sistema valida que a descrição do problema é um campo textual não vazio</t>
   </si>
   <si>
-    <t xml:space="preserve">10. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a edição e o estado atual da OS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. O sistema atualiza os dados da ordem de serviço, regista a data, hora, utilizador e o estado em que ficou, e apresenta os dados atualizados</t>
+    <t xml:space="preserve">10. O sistema atualiza os dados da ordem de serviço e apresenta os dados atualizados.</t>
   </si>
   <si>
     <t xml:space="preserve">Atualizar OS</t>
@@ -2504,10 +2409,7 @@
     <t xml:space="preserve">3. O funcionário seleciona a opção de eliminar a ordem de serviço</t>
   </si>
   <si>
-    <t xml:space="preserve">5. O sistema regista a data e a hora no formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a eliminação e o estado atual da OS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. O sistema altera o estado da OS para Eliminada, regista data, hora e utilizador, impossibilita o uso dos dados da OS para estatí­sticas e apresenta mensagem de eliminação bem-sucedida</t>
+    <t xml:space="preserve">5. O sistema altera o estado da OS para Eliminada, regista data, hora e utilizador, impossibilita o uso dos dados da OS para estatí­sticas e apresenta mensagem de eliminação bem-sucedida</t>
   </si>
   <si>
     <t xml:space="preserve">removerOS(id: int) : bool</t>
@@ -2634,7 +2536,7 @@
     <t xml:space="preserve">Validar quantidades</t>
   </si>
   <si>
-    <t xml:space="preserve">7. O sistema calcula o valor do orçamento e valida que é inferior a 50€</t>
+    <t xml:space="preserve">7. O sistema calcula o valor do orçamento e altera o estado da OS para "Pendente aprovação do orçamento" e gera um alerta com o identificador da OS e o seu estado para a secretária</t>
   </si>
   <si>
     <t xml:space="preserve">Validar limite orçamento</t>
@@ -2643,28 +2545,19 @@
     <t xml:space="preserve">calcularOrcamento(listaPecas: List(QuantidadePeca), reparacoes : List(Reparacao)): float</t>
   </si>
   <si>
-    <t xml:space="preserve">8. O sistema altera o estado da OS para 'Pendente Reparação'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. O sistema regista a data e a hora seguindo o formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou o diagnóstico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1) [O valor do orçamento é superior a 50€] (Passo 7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1 O sistema altera o estado da OS para 'Pendente aprovação do orçamento' e gera um alerta com o identificador da OS e o seu estado para a secretária</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerar alerta &amp;&amp; Atualizar estado OS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">criarNotificacao(descricao : string, id_remetente : int, id_destinatario : int) : Notificacao &amp;&amp; alterarEstadoOS(id : int, estado : EstadoOS) : void</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ordens de Serviço &amp;&amp; Notificacoes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2 Retorna ao passo 9</t>
+    <t xml:space="preserve">Fluxos Exceção:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1) [O funcionário cancela o diagnóstico] (Passo 5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1 - O sistema cancela o processo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2) [Quantidade inválida ou superior ao stock disponível] (Passo 6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1 - O sistema informa o funcionário que a quantidade da peça deve ser um valor inteiro positivo ou excede o stock disponível e impede a adição.</t>
   </si>
   <si>
     <r>
@@ -2756,7 +2649,10 @@
     <t xml:space="preserve">Atualizar estado OS/Gerar alerta</t>
   </si>
   <si>
-    <t xml:space="preserve">15. O sistema regista a data e a hora seguindo o formato (YYYY-MM-DD-HH:MM), juntamente com o utilizador que realizou a reparação</t>
+    <t xml:space="preserve">criarNotificacao(descricao : string, id_remetente : int, id_destinatario : int) : Notificacao &amp;&amp; alterarEstadoOS(id : int, estado : EstadoOS) : void</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ordens de Serviço &amp;&amp; Notificacoes</t>
   </si>
   <si>
     <t xml:space="preserve">(1) [Uma peça prescrita no diagnóstico não está disponí­vel em stock] (Passo 2)</t>
@@ -3077,7 +2973,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3203,10 +3099,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3414,7 +3306,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="65.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -3829,42 +3721,36 @@
       <c r="D31" s="12"/>
       <c r="E31" s="12"/>
     </row>
-    <row r="32" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="10"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+    </row>
+    <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6"/>
+      <c r="B33" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C33" s="8"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D32" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-    </row>
-    <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="10"/>
       <c r="C35" s="11"/>
       <c r="D35" s="12"/>
       <c r="E35" s="12"/>
@@ -3872,40 +3758,40 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
       <c r="B36" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
+      <c r="E36" s="12" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
       <c r="B37" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C37" s="11"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+    </row>
+    <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
       <c r="B38" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="12"/>
       <c r="E38" s="12"/>
     </row>
-    <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
       <c r="B39" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="12"/>
@@ -3914,41 +3800,43 @@
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
       <c r="B40" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="11"/>
+        <v>84</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="D40" s="12"/>
       <c r="E40" s="12"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
       <c r="B41" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="12"/>
     </row>
-    <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
       <c r="B42" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="12"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="12"/>
@@ -3956,21 +3844,21 @@
     <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
       <c r="B44" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="12"/>
     </row>
-    <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
       <c r="B45" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="12"/>
@@ -3978,10 +3866,10 @@
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
       <c r="B46" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="12"/>
@@ -3989,10 +3877,10 @@
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
       <c r="B47" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="12"/>
@@ -4000,10 +3888,10 @@
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
       <c r="B48" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="12"/>
@@ -4011,10 +3899,10 @@
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
       <c r="B49" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="12"/>
@@ -4022,21 +3910,21 @@
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
       <c r="B50" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="12"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
       <c r="B51" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="12"/>
@@ -4044,10 +3932,10 @@
     <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
       <c r="B52" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="12"/>
@@ -4055,10 +3943,10 @@
     <row r="53" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
       <c r="B53" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="12"/>
@@ -4066,10 +3954,10 @@
     <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
       <c r="B54" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="12"/>
@@ -4077,84 +3965,78 @@
     <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
       <c r="B55" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D55" s="12"/>
       <c r="E55" s="12"/>
     </row>
-    <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="244.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
       <c r="B56" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D56" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C56" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-    </row>
-    <row r="57" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E56" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="10"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+    </row>
+    <row r="58" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6"/>
+      <c r="B58" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C57" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="244.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2"/>
-      <c r="B58" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>24</v>
-      </c>
+      <c r="C58" s="8"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2"/>
+      <c r="A59" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="B59" s="10"/>
       <c r="C59" s="11"/>
       <c r="D59" s="12"/>
       <c r="E59" s="12"/>
     </row>
-    <row r="60" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6"/>
-      <c r="B60" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C60" s="8"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C60" s="11"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B61" s="10"/>
-      <c r="C61" s="11"/>
+      <c r="A61" s="2"/>
+      <c r="B61" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="D61" s="12"/>
       <c r="E61" s="12"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
       <c r="B62" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="12"/>
@@ -4163,22 +4045,26 @@
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
       <c r="B63" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>82</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="C63" s="11"/>
       <c r="D63" s="12"/>
       <c r="E63" s="12"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
       <c r="B64" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C64" s="11"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
+      <c r="E64" s="12" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
@@ -4189,62 +4075,56 @@
       <c r="D65" s="12"/>
       <c r="E65" s="12"/>
     </row>
-    <row r="66" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
-      <c r="B66" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>77</v>
-      </c>
+      <c r="B66" s="10"/>
+      <c r="C66" s="11"/>
       <c r="D66" s="12"/>
       <c r="E66" s="12"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2"/>
-      <c r="B67" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>24</v>
-      </c>
+    <row r="67" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="6"/>
+      <c r="B67" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C67" s="8"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="9"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2"/>
-      <c r="B68" s="10" t="s">
-        <v>116</v>
-      </c>
+      <c r="A68" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68" s="10"/>
       <c r="C68" s="11"/>
       <c r="D68" s="12"/>
       <c r="E68" s="12"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
-      <c r="B69" s="10"/>
+      <c r="B69" s="10" t="s">
+        <v>104</v>
+      </c>
       <c r="C69" s="11"/>
       <c r="D69" s="12"/>
       <c r="E69" s="12"/>
     </row>
-    <row r="70" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="6"/>
-      <c r="B70" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C70" s="8"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B71" s="10"/>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2"/>
+      <c r="B70" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+    </row>
+    <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="10" t="s">
+        <v>113</v>
+      </c>
       <c r="C71" s="11"/>
       <c r="D71" s="12"/>
       <c r="E71" s="12"/>
@@ -4252,7 +4132,7 @@
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
       <c r="B72" s="10" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="12"/>
@@ -4261,15 +4141,19 @@
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
       <c r="B73" s="10" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D73" s="12"/>
-      <c r="E73" s="12"/>
-    </row>
-    <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>116</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
       <c r="B74" s="10" t="s">
         <v>118</v>
@@ -4278,469 +4162,449 @@
       <c r="D74" s="12"/>
       <c r="E74" s="12"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
       <c r="B75" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="C75" s="11"/>
-      <c r="D75" s="12"/>
-      <c r="E75" s="12"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C75" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="G75" s="15"/>
+    </row>
+    <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
       <c r="B76" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="E76" s="12" t="s">
-        <v>24</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="C76" s="11"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
-      <c r="B77" s="10" t="s">
-        <v>123</v>
-      </c>
+      <c r="B77" s="10"/>
       <c r="C77" s="11"/>
       <c r="D77" s="12"/>
       <c r="E77" s="12"/>
     </row>
-    <row r="78" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2"/>
-      <c r="B78" s="10" t="s">
+    <row r="78" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="6"/>
+      <c r="B78" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C78" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E78" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
-      <c r="B79" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="E79" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F79" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="G79" s="15"/>
-    </row>
-    <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C78" s="8"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B79" s="10"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="12"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
       <c r="B80" s="10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="12"/>
       <c r="E80" s="12"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
-      <c r="B81" s="10"/>
+      <c r="B81" s="10" t="s">
+        <v>126</v>
+      </c>
       <c r="C81" s="11"/>
       <c r="D81" s="12"/>
       <c r="E81" s="12"/>
     </row>
-    <row r="82" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="6"/>
-      <c r="B82" s="7" t="s">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2"/>
+      <c r="B82" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C82" s="11"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+    </row>
+    <row r="83" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2"/>
+      <c r="B83" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D83" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C82" s="8"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B83" s="10"/>
-      <c r="C83" s="11"/>
-      <c r="D83" s="12"/>
-      <c r="E83" s="12"/>
+      <c r="E83" s="12" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
-      <c r="B84" s="10" t="s">
-        <v>131</v>
-      </c>
+      <c r="B84" s="10"/>
       <c r="C84" s="11"/>
       <c r="D84" s="12"/>
       <c r="E84" s="12"/>
     </row>
-    <row r="85" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2"/>
-      <c r="B85" s="10" t="s">
+    <row r="85" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="6"/>
+      <c r="B85" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C85" s="11"/>
-      <c r="D85" s="12"/>
-      <c r="E85" s="12"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2"/>
-      <c r="B86" s="10" t="s">
-        <v>133</v>
-      </c>
+      <c r="A86" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B86" s="10"/>
       <c r="C86" s="11"/>
       <c r="D86" s="12"/>
       <c r="E86" s="12"/>
     </row>
-    <row r="87" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
       <c r="B87" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C87" s="11"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+    </row>
+    <row r="88" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2"/>
+      <c r="B88" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C87" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2"/>
-      <c r="B88" s="10"/>
       <c r="C88" s="11"/>
       <c r="D88" s="12"/>
       <c r="E88" s="12"/>
     </row>
-    <row r="89" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="6"/>
-      <c r="B89" s="7" t="s">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2"/>
+      <c r="B89" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89" s="11"/>
+      <c r="D89" s="12"/>
+      <c r="E89" s="12"/>
+    </row>
+    <row r="90" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2"/>
+      <c r="B90" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E90" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="C89" s="8"/>
-      <c r="D89" s="9"/>
-      <c r="E89" s="9"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B90" s="10"/>
-      <c r="C90" s="11"/>
-      <c r="D90" s="12"/>
-      <c r="E90" s="12"/>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="91" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
       <c r="B91" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="C91" s="11"/>
-      <c r="D91" s="12"/>
-      <c r="E91" s="12"/>
+      <c r="C91" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
       <c r="B92" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="C92" s="11"/>
-      <c r="D92" s="12"/>
-      <c r="E92" s="12"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>142</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
       <c r="B93" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C93" s="11"/>
-      <c r="D93" s="12"/>
-      <c r="E93" s="12"/>
-    </row>
-    <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>145</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
-      <c r="B94" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="C94" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D94" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E94" s="12" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2"/>
-      <c r="B95" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="E95" s="12" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2"/>
-      <c r="B96" s="10" t="s">
+      <c r="B94" s="10"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="12"/>
+      <c r="E94" s="12"/>
+    </row>
+    <row r="95" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="6"/>
+      <c r="B95" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C96" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D96" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E96" s="12" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C95" s="8"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B96" s="10"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="12"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
       <c r="B97" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="C97" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E97" s="12" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>149</v>
+      </c>
+      <c r="C97" s="11"/>
+      <c r="D97" s="12"/>
+      <c r="E97" s="12"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
       <c r="B98" s="10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
-      <c r="B99" s="10"/>
+      <c r="B99" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="C99" s="11"/>
       <c r="D99" s="12"/>
       <c r="E99" s="12"/>
     </row>
-    <row r="100" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="6"/>
-      <c r="B100" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C100" s="8"/>
-      <c r="D100" s="9"/>
-      <c r="E100" s="9"/>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2"/>
+      <c r="B100" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C100" s="11"/>
+      <c r="D100" s="12"/>
+      <c r="E100" s="12"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B101" s="10"/>
+      <c r="A101" s="2"/>
+      <c r="B101" s="10" t="s">
+        <v>83</v>
+      </c>
       <c r="C101" s="11"/>
       <c r="D101" s="12"/>
       <c r="E101" s="12"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
       <c r="B102" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="C102" s="11"/>
+        <v>155</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>136</v>
+      </c>
       <c r="D102" s="12"/>
       <c r="E102" s="12"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
       <c r="B103" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="D103" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E103" s="12" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+      <c r="D103" s="12"/>
+      <c r="E103" s="12"/>
+    </row>
+    <row r="104" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
       <c r="B104" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="C104" s="11"/>
+        <v>157</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>143</v>
+      </c>
       <c r="D104" s="12"/>
       <c r="E104" s="12"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2"/>
       <c r="B105" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="C105" s="11"/>
-      <c r="D105" s="12"/>
-      <c r="E105" s="12"/>
+        <v>158</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2"/>
-      <c r="B106" s="10" t="s">
-        <v>86</v>
-      </c>
+      <c r="B106" s="10"/>
       <c r="C106" s="11"/>
       <c r="D106" s="12"/>
       <c r="E106" s="12"/>
     </row>
-    <row r="107" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2"/>
-      <c r="B107" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="C107" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D107" s="12"/>
-      <c r="E107" s="12"/>
-    </row>
-    <row r="108" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2"/>
-      <c r="B108" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="C108" s="11" t="s">
-        <v>146</v>
-      </c>
+    <row r="107" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="6"/>
+      <c r="B107" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C107" s="8"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="9"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B108" s="10"/>
+      <c r="C108" s="11"/>
       <c r="D108" s="12"/>
       <c r="E108" s="12"/>
     </row>
-    <row r="109" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2"/>
       <c r="B109" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="C109" s="11" t="s">
-        <v>149</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="C109" s="11"/>
       <c r="D109" s="12"/>
       <c r="E109" s="12"/>
     </row>
-    <row r="110" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2"/>
       <c r="B110" s="10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2"/>
       <c r="B111" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="C111" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="D111" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E111" s="12" t="s">
-        <v>144</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="C111" s="11"/>
+      <c r="D111" s="12"/>
+      <c r="E111" s="12"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2"/>
-      <c r="B112" s="10"/>
+      <c r="B112" s="10" t="s">
+        <v>107</v>
+      </c>
       <c r="C112" s="11"/>
       <c r="D112" s="12"/>
       <c r="E112" s="12"/>
     </row>
-    <row r="113" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="6"/>
-      <c r="B113" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C113" s="8"/>
-      <c r="D113" s="9"/>
-      <c r="E113" s="9"/>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2"/>
+      <c r="B113" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C113" s="11"/>
+      <c r="D113" s="12"/>
+      <c r="E113" s="12"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B114" s="10"/>
-      <c r="C114" s="11"/>
-      <c r="D114" s="12"/>
-      <c r="E114" s="12"/>
+      <c r="A114" s="2"/>
+      <c r="B114" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E114" s="12" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2"/>
-      <c r="B115" s="10" t="s">
-        <v>170</v>
-      </c>
+      <c r="B115" s="10"/>
       <c r="C115" s="11"/>
       <c r="D115" s="12"/>
       <c r="E115" s="12"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2"/>
-      <c r="B116" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="C116" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="D116" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E116" s="12" t="s">
-        <v>144</v>
-      </c>
+    <row r="116" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="6"/>
+      <c r="B116" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C116" s="8"/>
+      <c r="D116" s="9"/>
+      <c r="E116" s="9"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="2"/>
-      <c r="B117" s="10" t="s">
-        <v>172</v>
-      </c>
+      <c r="A117" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B117" s="10"/>
       <c r="C117" s="11"/>
       <c r="D117" s="12"/>
       <c r="E117" s="12"/>
@@ -4748,158 +4612,158 @@
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2"/>
       <c r="B118" s="10" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="12"/>
       <c r="E118" s="12"/>
     </row>
-    <row r="119" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2"/>
       <c r="B119" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D119" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E119" s="12" t="s">
-        <v>144</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="C119" s="11"/>
+      <c r="D119" s="12"/>
+      <c r="E119" s="12"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2"/>
       <c r="B120" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D120" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="C120" s="11"/>
-      <c r="D120" s="12"/>
-      <c r="E120" s="12"/>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E120" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2"/>
       <c r="B121" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="C121" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="D121" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="E121" s="12" t="s">
-        <v>144</v>
-      </c>
+      <c r="C121" s="11"/>
+      <c r="D121" s="12"/>
+      <c r="E121" s="12"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2"/>
-      <c r="B122" s="10"/>
+      <c r="B122" s="10" t="s">
+        <v>177</v>
+      </c>
       <c r="C122" s="11"/>
       <c r="D122" s="12"/>
       <c r="E122" s="12"/>
     </row>
-    <row r="123" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="6"/>
-      <c r="B123" s="7" t="s">
+    <row r="123" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="2"/>
+      <c r="B123" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C123" s="8"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
-    </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B124" s="10"/>
-      <c r="C124" s="11"/>
-      <c r="D124" s="12"/>
-      <c r="E124" s="12"/>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C123" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E123" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="2"/>
+      <c r="B124" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C124" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E124" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2"/>
       <c r="B125" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="C125" s="11"/>
-      <c r="D125" s="12"/>
-      <c r="E125" s="12"/>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>184</v>
+      </c>
+      <c r="C125" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D125" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E125" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2"/>
       <c r="B126" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="C126" s="11"/>
-      <c r="D126" s="12"/>
-      <c r="E126" s="12"/>
+        <v>187</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="E126" s="12" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2"/>
       <c r="B127" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="C127" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D127" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="E127" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>190</v>
+      </c>
+      <c r="C127" s="11"/>
+      <c r="D127" s="12"/>
+      <c r="E127" s="12"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2"/>
-      <c r="B128" s="10" t="s">
-        <v>185</v>
-      </c>
+      <c r="B128" s="10"/>
       <c r="C128" s="11"/>
       <c r="D128" s="12"/>
       <c r="E128" s="12"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="2"/>
-      <c r="B129" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="C129" s="11"/>
-      <c r="D129" s="12"/>
-      <c r="E129" s="12"/>
-    </row>
-    <row r="130" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="2"/>
-      <c r="B130" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="C130" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="D130" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="E130" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="6"/>
+      <c r="B129" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C129" s="8"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="9"/>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B130" s="10"/>
+      <c r="C130" s="11"/>
+      <c r="D130" s="12"/>
+      <c r="E130" s="12"/>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2"/>
       <c r="B131" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="C131" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="D131" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="E131" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C131" s="11"/>
+      <c r="D131" s="12"/>
+      <c r="E131" s="12"/>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2"/>
       <c r="B132" s="10" t="s">
         <v>193</v>
@@ -4911,111 +4775,105 @@
         <v>195</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2"/>
       <c r="B133" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="C133" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="D133" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="E133" s="12" t="s">
-        <v>184</v>
-      </c>
+      <c r="C133" s="11"/>
+      <c r="D133" s="12"/>
+      <c r="E133" s="12"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2"/>
       <c r="B134" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C134" s="11"/>
       <c r="D134" s="12"/>
       <c r="E134" s="12"/>
     </row>
-    <row r="135" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2"/>
       <c r="B135" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="C135" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D135" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E135" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>198</v>
+      </c>
+      <c r="C135" s="11"/>
+      <c r="D135" s="12"/>
+      <c r="E135" s="12"/>
+    </row>
+    <row r="136" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2"/>
-      <c r="B136" s="10"/>
-      <c r="C136" s="11"/>
+      <c r="B136" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>179</v>
+      </c>
       <c r="D136" s="12"/>
       <c r="E136" s="12"/>
     </row>
-    <row r="137" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="6"/>
-      <c r="B137" s="7" t="s">
+    <row r="137" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="2"/>
+      <c r="B137" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C137" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D137" s="12"/>
+      <c r="E137" s="12"/>
+    </row>
+    <row r="138" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="2"/>
+      <c r="B138" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="C137" s="8"/>
-      <c r="D137" s="9"/>
-      <c r="E137" s="9"/>
-    </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B138" s="10"/>
-      <c r="C138" s="11"/>
+      <c r="C138" s="11" t="s">
+        <v>185</v>
+      </c>
       <c r="D138" s="12"/>
       <c r="E138" s="12"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2"/>
       <c r="B139" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="C139" s="11"/>
-      <c r="D139" s="12"/>
-      <c r="E139" s="12"/>
+      <c r="C139" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D139" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="E139" s="12" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2"/>
-      <c r="B140" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C140" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="D140" s="12" t="s">
+      <c r="B140" s="10"/>
+      <c r="C140" s="11"/>
+      <c r="D140" s="12"/>
+      <c r="E140" s="12"/>
+    </row>
+    <row r="141" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="6"/>
+      <c r="B141" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="E140" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="2"/>
-      <c r="B141" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="C141" s="11"/>
-      <c r="D141" s="12"/>
-      <c r="E141" s="12"/>
+      <c r="C141" s="8"/>
+      <c r="D141" s="9"/>
+      <c r="E141" s="9"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="2"/>
-      <c r="B142" s="10" t="s">
-        <v>207</v>
-      </c>
+      <c r="A142" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B142" s="10"/>
       <c r="C142" s="11"/>
       <c r="D142" s="12"/>
       <c r="E142" s="12"/>
@@ -5023,125 +4881,120 @@
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2"/>
       <c r="B143" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="C143" s="11"/>
-      <c r="D143" s="12"/>
-      <c r="E143" s="12"/>
-    </row>
-    <row r="144" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>206</v>
+      </c>
+      <c r="C143" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="D143" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E143" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2"/>
       <c r="B144" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="C144" s="11" t="s">
-        <v>188</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="C144" s="11"/>
       <c r="D144" s="12"/>
       <c r="E144" s="12"/>
     </row>
-    <row r="145" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2"/>
       <c r="B145" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="C145" s="11" t="s">
-        <v>191</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="C145" s="11"/>
       <c r="D145" s="12"/>
       <c r="E145" s="12"/>
     </row>
-    <row r="146" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2"/>
       <c r="B146" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="C146" s="11" t="s">
-        <v>194</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="C146" s="11"/>
       <c r="D146" s="12"/>
       <c r="E146" s="12"/>
     </row>
-    <row r="147" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2"/>
       <c r="B147" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C147" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="D147" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="C147" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D147" s="12" t="s">
-        <v>78</v>
-      </c>
       <c r="E147" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2"/>
-      <c r="B148" s="10" t="s">
+      <c r="B148" s="10"/>
+      <c r="C148" s="11"/>
+      <c r="D148" s="12"/>
+      <c r="E148" s="12"/>
+      <c r="H148" s="1"/>
+    </row>
+    <row r="149" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="6"/>
+      <c r="B149" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C148" s="11" t="s">
+      <c r="C149" s="8"/>
+      <c r="D149" s="9"/>
+      <c r="E149" s="9"/>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B150" s="10"/>
+      <c r="C150" s="11"/>
+      <c r="D150" s="12"/>
+      <c r="E150" s="12"/>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="2"/>
+      <c r="B151" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="D148" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="E148" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="2"/>
-      <c r="B149" s="10"/>
-      <c r="C149" s="11"/>
-      <c r="D149" s="12"/>
-      <c r="E149" s="12"/>
-    </row>
-    <row r="150" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="6"/>
-      <c r="B150" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C150" s="8"/>
-      <c r="D150" s="9"/>
-      <c r="E150" s="9"/>
-    </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B151" s="10"/>
       <c r="C151" s="11"/>
       <c r="D151" s="12"/>
       <c r="E151" s="12"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2"/>
       <c r="B152" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C152" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="D152" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="E152" s="12" t="s">
-        <v>184</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="C152" s="11"/>
+      <c r="D152" s="12"/>
+      <c r="E152" s="12"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2"/>
       <c r="B153" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D153" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="C153" s="11"/>
-      <c r="D153" s="12"/>
-      <c r="E153" s="12"/>
-    </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E153" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2"/>
       <c r="B154" s="10" t="s">
         <v>219</v>
@@ -5159,215 +5012,207 @@
       <c r="D155" s="12"/>
       <c r="E155" s="12"/>
     </row>
-    <row r="156" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2"/>
       <c r="B156" s="10" t="s">
         <v>221</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>77</v>
+        <v>222</v>
       </c>
       <c r="D156" s="12" t="s">
-        <v>78</v>
+        <v>223</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2"/>
       <c r="B157" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D157" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2"/>
-      <c r="B158" s="10"/>
-      <c r="C158" s="11"/>
+      <c r="B158" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C158" s="11" t="s">
+        <v>228</v>
+      </c>
       <c r="D158" s="12"/>
       <c r="E158" s="12"/>
-      <c r="G158" s="1"/>
-      <c r="H158" s="1"/>
-    </row>
-    <row r="159" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="6"/>
-      <c r="B159" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="C159" s="8"/>
-      <c r="D159" s="9"/>
-      <c r="E159" s="9"/>
-    </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B160" s="10"/>
-      <c r="C160" s="11"/>
-      <c r="D160" s="12"/>
-      <c r="E160" s="12"/>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="2"/>
+      <c r="B159" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C159" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="D159" s="12"/>
+      <c r="E159" s="12"/>
+    </row>
+    <row r="160" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2"/>
+      <c r="B160" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C160" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="D160" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E160" s="12" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2"/>
-      <c r="B161" s="10" t="s">
-        <v>226</v>
-      </c>
+      <c r="B161" s="10"/>
       <c r="C161" s="11"/>
       <c r="D161" s="12"/>
       <c r="E161" s="12"/>
     </row>
-    <row r="162" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="2"/>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="2" t="s">
+        <v>234</v>
+      </c>
       <c r="B162" s="10" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C162" s="11"/>
       <c r="D162" s="12"/>
       <c r="E162" s="12"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2"/>
       <c r="B163" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="C163" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="D163" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E163" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>236</v>
+      </c>
+      <c r="C163" s="11"/>
+      <c r="D163" s="12"/>
+      <c r="E163" s="12"/>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2"/>
       <c r="B164" s="10" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C164" s="11"/>
       <c r="D164" s="12"/>
       <c r="E164" s="12"/>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2"/>
       <c r="B165" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="C165" s="11"/>
-      <c r="D165" s="12"/>
-      <c r="E165" s="12"/>
+        <v>238</v>
+      </c>
+      <c r="C165" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D165" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E165" s="12" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="166" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2"/>
       <c r="B166" s="10" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="E166" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2"/>
       <c r="B167" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="C167" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="D167" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="E167" s="12" t="s">
-        <v>184</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="C167" s="11"/>
+      <c r="D167" s="12"/>
+      <c r="E167" s="12"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2"/>
-      <c r="B168" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="C168" s="11" t="s">
-        <v>240</v>
-      </c>
+      <c r="B168" s="10"/>
+      <c r="C168" s="11"/>
       <c r="D168" s="12"/>
       <c r="E168" s="12"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="2"/>
-      <c r="B169" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="C169" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="D169" s="12"/>
-      <c r="E169" s="12"/>
-    </row>
-    <row r="170" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="2"/>
-      <c r="B170" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="C170" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="D170" s="12" t="s">
+    <row r="169" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="6"/>
+      <c r="B169" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="E170" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C169" s="8"/>
+      <c r="D169" s="9"/>
+      <c r="E169" s="9"/>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B170" s="10"/>
+      <c r="C170" s="20"/>
+      <c r="D170" s="12"/>
+      <c r="E170" s="12"/>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2"/>
       <c r="B171" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="C171" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D171" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E171" s="12" t="s">
-        <v>184</v>
-      </c>
+      <c r="C171" s="11"/>
+      <c r="D171" s="12"/>
+      <c r="E171" s="12"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2"/>
-      <c r="B172" s="10"/>
-      <c r="C172" s="11"/>
-      <c r="D172" s="12"/>
-      <c r="E172" s="12"/>
+      <c r="B172" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C172" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D172" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="E172" s="12" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="2" t="s">
-        <v>247</v>
-      </c>
+      <c r="A173" s="2"/>
       <c r="B173" s="10" t="s">
-        <v>248</v>
+        <v>196</v>
       </c>
       <c r="C173" s="11"/>
       <c r="D173" s="12"/>
       <c r="E173" s="12"/>
     </row>
-    <row r="174" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2"/>
       <c r="B174" s="10" t="s">
         <v>249</v>
@@ -5379,7 +5224,7 @@
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2"/>
       <c r="B175" s="10" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="C175" s="11"/>
       <c r="D175" s="12"/>
@@ -5388,224 +5233,240 @@
     <row r="176" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2"/>
       <c r="B176" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="D176" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="E176" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="177" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>225</v>
+      </c>
+      <c r="D176" s="12"/>
+      <c r="E176" s="12"/>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2"/>
       <c r="B177" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="D177" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="E177" s="12" t="s">
-        <v>184</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="D177" s="12"/>
+      <c r="E177" s="12"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2"/>
       <c r="B178" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="C178" s="11"/>
+        <v>252</v>
+      </c>
+      <c r="C178" s="11" t="s">
+        <v>253</v>
+      </c>
       <c r="D178" s="12"/>
       <c r="E178" s="12"/>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2"/>
-      <c r="B179" s="10"/>
-      <c r="C179" s="11"/>
-      <c r="D179" s="12"/>
-      <c r="E179" s="12"/>
-    </row>
-    <row r="180" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="6"/>
-      <c r="B180" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="C180" s="8"/>
-      <c r="D180" s="9"/>
-      <c r="E180" s="9"/>
-    </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="2" t="s">
+      <c r="B179" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C179" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="D179" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="E179" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="2"/>
+      <c r="B180" s="21"/>
+      <c r="C180" s="21"/>
+      <c r="D180" s="12"/>
+      <c r="E180" s="12"/>
+    </row>
+    <row r="181" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="6"/>
+      <c r="B181" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="C181" s="23"/>
+      <c r="D181" s="23"/>
+      <c r="E181" s="8"/>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B181" s="10"/>
-      <c r="C181" s="20"/>
-      <c r="D181" s="12"/>
-      <c r="E181" s="12"/>
-    </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="2"/>
-      <c r="B182" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="C182" s="11"/>
-      <c r="D182" s="12"/>
-      <c r="E182" s="12"/>
+      <c r="B182" s="21"/>
+      <c r="C182" s="21"/>
+      <c r="D182" s="21"/>
+      <c r="E182" s="11"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2"/>
-      <c r="B183" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C183" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="D183" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="E183" s="12" t="s">
-        <v>184</v>
-      </c>
+      <c r="B183" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="C183" s="21"/>
+      <c r="D183" s="21"/>
+      <c r="E183" s="11"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2"/>
-      <c r="B184" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="C184" s="11"/>
-      <c r="D184" s="12"/>
-      <c r="E184" s="12"/>
+      <c r="B184" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="C184" s="21"/>
+      <c r="D184" s="21"/>
+      <c r="E184" s="11"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2"/>
-      <c r="B185" s="10" t="s">
+      <c r="B185" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C185" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="D185" s="21"/>
+      <c r="E185" s="11"/>
+    </row>
+    <row r="186" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="2"/>
+      <c r="B186" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="C185" s="11"/>
-      <c r="D185" s="12"/>
-      <c r="E185" s="12"/>
-    </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="2"/>
-      <c r="B186" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="C186" s="11"/>
-      <c r="D186" s="12"/>
-      <c r="E186" s="12"/>
-    </row>
-    <row r="187" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C186" s="21"/>
+      <c r="D186" s="21"/>
+      <c r="E186" s="11"/>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2"/>
-      <c r="B187" s="10" t="s">
+      <c r="B187" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="C187" s="21"/>
+      <c r="D187" s="21"/>
+      <c r="E187" s="11"/>
+    </row>
+    <row r="188" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="2"/>
+      <c r="B188" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="C187" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="D187" s="12"/>
-      <c r="E187" s="12"/>
-    </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="2"/>
-      <c r="B188" s="10" t="s">
+      <c r="C188" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="C188" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="D188" s="12"/>
-      <c r="E188" s="12"/>
-    </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D188" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="E188" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F188" s="15"/>
+    </row>
+    <row r="189" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2"/>
-      <c r="B189" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="C189" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D189" s="12"/>
-      <c r="E189" s="12"/>
-    </row>
-    <row r="190" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B189" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="C189" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="D189" s="21"/>
+      <c r="E189" s="11"/>
+    </row>
+    <row r="190" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2"/>
-      <c r="B190" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="C190" s="11" t="s">
+      <c r="B190" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="D190" s="12" t="s">
+      <c r="C190" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="E190" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D190" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="E190" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2"/>
-      <c r="B191" s="21"/>
-      <c r="C191" s="21"/>
-      <c r="D191" s="12"/>
-      <c r="E191" s="12"/>
-    </row>
-    <row r="192" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="6"/>
-      <c r="B192" s="22" t="s">
-        <v>269</v>
-      </c>
-      <c r="C192" s="23"/>
-      <c r="D192" s="23"/>
-      <c r="E192" s="8"/>
+      <c r="B191" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="C191" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="D191" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="E191" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="2"/>
+      <c r="B192" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="C192" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="D192" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="E192" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F192" s="19" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B193" s="21"/>
+      <c r="A193" s="2"/>
+      <c r="B193" s="21" t="s">
+        <v>277</v>
+      </c>
       <c r="C193" s="21"/>
       <c r="D193" s="21"/>
       <c r="E193" s="11"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2"/>
-      <c r="B194" s="21" t="s">
-        <v>270</v>
-      </c>
+      <c r="B194" s="21"/>
       <c r="C194" s="21"/>
       <c r="D194" s="21"/>
       <c r="E194" s="11"/>
-    </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="2"/>
-      <c r="B195" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="C195" s="21"/>
-      <c r="D195" s="21"/>
-      <c r="E195" s="11"/>
+      <c r="F194" s="15"/>
+      <c r="H194" s="1"/>
+      <c r="I194" s="1"/>
+      <c r="J194" s="1"/>
+    </row>
+    <row r="195" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="6"/>
+      <c r="B195" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="C195" s="23"/>
+      <c r="D195" s="23"/>
+      <c r="E195" s="8"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="2"/>
-      <c r="B196" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="C196" s="21" t="s">
-        <v>273</v>
-      </c>
+      <c r="A196" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B196" s="21"/>
+      <c r="C196" s="21"/>
       <c r="D196" s="21"/>
       <c r="E196" s="11"/>
     </row>
-    <row r="197" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2"/>
       <c r="B197" s="21" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C197" s="21"/>
       <c r="D197" s="21"/>
@@ -5614,137 +5475,106 @@
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2"/>
       <c r="B198" s="21" t="s">
-        <v>186</v>
+        <v>280</v>
       </c>
       <c r="C198" s="21"/>
       <c r="D198" s="21"/>
       <c r="E198" s="11"/>
     </row>
-    <row r="199" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2"/>
       <c r="B199" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="C199" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="D199" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="E199" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F199" s="15"/>
+        <v>281</v>
+      </c>
+      <c r="C199" s="21"/>
+      <c r="D199" s="21"/>
+      <c r="E199" s="11"/>
     </row>
     <row r="200" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2"/>
       <c r="B200" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="C200" s="21" t="s">
-        <v>240</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="C200" s="21"/>
       <c r="D200" s="21"/>
       <c r="E200" s="11"/>
     </row>
-    <row r="201" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2"/>
       <c r="B201" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="C201" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="D201" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="E201" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="202" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>198</v>
+      </c>
+      <c r="C201" s="21"/>
+      <c r="D201" s="21"/>
+      <c r="E201" s="11"/>
+    </row>
+    <row r="202" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2"/>
       <c r="B202" s="21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C202" s="21" t="s">
-        <v>283</v>
-      </c>
-      <c r="D202" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="E202" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="203" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D202" s="21"/>
+      <c r="E202" s="11"/>
+    </row>
+    <row r="203" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2"/>
       <c r="B203" s="21" t="s">
         <v>285</v>
       </c>
       <c r="C203" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="D203" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="E203" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F203" s="19" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>228</v>
+      </c>
+      <c r="D203" s="21"/>
+      <c r="E203" s="11"/>
+    </row>
+    <row r="204" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2"/>
       <c r="B204" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="C204" s="21"/>
+        <v>286</v>
+      </c>
+      <c r="C204" s="21" t="s">
+        <v>268</v>
+      </c>
       <c r="D204" s="21"/>
       <c r="E204" s="11"/>
     </row>
-    <row r="205" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2"/>
       <c r="B205" s="21" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C205" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D205" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E205" s="11" t="s">
-        <v>184</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="D205" s="21"/>
+      <c r="E205" s="11"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2"/>
-      <c r="B206" s="21"/>
+      <c r="B206" s="21" t="s">
+        <v>289</v>
+      </c>
       <c r="C206" s="21"/>
       <c r="D206" s="21"/>
       <c r="E206" s="11"/>
-      <c r="F206" s="15"/>
-      <c r="G206" s="1"/>
-      <c r="H206" s="1"/>
-      <c r="I206" s="1"/>
-      <c r="J206" s="1"/>
-    </row>
-    <row r="207" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="6"/>
-      <c r="B207" s="22" t="s">
-        <v>291</v>
-      </c>
-      <c r="C207" s="23"/>
-      <c r="D207" s="23"/>
-      <c r="E207" s="8"/>
-    </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="2"/>
+      <c r="B207" s="21"/>
+      <c r="C207" s="21"/>
+      <c r="D207" s="21"/>
+      <c r="E207" s="11"/>
+    </row>
+    <row r="208" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B208" s="21"/>
+        <v>234</v>
+      </c>
+      <c r="B208" s="21" t="s">
+        <v>290</v>
+      </c>
       <c r="C208" s="21"/>
       <c r="D208" s="21"/>
       <c r="E208" s="11"/>
@@ -5752,25 +5582,34 @@
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2"/>
       <c r="B209" s="21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C209" s="21"/>
       <c r="D209" s="21"/>
       <c r="E209" s="11"/>
     </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2"/>
       <c r="B210" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C210" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="D210" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="C210" s="21"/>
-      <c r="D210" s="21"/>
-      <c r="E210" s="11"/>
+      <c r="E210" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F210" s="19" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2"/>
       <c r="B211" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C211" s="21"/>
       <c r="D211" s="21"/>
@@ -5779,195 +5618,201 @@
     <row r="212" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2"/>
       <c r="B212" s="21" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C212" s="21"/>
       <c r="D212" s="21"/>
       <c r="E212" s="11"/>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2"/>
       <c r="B213" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="C213" s="21"/>
-      <c r="D213" s="21"/>
-      <c r="E213" s="11"/>
-    </row>
-    <row r="214" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>297</v>
+      </c>
+      <c r="C213" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="D213" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="E213" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F213" s="19" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2"/>
       <c r="B214" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="C214" s="21" t="s">
-        <v>297</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="C214" s="21"/>
       <c r="D214" s="21"/>
       <c r="E214" s="11"/>
     </row>
-    <row r="215" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2"/>
-      <c r="B215" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="C215" s="21" t="s">
-        <v>240</v>
-      </c>
+      <c r="B215" s="21"/>
+      <c r="C215" s="21"/>
       <c r="D215" s="21"/>
       <c r="E215" s="11"/>
     </row>
-    <row r="216" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="2"/>
-      <c r="B216" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="C216" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="D216" s="21"/>
-      <c r="E216" s="11"/>
+    <row r="216" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="6"/>
+      <c r="B216" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="C216" s="23"/>
+      <c r="D216" s="23"/>
+      <c r="E216" s="8"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="2"/>
-      <c r="B217" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="C217" s="21" t="s">
-        <v>301</v>
-      </c>
+      <c r="A217" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B217" s="21"/>
+      <c r="C217" s="21"/>
       <c r="D217" s="21"/>
       <c r="E217" s="11"/>
     </row>
-    <row r="218" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2"/>
       <c r="B218" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="C218" s="21" t="s">
-        <v>77</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="C218" s="21"/>
       <c r="D218" s="21"/>
       <c r="E218" s="11"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2"/>
-      <c r="B219" s="21"/>
-      <c r="C219" s="21"/>
-      <c r="D219" s="21"/>
-      <c r="E219" s="11"/>
-    </row>
-    <row r="220" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="2" t="s">
-        <v>247</v>
-      </c>
+      <c r="B219" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="C219" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="D219" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="E219" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="2"/>
       <c r="B220" s="21" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C220" s="21"/>
       <c r="D220" s="21"/>
       <c r="E220" s="11"/>
     </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2"/>
       <c r="B221" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="C221" s="21"/>
-      <c r="D221" s="21"/>
-      <c r="E221" s="11"/>
-    </row>
-    <row r="222" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>307</v>
+      </c>
+      <c r="C221" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="D221" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="E221" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2"/>
       <c r="B222" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="C222" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="D222" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="E222" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F222" s="19" t="s">
-        <v>307</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="C222" s="21"/>
+      <c r="D222" s="21"/>
+      <c r="E222" s="11"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2"/>
       <c r="B223" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="C223" s="21"/>
-      <c r="D223" s="21"/>
-      <c r="E223" s="11"/>
-    </row>
-    <row r="224" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>311</v>
+      </c>
+      <c r="C223" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="D223" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="E223" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2"/>
       <c r="B224" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="C224" s="21"/>
-      <c r="D224" s="21"/>
-      <c r="E224" s="11"/>
+        <v>314</v>
+      </c>
+      <c r="C224" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="D224" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="E224" s="11" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="225" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2"/>
       <c r="B225" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="C225" s="21" t="s">
-        <v>311</v>
-      </c>
-      <c r="D225" s="21" t="s">
-        <v>312</v>
-      </c>
-      <c r="E225" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="F225" s="19" t="s">
-        <v>313</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="C225" s="21"/>
+      <c r="D225" s="21"/>
+      <c r="E225" s="11"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2"/>
-      <c r="B226" s="21" t="s">
-        <v>314</v>
-      </c>
+      <c r="B226" s="21"/>
       <c r="C226" s="21"/>
       <c r="D226" s="21"/>
       <c r="E226" s="11"/>
-    </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="2"/>
-      <c r="B227" s="21"/>
-      <c r="C227" s="21"/>
-      <c r="D227" s="21"/>
-      <c r="E227" s="11"/>
-    </row>
-    <row r="228" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="6"/>
-      <c r="B228" s="22" t="s">
-        <v>315</v>
-      </c>
-      <c r="C228" s="23"/>
-      <c r="D228" s="23"/>
-      <c r="E228" s="8"/>
+      <c r="H226" s="1"/>
+      <c r="I226" s="1"/>
+      <c r="J226" s="1"/>
+    </row>
+    <row r="227" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="6"/>
+      <c r="B227" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="C227" s="23"/>
+      <c r="D227" s="23"/>
+      <c r="E227" s="8"/>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B228" s="21"/>
+      <c r="C228" s="21"/>
+      <c r="D228" s="21"/>
+      <c r="E228" s="11"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B229" s="21"/>
+      <c r="A229" s="2"/>
+      <c r="B229" s="21" t="s">
+        <v>317</v>
+      </c>
       <c r="C229" s="21"/>
       <c r="D229" s="21"/>
       <c r="E229" s="11"/>
     </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2"/>
       <c r="B230" s="21" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C230" s="21"/>
       <c r="D230" s="21"/>
@@ -5976,24 +5821,20 @@
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2"/>
       <c r="B231" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="C231" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="D231" s="21" t="s">
-        <v>318</v>
-      </c>
-      <c r="E231" s="11" t="s">
-        <v>184</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C231" s="21"/>
+      <c r="D231" s="21"/>
+      <c r="E231" s="11"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="2"/>
       <c r="B232" s="21" t="s">
-        <v>319</v>
-      </c>
-      <c r="C232" s="21"/>
+        <v>21</v>
+      </c>
+      <c r="C232" s="21" t="s">
+        <v>22</v>
+      </c>
       <c r="D232" s="21"/>
       <c r="E232" s="11"/>
     </row>
@@ -6005,101 +5846,87 @@
       <c r="C233" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="D233" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="E233" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D233" s="21"/>
+      <c r="E233" s="11"/>
+    </row>
+    <row r="234" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2"/>
       <c r="B234" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="C234" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="C234" s="21"/>
-      <c r="D234" s="21"/>
-      <c r="E234" s="11"/>
+      <c r="D234" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="E234" s="11" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2"/>
-      <c r="B235" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="C235" s="21" t="s">
+      <c r="B235" s="21"/>
+      <c r="C235" s="21"/>
+      <c r="D235" s="21"/>
+      <c r="E235" s="11"/>
+    </row>
+    <row r="236" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="6"/>
+      <c r="B236" s="22" t="s">
         <v>325</v>
       </c>
-      <c r="D235" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="E235" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="236" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="2"/>
-      <c r="B236" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="C236" s="21" t="s">
-        <v>311</v>
-      </c>
-      <c r="D236" s="21" t="s">
-        <v>312</v>
-      </c>
-      <c r="E236" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="237" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="2"/>
-      <c r="B237" s="21" t="s">
-        <v>328</v>
-      </c>
+      <c r="C236" s="23"/>
+      <c r="D236" s="23"/>
+      <c r="E236" s="8"/>
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B237" s="21"/>
       <c r="C237" s="21"/>
       <c r="D237" s="21"/>
       <c r="E237" s="11"/>
     </row>
-    <row r="238" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2"/>
       <c r="B238" s="21" t="s">
-        <v>329</v>
-      </c>
-      <c r="C238" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D238" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E238" s="11" t="s">
-        <v>184</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="C238" s="21"/>
+      <c r="D238" s="21"/>
+      <c r="E238" s="11"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="2"/>
-      <c r="B239" s="21"/>
-      <c r="C239" s="21"/>
-      <c r="D239" s="21"/>
-      <c r="E239" s="11"/>
-      <c r="G239" s="1"/>
-      <c r="H239" s="1"/>
-      <c r="I239" s="1"/>
-      <c r="J239" s="1"/>
-    </row>
-    <row r="240" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="6"/>
-      <c r="B240" s="22" t="s">
+      <c r="B239" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="C239" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="D239" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="E239" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="2"/>
+      <c r="B240" s="21" t="s">
         <v>330</v>
       </c>
-      <c r="C240" s="23"/>
-      <c r="D240" s="23"/>
-      <c r="E240" s="8"/>
-    </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B241" s="21"/>
+      <c r="C240" s="21"/>
+      <c r="D240" s="21"/>
+      <c r="E240" s="11"/>
+    </row>
+    <row r="241" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="2"/>
+      <c r="B241" s="21" t="s">
+        <v>282</v>
+      </c>
       <c r="C241" s="21"/>
       <c r="D241" s="21"/>
       <c r="E241" s="11"/>
@@ -6107,103 +5934,103 @@
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2"/>
       <c r="B242" s="21" t="s">
-        <v>331</v>
+        <v>198</v>
       </c>
       <c r="C242" s="21"/>
       <c r="D242" s="21"/>
       <c r="E242" s="11"/>
     </row>
-    <row r="243" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2"/>
       <c r="B243" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="C243" s="21"/>
+        <v>331</v>
+      </c>
+      <c r="C243" s="21" t="s">
+        <v>22</v>
+      </c>
       <c r="D243" s="21"/>
       <c r="E243" s="11"/>
     </row>
-    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2"/>
       <c r="B244" s="21" t="s">
-        <v>333</v>
-      </c>
-      <c r="C244" s="21"/>
+        <v>332</v>
+      </c>
+      <c r="C244" s="21" t="s">
+        <v>321</v>
+      </c>
       <c r="D244" s="21"/>
       <c r="E244" s="11"/>
     </row>
-    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2"/>
       <c r="B245" s="21" t="s">
-        <v>21</v>
+        <v>333</v>
       </c>
       <c r="C245" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D245" s="21"/>
-      <c r="E245" s="11"/>
-    </row>
-    <row r="246" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>334</v>
+      </c>
+      <c r="D245" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="E245" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="2"/>
-      <c r="B246" s="21" t="s">
-        <v>334</v>
-      </c>
-      <c r="C246" s="21" t="s">
-        <v>335</v>
-      </c>
+      <c r="B246" s="21"/>
+      <c r="C246" s="21"/>
       <c r="D246" s="21"/>
       <c r="E246" s="11"/>
     </row>
-    <row r="247" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="2"/>
-      <c r="B247" s="21" t="s">
+    <row r="247" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="6"/>
+      <c r="B247" s="22" t="s">
         <v>336</v>
       </c>
-      <c r="C247" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="D247" s="21" t="s">
-        <v>338</v>
-      </c>
-      <c r="E247" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="248" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="2"/>
-      <c r="B248" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="C248" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D248" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E248" s="11" t="s">
-        <v>184</v>
-      </c>
+      <c r="C247" s="23"/>
+      <c r="D247" s="23"/>
+      <c r="E247" s="8"/>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B248" s="21"/>
+      <c r="C248" s="21"/>
+      <c r="D248" s="21"/>
+      <c r="E248" s="11"/>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2"/>
-      <c r="B249" s="21"/>
+      <c r="B249" s="21" t="s">
+        <v>337</v>
+      </c>
       <c r="C249" s="21"/>
       <c r="D249" s="21"/>
       <c r="E249" s="11"/>
     </row>
-    <row r="250" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="6"/>
-      <c r="B250" s="22" t="s">
-        <v>340</v>
-      </c>
-      <c r="C250" s="23"/>
-      <c r="D250" s="23"/>
-      <c r="E250" s="8"/>
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="2"/>
+      <c r="B250" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="C250" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="D250" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="E250" s="11" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B251" s="21"/>
+      <c r="A251" s="2"/>
+      <c r="B251" s="21" t="s">
+        <v>339</v>
+      </c>
       <c r="C251" s="21"/>
       <c r="D251" s="21"/>
       <c r="E251" s="11"/>
@@ -6211,50 +6038,49 @@
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2"/>
       <c r="B252" s="21" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C252" s="21"/>
       <c r="D252" s="21"/>
       <c r="E252" s="11"/>
     </row>
-    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2"/>
       <c r="B253" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="C253" s="21" t="s">
         <v>342</v>
       </c>
-      <c r="C253" s="21" t="s">
+      <c r="D253" s="21" t="s">
         <v>343</v>
       </c>
-      <c r="D253" s="21" t="s">
-        <v>344</v>
-      </c>
       <c r="E253" s="11" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="2"/>
-      <c r="B254" s="21" t="s">
-        <v>345</v>
-      </c>
+      <c r="B254" s="21"/>
       <c r="C254" s="21"/>
       <c r="D254" s="21"/>
       <c r="E254" s="11"/>
-    </row>
-    <row r="255" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="2"/>
-      <c r="B255" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="C255" s="21"/>
-      <c r="D255" s="21"/>
-      <c r="E255" s="11"/>
+      <c r="F254" s="15"/>
+    </row>
+    <row r="255" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="6"/>
+      <c r="B255" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="C255" s="23"/>
+      <c r="D255" s="23"/>
+      <c r="E255" s="8"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="2"/>
-      <c r="B256" s="21" t="s">
-        <v>208</v>
-      </c>
+      <c r="A256" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B256" s="21"/>
       <c r="C256" s="21"/>
       <c r="D256" s="21"/>
       <c r="E256" s="11"/>
@@ -6262,84 +6088,82 @@
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="2"/>
       <c r="B257" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="C257" s="21" t="s">
-        <v>22</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="C257" s="21"/>
       <c r="D257" s="21"/>
       <c r="E257" s="11"/>
     </row>
-    <row r="258" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="2"/>
       <c r="B258" s="21" t="s">
-        <v>347</v>
-      </c>
-      <c r="C258" s="21" t="s">
-        <v>335</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="C258" s="21"/>
       <c r="D258" s="21"/>
       <c r="E258" s="11"/>
     </row>
-    <row r="259" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2"/>
       <c r="B259" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="C259" s="21" t="s">
         <v>348</v>
       </c>
-      <c r="C259" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D259" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E259" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="260" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D259" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="E259" s="25" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="2"/>
       <c r="B260" s="21" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C260" s="21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D260" s="21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E260" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="2"/>
-      <c r="B261" s="21"/>
+      <c r="B261" s="21" t="s">
+        <v>353</v>
+      </c>
       <c r="C261" s="21"/>
       <c r="D261" s="21"/>
       <c r="E261" s="11"/>
     </row>
-    <row r="262" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="6"/>
-      <c r="B262" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="C262" s="23"/>
-      <c r="D262" s="23"/>
-      <c r="E262" s="8"/>
+    <row r="262" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="2"/>
+      <c r="B262" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="C262" s="21"/>
+      <c r="D262" s="21"/>
+      <c r="E262" s="11"/>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B263" s="21"/>
+      <c r="A263" s="2"/>
+      <c r="B263" s="21" t="s">
+        <v>355</v>
+      </c>
       <c r="C263" s="21"/>
       <c r="D263" s="21"/>
       <c r="E263" s="11"/>
     </row>
-    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="2"/>
       <c r="B264" s="21" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C264" s="21"/>
       <c r="D264" s="21"/>
@@ -6348,97 +6172,91 @@
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="2"/>
       <c r="B265" s="21" t="s">
-        <v>354</v>
-      </c>
-      <c r="C265" s="21" t="s">
-        <v>343</v>
-      </c>
-      <c r="D265" s="21" t="s">
-        <v>344</v>
-      </c>
-      <c r="E265" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>357</v>
+      </c>
+      <c r="C265" s="21"/>
+      <c r="D265" s="21"/>
+      <c r="E265" s="11"/>
+    </row>
+    <row r="266" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="2"/>
       <c r="B266" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="C266" s="21"/>
+        <v>358</v>
+      </c>
+      <c r="C266" s="21" t="s">
+        <v>359</v>
+      </c>
       <c r="D266" s="21"/>
       <c r="E266" s="11"/>
     </row>
-    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2"/>
       <c r="B267" s="21" t="s">
-        <v>356</v>
-      </c>
-      <c r="C267" s="21"/>
-      <c r="D267" s="21"/>
-      <c r="E267" s="11"/>
-    </row>
-    <row r="268" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>360</v>
+      </c>
+      <c r="C267" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="D267" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="E267" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="2"/>
-      <c r="B268" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="C268" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D268" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E268" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="269" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="2"/>
-      <c r="B269" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="C269" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="D269" s="21" t="s">
-        <v>360</v>
-      </c>
-      <c r="E269" s="11" t="s">
-        <v>184</v>
-      </c>
+      <c r="B268" s="21"/>
+      <c r="C268" s="21"/>
+      <c r="D268" s="21"/>
+      <c r="E268" s="11"/>
+    </row>
+    <row r="269" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="6"/>
+      <c r="B269" s="22" t="s">
+        <v>363</v>
+      </c>
+      <c r="C269" s="23"/>
+      <c r="D269" s="23"/>
+      <c r="E269" s="8"/>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="2"/>
+      <c r="A270" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="B270" s="21"/>
       <c r="C270" s="21"/>
       <c r="D270" s="21"/>
       <c r="E270" s="11"/>
-      <c r="F270" s="15"/>
-      <c r="G270" s="1"/>
-    </row>
-    <row r="271" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="6"/>
-      <c r="B271" s="22" t="s">
-        <v>361</v>
-      </c>
-      <c r="C271" s="23"/>
-      <c r="D271" s="23"/>
-      <c r="E271" s="8"/>
+    </row>
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="2"/>
+      <c r="B271" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="C271" s="21"/>
+      <c r="D271" s="21"/>
+      <c r="E271" s="11"/>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B272" s="21"/>
-      <c r="C272" s="21"/>
-      <c r="D272" s="21"/>
-      <c r="E272" s="11"/>
+      <c r="A272" s="2"/>
+      <c r="B272" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="C272" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="D272" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="E272" s="11" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="2"/>
       <c r="B273" s="21" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C273" s="21"/>
       <c r="D273" s="21"/>
@@ -6447,73 +6265,75 @@
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="2"/>
       <c r="B274" s="21" t="s">
-        <v>363</v>
-      </c>
-      <c r="C274" s="21"/>
-      <c r="D274" s="21"/>
-      <c r="E274" s="11"/>
-    </row>
-    <row r="275" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>369</v>
+      </c>
+      <c r="C274" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="D274" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="E274" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="2"/>
       <c r="B275" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="C275" s="21" t="s">
-        <v>365</v>
-      </c>
-      <c r="D275" s="24" t="s">
-        <v>366</v>
-      </c>
-      <c r="E275" s="25" t="s">
-        <v>184</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="C275" s="21"/>
+      <c r="D275" s="21"/>
+      <c r="E275" s="11"/>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="2"/>
       <c r="B276" s="21" t="s">
-        <v>367</v>
-      </c>
-      <c r="C276" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="D276" s="21" t="s">
-        <v>369</v>
-      </c>
-      <c r="E276" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="277" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>373</v>
+      </c>
+      <c r="C276" s="21"/>
+      <c r="D276" s="21"/>
+      <c r="E276" s="11"/>
+    </row>
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="2"/>
       <c r="B277" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="C277" s="21"/>
+        <v>374</v>
+      </c>
+      <c r="C277" s="21" t="s">
+        <v>288</v>
+      </c>
       <c r="D277" s="21"/>
       <c r="E277" s="11"/>
     </row>
-    <row r="278" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="2"/>
       <c r="B278" s="21" t="s">
-        <v>371</v>
-      </c>
-      <c r="C278" s="21"/>
-      <c r="D278" s="21"/>
-      <c r="E278" s="11"/>
+        <v>375</v>
+      </c>
+      <c r="C278" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="D278" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="E278" s="11" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="2"/>
-      <c r="B279" s="21" t="s">
-        <v>372</v>
-      </c>
+      <c r="B279" s="21"/>
       <c r="C279" s="21"/>
       <c r="D279" s="21"/>
       <c r="E279" s="11"/>
     </row>
-    <row r="280" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="2"/>
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="2" t="s">
+        <v>234</v>
+      </c>
       <c r="B280" s="21" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C280" s="21"/>
       <c r="D280" s="21"/>
@@ -6522,74 +6342,70 @@
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="2"/>
       <c r="B281" s="21" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C281" s="21"/>
       <c r="D281" s="21"/>
       <c r="E281" s="11"/>
     </row>
-    <row r="282" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="2"/>
       <c r="B282" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="C282" s="21" t="s">
-        <v>376</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="C282" s="21"/>
       <c r="D282" s="21"/>
       <c r="E282" s="11"/>
     </row>
     <row r="283" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="2"/>
       <c r="B283" s="21" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C283" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="D283" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="E283" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="284" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>382</v>
+      </c>
+      <c r="D283" s="21"/>
+      <c r="E283" s="11"/>
+    </row>
+    <row r="284" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="2"/>
       <c r="B284" s="21" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C284" s="21" t="s">
-        <v>77</v>
+        <v>384</v>
       </c>
       <c r="D284" s="21" t="s">
-        <v>78</v>
+        <v>385</v>
       </c>
       <c r="E284" s="11" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="2"/>
-      <c r="B285" s="21"/>
+      <c r="B285" s="21" t="s">
+        <v>386</v>
+      </c>
       <c r="C285" s="21"/>
       <c r="D285" s="21"/>
       <c r="E285" s="11"/>
     </row>
-    <row r="286" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="6"/>
-      <c r="B286" s="22" t="s">
-        <v>381</v>
-      </c>
-      <c r="C286" s="23"/>
-      <c r="D286" s="23"/>
-      <c r="E286" s="8"/>
-    </row>
-    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B287" s="21"/>
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="2"/>
+      <c r="B286" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="C286" s="21"/>
+      <c r="D286" s="21"/>
+      <c r="E286" s="11"/>
+    </row>
+    <row r="287" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="2"/>
+      <c r="B287" s="21" t="s">
+        <v>388</v>
+      </c>
       <c r="C287" s="21"/>
       <c r="D287" s="21"/>
       <c r="E287" s="11"/>
@@ -6597,7 +6413,7 @@
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="2"/>
       <c r="B288" s="21" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="C288" s="21"/>
       <c r="D288" s="21"/>
@@ -6606,46 +6422,44 @@
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="2"/>
       <c r="B289" s="21" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="C289" s="21" t="s">
-        <v>384</v>
-      </c>
-      <c r="D289" s="21" t="s">
-        <v>385</v>
-      </c>
-      <c r="E289" s="11" t="s">
-        <v>184</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="D289" s="21"/>
+      <c r="E289" s="11"/>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="2"/>
       <c r="B290" s="21" t="s">
-        <v>386</v>
-      </c>
-      <c r="C290" s="21"/>
+        <v>392</v>
+      </c>
+      <c r="C290" s="21" t="s">
+        <v>393</v>
+      </c>
       <c r="D290" s="21"/>
       <c r="E290" s="11"/>
     </row>
-    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="2"/>
       <c r="B291" s="21" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C291" s="21" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D291" s="21" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E291" s="11" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2"/>
       <c r="B292" s="21" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C292" s="21"/>
       <c r="D292" s="21"/>
@@ -6653,67 +6467,51 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="2"/>
-      <c r="B293" s="21" t="s">
-        <v>391</v>
-      </c>
+      <c r="B293" s="21"/>
       <c r="C293" s="21"/>
       <c r="D293" s="21"/>
       <c r="E293" s="11"/>
     </row>
-    <row r="294" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="2"/>
-      <c r="B294" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="C294" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D294" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E294" s="11" t="s">
-        <v>184</v>
-      </c>
+    <row r="294" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="6"/>
+      <c r="B294" s="22" t="s">
+        <v>397</v>
+      </c>
+      <c r="C294" s="23"/>
+      <c r="D294" s="23"/>
+      <c r="E294" s="8"/>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="2"/>
-      <c r="B295" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="C295" s="21" t="s">
-        <v>301</v>
-      </c>
+      <c r="A295" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B295" s="20"/>
+      <c r="C295" s="21"/>
       <c r="D295" s="21"/>
       <c r="E295" s="11"/>
     </row>
-    <row r="296" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="2"/>
       <c r="B296" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="C296" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="D296" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="E296" s="11" t="s">
-        <v>184</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="C296" s="21"/>
+      <c r="D296" s="21"/>
+      <c r="E296" s="11"/>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="2"/>
-      <c r="B297" s="21"/>
+      <c r="B297" s="21" t="s">
+        <v>399</v>
+      </c>
       <c r="C297" s="21"/>
       <c r="D297" s="21"/>
       <c r="E297" s="11"/>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="2" t="s">
-        <v>247</v>
-      </c>
+      <c r="A298" s="2"/>
       <c r="B298" s="21" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C298" s="21"/>
       <c r="D298" s="21"/>
@@ -6722,52 +6520,48 @@
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="2"/>
       <c r="B299" s="21" t="s">
-        <v>398</v>
+        <v>340</v>
       </c>
       <c r="C299" s="21"/>
       <c r="D299" s="21"/>
       <c r="E299" s="11"/>
     </row>
-    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="2"/>
       <c r="B300" s="21" t="s">
-        <v>399</v>
-      </c>
-      <c r="C300" s="21"/>
-      <c r="D300" s="21"/>
-      <c r="E300" s="11"/>
-    </row>
-    <row r="301" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>401</v>
+      </c>
+      <c r="C300" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="D300" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="E300" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="2"/>
-      <c r="B301" s="21" t="s">
-        <v>400</v>
-      </c>
-      <c r="C301" s="21" t="s">
-        <v>401</v>
-      </c>
+      <c r="B301" s="20"/>
+      <c r="C301" s="21"/>
       <c r="D301" s="21"/>
       <c r="E301" s="11"/>
     </row>
-    <row r="302" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="2"/>
-      <c r="B302" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="C302" s="21" t="s">
-        <v>403</v>
-      </c>
-      <c r="D302" s="21" t="s">
+    <row r="302" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="6"/>
+      <c r="B302" s="22" t="s">
         <v>404</v>
       </c>
-      <c r="E302" s="11" t="s">
-        <v>184</v>
-      </c>
+      <c r="C302" s="23"/>
+      <c r="D302" s="23"/>
+      <c r="E302" s="8"/>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="2"/>
-      <c r="B303" s="21" t="s">
-        <v>405</v>
-      </c>
+      <c r="A303" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B303" s="20"/>
       <c r="C303" s="21"/>
       <c r="D303" s="21"/>
       <c r="E303" s="11"/>
@@ -6775,7 +6569,7 @@
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="2"/>
       <c r="B304" s="21" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C304" s="21"/>
       <c r="D304" s="21"/>
@@ -6784,7 +6578,7 @@
     <row r="305" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="2"/>
       <c r="B305" s="21" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C305" s="21"/>
       <c r="D305" s="21"/>
@@ -6793,7 +6587,7 @@
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="2"/>
       <c r="B306" s="21" t="s">
-        <v>408</v>
+        <v>319</v>
       </c>
       <c r="C306" s="21"/>
       <c r="D306" s="21"/>
@@ -6802,10 +6596,10 @@
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="2"/>
       <c r="B307" s="21" t="s">
-        <v>409</v>
+        <v>21</v>
       </c>
       <c r="C307" s="21" t="s">
-        <v>410</v>
+        <v>22</v>
       </c>
       <c r="D307" s="21"/>
       <c r="E307" s="11"/>
@@ -6813,68 +6607,72 @@
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="2"/>
       <c r="B308" s="21" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C308" s="21" t="s">
-        <v>412</v>
+        <v>42</v>
       </c>
       <c r="D308" s="21"/>
       <c r="E308" s="11"/>
     </row>
-    <row r="309" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="2"/>
       <c r="B309" s="21" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C309" s="21" t="s">
-        <v>403</v>
-      </c>
-      <c r="D309" s="21" t="s">
-        <v>414</v>
-      </c>
-      <c r="E309" s="11" t="s">
-        <v>184</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="D309" s="21"/>
+      <c r="E309" s="11"/>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="2"/>
       <c r="B310" s="21" t="s">
-        <v>415</v>
-      </c>
-      <c r="C310" s="21"/>
+        <v>410</v>
+      </c>
+      <c r="C310" s="21" t="s">
+        <v>51</v>
+      </c>
       <c r="D310" s="21"/>
       <c r="E310" s="11"/>
     </row>
-    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="2"/>
-      <c r="B311" s="21"/>
-      <c r="C311" s="21"/>
-      <c r="D311" s="21"/>
-      <c r="E311" s="11"/>
-    </row>
-    <row r="312" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="6"/>
-      <c r="B312" s="22" t="s">
-        <v>416</v>
-      </c>
-      <c r="C312" s="23"/>
-      <c r="D312" s="23"/>
-      <c r="E312" s="8"/>
-    </row>
-    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="2" t="s">
+      <c r="B311" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="C311" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="D311" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="E311" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="2"/>
+      <c r="B312" s="21"/>
+      <c r="C312" s="21"/>
+      <c r="D312" s="21"/>
+      <c r="E312" s="11"/>
+    </row>
+    <row r="313" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A313" s="6"/>
+      <c r="B313" s="22" t="s">
+        <v>415</v>
+      </c>
+      <c r="C313" s="23"/>
+      <c r="D313" s="23"/>
+      <c r="E313" s="8"/>
+    </row>
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A314" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B313" s="20"/>
-      <c r="C313" s="21"/>
-      <c r="D313" s="21"/>
-      <c r="E313" s="11"/>
-    </row>
-    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="2"/>
-      <c r="B314" s="21" t="s">
-        <v>417</v>
-      </c>
+      <c r="B314" s="20"/>
       <c r="C314" s="21"/>
       <c r="D314" s="21"/>
       <c r="E314" s="11"/>
@@ -6882,131 +6680,135 @@
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="2"/>
       <c r="B315" s="21" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C315" s="21"/>
       <c r="D315" s="21"/>
       <c r="E315" s="11"/>
     </row>
-    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="2"/>
       <c r="B316" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="C316" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="D316" s="21" t="s">
         <v>419</v>
       </c>
-      <c r="C316" s="21"/>
-      <c r="D316" s="21"/>
-      <c r="E316" s="11"/>
+      <c r="E316" s="11" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="2"/>
       <c r="B317" s="21" t="s">
-        <v>356</v>
+        <v>420</v>
       </c>
       <c r="C317" s="21"/>
       <c r="D317" s="21"/>
       <c r="E317" s="11"/>
     </row>
-    <row r="318" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="2"/>
       <c r="B318" s="21" t="s">
-        <v>420</v>
-      </c>
-      <c r="C318" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D318" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E318" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="319" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>282</v>
+      </c>
+      <c r="C318" s="21"/>
+      <c r="D318" s="21"/>
+      <c r="E318" s="11"/>
+    </row>
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="2"/>
       <c r="B319" s="21" t="s">
-        <v>421</v>
-      </c>
-      <c r="C319" s="21" t="s">
-        <v>422</v>
-      </c>
-      <c r="D319" s="21" t="s">
-        <v>423</v>
-      </c>
-      <c r="E319" s="11" t="s">
-        <v>184</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="C319" s="21"/>
+      <c r="D319" s="21"/>
+      <c r="E319" s="11"/>
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="2"/>
-      <c r="B320" s="20"/>
-      <c r="C320" s="21"/>
+      <c r="B320" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="C320" s="21" t="s">
+        <v>22</v>
+      </c>
       <c r="D320" s="21"/>
       <c r="E320" s="11"/>
     </row>
-    <row r="321" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="6"/>
-      <c r="B321" s="22" t="s">
-        <v>424</v>
-      </c>
-      <c r="C321" s="23"/>
-      <c r="D321" s="23"/>
-      <c r="E321" s="8"/>
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A321" s="2"/>
+      <c r="B321" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="C321" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D321" s="21"/>
+      <c r="E321" s="11"/>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B322" s="20"/>
-      <c r="C322" s="21"/>
+      <c r="A322" s="2"/>
+      <c r="B322" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="C322" s="21" t="s">
+        <v>409</v>
+      </c>
       <c r="D322" s="21"/>
       <c r="E322" s="11"/>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="2"/>
       <c r="B323" s="21" t="s">
-        <v>425</v>
-      </c>
-      <c r="C323" s="21"/>
+        <v>423</v>
+      </c>
+      <c r="C323" s="21" t="s">
+        <v>51</v>
+      </c>
       <c r="D323" s="21"/>
       <c r="E323" s="11"/>
     </row>
-    <row r="324" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="2"/>
       <c r="B324" s="21" t="s">
+        <v>424</v>
+      </c>
+      <c r="C324" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="D324" s="21" t="s">
         <v>426</v>
       </c>
-      <c r="C324" s="21"/>
-      <c r="D324" s="21"/>
-      <c r="E324" s="11"/>
+      <c r="E324" s="11" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="2"/>
-      <c r="B325" s="21" t="s">
-        <v>333</v>
-      </c>
+      <c r="B325" s="21"/>
       <c r="C325" s="21"/>
       <c r="D325" s="21"/>
       <c r="E325" s="11"/>
     </row>
-    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="2"/>
-      <c r="B326" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C326" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D326" s="21"/>
-      <c r="E326" s="11"/>
+    <row r="326" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A326" s="6"/>
+      <c r="B326" s="22" t="s">
+        <v>427</v>
+      </c>
+      <c r="C326" s="23"/>
+      <c r="D326" s="23"/>
+      <c r="E326" s="8"/>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="2"/>
-      <c r="B327" s="21" t="s">
-        <v>427</v>
-      </c>
-      <c r="C327" s="21" t="s">
-        <v>42</v>
-      </c>
+      <c r="A327" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B327" s="20"/>
+      <c r="C327" s="21"/>
       <c r="D327" s="21"/>
       <c r="E327" s="11"/>
     </row>
@@ -7015,137 +6817,131 @@
       <c r="B328" s="21" t="s">
         <v>428</v>
       </c>
-      <c r="C328" s="21" t="s">
-        <v>429</v>
-      </c>
+      <c r="C328" s="21"/>
       <c r="D328" s="21"/>
       <c r="E328" s="11"/>
     </row>
-    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="329" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="2"/>
       <c r="B329" s="21" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C329" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D329" s="21"/>
-      <c r="E329" s="11"/>
-    </row>
-    <row r="330" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>418</v>
+      </c>
+      <c r="D329" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="E329" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="2"/>
       <c r="B330" s="21" t="s">
-        <v>431</v>
-      </c>
-      <c r="C330" s="21" t="s">
-        <v>432</v>
-      </c>
-      <c r="D330" s="21" t="s">
-        <v>433</v>
-      </c>
-      <c r="E330" s="11" t="s">
-        <v>434</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="C330" s="21"/>
+      <c r="D330" s="21"/>
+      <c r="E330" s="11"/>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="2"/>
       <c r="B331" s="21" t="s">
-        <v>435</v>
-      </c>
-      <c r="C331" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D331" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E331" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C331" s="21"/>
+      <c r="D331" s="21"/>
+      <c r="E331" s="11"/>
+    </row>
+    <row r="332" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="2"/>
+      <c r="B332" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="C332" s="21" t="s">
+        <v>432</v>
+      </c>
+      <c r="D332" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="E332" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="2"/>
+      <c r="B333" s="21"/>
+      <c r="C333" s="21"/>
+      <c r="D333" s="21"/>
+      <c r="E333" s="11"/>
+    </row>
+    <row r="334" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A334" s="6"/>
+      <c r="B334" s="22" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="2"/>
-      <c r="B332" s="21"/>
-      <c r="C332" s="21"/>
-      <c r="D332" s="21"/>
-      <c r="E332" s="11"/>
-    </row>
-    <row r="333" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="6"/>
-      <c r="B333" s="22" t="s">
-        <v>436</v>
-      </c>
-      <c r="C333" s="23"/>
-      <c r="D333" s="23"/>
-      <c r="E333" s="8"/>
-    </row>
-    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="2" t="s">
+      <c r="C334" s="23"/>
+      <c r="D334" s="23"/>
+      <c r="E334" s="8"/>
+    </row>
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A335" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B334" s="20"/>
-      <c r="C334" s="21"/>
-      <c r="D334" s="21"/>
-      <c r="E334" s="11"/>
-    </row>
-    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="2"/>
-      <c r="B335" s="21" t="s">
-        <v>437</v>
-      </c>
+      <c r="B335" s="20"/>
       <c r="C335" s="21"/>
       <c r="D335" s="21"/>
       <c r="E335" s="11"/>
     </row>
-    <row r="336" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="2"/>
       <c r="B336" s="21" t="s">
-        <v>438</v>
-      </c>
-      <c r="C336" s="21" t="s">
-        <v>439</v>
-      </c>
-      <c r="D336" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="E336" s="11" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>435</v>
+      </c>
+      <c r="C336" s="21"/>
+      <c r="D336" s="21"/>
+      <c r="E336" s="11"/>
+    </row>
+    <row r="337" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="2"/>
       <c r="B337" s="21" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C337" s="21"/>
       <c r="D337" s="21"/>
       <c r="E337" s="11"/>
     </row>
-    <row r="338" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="2"/>
       <c r="B338" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="C338" s="21"/>
-      <c r="D338" s="21"/>
-      <c r="E338" s="11"/>
+        <v>437</v>
+      </c>
+      <c r="C338" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="D338" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="E338" s="11" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="2"/>
       <c r="B339" s="21" t="s">
-        <v>208</v>
+        <v>440</v>
       </c>
       <c r="C339" s="21"/>
       <c r="D339" s="21"/>
       <c r="E339" s="11"/>
     </row>
-    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="2"/>
       <c r="B340" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="C340" s="21" t="s">
-        <v>22</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="C340" s="21"/>
       <c r="D340" s="21"/>
       <c r="E340" s="11"/>
     </row>
@@ -7154,9 +6950,7 @@
       <c r="B341" s="21" t="s">
         <v>442</v>
       </c>
-      <c r="C341" s="21" t="s">
-        <v>42</v>
-      </c>
+      <c r="C341" s="21"/>
       <c r="D341" s="21"/>
       <c r="E341" s="11"/>
     </row>
@@ -7166,221 +6960,227 @@
         <v>443</v>
       </c>
       <c r="C342" s="21" t="s">
-        <v>429</v>
-      </c>
-      <c r="D342" s="21"/>
-      <c r="E342" s="11"/>
+        <v>444</v>
+      </c>
+      <c r="D342" s="21" t="s">
+        <v>445</v>
+      </c>
+      <c r="E342" s="11" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="2"/>
       <c r="B343" s="21" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C343" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D343" s="21"/>
-      <c r="E343" s="11"/>
-    </row>
-    <row r="344" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>447</v>
+      </c>
+      <c r="D343" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="E343" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="2"/>
       <c r="B344" s="21" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C344" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D344" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E344" s="11" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="345" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>391</v>
+      </c>
+      <c r="D344" s="21"/>
+      <c r="E344" s="11"/>
+    </row>
+    <row r="345" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="2"/>
       <c r="B345" s="21" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C345" s="21" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D345" s="21" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E345" s="11" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="2"/>
-      <c r="B346" s="21"/>
-      <c r="C346" s="21"/>
-      <c r="D346" s="21"/>
-      <c r="E346" s="11"/>
-    </row>
-    <row r="347" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="6"/>
-      <c r="B347" s="22" t="s">
-        <v>449</v>
-      </c>
-      <c r="C347" s="23"/>
-      <c r="D347" s="23"/>
-      <c r="E347" s="8"/>
-    </row>
-    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="2" t="s">
+      <c r="B346" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="C346" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="D346" s="21" t="s">
+        <v>455</v>
+      </c>
+      <c r="E346" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A347" s="2"/>
+      <c r="B347" s="21"/>
+      <c r="C347" s="21"/>
+      <c r="D347" s="21"/>
+      <c r="E347" s="11"/>
+    </row>
+    <row r="348" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A348" s="26"/>
+      <c r="B348" s="22" t="s">
+        <v>456</v>
+      </c>
+      <c r="C348" s="23"/>
+      <c r="D348" s="23"/>
+      <c r="E348" s="23"/>
+    </row>
+    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A349" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B348" s="20"/>
-      <c r="C348" s="21"/>
-      <c r="D348" s="21"/>
-      <c r="E348" s="11"/>
-    </row>
-    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="2"/>
-      <c r="B349" s="21" t="s">
-        <v>450</v>
-      </c>
+      <c r="B349" s="20"/>
       <c r="C349" s="21"/>
       <c r="D349" s="21"/>
       <c r="E349" s="11"/>
     </row>
-    <row r="350" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="2"/>
       <c r="B350" s="21" t="s">
-        <v>451</v>
-      </c>
-      <c r="C350" s="21" t="s">
-        <v>439</v>
-      </c>
-      <c r="D350" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="E350" s="11" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>457</v>
+      </c>
+      <c r="C350" s="21"/>
+      <c r="D350" s="21"/>
+      <c r="E350" s="11"/>
+    </row>
+    <row r="351" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="2"/>
       <c r="B351" s="21" t="s">
-        <v>452</v>
-      </c>
-      <c r="C351" s="21"/>
-      <c r="D351" s="21"/>
-      <c r="E351" s="11"/>
+        <v>458</v>
+      </c>
+      <c r="C351" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="D351" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="E351" s="11" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="2"/>
       <c r="B352" s="21" t="s">
-        <v>356</v>
+        <v>461</v>
       </c>
       <c r="C352" s="21"/>
       <c r="D352" s="21"/>
       <c r="E352" s="11"/>
     </row>
-    <row r="353" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="2"/>
       <c r="B353" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="C353" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D353" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E353" s="11" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="354" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>462</v>
+      </c>
+      <c r="C353" s="21"/>
+      <c r="D353" s="21"/>
+      <c r="E353" s="11"/>
+    </row>
+    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="2"/>
       <c r="B354" s="21" t="s">
-        <v>454</v>
-      </c>
-      <c r="C354" s="21" t="s">
-        <v>455</v>
-      </c>
-      <c r="D354" s="21" t="s">
-        <v>456</v>
-      </c>
-      <c r="E354" s="11" t="s">
-        <v>434</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="C354" s="21"/>
+      <c r="D354" s="21"/>
+      <c r="E354" s="11"/>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="2"/>
-      <c r="B355" s="21"/>
-      <c r="C355" s="21"/>
+      <c r="B355" s="21" t="s">
+        <v>463</v>
+      </c>
+      <c r="C355" s="21" t="s">
+        <v>444</v>
+      </c>
       <c r="D355" s="21"/>
       <c r="E355" s="11"/>
     </row>
-    <row r="356" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="6"/>
-      <c r="B356" s="22" t="s">
-        <v>457</v>
-      </c>
-      <c r="C356" s="23"/>
-      <c r="D356" s="23"/>
-      <c r="E356" s="8"/>
-    </row>
-    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B357" s="20"/>
-      <c r="C357" s="21"/>
+    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A356" s="2"/>
+      <c r="B356" s="21" t="s">
+        <v>464</v>
+      </c>
+      <c r="C356" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="D356" s="21"/>
+      <c r="E356" s="11"/>
+    </row>
+    <row r="357" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A357" s="2"/>
+      <c r="B357" s="21" t="s">
+        <v>465</v>
+      </c>
+      <c r="C357" s="21" t="s">
+        <v>391</v>
+      </c>
       <c r="D357" s="21"/>
       <c r="E357" s="11"/>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2"/>
       <c r="B358" s="21" t="s">
-        <v>458</v>
-      </c>
-      <c r="C358" s="21"/>
+        <v>466</v>
+      </c>
+      <c r="C358" s="21" t="s">
+        <v>451</v>
+      </c>
       <c r="D358" s="21"/>
       <c r="E358" s="11"/>
     </row>
-    <row r="359" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="2"/>
       <c r="B359" s="21" t="s">
-        <v>459</v>
-      </c>
-      <c r="C359" s="21"/>
-      <c r="D359" s="21"/>
-      <c r="E359" s="11"/>
+        <v>467</v>
+      </c>
+      <c r="C359" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="D359" s="21" t="s">
+        <v>469</v>
+      </c>
+      <c r="E359" s="11" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="2"/>
-      <c r="B360" s="21" t="s">
-        <v>460</v>
-      </c>
-      <c r="C360" s="21" t="s">
-        <v>461</v>
-      </c>
-      <c r="D360" s="21" t="s">
-        <v>462</v>
-      </c>
-      <c r="E360" s="11" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="2"/>
-      <c r="B361" s="21" t="s">
-        <v>463</v>
-      </c>
-      <c r="C361" s="21"/>
-      <c r="D361" s="21"/>
-      <c r="E361" s="11"/>
-    </row>
-    <row r="362" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="2"/>
-      <c r="B362" s="21" t="s">
-        <v>464</v>
-      </c>
+      <c r="B360" s="21"/>
+      <c r="C360" s="21"/>
+      <c r="D360" s="21"/>
+      <c r="E360" s="11"/>
+    </row>
+    <row r="361" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A361" s="6"/>
+      <c r="B361" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="C361" s="23"/>
+      <c r="D361" s="23"/>
+      <c r="E361" s="8"/>
+    </row>
+    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A362" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B362" s="20"/>
       <c r="C362" s="21"/>
       <c r="D362" s="21"/>
       <c r="E362" s="11"/>
@@ -7388,119 +7188,99 @@
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="2"/>
       <c r="B363" s="21" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C363" s="21"/>
       <c r="D363" s="21"/>
       <c r="E363" s="11"/>
     </row>
-    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="2"/>
       <c r="B364" s="21" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C364" s="21" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="D364" s="21" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="E364" s="11" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="2"/>
       <c r="B365" s="21" t="s">
-        <v>469</v>
-      </c>
-      <c r="C365" s="21" t="s">
-        <v>470</v>
-      </c>
-      <c r="D365" s="21" t="s">
-        <v>471</v>
-      </c>
-      <c r="E365" s="11" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="366" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>473</v>
+      </c>
+      <c r="C365" s="21"/>
+      <c r="D365" s="21"/>
+      <c r="E365" s="11"/>
+    </row>
+    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="2"/>
       <c r="B366" s="21" t="s">
-        <v>472</v>
-      </c>
-      <c r="C366" s="21" t="s">
-        <v>410</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="C366" s="21"/>
       <c r="D366" s="21"/>
       <c r="E366" s="11"/>
     </row>
-    <row r="367" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="2"/>
       <c r="B367" s="21" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C367" s="21" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D367" s="21" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E367" s="11" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="368" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="2"/>
-      <c r="B368" s="21" t="s">
-        <v>476</v>
-      </c>
-      <c r="C368" s="21" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A368" s="27"/>
+      <c r="B368" s="21"/>
+      <c r="C368" s="21"/>
+      <c r="D368" s="21"/>
+      <c r="E368" s="11"/>
+    </row>
+    <row r="369" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A369" s="28"/>
+      <c r="B369" s="29" t="s">
         <v>477</v>
       </c>
-      <c r="D368" s="21" t="s">
-        <v>478</v>
-      </c>
-      <c r="E368" s="11" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="369" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="2"/>
-      <c r="B369" s="21" t="s">
-        <v>479</v>
-      </c>
-      <c r="C369" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D369" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E369" s="11" t="s">
-        <v>434</v>
-      </c>
+      <c r="C369" s="30"/>
+      <c r="D369" s="30"/>
+      <c r="E369" s="31"/>
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A370" s="2"/>
-      <c r="B370" s="21"/>
+      <c r="A370" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B370" s="20"/>
       <c r="C370" s="21"/>
       <c r="D370" s="21"/>
       <c r="E370" s="11"/>
     </row>
-    <row r="371" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="26"/>
-      <c r="B371" s="22" t="s">
-        <v>480</v>
-      </c>
-      <c r="C371" s="23"/>
-      <c r="D371" s="23"/>
-      <c r="E371" s="23"/>
-    </row>
-    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B372" s="20"/>
+    <row r="371" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A371" s="2"/>
+      <c r="B371" s="21" t="s">
+        <v>478</v>
+      </c>
+      <c r="C371" s="21"/>
+      <c r="D371" s="21"/>
+      <c r="E371" s="11"/>
+    </row>
+    <row r="372" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A372" s="2"/>
+      <c r="B372" s="21" t="s">
+        <v>479</v>
+      </c>
       <c r="C372" s="21"/>
       <c r="D372" s="21"/>
       <c r="E372" s="11"/>
@@ -7508,40 +7288,36 @@
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="2"/>
       <c r="B373" s="21" t="s">
-        <v>481</v>
-      </c>
-      <c r="C373" s="21"/>
+        <v>437</v>
+      </c>
+      <c r="C373" s="21" t="s">
+        <v>438</v>
+      </c>
       <c r="D373" s="21"/>
       <c r="E373" s="11"/>
     </row>
-    <row r="374" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="2"/>
       <c r="B374" s="21" t="s">
-        <v>482</v>
-      </c>
-      <c r="C374" s="21" t="s">
-        <v>483</v>
-      </c>
-      <c r="D374" s="21" t="s">
-        <v>484</v>
-      </c>
-      <c r="E374" s="11" t="s">
-        <v>434</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="C374" s="21"/>
+      <c r="D374" s="21"/>
+      <c r="E374" s="11"/>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="2"/>
       <c r="B375" s="21" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C375" s="21"/>
       <c r="D375" s="21"/>
       <c r="E375" s="11"/>
     </row>
-    <row r="376" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="2"/>
       <c r="B376" s="21" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C376" s="21"/>
       <c r="D376" s="21"/>
@@ -7550,7 +7326,7 @@
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="2"/>
       <c r="B377" s="21" t="s">
-        <v>208</v>
+        <v>482</v>
       </c>
       <c r="C377" s="21"/>
       <c r="D377" s="21"/>
@@ -7559,106 +7335,96 @@
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="2"/>
       <c r="B378" s="21" t="s">
-        <v>487</v>
-      </c>
-      <c r="C378" s="21" t="s">
-        <v>467</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="C378" s="21"/>
       <c r="D378" s="21"/>
       <c r="E378" s="11"/>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="2"/>
       <c r="B379" s="21" t="s">
-        <v>488</v>
-      </c>
-      <c r="C379" s="21" t="s">
-        <v>470</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="C379" s="21"/>
       <c r="D379" s="21"/>
       <c r="E379" s="11"/>
     </row>
     <row r="380" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2"/>
       <c r="B380" s="21" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C380" s="21" t="s">
-        <v>410</v>
+        <v>140</v>
       </c>
       <c r="D380" s="21"/>
       <c r="E380" s="11"/>
     </row>
-    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="2"/>
       <c r="B381" s="21" t="s">
+        <v>486</v>
+      </c>
+      <c r="C381" s="21" t="s">
+        <v>487</v>
+      </c>
+      <c r="D381" s="21" t="s">
+        <v>488</v>
+      </c>
+      <c r="E381" s="11" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A382" s="2"/>
+      <c r="B382" s="21"/>
+      <c r="C382" s="21"/>
+      <c r="D382" s="21"/>
+      <c r="E382" s="11"/>
+    </row>
+    <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A383" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B383" s="21" t="s">
         <v>490</v>
       </c>
-      <c r="C381" s="21" t="s">
-        <v>474</v>
-      </c>
-      <c r="D381" s="21"/>
-      <c r="E381" s="11"/>
-    </row>
-    <row r="382" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="2"/>
-      <c r="B382" s="21" t="s">
+      <c r="C383" s="21"/>
+      <c r="D383" s="21"/>
+      <c r="E383" s="11"/>
+    </row>
+    <row r="384" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A384" s="2"/>
+      <c r="B384" s="21" t="s">
         <v>491</v>
       </c>
-      <c r="C382" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D382" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E382" s="11" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="383" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="2"/>
-      <c r="B383" s="21" t="s">
-        <v>492</v>
-      </c>
-      <c r="C383" s="21" t="s">
-        <v>493</v>
-      </c>
-      <c r="D383" s="21" t="s">
-        <v>494</v>
-      </c>
-      <c r="E383" s="11" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="2"/>
-      <c r="B384" s="21"/>
       <c r="C384" s="21"/>
       <c r="D384" s="21"/>
       <c r="E384" s="11"/>
     </row>
-    <row r="385" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="6"/>
-      <c r="B385" s="22" t="s">
-        <v>495</v>
-      </c>
-      <c r="C385" s="23"/>
-      <c r="D385" s="23"/>
-      <c r="E385" s="8"/>
+    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A385" s="2"/>
+      <c r="B385" s="21" t="s">
+        <v>492</v>
+      </c>
+      <c r="C385" s="21"/>
+      <c r="D385" s="21"/>
+      <c r="E385" s="11"/>
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B386" s="20"/>
+      <c r="A386" s="2"/>
+      <c r="B386" s="21" t="s">
+        <v>493</v>
+      </c>
       <c r="C386" s="21"/>
       <c r="D386" s="21"/>
       <c r="E386" s="11"/>
     </row>
-    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="2"/>
       <c r="B387" s="21" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C387" s="21"/>
       <c r="D387" s="21"/>
@@ -7667,16 +7433,16 @@
     <row r="388" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="2"/>
       <c r="B388" s="21" t="s">
+        <v>495</v>
+      </c>
+      <c r="C388" s="21" t="s">
+        <v>496</v>
+      </c>
+      <c r="D388" s="21" t="s">
         <v>497</v>
       </c>
-      <c r="C388" s="21" t="s">
-        <v>483</v>
-      </c>
-      <c r="D388" s="21" t="s">
-        <v>484</v>
-      </c>
       <c r="E388" s="11" t="s">
-        <v>434</v>
+        <v>489</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7688,79 +7454,77 @@
       <c r="D389" s="21"/>
       <c r="E389" s="11"/>
     </row>
-    <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="2"/>
       <c r="B390" s="21" t="s">
-        <v>356</v>
+        <v>499</v>
       </c>
       <c r="C390" s="21"/>
       <c r="D390" s="21"/>
       <c r="E390" s="11"/>
     </row>
-    <row r="391" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="2"/>
       <c r="B391" s="21" t="s">
-        <v>499</v>
-      </c>
-      <c r="C391" s="21" t="s">
-        <v>77</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="C391" s="21"/>
       <c r="D391" s="21"/>
       <c r="E391" s="11"/>
     </row>
-    <row r="392" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="2"/>
       <c r="B392" s="21" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C392" s="21" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D392" s="21" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E392" s="11" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="393" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A393" s="27"/>
-      <c r="B393" s="21"/>
+        <v>489</v>
+      </c>
+    </row>
+    <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A393" s="2"/>
+      <c r="B393" s="21" t="s">
+        <v>504</v>
+      </c>
       <c r="C393" s="21"/>
       <c r="D393" s="21"/>
       <c r="E393" s="11"/>
     </row>
-    <row r="394" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A394" s="28"/>
-      <c r="B394" s="29" t="s">
-        <v>503</v>
-      </c>
-      <c r="C394" s="30"/>
-      <c r="D394" s="30"/>
-      <c r="E394" s="31"/>
-    </row>
-    <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A395" s="2" t="s">
+    <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A394" s="2"/>
+      <c r="B394" s="21"/>
+      <c r="C394" s="21"/>
+      <c r="D394" s="21"/>
+      <c r="E394" s="11"/>
+    </row>
+    <row r="395" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A395" s="6"/>
+      <c r="B395" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="C395" s="23"/>
+      <c r="D395" s="23"/>
+      <c r="E395" s="8"/>
+    </row>
+    <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A396" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B395" s="20"/>
-      <c r="C395" s="21"/>
-      <c r="D395" s="21"/>
-      <c r="E395" s="11"/>
-    </row>
-    <row r="396" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="2"/>
-      <c r="B396" s="21" t="s">
-        <v>504</v>
-      </c>
+      <c r="B396" s="20"/>
       <c r="C396" s="21"/>
       <c r="D396" s="21"/>
       <c r="E396" s="11"/>
     </row>
-    <row r="397" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="2"/>
       <c r="B397" s="21" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C397" s="21"/>
       <c r="D397" s="21"/>
@@ -7769,36 +7533,40 @@
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="2"/>
       <c r="B398" s="21" t="s">
-        <v>460</v>
+        <v>507</v>
       </c>
       <c r="C398" s="21" t="s">
-        <v>461</v>
-      </c>
-      <c r="D398" s="21"/>
-      <c r="E398" s="11"/>
+        <v>508</v>
+      </c>
+      <c r="D398" s="21" t="s">
+        <v>509</v>
+      </c>
+      <c r="E398" s="11" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="2"/>
       <c r="B399" s="21" t="s">
-        <v>463</v>
+        <v>510</v>
       </c>
       <c r="C399" s="21"/>
       <c r="D399" s="21"/>
       <c r="E399" s="11"/>
     </row>
-    <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="2"/>
       <c r="B400" s="21" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C400" s="21"/>
       <c r="D400" s="21"/>
       <c r="E400" s="11"/>
     </row>
-    <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="2"/>
       <c r="B401" s="21" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C401" s="21"/>
       <c r="D401" s="21"/>
@@ -7807,7 +7575,7 @@
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2"/>
       <c r="B402" s="21" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C402" s="21"/>
       <c r="D402" s="21"/>
@@ -7816,7 +7584,7 @@
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="2"/>
       <c r="B403" s="21" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C403" s="21"/>
       <c r="D403" s="21"/>
@@ -7825,7 +7593,7 @@
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="2"/>
       <c r="B404" s="21" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C404" s="21"/>
       <c r="D404" s="21"/>
@@ -7834,57 +7602,52 @@
     <row r="405" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="2"/>
       <c r="B405" s="21" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C405" s="21" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D405" s="21"/>
       <c r="E405" s="11"/>
-    </row>
-    <row r="406" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F405" s="15"/>
+    </row>
+    <row r="406" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="2"/>
       <c r="B406" s="21" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C406" s="21" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="D406" s="21" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E406" s="11" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="407" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="2"/>
-      <c r="B407" s="21" t="s">
-        <v>516</v>
-      </c>
-      <c r="C407" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D407" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E407" s="11" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A408" s="2"/>
-      <c r="B408" s="21"/>
+      <c r="B407" s="21"/>
+      <c r="C407" s="21"/>
+      <c r="D407" s="21"/>
+      <c r="E407" s="11"/>
+    </row>
+    <row r="408" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A408" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B408" s="21" t="s">
+        <v>520</v>
+      </c>
       <c r="C408" s="21"/>
       <c r="D408" s="21"/>
       <c r="E408" s="11"/>
     </row>
-    <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A409" s="2" t="s">
-        <v>247</v>
-      </c>
+    <row r="409" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A409" s="2"/>
       <c r="B409" s="21" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C409" s="21"/>
       <c r="D409" s="21"/>
@@ -7893,25 +7656,27 @@
     <row r="410" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="2"/>
       <c r="B410" s="21" t="s">
-        <v>518</v>
-      </c>
-      <c r="C410" s="21"/>
+        <v>522</v>
+      </c>
+      <c r="C410" s="21" t="s">
+        <v>496</v>
+      </c>
       <c r="D410" s="21"/>
       <c r="E410" s="11"/>
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="2"/>
       <c r="B411" s="21" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C411" s="21"/>
       <c r="D411" s="21"/>
       <c r="E411" s="11"/>
     </row>
-    <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="2"/>
       <c r="B412" s="21" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C412" s="21"/>
       <c r="D412" s="21"/>
@@ -7920,49 +7685,45 @@
     <row r="413" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="2"/>
       <c r="B413" s="21" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C413" s="21"/>
       <c r="D413" s="21"/>
       <c r="E413" s="11"/>
     </row>
-    <row r="414" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="2"/>
       <c r="B414" s="21" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C414" s="21" t="s">
-        <v>523</v>
-      </c>
-      <c r="D414" s="21" t="s">
-        <v>524</v>
-      </c>
-      <c r="E414" s="11" t="s">
-        <v>515</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="D414" s="21"/>
+      <c r="E414" s="11"/>
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="2"/>
       <c r="B415" s="21" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C415" s="21"/>
       <c r="D415" s="21"/>
       <c r="E415" s="11"/>
     </row>
-    <row r="416" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="2"/>
       <c r="B416" s="21" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C416" s="21"/>
       <c r="D416" s="21"/>
       <c r="E416" s="11"/>
     </row>
-    <row r="417" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="2"/>
       <c r="B417" s="21" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C417" s="21"/>
       <c r="D417" s="21"/>
@@ -7971,17 +7732,11 @@
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="2"/>
       <c r="B418" s="21" t="s">
-        <v>528</v>
-      </c>
-      <c r="C418" s="21" t="s">
-        <v>529</v>
-      </c>
-      <c r="D418" s="21" t="s">
         <v>530</v>
       </c>
-      <c r="E418" s="11" t="s">
-        <v>515</v>
-      </c>
+      <c r="C418" s="21"/>
+      <c r="D418" s="21"/>
+      <c r="E418" s="11"/>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="2"/>
@@ -7994,33 +7749,41 @@
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="2"/>
-      <c r="B420" s="21"/>
+      <c r="B420" s="21" t="s">
+        <v>532</v>
+      </c>
       <c r="C420" s="21"/>
       <c r="D420" s="21"/>
       <c r="E420" s="11"/>
     </row>
-    <row r="421" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A421" s="6"/>
-      <c r="B421" s="22" t="s">
-        <v>532</v>
-      </c>
-      <c r="C421" s="23"/>
-      <c r="D421" s="23"/>
-      <c r="E421" s="8"/>
-    </row>
-    <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A422" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B422" s="20"/>
-      <c r="C422" s="21"/>
-      <c r="D422" s="21"/>
-      <c r="E422" s="11"/>
+    <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A421" s="2"/>
+      <c r="B421" s="21" t="s">
+        <v>533</v>
+      </c>
+      <c r="C421" s="21"/>
+      <c r="D421" s="21"/>
+      <c r="E421" s="11"/>
+    </row>
+    <row r="422" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A422" s="2"/>
+      <c r="B422" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="C422" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="D422" s="21" t="s">
+        <v>536</v>
+      </c>
+      <c r="E422" s="11" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2"/>
       <c r="B423" s="21" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C423" s="21"/>
       <c r="D423" s="21"/>
@@ -8029,40 +7792,34 @@
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2"/>
       <c r="B424" s="21" t="s">
-        <v>534</v>
-      </c>
-      <c r="C424" s="21" t="s">
-        <v>535</v>
-      </c>
-      <c r="D424" s="21" t="s">
-        <v>536</v>
-      </c>
-      <c r="E424" s="11" t="s">
-        <v>515</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="C424" s="21"/>
+      <c r="D424" s="21"/>
+      <c r="E424" s="11"/>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2"/>
       <c r="B425" s="21" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C425" s="21"/>
       <c r="D425" s="21"/>
       <c r="E425" s="11"/>
     </row>
-    <row r="426" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2"/>
       <c r="B426" s="21" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C426" s="21"/>
       <c r="D426" s="21"/>
       <c r="E426" s="11"/>
     </row>
-    <row r="427" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2"/>
       <c r="B427" s="21" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C427" s="21"/>
       <c r="D427" s="21"/>
@@ -8071,7 +7828,7 @@
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2"/>
       <c r="B428" s="21" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C428" s="21"/>
       <c r="D428" s="21"/>
@@ -8080,120 +7837,135 @@
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="2"/>
       <c r="B429" s="21" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C429" s="21"/>
       <c r="D429" s="21"/>
       <c r="E429" s="11"/>
     </row>
-    <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="2"/>
       <c r="B430" s="21" t="s">
-        <v>542</v>
-      </c>
-      <c r="C430" s="21"/>
-      <c r="D430" s="21"/>
-      <c r="E430" s="11"/>
-    </row>
-    <row r="431" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>544</v>
+      </c>
+      <c r="C430" s="21" t="s">
+        <v>545</v>
+      </c>
+      <c r="D430" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="E430" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="F430" s="18" t="s">
+        <v>548</v>
+      </c>
+      <c r="G430" s="18" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="2"/>
       <c r="B431" s="21" t="s">
-        <v>543</v>
-      </c>
-      <c r="C431" s="21" t="s">
-        <v>146</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="C431" s="21"/>
       <c r="D431" s="21"/>
       <c r="E431" s="11"/>
-      <c r="F431" s="15"/>
-      <c r="G431" s="1"/>
-    </row>
-    <row r="432" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2"/>
       <c r="B432" s="21" t="s">
-        <v>544</v>
-      </c>
-      <c r="C432" s="21" t="s">
-        <v>77</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="C432" s="21"/>
       <c r="D432" s="21"/>
       <c r="E432" s="11"/>
     </row>
-    <row r="433" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="2"/>
       <c r="B433" s="21" t="s">
-        <v>545</v>
-      </c>
-      <c r="C433" s="21" t="s">
-        <v>546</v>
-      </c>
-      <c r="D433" s="21" t="s">
-        <v>547</v>
-      </c>
-      <c r="E433" s="11" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>552</v>
+      </c>
+      <c r="C433" s="21"/>
+      <c r="D433" s="21"/>
+      <c r="E433" s="11"/>
+    </row>
+    <row r="434" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="2"/>
-      <c r="B434" s="21"/>
+      <c r="B434" s="21" t="s">
+        <v>553</v>
+      </c>
       <c r="C434" s="21"/>
       <c r="D434" s="21"/>
       <c r="E434" s="11"/>
     </row>
-    <row r="435" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A435" s="2" t="s">
-        <v>247</v>
-      </c>
+    <row r="435" customFormat="false" ht="67.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A435" s="2"/>
       <c r="B435" s="21" t="s">
-        <v>548</v>
-      </c>
-      <c r="C435" s="21"/>
-      <c r="D435" s="21"/>
-      <c r="E435" s="11"/>
+        <v>554</v>
+      </c>
+      <c r="C435" s="21" t="s">
+        <v>555</v>
+      </c>
+      <c r="D435" s="21" t="s">
+        <v>556</v>
+      </c>
+      <c r="E435" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F435" s="21"/>
     </row>
     <row r="436" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2"/>
       <c r="B436" s="21" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="C436" s="21"/>
       <c r="D436" s="21"/>
       <c r="E436" s="11"/>
     </row>
-    <row r="437" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2"/>
       <c r="B437" s="21" t="s">
-        <v>550</v>
-      </c>
-      <c r="C437" s="21" t="s">
-        <v>523</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="C437" s="21"/>
       <c r="D437" s="21"/>
       <c r="E437" s="11"/>
     </row>
-    <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2"/>
       <c r="B438" s="21" t="s">
-        <v>551</v>
-      </c>
-      <c r="C438" s="21"/>
+        <v>559</v>
+      </c>
+      <c r="C438" s="21" t="s">
+        <v>222</v>
+      </c>
       <c r="D438" s="21"/>
-      <c r="E438" s="11"/>
+      <c r="E438" s="11" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="439" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="2"/>
       <c r="B439" s="21" t="s">
-        <v>552</v>
-      </c>
-      <c r="C439" s="21"/>
-      <c r="D439" s="21"/>
-      <c r="E439" s="11"/>
-    </row>
-    <row r="440" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>560</v>
+      </c>
+      <c r="C439" s="21" t="s">
+        <v>518</v>
+      </c>
+      <c r="D439" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="E439" s="11" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="2"/>
       <c r="B440" s="21" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="C440" s="21"/>
       <c r="D440" s="21"/>
@@ -8202,27 +7974,31 @@
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="2"/>
       <c r="B441" s="21" t="s">
-        <v>554</v>
-      </c>
-      <c r="C441" s="21" t="s">
-        <v>529</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="C441" s="21"/>
       <c r="D441" s="21"/>
       <c r="E441" s="11"/>
     </row>
-    <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2"/>
       <c r="B442" s="21" t="s">
-        <v>555</v>
-      </c>
-      <c r="C442" s="21"/>
-      <c r="D442" s="21"/>
-      <c r="E442" s="11"/>
+        <v>564</v>
+      </c>
+      <c r="C442" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="D442" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="E442" s="11" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2"/>
       <c r="B443" s="21" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="C443" s="21"/>
       <c r="D443" s="21"/>
@@ -8231,25 +8007,31 @@
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2"/>
       <c r="B444" s="21" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="C444" s="21"/>
       <c r="D444" s="21"/>
       <c r="E444" s="11"/>
     </row>
-    <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="445" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2"/>
       <c r="B445" s="21" t="s">
-        <v>558</v>
-      </c>
-      <c r="C445" s="21"/>
-      <c r="D445" s="21"/>
-      <c r="E445" s="11"/>
+        <v>569</v>
+      </c>
+      <c r="C445" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="D445" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="E445" s="11" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2"/>
       <c r="B446" s="21" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="C446" s="21"/>
       <c r="D446" s="21"/>
@@ -8257,41 +8039,41 @@
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="2"/>
-      <c r="B447" s="21" t="s">
-        <v>560</v>
-      </c>
+      <c r="B447" s="21"/>
       <c r="C447" s="21"/>
       <c r="D447" s="21"/>
       <c r="E447" s="11"/>
     </row>
-    <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A448" s="2"/>
+    <row r="448" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A448" s="2" t="s">
+        <v>572</v>
+      </c>
       <c r="B448" s="21" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="C448" s="21"/>
       <c r="D448" s="21"/>
       <c r="E448" s="11"/>
     </row>
-    <row r="449" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="2"/>
       <c r="B449" s="21" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="C449" s="21" t="s">
-        <v>563</v>
+        <v>535</v>
       </c>
       <c r="D449" s="21" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="E449" s="11" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="2"/>
       <c r="B450" s="21" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="C450" s="21"/>
       <c r="D450" s="21"/>
@@ -8299,35 +8081,32 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="2"/>
-      <c r="B451" s="21" t="s">
-        <v>566</v>
-      </c>
+      <c r="B451" s="21"/>
       <c r="C451" s="21"/>
       <c r="D451" s="21"/>
       <c r="E451" s="11"/>
     </row>
-    <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A452" s="2"/>
-      <c r="B452" s="21" t="s">
-        <v>567</v>
-      </c>
-      <c r="C452" s="21"/>
-      <c r="D452" s="21"/>
-      <c r="E452" s="11"/>
+    <row r="452" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A452" s="6"/>
+      <c r="B452" s="22" t="s">
+        <v>576</v>
+      </c>
+      <c r="C452" s="23"/>
+      <c r="D452" s="23"/>
+      <c r="E452" s="8"/>
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A453" s="2"/>
-      <c r="B453" s="21" t="s">
-        <v>568</v>
+      <c r="A453" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C453" s="21"/>
       <c r="D453" s="21"/>
       <c r="E453" s="11"/>
     </row>
-    <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2"/>
       <c r="B454" s="21" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="C454" s="21"/>
       <c r="D454" s="21"/>
@@ -8336,207 +8115,192 @@
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2"/>
       <c r="B455" s="21" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="C455" s="21"/>
       <c r="D455" s="21"/>
       <c r="E455" s="11"/>
     </row>
-    <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="456" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2"/>
       <c r="B456" s="21" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="C456" s="21"/>
       <c r="D456" s="21"/>
       <c r="E456" s="11"/>
     </row>
-    <row r="457" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2"/>
       <c r="B457" s="21" t="s">
-        <v>572</v>
-      </c>
-      <c r="C457" s="21" t="s">
-        <v>573</v>
-      </c>
-      <c r="D457" s="21" t="s">
-        <v>574</v>
-      </c>
-      <c r="E457" s="11" t="s">
-        <v>575</v>
-      </c>
-      <c r="F457" s="18" t="s">
-        <v>576</v>
-      </c>
-      <c r="G457" s="32" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>340</v>
+      </c>
+      <c r="C457" s="21"/>
+      <c r="D457" s="21"/>
+      <c r="E457" s="11"/>
+    </row>
+    <row r="458" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2"/>
       <c r="B458" s="21" t="s">
-        <v>578</v>
-      </c>
-      <c r="C458" s="21"/>
-      <c r="D458" s="21"/>
-      <c r="E458" s="11"/>
+        <v>580</v>
+      </c>
+      <c r="C458" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="D458" s="21" t="s">
+        <v>581</v>
+      </c>
+      <c r="E458" s="11" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="2"/>
-      <c r="B459" s="21" t="s">
-        <v>579</v>
-      </c>
+      <c r="B459" s="21"/>
       <c r="C459" s="21"/>
       <c r="D459" s="21"/>
       <c r="E459" s="11"/>
     </row>
-    <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A460" s="2"/>
-      <c r="B460" s="21" t="s">
-        <v>580</v>
-      </c>
-      <c r="C460" s="21"/>
-      <c r="D460" s="21"/>
-      <c r="E460" s="11"/>
-    </row>
-    <row r="461" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A461" s="2"/>
-      <c r="B461" s="21" t="s">
-        <v>581</v>
+    <row r="460" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A460" s="6"/>
+      <c r="B460" s="22" t="s">
+        <v>582</v>
+      </c>
+      <c r="C460" s="23"/>
+      <c r="D460" s="23"/>
+      <c r="E460" s="8"/>
+    </row>
+    <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A461" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C461" s="21"/>
       <c r="D461" s="21"/>
       <c r="E461" s="11"/>
     </row>
-    <row r="462" customFormat="false" ht="67.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="462" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="2"/>
       <c r="B462" s="21" t="s">
-        <v>582</v>
-      </c>
-      <c r="C462" s="21" t="s">
         <v>583</v>
       </c>
-      <c r="D462" s="21" t="s">
-        <v>584</v>
-      </c>
-      <c r="E462" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F462" s="21"/>
-    </row>
-    <row r="463" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C462" s="21"/>
+      <c r="D462" s="21"/>
+      <c r="E462" s="11"/>
+    </row>
+    <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2"/>
       <c r="B463" s="21" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C463" s="21"/>
       <c r="D463" s="21"/>
       <c r="E463" s="11"/>
     </row>
-    <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2"/>
       <c r="B464" s="21" t="s">
-        <v>586</v>
-      </c>
-      <c r="C464" s="21"/>
+        <v>585</v>
+      </c>
+      <c r="C464" s="21" t="s">
+        <v>308</v>
+      </c>
       <c r="D464" s="21"/>
       <c r="E464" s="11"/>
     </row>
     <row r="465" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2"/>
       <c r="B465" s="21" t="s">
+        <v>586</v>
+      </c>
+      <c r="C465" s="21" t="s">
         <v>587</v>
       </c>
-      <c r="C465" s="21" t="s">
-        <v>234</v>
-      </c>
       <c r="D465" s="21"/>
-      <c r="E465" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="466" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E465" s="11"/>
+    </row>
+    <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2"/>
       <c r="B466" s="21" t="s">
         <v>588</v>
       </c>
       <c r="C466" s="21" t="s">
-        <v>546</v>
-      </c>
-      <c r="D466" s="21" t="s">
-        <v>589</v>
-      </c>
-      <c r="E466" s="11" t="s">
-        <v>515</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="D466" s="21"/>
+      <c r="E466" s="11"/>
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2"/>
       <c r="B467" s="21" t="s">
+        <v>589</v>
+      </c>
+      <c r="C467" s="21" t="s">
         <v>590</v>
       </c>
-      <c r="C467" s="21"/>
-      <c r="D467" s="21"/>
-      <c r="E467" s="11"/>
-    </row>
-    <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D467" s="21" t="s">
+        <v>591</v>
+      </c>
+      <c r="E467" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="468" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2"/>
       <c r="B468" s="21" t="s">
-        <v>591</v>
-      </c>
-      <c r="C468" s="21"/>
-      <c r="D468" s="21"/>
-      <c r="E468" s="11"/>
-    </row>
-    <row r="469" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>592</v>
+      </c>
+      <c r="C468" s="21" t="s">
+        <v>593</v>
+      </c>
+      <c r="D468" s="21" t="s">
+        <v>594</v>
+      </c>
+      <c r="E468" s="11" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="469" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="2"/>
       <c r="B469" s="21" t="s">
-        <v>592</v>
-      </c>
-      <c r="C469" s="21" t="s">
-        <v>593</v>
-      </c>
-      <c r="D469" s="21" t="s">
-        <v>594</v>
-      </c>
-      <c r="E469" s="11" t="s">
-        <v>515</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="C469" s="21"/>
+      <c r="D469" s="21"/>
+      <c r="E469" s="11"/>
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="2"/>
-      <c r="B470" s="21" t="s">
-        <v>595</v>
-      </c>
+      <c r="B470" s="21"/>
       <c r="C470" s="21"/>
       <c r="D470" s="21"/>
       <c r="E470" s="11"/>
     </row>
-    <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A471" s="2"/>
-      <c r="B471" s="21" t="s">
+    <row r="471" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A471" s="6"/>
+      <c r="B471" s="22" t="s">
         <v>596</v>
       </c>
-      <c r="C471" s="21"/>
-      <c r="D471" s="21"/>
-      <c r="E471" s="11"/>
-    </row>
-    <row r="472" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A472" s="2"/>
-      <c r="B472" s="21" t="s">
+      <c r="C471" s="23"/>
+      <c r="D471" s="23" t="s">
         <v>597</v>
       </c>
-      <c r="C472" s="21" t="s">
-        <v>563</v>
-      </c>
-      <c r="D472" s="21" t="s">
+      <c r="E471" s="23" t="s">
+        <v>489</v>
+      </c>
+      <c r="F471" s="18" t="s">
         <v>598</v>
       </c>
-      <c r="E472" s="11" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A472" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B472" s="21"/>
+      <c r="C472" s="21"/>
+      <c r="D472" s="21"/>
+      <c r="E472" s="11"/>
+    </row>
+    <row r="473" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2"/>
       <c r="B473" s="21" t="s">
         <v>599</v>
@@ -8545,19 +8309,28 @@
       <c r="D473" s="21"/>
       <c r="E473" s="11"/>
     </row>
-    <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="474" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="2"/>
-      <c r="B474" s="21"/>
-      <c r="C474" s="21"/>
-      <c r="D474" s="21"/>
-      <c r="E474" s="11"/>
-    </row>
-    <row r="475" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A475" s="2" t="s">
+      <c r="B474" s="21" t="s">
         <v>600</v>
       </c>
+      <c r="C474" s="21" t="s">
+        <v>508</v>
+      </c>
+      <c r="D474" s="21" t="s">
+        <v>601</v>
+      </c>
+      <c r="E474" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="F474" s="18" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="475" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A475" s="2"/>
       <c r="B475" s="21" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C475" s="21"/>
       <c r="D475" s="21"/>
@@ -8566,55 +8339,60 @@
     <row r="476" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2"/>
       <c r="B476" s="21" t="s">
-        <v>602</v>
-      </c>
-      <c r="C476" s="21" t="s">
-        <v>563</v>
-      </c>
-      <c r="D476" s="21" t="s">
-        <v>598</v>
-      </c>
-      <c r="E476" s="11" t="s">
-        <v>515</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="C476" s="21"/>
+      <c r="D476" s="21"/>
+      <c r="E476" s="11"/>
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2"/>
       <c r="B477" s="21" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C477" s="21"/>
       <c r="D477" s="21"/>
       <c r="E477" s="11"/>
     </row>
-    <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="478" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2"/>
-      <c r="B478" s="21"/>
-      <c r="C478" s="21"/>
+      <c r="B478" s="21" t="s">
+        <v>607</v>
+      </c>
+      <c r="C478" s="21" t="s">
+        <v>608</v>
+      </c>
       <c r="D478" s="21"/>
       <c r="E478" s="11"/>
     </row>
-    <row r="479" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A479" s="6"/>
-      <c r="B479" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="C479" s="23"/>
-      <c r="D479" s="23"/>
-      <c r="E479" s="8"/>
+    <row r="479" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A479" s="2"/>
+      <c r="B479" s="21" t="s">
+        <v>609</v>
+      </c>
+      <c r="C479" s="21" t="s">
+        <v>610</v>
+      </c>
+      <c r="D479" s="21" t="s">
+        <v>611</v>
+      </c>
+      <c r="E479" s="11" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A480" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A480" s="2"/>
+      <c r="B480" s="21"/>
       <c r="C480" s="21"/>
       <c r="D480" s="21"/>
       <c r="E480" s="11"/>
     </row>
-    <row r="481" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A481" s="2"/>
+    <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A481" s="2" t="s">
+        <v>612</v>
+      </c>
       <c r="B481" s="21" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="C481" s="21"/>
       <c r="D481" s="21"/>
@@ -8623,25 +8401,23 @@
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2"/>
       <c r="B482" s="21" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="C482" s="21"/>
       <c r="D482" s="21"/>
       <c r="E482" s="11"/>
     </row>
-    <row r="483" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="2"/>
-      <c r="B483" s="21" t="s">
-        <v>607</v>
-      </c>
+      <c r="B483" s="21"/>
       <c r="C483" s="21"/>
       <c r="D483" s="21"/>
       <c r="E483" s="11"/>
     </row>
-    <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2"/>
       <c r="B484" s="21" t="s">
-        <v>356</v>
+        <v>615</v>
       </c>
       <c r="C484" s="21"/>
       <c r="D484" s="21"/>
@@ -8650,48 +8426,45 @@
     <row r="485" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2"/>
       <c r="B485" s="21" t="s">
-        <v>608</v>
-      </c>
-      <c r="C485" s="21" t="s">
-        <v>77</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="C485" s="21"/>
       <c r="D485" s="21"/>
       <c r="E485" s="11"/>
     </row>
-    <row r="486" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2"/>
-      <c r="B486" s="21" t="s">
-        <v>609</v>
-      </c>
-      <c r="C486" s="21" t="s">
-        <v>563</v>
-      </c>
-      <c r="D486" s="21" t="s">
-        <v>610</v>
-      </c>
-      <c r="E486" s="11" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A487" s="2"/>
-      <c r="B487" s="21"/>
-      <c r="C487" s="21"/>
-      <c r="D487" s="21"/>
-      <c r="E487" s="11"/>
-    </row>
-    <row r="488" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A488" s="6"/>
-      <c r="B488" s="22" t="s">
-        <v>611</v>
-      </c>
-      <c r="C488" s="23"/>
-      <c r="D488" s="23"/>
-      <c r="E488" s="8"/>
-    </row>
-    <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A489" s="2" t="s">
+      <c r="B486" s="21"/>
+      <c r="C486" s="21"/>
+      <c r="D486" s="21"/>
+      <c r="E486" s="11"/>
+    </row>
+    <row r="487" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A487" s="6"/>
+      <c r="B487" s="22" t="s">
+        <v>617</v>
+      </c>
+      <c r="C487" s="23"/>
+      <c r="D487" s="23" t="s">
+        <v>618</v>
+      </c>
+      <c r="E487" s="8" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A488" s="2" t="s">
         <v>5</v>
+      </c>
+      <c r="B488" s="21"/>
+      <c r="C488" s="21"/>
+      <c r="D488" s="21"/>
+      <c r="E488" s="11"/>
+    </row>
+    <row r="489" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A489" s="2"/>
+      <c r="B489" s="21" t="s">
+        <v>619</v>
       </c>
       <c r="C489" s="21"/>
       <c r="D489" s="21"/>
@@ -8700,121 +8473,117 @@
     <row r="490" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="2"/>
       <c r="B490" s="21" t="s">
-        <v>612</v>
-      </c>
-      <c r="C490" s="21"/>
-      <c r="D490" s="21"/>
-      <c r="E490" s="11"/>
-    </row>
-    <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>620</v>
+      </c>
+      <c r="C490" s="21" t="s">
+        <v>621</v>
+      </c>
+      <c r="D490" s="21" t="s">
+        <v>622</v>
+      </c>
+      <c r="E490" s="11" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="491" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="2"/>
       <c r="B491" s="21" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="C491" s="21"/>
-      <c r="D491" s="21"/>
-      <c r="E491" s="11"/>
-    </row>
-    <row r="492" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D491" s="21" t="s">
+        <v>624</v>
+      </c>
+      <c r="E491" s="11" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="492" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2"/>
       <c r="B492" s="21" t="s">
-        <v>614</v>
-      </c>
-      <c r="C492" s="21" t="s">
-        <v>321</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="C492" s="21"/>
       <c r="D492" s="21"/>
       <c r="E492" s="11"/>
     </row>
-    <row r="493" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="493" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2"/>
       <c r="B493" s="21" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="C493" s="21" t="s">
-        <v>616</v>
-      </c>
-      <c r="D493" s="21"/>
-      <c r="E493" s="11"/>
+        <v>274</v>
+      </c>
+      <c r="D493" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="E493" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F493" s="18" t="s">
+        <v>627</v>
+      </c>
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2"/>
       <c r="B494" s="21" t="s">
-        <v>617</v>
-      </c>
-      <c r="C494" s="21" t="s">
-        <v>461</v>
-      </c>
+        <v>628</v>
+      </c>
+      <c r="C494" s="21"/>
       <c r="D494" s="21"/>
       <c r="E494" s="11"/>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2"/>
       <c r="B495" s="21" t="s">
-        <v>618</v>
-      </c>
-      <c r="C495" s="21" t="s">
-        <v>619</v>
-      </c>
-      <c r="D495" s="21" t="s">
-        <v>620</v>
-      </c>
-      <c r="E495" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="496" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>629</v>
+      </c>
+      <c r="C495" s="21"/>
+      <c r="D495" s="21"/>
+      <c r="E495" s="11"/>
+    </row>
+    <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2"/>
       <c r="B496" s="21" t="s">
-        <v>621</v>
-      </c>
-      <c r="C496" s="21" t="s">
-        <v>622</v>
-      </c>
-      <c r="D496" s="21" t="s">
-        <v>623</v>
-      </c>
-      <c r="E496" s="11" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="497" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>630</v>
+      </c>
+      <c r="C496" s="21"/>
+      <c r="D496" s="21"/>
+      <c r="E496" s="11"/>
+    </row>
+    <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2"/>
       <c r="B497" s="21" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="C497" s="21"/>
       <c r="D497" s="21"/>
       <c r="E497" s="11"/>
     </row>
-    <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="498" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="2"/>
-      <c r="B498" s="21"/>
+      <c r="B498" s="21" t="s">
+        <v>632</v>
+      </c>
       <c r="C498" s="21"/>
       <c r="D498" s="21"/>
       <c r="E498" s="11"/>
     </row>
-    <row r="499" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A499" s="6"/>
-      <c r="B499" s="22" t="s">
-        <v>625</v>
-      </c>
-      <c r="C499" s="23"/>
-      <c r="D499" s="23" t="s">
-        <v>626</v>
-      </c>
-      <c r="E499" s="23" t="s">
-        <v>515</v>
-      </c>
-      <c r="F499" s="18" t="s">
-        <v>627</v>
-      </c>
+    <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A499" s="2"/>
+      <c r="B499" s="21" t="s">
+        <v>633</v>
+      </c>
+      <c r="C499" s="21"/>
+      <c r="D499" s="21"/>
+      <c r="E499" s="11"/>
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A500" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B500" s="21"/>
+      <c r="A500" s="2"/>
+      <c r="B500" s="21" t="s">
+        <v>634</v>
+      </c>
       <c r="C500" s="21"/>
       <c r="D500" s="21"/>
       <c r="E500" s="11"/>
@@ -8822,52 +8591,55 @@
     <row r="501" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="2"/>
       <c r="B501" s="21" t="s">
-        <v>628</v>
-      </c>
-      <c r="C501" s="21"/>
-      <c r="D501" s="21"/>
-      <c r="E501" s="11"/>
-    </row>
-    <row r="502" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>635</v>
+      </c>
+      <c r="C501" s="21" t="s">
+        <v>636</v>
+      </c>
+      <c r="D501" s="21" t="s">
+        <v>637</v>
+      </c>
+      <c r="E501" s="11" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="502" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="2"/>
       <c r="B502" s="21" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="C502" s="21" t="s">
-        <v>535</v>
+        <v>639</v>
       </c>
       <c r="D502" s="21" t="s">
-        <v>630</v>
+        <v>640</v>
       </c>
       <c r="E502" s="11" t="s">
-        <v>631</v>
-      </c>
-      <c r="F502" s="18" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="503" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="2"/>
-      <c r="B503" s="21" t="s">
-        <v>633</v>
-      </c>
+      <c r="B503" s="21"/>
       <c r="C503" s="21"/>
       <c r="D503" s="21"/>
       <c r="E503" s="11"/>
     </row>
-    <row r="504" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A504" s="2"/>
+    <row r="504" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A504" s="2" t="s">
+        <v>234</v>
+      </c>
       <c r="B504" s="21" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="C504" s="21"/>
       <c r="D504" s="21"/>
       <c r="E504" s="11"/>
     </row>
-    <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="505" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="2"/>
       <c r="B505" s="21" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="C505" s="21"/>
       <c r="D505" s="21"/>
@@ -8876,194 +8648,171 @@
     <row r="506" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="2"/>
       <c r="B506" s="21" t="s">
-        <v>636</v>
-      </c>
-      <c r="C506" s="21" t="s">
-        <v>637</v>
-      </c>
+        <v>644</v>
+      </c>
+      <c r="C506" s="21"/>
       <c r="D506" s="21"/>
       <c r="E506" s="11"/>
     </row>
-    <row r="507" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="2"/>
       <c r="B507" s="21" t="s">
-        <v>638</v>
-      </c>
-      <c r="C507" s="21" t="s">
-        <v>639</v>
-      </c>
-      <c r="D507" s="21" t="s">
-        <v>640</v>
-      </c>
-      <c r="E507" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>645</v>
+      </c>
+      <c r="C507" s="21"/>
+      <c r="D507" s="21"/>
+      <c r="E507" s="11"/>
+    </row>
+    <row r="508" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="2"/>
       <c r="B508" s="21" t="s">
+        <v>646</v>
+      </c>
+      <c r="C508" s="21" t="s">
+        <v>639</v>
+      </c>
+      <c r="D508" s="21" t="s">
+        <v>640</v>
+      </c>
+      <c r="E508" s="11" t="s">
         <v>641</v>
       </c>
-      <c r="C508" s="21" t="s">
-        <v>563</v>
-      </c>
-      <c r="D508" s="21" t="s">
-        <v>598</v>
-      </c>
-      <c r="E508" s="11" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="509" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="2"/>
       <c r="B509" s="21" t="s">
-        <v>642</v>
-      </c>
-      <c r="C509" s="21" t="s">
-        <v>77</v>
-      </c>
+        <v>647</v>
+      </c>
+      <c r="C509" s="21"/>
       <c r="D509" s="21"/>
       <c r="E509" s="11"/>
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="2"/>
-      <c r="B510" s="21"/>
+      <c r="B510" s="21" t="s">
+        <v>648</v>
+      </c>
       <c r="C510" s="21"/>
       <c r="D510" s="21"/>
       <c r="E510" s="11"/>
     </row>
-    <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A511" s="2" t="s">
-        <v>247</v>
-      </c>
+    <row r="511" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A511" s="2"/>
       <c r="B511" s="21" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="C511" s="21"/>
       <c r="D511" s="21"/>
       <c r="E511" s="11"/>
     </row>
-    <row r="512" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="2"/>
       <c r="B512" s="21" t="s">
-        <v>644</v>
-      </c>
-      <c r="C512" s="21" t="s">
-        <v>645</v>
-      </c>
-      <c r="D512" s="21" t="s">
-        <v>646</v>
-      </c>
-      <c r="E512" s="11" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>650</v>
+      </c>
+      <c r="C512" s="21"/>
+      <c r="D512" s="21"/>
+      <c r="E512" s="11"/>
+    </row>
+    <row r="513" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2"/>
       <c r="B513" s="21" t="s">
-        <v>648</v>
-      </c>
-      <c r="C513" s="21"/>
+        <v>651</v>
+      </c>
+      <c r="C513" s="21" t="s">
+        <v>608</v>
+      </c>
       <c r="D513" s="21"/>
       <c r="E513" s="11"/>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="2"/>
-      <c r="B514" s="21"/>
+      <c r="B514" s="21" t="s">
+        <v>652</v>
+      </c>
       <c r="C514" s="21"/>
       <c r="D514" s="21"/>
       <c r="E514" s="11"/>
     </row>
     <row r="515" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A515" s="6"/>
-      <c r="B515" s="22" t="s">
-        <v>649</v>
-      </c>
-      <c r="C515" s="23"/>
-      <c r="D515" s="23" t="s">
-        <v>650</v>
-      </c>
-      <c r="E515" s="8" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A516" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B516" s="21"/>
+      <c r="A515" s="2"/>
+      <c r="B515" s="21" t="s">
+        <v>653</v>
+      </c>
+      <c r="C515" s="21"/>
+      <c r="D515" s="21"/>
+      <c r="E515" s="11"/>
+    </row>
+    <row r="516" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A516" s="2"/>
+      <c r="B516" s="21" t="s">
+        <v>654</v>
+      </c>
       <c r="C516" s="21"/>
       <c r="D516" s="21"/>
       <c r="E516" s="11"/>
     </row>
-    <row r="517" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="2"/>
       <c r="B517" s="21" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C517" s="21"/>
       <c r="D517" s="21"/>
       <c r="E517" s="11"/>
     </row>
-    <row r="518" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="2"/>
       <c r="B518" s="21" t="s">
-        <v>652</v>
-      </c>
-      <c r="C518" s="21" t="s">
-        <v>653</v>
-      </c>
-      <c r="D518" s="21" t="s">
-        <v>654</v>
-      </c>
-      <c r="E518" s="11" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="519" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>656</v>
+      </c>
+      <c r="C518" s="21"/>
+      <c r="D518" s="21"/>
+      <c r="E518" s="11"/>
+    </row>
+    <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="2"/>
       <c r="B519" s="21" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C519" s="21"/>
-      <c r="D519" s="21" t="s">
-        <v>656</v>
-      </c>
-      <c r="E519" s="11" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="520" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D519" s="21"/>
+      <c r="E519" s="11"/>
+    </row>
+    <row r="520" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="2"/>
       <c r="B520" s="21" t="s">
-        <v>657</v>
-      </c>
-      <c r="C520" s="21"/>
-      <c r="D520" s="21"/>
-      <c r="E520" s="11"/>
+        <v>658</v>
+      </c>
+      <c r="C520" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="D520" s="21" t="s">
+        <v>659</v>
+      </c>
+      <c r="E520" s="11" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="521" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="2"/>
       <c r="B521" s="21" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C521" s="21" t="s">
-        <v>286</v>
+        <v>661</v>
       </c>
       <c r="D521" s="21" t="s">
-        <v>287</v>
+        <v>662</v>
       </c>
       <c r="E521" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F521" s="18" t="s">
-        <v>659</v>
+        <v>175</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="2"/>
       <c r="B522" s="21" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C522" s="21"/>
       <c r="D522" s="21"/>
@@ -9071,363 +8820,109 @@
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="2"/>
-      <c r="B523" s="21" t="s">
-        <v>661</v>
-      </c>
+      <c r="B523" s="21"/>
       <c r="C523" s="21"/>
       <c r="D523" s="21"/>
       <c r="E523" s="11"/>
     </row>
-    <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A524" s="2"/>
+    <row r="524" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A524" s="2" t="s">
+        <v>572</v>
+      </c>
       <c r="B524" s="21" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C524" s="21"/>
       <c r="D524" s="21"/>
       <c r="E524" s="11"/>
     </row>
-    <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="525" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2"/>
       <c r="B525" s="21" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C525" s="21"/>
       <c r="D525" s="21"/>
       <c r="E525" s="11"/>
     </row>
-    <row r="526" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2"/>
       <c r="B526" s="21" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C526" s="21"/>
       <c r="D526" s="21"/>
       <c r="E526" s="11"/>
     </row>
-    <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="527" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2"/>
       <c r="B527" s="21" t="s">
-        <v>665</v>
-      </c>
-      <c r="C527" s="21"/>
-      <c r="D527" s="21"/>
-      <c r="E527" s="11"/>
+        <v>667</v>
+      </c>
+      <c r="C527" s="21" t="s">
+        <v>639</v>
+      </c>
+      <c r="D527" s="21" t="s">
+        <v>640</v>
+      </c>
+      <c r="E527" s="11" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="2"/>
-      <c r="B528" s="21" t="s">
-        <v>666</v>
-      </c>
+      <c r="B528" s="21"/>
       <c r="C528" s="21"/>
       <c r="D528" s="21"/>
       <c r="E528" s="11"/>
     </row>
-    <row r="529" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="2"/>
       <c r="B529" s="21" t="s">
-        <v>667</v>
-      </c>
-      <c r="C529" s="21" t="s">
         <v>668</v>
       </c>
-      <c r="D529" s="21" t="s">
+      <c r="C529" s="21"/>
+      <c r="D529" s="21"/>
+      <c r="E529" s="11"/>
+    </row>
+    <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A530" s="32"/>
+      <c r="B530" s="33" t="s">
         <v>669</v>
       </c>
-      <c r="E529" s="11" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="530" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A530" s="2"/>
-      <c r="B530" s="21" t="s">
-        <v>670</v>
-      </c>
-      <c r="C530" s="21" t="s">
-        <v>671</v>
-      </c>
-      <c r="D530" s="21"/>
-      <c r="E530" s="11"/>
-    </row>
-    <row r="531" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A531" s="2"/>
-      <c r="B531" s="21" t="s">
-        <v>672</v>
-      </c>
-      <c r="C531" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D531" s="21"/>
-      <c r="E531" s="11"/>
-    </row>
-    <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A532" s="2"/>
-      <c r="B532" s="21"/>
-      <c r="C532" s="21"/>
-      <c r="D532" s="21"/>
-      <c r="E532" s="11"/>
-    </row>
-    <row r="533" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A533" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B533" s="21" t="s">
-        <v>673</v>
-      </c>
-      <c r="C533" s="21"/>
-      <c r="D533" s="21"/>
-      <c r="E533" s="11"/>
-    </row>
-    <row r="534" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A534" s="2"/>
-      <c r="B534" s="21" t="s">
-        <v>674</v>
-      </c>
-      <c r="C534" s="21"/>
-      <c r="D534" s="21"/>
-      <c r="E534" s="11"/>
-    </row>
-    <row r="535" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A535" s="2"/>
-      <c r="B535" s="21" t="s">
-        <v>675</v>
-      </c>
-      <c r="C535" s="21"/>
-      <c r="D535" s="21"/>
-      <c r="E535" s="11"/>
-    </row>
-    <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A536" s="2"/>
-      <c r="B536" s="21" t="s">
-        <v>676</v>
-      </c>
-      <c r="C536" s="21"/>
-      <c r="D536" s="21"/>
-      <c r="E536" s="11"/>
-    </row>
-    <row r="537" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A537" s="2"/>
-      <c r="B537" s="21" t="s">
-        <v>677</v>
-      </c>
-      <c r="C537" s="21" t="s">
-        <v>671</v>
-      </c>
-      <c r="D537" s="21"/>
-      <c r="E537" s="11"/>
-    </row>
-    <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A538" s="2"/>
-      <c r="B538" s="21" t="s">
-        <v>678</v>
-      </c>
-      <c r="C538" s="21"/>
-      <c r="D538" s="21"/>
-      <c r="E538" s="11"/>
-    </row>
-    <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A539" s="2"/>
-      <c r="B539" s="21" t="s">
-        <v>679</v>
-      </c>
-      <c r="C539" s="21"/>
-      <c r="D539" s="21"/>
-      <c r="E539" s="11"/>
-    </row>
-    <row r="540" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A540" s="2"/>
-      <c r="B540" s="21" t="s">
-        <v>680</v>
-      </c>
-      <c r="C540" s="21"/>
-      <c r="D540" s="21"/>
-      <c r="E540" s="11"/>
-    </row>
-    <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A541" s="2"/>
-      <c r="B541" s="21" t="s">
-        <v>681</v>
-      </c>
-      <c r="C541" s="21"/>
-      <c r="D541" s="21"/>
-      <c r="E541" s="11"/>
-    </row>
-    <row r="542" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A542" s="2"/>
-      <c r="B542" s="21" t="s">
-        <v>682</v>
-      </c>
-      <c r="C542" s="21" t="s">
-        <v>637</v>
-      </c>
-      <c r="D542" s="21"/>
-      <c r="E542" s="11"/>
-    </row>
-    <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A543" s="2"/>
-      <c r="B543" s="21" t="s">
-        <v>683</v>
-      </c>
-      <c r="C543" s="21"/>
-      <c r="D543" s="21"/>
-      <c r="E543" s="11"/>
-    </row>
-    <row r="544" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A544" s="2"/>
-      <c r="B544" s="21" t="s">
-        <v>684</v>
-      </c>
-      <c r="C544" s="21"/>
-      <c r="D544" s="21"/>
-      <c r="E544" s="11"/>
-    </row>
-    <row r="545" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A545" s="2"/>
-      <c r="B545" s="21" t="s">
-        <v>685</v>
-      </c>
-      <c r="C545" s="21"/>
-      <c r="D545" s="21"/>
-      <c r="E545" s="11"/>
-    </row>
-    <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A546" s="2"/>
-      <c r="B546" s="21" t="s">
-        <v>686</v>
-      </c>
-      <c r="C546" s="21"/>
-      <c r="D546" s="21"/>
-      <c r="E546" s="11"/>
-    </row>
-    <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A547" s="2"/>
-      <c r="B547" s="21" t="s">
-        <v>687</v>
-      </c>
-      <c r="C547" s="21"/>
-      <c r="D547" s="21"/>
-      <c r="E547" s="11"/>
-    </row>
-    <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A548" s="2"/>
-      <c r="B548" s="21" t="s">
-        <v>688</v>
-      </c>
-      <c r="C548" s="21"/>
-      <c r="D548" s="21"/>
-      <c r="E548" s="11"/>
-    </row>
-    <row r="549" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A549" s="2"/>
-      <c r="B549" s="21" t="s">
-        <v>689</v>
-      </c>
-      <c r="C549" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="D549" s="21" t="s">
-        <v>690</v>
-      </c>
-      <c r="E549" s="11" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="550" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A550" s="2"/>
-      <c r="B550" s="21" t="s">
-        <v>691</v>
-      </c>
-      <c r="C550" s="21" t="s">
-        <v>692</v>
-      </c>
-      <c r="D550" s="21" t="s">
-        <v>693</v>
-      </c>
-      <c r="E550" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A551" s="2"/>
-      <c r="B551" s="21" t="s">
-        <v>694</v>
-      </c>
-      <c r="C551" s="21"/>
-      <c r="D551" s="21"/>
-      <c r="E551" s="11"/>
-    </row>
-    <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A552" s="2"/>
-      <c r="B552" s="21"/>
-      <c r="C552" s="21"/>
-      <c r="D552" s="21"/>
-      <c r="E552" s="11"/>
-    </row>
-    <row r="553" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A553" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="B553" s="21" t="s">
-        <v>695</v>
-      </c>
-      <c r="C553" s="21"/>
-      <c r="D553" s="21"/>
-      <c r="E553" s="11"/>
-    </row>
-    <row r="554" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A554" s="2"/>
-      <c r="B554" s="21" t="s">
-        <v>696</v>
-      </c>
-      <c r="C554" s="21"/>
-      <c r="D554" s="21"/>
-      <c r="E554" s="11"/>
-    </row>
-    <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A555" s="2"/>
-      <c r="B555" s="21" t="s">
-        <v>697</v>
-      </c>
-      <c r="C555" s="21"/>
-      <c r="D555" s="21"/>
-      <c r="E555" s="11"/>
-    </row>
-    <row r="556" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A556" s="2"/>
-      <c r="B556" s="21" t="s">
-        <v>698</v>
-      </c>
-      <c r="C556" s="21" t="s">
-        <v>671</v>
-      </c>
-      <c r="D556" s="21"/>
-      <c r="E556" s="11"/>
-    </row>
-    <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A557" s="2"/>
-      <c r="B557" s="21"/>
-      <c r="C557" s="21"/>
-      <c r="D557" s="21"/>
-      <c r="E557" s="11"/>
-    </row>
-    <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A558" s="2"/>
-      <c r="B558" s="21" t="s">
-        <v>699</v>
-      </c>
-      <c r="C558" s="21"/>
-      <c r="D558" s="21"/>
-      <c r="E558" s="11"/>
-    </row>
-    <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A559" s="33"/>
-      <c r="B559" s="34" t="s">
-        <v>700</v>
-      </c>
-      <c r="C559" s="34"/>
-      <c r="D559" s="34"/>
-      <c r="E559" s="35"/>
-    </row>
+      <c r="C530" s="33"/>
+      <c r="D530" s="33"/>
+      <c r="E530" s="34"/>
+    </row>
+    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/assets/responsabilidades.xlsx
+++ b/assets/responsabilidades.xlsx
@@ -1600,7 +1600,7 @@
     <t xml:space="preserve">Atualizar lista encomendas</t>
   </si>
   <si>
-    <t xml:space="preserve">atualizarPecasEncomenda(id : int, pecas : List(Stock)) : void &amp;&amp; atualizarDataChegadaEncomenda(id : int, data_chegada : DateTime) : void &amp;&amp; atualizarDataPedidoEncomenda(id : int, data_pedido : DateTime) : void &amp;&amp; atualizarEstadoEncomenda(id : int, estado : EstadoEncomenda) : void</t>
+    <t xml:space="preserve">atualizarPecasEncomenda(id : int, pecas : List(Stock)) : void &amp;&amp; atualizarDataRececaoEncomenda(id : int, data_chegada : DateTime) : void &amp;&amp; atualizarDataEnvioEncomenda(id : int, data_pedido : DateTime) : void &amp;&amp; atualizarEstadoEncomenda(id : int, estado : EstadoEncomenda) : void</t>
   </si>
   <si>
     <t xml:space="preserve">(1) [Estado alterado de 'Rascunho' para 'Enviada'] (Passo 7)</t>
@@ -7361,7 +7361,7 @@
       <c r="D380" s="21"/>
       <c r="E380" s="11"/>
     </row>
-    <row r="381" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="2"/>
       <c r="B381" s="21" t="s">
         <v>486</v>
@@ -8432,7 +8432,7 @@
       <c r="D485" s="21"/>
       <c r="E485" s="11"/>
     </row>
-    <row r="486" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2"/>
       <c r="B486" s="21"/>
       <c r="C486" s="21"/>

--- a/assets/responsabilidades.xlsx
+++ b/assets/responsabilidades.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="672">
   <si>
     <t xml:space="preserve">Use Case</t>
   </si>
@@ -714,6 +714,9 @@
     <t xml:space="preserve">removerReparacao(id: int) : bool</t>
   </si>
   <si>
+    <t xml:space="preserve">Este método deve meter a flag de disponibilidade da reparacao como false</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -905,6 +908,9 @@
   </si>
   <si>
     <t xml:space="preserve">removerPeca(id: int) : bool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quando o método é chamado deve meter a flag de disponibilidade da Peca a false</t>
   </si>
   <si>
     <r>
@@ -4569,7 +4575,7 @@
       <c r="D113" s="12"/>
       <c r="E113" s="12"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2"/>
       <c r="B114" s="10" t="s">
         <v>166</v>
@@ -4582,6 +4588,9 @@
       </c>
       <c r="E114" s="12" t="s">
         <v>138</v>
+      </c>
+      <c r="F114" s="18" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4594,7 +4603,7 @@
     <row r="116" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="6"/>
       <c r="B116" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C116" s="8"/>
       <c r="D116" s="9"/>
@@ -4612,7 +4621,7 @@
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2"/>
       <c r="B118" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="12"/>
@@ -4621,7 +4630,7 @@
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2"/>
       <c r="B119" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C119" s="11"/>
       <c r="D119" s="12"/>
@@ -4630,22 +4639,22 @@
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2"/>
       <c r="B120" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E120" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2"/>
       <c r="B121" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C121" s="11"/>
       <c r="D121" s="12"/>
@@ -4654,7 +4663,7 @@
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2"/>
       <c r="B122" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C122" s="11"/>
       <c r="D122" s="12"/>
@@ -4663,67 +4672,67 @@
     <row r="123" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2"/>
       <c r="B123" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E123" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2"/>
       <c r="B124" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E124" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2"/>
       <c r="B125" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E125" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2"/>
       <c r="B126" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E126" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2"/>
       <c r="B127" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C127" s="11"/>
       <c r="D127" s="12"/>
@@ -4739,7 +4748,7 @@
     <row r="129" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="6"/>
       <c r="B129" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C129" s="8"/>
       <c r="D129" s="9"/>
@@ -4757,7 +4766,7 @@
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2"/>
       <c r="B131" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C131" s="11"/>
       <c r="D131" s="12"/>
@@ -4766,22 +4775,22 @@
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2"/>
       <c r="B132" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2"/>
       <c r="B133" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C133" s="11"/>
       <c r="D133" s="12"/>
@@ -4790,7 +4799,7 @@
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2"/>
       <c r="B134" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C134" s="11"/>
       <c r="D134" s="12"/>
@@ -4799,7 +4808,7 @@
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2"/>
       <c r="B135" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C135" s="11"/>
       <c r="D135" s="12"/>
@@ -4808,10 +4817,10 @@
     <row r="136" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2"/>
       <c r="B136" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D136" s="12"/>
       <c r="E136" s="12"/>
@@ -4819,10 +4828,10 @@
     <row r="137" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2"/>
       <c r="B137" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D137" s="12"/>
       <c r="E137" s="12"/>
@@ -4830,10 +4839,10 @@
     <row r="138" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2"/>
       <c r="B138" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D138" s="12"/>
       <c r="E138" s="12"/>
@@ -4841,16 +4850,16 @@
     <row r="139" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2"/>
       <c r="B139" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D139" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E139" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4863,7 +4872,7 @@
     <row r="141" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="6"/>
       <c r="B141" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C141" s="8"/>
       <c r="D141" s="9"/>
@@ -4881,22 +4890,22 @@
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2"/>
       <c r="B143" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D143" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E143" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2"/>
       <c r="B144" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C144" s="11"/>
       <c r="D144" s="12"/>
@@ -4905,7 +4914,7 @@
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2"/>
       <c r="B145" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C145" s="11"/>
       <c r="D145" s="12"/>
@@ -4914,7 +4923,7 @@
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2"/>
       <c r="B146" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C146" s="11"/>
       <c r="D146" s="12"/>
@@ -4923,16 +4932,19 @@
     <row r="147" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2"/>
       <c r="B147" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E147" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
+      </c>
+      <c r="F147" s="18" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4946,7 +4958,7 @@
     <row r="149" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="6"/>
       <c r="B149" s="7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C149" s="8"/>
       <c r="D149" s="9"/>
@@ -4964,7 +4976,7 @@
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2"/>
       <c r="B151" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C151" s="11"/>
       <c r="D151" s="12"/>
@@ -4973,7 +4985,7 @@
     <row r="152" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2"/>
       <c r="B152" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C152" s="11"/>
       <c r="D152" s="12"/>
@@ -4982,22 +4994,22 @@
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2"/>
       <c r="B153" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2"/>
       <c r="B154" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C154" s="11"/>
       <c r="D154" s="12"/>
@@ -5006,7 +5018,7 @@
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2"/>
       <c r="B155" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C155" s="11"/>
       <c r="D155" s="12"/>
@@ -5015,40 +5027,40 @@
     <row r="156" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2"/>
       <c r="B156" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D156" s="12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2"/>
       <c r="B157" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D157" s="12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2"/>
       <c r="B158" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D158" s="12"/>
       <c r="E158" s="12"/>
@@ -5056,10 +5068,10 @@
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2"/>
       <c r="B159" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D159" s="12"/>
       <c r="E159" s="12"/>
@@ -5067,16 +5079,16 @@
     <row r="160" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2"/>
       <c r="B160" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E160" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5088,10 +5100,10 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C162" s="11"/>
       <c r="D162" s="12"/>
@@ -5100,7 +5112,7 @@
     <row r="163" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2"/>
       <c r="B163" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C163" s="11"/>
       <c r="D163" s="12"/>
@@ -5109,7 +5121,7 @@
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2"/>
       <c r="B164" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C164" s="11"/>
       <c r="D164" s="12"/>
@@ -5118,37 +5130,37 @@
     <row r="165" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2"/>
       <c r="B165" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D165" s="12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E165" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2"/>
       <c r="B166" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E166" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2"/>
       <c r="B167" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C167" s="11"/>
       <c r="D167" s="12"/>
@@ -5164,7 +5176,7 @@
     <row r="169" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="6"/>
       <c r="B169" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C169" s="8"/>
       <c r="D169" s="9"/>
@@ -5182,7 +5194,7 @@
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2"/>
       <c r="B171" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C171" s="11"/>
       <c r="D171" s="12"/>
@@ -5191,22 +5203,22 @@
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2"/>
       <c r="B172" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D172" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E172" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2"/>
       <c r="B173" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C173" s="11"/>
       <c r="D173" s="12"/>
@@ -5215,7 +5227,7 @@
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2"/>
       <c r="B174" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C174" s="11"/>
       <c r="D174" s="12"/>
@@ -5224,7 +5236,7 @@
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2"/>
       <c r="B175" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C175" s="11"/>
       <c r="D175" s="12"/>
@@ -5233,10 +5245,10 @@
     <row r="176" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2"/>
       <c r="B176" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D176" s="12"/>
       <c r="E176" s="12"/>
@@ -5244,10 +5256,10 @@
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2"/>
       <c r="B177" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D177" s="12"/>
       <c r="E177" s="12"/>
@@ -5255,10 +5267,10 @@
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2"/>
       <c r="B178" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D178" s="12"/>
       <c r="E178" s="12"/>
@@ -5266,16 +5278,16 @@
     <row r="179" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2"/>
       <c r="B179" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D179" s="12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E179" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5288,7 +5300,7 @@
     <row r="181" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="6"/>
       <c r="B181" s="22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C181" s="23"/>
       <c r="D181" s="23"/>
@@ -5306,7 +5318,7 @@
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2"/>
       <c r="B183" s="21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C183" s="21"/>
       <c r="D183" s="21"/>
@@ -5315,7 +5327,7 @@
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2"/>
       <c r="B184" s="21" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C184" s="21"/>
       <c r="D184" s="21"/>
@@ -5324,10 +5336,10 @@
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2"/>
       <c r="B185" s="21" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C185" s="21" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D185" s="21"/>
       <c r="E185" s="11"/>
@@ -5335,7 +5347,7 @@
     <row r="186" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2"/>
       <c r="B186" s="21" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C186" s="21"/>
       <c r="D186" s="21"/>
@@ -5344,7 +5356,7 @@
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2"/>
       <c r="B187" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C187" s="21"/>
       <c r="D187" s="21"/>
@@ -5353,26 +5365,26 @@
     <row r="188" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="2"/>
       <c r="B188" s="21" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C188" s="21" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D188" s="21" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E188" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F188" s="15"/>
     </row>
     <row r="189" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2"/>
       <c r="B189" s="21" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C189" s="21" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D189" s="21"/>
       <c r="E189" s="11"/>
@@ -5380,55 +5392,55 @@
     <row r="190" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2"/>
       <c r="B190" s="21" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C190" s="21" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D190" s="21" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E190" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2"/>
       <c r="B191" s="21" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C191" s="21" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D191" s="21" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E191" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="2"/>
       <c r="B192" s="21" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C192" s="21" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D192" s="21" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E192" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F192" s="19" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2"/>
       <c r="B193" s="21" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C193" s="21"/>
       <c r="D193" s="21"/>
@@ -5448,7 +5460,7 @@
     <row r="195" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="6"/>
       <c r="B195" s="22" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C195" s="23"/>
       <c r="D195" s="23"/>
@@ -5466,7 +5478,7 @@
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2"/>
       <c r="B197" s="21" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C197" s="21"/>
       <c r="D197" s="21"/>
@@ -5475,7 +5487,7 @@
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2"/>
       <c r="B198" s="21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C198" s="21"/>
       <c r="D198" s="21"/>
@@ -5484,7 +5496,7 @@
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2"/>
       <c r="B199" s="21" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C199" s="21"/>
       <c r="D199" s="21"/>
@@ -5493,7 +5505,7 @@
     <row r="200" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2"/>
       <c r="B200" s="21" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C200" s="21"/>
       <c r="D200" s="21"/>
@@ -5502,7 +5514,7 @@
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2"/>
       <c r="B201" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C201" s="21"/>
       <c r="D201" s="21"/>
@@ -5511,10 +5523,10 @@
     <row r="202" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2"/>
       <c r="B202" s="21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C202" s="21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D202" s="21"/>
       <c r="E202" s="11"/>
@@ -5522,10 +5534,10 @@
     <row r="203" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2"/>
       <c r="B203" s="21" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C203" s="21" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D203" s="21"/>
       <c r="E203" s="11"/>
@@ -5533,10 +5545,10 @@
     <row r="204" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2"/>
       <c r="B204" s="21" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C204" s="21" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D204" s="21"/>
       <c r="E204" s="11"/>
@@ -5544,10 +5556,10 @@
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2"/>
       <c r="B205" s="21" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C205" s="21" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D205" s="21"/>
       <c r="E205" s="11"/>
@@ -5555,7 +5567,7 @@
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2"/>
       <c r="B206" s="21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C206" s="21"/>
       <c r="D206" s="21"/>
@@ -5570,10 +5582,10 @@
     </row>
     <row r="208" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B208" s="21" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C208" s="21"/>
       <c r="D208" s="21"/>
@@ -5582,7 +5594,7 @@
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2"/>
       <c r="B209" s="21" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C209" s="21"/>
       <c r="D209" s="21"/>
@@ -5591,25 +5603,25 @@
     <row r="210" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2"/>
       <c r="B210" s="21" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C210" s="21" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D210" s="21" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E210" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F210" s="19" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2"/>
       <c r="B211" s="21" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C211" s="21"/>
       <c r="D211" s="21"/>
@@ -5618,7 +5630,7 @@
     <row r="212" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2"/>
       <c r="B212" s="21" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C212" s="21"/>
       <c r="D212" s="21"/>
@@ -5627,25 +5639,25 @@
     <row r="213" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2"/>
       <c r="B213" s="21" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C213" s="21" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D213" s="21" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E213" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F213" s="19" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2"/>
       <c r="B214" s="21" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C214" s="21"/>
       <c r="D214" s="21"/>
@@ -5661,7 +5673,7 @@
     <row r="216" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="6"/>
       <c r="B216" s="22" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C216" s="23"/>
       <c r="D216" s="23"/>
@@ -5679,7 +5691,7 @@
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2"/>
       <c r="B218" s="21" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C218" s="21"/>
       <c r="D218" s="21"/>
@@ -5688,22 +5700,22 @@
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2"/>
       <c r="B219" s="21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C219" s="21" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D219" s="21" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E219" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2"/>
       <c r="B220" s="21" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C220" s="21"/>
       <c r="D220" s="21"/>
@@ -5712,22 +5724,22 @@
     <row r="221" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2"/>
       <c r="B221" s="21" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C221" s="21" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D221" s="24" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E221" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2"/>
       <c r="B222" s="21" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C222" s="21"/>
       <c r="D222" s="21"/>
@@ -5736,28 +5748,28 @@
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2"/>
       <c r="B223" s="21" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C223" s="21" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D223" s="21" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E223" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2"/>
       <c r="B224" s="21" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C224" s="21" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D224" s="21" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E224" s="11" t="s">
         <v>131</v>
@@ -5766,7 +5778,7 @@
     <row r="225" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2"/>
       <c r="B225" s="21" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C225" s="21"/>
       <c r="D225" s="21"/>
@@ -5785,7 +5797,7 @@
     <row r="227" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="6"/>
       <c r="B227" s="22" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C227" s="23"/>
       <c r="D227" s="23"/>
@@ -5803,7 +5815,7 @@
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2"/>
       <c r="B229" s="21" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C229" s="21"/>
       <c r="D229" s="21"/>
@@ -5812,7 +5824,7 @@
     <row r="230" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2"/>
       <c r="B230" s="21" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C230" s="21"/>
       <c r="D230" s="21"/>
@@ -5821,7 +5833,7 @@
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2"/>
       <c r="B231" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C231" s="21"/>
       <c r="D231" s="21"/>
@@ -5841,10 +5853,10 @@
     <row r="233" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2"/>
       <c r="B233" s="21" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C233" s="21" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D233" s="21"/>
       <c r="E233" s="11"/>
@@ -5852,16 +5864,16 @@
     <row r="234" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2"/>
       <c r="B234" s="21" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C234" s="21" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D234" s="21" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E234" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5874,7 +5886,7 @@
     <row r="236" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="6"/>
       <c r="B236" s="22" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C236" s="23"/>
       <c r="D236" s="23"/>
@@ -5892,7 +5904,7 @@
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2"/>
       <c r="B238" s="21" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C238" s="21"/>
       <c r="D238" s="21"/>
@@ -5901,22 +5913,22 @@
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="2"/>
       <c r="B239" s="21" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C239" s="21" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D239" s="21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E239" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="2"/>
       <c r="B240" s="21" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C240" s="21"/>
       <c r="D240" s="21"/>
@@ -5925,7 +5937,7 @@
     <row r="241" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2"/>
       <c r="B241" s="21" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C241" s="21"/>
       <c r="D241" s="21"/>
@@ -5934,7 +5946,7 @@
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2"/>
       <c r="B242" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C242" s="21"/>
       <c r="D242" s="21"/>
@@ -5943,7 +5955,7 @@
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2"/>
       <c r="B243" s="21" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C243" s="21" t="s">
         <v>22</v>
@@ -5954,10 +5966,10 @@
     <row r="244" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2"/>
       <c r="B244" s="21" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C244" s="21" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D244" s="21"/>
       <c r="E244" s="11"/>
@@ -5965,16 +5977,16 @@
     <row r="245" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2"/>
       <c r="B245" s="21" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C245" s="21" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D245" s="21" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E245" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5987,7 +5999,7 @@
     <row r="247" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="6"/>
       <c r="B247" s="22" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C247" s="23"/>
       <c r="D247" s="23"/>
@@ -6005,7 +6017,7 @@
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2"/>
       <c r="B249" s="21" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C249" s="21"/>
       <c r="D249" s="21"/>
@@ -6014,22 +6026,22 @@
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="2"/>
       <c r="B250" s="21" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C250" s="21" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D250" s="21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E250" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="2"/>
       <c r="B251" s="21" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C251" s="21"/>
       <c r="D251" s="21"/>
@@ -6038,7 +6050,7 @@
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2"/>
       <c r="B252" s="21" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C252" s="21"/>
       <c r="D252" s="21"/>
@@ -6047,16 +6059,16 @@
     <row r="253" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2"/>
       <c r="B253" s="21" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C253" s="21" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D253" s="21" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E253" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6070,7 +6082,7 @@
     <row r="255" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="6"/>
       <c r="B255" s="22" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C255" s="23"/>
       <c r="D255" s="23"/>
@@ -6088,7 +6100,7 @@
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="2"/>
       <c r="B257" s="21" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C257" s="21"/>
       <c r="D257" s="21"/>
@@ -6097,7 +6109,7 @@
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="2"/>
       <c r="B258" s="21" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C258" s="21"/>
       <c r="D258" s="21"/>
@@ -6106,37 +6118,37 @@
     <row r="259" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2"/>
       <c r="B259" s="21" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C259" s="21" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D259" s="24" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E259" s="25" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="2"/>
       <c r="B260" s="21" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C260" s="21" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D260" s="21" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E260" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="2"/>
       <c r="B261" s="21" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C261" s="21"/>
       <c r="D261" s="21"/>
@@ -6145,7 +6157,7 @@
     <row r="262" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="2"/>
       <c r="B262" s="21" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C262" s="21"/>
       <c r="D262" s="21"/>
@@ -6154,7 +6166,7 @@
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="2"/>
       <c r="B263" s="21" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C263" s="21"/>
       <c r="D263" s="21"/>
@@ -6163,7 +6175,7 @@
     <row r="264" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="2"/>
       <c r="B264" s="21" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C264" s="21"/>
       <c r="D264" s="21"/>
@@ -6172,7 +6184,7 @@
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="2"/>
       <c r="B265" s="21" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C265" s="21"/>
       <c r="D265" s="21"/>
@@ -6181,10 +6193,10 @@
     <row r="266" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="2"/>
       <c r="B266" s="21" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C266" s="21" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D266" s="21"/>
       <c r="E266" s="11"/>
@@ -6192,16 +6204,16 @@
     <row r="267" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2"/>
       <c r="B267" s="21" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C267" s="21" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D267" s="21" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E267" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6214,7 +6226,7 @@
     <row r="269" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="6"/>
       <c r="B269" s="22" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C269" s="23"/>
       <c r="D269" s="23"/>
@@ -6232,7 +6244,7 @@
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="2"/>
       <c r="B271" s="21" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C271" s="21"/>
       <c r="D271" s="21"/>
@@ -6241,22 +6253,22 @@
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="2"/>
       <c r="B272" s="21" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C272" s="21" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D272" s="21" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E272" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="2"/>
       <c r="B273" s="21" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C273" s="21"/>
       <c r="D273" s="21"/>
@@ -6265,22 +6277,22 @@
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="2"/>
       <c r="B274" s="21" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C274" s="21" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D274" s="21" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E274" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="2"/>
       <c r="B275" s="21" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C275" s="21"/>
       <c r="D275" s="21"/>
@@ -6289,7 +6301,7 @@
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="2"/>
       <c r="B276" s="21" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C276" s="21"/>
       <c r="D276" s="21"/>
@@ -6298,10 +6310,10 @@
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="2"/>
       <c r="B277" s="21" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C277" s="21" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D277" s="21"/>
       <c r="E277" s="11"/>
@@ -6309,16 +6321,16 @@
     <row r="278" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="2"/>
       <c r="B278" s="21" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C278" s="21" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D278" s="21" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E278" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6330,10 +6342,10 @@
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B280" s="21" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C280" s="21"/>
       <c r="D280" s="21"/>
@@ -6342,7 +6354,7 @@
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="2"/>
       <c r="B281" s="21" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C281" s="21"/>
       <c r="D281" s="21"/>
@@ -6351,7 +6363,7 @@
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="2"/>
       <c r="B282" s="21" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C282" s="21"/>
       <c r="D282" s="21"/>
@@ -6360,10 +6372,10 @@
     <row r="283" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="2"/>
       <c r="B283" s="21" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C283" s="21" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D283" s="21"/>
       <c r="E283" s="11"/>
@@ -6371,22 +6383,22 @@
     <row r="284" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="2"/>
       <c r="B284" s="21" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C284" s="21" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D284" s="21" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E284" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="2"/>
       <c r="B285" s="21" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C285" s="21"/>
       <c r="D285" s="21"/>
@@ -6395,7 +6407,7 @@
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="2"/>
       <c r="B286" s="21" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C286" s="21"/>
       <c r="D286" s="21"/>
@@ -6404,7 +6416,7 @@
     <row r="287" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="2"/>
       <c r="B287" s="21" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C287" s="21"/>
       <c r="D287" s="21"/>
@@ -6413,7 +6425,7 @@
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="2"/>
       <c r="B288" s="21" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C288" s="21"/>
       <c r="D288" s="21"/>
@@ -6422,10 +6434,10 @@
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="2"/>
       <c r="B289" s="21" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C289" s="21" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D289" s="21"/>
       <c r="E289" s="11"/>
@@ -6433,10 +6445,10 @@
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="2"/>
       <c r="B290" s="21" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C290" s="21" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D290" s="21"/>
       <c r="E290" s="11"/>
@@ -6444,22 +6456,22 @@
     <row r="291" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="2"/>
       <c r="B291" s="21" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C291" s="21" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D291" s="21" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E291" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2"/>
       <c r="B292" s="21" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C292" s="21"/>
       <c r="D292" s="21"/>
@@ -6475,7 +6487,7 @@
     <row r="294" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="6"/>
       <c r="B294" s="22" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C294" s="23"/>
       <c r="D294" s="23"/>
@@ -6493,7 +6505,7 @@
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="2"/>
       <c r="B296" s="21" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C296" s="21"/>
       <c r="D296" s="21"/>
@@ -6502,7 +6514,7 @@
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="2"/>
       <c r="B297" s="21" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C297" s="21"/>
       <c r="D297" s="21"/>
@@ -6511,7 +6523,7 @@
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="2"/>
       <c r="B298" s="21" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C298" s="21"/>
       <c r="D298" s="21"/>
@@ -6520,7 +6532,7 @@
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="2"/>
       <c r="B299" s="21" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C299" s="21"/>
       <c r="D299" s="21"/>
@@ -6529,16 +6541,16 @@
     <row r="300" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="2"/>
       <c r="B300" s="21" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C300" s="21" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D300" s="21" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E300" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6551,7 +6563,7 @@
     <row r="302" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="6"/>
       <c r="B302" s="22" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C302" s="23"/>
       <c r="D302" s="23"/>
@@ -6569,7 +6581,7 @@
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="2"/>
       <c r="B304" s="21" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C304" s="21"/>
       <c r="D304" s="21"/>
@@ -6578,7 +6590,7 @@
     <row r="305" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="2"/>
       <c r="B305" s="21" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C305" s="21"/>
       <c r="D305" s="21"/>
@@ -6587,7 +6599,7 @@
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="2"/>
       <c r="B306" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C306" s="21"/>
       <c r="D306" s="21"/>
@@ -6607,7 +6619,7 @@
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="2"/>
       <c r="B308" s="21" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C308" s="21" t="s">
         <v>42</v>
@@ -6618,10 +6630,10 @@
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="2"/>
       <c r="B309" s="21" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C309" s="21" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D309" s="21"/>
       <c r="E309" s="11"/>
@@ -6629,7 +6641,7 @@
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="2"/>
       <c r="B310" s="21" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C310" s="21" t="s">
         <v>51</v>
@@ -6640,16 +6652,16 @@
     <row r="311" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="2"/>
       <c r="B311" s="21" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C311" s="21" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D311" s="21" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E311" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6662,7 +6674,7 @@
     <row r="313" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="6"/>
       <c r="B313" s="22" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C313" s="23"/>
       <c r="D313" s="23"/>
@@ -6680,7 +6692,7 @@
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="2"/>
       <c r="B315" s="21" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C315" s="21"/>
       <c r="D315" s="21"/>
@@ -6689,22 +6701,22 @@
     <row r="316" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="2"/>
       <c r="B316" s="21" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C316" s="21" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D316" s="21" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E316" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="2"/>
       <c r="B317" s="21" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C317" s="21"/>
       <c r="D317" s="21"/>
@@ -6713,7 +6725,7 @@
     <row r="318" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="2"/>
       <c r="B318" s="21" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C318" s="21"/>
       <c r="D318" s="21"/>
@@ -6722,7 +6734,7 @@
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="2"/>
       <c r="B319" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C319" s="21"/>
       <c r="D319" s="21"/>
@@ -6731,7 +6743,7 @@
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="2"/>
       <c r="B320" s="21" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C320" s="21" t="s">
         <v>22</v>
@@ -6742,7 +6754,7 @@
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="2"/>
       <c r="B321" s="21" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C321" s="21" t="s">
         <v>42</v>
@@ -6753,10 +6765,10 @@
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="2"/>
       <c r="B322" s="21" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C322" s="21" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D322" s="21"/>
       <c r="E322" s="11"/>
@@ -6764,7 +6776,7 @@
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="2"/>
       <c r="B323" s="21" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C323" s="21" t="s">
         <v>51</v>
@@ -6775,16 +6787,16 @@
     <row r="324" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="2"/>
       <c r="B324" s="21" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C324" s="21" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D324" s="21" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E324" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6797,7 +6809,7 @@
     <row r="326" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="6"/>
       <c r="B326" s="22" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C326" s="23"/>
       <c r="D326" s="23"/>
@@ -6815,7 +6827,7 @@
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="2"/>
       <c r="B328" s="21" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C328" s="21"/>
       <c r="D328" s="21"/>
@@ -6824,22 +6836,22 @@
     <row r="329" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="2"/>
       <c r="B329" s="21" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C329" s="21" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D329" s="21" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E329" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="2"/>
       <c r="B330" s="21" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C330" s="21"/>
       <c r="D330" s="21"/>
@@ -6848,7 +6860,7 @@
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="2"/>
       <c r="B331" s="21" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C331" s="21"/>
       <c r="D331" s="21"/>
@@ -6857,16 +6869,16 @@
     <row r="332" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="2"/>
       <c r="B332" s="21" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C332" s="21" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D332" s="21" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E332" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6879,7 +6891,7 @@
     <row r="334" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="6"/>
       <c r="B334" s="22" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C334" s="23"/>
       <c r="D334" s="23"/>
@@ -6897,7 +6909,7 @@
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="2"/>
       <c r="B336" s="21" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C336" s="21"/>
       <c r="D336" s="21"/>
@@ -6906,7 +6918,7 @@
     <row r="337" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="2"/>
       <c r="B337" s="21" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C337" s="21"/>
       <c r="D337" s="21"/>
@@ -6915,22 +6927,22 @@
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="2"/>
       <c r="B338" s="21" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C338" s="21" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D338" s="21" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E338" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="2"/>
       <c r="B339" s="21" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C339" s="21"/>
       <c r="D339" s="21"/>
@@ -6939,7 +6951,7 @@
     <row r="340" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="2"/>
       <c r="B340" s="21" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C340" s="21"/>
       <c r="D340" s="21"/>
@@ -6948,7 +6960,7 @@
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="2"/>
       <c r="B341" s="21" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C341" s="21"/>
       <c r="D341" s="21"/>
@@ -6957,40 +6969,40 @@
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="2"/>
       <c r="B342" s="21" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C342" s="21" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D342" s="21" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E342" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="2"/>
       <c r="B343" s="21" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C343" s="21" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D343" s="21" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E343" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="2"/>
       <c r="B344" s="21" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C344" s="21" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D344" s="21"/>
       <c r="E344" s="11"/>
@@ -6998,31 +7010,31 @@
     <row r="345" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="2"/>
       <c r="B345" s="21" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C345" s="21" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D345" s="21" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E345" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="2"/>
       <c r="B346" s="21" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C346" s="21" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D346" s="21" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E346" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7035,7 +7047,7 @@
     <row r="348" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="26"/>
       <c r="B348" s="22" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C348" s="23"/>
       <c r="D348" s="23"/>
@@ -7053,7 +7065,7 @@
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="2"/>
       <c r="B350" s="21" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C350" s="21"/>
       <c r="D350" s="21"/>
@@ -7062,22 +7074,22 @@
     <row r="351" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="2"/>
       <c r="B351" s="21" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C351" s="21" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D351" s="21" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E351" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="2"/>
       <c r="B352" s="21" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C352" s="21"/>
       <c r="D352" s="21"/>
@@ -7086,7 +7098,7 @@
     <row r="353" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="2"/>
       <c r="B353" s="21" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C353" s="21"/>
       <c r="D353" s="21"/>
@@ -7095,7 +7107,7 @@
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="2"/>
       <c r="B354" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C354" s="21"/>
       <c r="D354" s="21"/>
@@ -7104,10 +7116,10 @@
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="2"/>
       <c r="B355" s="21" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C355" s="21" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D355" s="21"/>
       <c r="E355" s="11"/>
@@ -7115,10 +7127,10 @@
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="2"/>
       <c r="B356" s="21" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C356" s="21" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D356" s="21"/>
       <c r="E356" s="11"/>
@@ -7126,10 +7138,10 @@
     <row r="357" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="2"/>
       <c r="B357" s="21" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C357" s="21" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D357" s="21"/>
       <c r="E357" s="11"/>
@@ -7137,10 +7149,10 @@
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2"/>
       <c r="B358" s="21" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C358" s="21" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D358" s="21"/>
       <c r="E358" s="11"/>
@@ -7148,16 +7160,16 @@
     <row r="359" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="2"/>
       <c r="B359" s="21" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C359" s="21" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D359" s="21" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E359" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7170,7 +7182,7 @@
     <row r="361" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="6"/>
       <c r="B361" s="22" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C361" s="23"/>
       <c r="D361" s="23"/>
@@ -7188,7 +7200,7 @@
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="2"/>
       <c r="B363" s="21" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C363" s="21"/>
       <c r="D363" s="21"/>
@@ -7197,22 +7209,22 @@
     <row r="364" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="2"/>
       <c r="B364" s="21" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C364" s="21" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D364" s="21" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E364" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="2"/>
       <c r="B365" s="21" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C365" s="21"/>
       <c r="D365" s="21"/>
@@ -7221,7 +7233,7 @@
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="2"/>
       <c r="B366" s="21" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C366" s="21"/>
       <c r="D366" s="21"/>
@@ -7230,16 +7242,16 @@
     <row r="367" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="2"/>
       <c r="B367" s="21" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C367" s="21" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D367" s="21" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E367" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7252,7 +7264,7 @@
     <row r="369" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="28"/>
       <c r="B369" s="29" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C369" s="30"/>
       <c r="D369" s="30"/>
@@ -7270,7 +7282,7 @@
     <row r="371" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="2"/>
       <c r="B371" s="21" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C371" s="21"/>
       <c r="D371" s="21"/>
@@ -7279,7 +7291,7 @@
     <row r="372" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="2"/>
       <c r="B372" s="21" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C372" s="21"/>
       <c r="D372" s="21"/>
@@ -7288,10 +7300,10 @@
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="2"/>
       <c r="B373" s="21" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C373" s="21" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D373" s="21"/>
       <c r="E373" s="11"/>
@@ -7299,7 +7311,7 @@
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="2"/>
       <c r="B374" s="21" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C374" s="21"/>
       <c r="D374" s="21"/>
@@ -7308,7 +7320,7 @@
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="2"/>
       <c r="B375" s="21" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C375" s="21"/>
       <c r="D375" s="21"/>
@@ -7317,7 +7329,7 @@
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="2"/>
       <c r="B376" s="21" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C376" s="21"/>
       <c r="D376" s="21"/>
@@ -7326,7 +7338,7 @@
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="2"/>
       <c r="B377" s="21" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C377" s="21"/>
       <c r="D377" s="21"/>
@@ -7335,7 +7347,7 @@
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="2"/>
       <c r="B378" s="21" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C378" s="21"/>
       <c r="D378" s="21"/>
@@ -7344,7 +7356,7 @@
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="2"/>
       <c r="B379" s="21" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C379" s="21"/>
       <c r="D379" s="21"/>
@@ -7353,7 +7365,7 @@
     <row r="380" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2"/>
       <c r="B380" s="21" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C380" s="21" t="s">
         <v>140</v>
@@ -7364,16 +7376,16 @@
     <row r="381" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="2"/>
       <c r="B381" s="21" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C381" s="21" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D381" s="21" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E381" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7385,10 +7397,10 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B383" s="21" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C383" s="21"/>
       <c r="D383" s="21"/>
@@ -7397,7 +7409,7 @@
     <row r="384" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="2"/>
       <c r="B384" s="21" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C384" s="21"/>
       <c r="D384" s="21"/>
@@ -7406,7 +7418,7 @@
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="2"/>
       <c r="B385" s="21" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C385" s="21"/>
       <c r="D385" s="21"/>
@@ -7415,7 +7427,7 @@
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="2"/>
       <c r="B386" s="21" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C386" s="21"/>
       <c r="D386" s="21"/>
@@ -7424,7 +7436,7 @@
     <row r="387" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="2"/>
       <c r="B387" s="21" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C387" s="21"/>
       <c r="D387" s="21"/>
@@ -7433,22 +7445,22 @@
     <row r="388" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="2"/>
       <c r="B388" s="21" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C388" s="21" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D388" s="21" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E388" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="2"/>
       <c r="B389" s="21" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C389" s="21"/>
       <c r="D389" s="21"/>
@@ -7457,7 +7469,7 @@
     <row r="390" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="2"/>
       <c r="B390" s="21" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C390" s="21"/>
       <c r="D390" s="21"/>
@@ -7466,7 +7478,7 @@
     <row r="391" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="2"/>
       <c r="B391" s="21" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C391" s="21"/>
       <c r="D391" s="21"/>
@@ -7475,22 +7487,22 @@
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="2"/>
       <c r="B392" s="21" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C392" s="21" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D392" s="21" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E392" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="2"/>
       <c r="B393" s="21" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C393" s="21"/>
       <c r="D393" s="21"/>
@@ -7506,7 +7518,7 @@
     <row r="395" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="6"/>
       <c r="B395" s="22" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C395" s="23"/>
       <c r="D395" s="23"/>
@@ -7524,7 +7536,7 @@
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="2"/>
       <c r="B397" s="21" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C397" s="21"/>
       <c r="D397" s="21"/>
@@ -7533,22 +7545,22 @@
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="2"/>
       <c r="B398" s="21" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C398" s="21" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D398" s="21" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E398" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="2"/>
       <c r="B399" s="21" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C399" s="21"/>
       <c r="D399" s="21"/>
@@ -7557,7 +7569,7 @@
     <row r="400" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="2"/>
       <c r="B400" s="21" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C400" s="21"/>
       <c r="D400" s="21"/>
@@ -7566,7 +7578,7 @@
     <row r="401" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="2"/>
       <c r="B401" s="21" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C401" s="21"/>
       <c r="D401" s="21"/>
@@ -7575,7 +7587,7 @@
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2"/>
       <c r="B402" s="21" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C402" s="21"/>
       <c r="D402" s="21"/>
@@ -7584,7 +7596,7 @@
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="2"/>
       <c r="B403" s="21" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C403" s="21"/>
       <c r="D403" s="21"/>
@@ -7593,7 +7605,7 @@
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="2"/>
       <c r="B404" s="21" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C404" s="21"/>
       <c r="D404" s="21"/>
@@ -7602,7 +7614,7 @@
     <row r="405" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="2"/>
       <c r="B405" s="21" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C405" s="21" t="s">
         <v>140</v>
@@ -7614,16 +7626,16 @@
     <row r="406" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="2"/>
       <c r="B406" s="21" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C406" s="21" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D406" s="21" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E406" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7635,10 +7647,10 @@
     </row>
     <row r="408" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B408" s="21" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C408" s="21"/>
       <c r="D408" s="21"/>
@@ -7647,7 +7659,7 @@
     <row r="409" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="2"/>
       <c r="B409" s="21" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C409" s="21"/>
       <c r="D409" s="21"/>
@@ -7656,10 +7668,10 @@
     <row r="410" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="2"/>
       <c r="B410" s="21" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C410" s="21" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D410" s="21"/>
       <c r="E410" s="11"/>
@@ -7667,7 +7679,7 @@
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="2"/>
       <c r="B411" s="21" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C411" s="21"/>
       <c r="D411" s="21"/>
@@ -7676,7 +7688,7 @@
     <row r="412" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="2"/>
       <c r="B412" s="21" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C412" s="21"/>
       <c r="D412" s="21"/>
@@ -7685,7 +7697,7 @@
     <row r="413" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="2"/>
       <c r="B413" s="21" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C413" s="21"/>
       <c r="D413" s="21"/>
@@ -7694,10 +7706,10 @@
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="2"/>
       <c r="B414" s="21" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C414" s="21" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D414" s="21"/>
       <c r="E414" s="11"/>
@@ -7705,7 +7717,7 @@
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="2"/>
       <c r="B415" s="21" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C415" s="21"/>
       <c r="D415" s="21"/>
@@ -7714,7 +7726,7 @@
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="2"/>
       <c r="B416" s="21" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C416" s="21"/>
       <c r="D416" s="21"/>
@@ -7723,7 +7735,7 @@
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="2"/>
       <c r="B417" s="21" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C417" s="21"/>
       <c r="D417" s="21"/>
@@ -7732,7 +7744,7 @@
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="2"/>
       <c r="B418" s="21" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C418" s="21"/>
       <c r="D418" s="21"/>
@@ -7741,7 +7753,7 @@
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="2"/>
       <c r="B419" s="21" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C419" s="21"/>
       <c r="D419" s="21"/>
@@ -7750,7 +7762,7 @@
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="2"/>
       <c r="B420" s="21" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C420" s="21"/>
       <c r="D420" s="21"/>
@@ -7759,7 +7771,7 @@
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="2"/>
       <c r="B421" s="21" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C421" s="21"/>
       <c r="D421" s="21"/>
@@ -7768,22 +7780,22 @@
     <row r="422" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="2"/>
       <c r="B422" s="21" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C422" s="21" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D422" s="21" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E422" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2"/>
       <c r="B423" s="21" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C423" s="21"/>
       <c r="D423" s="21"/>
@@ -7792,7 +7804,7 @@
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2"/>
       <c r="B424" s="21" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C424" s="21"/>
       <c r="D424" s="21"/>
@@ -7801,7 +7813,7 @@
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2"/>
       <c r="B425" s="21" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C425" s="21"/>
       <c r="D425" s="21"/>
@@ -7810,7 +7822,7 @@
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2"/>
       <c r="B426" s="21" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C426" s="21"/>
       <c r="D426" s="21"/>
@@ -7819,7 +7831,7 @@
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2"/>
       <c r="B427" s="21" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C427" s="21"/>
       <c r="D427" s="21"/>
@@ -7828,7 +7840,7 @@
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2"/>
       <c r="B428" s="21" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C428" s="21"/>
       <c r="D428" s="21"/>
@@ -7837,7 +7849,7 @@
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="2"/>
       <c r="B429" s="21" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C429" s="21"/>
       <c r="D429" s="21"/>
@@ -7846,28 +7858,28 @@
     <row r="430" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="2"/>
       <c r="B430" s="21" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C430" s="21" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D430" s="21" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E430" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F430" s="18" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G430" s="18" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="2"/>
       <c r="B431" s="21" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C431" s="21"/>
       <c r="D431" s="21"/>
@@ -7876,7 +7888,7 @@
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2"/>
       <c r="B432" s="21" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C432" s="21"/>
       <c r="D432" s="21"/>
@@ -7885,7 +7897,7 @@
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="2"/>
       <c r="B433" s="21" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C433" s="21"/>
       <c r="D433" s="21"/>
@@ -7894,7 +7906,7 @@
     <row r="434" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="2"/>
       <c r="B434" s="21" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C434" s="21"/>
       <c r="D434" s="21"/>
@@ -7903,23 +7915,23 @@
     <row r="435" customFormat="false" ht="67.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="2"/>
       <c r="B435" s="21" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C435" s="21" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D435" s="21" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E435" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F435" s="21"/>
     </row>
     <row r="436" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2"/>
       <c r="B436" s="21" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C436" s="21"/>
       <c r="D436" s="21"/>
@@ -7928,7 +7940,7 @@
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2"/>
       <c r="B437" s="21" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C437" s="21"/>
       <c r="D437" s="21"/>
@@ -7937,35 +7949,35 @@
     <row r="438" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2"/>
       <c r="B438" s="21" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C438" s="21" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D438" s="21"/>
       <c r="E438" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="2"/>
       <c r="B439" s="21" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C439" s="21" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D439" s="21" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E439" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="2"/>
       <c r="B440" s="21" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C440" s="21"/>
       <c r="D440" s="21"/>
@@ -7974,7 +7986,7 @@
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="2"/>
       <c r="B441" s="21" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C441" s="21"/>
       <c r="D441" s="21"/>
@@ -7983,22 +7995,22 @@
     <row r="442" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2"/>
       <c r="B442" s="21" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C442" s="21" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D442" s="21" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E442" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2"/>
       <c r="B443" s="21" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C443" s="21"/>
       <c r="D443" s="21"/>
@@ -8007,7 +8019,7 @@
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2"/>
       <c r="B444" s="21" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C444" s="21"/>
       <c r="D444" s="21"/>
@@ -8016,22 +8028,22 @@
     <row r="445" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2"/>
       <c r="B445" s="21" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C445" s="21" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D445" s="21" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E445" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2"/>
       <c r="B446" s="21" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C446" s="21"/>
       <c r="D446" s="21"/>
@@ -8046,10 +8058,10 @@
     </row>
     <row r="448" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B448" s="21" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C448" s="21"/>
       <c r="D448" s="21"/>
@@ -8058,22 +8070,22 @@
     <row r="449" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="2"/>
       <c r="B449" s="21" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C449" s="21" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D449" s="21" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E449" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="2"/>
       <c r="B450" s="21" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C450" s="21"/>
       <c r="D450" s="21"/>
@@ -8089,7 +8101,7 @@
     <row r="452" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="6"/>
       <c r="B452" s="22" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C452" s="23"/>
       <c r="D452" s="23"/>
@@ -8106,7 +8118,7 @@
     <row r="454" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2"/>
       <c r="B454" s="21" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C454" s="21"/>
       <c r="D454" s="21"/>
@@ -8115,7 +8127,7 @@
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2"/>
       <c r="B455" s="21" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C455" s="21"/>
       <c r="D455" s="21"/>
@@ -8124,7 +8136,7 @@
     <row r="456" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2"/>
       <c r="B456" s="21" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C456" s="21"/>
       <c r="D456" s="21"/>
@@ -8133,7 +8145,7 @@
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2"/>
       <c r="B457" s="21" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C457" s="21"/>
       <c r="D457" s="21"/>
@@ -8142,16 +8154,16 @@
     <row r="458" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2"/>
       <c r="B458" s="21" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C458" s="21" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D458" s="21" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E458" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8164,7 +8176,7 @@
     <row r="460" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="6"/>
       <c r="B460" s="22" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C460" s="23"/>
       <c r="D460" s="23"/>
@@ -8181,7 +8193,7 @@
     <row r="462" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="2"/>
       <c r="B462" s="21" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C462" s="21"/>
       <c r="D462" s="21"/>
@@ -8190,7 +8202,7 @@
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2"/>
       <c r="B463" s="21" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C463" s="21"/>
       <c r="D463" s="21"/>
@@ -8199,10 +8211,10 @@
     <row r="464" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2"/>
       <c r="B464" s="21" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C464" s="21" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D464" s="21"/>
       <c r="E464" s="11"/>
@@ -8210,10 +8222,10 @@
     <row r="465" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2"/>
       <c r="B465" s="21" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C465" s="21" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D465" s="21"/>
       <c r="E465" s="11"/>
@@ -8221,10 +8233,10 @@
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2"/>
       <c r="B466" s="21" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C466" s="21" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D466" s="21"/>
       <c r="E466" s="11"/>
@@ -8232,13 +8244,13 @@
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2"/>
       <c r="B467" s="21" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C467" s="21" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D467" s="21" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E467" s="11" t="s">
         <v>24</v>
@@ -8247,22 +8259,22 @@
     <row r="468" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2"/>
       <c r="B468" s="21" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C468" s="21" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D468" s="21" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E468" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="469" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="2"/>
       <c r="B469" s="21" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C469" s="21"/>
       <c r="D469" s="21"/>
@@ -8278,17 +8290,17 @@
     <row r="471" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="6"/>
       <c r="B471" s="22" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C471" s="23"/>
       <c r="D471" s="23" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E471" s="23" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F471" s="18" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8303,7 +8315,7 @@
     <row r="473" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2"/>
       <c r="B473" s="21" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C473" s="21"/>
       <c r="D473" s="21"/>
@@ -8312,25 +8324,25 @@
     <row r="474" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="2"/>
       <c r="B474" s="21" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C474" s="21" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D474" s="21" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E474" s="11" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F474" s="18" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="475" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="2"/>
       <c r="B475" s="21" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C475" s="21"/>
       <c r="D475" s="21"/>
@@ -8339,7 +8351,7 @@
     <row r="476" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2"/>
       <c r="B476" s="21" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C476" s="21"/>
       <c r="D476" s="21"/>
@@ -8348,7 +8360,7 @@
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2"/>
       <c r="B477" s="21" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C477" s="21"/>
       <c r="D477" s="21"/>
@@ -8357,10 +8369,10 @@
     <row r="478" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2"/>
       <c r="B478" s="21" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C478" s="21" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D478" s="21"/>
       <c r="E478" s="11"/>
@@ -8368,16 +8380,16 @@
     <row r="479" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="2"/>
       <c r="B479" s="21" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C479" s="21" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D479" s="21" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E479" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8389,10 +8401,10 @@
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B481" s="21" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C481" s="21"/>
       <c r="D481" s="21"/>
@@ -8401,7 +8413,7 @@
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2"/>
       <c r="B482" s="21" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C482" s="21"/>
       <c r="D482" s="21"/>
@@ -8417,7 +8429,7 @@
     <row r="484" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2"/>
       <c r="B484" s="21" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C484" s="21"/>
       <c r="D484" s="21"/>
@@ -8426,7 +8438,7 @@
     <row r="485" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2"/>
       <c r="B485" s="21" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C485" s="21"/>
       <c r="D485" s="21"/>
@@ -8442,14 +8454,14 @@
     <row r="487" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="6"/>
       <c r="B487" s="22" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C487" s="23"/>
       <c r="D487" s="23" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E487" s="8" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8464,7 +8476,7 @@
     <row r="489" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="2"/>
       <c r="B489" s="21" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C489" s="21"/>
       <c r="D489" s="21"/>
@@ -8473,35 +8485,35 @@
     <row r="490" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="2"/>
       <c r="B490" s="21" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C490" s="21" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D490" s="21" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E490" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="491" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="2"/>
       <c r="B491" s="21" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C491" s="21"/>
       <c r="D491" s="21" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E491" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2"/>
       <c r="B492" s="21" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C492" s="21"/>
       <c r="D492" s="21"/>
@@ -8510,25 +8522,25 @@
     <row r="493" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2"/>
       <c r="B493" s="21" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C493" s="21" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D493" s="21" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E493" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F493" s="18" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2"/>
       <c r="B494" s="21" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C494" s="21"/>
       <c r="D494" s="21"/>
@@ -8537,7 +8549,7 @@
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2"/>
       <c r="B495" s="21" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C495" s="21"/>
       <c r="D495" s="21"/>
@@ -8546,7 +8558,7 @@
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2"/>
       <c r="B496" s="21" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C496" s="21"/>
       <c r="D496" s="21"/>
@@ -8555,7 +8567,7 @@
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2"/>
       <c r="B497" s="21" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C497" s="21"/>
       <c r="D497" s="21"/>
@@ -8564,7 +8576,7 @@
     <row r="498" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="2"/>
       <c r="B498" s="21" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C498" s="21"/>
       <c r="D498" s="21"/>
@@ -8573,7 +8585,7 @@
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="2"/>
       <c r="B499" s="21" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C499" s="21"/>
       <c r="D499" s="21"/>
@@ -8582,7 +8594,7 @@
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="2"/>
       <c r="B500" s="21" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C500" s="21"/>
       <c r="D500" s="21"/>
@@ -8591,31 +8603,31 @@
     <row r="501" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="2"/>
       <c r="B501" s="21" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C501" s="21" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D501" s="21" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E501" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="502" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="2"/>
       <c r="B502" s="21" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C502" s="21" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D502" s="21" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E502" s="11" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8627,10 +8639,10 @@
     </row>
     <row r="504" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B504" s="21" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C504" s="21"/>
       <c r="D504" s="21"/>
@@ -8639,7 +8651,7 @@
     <row r="505" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="2"/>
       <c r="B505" s="21" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C505" s="21"/>
       <c r="D505" s="21"/>
@@ -8648,7 +8660,7 @@
     <row r="506" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="2"/>
       <c r="B506" s="21" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C506" s="21"/>
       <c r="D506" s="21"/>
@@ -8657,7 +8669,7 @@
     <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="2"/>
       <c r="B507" s="21" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C507" s="21"/>
       <c r="D507" s="21"/>
@@ -8666,22 +8678,22 @@
     <row r="508" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="2"/>
       <c r="B508" s="21" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C508" s="21" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D508" s="21" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E508" s="11" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="2"/>
       <c r="B509" s="21" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C509" s="21"/>
       <c r="D509" s="21"/>
@@ -8690,7 +8702,7 @@
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="2"/>
       <c r="B510" s="21" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C510" s="21"/>
       <c r="D510" s="21"/>
@@ -8699,7 +8711,7 @@
     <row r="511" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="2"/>
       <c r="B511" s="21" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C511" s="21"/>
       <c r="D511" s="21"/>
@@ -8708,7 +8720,7 @@
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="2"/>
       <c r="B512" s="21" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C512" s="21"/>
       <c r="D512" s="21"/>
@@ -8717,10 +8729,10 @@
     <row r="513" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2"/>
       <c r="B513" s="21" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C513" s="21" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D513" s="21"/>
       <c r="E513" s="11"/>
@@ -8728,7 +8740,7 @@
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="2"/>
       <c r="B514" s="21" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C514" s="21"/>
       <c r="D514" s="21"/>
@@ -8737,7 +8749,7 @@
     <row r="515" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="2"/>
       <c r="B515" s="21" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C515" s="21"/>
       <c r="D515" s="21"/>
@@ -8746,7 +8758,7 @@
     <row r="516" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="2"/>
       <c r="B516" s="21" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C516" s="21"/>
       <c r="D516" s="21"/>
@@ -8755,7 +8767,7 @@
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="2"/>
       <c r="B517" s="21" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C517" s="21"/>
       <c r="D517" s="21"/>
@@ -8764,7 +8776,7 @@
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="2"/>
       <c r="B518" s="21" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C518" s="21"/>
       <c r="D518" s="21"/>
@@ -8773,7 +8785,7 @@
     <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="2"/>
       <c r="B519" s="21" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C519" s="21"/>
       <c r="D519" s="21"/>
@@ -8782,37 +8794,37 @@
     <row r="520" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="2"/>
       <c r="B520" s="21" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C520" s="21" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D520" s="21" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E520" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="2"/>
       <c r="B521" s="21" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C521" s="21" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D521" s="21" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E521" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="2"/>
       <c r="B522" s="21" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C522" s="21"/>
       <c r="D522" s="21"/>
@@ -8827,10 +8839,10 @@
     </row>
     <row r="524" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B524" s="21" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C524" s="21"/>
       <c r="D524" s="21"/>
@@ -8839,7 +8851,7 @@
     <row r="525" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2"/>
       <c r="B525" s="21" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C525" s="21"/>
       <c r="D525" s="21"/>
@@ -8848,7 +8860,7 @@
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2"/>
       <c r="B526" s="21" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C526" s="21"/>
       <c r="D526" s="21"/>
@@ -8857,16 +8869,16 @@
     <row r="527" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2"/>
       <c r="B527" s="21" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C527" s="21" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D527" s="21" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E527" s="11" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8879,7 +8891,7 @@
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="2"/>
       <c r="B529" s="21" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C529" s="21"/>
       <c r="D529" s="21"/>
@@ -8888,7 +8900,7 @@
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="32"/>
       <c r="B530" s="33" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C530" s="33"/>
       <c r="D530" s="33"/>

--- a/assets/responsabilidades.xlsx
+++ b/assets/responsabilidades.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="671">
   <si>
     <t xml:space="preserve">Use Case</t>
   </si>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">Atualizar stock</t>
   </si>
   <si>
-    <t xml:space="preserve">atualizaEstadoStock(id : int, estado : EstadosStock) : void</t>
+    <t xml:space="preserve">atualizaEstadoStock(id : int, estado : EstadoStock) : void</t>
   </si>
   <si>
     <t xml:space="preserve"> (alterar o estado das entradas de stock para ‘PendenteDevolucao’)</t>
@@ -1234,10 +1234,7 @@
     <t xml:space="preserve">9.1.2 O sistema atualiza o estado das entradas de stock devolvidas para o estado ‘Devolvida ao Fornecedor’</t>
   </si>
   <si>
-    <t xml:space="preserve">alteraEstado_Stock_Devolvida(pecas: List(string)) : void</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(alterar o estado das entradas de stock para ‘Devolvida_ao_Fornecedor’)</t>
+    <t xml:space="preserve">(alterar o estado das entradas de stock para ‘Devolvida_ao_Fornecedor’)/Repetir para todas as entradas</t>
   </si>
   <si>
     <t xml:space="preserve">9.1.3 Retorna ao passo 10</t>
@@ -5600,7 +5597,7 @@
       <c r="D209" s="21"/>
       <c r="E209" s="11"/>
     </row>
-    <row r="210" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2"/>
       <c r="B210" s="21" t="s">
         <v>294</v>
@@ -5609,19 +5606,19 @@
         <v>276</v>
       </c>
       <c r="D210" s="21" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="E210" s="11" t="s">
         <v>176</v>
       </c>
       <c r="F210" s="19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2"/>
       <c r="B211" s="21" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C211" s="21"/>
       <c r="D211" s="21"/>
@@ -5630,7 +5627,7 @@
     <row r="212" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2"/>
       <c r="B212" s="21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C212" s="21"/>
       <c r="D212" s="21"/>
@@ -5639,25 +5636,25 @@
     <row r="213" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2"/>
       <c r="B213" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="C213" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="C213" s="21" t="s">
+      <c r="D213" s="21" t="s">
         <v>300</v>
-      </c>
-      <c r="D213" s="21" t="s">
-        <v>301</v>
       </c>
       <c r="E213" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F213" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2"/>
       <c r="B214" s="21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C214" s="21"/>
       <c r="D214" s="21"/>
@@ -5673,7 +5670,7 @@
     <row r="216" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="6"/>
       <c r="B216" s="22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C216" s="23"/>
       <c r="D216" s="23"/>
@@ -5691,7 +5688,7 @@
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2"/>
       <c r="B218" s="21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C218" s="21"/>
       <c r="D218" s="21"/>
@@ -5703,10 +5700,10 @@
         <v>282</v>
       </c>
       <c r="C219" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="D219" s="21" t="s">
         <v>306</v>
-      </c>
-      <c r="D219" s="21" t="s">
-        <v>307</v>
       </c>
       <c r="E219" s="11" t="s">
         <v>176</v>
@@ -5715,7 +5712,7 @@
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2"/>
       <c r="B220" s="21" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C220" s="21"/>
       <c r="D220" s="21"/>
@@ -5724,13 +5721,13 @@
     <row r="221" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2"/>
       <c r="B221" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="C221" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="C221" s="21" t="s">
+      <c r="D221" s="24" t="s">
         <v>310</v>
-      </c>
-      <c r="D221" s="24" t="s">
-        <v>311</v>
       </c>
       <c r="E221" s="11" t="s">
         <v>176</v>
@@ -5739,7 +5736,7 @@
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2"/>
       <c r="B222" s="21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C222" s="21"/>
       <c r="D222" s="21"/>
@@ -5748,13 +5745,13 @@
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2"/>
       <c r="B223" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="C223" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="C223" s="21" t="s">
+      <c r="D223" s="21" t="s">
         <v>314</v>
-      </c>
-      <c r="D223" s="21" t="s">
-        <v>315</v>
       </c>
       <c r="E223" s="11" t="s">
         <v>176</v>
@@ -5763,13 +5760,13 @@
     <row r="224" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2"/>
       <c r="B224" s="21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C224" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="D224" s="21" t="s">
         <v>300</v>
-      </c>
-      <c r="D224" s="21" t="s">
-        <v>301</v>
       </c>
       <c r="E224" s="11" t="s">
         <v>131</v>
@@ -5778,7 +5775,7 @@
     <row r="225" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2"/>
       <c r="B225" s="21" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C225" s="21"/>
       <c r="D225" s="21"/>
@@ -5797,7 +5794,7 @@
     <row r="227" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="6"/>
       <c r="B227" s="22" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C227" s="23"/>
       <c r="D227" s="23"/>
@@ -5815,7 +5812,7 @@
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2"/>
       <c r="B229" s="21" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C229" s="21"/>
       <c r="D229" s="21"/>
@@ -5824,7 +5821,7 @@
     <row r="230" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2"/>
       <c r="B230" s="21" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C230" s="21"/>
       <c r="D230" s="21"/>
@@ -5833,7 +5830,7 @@
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2"/>
       <c r="B231" s="21" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C231" s="21"/>
       <c r="D231" s="21"/>
@@ -5853,10 +5850,10 @@
     <row r="233" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2"/>
       <c r="B233" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="C233" s="21" t="s">
         <v>322</v>
-      </c>
-      <c r="C233" s="21" t="s">
-        <v>323</v>
       </c>
       <c r="D233" s="21"/>
       <c r="E233" s="11"/>
@@ -5864,13 +5861,13 @@
     <row r="234" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2"/>
       <c r="B234" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="C234" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="C234" s="21" t="s">
+      <c r="D234" s="21" t="s">
         <v>325</v>
-      </c>
-      <c r="D234" s="21" t="s">
-        <v>326</v>
       </c>
       <c r="E234" s="11" t="s">
         <v>176</v>
@@ -5886,7 +5883,7 @@
     <row r="236" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="6"/>
       <c r="B236" s="22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C236" s="23"/>
       <c r="D236" s="23"/>
@@ -5904,7 +5901,7 @@
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2"/>
       <c r="B238" s="21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C238" s="21"/>
       <c r="D238" s="21"/>
@@ -5913,13 +5910,13 @@
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="2"/>
       <c r="B239" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="C239" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="C239" s="21" t="s">
+      <c r="D239" s="21" t="s">
         <v>330</v>
-      </c>
-      <c r="D239" s="21" t="s">
-        <v>331</v>
       </c>
       <c r="E239" s="11" t="s">
         <v>176</v>
@@ -5928,7 +5925,7 @@
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="2"/>
       <c r="B240" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C240" s="21"/>
       <c r="D240" s="21"/>
@@ -5955,7 +5952,7 @@
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2"/>
       <c r="B243" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C243" s="21" t="s">
         <v>22</v>
@@ -5966,10 +5963,10 @@
     <row r="244" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2"/>
       <c r="B244" s="21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C244" s="21" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D244" s="21"/>
       <c r="E244" s="11"/>
@@ -5977,13 +5974,13 @@
     <row r="245" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2"/>
       <c r="B245" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="C245" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="C245" s="21" t="s">
+      <c r="D245" s="21" t="s">
         <v>336</v>
-      </c>
-      <c r="D245" s="21" t="s">
-        <v>337</v>
       </c>
       <c r="E245" s="11" t="s">
         <v>176</v>
@@ -5999,7 +5996,7 @@
     <row r="247" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="6"/>
       <c r="B247" s="22" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C247" s="23"/>
       <c r="D247" s="23"/>
@@ -6017,7 +6014,7 @@
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2"/>
       <c r="B249" s="21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C249" s="21"/>
       <c r="D249" s="21"/>
@@ -6026,13 +6023,13 @@
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="2"/>
       <c r="B250" s="21" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C250" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="D250" s="21" t="s">
         <v>330</v>
-      </c>
-      <c r="D250" s="21" t="s">
-        <v>331</v>
       </c>
       <c r="E250" s="11" t="s">
         <v>176</v>
@@ -6041,7 +6038,7 @@
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="2"/>
       <c r="B251" s="21" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C251" s="21"/>
       <c r="D251" s="21"/>
@@ -6050,7 +6047,7 @@
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2"/>
       <c r="B252" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C252" s="21"/>
       <c r="D252" s="21"/>
@@ -6059,13 +6056,13 @@
     <row r="253" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2"/>
       <c r="B253" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="C253" s="21" t="s">
         <v>343</v>
       </c>
-      <c r="C253" s="21" t="s">
+      <c r="D253" s="21" t="s">
         <v>344</v>
-      </c>
-      <c r="D253" s="21" t="s">
-        <v>345</v>
       </c>
       <c r="E253" s="11" t="s">
         <v>176</v>
@@ -6082,7 +6079,7 @@
     <row r="255" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="6"/>
       <c r="B255" s="22" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C255" s="23"/>
       <c r="D255" s="23"/>
@@ -6100,7 +6097,7 @@
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="2"/>
       <c r="B257" s="21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C257" s="21"/>
       <c r="D257" s="21"/>
@@ -6109,7 +6106,7 @@
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="2"/>
       <c r="B258" s="21" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C258" s="21"/>
       <c r="D258" s="21"/>
@@ -6118,13 +6115,13 @@
     <row r="259" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2"/>
       <c r="B259" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="C259" s="21" t="s">
         <v>349</v>
       </c>
-      <c r="C259" s="21" t="s">
+      <c r="D259" s="24" t="s">
         <v>350</v>
-      </c>
-      <c r="D259" s="24" t="s">
-        <v>351</v>
       </c>
       <c r="E259" s="25" t="s">
         <v>176</v>
@@ -6133,13 +6130,13 @@
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="2"/>
       <c r="B260" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="C260" s="21" t="s">
         <v>352</v>
       </c>
-      <c r="C260" s="21" t="s">
+      <c r="D260" s="21" t="s">
         <v>353</v>
-      </c>
-      <c r="D260" s="21" t="s">
-        <v>354</v>
       </c>
       <c r="E260" s="11" t="s">
         <v>176</v>
@@ -6148,7 +6145,7 @@
     <row r="261" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="2"/>
       <c r="B261" s="21" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C261" s="21"/>
       <c r="D261" s="21"/>
@@ -6157,7 +6154,7 @@
     <row r="262" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="2"/>
       <c r="B262" s="21" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C262" s="21"/>
       <c r="D262" s="21"/>
@@ -6166,7 +6163,7 @@
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="2"/>
       <c r="B263" s="21" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C263" s="21"/>
       <c r="D263" s="21"/>
@@ -6175,7 +6172,7 @@
     <row r="264" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="2"/>
       <c r="B264" s="21" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C264" s="21"/>
       <c r="D264" s="21"/>
@@ -6184,7 +6181,7 @@
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="2"/>
       <c r="B265" s="21" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C265" s="21"/>
       <c r="D265" s="21"/>
@@ -6193,10 +6190,10 @@
     <row r="266" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="2"/>
       <c r="B266" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="C266" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="C266" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="D266" s="21"/>
       <c r="E266" s="11"/>
@@ -6204,13 +6201,13 @@
     <row r="267" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2"/>
       <c r="B267" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="C267" s="21" t="s">
         <v>362</v>
       </c>
-      <c r="C267" s="21" t="s">
+      <c r="D267" s="21" t="s">
         <v>363</v>
-      </c>
-      <c r="D267" s="21" t="s">
-        <v>364</v>
       </c>
       <c r="E267" s="11" t="s">
         <v>176</v>
@@ -6226,7 +6223,7 @@
     <row r="269" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="6"/>
       <c r="B269" s="22" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C269" s="23"/>
       <c r="D269" s="23"/>
@@ -6244,7 +6241,7 @@
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="2"/>
       <c r="B271" s="21" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C271" s="21"/>
       <c r="D271" s="21"/>
@@ -6253,13 +6250,13 @@
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="2"/>
       <c r="B272" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="C272" s="21" t="s">
         <v>367</v>
       </c>
-      <c r="C272" s="21" t="s">
+      <c r="D272" s="21" t="s">
         <v>368</v>
-      </c>
-      <c r="D272" s="21" t="s">
-        <v>369</v>
       </c>
       <c r="E272" s="11" t="s">
         <v>176</v>
@@ -6268,7 +6265,7 @@
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="2"/>
       <c r="B273" s="21" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C273" s="21"/>
       <c r="D273" s="21"/>
@@ -6277,13 +6274,13 @@
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="2"/>
       <c r="B274" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="C274" s="21" t="s">
         <v>371</v>
       </c>
-      <c r="C274" s="21" t="s">
+      <c r="D274" s="21" t="s">
         <v>372</v>
-      </c>
-      <c r="D274" s="21" t="s">
-        <v>373</v>
       </c>
       <c r="E274" s="11" t="s">
         <v>176</v>
@@ -6292,7 +6289,7 @@
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="2"/>
       <c r="B275" s="21" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C275" s="21"/>
       <c r="D275" s="21"/>
@@ -6301,7 +6298,7 @@
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="2"/>
       <c r="B276" s="21" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C276" s="21"/>
       <c r="D276" s="21"/>
@@ -6310,7 +6307,7 @@
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="2"/>
       <c r="B277" s="21" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C277" s="21" t="s">
         <v>290</v>
@@ -6321,13 +6318,13 @@
     <row r="278" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="2"/>
       <c r="B278" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C278" s="21" t="s">
         <v>377</v>
       </c>
-      <c r="C278" s="21" t="s">
+      <c r="D278" s="21" t="s">
         <v>378</v>
-      </c>
-      <c r="D278" s="21" t="s">
-        <v>379</v>
       </c>
       <c r="E278" s="11" t="s">
         <v>176</v>
@@ -6345,7 +6342,7 @@
         <v>236</v>
       </c>
       <c r="B280" s="21" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C280" s="21"/>
       <c r="D280" s="21"/>
@@ -6354,7 +6351,7 @@
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="2"/>
       <c r="B281" s="21" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C281" s="21"/>
       <c r="D281" s="21"/>
@@ -6363,7 +6360,7 @@
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="2"/>
       <c r="B282" s="21" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C282" s="21"/>
       <c r="D282" s="21"/>
@@ -6372,10 +6369,10 @@
     <row r="283" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="2"/>
       <c r="B283" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="C283" s="21" t="s">
         <v>383</v>
-      </c>
-      <c r="C283" s="21" t="s">
-        <v>384</v>
       </c>
       <c r="D283" s="21"/>
       <c r="E283" s="11"/>
@@ -6383,13 +6380,13 @@
     <row r="284" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="2"/>
       <c r="B284" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="C284" s="21" t="s">
         <v>385</v>
       </c>
-      <c r="C284" s="21" t="s">
+      <c r="D284" s="21" t="s">
         <v>386</v>
-      </c>
-      <c r="D284" s="21" t="s">
-        <v>387</v>
       </c>
       <c r="E284" s="11" t="s">
         <v>176</v>
@@ -6398,7 +6395,7 @@
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="2"/>
       <c r="B285" s="21" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C285" s="21"/>
       <c r="D285" s="21"/>
@@ -6407,7 +6404,7 @@
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="2"/>
       <c r="B286" s="21" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C286" s="21"/>
       <c r="D286" s="21"/>
@@ -6416,7 +6413,7 @@
     <row r="287" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="2"/>
       <c r="B287" s="21" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C287" s="21"/>
       <c r="D287" s="21"/>
@@ -6425,7 +6422,7 @@
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="2"/>
       <c r="B288" s="21" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C288" s="21"/>
       <c r="D288" s="21"/>
@@ -6434,10 +6431,10 @@
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="2"/>
       <c r="B289" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C289" s="21" t="s">
         <v>392</v>
-      </c>
-      <c r="C289" s="21" t="s">
-        <v>393</v>
       </c>
       <c r="D289" s="21"/>
       <c r="E289" s="11"/>
@@ -6445,10 +6442,10 @@
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="2"/>
       <c r="B290" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="C290" s="21" t="s">
         <v>394</v>
-      </c>
-      <c r="C290" s="21" t="s">
-        <v>395</v>
       </c>
       <c r="D290" s="21"/>
       <c r="E290" s="11"/>
@@ -6456,13 +6453,13 @@
     <row r="291" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="2"/>
       <c r="B291" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="C291" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="D291" s="21" t="s">
         <v>396</v>
-      </c>
-      <c r="C291" s="21" t="s">
-        <v>386</v>
-      </c>
-      <c r="D291" s="21" t="s">
-        <v>397</v>
       </c>
       <c r="E291" s="11" t="s">
         <v>176</v>
@@ -6471,7 +6468,7 @@
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2"/>
       <c r="B292" s="21" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C292" s="21"/>
       <c r="D292" s="21"/>
@@ -6487,7 +6484,7 @@
     <row r="294" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="6"/>
       <c r="B294" s="22" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C294" s="23"/>
       <c r="D294" s="23"/>
@@ -6505,7 +6502,7 @@
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="2"/>
       <c r="B296" s="21" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C296" s="21"/>
       <c r="D296" s="21"/>
@@ -6514,7 +6511,7 @@
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="2"/>
       <c r="B297" s="21" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C297" s="21"/>
       <c r="D297" s="21"/>
@@ -6523,7 +6520,7 @@
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="2"/>
       <c r="B298" s="21" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C298" s="21"/>
       <c r="D298" s="21"/>
@@ -6532,7 +6529,7 @@
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="2"/>
       <c r="B299" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C299" s="21"/>
       <c r="D299" s="21"/>
@@ -6541,13 +6538,13 @@
     <row r="300" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="2"/>
       <c r="B300" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="C300" s="21" t="s">
         <v>403</v>
       </c>
-      <c r="C300" s="21" t="s">
+      <c r="D300" s="21" t="s">
         <v>404</v>
-      </c>
-      <c r="D300" s="21" t="s">
-        <v>405</v>
       </c>
       <c r="E300" s="11" t="s">
         <v>176</v>
@@ -6563,7 +6560,7 @@
     <row r="302" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="6"/>
       <c r="B302" s="22" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C302" s="23"/>
       <c r="D302" s="23"/>
@@ -6581,7 +6578,7 @@
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="2"/>
       <c r="B304" s="21" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C304" s="21"/>
       <c r="D304" s="21"/>
@@ -6590,7 +6587,7 @@
     <row r="305" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="2"/>
       <c r="B305" s="21" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C305" s="21"/>
       <c r="D305" s="21"/>
@@ -6599,7 +6596,7 @@
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="2"/>
       <c r="B306" s="21" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C306" s="21"/>
       <c r="D306" s="21"/>
@@ -6619,7 +6616,7 @@
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="2"/>
       <c r="B308" s="21" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C308" s="21" t="s">
         <v>42</v>
@@ -6630,10 +6627,10 @@
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="2"/>
       <c r="B309" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="C309" s="21" t="s">
         <v>410</v>
-      </c>
-      <c r="C309" s="21" t="s">
-        <v>411</v>
       </c>
       <c r="D309" s="21"/>
       <c r="E309" s="11"/>
@@ -6641,7 +6638,7 @@
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="2"/>
       <c r="B310" s="21" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C310" s="21" t="s">
         <v>51</v>
@@ -6652,16 +6649,16 @@
     <row r="311" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="2"/>
       <c r="B311" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="C311" s="21" t="s">
         <v>413</v>
       </c>
-      <c r="C311" s="21" t="s">
+      <c r="D311" s="21" t="s">
         <v>414</v>
       </c>
-      <c r="D311" s="21" t="s">
+      <c r="E311" s="11" t="s">
         <v>415</v>
-      </c>
-      <c r="E311" s="11" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6674,7 +6671,7 @@
     <row r="313" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="6"/>
       <c r="B313" s="22" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C313" s="23"/>
       <c r="D313" s="23"/>
@@ -6692,7 +6689,7 @@
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="2"/>
       <c r="B315" s="21" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C315" s="21"/>
       <c r="D315" s="21"/>
@@ -6701,22 +6698,22 @@
     <row r="316" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="2"/>
       <c r="B316" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="C316" s="21" t="s">
         <v>419</v>
       </c>
-      <c r="C316" s="21" t="s">
+      <c r="D316" s="21" t="s">
         <v>420</v>
       </c>
-      <c r="D316" s="21" t="s">
-        <v>421</v>
-      </c>
       <c r="E316" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="2"/>
       <c r="B317" s="21" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C317" s="21"/>
       <c r="D317" s="21"/>
@@ -6743,7 +6740,7 @@
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="2"/>
       <c r="B320" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C320" s="21" t="s">
         <v>22</v>
@@ -6754,7 +6751,7 @@
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="2"/>
       <c r="B321" s="21" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C321" s="21" t="s">
         <v>42</v>
@@ -6765,10 +6762,10 @@
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="2"/>
       <c r="B322" s="21" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C322" s="21" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D322" s="21"/>
       <c r="E322" s="11"/>
@@ -6776,7 +6773,7 @@
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="2"/>
       <c r="B323" s="21" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C323" s="21" t="s">
         <v>51</v>
@@ -6787,16 +6784,16 @@
     <row r="324" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="2"/>
       <c r="B324" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="C324" s="21" t="s">
         <v>426</v>
       </c>
-      <c r="C324" s="21" t="s">
+      <c r="D324" s="21" t="s">
         <v>427</v>
       </c>
-      <c r="D324" s="21" t="s">
-        <v>428</v>
-      </c>
       <c r="E324" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6809,7 +6806,7 @@
     <row r="326" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="6"/>
       <c r="B326" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C326" s="23"/>
       <c r="D326" s="23"/>
@@ -6827,7 +6824,7 @@
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="2"/>
       <c r="B328" s="21" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C328" s="21"/>
       <c r="D328" s="21"/>
@@ -6836,22 +6833,22 @@
     <row r="329" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="2"/>
       <c r="B329" s="21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C329" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="D329" s="21" t="s">
         <v>420</v>
       </c>
-      <c r="D329" s="21" t="s">
-        <v>421</v>
-      </c>
       <c r="E329" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="2"/>
       <c r="B330" s="21" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C330" s="21"/>
       <c r="D330" s="21"/>
@@ -6860,7 +6857,7 @@
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="2"/>
       <c r="B331" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C331" s="21"/>
       <c r="D331" s="21"/>
@@ -6869,16 +6866,16 @@
     <row r="332" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="2"/>
       <c r="B332" s="21" t="s">
+        <v>432</v>
+      </c>
+      <c r="C332" s="21" t="s">
         <v>433</v>
       </c>
-      <c r="C332" s="21" t="s">
+      <c r="D332" s="21" t="s">
         <v>434</v>
       </c>
-      <c r="D332" s="21" t="s">
-        <v>435</v>
-      </c>
       <c r="E332" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6891,7 +6888,7 @@
     <row r="334" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="6"/>
       <c r="B334" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C334" s="23"/>
       <c r="D334" s="23"/>
@@ -6909,7 +6906,7 @@
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="2"/>
       <c r="B336" s="21" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C336" s="21"/>
       <c r="D336" s="21"/>
@@ -6918,7 +6915,7 @@
     <row r="337" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="2"/>
       <c r="B337" s="21" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C337" s="21"/>
       <c r="D337" s="21"/>
@@ -6927,22 +6924,22 @@
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="2"/>
       <c r="B338" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="C338" s="21" t="s">
         <v>439</v>
       </c>
-      <c r="C338" s="21" t="s">
+      <c r="D338" s="21" t="s">
         <v>440</v>
       </c>
-      <c r="D338" s="21" t="s">
-        <v>441</v>
-      </c>
       <c r="E338" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="2"/>
       <c r="B339" s="21" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C339" s="21"/>
       <c r="D339" s="21"/>
@@ -6951,7 +6948,7 @@
     <row r="340" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="2"/>
       <c r="B340" s="21" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C340" s="21"/>
       <c r="D340" s="21"/>
@@ -6960,7 +6957,7 @@
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="2"/>
       <c r="B341" s="21" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C341" s="21"/>
       <c r="D341" s="21"/>
@@ -6969,40 +6966,40 @@
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="2"/>
       <c r="B342" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="C342" s="21" t="s">
         <v>445</v>
       </c>
-      <c r="C342" s="21" t="s">
+      <c r="D342" s="21" t="s">
         <v>446</v>
       </c>
-      <c r="D342" s="21" t="s">
-        <v>447</v>
-      </c>
       <c r="E342" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="2"/>
       <c r="B343" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="C343" s="21" t="s">
         <v>448</v>
       </c>
-      <c r="C343" s="21" t="s">
+      <c r="D343" s="21" t="s">
         <v>449</v>
       </c>
-      <c r="D343" s="21" t="s">
-        <v>450</v>
-      </c>
       <c r="E343" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="2"/>
       <c r="B344" s="21" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C344" s="21" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D344" s="21"/>
       <c r="E344" s="11"/>
@@ -7010,31 +7007,31 @@
     <row r="345" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="2"/>
       <c r="B345" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="C345" s="21" t="s">
         <v>452</v>
       </c>
-      <c r="C345" s="21" t="s">
+      <c r="D345" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="D345" s="21" t="s">
-        <v>454</v>
-      </c>
       <c r="E345" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="2"/>
       <c r="B346" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="C346" s="21" t="s">
         <v>455</v>
       </c>
-      <c r="C346" s="21" t="s">
+      <c r="D346" s="21" t="s">
         <v>456</v>
       </c>
-      <c r="D346" s="21" t="s">
-        <v>457</v>
-      </c>
       <c r="E346" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7047,7 +7044,7 @@
     <row r="348" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="26"/>
       <c r="B348" s="22" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C348" s="23"/>
       <c r="D348" s="23"/>
@@ -7065,7 +7062,7 @@
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="2"/>
       <c r="B350" s="21" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C350" s="21"/>
       <c r="D350" s="21"/>
@@ -7074,22 +7071,22 @@
     <row r="351" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="2"/>
       <c r="B351" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="C351" s="21" t="s">
         <v>460</v>
       </c>
-      <c r="C351" s="21" t="s">
+      <c r="D351" s="21" t="s">
         <v>461</v>
       </c>
-      <c r="D351" s="21" t="s">
-        <v>462</v>
-      </c>
       <c r="E351" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="2"/>
       <c r="B352" s="21" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C352" s="21"/>
       <c r="D352" s="21"/>
@@ -7098,7 +7095,7 @@
     <row r="353" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="2"/>
       <c r="B353" s="21" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C353" s="21"/>
       <c r="D353" s="21"/>
@@ -7116,10 +7113,10 @@
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="2"/>
       <c r="B355" s="21" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C355" s="21" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D355" s="21"/>
       <c r="E355" s="11"/>
@@ -7127,10 +7124,10 @@
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="2"/>
       <c r="B356" s="21" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C356" s="21" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D356" s="21"/>
       <c r="E356" s="11"/>
@@ -7138,10 +7135,10 @@
     <row r="357" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="2"/>
       <c r="B357" s="21" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C357" s="21" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D357" s="21"/>
       <c r="E357" s="11"/>
@@ -7149,10 +7146,10 @@
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2"/>
       <c r="B358" s="21" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C358" s="21" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D358" s="21"/>
       <c r="E358" s="11"/>
@@ -7160,16 +7157,16 @@
     <row r="359" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="2"/>
       <c r="B359" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="C359" s="21" t="s">
         <v>469</v>
       </c>
-      <c r="C359" s="21" t="s">
+      <c r="D359" s="21" t="s">
         <v>470</v>
       </c>
-      <c r="D359" s="21" t="s">
-        <v>471</v>
-      </c>
       <c r="E359" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7182,7 +7179,7 @@
     <row r="361" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="6"/>
       <c r="B361" s="22" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C361" s="23"/>
       <c r="D361" s="23"/>
@@ -7200,7 +7197,7 @@
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="2"/>
       <c r="B363" s="21" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C363" s="21"/>
       <c r="D363" s="21"/>
@@ -7209,22 +7206,22 @@
     <row r="364" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="2"/>
       <c r="B364" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C364" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="D364" s="21" t="s">
         <v>461</v>
       </c>
-      <c r="D364" s="21" t="s">
-        <v>462</v>
-      </c>
       <c r="E364" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="2"/>
       <c r="B365" s="21" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C365" s="21"/>
       <c r="D365" s="21"/>
@@ -7233,7 +7230,7 @@
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="2"/>
       <c r="B366" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C366" s="21"/>
       <c r="D366" s="21"/>
@@ -7242,16 +7239,16 @@
     <row r="367" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="2"/>
       <c r="B367" s="21" t="s">
+        <v>475</v>
+      </c>
+      <c r="C367" s="21" t="s">
         <v>476</v>
       </c>
-      <c r="C367" s="21" t="s">
+      <c r="D367" s="21" t="s">
         <v>477</v>
       </c>
-      <c r="D367" s="21" t="s">
-        <v>478</v>
-      </c>
       <c r="E367" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7264,7 +7261,7 @@
     <row r="369" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="28"/>
       <c r="B369" s="29" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C369" s="30"/>
       <c r="D369" s="30"/>
@@ -7282,7 +7279,7 @@
     <row r="371" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="2"/>
       <c r="B371" s="21" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C371" s="21"/>
       <c r="D371" s="21"/>
@@ -7291,7 +7288,7 @@
     <row r="372" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="2"/>
       <c r="B372" s="21" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C372" s="21"/>
       <c r="D372" s="21"/>
@@ -7300,10 +7297,10 @@
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="2"/>
       <c r="B373" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="C373" s="21" t="s">
         <v>439</v>
-      </c>
-      <c r="C373" s="21" t="s">
-        <v>440</v>
       </c>
       <c r="D373" s="21"/>
       <c r="E373" s="11"/>
@@ -7311,7 +7308,7 @@
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="2"/>
       <c r="B374" s="21" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C374" s="21"/>
       <c r="D374" s="21"/>
@@ -7320,7 +7317,7 @@
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="2"/>
       <c r="B375" s="21" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C375" s="21"/>
       <c r="D375" s="21"/>
@@ -7329,7 +7326,7 @@
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="2"/>
       <c r="B376" s="21" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C376" s="21"/>
       <c r="D376" s="21"/>
@@ -7338,7 +7335,7 @@
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="2"/>
       <c r="B377" s="21" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C377" s="21"/>
       <c r="D377" s="21"/>
@@ -7347,7 +7344,7 @@
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="2"/>
       <c r="B378" s="21" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C378" s="21"/>
       <c r="D378" s="21"/>
@@ -7356,7 +7353,7 @@
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="2"/>
       <c r="B379" s="21" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C379" s="21"/>
       <c r="D379" s="21"/>
@@ -7365,7 +7362,7 @@
     <row r="380" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2"/>
       <c r="B380" s="21" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C380" s="21" t="s">
         <v>140</v>
@@ -7376,16 +7373,16 @@
     <row r="381" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="2"/>
       <c r="B381" s="21" t="s">
+        <v>487</v>
+      </c>
+      <c r="C381" s="21" t="s">
         <v>488</v>
       </c>
-      <c r="C381" s="21" t="s">
+      <c r="D381" s="21" t="s">
         <v>489</v>
       </c>
-      <c r="D381" s="21" t="s">
+      <c r="E381" s="11" t="s">
         <v>490</v>
-      </c>
-      <c r="E381" s="11" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7400,7 +7397,7 @@
         <v>236</v>
       </c>
       <c r="B383" s="21" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C383" s="21"/>
       <c r="D383" s="21"/>
@@ -7409,7 +7406,7 @@
     <row r="384" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="2"/>
       <c r="B384" s="21" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C384" s="21"/>
       <c r="D384" s="21"/>
@@ -7418,7 +7415,7 @@
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="2"/>
       <c r="B385" s="21" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C385" s="21"/>
       <c r="D385" s="21"/>
@@ -7427,7 +7424,7 @@
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="2"/>
       <c r="B386" s="21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C386" s="21"/>
       <c r="D386" s="21"/>
@@ -7436,7 +7433,7 @@
     <row r="387" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="2"/>
       <c r="B387" s="21" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C387" s="21"/>
       <c r="D387" s="21"/>
@@ -7445,22 +7442,22 @@
     <row r="388" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="2"/>
       <c r="B388" s="21" t="s">
+        <v>496</v>
+      </c>
+      <c r="C388" s="21" t="s">
         <v>497</v>
       </c>
-      <c r="C388" s="21" t="s">
+      <c r="D388" s="21" t="s">
         <v>498</v>
       </c>
-      <c r="D388" s="21" t="s">
-        <v>499</v>
-      </c>
       <c r="E388" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="2"/>
       <c r="B389" s="21" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C389" s="21"/>
       <c r="D389" s="21"/>
@@ -7469,7 +7466,7 @@
     <row r="390" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="2"/>
       <c r="B390" s="21" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C390" s="21"/>
       <c r="D390" s="21"/>
@@ -7478,7 +7475,7 @@
     <row r="391" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="2"/>
       <c r="B391" s="21" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C391" s="21"/>
       <c r="D391" s="21"/>
@@ -7487,22 +7484,22 @@
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="2"/>
       <c r="B392" s="21" t="s">
+        <v>502</v>
+      </c>
+      <c r="C392" s="21" t="s">
         <v>503</v>
       </c>
-      <c r="C392" s="21" t="s">
+      <c r="D392" s="21" t="s">
         <v>504</v>
       </c>
-      <c r="D392" s="21" t="s">
-        <v>505</v>
-      </c>
       <c r="E392" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="2"/>
       <c r="B393" s="21" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C393" s="21"/>
       <c r="D393" s="21"/>
@@ -7518,7 +7515,7 @@
     <row r="395" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="6"/>
       <c r="B395" s="22" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C395" s="23"/>
       <c r="D395" s="23"/>
@@ -7536,7 +7533,7 @@
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="2"/>
       <c r="B397" s="21" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C397" s="21"/>
       <c r="D397" s="21"/>
@@ -7545,22 +7542,22 @@
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="2"/>
       <c r="B398" s="21" t="s">
+        <v>508</v>
+      </c>
+      <c r="C398" s="21" t="s">
         <v>509</v>
       </c>
-      <c r="C398" s="21" t="s">
+      <c r="D398" s="21" t="s">
         <v>510</v>
       </c>
-      <c r="D398" s="21" t="s">
-        <v>511</v>
-      </c>
       <c r="E398" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="2"/>
       <c r="B399" s="21" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C399" s="21"/>
       <c r="D399" s="21"/>
@@ -7569,7 +7566,7 @@
     <row r="400" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="2"/>
       <c r="B400" s="21" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C400" s="21"/>
       <c r="D400" s="21"/>
@@ -7578,7 +7575,7 @@
     <row r="401" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="2"/>
       <c r="B401" s="21" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C401" s="21"/>
       <c r="D401" s="21"/>
@@ -7587,7 +7584,7 @@
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2"/>
       <c r="B402" s="21" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C402" s="21"/>
       <c r="D402" s="21"/>
@@ -7596,7 +7593,7 @@
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="2"/>
       <c r="B403" s="21" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C403" s="21"/>
       <c r="D403" s="21"/>
@@ -7605,7 +7602,7 @@
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="2"/>
       <c r="B404" s="21" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C404" s="21"/>
       <c r="D404" s="21"/>
@@ -7614,7 +7611,7 @@
     <row r="405" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="2"/>
       <c r="B405" s="21" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C405" s="21" t="s">
         <v>140</v>
@@ -7626,16 +7623,16 @@
     <row r="406" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="2"/>
       <c r="B406" s="21" t="s">
+        <v>518</v>
+      </c>
+      <c r="C406" s="21" t="s">
         <v>519</v>
       </c>
-      <c r="C406" s="21" t="s">
+      <c r="D406" s="21" t="s">
         <v>520</v>
       </c>
-      <c r="D406" s="21" t="s">
-        <v>521</v>
-      </c>
       <c r="E406" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7650,7 +7647,7 @@
         <v>236</v>
       </c>
       <c r="B408" s="21" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C408" s="21"/>
       <c r="D408" s="21"/>
@@ -7659,7 +7656,7 @@
     <row r="409" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="2"/>
       <c r="B409" s="21" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C409" s="21"/>
       <c r="D409" s="21"/>
@@ -7668,10 +7665,10 @@
     <row r="410" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="2"/>
       <c r="B410" s="21" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C410" s="21" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D410" s="21"/>
       <c r="E410" s="11"/>
@@ -7679,7 +7676,7 @@
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="2"/>
       <c r="B411" s="21" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C411" s="21"/>
       <c r="D411" s="21"/>
@@ -7688,7 +7685,7 @@
     <row r="412" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="2"/>
       <c r="B412" s="21" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C412" s="21"/>
       <c r="D412" s="21"/>
@@ -7697,7 +7694,7 @@
     <row r="413" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="2"/>
       <c r="B413" s="21" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C413" s="21"/>
       <c r="D413" s="21"/>
@@ -7706,10 +7703,10 @@
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="2"/>
       <c r="B414" s="21" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C414" s="21" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D414" s="21"/>
       <c r="E414" s="11"/>
@@ -7717,7 +7714,7 @@
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="2"/>
       <c r="B415" s="21" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C415" s="21"/>
       <c r="D415" s="21"/>
@@ -7726,7 +7723,7 @@
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="2"/>
       <c r="B416" s="21" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C416" s="21"/>
       <c r="D416" s="21"/>
@@ -7735,7 +7732,7 @@
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="2"/>
       <c r="B417" s="21" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C417" s="21"/>
       <c r="D417" s="21"/>
@@ -7744,7 +7741,7 @@
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="2"/>
       <c r="B418" s="21" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C418" s="21"/>
       <c r="D418" s="21"/>
@@ -7753,7 +7750,7 @@
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="2"/>
       <c r="B419" s="21" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C419" s="21"/>
       <c r="D419" s="21"/>
@@ -7762,7 +7759,7 @@
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="2"/>
       <c r="B420" s="21" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C420" s="21"/>
       <c r="D420" s="21"/>
@@ -7771,7 +7768,7 @@
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="2"/>
       <c r="B421" s="21" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C421" s="21"/>
       <c r="D421" s="21"/>
@@ -7780,22 +7777,22 @@
     <row r="422" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="2"/>
       <c r="B422" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="C422" s="21" t="s">
         <v>536</v>
       </c>
-      <c r="C422" s="21" t="s">
+      <c r="D422" s="21" t="s">
         <v>537</v>
       </c>
-      <c r="D422" s="21" t="s">
-        <v>538</v>
-      </c>
       <c r="E422" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2"/>
       <c r="B423" s="21" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C423" s="21"/>
       <c r="D423" s="21"/>
@@ -7804,7 +7801,7 @@
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2"/>
       <c r="B424" s="21" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C424" s="21"/>
       <c r="D424" s="21"/>
@@ -7813,7 +7810,7 @@
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2"/>
       <c r="B425" s="21" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C425" s="21"/>
       <c r="D425" s="21"/>
@@ -7822,7 +7819,7 @@
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2"/>
       <c r="B426" s="21" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C426" s="21"/>
       <c r="D426" s="21"/>
@@ -7831,7 +7828,7 @@
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2"/>
       <c r="B427" s="21" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C427" s="21"/>
       <c r="D427" s="21"/>
@@ -7840,7 +7837,7 @@
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2"/>
       <c r="B428" s="21" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C428" s="21"/>
       <c r="D428" s="21"/>
@@ -7849,7 +7846,7 @@
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="2"/>
       <c r="B429" s="21" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C429" s="21"/>
       <c r="D429" s="21"/>
@@ -7858,28 +7855,28 @@
     <row r="430" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="2"/>
       <c r="B430" s="21" t="s">
+        <v>545</v>
+      </c>
+      <c r="C430" s="21" t="s">
         <v>546</v>
       </c>
-      <c r="C430" s="21" t="s">
+      <c r="D430" s="21" t="s">
         <v>547</v>
       </c>
-      <c r="D430" s="21" t="s">
+      <c r="E430" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="E430" s="11" t="s">
+      <c r="F430" s="18" t="s">
         <v>549</v>
       </c>
-      <c r="F430" s="18" t="s">
+      <c r="G430" s="18" t="s">
         <v>550</v>
-      </c>
-      <c r="G430" s="18" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="2"/>
       <c r="B431" s="21" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C431" s="21"/>
       <c r="D431" s="21"/>
@@ -7888,7 +7885,7 @@
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2"/>
       <c r="B432" s="21" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C432" s="21"/>
       <c r="D432" s="21"/>
@@ -7897,7 +7894,7 @@
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="2"/>
       <c r="B433" s="21" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C433" s="21"/>
       <c r="D433" s="21"/>
@@ -7906,7 +7903,7 @@
     <row r="434" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="2"/>
       <c r="B434" s="21" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C434" s="21"/>
       <c r="D434" s="21"/>
@@ -7915,13 +7912,13 @@
     <row r="435" customFormat="false" ht="67.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="2"/>
       <c r="B435" s="21" t="s">
+        <v>555</v>
+      </c>
+      <c r="C435" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="C435" s="21" t="s">
+      <c r="D435" s="21" t="s">
         <v>557</v>
-      </c>
-      <c r="D435" s="21" t="s">
-        <v>558</v>
       </c>
       <c r="E435" s="11" t="s">
         <v>176</v>
@@ -7931,7 +7928,7 @@
     <row r="436" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2"/>
       <c r="B436" s="21" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C436" s="21"/>
       <c r="D436" s="21"/>
@@ -7940,7 +7937,7 @@
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2"/>
       <c r="B437" s="21" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C437" s="21"/>
       <c r="D437" s="21"/>
@@ -7949,7 +7946,7 @@
     <row r="438" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2"/>
       <c r="B438" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C438" s="21" t="s">
         <v>224</v>
@@ -7962,22 +7959,22 @@
     <row r="439" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="2"/>
       <c r="B439" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="C439" s="21" t="s">
+        <v>519</v>
+      </c>
+      <c r="D439" s="21" t="s">
         <v>562</v>
       </c>
-      <c r="C439" s="21" t="s">
-        <v>520</v>
-      </c>
-      <c r="D439" s="21" t="s">
-        <v>563</v>
-      </c>
       <c r="E439" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="2"/>
       <c r="B440" s="21" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C440" s="21"/>
       <c r="D440" s="21"/>
@@ -7986,7 +7983,7 @@
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="2"/>
       <c r="B441" s="21" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C441" s="21"/>
       <c r="D441" s="21"/>
@@ -7995,22 +7992,22 @@
     <row r="442" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2"/>
       <c r="B442" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="C442" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="C442" s="21" t="s">
+      <c r="D442" s="21" t="s">
         <v>567</v>
       </c>
-      <c r="D442" s="21" t="s">
-        <v>568</v>
-      </c>
       <c r="E442" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2"/>
       <c r="B443" s="21" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C443" s="21"/>
       <c r="D443" s="21"/>
@@ -8019,7 +8016,7 @@
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2"/>
       <c r="B444" s="21" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C444" s="21"/>
       <c r="D444" s="21"/>
@@ -8028,22 +8025,22 @@
     <row r="445" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2"/>
       <c r="B445" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="C445" s="21" t="s">
+        <v>536</v>
+      </c>
+      <c r="D445" s="21" t="s">
         <v>571</v>
       </c>
-      <c r="C445" s="21" t="s">
-        <v>537</v>
-      </c>
-      <c r="D445" s="21" t="s">
-        <v>572</v>
-      </c>
       <c r="E445" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2"/>
       <c r="B446" s="21" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C446" s="21"/>
       <c r="D446" s="21"/>
@@ -8058,10 +8055,10 @@
     </row>
     <row r="448" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B448" s="21" t="s">
         <v>574</v>
-      </c>
-      <c r="B448" s="21" t="s">
-        <v>575</v>
       </c>
       <c r="C448" s="21"/>
       <c r="D448" s="21"/>
@@ -8070,22 +8067,22 @@
     <row r="449" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="2"/>
       <c r="B449" s="21" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C449" s="21" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D449" s="21" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E449" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="2"/>
       <c r="B450" s="21" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C450" s="21"/>
       <c r="D450" s="21"/>
@@ -8101,7 +8098,7 @@
     <row r="452" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="6"/>
       <c r="B452" s="22" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C452" s="23"/>
       <c r="D452" s="23"/>
@@ -8118,7 +8115,7 @@
     <row r="454" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2"/>
       <c r="B454" s="21" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C454" s="21"/>
       <c r="D454" s="21"/>
@@ -8127,7 +8124,7 @@
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2"/>
       <c r="B455" s="21" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C455" s="21"/>
       <c r="D455" s="21"/>
@@ -8136,7 +8133,7 @@
     <row r="456" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2"/>
       <c r="B456" s="21" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C456" s="21"/>
       <c r="D456" s="21"/>
@@ -8145,7 +8142,7 @@
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2"/>
       <c r="B457" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C457" s="21"/>
       <c r="D457" s="21"/>
@@ -8154,16 +8151,16 @@
     <row r="458" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2"/>
       <c r="B458" s="21" t="s">
+        <v>581</v>
+      </c>
+      <c r="C458" s="21" t="s">
+        <v>536</v>
+      </c>
+      <c r="D458" s="21" t="s">
         <v>582</v>
       </c>
-      <c r="C458" s="21" t="s">
-        <v>537</v>
-      </c>
-      <c r="D458" s="21" t="s">
-        <v>583</v>
-      </c>
       <c r="E458" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8176,7 +8173,7 @@
     <row r="460" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="6"/>
       <c r="B460" s="22" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C460" s="23"/>
       <c r="D460" s="23"/>
@@ -8193,7 +8190,7 @@
     <row r="462" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="2"/>
       <c r="B462" s="21" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C462" s="21"/>
       <c r="D462" s="21"/>
@@ -8202,7 +8199,7 @@
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2"/>
       <c r="B463" s="21" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C463" s="21"/>
       <c r="D463" s="21"/>
@@ -8211,10 +8208,10 @@
     <row r="464" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2"/>
       <c r="B464" s="21" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C464" s="21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D464" s="21"/>
       <c r="E464" s="11"/>
@@ -8222,10 +8219,10 @@
     <row r="465" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2"/>
       <c r="B465" s="21" t="s">
+        <v>587</v>
+      </c>
+      <c r="C465" s="21" t="s">
         <v>588</v>
-      </c>
-      <c r="C465" s="21" t="s">
-        <v>589</v>
       </c>
       <c r="D465" s="21"/>
       <c r="E465" s="11"/>
@@ -8233,10 +8230,10 @@
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2"/>
       <c r="B466" s="21" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C466" s="21" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D466" s="21"/>
       <c r="E466" s="11"/>
@@ -8244,13 +8241,13 @@
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2"/>
       <c r="B467" s="21" t="s">
+        <v>590</v>
+      </c>
+      <c r="C467" s="21" t="s">
         <v>591</v>
       </c>
-      <c r="C467" s="21" t="s">
+      <c r="D467" s="21" t="s">
         <v>592</v>
-      </c>
-      <c r="D467" s="21" t="s">
-        <v>593</v>
       </c>
       <c r="E467" s="11" t="s">
         <v>24</v>
@@ -8259,22 +8256,22 @@
     <row r="468" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2"/>
       <c r="B468" s="21" t="s">
+        <v>593</v>
+      </c>
+      <c r="C468" s="21" t="s">
         <v>594</v>
       </c>
-      <c r="C468" s="21" t="s">
+      <c r="D468" s="21" t="s">
         <v>595</v>
       </c>
-      <c r="D468" s="21" t="s">
-        <v>596</v>
-      </c>
       <c r="E468" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="469" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="2"/>
       <c r="B469" s="21" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C469" s="21"/>
       <c r="D469" s="21"/>
@@ -8290,17 +8287,17 @@
     <row r="471" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="6"/>
       <c r="B471" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C471" s="23"/>
       <c r="D471" s="23" t="s">
+        <v>598</v>
+      </c>
+      <c r="E471" s="23" t="s">
+        <v>490</v>
+      </c>
+      <c r="F471" s="18" t="s">
         <v>599</v>
-      </c>
-      <c r="E471" s="23" t="s">
-        <v>491</v>
-      </c>
-      <c r="F471" s="18" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8315,7 +8312,7 @@
     <row r="473" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2"/>
       <c r="B473" s="21" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C473" s="21"/>
       <c r="D473" s="21"/>
@@ -8324,25 +8321,25 @@
     <row r="474" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="2"/>
       <c r="B474" s="21" t="s">
+        <v>601</v>
+      </c>
+      <c r="C474" s="21" t="s">
+        <v>509</v>
+      </c>
+      <c r="D474" s="21" t="s">
         <v>602</v>
       </c>
-      <c r="C474" s="21" t="s">
-        <v>510</v>
-      </c>
-      <c r="D474" s="21" t="s">
+      <c r="E474" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="E474" s="11" t="s">
+      <c r="F474" s="18" t="s">
         <v>604</v>
-      </c>
-      <c r="F474" s="18" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="475" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="2"/>
       <c r="B475" s="21" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C475" s="21"/>
       <c r="D475" s="21"/>
@@ -8351,7 +8348,7 @@
     <row r="476" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2"/>
       <c r="B476" s="21" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C476" s="21"/>
       <c r="D476" s="21"/>
@@ -8360,7 +8357,7 @@
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2"/>
       <c r="B477" s="21" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C477" s="21"/>
       <c r="D477" s="21"/>
@@ -8369,10 +8366,10 @@
     <row r="478" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2"/>
       <c r="B478" s="21" t="s">
+        <v>608</v>
+      </c>
+      <c r="C478" s="21" t="s">
         <v>609</v>
-      </c>
-      <c r="C478" s="21" t="s">
-        <v>610</v>
       </c>
       <c r="D478" s="21"/>
       <c r="E478" s="11"/>
@@ -8380,13 +8377,13 @@
     <row r="479" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="2"/>
       <c r="B479" s="21" t="s">
+        <v>610</v>
+      </c>
+      <c r="C479" s="21" t="s">
         <v>611</v>
       </c>
-      <c r="C479" s="21" t="s">
+      <c r="D479" s="21" t="s">
         <v>612</v>
-      </c>
-      <c r="D479" s="21" t="s">
-        <v>613</v>
       </c>
       <c r="E479" s="11" t="s">
         <v>176</v>
@@ -8401,10 +8398,10 @@
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B481" s="21" t="s">
         <v>614</v>
-      </c>
-      <c r="B481" s="21" t="s">
-        <v>615</v>
       </c>
       <c r="C481" s="21"/>
       <c r="D481" s="21"/>
@@ -8413,7 +8410,7 @@
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2"/>
       <c r="B482" s="21" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C482" s="21"/>
       <c r="D482" s="21"/>
@@ -8429,7 +8426,7 @@
     <row r="484" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2"/>
       <c r="B484" s="21" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C484" s="21"/>
       <c r="D484" s="21"/>
@@ -8438,7 +8435,7 @@
     <row r="485" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2"/>
       <c r="B485" s="21" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C485" s="21"/>
       <c r="D485" s="21"/>
@@ -8454,14 +8451,14 @@
     <row r="487" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="6"/>
       <c r="B487" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C487" s="23"/>
       <c r="D487" s="23" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E487" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8476,7 +8473,7 @@
     <row r="489" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="2"/>
       <c r="B489" s="21" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C489" s="21"/>
       <c r="D489" s="21"/>
@@ -8485,35 +8482,35 @@
     <row r="490" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="2"/>
       <c r="B490" s="21" t="s">
+        <v>621</v>
+      </c>
+      <c r="C490" s="21" t="s">
         <v>622</v>
       </c>
-      <c r="C490" s="21" t="s">
+      <c r="D490" s="21" t="s">
         <v>623</v>
       </c>
-      <c r="D490" s="21" t="s">
-        <v>624</v>
-      </c>
       <c r="E490" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="491" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="2"/>
       <c r="B491" s="21" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C491" s="21"/>
       <c r="D491" s="21" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E491" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2"/>
       <c r="B492" s="21" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C492" s="21"/>
       <c r="D492" s="21"/>
@@ -8522,7 +8519,7 @@
     <row r="493" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2"/>
       <c r="B493" s="21" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C493" s="21" t="s">
         <v>276</v>
@@ -8534,13 +8531,13 @@
         <v>176</v>
       </c>
       <c r="F493" s="18" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2"/>
       <c r="B494" s="21" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C494" s="21"/>
       <c r="D494" s="21"/>
@@ -8549,7 +8546,7 @@
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2"/>
       <c r="B495" s="21" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C495" s="21"/>
       <c r="D495" s="21"/>
@@ -8558,7 +8555,7 @@
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2"/>
       <c r="B496" s="21" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C496" s="21"/>
       <c r="D496" s="21"/>
@@ -8567,7 +8564,7 @@
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2"/>
       <c r="B497" s="21" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C497" s="21"/>
       <c r="D497" s="21"/>
@@ -8576,7 +8573,7 @@
     <row r="498" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="2"/>
       <c r="B498" s="21" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C498" s="21"/>
       <c r="D498" s="21"/>
@@ -8585,7 +8582,7 @@
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="2"/>
       <c r="B499" s="21" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C499" s="21"/>
       <c r="D499" s="21"/>
@@ -8594,7 +8591,7 @@
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="2"/>
       <c r="B500" s="21" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C500" s="21"/>
       <c r="D500" s="21"/>
@@ -8603,31 +8600,31 @@
     <row r="501" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="2"/>
       <c r="B501" s="21" t="s">
+        <v>636</v>
+      </c>
+      <c r="C501" s="21" t="s">
         <v>637</v>
       </c>
-      <c r="C501" s="21" t="s">
+      <c r="D501" s="21" t="s">
         <v>638</v>
       </c>
-      <c r="D501" s="21" t="s">
-        <v>639</v>
-      </c>
       <c r="E501" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="502" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="2"/>
       <c r="B502" s="21" t="s">
+        <v>639</v>
+      </c>
+      <c r="C502" s="21" t="s">
         <v>640</v>
       </c>
-      <c r="C502" s="21" t="s">
+      <c r="D502" s="21" t="s">
         <v>641</v>
       </c>
-      <c r="D502" s="21" t="s">
+      <c r="E502" s="11" t="s">
         <v>642</v>
-      </c>
-      <c r="E502" s="11" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8642,7 +8639,7 @@
         <v>236</v>
       </c>
       <c r="B504" s="21" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C504" s="21"/>
       <c r="D504" s="21"/>
@@ -8651,7 +8648,7 @@
     <row r="505" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="2"/>
       <c r="B505" s="21" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C505" s="21"/>
       <c r="D505" s="21"/>
@@ -8660,7 +8657,7 @@
     <row r="506" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="2"/>
       <c r="B506" s="21" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C506" s="21"/>
       <c r="D506" s="21"/>
@@ -8669,7 +8666,7 @@
     <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="2"/>
       <c r="B507" s="21" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C507" s="21"/>
       <c r="D507" s="21"/>
@@ -8678,22 +8675,22 @@
     <row r="508" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="2"/>
       <c r="B508" s="21" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C508" s="21" t="s">
+        <v>640</v>
+      </c>
+      <c r="D508" s="21" t="s">
         <v>641</v>
       </c>
-      <c r="D508" s="21" t="s">
+      <c r="E508" s="11" t="s">
         <v>642</v>
-      </c>
-      <c r="E508" s="11" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="2"/>
       <c r="B509" s="21" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C509" s="21"/>
       <c r="D509" s="21"/>
@@ -8702,7 +8699,7 @@
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="2"/>
       <c r="B510" s="21" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C510" s="21"/>
       <c r="D510" s="21"/>
@@ -8711,7 +8708,7 @@
     <row r="511" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="2"/>
       <c r="B511" s="21" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C511" s="21"/>
       <c r="D511" s="21"/>
@@ -8720,7 +8717,7 @@
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="2"/>
       <c r="B512" s="21" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C512" s="21"/>
       <c r="D512" s="21"/>
@@ -8729,10 +8726,10 @@
     <row r="513" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2"/>
       <c r="B513" s="21" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C513" s="21" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D513" s="21"/>
       <c r="E513" s="11"/>
@@ -8740,7 +8737,7 @@
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="2"/>
       <c r="B514" s="21" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C514" s="21"/>
       <c r="D514" s="21"/>
@@ -8749,7 +8746,7 @@
     <row r="515" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="2"/>
       <c r="B515" s="21" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C515" s="21"/>
       <c r="D515" s="21"/>
@@ -8758,7 +8755,7 @@
     <row r="516" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="2"/>
       <c r="B516" s="21" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C516" s="21"/>
       <c r="D516" s="21"/>
@@ -8767,7 +8764,7 @@
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="2"/>
       <c r="B517" s="21" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C517" s="21"/>
       <c r="D517" s="21"/>
@@ -8776,7 +8773,7 @@
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="2"/>
       <c r="B518" s="21" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C518" s="21"/>
       <c r="D518" s="21"/>
@@ -8785,7 +8782,7 @@
     <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="2"/>
       <c r="B519" s="21" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C519" s="21"/>
       <c r="D519" s="21"/>
@@ -8794,28 +8791,28 @@
     <row r="520" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="2"/>
       <c r="B520" s="21" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C520" s="21" t="s">
         <v>276</v>
       </c>
       <c r="D520" s="21" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E520" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="2"/>
       <c r="B521" s="21" t="s">
+        <v>661</v>
+      </c>
+      <c r="C521" s="21" t="s">
         <v>662</v>
       </c>
-      <c r="C521" s="21" t="s">
+      <c r="D521" s="21" t="s">
         <v>663</v>
-      </c>
-      <c r="D521" s="21" t="s">
-        <v>664</v>
       </c>
       <c r="E521" s="11" t="s">
         <v>176</v>
@@ -8824,7 +8821,7 @@
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="2"/>
       <c r="B522" s="21" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C522" s="21"/>
       <c r="D522" s="21"/>
@@ -8839,10 +8836,10 @@
     </row>
     <row r="524" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B524" s="21" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C524" s="21"/>
       <c r="D524" s="21"/>
@@ -8851,7 +8848,7 @@
     <row r="525" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2"/>
       <c r="B525" s="21" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C525" s="21"/>
       <c r="D525" s="21"/>
@@ -8860,7 +8857,7 @@
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2"/>
       <c r="B526" s="21" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C526" s="21"/>
       <c r="D526" s="21"/>
@@ -8869,16 +8866,16 @@
     <row r="527" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2"/>
       <c r="B527" s="21" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C527" s="21" t="s">
+        <v>640</v>
+      </c>
+      <c r="D527" s="21" t="s">
         <v>641</v>
       </c>
-      <c r="D527" s="21" t="s">
+      <c r="E527" s="11" t="s">
         <v>642</v>
-      </c>
-      <c r="E527" s="11" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8891,7 +8888,7 @@
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="2"/>
       <c r="B529" s="21" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C529" s="21"/>
       <c r="D529" s="21"/>
@@ -8900,7 +8897,7 @@
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="32"/>
       <c r="B530" s="33" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C530" s="33"/>
       <c r="D530" s="33"/>
